--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC810AC4-8CE7-4614-A379-810F4A2EA79C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DAEC4D2-E15E-43F7-B61C-1EA9AD721D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="112">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -305,6 +305,60 @@
   <si>
     <t>Acc Adress</t>
   </si>
+  <si>
+    <t>Gourmet Food Davis Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Shadman </t>
+  </si>
+  <si>
+    <t>Gourmet Food Rehmanpura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food 18-Gulshan </t>
+  </si>
+  <si>
+    <t>Gourmet Food Nisbat Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Jinah Hospital </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Shama </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food C Block </t>
+  </si>
+  <si>
+    <t>Gourmet Food Nadeem Shaheed Road</t>
+  </si>
+  <si>
+    <t>Gourmet Food Firdos Market</t>
+  </si>
+  <si>
+    <t>Gourmet Food Link Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Neelam Cenema </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Shadbagh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Railway Plaza </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food kot abdul malik </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Shadra Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Kareem Park </t>
+  </si>
+  <si>
+    <t>Gourmet Food Imamia Colony</t>
+  </si>
 </sst>
 </file>
 
@@ -1585,6 +1639,45 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1619,45 +1712,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2279,13 +2333,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="149">
+      <c r="B1" s="162">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
-      </c>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
+        <v>46297</v>
+      </c>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2307,10 +2361,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="171" t="s">
+      <c r="A2" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="150" t="s">
+      <c r="B2" s="163" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2340,13 +2394,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="163"/>
-      <c r="M2" s="164"/>
-      <c r="N2" s="165"/>
-      <c r="O2" s="166" t="s">
+      <c r="L2" s="151"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="153"/>
+      <c r="O2" s="154" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="167"/>
+      <c r="P2" s="155"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2365,8 +2419,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="171"/>
-      <c r="B3" s="151"/>
+      <c r="A3" s="159"/>
+      <c r="B3" s="164"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2394,29 +2448,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="168" t="s">
+      <c r="L3" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="169"/>
-      <c r="N3" s="170"/>
+      <c r="M3" s="157"/>
+      <c r="N3" s="158"/>
       <c r="O3" s="65"/>
       <c r="P3" s="66"/>
-      <c r="Q3" s="153" t="s">
+      <c r="Q3" s="166" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="154"/>
-      <c r="S3" s="154"/>
-      <c r="T3" s="155"/>
-      <c r="U3" s="156" t="s">
+      <c r="R3" s="167"/>
+      <c r="S3" s="167"/>
+      <c r="T3" s="168"/>
+      <c r="U3" s="169" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="157"/>
-      <c r="W3" s="157"/>
-      <c r="X3" s="158"/>
+      <c r="V3" s="170"/>
+      <c r="W3" s="170"/>
+      <c r="X3" s="171"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="171"/>
-      <c r="B4" s="152"/>
+      <c r="A4" s="159"/>
+      <c r="B4" s="165"/>
       <c r="C4" s="139" t="s">
         <v>90</v>
       </c>
@@ -2485,32 +2539,46 @@
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A5" s="72"/>
+      <c r="A5" s="72">
+        <v>46296</v>
+      </c>
       <c r="B5" s="127">
         <v>1</v>
       </c>
-      <c r="C5" s="140"/>
+      <c r="C5" s="140" t="s">
+        <v>94</v>
+      </c>
       <c r="D5" s="140"/>
       <c r="E5" s="129"/>
-      <c r="F5" s="129"/>
+      <c r="F5" s="129">
+        <v>30</v>
+      </c>
       <c r="G5" s="128"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="129"/>
-      <c r="J5" s="128"/>
+      <c r="H5" s="32">
+        <v>40</v>
+      </c>
+      <c r="I5" s="129">
+        <v>20</v>
+      </c>
+      <c r="J5" s="128">
+        <v>20</v>
+      </c>
       <c r="K5" s="130"/>
       <c r="L5" s="31">
         <f t="shared" ref="L5:L36" si="0">SUM(E5:K5)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M5" s="33"/>
+        <v>2.75</v>
+      </c>
+      <c r="M5" s="33">
+        <v>18</v>
+      </c>
       <c r="N5" s="32"/>
       <c r="O5" s="67">
         <f>SUM(F5:H5)/20</f>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P5" s="34">
         <f>SUM(I5:K5)/20</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="35" t="e">
         <f t="shared" ref="Q5:Q46" si="1">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
@@ -2546,32 +2614,42 @@
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A6" s="72"/>
+      <c r="A6" s="72">
+        <v>46296</v>
+      </c>
       <c r="B6" s="41">
         <v>2</v>
       </c>
-      <c r="C6" s="140"/>
+      <c r="C6" s="140" t="s">
+        <v>95</v>
+      </c>
       <c r="D6" s="140"/>
       <c r="E6" s="44"/>
       <c r="F6" s="44"/>
       <c r="G6" s="69"/>
-      <c r="H6" s="43"/>
+      <c r="H6" s="43">
+        <v>40</v>
+      </c>
       <c r="I6" s="44"/>
       <c r="J6" s="69"/>
-      <c r="K6" s="70"/>
+      <c r="K6" s="70">
+        <v>20</v>
+      </c>
       <c r="L6" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M6" s="33"/>
+        <v>1.5</v>
+      </c>
+      <c r="M6" s="33">
+        <v>18</v>
+      </c>
       <c r="N6" s="43"/>
       <c r="O6" s="67">
         <f t="shared" ref="O6" si="3">SUM(F6:H6)/20</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P6" s="34">
         <f t="shared" ref="P6" si="4">SUM(I6:K6)/20</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="45" t="e">
         <f t="shared" si="1"/>
@@ -2607,32 +2685,44 @@
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A7" s="72"/>
+      <c r="A7" s="72">
+        <v>46296</v>
+      </c>
       <c r="B7" s="41">
         <v>3</v>
       </c>
-      <c r="C7" s="140"/>
+      <c r="C7" s="140" t="s">
+        <v>96</v>
+      </c>
       <c r="D7" s="140"/>
       <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="69"/>
+      <c r="F7" s="44">
+        <v>30</v>
+      </c>
+      <c r="G7" s="69">
+        <v>40</v>
+      </c>
       <c r="H7" s="43"/>
-      <c r="I7" s="44"/>
+      <c r="I7" s="44">
+        <v>20</v>
+      </c>
       <c r="J7" s="69"/>
       <c r="K7" s="70"/>
       <c r="L7" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="33"/>
+        <v>2.25</v>
+      </c>
+      <c r="M7" s="33">
+        <v>18</v>
+      </c>
       <c r="N7" s="43"/>
       <c r="O7" s="67">
         <f t="shared" ref="O7:O15" si="11">SUM(F7:H7)/20</f>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7" s="34">
         <f t="shared" ref="P7:P15" si="12">SUM(I7:K7)/20</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="45" t="e">
         <f t="shared" si="1"/>
@@ -2668,32 +2758,46 @@
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A8" s="72"/>
+      <c r="A8" s="72">
+        <v>46296</v>
+      </c>
       <c r="B8" s="41">
         <v>4</v>
       </c>
-      <c r="C8" s="140"/>
+      <c r="C8" s="140" t="s">
+        <v>97</v>
+      </c>
       <c r="D8" s="140"/>
       <c r="E8" s="44"/>
       <c r="F8" s="44"/>
       <c r="G8" s="69"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="70"/>
+      <c r="H8" s="43">
+        <v>30</v>
+      </c>
+      <c r="I8" s="44">
+        <v>20</v>
+      </c>
+      <c r="J8" s="69">
+        <v>20</v>
+      </c>
+      <c r="K8" s="70">
+        <v>20</v>
+      </c>
       <c r="L8" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="33"/>
+        <v>2.25</v>
+      </c>
+      <c r="M8" s="33">
+        <v>18</v>
+      </c>
       <c r="N8" s="43"/>
       <c r="O8" s="67">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P8" s="34">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="45" t="e">
         <f t="shared" si="1"/>
@@ -2729,32 +2833,50 @@
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A9" s="72"/>
+      <c r="A9" s="72">
+        <v>46296</v>
+      </c>
       <c r="B9" s="41">
         <v>5</v>
       </c>
-      <c r="C9" s="140"/>
+      <c r="C9" s="140" t="s">
+        <v>98</v>
+      </c>
       <c r="D9" s="140"/>
       <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="70"/>
+      <c r="F9" s="44">
+        <v>40</v>
+      </c>
+      <c r="G9" s="69">
+        <v>40</v>
+      </c>
+      <c r="H9" s="43">
+        <v>40</v>
+      </c>
+      <c r="I9" s="44">
+        <v>20</v>
+      </c>
+      <c r="J9" s="69">
+        <v>20</v>
+      </c>
+      <c r="K9" s="70">
+        <v>20</v>
+      </c>
       <c r="L9" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="33"/>
+        <v>4.5</v>
+      </c>
+      <c r="M9" s="33">
+        <v>18</v>
+      </c>
       <c r="N9" s="43"/>
       <c r="O9" s="67">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P9" s="34">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q9" s="45" t="e">
         <f t="shared" si="1"/>
@@ -2790,32 +2912,50 @@
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A10" s="72"/>
+      <c r="A10" s="72">
+        <v>46296</v>
+      </c>
       <c r="B10" s="41">
         <v>6</v>
       </c>
-      <c r="C10" s="140"/>
+      <c r="C10" s="140" t="s">
+        <v>99</v>
+      </c>
       <c r="D10" s="140"/>
       <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="69"/>
-      <c r="K10" s="70"/>
+      <c r="F10" s="44">
+        <v>40</v>
+      </c>
+      <c r="G10" s="69">
+        <v>40</v>
+      </c>
+      <c r="H10" s="43">
+        <v>25</v>
+      </c>
+      <c r="I10" s="44">
+        <v>20</v>
+      </c>
+      <c r="J10" s="69">
+        <v>20</v>
+      </c>
+      <c r="K10" s="70">
+        <v>20</v>
+      </c>
       <c r="L10" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="33"/>
+        <v>4.125</v>
+      </c>
+      <c r="M10" s="33">
+        <v>18</v>
+      </c>
       <c r="N10" s="43"/>
       <c r="O10" s="67">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P10" s="34">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="45" t="e">
         <f t="shared" si="1"/>
@@ -2851,28 +2991,40 @@
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A11" s="72"/>
+      <c r="A11" s="72">
+        <v>46296</v>
+      </c>
       <c r="B11" s="41">
         <v>7</v>
       </c>
-      <c r="C11" s="140"/>
+      <c r="C11" s="140" t="s">
+        <v>100</v>
+      </c>
       <c r="D11" s="140"/>
       <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="43"/>
+      <c r="F11" s="44">
+        <v>40</v>
+      </c>
+      <c r="G11" s="69">
+        <v>40</v>
+      </c>
+      <c r="H11" s="43">
+        <v>40</v>
+      </c>
       <c r="I11" s="44"/>
       <c r="J11" s="69"/>
       <c r="K11" s="70"/>
       <c r="L11" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="33"/>
+        <v>3</v>
+      </c>
+      <c r="M11" s="33">
+        <v>18</v>
+      </c>
       <c r="N11" s="43"/>
       <c r="O11" s="67">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P11" s="34">
         <f t="shared" si="12"/>
@@ -2912,32 +3064,44 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A12" s="72"/>
+      <c r="A12" s="72">
+        <v>46296</v>
+      </c>
       <c r="B12" s="41">
         <v>8</v>
       </c>
-      <c r="C12" s="140"/>
+      <c r="C12" s="140" t="s">
+        <v>101</v>
+      </c>
       <c r="D12" s="140"/>
       <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="69"/>
+      <c r="F12" s="44">
+        <v>30</v>
+      </c>
+      <c r="G12" s="69">
+        <v>40</v>
+      </c>
       <c r="H12" s="43"/>
-      <c r="I12" s="44"/>
+      <c r="I12" s="44">
+        <v>20</v>
+      </c>
       <c r="J12" s="69"/>
       <c r="K12" s="70"/>
       <c r="L12" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="33"/>
+        <v>2.25</v>
+      </c>
+      <c r="M12" s="33">
+        <v>18</v>
+      </c>
       <c r="N12" s="43"/>
       <c r="O12" s="67">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P12" s="34">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="45" t="e">
         <f t="shared" si="1"/>
@@ -2973,32 +3137,50 @@
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A13" s="72"/>
+      <c r="A13" s="72">
+        <v>46296</v>
+      </c>
       <c r="B13" s="41">
         <v>9</v>
       </c>
-      <c r="C13" s="140"/>
+      <c r="C13" s="140" t="s">
+        <v>102</v>
+      </c>
       <c r="D13" s="140"/>
       <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="69"/>
-      <c r="K13" s="70"/>
+      <c r="F13" s="44">
+        <v>40</v>
+      </c>
+      <c r="G13" s="69">
+        <v>30</v>
+      </c>
+      <c r="H13" s="43">
+        <v>40</v>
+      </c>
+      <c r="I13" s="44">
+        <v>20</v>
+      </c>
+      <c r="J13" s="69">
+        <v>20</v>
+      </c>
+      <c r="K13" s="70">
+        <v>20</v>
+      </c>
       <c r="L13" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="33"/>
+        <v>4.25</v>
+      </c>
+      <c r="M13" s="33">
+        <v>18</v>
+      </c>
       <c r="N13" s="43"/>
       <c r="O13" s="67">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P13" s="34">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q13" s="45" t="e">
         <f t="shared" si="1"/>
@@ -3034,32 +3216,46 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A14" s="72"/>
+      <c r="A14" s="72">
+        <v>46296</v>
+      </c>
       <c r="B14" s="41">
         <v>10</v>
       </c>
-      <c r="C14" s="140"/>
+      <c r="C14" s="140" t="s">
+        <v>103</v>
+      </c>
       <c r="D14" s="140"/>
       <c r="E14" s="44"/>
       <c r="F14" s="44"/>
-      <c r="G14" s="69"/>
+      <c r="G14" s="69">
+        <v>40</v>
+      </c>
       <c r="H14" s="43"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="70"/>
+      <c r="I14" s="44">
+        <v>20</v>
+      </c>
+      <c r="J14" s="69">
+        <v>20</v>
+      </c>
+      <c r="K14" s="70">
+        <v>20</v>
+      </c>
       <c r="L14" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="33"/>
+        <v>2.5</v>
+      </c>
+      <c r="M14" s="33">
+        <v>18</v>
+      </c>
       <c r="N14" s="43"/>
       <c r="O14" s="67">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P14" s="34">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q14" s="45" t="e">
         <f t="shared" si="1"/>
@@ -3095,32 +3291,48 @@
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A15" s="72"/>
+      <c r="A15" s="72">
+        <v>46296</v>
+      </c>
       <c r="B15" s="41">
         <v>11</v>
       </c>
-      <c r="C15" s="140"/>
+      <c r="C15" s="140" t="s">
+        <v>104</v>
+      </c>
       <c r="D15" s="140"/>
       <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="69"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="69"/>
+      <c r="F15" s="44">
+        <v>15</v>
+      </c>
+      <c r="G15" s="69">
+        <v>15</v>
+      </c>
+      <c r="H15" s="43">
+        <v>15</v>
+      </c>
+      <c r="I15" s="44">
+        <v>15</v>
+      </c>
+      <c r="J15" s="69">
+        <v>15</v>
+      </c>
       <c r="K15" s="70"/>
       <c r="L15" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="33"/>
+        <v>1.875</v>
+      </c>
+      <c r="M15" s="33">
+        <v>18</v>
+      </c>
       <c r="N15" s="43"/>
       <c r="O15" s="67">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P15" s="34">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q15" s="45" t="e">
         <f t="shared" si="1"/>
@@ -3156,32 +3368,48 @@
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A16" s="72"/>
+      <c r="A16" s="72">
+        <v>46296</v>
+      </c>
       <c r="B16" s="41">
         <v>12</v>
       </c>
-      <c r="C16" s="140"/>
+      <c r="C16" s="140" t="s">
+        <v>105</v>
+      </c>
       <c r="D16" s="140"/>
       <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="69"/>
+      <c r="F16" s="44">
+        <v>40</v>
+      </c>
+      <c r="G16" s="69">
+        <v>40</v>
+      </c>
+      <c r="H16" s="43">
+        <v>40</v>
+      </c>
+      <c r="I16" s="44">
+        <v>20</v>
+      </c>
+      <c r="J16" s="69">
+        <v>20</v>
+      </c>
       <c r="K16" s="70"/>
       <c r="L16" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="33"/>
+        <v>4</v>
+      </c>
+      <c r="M16" s="33">
+        <v>18</v>
+      </c>
       <c r="N16" s="43"/>
       <c r="O16" s="67">
         <f t="shared" ref="O16:O17" si="17">SUM(F16:H16)/20</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P16" s="34">
         <f t="shared" ref="P16:P17" si="18">SUM(I16:K16)/20</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="45" t="e">
         <f t="shared" si="1"/>
@@ -3217,32 +3445,46 @@
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A17" s="72"/>
+      <c r="A17" s="72">
+        <v>46296</v>
+      </c>
       <c r="B17" s="41">
         <v>13</v>
       </c>
-      <c r="C17" s="140"/>
+      <c r="C17" s="140" t="s">
+        <v>106</v>
+      </c>
       <c r="D17" s="140"/>
       <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
+      <c r="F17" s="44">
+        <v>40</v>
+      </c>
       <c r="G17" s="69"/>
       <c r="H17" s="43"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="70"/>
+      <c r="I17" s="44">
+        <v>20</v>
+      </c>
+      <c r="J17" s="69">
+        <v>20</v>
+      </c>
+      <c r="K17" s="70">
+        <v>20</v>
+      </c>
       <c r="L17" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="33"/>
+        <v>2.5</v>
+      </c>
+      <c r="M17" s="33">
+        <v>18</v>
+      </c>
       <c r="N17" s="43"/>
       <c r="O17" s="67">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P17" s="34">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="45" t="e">
         <f t="shared" si="1"/>
@@ -3278,32 +3520,44 @@
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A18" s="72"/>
+      <c r="A18" s="72">
+        <v>46296</v>
+      </c>
       <c r="B18" s="41">
         <v>14</v>
       </c>
-      <c r="C18" s="140"/>
+      <c r="C18" s="140" t="s">
+        <v>107</v>
+      </c>
       <c r="D18" s="140"/>
       <c r="E18" s="44"/>
       <c r="F18" s="44"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="44"/>
+      <c r="G18" s="69">
+        <v>30</v>
+      </c>
+      <c r="H18" s="43">
+        <v>30</v>
+      </c>
+      <c r="I18" s="44">
+        <v>20</v>
+      </c>
       <c r="J18" s="69"/>
       <c r="K18" s="70"/>
       <c r="L18" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="33"/>
+        <v>2</v>
+      </c>
+      <c r="M18" s="33">
+        <v>18</v>
+      </c>
       <c r="N18" s="43"/>
       <c r="O18" s="67">
         <f t="shared" ref="O18:O20" si="23">SUM(F18:H18)/20</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P18" s="34">
         <f t="shared" ref="P18:P20" si="24">SUM(I18:K18)/20</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="45" t="e">
         <f t="shared" si="1"/>
@@ -3339,32 +3593,44 @@
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A19" s="72"/>
+      <c r="A19" s="72">
+        <v>46296</v>
+      </c>
       <c r="B19" s="41">
         <v>15</v>
       </c>
-      <c r="C19" s="140"/>
+      <c r="C19" s="140" t="s">
+        <v>108</v>
+      </c>
       <c r="D19" s="140"/>
       <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
+      <c r="F19" s="44">
+        <v>40</v>
+      </c>
       <c r="G19" s="69"/>
       <c r="H19" s="43"/>
-      <c r="I19" s="44"/>
+      <c r="I19" s="44">
+        <v>20</v>
+      </c>
       <c r="J19" s="69"/>
-      <c r="K19" s="70"/>
+      <c r="K19" s="70">
+        <v>20</v>
+      </c>
       <c r="L19" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="33"/>
+        <v>2</v>
+      </c>
+      <c r="M19" s="33">
+        <v>18</v>
+      </c>
       <c r="N19" s="43"/>
       <c r="O19" s="67">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P19" s="34">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="45" t="e">
         <f t="shared" si="1"/>
@@ -3400,32 +3666,48 @@
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A20" s="72"/>
+      <c r="A20" s="72">
+        <v>46296</v>
+      </c>
       <c r="B20" s="41">
         <v>16</v>
       </c>
-      <c r="C20" s="140"/>
+      <c r="C20" s="140" t="s">
+        <v>109</v>
+      </c>
       <c r="D20" s="140"/>
       <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
+      <c r="F20" s="44">
+        <v>40</v>
+      </c>
       <c r="G20" s="69"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="69"/>
-      <c r="K20" s="70"/>
+      <c r="H20" s="43">
+        <v>40</v>
+      </c>
+      <c r="I20" s="44">
+        <v>20</v>
+      </c>
+      <c r="J20" s="69">
+        <v>20</v>
+      </c>
+      <c r="K20" s="70">
+        <v>20</v>
+      </c>
       <c r="L20" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="33"/>
+        <v>3.5</v>
+      </c>
+      <c r="M20" s="33">
+        <v>18</v>
+      </c>
       <c r="N20" s="43"/>
       <c r="O20" s="67">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P20" s="34">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="45" t="e">
         <f t="shared" si="1"/>
@@ -3461,32 +3743,44 @@
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A21" s="72"/>
+      <c r="A21" s="72">
+        <v>46296</v>
+      </c>
       <c r="B21" s="41">
         <v>17</v>
       </c>
-      <c r="C21" s="140"/>
+      <c r="C21" s="140" t="s">
+        <v>110</v>
+      </c>
       <c r="D21" s="140"/>
       <c r="E21" s="44"/>
       <c r="F21" s="44"/>
       <c r="G21" s="69"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="44"/>
+      <c r="H21" s="43">
+        <v>40</v>
+      </c>
+      <c r="I21" s="44">
+        <v>20</v>
+      </c>
       <c r="J21" s="69"/>
-      <c r="K21" s="70"/>
+      <c r="K21" s="70">
+        <v>20</v>
+      </c>
       <c r="L21" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="33"/>
+        <v>2</v>
+      </c>
+      <c r="M21" s="33">
+        <v>18</v>
+      </c>
       <c r="N21" s="43"/>
       <c r="O21" s="67">
         <f t="shared" ref="O21:O23" si="29">SUM(F21:H21)/20</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P21" s="34">
         <f t="shared" ref="P21:P23" si="30">SUM(I21:K21)/20</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="45" t="e">
         <f t="shared" si="1"/>
@@ -3522,32 +3816,46 @@
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A22" s="72"/>
+      <c r="A22" s="72">
+        <v>46296</v>
+      </c>
       <c r="B22" s="41">
         <v>18</v>
       </c>
-      <c r="C22" s="140"/>
+      <c r="C22" s="140" t="s">
+        <v>111</v>
+      </c>
       <c r="D22" s="140"/>
       <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="43"/>
+      <c r="F22" s="44">
+        <v>40</v>
+      </c>
+      <c r="G22" s="69">
+        <v>40</v>
+      </c>
+      <c r="H22" s="43">
+        <v>40</v>
+      </c>
       <c r="I22" s="44"/>
       <c r="J22" s="69"/>
-      <c r="K22" s="70"/>
+      <c r="K22" s="70">
+        <v>20</v>
+      </c>
       <c r="L22" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="33"/>
+        <v>3.5</v>
+      </c>
+      <c r="M22" s="33">
+        <v>18</v>
+      </c>
       <c r="N22" s="43"/>
       <c r="O22" s="67">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P22" s="34">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="45" t="e">
         <f t="shared" si="1"/>
@@ -4274,7 +4582,7 @@
       <c r="M34" s="33"/>
       <c r="N34" s="43">
         <f t="shared" ref="N34:N65" si="52">SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O34" s="67">
         <f t="shared" ref="O34:O47" si="53">SUM(F34:H34)/20</f>
@@ -4338,7 +4646,7 @@
       <c r="M35" s="33"/>
       <c r="N35" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O35" s="67">
         <f t="shared" ref="O35" si="59">SUM(F35:H35)/20</f>
@@ -4402,7 +4710,7 @@
       <c r="M36" s="33"/>
       <c r="N36" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O36" s="67">
         <f t="shared" si="53"/>
@@ -4466,7 +4774,7 @@
       <c r="M37" s="33"/>
       <c r="N37" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O37" s="67">
         <f t="shared" si="53"/>
@@ -4530,7 +4838,7 @@
       <c r="M38" s="33"/>
       <c r="N38" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O38" s="67">
         <f t="shared" si="53"/>
@@ -4594,7 +4902,7 @@
       <c r="M39" s="33"/>
       <c r="N39" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O39" s="67">
         <f t="shared" si="53"/>
@@ -4658,7 +4966,7 @@
       <c r="M40" s="33"/>
       <c r="N40" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O40" s="67">
         <f t="shared" si="53"/>
@@ -4722,7 +5030,7 @@
       <c r="M41" s="33"/>
       <c r="N41" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O41" s="67">
         <f t="shared" si="53"/>
@@ -4786,7 +5094,7 @@
       <c r="M42" s="33"/>
       <c r="N42" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O42" s="67">
         <f t="shared" si="53"/>
@@ -4850,7 +5158,7 @@
       <c r="M43" s="33"/>
       <c r="N43" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O43" s="67">
         <f t="shared" si="53"/>
@@ -4914,7 +5222,7 @@
       <c r="M44" s="33"/>
       <c r="N44" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O44" s="67">
         <f t="shared" si="53"/>
@@ -4978,7 +5286,7 @@
       <c r="M45" s="33"/>
       <c r="N45" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O45" s="67">
         <f t="shared" si="53"/>
@@ -5042,7 +5350,7 @@
       <c r="M46" s="33"/>
       <c r="N46" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O46" s="67">
         <f t="shared" si="53"/>
@@ -5106,7 +5414,7 @@
       <c r="M47" s="33"/>
       <c r="N47" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O47" s="67">
         <f t="shared" si="53"/>
@@ -5152,7 +5460,7 @@
       <c r="M48" s="33"/>
       <c r="N48" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O48" s="67">
         <f t="shared" ref="O48:O60" si="66">SUM(F48:H48)/20</f>
@@ -5198,7 +5506,7 @@
       <c r="M49" s="33"/>
       <c r="N49" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O49" s="67">
         <f t="shared" si="66"/>
@@ -5244,7 +5552,7 @@
       <c r="M50" s="33"/>
       <c r="N50" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O50" s="67">
         <f t="shared" si="66"/>
@@ -5290,7 +5598,7 @@
       <c r="M51" s="33"/>
       <c r="N51" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O51" s="67">
         <f t="shared" si="66"/>
@@ -5336,7 +5644,7 @@
       <c r="M52" s="33"/>
       <c r="N52" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O52" s="67">
         <f t="shared" si="66"/>
@@ -5382,7 +5690,7 @@
       <c r="M53" s="33"/>
       <c r="N53" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O53" s="67">
         <f t="shared" si="66"/>
@@ -5428,7 +5736,7 @@
       <c r="M54" s="33"/>
       <c r="N54" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O54" s="67">
         <f t="shared" si="66"/>
@@ -5474,7 +5782,7 @@
       <c r="M55" s="33"/>
       <c r="N55" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O55" s="67">
         <f t="shared" si="66"/>
@@ -5520,7 +5828,7 @@
       <c r="M56" s="33"/>
       <c r="N56" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O56" s="67">
         <f t="shared" si="66"/>
@@ -5566,7 +5874,7 @@
       <c r="M57" s="33"/>
       <c r="N57" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O57" s="67">
         <f t="shared" si="66"/>
@@ -5612,7 +5920,7 @@
       <c r="M58" s="33"/>
       <c r="N58" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O58" s="67">
         <f t="shared" si="66"/>
@@ -5658,7 +5966,7 @@
       <c r="M59" s="33"/>
       <c r="N59" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O59" s="67">
         <f t="shared" si="66"/>
@@ -5704,7 +6012,7 @@
       <c r="M60" s="33"/>
       <c r="N60" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O60" s="67">
         <f t="shared" si="66"/>
@@ -5750,7 +6058,7 @@
       <c r="M61" s="33"/>
       <c r="N61" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O61" s="67">
         <f t="shared" si="40"/>
@@ -5814,7 +6122,7 @@
       <c r="M62" s="33"/>
       <c r="N62" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O62" s="67">
         <f t="shared" ref="O62:O79" si="72">SUM(F62:H62)/20</f>
@@ -5878,7 +6186,7 @@
       <c r="M63" s="33"/>
       <c r="N63" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O63" s="67">
         <f t="shared" si="72"/>
@@ -5942,7 +6250,7 @@
       <c r="M64" s="33"/>
       <c r="N64" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O64" s="67">
         <f t="shared" si="72"/>
@@ -6006,7 +6314,7 @@
       <c r="M65" s="33"/>
       <c r="N65" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O65" s="67">
         <f t="shared" si="72"/>
@@ -6070,7 +6378,7 @@
       <c r="M66" s="33"/>
       <c r="N66" s="43">
         <f t="shared" ref="N66:N97" si="78">SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O66" s="67">
         <f t="shared" si="72"/>
@@ -6134,7 +6442,7 @@
       <c r="M67" s="33"/>
       <c r="N67" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O67" s="67">
         <f t="shared" si="72"/>
@@ -6198,7 +6506,7 @@
       <c r="M68" s="33"/>
       <c r="N68" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O68" s="67">
         <f t="shared" si="72"/>
@@ -6262,7 +6570,7 @@
       <c r="M69" s="33"/>
       <c r="N69" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O69" s="67">
         <f t="shared" si="72"/>
@@ -6326,7 +6634,7 @@
       <c r="M70" s="33"/>
       <c r="N70" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O70" s="67">
         <f t="shared" si="72"/>
@@ -6390,7 +6698,7 @@
       <c r="M71" s="33"/>
       <c r="N71" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O71" s="67">
         <f t="shared" si="72"/>
@@ -6454,7 +6762,7 @@
       <c r="M72" s="33"/>
       <c r="N72" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O72" s="67">
         <f t="shared" si="72"/>
@@ -6518,7 +6826,7 @@
       <c r="M73" s="33"/>
       <c r="N73" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O73" s="67">
         <f t="shared" si="72"/>
@@ -6582,7 +6890,7 @@
       <c r="M74" s="33"/>
       <c r="N74" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O74" s="67">
         <f t="shared" si="72"/>
@@ -6646,7 +6954,7 @@
       <c r="M75" s="33"/>
       <c r="N75" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O75" s="67">
         <f t="shared" si="72"/>
@@ -6710,7 +7018,7 @@
       <c r="M76" s="33"/>
       <c r="N76" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O76" s="67">
         <f t="shared" si="72"/>
@@ -6774,7 +7082,7 @@
       <c r="M77" s="33"/>
       <c r="N77" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O77" s="67">
         <f t="shared" si="72"/>
@@ -6838,7 +7146,7 @@
       <c r="M78" s="33"/>
       <c r="N78" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O78" s="67">
         <f t="shared" si="72"/>
@@ -6902,7 +7210,7 @@
       <c r="M79" s="33"/>
       <c r="N79" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O79" s="67">
         <f t="shared" si="72"/>
@@ -6966,7 +7274,7 @@
       <c r="M80" s="33"/>
       <c r="N80" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O80" s="67">
         <f t="shared" ref="O80:O84" si="80">SUM(F80:H80)/20</f>
@@ -7030,7 +7338,7 @@
       <c r="M81" s="33"/>
       <c r="N81" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O81" s="67">
         <f t="shared" si="80"/>
@@ -7094,7 +7402,7 @@
       <c r="M82" s="33"/>
       <c r="N82" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O82" s="67">
         <f t="shared" si="80"/>
@@ -7158,7 +7466,7 @@
       <c r="M83" s="33"/>
       <c r="N83" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O83" s="67">
         <f t="shared" si="80"/>
@@ -7222,7 +7530,7 @@
       <c r="M84" s="33"/>
       <c r="N84" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O84" s="67">
         <f t="shared" si="80"/>
@@ -7286,7 +7594,7 @@
       <c r="M85" s="33"/>
       <c r="N85" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O85" s="67">
         <f t="shared" ref="O85:O132" si="86">SUM(F85:H85)/20</f>
@@ -7350,7 +7658,7 @@
       <c r="M86" s="33"/>
       <c r="N86" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O86" s="67">
         <f t="shared" si="86"/>
@@ -7414,7 +7722,7 @@
       <c r="M87" s="33"/>
       <c r="N87" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O87" s="67">
         <f t="shared" si="86"/>
@@ -7478,7 +7786,7 @@
       <c r="M88" s="33"/>
       <c r="N88" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O88" s="67">
         <f t="shared" si="86"/>
@@ -7542,7 +7850,7 @@
       <c r="M89" s="33"/>
       <c r="N89" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O89" s="67">
         <f t="shared" si="86"/>
@@ -7606,7 +7914,7 @@
       <c r="M90" s="145"/>
       <c r="N90" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O90" s="67">
         <f t="shared" si="86"/>
@@ -7670,7 +7978,7 @@
       <c r="M91" s="145"/>
       <c r="N91" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O91" s="67">
         <f t="shared" si="86"/>
@@ -7734,7 +8042,7 @@
       <c r="M92" s="145"/>
       <c r="N92" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O92" s="67">
         <f t="shared" si="86"/>
@@ -7798,7 +8106,7 @@
       <c r="M93" s="145"/>
       <c r="N93" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O93" s="67">
         <f t="shared" si="86"/>
@@ -7862,7 +8170,7 @@
       <c r="M94" s="33"/>
       <c r="N94" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O94" s="67">
         <f t="shared" si="86"/>
@@ -7926,7 +8234,7 @@
       <c r="M95" s="33"/>
       <c r="N95" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O95" s="67">
         <f t="shared" si="86"/>
@@ -7990,7 +8298,7 @@
       <c r="M96" s="33"/>
       <c r="N96" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O96" s="67">
         <f t="shared" si="86"/>
@@ -8054,7 +8362,7 @@
       <c r="M97" s="33"/>
       <c r="N97" s="43">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O97" s="67">
         <f t="shared" si="86"/>
@@ -8118,7 +8426,7 @@
       <c r="M98" s="33"/>
       <c r="N98" s="43">
         <f t="shared" ref="N98:N133" si="94">SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O98" s="67">
         <f t="shared" si="86"/>
@@ -8182,7 +8490,7 @@
       <c r="M99" s="33"/>
       <c r="N99" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O99" s="67">
         <f t="shared" si="86"/>
@@ -8246,7 +8554,7 @@
       <c r="M100" s="33"/>
       <c r="N100" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O100" s="67">
         <f t="shared" si="86"/>
@@ -8310,7 +8618,7 @@
       <c r="M101" s="33"/>
       <c r="N101" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O101" s="67">
         <f t="shared" si="86"/>
@@ -8374,7 +8682,7 @@
       <c r="M102" s="33"/>
       <c r="N102" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O102" s="67">
         <f t="shared" si="86"/>
@@ -8438,7 +8746,7 @@
       <c r="M103" s="33"/>
       <c r="N103" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O103" s="67">
         <f t="shared" si="86"/>
@@ -8502,7 +8810,7 @@
       <c r="M104" s="33"/>
       <c r="N104" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O104" s="67">
         <f t="shared" si="86"/>
@@ -8566,7 +8874,7 @@
       <c r="M105" s="33"/>
       <c r="N105" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O105" s="67">
         <f t="shared" si="86"/>
@@ -8630,7 +8938,7 @@
       <c r="M106" s="33"/>
       <c r="N106" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O106" s="67">
         <f t="shared" si="86"/>
@@ -8694,7 +9002,7 @@
       <c r="M107" s="33"/>
       <c r="N107" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O107" s="67">
         <f t="shared" si="86"/>
@@ -8758,7 +9066,7 @@
       <c r="M108" s="33"/>
       <c r="N108" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O108" s="67">
         <f t="shared" si="86"/>
@@ -8822,7 +9130,7 @@
       <c r="M109" s="33"/>
       <c r="N109" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O109" s="67">
         <f t="shared" si="86"/>
@@ -8886,7 +9194,7 @@
       <c r="M110" s="33"/>
       <c r="N110" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O110" s="67">
         <f t="shared" si="86"/>
@@ -8950,7 +9258,7 @@
       <c r="M111" s="33"/>
       <c r="N111" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O111" s="67">
         <f t="shared" si="86"/>
@@ -9014,7 +9322,7 @@
       <c r="M112" s="33"/>
       <c r="N112" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O112" s="67">
         <f t="shared" si="86"/>
@@ -9078,7 +9386,7 @@
       <c r="M113" s="33"/>
       <c r="N113" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O113" s="67">
         <f t="shared" si="86"/>
@@ -9142,7 +9450,7 @@
       <c r="M114" s="33"/>
       <c r="N114" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O114" s="67">
         <f t="shared" si="86"/>
@@ -9206,7 +9514,7 @@
       <c r="M115" s="33"/>
       <c r="N115" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O115" s="67">
         <f t="shared" si="86"/>
@@ -9270,7 +9578,7 @@
       <c r="M116" s="33"/>
       <c r="N116" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O116" s="67">
         <f t="shared" si="86"/>
@@ -9334,7 +9642,7 @@
       <c r="M117" s="33"/>
       <c r="N117" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O117" s="67">
         <f t="shared" si="86"/>
@@ -9398,7 +9706,7 @@
       <c r="M118" s="33"/>
       <c r="N118" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O118" s="67">
         <f t="shared" si="86"/>
@@ -9462,7 +9770,7 @@
       <c r="M119" s="33"/>
       <c r="N119" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O119" s="67">
         <f t="shared" si="86"/>
@@ -9526,7 +9834,7 @@
       <c r="M120" s="33"/>
       <c r="N120" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O120" s="67">
         <f t="shared" si="86"/>
@@ -9590,7 +9898,7 @@
       <c r="M121" s="33"/>
       <c r="N121" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O121" s="67">
         <f t="shared" si="86"/>
@@ -9654,7 +9962,7 @@
       <c r="M122" s="33"/>
       <c r="N122" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O122" s="67">
         <f t="shared" si="86"/>
@@ -9718,7 +10026,7 @@
       <c r="M123" s="33"/>
       <c r="N123" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O123" s="67">
         <f t="shared" si="86"/>
@@ -9782,7 +10090,7 @@
       <c r="M124" s="33"/>
       <c r="N124" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O124" s="67">
         <f t="shared" si="86"/>
@@ -9844,7 +10152,7 @@
       <c r="M125" s="33"/>
       <c r="N125" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O125" s="67">
         <f t="shared" si="86"/>
@@ -9904,12 +10212,12 @@
         <v>0</v>
       </c>
       <c r="M126" s="33">
-        <f t="shared" ref="M123:M133" si="98">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
+        <f t="shared" ref="M126:M133" si="98">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N126" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O126" s="67">
         <f t="shared" si="86"/>
@@ -9974,7 +10282,7 @@
       </c>
       <c r="N127" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O127" s="67">
         <f t="shared" si="86"/>
@@ -10039,7 +10347,7 @@
       </c>
       <c r="N128" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O128" s="67">
         <f t="shared" si="86"/>
@@ -10104,7 +10412,7 @@
       </c>
       <c r="N129" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O129" s="67">
         <f t="shared" si="86"/>
@@ -10169,7 +10477,7 @@
       </c>
       <c r="N130" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O130" s="67">
         <f t="shared" si="86"/>
@@ -10234,7 +10542,7 @@
       </c>
       <c r="N131" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O131" s="67">
         <f t="shared" si="86"/>
@@ -10299,7 +10607,7 @@
       </c>
       <c r="N132" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O132" s="67">
         <f t="shared" si="86"/>
@@ -10344,10 +10652,10 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="72"/>
-      <c r="B133" s="159" t="s">
+      <c r="B133" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="160"/>
+      <c r="C133" s="173"/>
       <c r="D133" s="136"/>
       <c r="E133" s="78">
         <f t="shared" ref="E133:K133" si="99">SUM(E6:E61)</f>
@@ -10355,31 +10663,31 @@
       </c>
       <c r="F133" s="78">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>435</v>
       </c>
       <c r="G133" s="78">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>395</v>
       </c>
       <c r="H133" s="78">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="I133" s="78">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="J133" s="78">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="K133" s="78">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="L133" s="42">
         <f t="shared" ref="L133" si="100">SUM(E133:K133)/40</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M133" s="33">
         <f t="shared" si="98"/>
@@ -10387,15 +10695,15 @@
       </c>
       <c r="N133" s="43">
         <f t="shared" si="94"/>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O133" s="67">
         <f t="shared" ref="O133:O137" si="101">SUM(F133:H133)/20</f>
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="P133" s="34">
         <f t="shared" ref="P133:P137" si="102">SUM(I133:K133)/20</f>
-        <v>0</v>
+        <v>33.5</v>
       </c>
       <c r="Q133" s="45" t="e">
         <f t="shared" si="96"/>
@@ -10489,7 +10797,7 @@
       </c>
       <c r="N135" s="43">
         <f>SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O135" s="67">
         <f t="shared" si="101"/>
@@ -10557,7 +10865,7 @@
       </c>
       <c r="N136" s="43">
         <f>SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O136" s="67">
         <f t="shared" si="101"/>
@@ -10601,10 +10909,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="172" t="s">
+      <c r="B137" s="160" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="173"/>
+      <c r="C137" s="161"/>
       <c r="D137" s="137"/>
       <c r="E137" s="77">
         <f>SUM(E135:E136)</f>
@@ -10644,7 +10952,7 @@
       </c>
       <c r="N137" s="52">
         <f>SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
-        <v>0</v>
+        <v>3.5513000000000003</v>
       </c>
       <c r="O137" s="67">
         <f t="shared" si="101"/>
@@ -10688,10 +10996,10 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="161" t="s">
+      <c r="B138" s="149" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="162"/>
+      <c r="C138" s="150"/>
       <c r="D138" s="138"/>
       <c r="E138" s="79">
         <f>SUM(E133,E137)</f>
@@ -10699,47 +11007,47 @@
       </c>
       <c r="F138" s="79">
         <f t="shared" ref="F138:K138" si="106">SUM(F133,F137)</f>
-        <v>0</v>
+        <v>435</v>
       </c>
       <c r="G138" s="79">
         <f t="shared" si="106"/>
-        <v>0</v>
+        <v>395</v>
       </c>
       <c r="H138" s="79">
         <f t="shared" si="106"/>
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="I138" s="79">
         <f t="shared" si="106"/>
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="J138" s="79">
         <f t="shared" si="106"/>
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="K138" s="79">
         <f t="shared" si="106"/>
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="L138" s="54">
         <f>SUM(E138:K138)/40</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M138" s="57">
         <f>SUM(M5:M137)</f>
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="N138" s="55">
         <f t="shared" ref="N138:X138" si="107">SUM(N5:N137)</f>
-        <v>0</v>
+        <v>365.78390000000064</v>
       </c>
       <c r="O138" s="56">
         <f t="shared" si="107"/>
-        <v>0</v>
+        <v>128.5</v>
       </c>
       <c r="P138" s="58">
         <f t="shared" si="107"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="Q138" s="59" t="e">
         <f t="shared" si="107"/>
@@ -10776,17 +11084,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:D60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F426D06C-CFDD-4EF5-9B31-17463967AEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7525FB1-4109-4F1E-A4F4-C81211F4B258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="142">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -400,6 +400,54 @@
   </si>
   <si>
     <t>Barki Road</t>
+  </si>
+  <si>
+    <t>Raheem Store Thoker Free Ctn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thoker </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TN Traders </t>
+  </si>
+  <si>
+    <t>Thoker Niaz Baig</t>
+  </si>
+  <si>
+    <t>Gourmet Food Islam Pura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Walton </t>
+  </si>
+  <si>
+    <t>Gourmet Food Krishan Nager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Rustam Park </t>
+  </si>
+  <si>
+    <t>Gourmet Food Dharampura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Awan Town </t>
+  </si>
+  <si>
+    <t>FIBCJ001</t>
+  </si>
+  <si>
+    <t>FIBCN001</t>
+  </si>
+  <si>
+    <t>FICCJ001</t>
+  </si>
+  <si>
+    <t>FICCN001</t>
+  </si>
+  <si>
+    <t>FIVTJ001</t>
+  </si>
+  <si>
+    <t>FIVTN001</t>
   </si>
 </sst>
 </file>
@@ -1267,7 +1315,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1642,6 +1690,39 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1681,39 +1762,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1741,6 +1789,7 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2333,13 +2382,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="157">
+      <c r="B1" s="144">
         <f ca="1">TODAY()</f>
-        <v>46298</v>
-      </c>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
+        <v>46300</v>
+      </c>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2361,10 +2410,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="154" t="s">
+      <c r="A2" s="165" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="158" t="s">
+      <c r="B2" s="145" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2394,13 +2443,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="146"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="148"/>
-      <c r="O2" s="149" t="s">
+      <c r="L2" s="157"/>
+      <c r="M2" s="158"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="160" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="150"/>
+      <c r="P2" s="161"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2419,8 +2468,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="154"/>
-      <c r="B3" s="159"/>
+      <c r="A3" s="165"/>
+      <c r="B3" s="146"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2448,29 +2497,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="151" t="s">
+      <c r="L3" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="152"/>
-      <c r="N3" s="153"/>
+      <c r="M3" s="163"/>
+      <c r="N3" s="164"/>
       <c r="O3" s="64"/>
       <c r="P3" s="65"/>
-      <c r="Q3" s="161" t="s">
+      <c r="Q3" s="148" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="162"/>
-      <c r="S3" s="162"/>
-      <c r="T3" s="163"/>
-      <c r="U3" s="164" t="s">
+      <c r="R3" s="149"/>
+      <c r="S3" s="149"/>
+      <c r="T3" s="150"/>
+      <c r="U3" s="151" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="165"/>
-      <c r="W3" s="165"/>
-      <c r="X3" s="166"/>
+      <c r="V3" s="152"/>
+      <c r="W3" s="152"/>
+      <c r="X3" s="153"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="154"/>
-      <c r="B4" s="160"/>
+      <c r="A4" s="165"/>
+      <c r="B4" s="147"/>
       <c r="C4" s="130" t="s">
         <v>90</v>
       </c>
@@ -3891,35 +3940,35 @@
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A23" s="134">
+      <c r="A23" s="71">
         <v>46297</v>
       </c>
-      <c r="B23" s="135">
+      <c r="B23" s="40">
         <v>19</v>
       </c>
-      <c r="C23" s="141" t="s">
+      <c r="C23" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="141" t="s">
+      <c r="D23" s="131" t="s">
         <v>112</v>
       </c>
-      <c r="E23" s="142"/>
-      <c r="F23" s="142">
+      <c r="E23" s="68"/>
+      <c r="F23" s="68">
         <v>80</v>
       </c>
-      <c r="G23" s="142">
+      <c r="G23" s="68">
         <v>40</v>
       </c>
-      <c r="H23" s="143">
+      <c r="H23" s="124">
         <v>80</v>
       </c>
-      <c r="I23" s="142">
+      <c r="I23" s="68">
         <v>120</v>
       </c>
-      <c r="J23" s="142">
+      <c r="J23" s="68">
         <v>160</v>
       </c>
-      <c r="K23" s="142">
+      <c r="K23" s="68">
         <v>240</v>
       </c>
       <c r="L23" s="124">
@@ -3972,35 +4021,35 @@
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A24" s="134">
+      <c r="A24" s="71">
         <v>46297</v>
       </c>
-      <c r="B24" s="135">
+      <c r="B24" s="40">
         <v>20</v>
       </c>
-      <c r="C24" s="141" t="s">
+      <c r="C24" s="131" t="s">
         <v>113</v>
       </c>
-      <c r="D24" s="141" t="s">
+      <c r="D24" s="131" t="s">
         <v>114</v>
       </c>
-      <c r="E24" s="142"/>
-      <c r="F24" s="142">
+      <c r="E24" s="68"/>
+      <c r="F24" s="68">
         <v>73</v>
       </c>
-      <c r="G24" s="142">
+      <c r="G24" s="68">
         <v>55</v>
       </c>
-      <c r="H24" s="143">
+      <c r="H24" s="124">
         <v>75</v>
       </c>
-      <c r="I24" s="142">
+      <c r="I24" s="68">
         <v>80</v>
       </c>
-      <c r="J24" s="142">
+      <c r="J24" s="68">
         <v>80</v>
       </c>
-      <c r="K24" s="142">
+      <c r="K24" s="68">
         <v>80</v>
       </c>
       <c r="L24" s="124">
@@ -4053,35 +4102,35 @@
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A25" s="134">
+      <c r="A25" s="71">
         <v>46297</v>
       </c>
-      <c r="B25" s="135">
+      <c r="B25" s="40">
         <v>21</v>
       </c>
-      <c r="C25" s="141" t="s">
+      <c r="C25" s="131" t="s">
         <v>113</v>
       </c>
-      <c r="D25" s="141" t="s">
+      <c r="D25" s="131" t="s">
         <v>115</v>
       </c>
-      <c r="E25" s="142"/>
-      <c r="F25" s="142">
+      <c r="E25" s="68"/>
+      <c r="F25" s="68">
         <v>40</v>
       </c>
-      <c r="G25" s="142">
+      <c r="G25" s="68">
         <v>40</v>
       </c>
-      <c r="H25" s="143">
+      <c r="H25" s="124">
         <v>40</v>
       </c>
-      <c r="I25" s="142">
+      <c r="I25" s="68">
         <v>40</v>
       </c>
-      <c r="J25" s="142">
+      <c r="J25" s="68">
         <v>40</v>
       </c>
-      <c r="K25" s="142">
+      <c r="K25" s="68">
         <v>40</v>
       </c>
       <c r="L25" s="124">
@@ -4134,29 +4183,29 @@
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A26" s="134">
+      <c r="A26" s="71">
         <v>46297</v>
       </c>
-      <c r="B26" s="135">
+      <c r="B26" s="40">
         <v>22</v>
       </c>
-      <c r="C26" s="141" t="s">
+      <c r="C26" s="131" t="s">
         <v>116</v>
       </c>
-      <c r="D26" s="141" t="s">
+      <c r="D26" s="131" t="s">
         <v>118</v>
       </c>
-      <c r="E26" s="142"/>
-      <c r="F26" s="142">
+      <c r="E26" s="68"/>
+      <c r="F26" s="68">
         <v>40</v>
       </c>
-      <c r="G26" s="142"/>
-      <c r="H26" s="143"/>
-      <c r="I26" s="142"/>
-      <c r="J26" s="142">
+      <c r="G26" s="68"/>
+      <c r="H26" s="124"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="68">
         <v>80</v>
       </c>
-      <c r="K26" s="142">
+      <c r="K26" s="68">
         <v>40</v>
       </c>
       <c r="L26" s="124">
@@ -4209,27 +4258,27 @@
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A27" s="134">
+      <c r="A27" s="71">
         <v>46297</v>
       </c>
-      <c r="B27" s="135">
+      <c r="B27" s="40">
         <v>23</v>
       </c>
-      <c r="C27" s="141" t="s">
+      <c r="C27" s="131" t="s">
         <v>117</v>
       </c>
-      <c r="D27" s="141" t="s">
+      <c r="D27" s="131" t="s">
         <v>119</v>
       </c>
-      <c r="E27" s="142"/>
-      <c r="F27" s="142"/>
-      <c r="G27" s="142"/>
-      <c r="H27" s="143">
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="124">
         <v>40</v>
       </c>
-      <c r="I27" s="142"/>
-      <c r="J27" s="142"/>
-      <c r="K27" s="142"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="68"/>
       <c r="L27" s="124">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -4280,33 +4329,33 @@
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A28" s="134">
+      <c r="A28" s="71">
         <v>46297</v>
       </c>
-      <c r="B28" s="135">
+      <c r="B28" s="40">
         <v>24</v>
       </c>
-      <c r="C28" s="141" t="s">
+      <c r="C28" s="131" t="s">
         <v>116</v>
       </c>
-      <c r="D28" s="141" t="s">
+      <c r="D28" s="131" t="s">
         <v>120</v>
       </c>
-      <c r="E28" s="142"/>
-      <c r="F28" s="142">
+      <c r="E28" s="68"/>
+      <c r="F28" s="68">
         <v>40</v>
       </c>
-      <c r="G28" s="142">
+      <c r="G28" s="68">
         <v>40</v>
       </c>
-      <c r="H28" s="143">
+      <c r="H28" s="124">
         <v>80</v>
       </c>
-      <c r="I28" s="142"/>
-      <c r="J28" s="142">
+      <c r="I28" s="68"/>
+      <c r="J28" s="68">
         <v>40</v>
       </c>
-      <c r="K28" s="142"/>
+      <c r="K28" s="68"/>
       <c r="L28" s="124">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -4357,27 +4406,27 @@
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A29" s="134">
+      <c r="A29" s="71">
         <v>46297</v>
       </c>
-      <c r="B29" s="135">
+      <c r="B29" s="40">
         <v>25</v>
       </c>
-      <c r="C29" s="141" t="s">
+      <c r="C29" s="131" t="s">
         <v>116</v>
       </c>
-      <c r="D29" s="141" t="s">
+      <c r="D29" s="131" t="s">
         <v>121</v>
       </c>
-      <c r="E29" s="142"/>
-      <c r="F29" s="142"/>
-      <c r="G29" s="142"/>
-      <c r="H29" s="143">
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="124">
         <v>40</v>
       </c>
-      <c r="I29" s="142"/>
-      <c r="J29" s="142"/>
-      <c r="K29" s="142"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
       <c r="L29" s="124">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -4428,31 +4477,31 @@
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A30" s="134">
+      <c r="A30" s="71">
         <v>46297</v>
       </c>
-      <c r="B30" s="135">
+      <c r="B30" s="40">
         <v>26</v>
       </c>
-      <c r="C30" s="141" t="s">
+      <c r="C30" s="131" t="s">
         <v>116</v>
       </c>
-      <c r="D30" s="141" t="s">
+      <c r="D30" s="131" t="s">
         <v>122</v>
       </c>
-      <c r="E30" s="142"/>
-      <c r="F30" s="142">
+      <c r="E30" s="68"/>
+      <c r="F30" s="68">
         <v>40</v>
       </c>
-      <c r="G30" s="142"/>
-      <c r="H30" s="143">
+      <c r="G30" s="68"/>
+      <c r="H30" s="124">
         <v>180</v>
       </c>
-      <c r="I30" s="142">
+      <c r="I30" s="68">
         <v>40</v>
       </c>
-      <c r="J30" s="142"/>
-      <c r="K30" s="142">
+      <c r="J30" s="68"/>
+      <c r="K30" s="68">
         <v>120</v>
       </c>
       <c r="L30" s="124">
@@ -4505,27 +4554,27 @@
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A31" s="134">
+      <c r="A31" s="71">
         <v>46297</v>
       </c>
-      <c r="B31" s="135">
+      <c r="B31" s="40">
         <v>27</v>
       </c>
-      <c r="C31" s="141" t="s">
+      <c r="C31" s="131" t="s">
         <v>116</v>
       </c>
-      <c r="D31" s="141" t="s">
+      <c r="D31" s="131" t="s">
         <v>123</v>
       </c>
-      <c r="E31" s="142"/>
-      <c r="F31" s="142"/>
-      <c r="G31" s="142"/>
-      <c r="H31" s="143"/>
-      <c r="I31" s="142">
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="68"/>
+      <c r="H31" s="124"/>
+      <c r="I31" s="68">
         <v>40</v>
       </c>
-      <c r="J31" s="142"/>
-      <c r="K31" s="142">
+      <c r="J31" s="68"/>
+      <c r="K31" s="68">
         <v>120</v>
       </c>
       <c r="L31" s="124">
@@ -4578,31 +4627,31 @@
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A32" s="134">
+      <c r="A32" s="71">
         <v>46297</v>
       </c>
-      <c r="B32" s="135">
+      <c r="B32" s="40">
         <v>28</v>
       </c>
-      <c r="C32" s="141" t="s">
+      <c r="C32" s="131" t="s">
         <v>116</v>
       </c>
-      <c r="D32" s="141" t="s">
+      <c r="D32" s="131" t="s">
         <v>124</v>
       </c>
-      <c r="E32" s="142"/>
-      <c r="F32" s="142"/>
-      <c r="G32" s="142"/>
-      <c r="H32" s="143">
+      <c r="E32" s="68"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="68"/>
+      <c r="H32" s="124">
         <v>40</v>
       </c>
-      <c r="I32" s="142">
+      <c r="I32" s="68">
         <v>40</v>
       </c>
-      <c r="J32" s="142">
+      <c r="J32" s="68">
         <v>40</v>
       </c>
-      <c r="K32" s="142"/>
+      <c r="K32" s="68"/>
       <c r="L32" s="124">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -4653,31 +4702,31 @@
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A33" s="134">
+      <c r="A33" s="71">
         <v>46297</v>
       </c>
-      <c r="B33" s="135">
+      <c r="B33" s="40">
         <v>29</v>
       </c>
-      <c r="C33" s="141" t="s">
+      <c r="C33" s="131" t="s">
         <v>116</v>
       </c>
-      <c r="D33" s="141" t="s">
+      <c r="D33" s="131" t="s">
         <v>125</v>
       </c>
-      <c r="E33" s="142"/>
-      <c r="F33" s="142">
+      <c r="E33" s="68"/>
+      <c r="F33" s="68">
         <v>4</v>
       </c>
-      <c r="G33" s="142"/>
-      <c r="H33" s="143">
+      <c r="G33" s="68"/>
+      <c r="H33" s="124">
         <v>36</v>
       </c>
-      <c r="I33" s="142"/>
-      <c r="J33" s="142">
+      <c r="I33" s="68"/>
+      <c r="J33" s="68">
         <v>2</v>
       </c>
-      <c r="K33" s="142">
+      <c r="K33" s="68">
         <v>80</v>
       </c>
       <c r="L33" s="124">
@@ -4730,28 +4779,36 @@
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A34" s="71"/>
-      <c r="B34" s="40">
+      <c r="A34" s="134">
+        <v>46298</v>
+      </c>
+      <c r="B34" s="135">
         <v>30</v>
       </c>
-      <c r="C34" s="131"/>
-      <c r="D34" s="131"/>
-      <c r="E34" s="68"/>
-      <c r="F34" s="68"/>
-      <c r="G34" s="68"/>
-      <c r="H34" s="124"/>
-      <c r="I34" s="68"/>
-      <c r="J34" s="68"/>
-      <c r="K34" s="68"/>
+      <c r="C34" s="141" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" s="141" t="s">
+        <v>127</v>
+      </c>
+      <c r="E34" s="142"/>
+      <c r="F34" s="142">
+        <v>40</v>
+      </c>
+      <c r="G34" s="142"/>
+      <c r="H34" s="143"/>
+      <c r="I34" s="142"/>
+      <c r="J34" s="142"/>
+      <c r="K34" s="142"/>
       <c r="L34" s="124">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="138"/>
       <c r="N34" s="42"/>
       <c r="O34" s="66">
         <f t="shared" ref="O34:O47" si="52">SUM(F34:H34)/20</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P34" s="33">
         <f t="shared" ref="P34:P47" si="53">SUM(I34:K34)/20</f>
@@ -4791,32 +4848,50 @@
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A35" s="71"/>
-      <c r="B35" s="40">
+      <c r="A35" s="134">
+        <v>46298</v>
+      </c>
+      <c r="B35" s="135">
         <v>31</v>
       </c>
-      <c r="C35" s="131"/>
-      <c r="D35" s="131"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="68"/>
-      <c r="H35" s="124"/>
-      <c r="I35" s="68"/>
-      <c r="J35" s="68"/>
-      <c r="K35" s="68"/>
+      <c r="C35" s="141" t="s">
+        <v>128</v>
+      </c>
+      <c r="D35" s="141" t="s">
+        <v>129</v>
+      </c>
+      <c r="E35" s="142"/>
+      <c r="F35" s="142">
+        <v>40</v>
+      </c>
+      <c r="G35" s="142">
+        <v>40</v>
+      </c>
+      <c r="H35" s="143">
+        <v>40</v>
+      </c>
+      <c r="I35" s="142"/>
+      <c r="J35" s="142">
+        <v>40</v>
+      </c>
+      <c r="K35" s="142">
+        <v>80</v>
+      </c>
       <c r="L35" s="124">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M35" s="138"/>
+        <v>6</v>
+      </c>
+      <c r="M35" s="138">
+        <v>14</v>
+      </c>
       <c r="N35" s="42"/>
       <c r="O35" s="66">
         <f t="shared" ref="O35" si="58">SUM(F35:H35)/20</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P35" s="33">
         <f t="shared" ref="P35" si="59">SUM(I35:K35)/20</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q35" s="44" t="e">
         <f t="shared" si="1"/>
@@ -4852,32 +4927,46 @@
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A36" s="71"/>
-      <c r="B36" s="40">
+      <c r="A36" s="134">
+        <v>46298</v>
+      </c>
+      <c r="B36" s="135">
         <v>32</v>
       </c>
-      <c r="C36" s="131"/>
-      <c r="D36" s="131"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
-      <c r="H36" s="124"/>
-      <c r="I36" s="68"/>
-      <c r="J36" s="68"/>
-      <c r="K36" s="68"/>
+      <c r="C36" s="141" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="141"/>
+      <c r="E36" s="142"/>
+      <c r="F36" s="142">
+        <v>40</v>
+      </c>
+      <c r="G36" s="142"/>
+      <c r="H36" s="143">
+        <v>30</v>
+      </c>
+      <c r="I36" s="142">
+        <v>20</v>
+      </c>
+      <c r="J36" s="142"/>
+      <c r="K36" s="142">
+        <v>20</v>
+      </c>
       <c r="L36" s="124">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M36" s="138"/>
+        <v>2.75</v>
+      </c>
+      <c r="M36" s="138">
+        <v>18</v>
+      </c>
       <c r="N36" s="42"/>
       <c r="O36" s="66">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P36" s="33">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q36" s="44" t="e">
         <f t="shared" si="1"/>
@@ -4913,24 +5002,36 @@
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A37" s="71"/>
-      <c r="B37" s="40">
+      <c r="A37" s="134">
+        <v>46298</v>
+      </c>
+      <c r="B37" s="135">
         <v>33</v>
       </c>
-      <c r="C37" s="131"/>
-      <c r="D37" s="131"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="68"/>
-      <c r="H37" s="124"/>
-      <c r="I37" s="68"/>
-      <c r="J37" s="68"/>
-      <c r="K37" s="68"/>
+      <c r="C37" s="141" t="s">
+        <v>131</v>
+      </c>
+      <c r="D37" s="141"/>
+      <c r="E37" s="142"/>
+      <c r="F37" s="142"/>
+      <c r="G37" s="142"/>
+      <c r="H37" s="143"/>
+      <c r="I37" s="142">
+        <v>20</v>
+      </c>
+      <c r="J37" s="142">
+        <v>20</v>
+      </c>
+      <c r="K37" s="142">
+        <v>20</v>
+      </c>
       <c r="L37" s="124">
         <f t="shared" ref="L37:L68" si="64">SUM(E37:K37)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M37" s="138"/>
+        <v>1.5</v>
+      </c>
+      <c r="M37" s="138">
+        <v>18</v>
+      </c>
       <c r="N37" s="42"/>
       <c r="O37" s="66">
         <f t="shared" si="52"/>
@@ -4938,7 +5039,7 @@
       </c>
       <c r="P37" s="33">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q37" s="44" t="e">
         <f t="shared" si="1"/>
@@ -4974,32 +5075,46 @@
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A38" s="71"/>
-      <c r="B38" s="40">
+      <c r="A38" s="134">
+        <v>46298</v>
+      </c>
+      <c r="B38" s="135">
         <v>34</v>
       </c>
-      <c r="C38" s="131"/>
-      <c r="D38" s="131"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
-      <c r="H38" s="124"/>
-      <c r="I38" s="68"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="68"/>
+      <c r="C38" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="D38" s="141"/>
+      <c r="E38" s="142"/>
+      <c r="F38" s="142"/>
+      <c r="G38" s="142">
+        <v>40</v>
+      </c>
+      <c r="H38" s="143"/>
+      <c r="I38" s="142">
+        <v>20</v>
+      </c>
+      <c r="J38" s="142">
+        <v>20</v>
+      </c>
+      <c r="K38" s="142">
+        <v>20</v>
+      </c>
       <c r="L38" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M38" s="138"/>
+        <v>2.5</v>
+      </c>
+      <c r="M38" s="138">
+        <v>18</v>
+      </c>
       <c r="N38" s="42"/>
       <c r="O38" s="66">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P38" s="33">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q38" s="44" t="e">
         <f t="shared" si="1"/>
@@ -5035,32 +5150,46 @@
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A39" s="71"/>
-      <c r="B39" s="40">
+      <c r="A39" s="134">
+        <v>46298</v>
+      </c>
+      <c r="B39" s="135">
         <v>35</v>
       </c>
-      <c r="C39" s="131"/>
-      <c r="D39" s="131"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="68"/>
-      <c r="H39" s="124"/>
-      <c r="I39" s="68"/>
-      <c r="J39" s="68"/>
-      <c r="K39" s="68"/>
+      <c r="C39" s="141" t="s">
+        <v>133</v>
+      </c>
+      <c r="D39" s="141"/>
+      <c r="E39" s="142"/>
+      <c r="F39" s="142">
+        <v>30</v>
+      </c>
+      <c r="G39" s="142"/>
+      <c r="H39" s="143">
+        <v>30</v>
+      </c>
+      <c r="I39" s="142">
+        <v>20</v>
+      </c>
+      <c r="J39" s="142">
+        <v>20</v>
+      </c>
+      <c r="K39" s="142"/>
       <c r="L39" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M39" s="138"/>
+        <v>2.5</v>
+      </c>
+      <c r="M39" s="138">
+        <v>18</v>
+      </c>
       <c r="N39" s="42"/>
       <c r="O39" s="66">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P39" s="33">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q39" s="44" t="e">
         <f t="shared" si="1"/>
@@ -5096,32 +5225,48 @@
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A40" s="71"/>
-      <c r="B40" s="40">
+      <c r="A40" s="134">
+        <v>46298</v>
+      </c>
+      <c r="B40" s="135">
         <v>36</v>
       </c>
-      <c r="C40" s="131"/>
-      <c r="D40" s="131"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
-      <c r="H40" s="124"/>
-      <c r="I40" s="68"/>
-      <c r="J40" s="68"/>
-      <c r="K40" s="68"/>
+      <c r="C40" s="141" t="s">
+        <v>134</v>
+      </c>
+      <c r="D40" s="141"/>
+      <c r="E40" s="142"/>
+      <c r="F40" s="142"/>
+      <c r="G40" s="142">
+        <v>30</v>
+      </c>
+      <c r="H40" s="143">
+        <v>40</v>
+      </c>
+      <c r="I40" s="142">
+        <v>20</v>
+      </c>
+      <c r="J40" s="142">
+        <v>20</v>
+      </c>
+      <c r="K40" s="142">
+        <v>20</v>
+      </c>
       <c r="L40" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M40" s="138"/>
+        <v>3.25</v>
+      </c>
+      <c r="M40" s="138">
+        <v>18</v>
+      </c>
       <c r="N40" s="42"/>
       <c r="O40" s="66">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P40" s="33">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q40" s="44" t="e">
         <f t="shared" si="1"/>
@@ -5157,32 +5302,50 @@
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A41" s="71"/>
-      <c r="B41" s="40">
+      <c r="A41" s="134">
+        <v>46298</v>
+      </c>
+      <c r="B41" s="135">
         <v>37</v>
       </c>
-      <c r="C41" s="131"/>
-      <c r="D41" s="131"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="68"/>
-      <c r="H41" s="124"/>
-      <c r="I41" s="68"/>
-      <c r="J41" s="68"/>
-      <c r="K41" s="68"/>
+      <c r="C41" s="141" t="s">
+        <v>135</v>
+      </c>
+      <c r="D41" s="141"/>
+      <c r="E41" s="142"/>
+      <c r="F41" s="142">
+        <v>40</v>
+      </c>
+      <c r="G41" s="142">
+        <v>30</v>
+      </c>
+      <c r="H41" s="143">
+        <v>40</v>
+      </c>
+      <c r="I41" s="142">
+        <v>20</v>
+      </c>
+      <c r="J41" s="142">
+        <v>20</v>
+      </c>
+      <c r="K41" s="142">
+        <v>20</v>
+      </c>
       <c r="L41" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M41" s="138"/>
+        <v>4.25</v>
+      </c>
+      <c r="M41" s="138">
+        <v>18</v>
+      </c>
       <c r="N41" s="42"/>
       <c r="O41" s="66">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P41" s="33">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q41" s="44" t="e">
         <f t="shared" si="1"/>
@@ -10523,10 +10686,10 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="71"/>
-      <c r="B133" s="167" t="s">
+      <c r="B133" s="154" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="167"/>
+      <c r="C133" s="154"/>
       <c r="D133" s="135"/>
       <c r="E133" s="140">
         <f t="shared" ref="E133:K133" si="96">SUM(E6:E61)</f>
@@ -10534,31 +10697,31 @@
       </c>
       <c r="F133" s="140">
         <f t="shared" si="96"/>
-        <v>752</v>
+        <v>942</v>
       </c>
       <c r="G133" s="140">
         <f t="shared" si="96"/>
-        <v>570</v>
+        <v>710</v>
       </c>
       <c r="H133" s="140">
         <f t="shared" si="96"/>
-        <v>1031</v>
+        <v>1211</v>
       </c>
       <c r="I133" s="140">
         <f t="shared" si="96"/>
-        <v>635</v>
+        <v>755</v>
       </c>
       <c r="J133" s="140">
         <f t="shared" si="96"/>
-        <v>617</v>
+        <v>757</v>
       </c>
       <c r="K133" s="140">
         <f t="shared" si="96"/>
-        <v>940</v>
+        <v>1120</v>
       </c>
       <c r="L133" s="124">
         <f t="shared" ref="L133" si="97">SUM(E133:K133)/40</f>
-        <v>113.625</v>
+        <v>137.375</v>
       </c>
       <c r="M133" s="138">
         <f t="shared" si="95"/>
@@ -10567,11 +10730,11 @@
       <c r="N133" s="42"/>
       <c r="O133" s="66">
         <f t="shared" ref="O133:O137" si="98">SUM(F133:H133)/20</f>
-        <v>117.65</v>
+        <v>143.15</v>
       </c>
       <c r="P133" s="33">
         <f t="shared" ref="P133:P137" si="99">SUM(I133:K133)/20</f>
-        <v>109.6</v>
+        <v>131.6</v>
       </c>
       <c r="Q133" s="44" t="e">
         <f t="shared" si="93"/>
@@ -10777,10 +10940,10 @@
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="155" t="s">
+      <c r="B137" s="166" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="156"/>
+      <c r="C137" s="167"/>
       <c r="D137" s="128"/>
       <c r="E137" s="76">
         <f>SUM(E135:E136)</f>
@@ -10864,10 +11027,10 @@
       </c>
     </row>
     <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="144" t="s">
+      <c r="B138" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="145"/>
+      <c r="C138" s="156"/>
       <c r="D138" s="129"/>
       <c r="E138" s="77">
         <f>SUM(E133,E137)</f>
@@ -10875,35 +11038,35 @@
       </c>
       <c r="F138" s="77">
         <f t="shared" ref="F138:K138" si="103">SUM(F133,F137)</f>
-        <v>752</v>
+        <v>942</v>
       </c>
       <c r="G138" s="77">
         <f t="shared" si="103"/>
-        <v>570</v>
+        <v>710</v>
       </c>
       <c r="H138" s="77">
         <f t="shared" si="103"/>
-        <v>1031</v>
+        <v>1211</v>
       </c>
       <c r="I138" s="77">
         <f t="shared" si="103"/>
-        <v>635</v>
+        <v>755</v>
       </c>
       <c r="J138" s="77">
         <f t="shared" si="103"/>
-        <v>617</v>
+        <v>757</v>
       </c>
       <c r="K138" s="77">
         <f t="shared" si="103"/>
-        <v>940</v>
+        <v>1120</v>
       </c>
       <c r="L138" s="53">
         <f>SUM(E138:K138)/40</f>
-        <v>113.625</v>
+        <v>137.375</v>
       </c>
       <c r="M138" s="56">
         <f>SUM(M5:M137)</f>
-        <v>474</v>
+        <v>596</v>
       </c>
       <c r="N138" s="54">
         <f t="shared" ref="N138:X138" si="104">SUM(N5:N137)</f>
@@ -10911,11 +11074,11 @@
       </c>
       <c r="O138" s="55">
         <f t="shared" si="104"/>
-        <v>238.8</v>
+        <v>289.8</v>
       </c>
       <c r="P138" s="57">
         <f t="shared" si="104"/>
-        <v>221.2</v>
+        <v>265.2</v>
       </c>
       <c r="Q138" s="58" t="e">
         <f t="shared" si="104"/>
@@ -10952,17 +11115,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:D60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -11062,22 +11225,22 @@
         <v>47</v>
       </c>
       <c r="D5" s="80">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="E5" s="72">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="F5" s="72"/>
       <c r="G5" s="94">
         <f>SUM(D5:F5)</f>
-        <v>179</v>
+        <v>232</v>
       </c>
       <c r="H5" s="87">
         <v>10000</v>
       </c>
       <c r="I5" s="88">
         <f>G5-H5</f>
-        <v>-9821</v>
+        <v>-9768</v>
       </c>
       <c r="K5" s="132" t="s">
         <v>1</v>
@@ -11086,14 +11249,21 @@
         <v>70</v>
       </c>
       <c r="M5" s="5">
-        <v>12171</v>
+        <v>12766</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>304.27499999999998</v>
+        <v>319.14999999999998</v>
       </c>
       <c r="O5" s="74"/>
       <c r="P5" s="133"/>
+      <c r="Q5">
+        <v>267.20999999999998</v>
+      </c>
+      <c r="R5" s="177">
+        <f>N5-Q5</f>
+        <v>51.94</v>
+      </c>
     </row>
     <row r="6" spans="3:26" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="C6" s="95" t="s">
@@ -11101,11 +11271,11 @@
       </c>
       <c r="D6" s="96">
         <f>D5*40</f>
-        <v>2520</v>
+        <v>3680</v>
       </c>
       <c r="E6" s="96">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>4640</v>
+        <v>5600</v>
       </c>
       <c r="F6" s="96">
         <f t="shared" si="1"/>
@@ -11113,7 +11283,7 @@
       </c>
       <c r="G6" s="97">
         <f>SUM(D6:F6)</f>
-        <v>7160</v>
+        <v>9280</v>
       </c>
       <c r="H6" s="89">
         <f>H5*40</f>
@@ -11121,7 +11291,7 @@
       </c>
       <c r="I6" s="90">
         <f>G6-H6</f>
-        <v>-392840</v>
+        <v>-390720</v>
       </c>
       <c r="K6" s="132" t="s">
         <v>2</v>
@@ -11130,14 +11300,21 @@
         <v>70</v>
       </c>
       <c r="M6" s="5">
-        <v>12154</v>
+        <v>13501</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>303.85000000000002</v>
+        <v>337.52499999999998</v>
       </c>
       <c r="O6" s="74"/>
       <c r="P6" s="133"/>
+      <c r="Q6">
+        <v>174.27</v>
+      </c>
+      <c r="R6" s="177">
+        <f t="shared" ref="R6:R10" si="2">N6-Q6</f>
+        <v>163.25499999999997</v>
+      </c>
       <c r="S6" s="116"/>
       <c r="T6" s="116"/>
       <c r="U6" s="122">
@@ -11165,14 +11342,21 @@
         <v>70</v>
       </c>
       <c r="M7" s="5">
-        <v>9169</v>
+        <v>12038</v>
       </c>
       <c r="N7" s="6">
         <f t="shared" si="0"/>
-        <v>229.22499999999999</v>
+        <v>300.95</v>
       </c>
       <c r="O7" s="74"/>
       <c r="P7" s="133"/>
+      <c r="Q7">
+        <v>76.239999999999995</v>
+      </c>
+      <c r="R7" s="177">
+        <f t="shared" si="2"/>
+        <v>224.70999999999998</v>
+      </c>
       <c r="S7" s="121" t="s">
         <v>85</v>
       </c>
@@ -11209,16 +11393,23 @@
         <v>120</v>
       </c>
       <c r="M8" s="5">
-        <v>8692</v>
+        <v>9642</v>
       </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>217.3</v>
+        <v>241.05</v>
       </c>
       <c r="O8" s="74">
         <v>50</v>
       </c>
       <c r="P8" s="133"/>
+      <c r="Q8">
+        <v>84.3</v>
+      </c>
+      <c r="R8" s="177">
+        <f t="shared" si="2"/>
+        <v>156.75</v>
+      </c>
       <c r="S8" s="72">
         <v>120</v>
       </c>
@@ -11249,11 +11440,11 @@
       </c>
       <c r="D9" s="98">
         <f>D8-D5</f>
-        <v>-63</v>
+        <v>-92</v>
       </c>
       <c r="E9" s="98">
         <f>E8-E5</f>
-        <v>-116</v>
+        <v>-140</v>
       </c>
       <c r="K9" s="132" t="s">
         <v>5</v>
@@ -11262,16 +11453,23 @@
         <v>120</v>
       </c>
       <c r="M9" s="5">
-        <v>5183</v>
+        <v>10707</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>129.57499999999999</v>
+        <v>267.67500000000001</v>
       </c>
       <c r="O9" s="74">
         <v>23</v>
       </c>
       <c r="P9" s="133"/>
+      <c r="Q9">
+        <v>109.17</v>
+      </c>
+      <c r="R9" s="177">
+        <f t="shared" si="2"/>
+        <v>158.505</v>
+      </c>
       <c r="S9" s="72">
         <v>120</v>
       </c>
@@ -11294,7 +11492,7 @@
         <v>1</v>
       </c>
       <c r="Z9" s="72">
-        <f t="shared" ref="Z9:Z13" si="2">SUM(U9:Y9)</f>
+        <f t="shared" ref="Z9:Z13" si="3">SUM(U9:Y9)</f>
         <v>80</v>
       </c>
     </row>
@@ -11306,14 +11504,21 @@
         <v>120</v>
       </c>
       <c r="M10" s="5">
-        <v>9154</v>
+        <v>10700</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>228.85</v>
+        <v>267.5</v>
       </c>
       <c r="O10" s="74"/>
       <c r="P10" s="133"/>
+      <c r="Q10">
+        <v>198.35</v>
+      </c>
+      <c r="R10" s="177">
+        <f t="shared" si="2"/>
+        <v>69.150000000000006</v>
+      </c>
       <c r="S10" s="72">
         <v>120</v>
       </c>
@@ -11332,7 +11537,7 @@
       </c>
       <c r="Y10" s="72"/>
       <c r="Z10" s="72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
     </row>
@@ -11351,10 +11556,12 @@
       <c r="L11" s="7">
         <v>60</v>
       </c>
-      <c r="M11" s="5"/>
+      <c r="M11" s="5">
+        <v>8</v>
+      </c>
       <c r="N11" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O11" s="74">
         <v>125</v>
@@ -11378,7 +11585,7 @@
         <v>1</v>
       </c>
       <c r="Z11" s="72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
@@ -11394,7 +11601,7 @@
       </c>
       <c r="G12" s="83">
         <f>D12+G5</f>
-        <v>4379</v>
+        <v>4432</v>
       </c>
       <c r="K12" s="132" t="s">
         <v>11</v>
@@ -11402,11 +11609,11 @@
       <c r="L12" s="74"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>56523</v>
+        <v>69362</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>1413.075</v>
+        <v>1734.05</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
@@ -11429,7 +11636,7 @@
         <v>1</v>
       </c>
       <c r="Z12" s="72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
@@ -11446,7 +11653,7 @@
       </c>
       <c r="G13" s="83">
         <f>G12*40</f>
-        <v>175160</v>
+        <v>177280</v>
       </c>
       <c r="S13" s="168" t="s">
         <v>83</v>
@@ -11457,23 +11664,23 @@
         <v>100</v>
       </c>
       <c r="V13" s="72">
-        <f t="shared" ref="V13:Y13" si="3">SUM(V8:V12)</f>
+        <f t="shared" ref="V13:Y13" si="4">SUM(V8:V12)</f>
         <v>9</v>
       </c>
       <c r="W13" s="72">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="X13" s="72">
+        <f t="shared" si="4"/>
+        <v>77</v>
+      </c>
+      <c r="Y13" s="72">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="Z13" s="5">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="X13" s="72">
-        <f t="shared" si="3"/>
-        <v>77</v>
-      </c>
-      <c r="Y13" s="72">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="Z13" s="5">
-        <f t="shared" si="2"/>
         <v>192</v>
       </c>
     </row>
@@ -11494,7 +11701,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="K17" s="105" t="s">
         <v>1</v>
       </c>
@@ -11505,10 +11712,16 @@
       <c r="N17" s="113"/>
       <c r="O17" s="114">
         <f>N17-M5</f>
-        <v>-12171</v>
-      </c>
-    </row>
-    <row r="18" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>-12766</v>
+      </c>
+      <c r="R17">
+        <v>51.94</v>
+      </c>
+      <c r="S17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="K18" s="1" t="s">
         <v>2</v>
       </c>
@@ -11519,10 +11732,16 @@
       <c r="N18" s="5"/>
       <c r="O18" s="114">
         <f>N18-M6</f>
-        <v>-12154</v>
-      </c>
-    </row>
-    <row r="19" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>-13501</v>
+      </c>
+      <c r="R18">
+        <v>163.25499999999997</v>
+      </c>
+      <c r="S18" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="F19" t="s">
         <v>87</v>
       </c>
@@ -11535,11 +11754,17 @@
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
       <c r="O19" s="114">
-        <f t="shared" ref="O19:O23" si="4">N19-M7</f>
-        <v>-9169</v>
-      </c>
-    </row>
-    <row r="20" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
+        <f t="shared" ref="O19:O23" si="5">N19-M7</f>
+        <v>-12038</v>
+      </c>
+      <c r="R19">
+        <v>224.70999999999998</v>
+      </c>
+      <c r="S19" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
       <c r="D20" s="169" t="s">
         <v>64</v>
       </c>
@@ -11556,11 +11781,17 @@
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
       <c r="O20" s="114">
-        <f t="shared" si="4"/>
-        <v>-8692</v>
-      </c>
-    </row>
-    <row r="21" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="5"/>
+        <v>-9642</v>
+      </c>
+      <c r="R20">
+        <v>156.75</v>
+      </c>
+      <c r="S20" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="D21" s="3" t="s">
         <v>0</v>
       </c>
@@ -11585,11 +11816,17 @@
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
       <c r="O21" s="114">
-        <f t="shared" si="4"/>
-        <v>-5183</v>
-      </c>
-    </row>
-    <row r="22" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="5"/>
+        <v>-10707</v>
+      </c>
+      <c r="R21">
+        <v>158.505</v>
+      </c>
+      <c r="S21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="D22" s="1" t="s">
         <v>1</v>
       </c>
@@ -11598,7 +11835,7 @@
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="6">
-        <f t="shared" ref="G22:G28" si="5">F22/40</f>
+        <f t="shared" ref="G22:G28" si="6">F22/40</f>
         <v>0</v>
       </c>
       <c r="H22" s="74"/>
@@ -11611,11 +11848,17 @@
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
       <c r="O22" s="114">
-        <f t="shared" si="4"/>
-        <v>-9154</v>
-      </c>
-    </row>
-    <row r="23" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="5"/>
+        <v>-10700</v>
+      </c>
+      <c r="R22">
+        <v>69.150000000000006</v>
+      </c>
+      <c r="S22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="D23" s="1" t="s">
         <v>2</v>
       </c>
@@ -11624,7 +11867,7 @@
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H23" s="74"/>
@@ -11637,11 +11880,11 @@
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
       <c r="O23" s="114">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
+        <f t="shared" si="5"/>
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="24" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
       <c r="D24" s="1" t="s">
         <v>3</v>
       </c>
@@ -11650,7 +11893,7 @@
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H24" s="74"/>
@@ -11668,10 +11911,10 @@
       </c>
       <c r="O24" s="109">
         <f>SUM(O17:O23)</f>
-        <v>-56523</v>
-      </c>
-    </row>
-    <row r="25" spans="4:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
+        <v>-69362</v>
+      </c>
+    </row>
+    <row r="25" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
       <c r="D25" s="1" t="s">
         <v>4</v>
       </c>
@@ -11680,7 +11923,7 @@
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H25" s="74"/>
@@ -11698,10 +11941,10 @@
       </c>
       <c r="O25" s="109">
         <f>O24/40</f>
-        <v>-1413.075</v>
-      </c>
-    </row>
-    <row r="26" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>-1734.05</v>
+      </c>
+    </row>
+    <row r="26" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="D26" s="1" t="s">
         <v>5</v>
       </c>
@@ -11710,12 +11953,12 @@
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H26" s="74"/>
     </row>
-    <row r="27" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="D27" s="1" t="s">
         <v>6</v>
       </c>
@@ -11724,12 +11967,12 @@
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H27" s="74"/>
     </row>
-    <row r="28" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="D28" s="1" t="s">
         <v>7</v>
       </c>
@@ -11738,12 +11981,12 @@
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H28" s="74"/>
     </row>
-    <row r="29" spans="4:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="D29" s="1" t="s">
         <v>11</v>
       </c>

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7525FB1-4109-4F1E-A4F4-C81211F4B258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52415CC2-4CA2-410F-9125-11C670AEA902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="162">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -402,9 +402,6 @@
     <t>Barki Road</t>
   </si>
   <si>
-    <t>Raheem Store Thoker Free Ctn</t>
-  </si>
-  <si>
     <t xml:space="preserve">Thoker </t>
   </si>
   <si>
@@ -448,6 +445,69 @@
   </si>
   <si>
     <t>FIVTN001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crown Super Market </t>
+  </si>
+  <si>
+    <t>Singh pura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euro Garhi Shahu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garhi Shahu </t>
+  </si>
+  <si>
+    <t>Gourmet Food Batapur</t>
+  </si>
+  <si>
+    <t>Batapur</t>
+  </si>
+  <si>
+    <t>Gourmet Shalimat Link Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Lal Pull </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Tajbagh </t>
+  </si>
+  <si>
+    <t>Gourmet Food Baghbanpura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CB Traders Risen Manawan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manawan </t>
+  </si>
+  <si>
+    <t>Sohail Traders SD</t>
+  </si>
+  <si>
+    <t>Kasoor</t>
+  </si>
+  <si>
+    <t>Swera Store</t>
+  </si>
+  <si>
+    <t>GT Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalal Sons Main Market </t>
+  </si>
+  <si>
+    <t>Gullberg Main Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalal Sons Lake City </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake city </t>
+  </si>
+  <si>
+    <t>Risen Store Thoker Free Ctn</t>
   </si>
 </sst>
 </file>
@@ -1315,7 +1375,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1685,11 +1745,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1789,7 +1845,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2372,7 +2427,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:X138"/>
+  <dimension ref="A1:X140"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.453125" bestFit="1" customWidth="1"/>
@@ -2382,13 +2437,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="144">
+      <c r="B1" s="142">
         <f ca="1">TODAY()</f>
-        <v>46300</v>
-      </c>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
+        <v>46302</v>
+      </c>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2410,10 +2465,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="165" t="s">
+      <c r="A2" s="163" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="145" t="s">
+      <c r="B2" s="143" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2443,13 +2498,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="157"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="159"/>
-      <c r="O2" s="160" t="s">
+      <c r="L2" s="155"/>
+      <c r="M2" s="156"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="158" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="161"/>
+      <c r="P2" s="159"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2468,8 +2523,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="165"/>
-      <c r="B3" s="146"/>
+      <c r="A3" s="163"/>
+      <c r="B3" s="144"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2497,29 +2552,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="162" t="s">
+      <c r="L3" s="160" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="163"/>
-      <c r="N3" s="164"/>
+      <c r="M3" s="161"/>
+      <c r="N3" s="162"/>
       <c r="O3" s="64"/>
       <c r="P3" s="65"/>
-      <c r="Q3" s="148" t="s">
+      <c r="Q3" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="149"/>
-      <c r="S3" s="149"/>
-      <c r="T3" s="150"/>
-      <c r="U3" s="151" t="s">
+      <c r="R3" s="147"/>
+      <c r="S3" s="147"/>
+      <c r="T3" s="148"/>
+      <c r="U3" s="149" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="152"/>
-      <c r="W3" s="152"/>
-      <c r="X3" s="153"/>
+      <c r="V3" s="150"/>
+      <c r="W3" s="150"/>
+      <c r="X3" s="151"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="165"/>
-      <c r="B4" s="147"/>
+      <c r="A4" s="163"/>
+      <c r="B4" s="145"/>
       <c r="C4" s="130" t="s">
         <v>90</v>
       </c>
@@ -2630,7 +2685,7 @@
         <v>2</v>
       </c>
       <c r="Q5" s="34" t="e">
-        <f t="shared" ref="Q5:Q46" si="1">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
+        <f t="shared" ref="Q5:Q48" si="1">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="R5" s="35">
@@ -2646,7 +2701,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="U5" s="37" t="e">
-        <f t="shared" ref="U5:U46" si="2">SUM(E5:E5)*$U$3</f>
+        <f t="shared" ref="U5:U48" si="2">SUM(E5:E5)*$U$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="V5" s="38">
@@ -2705,11 +2760,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="R6" s="45">
-        <f t="shared" ref="R6:R137" si="5">SUMPRODUCT($F$4:$H$4,$F$6:$H$6)*$R$3</f>
+        <f t="shared" ref="R6:R139" si="5">SUMPRODUCT($F$4:$H$4,$F$6:$H$6)*$R$3</f>
         <v>0</v>
       </c>
       <c r="S6" s="45">
-        <f t="shared" ref="S6:S137" si="6">SUMPRODUCT($I$4:$K$4,$I$6:$K$6)*$S$3</f>
+        <f t="shared" ref="S6:S139" si="6">SUMPRODUCT($I$4:$K$4,$I$6:$K$6)*$S$3</f>
         <v>0</v>
       </c>
       <c r="T6" s="46" t="e">
@@ -3244,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="T13" s="46" t="e">
-        <f t="shared" ref="T13:T137" si="15">SUM(Q13:S13)</f>
+        <f t="shared" ref="T13:T139" si="15">SUM(Q13:S13)</f>
         <v>#VALUE!</v>
       </c>
       <c r="U13" s="47" t="e">
@@ -3260,7 +3315,7 @@
         <v>0</v>
       </c>
       <c r="X13" s="49" t="e">
-        <f t="shared" ref="X13:X137" si="16">SUM(U13:W13)</f>
+        <f t="shared" ref="X13:X139" si="16">SUM(U13:W13)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3860,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="X21" s="49" t="e">
-        <f t="shared" ref="X21:X133" si="34">SUM(U21:W21)</f>
+        <f t="shared" ref="X21:X135" si="34">SUM(U21:W21)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4365,11 +4420,11 @@
       </c>
       <c r="N28" s="42"/>
       <c r="O28" s="66">
-        <f t="shared" ref="O28:O61" si="40">SUM(F28:H28)/20</f>
+        <f t="shared" ref="O28:O63" si="40">SUM(F28:H28)/20</f>
         <v>8</v>
       </c>
       <c r="P28" s="33">
-        <f t="shared" ref="P28:P61" si="41">SUM(I28:K28)/20</f>
+        <f t="shared" ref="P28:P63" si="41">SUM(I28:K28)/20</f>
         <v>2</v>
       </c>
       <c r="Q28" s="44" t="e">
@@ -4385,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="T28" s="46" t="e">
-        <f t="shared" ref="T28:T61" si="42">SUM(Q28:S28)</f>
+        <f t="shared" ref="T28:T63" si="42">SUM(Q28:S28)</f>
         <v>#VALUE!</v>
       </c>
       <c r="U28" s="47" t="e">
@@ -4393,15 +4448,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V28" s="48">
-        <f t="shared" ref="V28:V61" si="43">SUM(F28:H28)*$V$3</f>
+        <f t="shared" ref="V28:V63" si="43">SUM(F28:H28)*$V$3</f>
         <v>0</v>
       </c>
       <c r="W28" s="48">
-        <f t="shared" ref="W28:W61" si="44">SUM(I28:K28)*$W$3</f>
+        <f t="shared" ref="W28:W63" si="44">SUM(I28:K28)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X28" s="49" t="e">
-        <f t="shared" ref="X28:X61" si="45">SUM(U28:W28)</f>
+        <f t="shared" ref="X28:X63" si="45">SUM(U28:W28)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4779,27 +4834,27 @@
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A34" s="134">
+      <c r="A34" s="71">
         <v>46298</v>
       </c>
-      <c r="B34" s="135">
+      <c r="B34" s="40">
         <v>30</v>
       </c>
-      <c r="C34" s="141" t="s">
+      <c r="C34" s="131" t="s">
+        <v>161</v>
+      </c>
+      <c r="D34" s="131" t="s">
         <v>126</v>
       </c>
-      <c r="D34" s="141" t="s">
-        <v>127</v>
-      </c>
-      <c r="E34" s="142"/>
-      <c r="F34" s="142">
+      <c r="E34" s="68"/>
+      <c r="F34" s="68">
         <v>40</v>
       </c>
-      <c r="G34" s="142"/>
-      <c r="H34" s="143"/>
-      <c r="I34" s="142"/>
-      <c r="J34" s="142"/>
-      <c r="K34" s="142"/>
+      <c r="G34" s="68"/>
+      <c r="H34" s="124"/>
+      <c r="I34" s="68"/>
+      <c r="J34" s="68"/>
+      <c r="K34" s="68"/>
       <c r="L34" s="124">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -4807,11 +4862,11 @@
       <c r="M34" s="138"/>
       <c r="N34" s="42"/>
       <c r="O34" s="66">
-        <f t="shared" ref="O34:O47" si="52">SUM(F34:H34)/20</f>
+        <f t="shared" ref="O34:O49" si="52">SUM(F34:H34)/20</f>
         <v>2</v>
       </c>
       <c r="P34" s="33">
-        <f t="shared" ref="P34:P47" si="53">SUM(I34:K34)/20</f>
+        <f t="shared" ref="P34:P49" si="53">SUM(I34:K34)/20</f>
         <v>0</v>
       </c>
       <c r="Q34" s="44" t="e">
@@ -4827,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="46" t="e">
-        <f t="shared" ref="T34:T46" si="54">SUM(Q34:S34)</f>
+        <f t="shared" ref="T34:T48" si="54">SUM(Q34:S34)</f>
         <v>#VALUE!</v>
       </c>
       <c r="U34" s="47" t="e">
@@ -4835,46 +4890,46 @@
         <v>#VALUE!</v>
       </c>
       <c r="V34" s="48">
-        <f t="shared" ref="V34:V47" si="55">SUM(F34:H34)*$V$3</f>
+        <f t="shared" ref="V34:V49" si="55">SUM(F34:H34)*$V$3</f>
         <v>0</v>
       </c>
       <c r="W34" s="48">
-        <f t="shared" ref="W34:W47" si="56">SUM(I34:K34)*$W$3</f>
+        <f t="shared" ref="W34:W49" si="56">SUM(I34:K34)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X34" s="49" t="e">
-        <f t="shared" ref="X34:X46" si="57">SUM(U34:W34)</f>
+        <f t="shared" ref="X34:X48" si="57">SUM(U34:W34)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A35" s="134">
+      <c r="A35" s="71">
         <v>46298</v>
       </c>
-      <c r="B35" s="135">
+      <c r="B35" s="40">
         <v>31</v>
       </c>
-      <c r="C35" s="141" t="s">
+      <c r="C35" s="131" t="s">
+        <v>127</v>
+      </c>
+      <c r="D35" s="131" t="s">
         <v>128</v>
       </c>
-      <c r="D35" s="141" t="s">
-        <v>129</v>
-      </c>
-      <c r="E35" s="142"/>
-      <c r="F35" s="142">
+      <c r="E35" s="68"/>
+      <c r="F35" s="68">
         <v>40</v>
       </c>
-      <c r="G35" s="142">
+      <c r="G35" s="68">
         <v>40</v>
       </c>
-      <c r="H35" s="143">
+      <c r="H35" s="124">
         <v>40</v>
       </c>
-      <c r="I35" s="142"/>
-      <c r="J35" s="142">
+      <c r="I35" s="68"/>
+      <c r="J35" s="68">
         <v>40</v>
       </c>
-      <c r="K35" s="142">
+      <c r="K35" s="68">
         <v>80</v>
       </c>
       <c r="L35" s="124">
@@ -4927,29 +4982,29 @@
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A36" s="134">
+      <c r="A36" s="71">
         <v>46298</v>
       </c>
-      <c r="B36" s="135">
+      <c r="B36" s="40">
         <v>32</v>
       </c>
-      <c r="C36" s="141" t="s">
-        <v>130</v>
-      </c>
-      <c r="D36" s="141"/>
-      <c r="E36" s="142"/>
-      <c r="F36" s="142">
+      <c r="C36" s="131" t="s">
+        <v>129</v>
+      </c>
+      <c r="D36" s="131"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="68">
         <v>40</v>
       </c>
-      <c r="G36" s="142"/>
-      <c r="H36" s="143">
+      <c r="G36" s="68"/>
+      <c r="H36" s="124">
         <v>30</v>
       </c>
-      <c r="I36" s="142">
+      <c r="I36" s="68">
         <v>20</v>
       </c>
-      <c r="J36" s="142"/>
-      <c r="K36" s="142">
+      <c r="J36" s="68"/>
+      <c r="K36" s="68">
         <v>20</v>
       </c>
       <c r="L36" s="124">
@@ -5002,31 +5057,31 @@
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A37" s="134">
+      <c r="A37" s="71">
         <v>46298</v>
       </c>
-      <c r="B37" s="135">
+      <c r="B37" s="40">
         <v>33</v>
       </c>
-      <c r="C37" s="141" t="s">
-        <v>131</v>
-      </c>
-      <c r="D37" s="141"/>
-      <c r="E37" s="142"/>
-      <c r="F37" s="142"/>
-      <c r="G37" s="142"/>
-      <c r="H37" s="143"/>
-      <c r="I37" s="142">
+      <c r="C37" s="131" t="s">
+        <v>130</v>
+      </c>
+      <c r="D37" s="131"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="68"/>
+      <c r="H37" s="124"/>
+      <c r="I37" s="68">
         <v>20</v>
       </c>
-      <c r="J37" s="142">
+      <c r="J37" s="68">
         <v>20</v>
       </c>
-      <c r="K37" s="142">
+      <c r="K37" s="68">
         <v>20</v>
       </c>
       <c r="L37" s="124">
-        <f t="shared" ref="L37:L68" si="64">SUM(E37:K37)/40</f>
+        <f t="shared" ref="L37:L70" si="64">SUM(E37:K37)/40</f>
         <v>1.5</v>
       </c>
       <c r="M37" s="138">
@@ -5075,29 +5130,29 @@
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A38" s="134">
+      <c r="A38" s="71">
         <v>46298</v>
       </c>
-      <c r="B38" s="135">
+      <c r="B38" s="40">
         <v>34</v>
       </c>
-      <c r="C38" s="141" t="s">
-        <v>132</v>
-      </c>
-      <c r="D38" s="141"/>
-      <c r="E38" s="142"/>
-      <c r="F38" s="142"/>
-      <c r="G38" s="142">
+      <c r="C38" s="131" t="s">
+        <v>131</v>
+      </c>
+      <c r="D38" s="131"/>
+      <c r="E38" s="68"/>
+      <c r="F38" s="68"/>
+      <c r="G38" s="68">
         <v>40</v>
       </c>
-      <c r="H38" s="143"/>
-      <c r="I38" s="142">
+      <c r="H38" s="124"/>
+      <c r="I38" s="68">
         <v>20</v>
       </c>
-      <c r="J38" s="142">
+      <c r="J38" s="68">
         <v>20</v>
       </c>
-      <c r="K38" s="142">
+      <c r="K38" s="68">
         <v>20</v>
       </c>
       <c r="L38" s="124">
@@ -5150,31 +5205,31 @@
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A39" s="134">
+      <c r="A39" s="71">
         <v>46298</v>
       </c>
-      <c r="B39" s="135">
+      <c r="B39" s="40">
         <v>35</v>
       </c>
-      <c r="C39" s="141" t="s">
-        <v>133</v>
-      </c>
-      <c r="D39" s="141"/>
-      <c r="E39" s="142"/>
-      <c r="F39" s="142">
+      <c r="C39" s="131" t="s">
+        <v>132</v>
+      </c>
+      <c r="D39" s="131"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="68">
         <v>30</v>
       </c>
-      <c r="G39" s="142"/>
-      <c r="H39" s="143">
+      <c r="G39" s="68"/>
+      <c r="H39" s="124">
         <v>30</v>
       </c>
-      <c r="I39" s="142">
+      <c r="I39" s="68">
         <v>20</v>
       </c>
-      <c r="J39" s="142">
+      <c r="J39" s="68">
         <v>20</v>
       </c>
-      <c r="K39" s="142"/>
+      <c r="K39" s="68"/>
       <c r="L39" s="124">
         <f t="shared" si="64"/>
         <v>2.5</v>
@@ -5225,31 +5280,31 @@
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A40" s="134">
+      <c r="A40" s="71">
         <v>46298</v>
       </c>
-      <c r="B40" s="135">
+      <c r="B40" s="40">
         <v>36</v>
       </c>
-      <c r="C40" s="141" t="s">
-        <v>134</v>
-      </c>
-      <c r="D40" s="141"/>
-      <c r="E40" s="142"/>
-      <c r="F40" s="142"/>
-      <c r="G40" s="142">
+      <c r="C40" s="131" t="s">
+        <v>133</v>
+      </c>
+      <c r="D40" s="131"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="68">
         <v>30</v>
       </c>
-      <c r="H40" s="143">
+      <c r="H40" s="124">
         <v>40</v>
       </c>
-      <c r="I40" s="142">
+      <c r="I40" s="68">
         <v>20</v>
       </c>
-      <c r="J40" s="142">
+      <c r="J40" s="68">
         <v>20</v>
       </c>
-      <c r="K40" s="142">
+      <c r="K40" s="68">
         <v>20</v>
       </c>
       <c r="L40" s="124">
@@ -5302,50 +5357,52 @@
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A41" s="134">
+      <c r="A41" s="71">
         <v>46298</v>
       </c>
-      <c r="B41" s="135">
-        <v>37</v>
-      </c>
-      <c r="C41" s="141" t="s">
-        <v>135</v>
-      </c>
-      <c r="D41" s="141"/>
-      <c r="E41" s="142"/>
-      <c r="F41" s="142">
+      <c r="B41" s="40">
+        <v>36</v>
+      </c>
+      <c r="C41" s="131" t="s">
+        <v>159</v>
+      </c>
+      <c r="D41" s="131" t="s">
+        <v>160</v>
+      </c>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68">
+        <v>39</v>
+      </c>
+      <c r="G41" s="68">
         <v>40</v>
       </c>
-      <c r="G41" s="142">
-        <v>30</v>
-      </c>
-      <c r="H41" s="143">
+      <c r="H41" s="124">
         <v>40</v>
       </c>
-      <c r="I41" s="142">
-        <v>20</v>
-      </c>
-      <c r="J41" s="142">
-        <v>20</v>
-      </c>
-      <c r="K41" s="142">
-        <v>20</v>
+      <c r="I41" s="68">
+        <v>80</v>
+      </c>
+      <c r="J41" s="68">
+        <v>80</v>
+      </c>
+      <c r="K41" s="68">
+        <v>80</v>
       </c>
       <c r="L41" s="124">
         <f t="shared" si="64"/>
-        <v>4.25</v>
+        <v>8.9749999999999996</v>
       </c>
       <c r="M41" s="138">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N41" s="42"/>
       <c r="O41" s="66">
-        <f t="shared" si="52"/>
-        <v>5.5</v>
+        <f t="shared" ref="O41:O42" si="65">SUM(F41:H41)/20</f>
+        <v>5.95</v>
       </c>
       <c r="P41" s="33">
-        <f t="shared" si="53"/>
-        <v>3</v>
+        <f t="shared" ref="P41:P42" si="66">SUM(I41:K41)/20</f>
+        <v>12</v>
       </c>
       <c r="Q41" s="44" t="e">
         <f t="shared" si="1"/>
@@ -5360,53 +5417,73 @@
         <v>0</v>
       </c>
       <c r="T41" s="46" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" ref="T41:T42" si="67">SUM(Q41:S41)</f>
         <v>#VALUE!</v>
       </c>
       <c r="U41" s="47" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="U41:U42" si="68">SUM(E41:E41)*$U$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="V41" s="48">
-        <f t="shared" si="55"/>
+        <f t="shared" ref="V41:V42" si="69">SUM(F41:H41)*$V$3</f>
         <v>0</v>
       </c>
       <c r="W41" s="48">
-        <f t="shared" si="56"/>
+        <f t="shared" ref="W41:W42" si="70">SUM(I41:K41)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X41" s="49" t="e">
-        <f t="shared" si="57"/>
+        <f t="shared" ref="X41:X42" si="71">SUM(U41:W41)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A42" s="71"/>
+      <c r="A42" s="71">
+        <v>46298</v>
+      </c>
       <c r="B42" s="40">
-        <v>38</v>
-      </c>
-      <c r="C42" s="131"/>
-      <c r="D42" s="131"/>
+        <v>36</v>
+      </c>
+      <c r="C42" s="131" t="s">
+        <v>157</v>
+      </c>
+      <c r="D42" s="131" t="s">
+        <v>158</v>
+      </c>
       <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="68"/>
-      <c r="H42" s="124"/>
-      <c r="I42" s="68"/>
-      <c r="J42" s="68"/>
-      <c r="K42" s="68"/>
+      <c r="F42" s="68">
+        <v>160</v>
+      </c>
+      <c r="G42" s="68">
+        <v>80</v>
+      </c>
+      <c r="H42" s="124">
+        <v>240</v>
+      </c>
+      <c r="I42" s="68">
+        <v>200</v>
+      </c>
+      <c r="J42" s="68">
+        <v>160</v>
+      </c>
+      <c r="K42" s="68">
+        <v>400</v>
+      </c>
       <c r="L42" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M42" s="138"/>
+        <v>31</v>
+      </c>
+      <c r="M42" s="138">
+        <v>15</v>
+      </c>
       <c r="N42" s="42"/>
       <c r="O42" s="66">
-        <f t="shared" si="52"/>
-        <v>0</v>
+        <f t="shared" si="65"/>
+        <v>24</v>
       </c>
       <c r="P42" s="33">
-        <f t="shared" si="53"/>
-        <v>0</v>
+        <f t="shared" si="66"/>
+        <v>38</v>
       </c>
       <c r="Q42" s="44" t="e">
         <f t="shared" si="1"/>
@@ -5421,53 +5498,71 @@
         <v>0</v>
       </c>
       <c r="T42" s="46" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="67"/>
         <v>#VALUE!</v>
       </c>
       <c r="U42" s="47" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="68"/>
         <v>#VALUE!</v>
       </c>
       <c r="V42" s="48">
-        <f t="shared" si="55"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="W42" s="48">
-        <f t="shared" si="56"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="X42" s="49" t="e">
-        <f t="shared" si="57"/>
+        <f t="shared" si="71"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A43" s="71"/>
+      <c r="A43" s="71">
+        <v>46298</v>
+      </c>
       <c r="B43" s="40">
-        <v>39</v>
-      </c>
-      <c r="C43" s="131"/>
+        <v>37</v>
+      </c>
+      <c r="C43" s="131" t="s">
+        <v>134</v>
+      </c>
       <c r="D43" s="131"/>
       <c r="E43" s="68"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="68"/>
-      <c r="H43" s="124"/>
-      <c r="I43" s="68"/>
-      <c r="J43" s="68"/>
-      <c r="K43" s="68"/>
+      <c r="F43" s="68">
+        <v>40</v>
+      </c>
+      <c r="G43" s="68">
+        <v>30</v>
+      </c>
+      <c r="H43" s="124">
+        <v>40</v>
+      </c>
+      <c r="I43" s="68">
+        <v>20</v>
+      </c>
+      <c r="J43" s="68">
+        <v>20</v>
+      </c>
+      <c r="K43" s="68">
+        <v>20</v>
+      </c>
       <c r="L43" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M43" s="138"/>
+        <v>4.25</v>
+      </c>
+      <c r="M43" s="138">
+        <v>18</v>
+      </c>
       <c r="N43" s="42"/>
       <c r="O43" s="66">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P43" s="33">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q43" s="44" t="e">
         <f t="shared" si="1"/>
@@ -5503,32 +5598,52 @@
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A44" s="71"/>
+      <c r="A44" s="134">
+        <v>46301</v>
+      </c>
       <c r="B44" s="40">
+        <v>38</v>
+      </c>
+      <c r="C44" s="131" t="s">
+        <v>141</v>
+      </c>
+      <c r="D44" s="131" t="s">
+        <v>142</v>
+      </c>
+      <c r="E44" s="68"/>
+      <c r="F44" s="68">
+        <v>80</v>
+      </c>
+      <c r="G44" s="68">
         <v>40</v>
       </c>
-      <c r="C44" s="131"/>
-      <c r="D44" s="131"/>
-      <c r="E44" s="68"/>
-      <c r="F44" s="68"/>
-      <c r="G44" s="68"/>
-      <c r="H44" s="124"/>
-      <c r="I44" s="68"/>
-      <c r="J44" s="68"/>
-      <c r="K44" s="68"/>
+      <c r="H44" s="124">
+        <v>40</v>
+      </c>
+      <c r="I44" s="68">
+        <v>80</v>
+      </c>
+      <c r="J44" s="68">
+        <v>80</v>
+      </c>
+      <c r="K44" s="68">
+        <v>80</v>
+      </c>
       <c r="L44" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M44" s="138"/>
+        <v>10</v>
+      </c>
+      <c r="M44" s="138">
+        <v>12</v>
+      </c>
       <c r="N44" s="42"/>
       <c r="O44" s="66">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P44" s="33">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q44" s="44" t="e">
         <f t="shared" si="1"/>
@@ -5564,32 +5679,52 @@
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A45" s="71"/>
+      <c r="A45" s="134">
+        <v>46301</v>
+      </c>
       <c r="B45" s="40">
-        <v>41</v>
-      </c>
-      <c r="C45" s="131"/>
-      <c r="D45" s="131"/>
+        <v>39</v>
+      </c>
+      <c r="C45" s="131" t="s">
+        <v>143</v>
+      </c>
+      <c r="D45" s="131" t="s">
+        <v>144</v>
+      </c>
       <c r="E45" s="68"/>
-      <c r="F45" s="68"/>
-      <c r="G45" s="68"/>
-      <c r="H45" s="124"/>
-      <c r="I45" s="68"/>
-      <c r="J45" s="68"/>
-      <c r="K45" s="68"/>
+      <c r="F45" s="68">
+        <v>40</v>
+      </c>
+      <c r="G45" s="68">
+        <v>40</v>
+      </c>
+      <c r="H45" s="124">
+        <v>40</v>
+      </c>
+      <c r="I45" s="68">
+        <v>40</v>
+      </c>
+      <c r="J45" s="68">
+        <v>40</v>
+      </c>
+      <c r="K45" s="68">
+        <v>40</v>
+      </c>
       <c r="L45" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M45" s="138"/>
+        <v>6</v>
+      </c>
+      <c r="M45" s="138">
+        <v>14</v>
+      </c>
       <c r="N45" s="42"/>
       <c r="O45" s="66">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P45" s="33">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q45" s="44" t="e">
         <f t="shared" si="1"/>
@@ -5625,32 +5760,50 @@
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A46" s="71"/>
+      <c r="A46" s="134">
+        <v>46301</v>
+      </c>
       <c r="B46" s="40">
-        <v>42</v>
-      </c>
-      <c r="C46" s="131"/>
-      <c r="D46" s="131"/>
+        <v>40</v>
+      </c>
+      <c r="C46" s="131" t="s">
+        <v>145</v>
+      </c>
+      <c r="D46" s="131" t="s">
+        <v>146</v>
+      </c>
       <c r="E46" s="68"/>
       <c r="F46" s="68"/>
-      <c r="G46" s="68"/>
-      <c r="H46" s="124"/>
-      <c r="I46" s="68"/>
-      <c r="J46" s="68"/>
-      <c r="K46" s="68"/>
+      <c r="G46" s="68">
+        <v>40</v>
+      </c>
+      <c r="H46" s="124">
+        <v>40</v>
+      </c>
+      <c r="I46" s="68">
+        <v>40</v>
+      </c>
+      <c r="J46" s="68">
+        <v>40</v>
+      </c>
+      <c r="K46" s="68">
+        <v>40</v>
+      </c>
       <c r="L46" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M46" s="138"/>
+        <v>5</v>
+      </c>
+      <c r="M46" s="138">
+        <v>18</v>
+      </c>
       <c r="N46" s="42"/>
       <c r="O46" s="66">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P46" s="33">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q46" s="44" t="e">
         <f t="shared" si="1"/>
@@ -5686,24 +5839,34 @@
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A47" s="71"/>
+      <c r="A47" s="134">
+        <v>46301</v>
+      </c>
       <c r="B47" s="40">
-        <v>43</v>
-      </c>
-      <c r="C47" s="131"/>
+        <v>41</v>
+      </c>
+      <c r="C47" s="131" t="s">
+        <v>147</v>
+      </c>
       <c r="D47" s="131"/>
       <c r="E47" s="68"/>
       <c r="F47" s="68"/>
       <c r="G47" s="68"/>
       <c r="H47" s="124"/>
       <c r="I47" s="68"/>
-      <c r="J47" s="68"/>
-      <c r="K47" s="68"/>
+      <c r="J47" s="68">
+        <v>40</v>
+      </c>
+      <c r="K47" s="68">
+        <v>40</v>
+      </c>
       <c r="L47" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M47" s="138"/>
+        <v>2</v>
+      </c>
+      <c r="M47" s="138">
+        <v>18</v>
+      </c>
       <c r="N47" s="42"/>
       <c r="O47" s="66">
         <f t="shared" si="52"/>
@@ -5711,13 +5874,28 @@
       </c>
       <c r="P47" s="33">
         <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="Q47" s="44"/>
-      <c r="R47" s="45"/>
-      <c r="S47" s="45"/>
-      <c r="T47" s="46"/>
-      <c r="U47" s="47"/>
+        <v>4</v>
+      </c>
+      <c r="Q47" s="44" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R47" s="45">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="45">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="46" t="e">
+        <f t="shared" si="54"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U47" s="47" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="V47" s="48">
         <f t="shared" si="55"/>
         <v>0</v>
@@ -5726,78 +5904,117 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="X47" s="49"/>
+      <c r="X47" s="49" t="e">
+        <f t="shared" si="57"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A48" s="71"/>
+      <c r="A48" s="134">
+        <v>46301</v>
+      </c>
       <c r="B48" s="40">
-        <v>44</v>
-      </c>
-      <c r="C48" s="131"/>
+        <v>42</v>
+      </c>
+      <c r="C48" s="131" t="s">
+        <v>148</v>
+      </c>
       <c r="D48" s="131"/>
       <c r="E48" s="68"/>
       <c r="F48" s="68"/>
       <c r="G48" s="68"/>
-      <c r="H48" s="124"/>
+      <c r="H48" s="124">
+        <v>40</v>
+      </c>
       <c r="I48" s="68"/>
       <c r="J48" s="68"/>
       <c r="K48" s="68"/>
       <c r="L48" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M48" s="138"/>
+        <v>1</v>
+      </c>
+      <c r="M48" s="138">
+        <v>18</v>
+      </c>
       <c r="N48" s="42"/>
       <c r="O48" s="66">
-        <f t="shared" ref="O48:O60" si="65">SUM(F48:H48)/20</f>
-        <v>0</v>
+        <f t="shared" si="52"/>
+        <v>2</v>
       </c>
       <c r="P48" s="33">
-        <f t="shared" ref="P48:P60" si="66">SUM(I48:K48)/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q48" s="44"/>
-      <c r="R48" s="45"/>
-      <c r="S48" s="45"/>
-      <c r="T48" s="46"/>
-      <c r="U48" s="47"/>
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="44" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R48" s="45">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="45">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="46" t="e">
+        <f t="shared" si="54"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U48" s="47" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="V48" s="48">
-        <f t="shared" ref="V48:V60" si="67">SUM(F48:H48)*$V$3</f>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="W48" s="48">
-        <f t="shared" ref="W48:W60" si="68">SUM(I48:K48)*$W$3</f>
-        <v>0</v>
-      </c>
-      <c r="X48" s="49"/>
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="X48" s="49" t="e">
+        <f t="shared" si="57"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A49" s="71"/>
+      <c r="A49" s="134">
+        <v>46301</v>
+      </c>
       <c r="B49" s="40">
-        <v>45</v>
-      </c>
-      <c r="C49" s="131"/>
+        <v>43</v>
+      </c>
+      <c r="C49" s="131" t="s">
+        <v>149</v>
+      </c>
       <c r="D49" s="131"/>
       <c r="E49" s="68"/>
       <c r="F49" s="68"/>
       <c r="G49" s="68"/>
       <c r="H49" s="124"/>
-      <c r="I49" s="68"/>
+      <c r="I49" s="68">
+        <v>40</v>
+      </c>
       <c r="J49" s="68"/>
-      <c r="K49" s="68"/>
+      <c r="K49" s="68">
+        <v>40</v>
+      </c>
       <c r="L49" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M49" s="138"/>
+        <v>2</v>
+      </c>
+      <c r="M49" s="138">
+        <v>18</v>
+      </c>
       <c r="N49" s="42"/>
       <c r="O49" s="66">
-        <f t="shared" si="65"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="P49" s="33">
-        <f t="shared" si="66"/>
-        <v>0</v>
+        <f t="shared" si="53"/>
+        <v>4</v>
       </c>
       <c r="Q49" s="44"/>
       <c r="R49" s="45"/>
@@ -5805,42 +6022,56 @@
       <c r="T49" s="46"/>
       <c r="U49" s="47"/>
       <c r="V49" s="48">
-        <f t="shared" si="67"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="W49" s="48">
-        <f t="shared" si="68"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="X49" s="49"/>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A50" s="71"/>
+      <c r="A50" s="134">
+        <v>46301</v>
+      </c>
       <c r="B50" s="40">
-        <v>46</v>
-      </c>
-      <c r="C50" s="131"/>
+        <v>44</v>
+      </c>
+      <c r="C50" s="131" t="s">
+        <v>150</v>
+      </c>
       <c r="D50" s="131"/>
       <c r="E50" s="68"/>
       <c r="F50" s="68"/>
       <c r="G50" s="68"/>
-      <c r="H50" s="124"/>
-      <c r="I50" s="68"/>
-      <c r="J50" s="68"/>
-      <c r="K50" s="68"/>
+      <c r="H50" s="124">
+        <v>40</v>
+      </c>
+      <c r="I50" s="68">
+        <v>40</v>
+      </c>
+      <c r="J50" s="68">
+        <v>40</v>
+      </c>
+      <c r="K50" s="68">
+        <v>40</v>
+      </c>
       <c r="L50" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M50" s="138"/>
+        <v>4</v>
+      </c>
+      <c r="M50" s="138">
+        <v>18</v>
+      </c>
       <c r="N50" s="42"/>
       <c r="O50" s="66">
-        <f t="shared" si="65"/>
-        <v>0</v>
+        <f t="shared" ref="O50:O62" si="72">SUM(F50:H50)/20</f>
+        <v>2</v>
       </c>
       <c r="P50" s="33">
-        <f t="shared" si="66"/>
-        <v>0</v>
+        <f t="shared" ref="P50:P62" si="73">SUM(I50:K50)/20</f>
+        <v>6</v>
       </c>
       <c r="Q50" s="44"/>
       <c r="R50" s="45"/>
@@ -5848,42 +6079,58 @@
       <c r="T50" s="46"/>
       <c r="U50" s="47"/>
       <c r="V50" s="48">
-        <f t="shared" si="67"/>
+        <f t="shared" ref="V50:V62" si="74">SUM(F50:H50)*$V$3</f>
         <v>0</v>
       </c>
       <c r="W50" s="48">
-        <f t="shared" si="68"/>
+        <f t="shared" ref="W50:W62" si="75">SUM(I50:K50)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X50" s="49"/>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A51" s="71"/>
+      <c r="A51" s="134">
+        <v>46301</v>
+      </c>
       <c r="B51" s="40">
-        <v>47</v>
-      </c>
-      <c r="C51" s="131"/>
-      <c r="D51" s="131"/>
+        <v>45</v>
+      </c>
+      <c r="C51" s="131" t="s">
+        <v>151</v>
+      </c>
+      <c r="D51" s="131" t="s">
+        <v>152</v>
+      </c>
       <c r="E51" s="68"/>
       <c r="F51" s="68"/>
-      <c r="G51" s="68"/>
-      <c r="H51" s="124"/>
+      <c r="G51" s="68">
+        <v>40</v>
+      </c>
+      <c r="H51" s="124">
+        <v>80</v>
+      </c>
       <c r="I51" s="68"/>
-      <c r="J51" s="68"/>
-      <c r="K51" s="68"/>
+      <c r="J51" s="68">
+        <v>120</v>
+      </c>
+      <c r="K51" s="68">
+        <v>80</v>
+      </c>
       <c r="L51" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M51" s="138"/>
+        <v>8</v>
+      </c>
+      <c r="M51" s="138">
+        <v>14</v>
+      </c>
       <c r="N51" s="42"/>
       <c r="O51" s="66">
-        <f t="shared" si="65"/>
-        <v>0</v>
+        <f t="shared" si="72"/>
+        <v>6</v>
       </c>
       <c r="P51" s="33">
-        <f t="shared" si="66"/>
-        <v>0</v>
+        <f t="shared" si="73"/>
+        <v>10</v>
       </c>
       <c r="Q51" s="44"/>
       <c r="R51" s="45"/>
@@ -5891,42 +6138,58 @@
       <c r="T51" s="46"/>
       <c r="U51" s="47"/>
       <c r="V51" s="48">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="W51" s="48">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="X51" s="49"/>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A52" s="71"/>
+      <c r="A52" s="134">
+        <v>46301</v>
+      </c>
       <c r="B52" s="40">
-        <v>48</v>
-      </c>
-      <c r="C52" s="131"/>
-      <c r="D52" s="131"/>
+        <v>46</v>
+      </c>
+      <c r="C52" s="131" t="s">
+        <v>153</v>
+      </c>
+      <c r="D52" s="131" t="s">
+        <v>154</v>
+      </c>
       <c r="E52" s="68"/>
       <c r="F52" s="68"/>
       <c r="G52" s="68"/>
-      <c r="H52" s="124"/>
-      <c r="I52" s="68"/>
-      <c r="J52" s="68"/>
-      <c r="K52" s="68"/>
+      <c r="H52" s="124">
+        <v>600</v>
+      </c>
+      <c r="I52" s="68">
+        <v>800</v>
+      </c>
+      <c r="J52" s="68">
+        <v>1200</v>
+      </c>
+      <c r="K52" s="68">
+        <v>1000</v>
+      </c>
       <c r="L52" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M52" s="138"/>
+        <v>90</v>
+      </c>
+      <c r="M52" s="138">
+        <v>16</v>
+      </c>
       <c r="N52" s="42"/>
       <c r="O52" s="66">
-        <f t="shared" si="65"/>
-        <v>0</v>
+        <f t="shared" si="72"/>
+        <v>30</v>
       </c>
       <c r="P52" s="33">
-        <f t="shared" si="66"/>
-        <v>0</v>
+        <f t="shared" si="73"/>
+        <v>150</v>
       </c>
       <c r="Q52" s="44"/>
       <c r="R52" s="45"/>
@@ -5934,42 +6197,58 @@
       <c r="T52" s="46"/>
       <c r="U52" s="47"/>
       <c r="V52" s="48">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="W52" s="48">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="X52" s="49"/>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A53" s="71"/>
+      <c r="A53" s="134">
+        <v>46301</v>
+      </c>
       <c r="B53" s="40">
-        <v>49</v>
-      </c>
-      <c r="C53" s="125"/>
-      <c r="D53" s="125"/>
+        <v>47</v>
+      </c>
+      <c r="C53" s="131" t="s">
+        <v>155</v>
+      </c>
+      <c r="D53" s="131" t="s">
+        <v>156</v>
+      </c>
       <c r="E53" s="68"/>
       <c r="F53" s="68"/>
       <c r="G53" s="68"/>
-      <c r="H53" s="124"/>
-      <c r="I53" s="68"/>
-      <c r="J53" s="68"/>
-      <c r="K53" s="68"/>
+      <c r="H53" s="124">
+        <v>200</v>
+      </c>
+      <c r="I53" s="68">
+        <v>80</v>
+      </c>
+      <c r="J53" s="68">
+        <v>80</v>
+      </c>
+      <c r="K53" s="68">
+        <v>200</v>
+      </c>
       <c r="L53" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M53" s="138"/>
+        <v>14</v>
+      </c>
+      <c r="M53" s="138">
+        <v>12</v>
+      </c>
       <c r="N53" s="42"/>
       <c r="O53" s="66">
-        <f t="shared" si="65"/>
-        <v>0</v>
+        <f t="shared" si="72"/>
+        <v>10</v>
       </c>
       <c r="P53" s="33">
-        <f t="shared" si="66"/>
-        <v>0</v>
+        <f t="shared" si="73"/>
+        <v>18</v>
       </c>
       <c r="Q53" s="44"/>
       <c r="R53" s="45"/>
@@ -5977,11 +6256,11 @@
       <c r="T53" s="46"/>
       <c r="U53" s="47"/>
       <c r="V53" s="48">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="W53" s="48">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="X53" s="49"/>
@@ -5989,10 +6268,10 @@
     <row r="54" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A54" s="71"/>
       <c r="B54" s="40">
-        <v>50</v>
-      </c>
-      <c r="C54" s="125"/>
-      <c r="D54" s="125"/>
+        <v>48</v>
+      </c>
+      <c r="C54" s="131"/>
+      <c r="D54" s="131"/>
       <c r="E54" s="68"/>
       <c r="F54" s="68"/>
       <c r="G54" s="68"/>
@@ -6007,11 +6286,11 @@
       <c r="M54" s="138"/>
       <c r="N54" s="42"/>
       <c r="O54" s="66">
-        <f t="shared" si="65"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="P54" s="33">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="Q54" s="44"/>
@@ -6020,11 +6299,11 @@
       <c r="T54" s="46"/>
       <c r="U54" s="47"/>
       <c r="V54" s="48">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="W54" s="48">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="X54" s="49"/>
@@ -6032,7 +6311,7 @@
     <row r="55" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A55" s="71"/>
       <c r="B55" s="40">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C55" s="125"/>
       <c r="D55" s="125"/>
@@ -6050,11 +6329,11 @@
       <c r="M55" s="138"/>
       <c r="N55" s="42"/>
       <c r="O55" s="66">
-        <f t="shared" si="65"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="P55" s="33">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="Q55" s="44"/>
@@ -6063,11 +6342,11 @@
       <c r="T55" s="46"/>
       <c r="U55" s="47"/>
       <c r="V55" s="48">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="W55" s="48">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="X55" s="49"/>
@@ -6075,7 +6354,7 @@
     <row r="56" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A56" s="71"/>
       <c r="B56" s="40">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C56" s="125"/>
       <c r="D56" s="125"/>
@@ -6093,11 +6372,11 @@
       <c r="M56" s="138"/>
       <c r="N56" s="42"/>
       <c r="O56" s="66">
-        <f t="shared" si="65"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="P56" s="33">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="Q56" s="44"/>
@@ -6106,11 +6385,11 @@
       <c r="T56" s="46"/>
       <c r="U56" s="47"/>
       <c r="V56" s="48">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="W56" s="48">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="X56" s="49"/>
@@ -6118,7 +6397,7 @@
     <row r="57" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A57" s="71"/>
       <c r="B57" s="40">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C57" s="125"/>
       <c r="D57" s="125"/>
@@ -6136,11 +6415,11 @@
       <c r="M57" s="138"/>
       <c r="N57" s="42"/>
       <c r="O57" s="66">
-        <f t="shared" si="65"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="P57" s="33">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="Q57" s="44"/>
@@ -6149,11 +6428,11 @@
       <c r="T57" s="46"/>
       <c r="U57" s="47"/>
       <c r="V57" s="48">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="W57" s="48">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="X57" s="49"/>
@@ -6161,7 +6440,7 @@
     <row r="58" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A58" s="71"/>
       <c r="B58" s="40">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C58" s="125"/>
       <c r="D58" s="125"/>
@@ -6179,11 +6458,11 @@
       <c r="M58" s="138"/>
       <c r="N58" s="42"/>
       <c r="O58" s="66">
-        <f t="shared" si="65"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="P58" s="33">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="Q58" s="44"/>
@@ -6192,11 +6471,11 @@
       <c r="T58" s="46"/>
       <c r="U58" s="47"/>
       <c r="V58" s="48">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="W58" s="48">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="X58" s="49"/>
@@ -6204,7 +6483,7 @@
     <row r="59" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A59" s="71"/>
       <c r="B59" s="40">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C59" s="125"/>
       <c r="D59" s="125"/>
@@ -6222,11 +6501,11 @@
       <c r="M59" s="138"/>
       <c r="N59" s="42"/>
       <c r="O59" s="66">
-        <f t="shared" si="65"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="P59" s="33">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="Q59" s="44"/>
@@ -6235,11 +6514,11 @@
       <c r="T59" s="46"/>
       <c r="U59" s="47"/>
       <c r="V59" s="48">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="W59" s="48">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="X59" s="49"/>
@@ -6247,7 +6526,7 @@
     <row r="60" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A60" s="71"/>
       <c r="B60" s="40">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C60" s="125"/>
       <c r="D60" s="125"/>
@@ -6265,11 +6544,11 @@
       <c r="M60" s="138"/>
       <c r="N60" s="42"/>
       <c r="O60" s="66">
-        <f t="shared" si="65"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="P60" s="33">
-        <f t="shared" si="66"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="Q60" s="44"/>
@@ -6278,11 +6557,11 @@
       <c r="T60" s="46"/>
       <c r="U60" s="47"/>
       <c r="V60" s="48">
-        <f t="shared" si="67"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="W60" s="48">
-        <f t="shared" si="68"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="X60" s="49"/>
@@ -6290,7 +6569,7 @@
     <row r="61" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A61" s="71"/>
       <c r="B61" s="40">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C61" s="125"/>
       <c r="D61" s="125"/>
@@ -6308,50 +6587,32 @@
       <c r="M61" s="138"/>
       <c r="N61" s="42"/>
       <c r="O61" s="66">
-        <f t="shared" si="40"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="P61" s="33">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="Q61" s="44" t="e">
-        <f t="shared" ref="Q61:Q92" si="69">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R61" s="45">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S61" s="45">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T61" s="46" t="e">
-        <f t="shared" si="42"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U61" s="47" t="e">
-        <f t="shared" ref="U61:U92" si="70">SUM(E61:E61)*$U$3</f>
-        <v>#VALUE!</v>
-      </c>
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="Q61" s="44"/>
+      <c r="R61" s="45"/>
+      <c r="S61" s="45"/>
+      <c r="T61" s="46"/>
+      <c r="U61" s="47"/>
       <c r="V61" s="48">
-        <f t="shared" si="43"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="W61" s="48">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="X61" s="49" t="e">
-        <f t="shared" si="45"/>
-        <v>#VALUE!</v>
-      </c>
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="X61" s="49"/>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A62" s="71"/>
       <c r="B62" s="40">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C62" s="125"/>
       <c r="D62" s="125"/>
@@ -6369,50 +6630,32 @@
       <c r="M62" s="138"/>
       <c r="N62" s="42"/>
       <c r="O62" s="66">
-        <f t="shared" ref="O62:O79" si="71">SUM(F62:H62)/20</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="P62" s="33">
-        <f t="shared" ref="P62:P79" si="72">SUM(I62:K62)/20</f>
-        <v>0</v>
-      </c>
-      <c r="Q62" s="44" t="e">
-        <f t="shared" si="69"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R62" s="45">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S62" s="45">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T62" s="46" t="e">
-        <f t="shared" ref="T62:T79" si="73">SUM(Q62:S62)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U62" s="47" t="e">
-        <f t="shared" si="70"/>
-        <v>#VALUE!</v>
-      </c>
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="Q62" s="44"/>
+      <c r="R62" s="45"/>
+      <c r="S62" s="45"/>
+      <c r="T62" s="46"/>
+      <c r="U62" s="47"/>
       <c r="V62" s="48">
-        <f t="shared" ref="V62:V79" si="74">SUM(F62:H62)*$V$3</f>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="W62" s="48">
-        <f t="shared" ref="W62:W79" si="75">SUM(I62:K62)*$W$3</f>
-        <v>0</v>
-      </c>
-      <c r="X62" s="49" t="e">
-        <f t="shared" ref="X62:X79" si="76">SUM(U62:W62)</f>
-        <v>#VALUE!</v>
-      </c>
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="X62" s="49"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A63" s="71"/>
       <c r="B63" s="40">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C63" s="125"/>
       <c r="D63" s="125"/>
@@ -6430,15 +6673,15 @@
       <c r="M63" s="138"/>
       <c r="N63" s="42"/>
       <c r="O63" s="66">
-        <f t="shared" si="71"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="P63" s="33">
-        <f t="shared" si="72"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="Q63" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" ref="Q63:Q94" si="76">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="R63" s="45">
@@ -6450,30 +6693,30 @@
         <v>0</v>
       </c>
       <c r="T63" s="46" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="42"/>
         <v>#VALUE!</v>
       </c>
       <c r="U63" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" ref="U63:U94" si="77">SUM(E63:E63)*$U$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="V63" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="W63" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="X63" s="49" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="45"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A64" s="71"/>
       <c r="B64" s="40">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C64" s="125"/>
       <c r="D64" s="125"/>
@@ -6491,15 +6734,15 @@
       <c r="M64" s="138"/>
       <c r="N64" s="42"/>
       <c r="O64" s="66">
-        <f t="shared" si="71"/>
+        <f t="shared" ref="O64:O81" si="78">SUM(F64:H64)/20</f>
         <v>0</v>
       </c>
       <c r="P64" s="33">
-        <f t="shared" si="72"/>
+        <f t="shared" ref="P64:P81" si="79">SUM(I64:K64)/20</f>
         <v>0</v>
       </c>
       <c r="Q64" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R64" s="45">
@@ -6511,30 +6754,30 @@
         <v>0</v>
       </c>
       <c r="T64" s="46" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" ref="T64:T81" si="80">SUM(Q64:S64)</f>
         <v>#VALUE!</v>
       </c>
       <c r="U64" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V64" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" ref="V64:V81" si="81">SUM(F64:H64)*$V$3</f>
         <v>0</v>
       </c>
       <c r="W64" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" ref="W64:W81" si="82">SUM(I64:K64)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X64" s="49" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" ref="X64:X81" si="83">SUM(U64:W64)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A65" s="71"/>
       <c r="B65" s="40">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C65" s="125"/>
       <c r="D65" s="125"/>
@@ -6552,15 +6795,15 @@
       <c r="M65" s="138"/>
       <c r="N65" s="42"/>
       <c r="O65" s="66">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P65" s="33">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q65" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R65" s="45">
@@ -6572,30 +6815,30 @@
         <v>0</v>
       </c>
       <c r="T65" s="46" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>#VALUE!</v>
       </c>
       <c r="U65" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V65" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="W65" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="X65" s="49" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A66" s="71"/>
       <c r="B66" s="40">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C66" s="125"/>
       <c r="D66" s="125"/>
@@ -6613,15 +6856,15 @@
       <c r="M66" s="138"/>
       <c r="N66" s="42"/>
       <c r="O66" s="66">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P66" s="33">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q66" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R66" s="45">
@@ -6633,30 +6876,30 @@
         <v>0</v>
       </c>
       <c r="T66" s="46" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>#VALUE!</v>
       </c>
       <c r="U66" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V66" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="W66" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="X66" s="49" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A67" s="71"/>
       <c r="B67" s="40">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C67" s="125"/>
       <c r="D67" s="125"/>
@@ -6674,15 +6917,15 @@
       <c r="M67" s="138"/>
       <c r="N67" s="42"/>
       <c r="O67" s="66">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P67" s="33">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q67" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R67" s="45">
@@ -6694,30 +6937,30 @@
         <v>0</v>
       </c>
       <c r="T67" s="46" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>#VALUE!</v>
       </c>
       <c r="U67" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V67" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="W67" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="X67" s="49" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A68" s="71"/>
       <c r="B68" s="40">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C68" s="125"/>
       <c r="D68" s="125"/>
@@ -6735,15 +6978,15 @@
       <c r="M68" s="138"/>
       <c r="N68" s="42"/>
       <c r="O68" s="66">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P68" s="33">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q68" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R68" s="45">
@@ -6755,30 +6998,30 @@
         <v>0</v>
       </c>
       <c r="T68" s="46" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>#VALUE!</v>
       </c>
       <c r="U68" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V68" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="W68" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="X68" s="49" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A69" s="71"/>
       <c r="B69" s="40">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C69" s="125"/>
       <c r="D69" s="125"/>
@@ -6790,21 +7033,21 @@
       <c r="J69" s="68"/>
       <c r="K69" s="68"/>
       <c r="L69" s="124">
-        <f t="shared" ref="L69:L100" si="77">SUM(E69:K69)/40</f>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M69" s="138"/>
       <c r="N69" s="42"/>
       <c r="O69" s="66">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P69" s="33">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q69" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R69" s="45">
@@ -6816,30 +7059,30 @@
         <v>0</v>
       </c>
       <c r="T69" s="46" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>#VALUE!</v>
       </c>
       <c r="U69" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V69" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="W69" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="X69" s="49" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A70" s="71"/>
       <c r="B70" s="40">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C70" s="125"/>
       <c r="D70" s="125"/>
@@ -6851,21 +7094,21 @@
       <c r="J70" s="68"/>
       <c r="K70" s="68"/>
       <c r="L70" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="M70" s="138"/>
       <c r="N70" s="42"/>
       <c r="O70" s="66">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P70" s="33">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q70" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R70" s="45">
@@ -6877,30 +7120,30 @@
         <v>0</v>
       </c>
       <c r="T70" s="46" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>#VALUE!</v>
       </c>
       <c r="U70" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V70" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="W70" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="X70" s="49" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A71" s="71"/>
       <c r="B71" s="40">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C71" s="125"/>
       <c r="D71" s="125"/>
@@ -6912,21 +7155,21 @@
       <c r="J71" s="68"/>
       <c r="K71" s="68"/>
       <c r="L71" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" ref="L71:L102" si="84">SUM(E71:K71)/40</f>
         <v>0</v>
       </c>
       <c r="M71" s="138"/>
       <c r="N71" s="42"/>
       <c r="O71" s="66">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P71" s="33">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q71" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R71" s="45">
@@ -6938,30 +7181,30 @@
         <v>0</v>
       </c>
       <c r="T71" s="46" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>#VALUE!</v>
       </c>
       <c r="U71" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V71" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="W71" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="X71" s="49" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A72" s="71"/>
       <c r="B72" s="40">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C72" s="125"/>
       <c r="D72" s="125"/>
@@ -6973,21 +7216,21 @@
       <c r="J72" s="68"/>
       <c r="K72" s="68"/>
       <c r="L72" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M72" s="138"/>
       <c r="N72" s="42"/>
       <c r="O72" s="66">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P72" s="33">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q72" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R72" s="45">
@@ -6999,30 +7242,30 @@
         <v>0</v>
       </c>
       <c r="T72" s="46" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>#VALUE!</v>
       </c>
       <c r="U72" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V72" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="W72" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="X72" s="49" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A73" s="71"/>
       <c r="B73" s="40">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C73" s="125"/>
       <c r="D73" s="125"/>
@@ -7034,21 +7277,21 @@
       <c r="J73" s="68"/>
       <c r="K73" s="68"/>
       <c r="L73" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M73" s="138"/>
       <c r="N73" s="42"/>
       <c r="O73" s="66">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P73" s="33">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q73" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R73" s="45">
@@ -7060,30 +7303,30 @@
         <v>0</v>
       </c>
       <c r="T73" s="46" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>#VALUE!</v>
       </c>
       <c r="U73" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V73" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="W73" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="X73" s="49" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A74" s="71"/>
       <c r="B74" s="40">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C74" s="125"/>
       <c r="D74" s="125"/>
@@ -7095,21 +7338,21 @@
       <c r="J74" s="68"/>
       <c r="K74" s="68"/>
       <c r="L74" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M74" s="138"/>
       <c r="N74" s="42"/>
       <c r="O74" s="66">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P74" s="33">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q74" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R74" s="45">
@@ -7121,30 +7364,30 @@
         <v>0</v>
       </c>
       <c r="T74" s="46" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>#VALUE!</v>
       </c>
       <c r="U74" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V74" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="W74" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="X74" s="49" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A75" s="71"/>
       <c r="B75" s="40">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C75" s="125"/>
       <c r="D75" s="125"/>
@@ -7156,21 +7399,21 @@
       <c r="J75" s="68"/>
       <c r="K75" s="68"/>
       <c r="L75" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M75" s="138"/>
       <c r="N75" s="42"/>
       <c r="O75" s="66">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P75" s="33">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q75" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R75" s="45">
@@ -7182,30 +7425,30 @@
         <v>0</v>
       </c>
       <c r="T75" s="46" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>#VALUE!</v>
       </c>
       <c r="U75" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V75" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="W75" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="X75" s="49" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A76" s="71"/>
       <c r="B76" s="40">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C76" s="125"/>
       <c r="D76" s="125"/>
@@ -7217,21 +7460,21 @@
       <c r="J76" s="68"/>
       <c r="K76" s="68"/>
       <c r="L76" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M76" s="138"/>
       <c r="N76" s="42"/>
       <c r="O76" s="66">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P76" s="33">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q76" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R76" s="45">
@@ -7243,30 +7486,30 @@
         <v>0</v>
       </c>
       <c r="T76" s="46" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>#VALUE!</v>
       </c>
       <c r="U76" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V76" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="W76" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="X76" s="49" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A77" s="71"/>
       <c r="B77" s="40">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C77" s="125"/>
       <c r="D77" s="125"/>
@@ -7278,21 +7521,21 @@
       <c r="J77" s="68"/>
       <c r="K77" s="68"/>
       <c r="L77" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M77" s="138"/>
       <c r="N77" s="42"/>
       <c r="O77" s="66">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P77" s="33">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q77" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R77" s="45">
@@ -7304,30 +7547,30 @@
         <v>0</v>
       </c>
       <c r="T77" s="46" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>#VALUE!</v>
       </c>
       <c r="U77" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V77" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="W77" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="X77" s="49" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A78" s="71"/>
       <c r="B78" s="40">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C78" s="125"/>
       <c r="D78" s="125"/>
@@ -7339,21 +7582,21 @@
       <c r="J78" s="68"/>
       <c r="K78" s="68"/>
       <c r="L78" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M78" s="138"/>
       <c r="N78" s="42"/>
       <c r="O78" s="66">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P78" s="33">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q78" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R78" s="45">
@@ -7365,30 +7608,30 @@
         <v>0</v>
       </c>
       <c r="T78" s="46" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>#VALUE!</v>
       </c>
       <c r="U78" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V78" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="W78" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="X78" s="49" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A79" s="71"/>
       <c r="B79" s="40">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C79" s="125"/>
       <c r="D79" s="125"/>
@@ -7400,21 +7643,21 @@
       <c r="J79" s="68"/>
       <c r="K79" s="68"/>
       <c r="L79" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M79" s="138"/>
       <c r="N79" s="42"/>
       <c r="O79" s="66">
-        <f t="shared" si="71"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P79" s="33">
-        <f t="shared" si="72"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q79" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R79" s="45">
@@ -7426,30 +7669,30 @@
         <v>0</v>
       </c>
       <c r="T79" s="46" t="e">
-        <f t="shared" si="73"/>
+        <f t="shared" si="80"/>
         <v>#VALUE!</v>
       </c>
       <c r="U79" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V79" s="48">
-        <f t="shared" si="74"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="W79" s="48">
-        <f t="shared" si="75"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="X79" s="49" t="e">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A80" s="71"/>
       <c r="B80" s="40">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C80" s="125"/>
       <c r="D80" s="125"/>
@@ -7461,21 +7704,21 @@
       <c r="J80" s="68"/>
       <c r="K80" s="68"/>
       <c r="L80" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M80" s="138"/>
       <c r="N80" s="42"/>
       <c r="O80" s="66">
-        <f t="shared" ref="O80:O84" si="78">SUM(F80:H80)/20</f>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="P80" s="33">
-        <f t="shared" ref="P80:P84" si="79">SUM(I80:K80)/20</f>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="Q80" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R80" s="45">
@@ -7487,30 +7730,30 @@
         <v>0</v>
       </c>
       <c r="T80" s="46" t="e">
-        <f t="shared" ref="T80:T84" si="80">SUM(Q80:S80)</f>
+        <f t="shared" si="80"/>
         <v>#VALUE!</v>
       </c>
       <c r="U80" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V80" s="48">
-        <f t="shared" ref="V80:V84" si="81">SUM(F80:H80)*$V$3</f>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="W80" s="48">
-        <f t="shared" ref="W80:W84" si="82">SUM(I80:K80)*$W$3</f>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="X80" s="49" t="e">
-        <f t="shared" ref="X80:X84" si="83">SUM(U80:W80)</f>
+        <f t="shared" si="83"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A81" s="71"/>
       <c r="B81" s="40">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C81" s="125"/>
       <c r="D81" s="125"/>
@@ -7522,7 +7765,7 @@
       <c r="J81" s="68"/>
       <c r="K81" s="68"/>
       <c r="L81" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M81" s="138"/>
@@ -7536,7 +7779,7 @@
         <v>0</v>
       </c>
       <c r="Q81" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R81" s="45">
@@ -7552,7 +7795,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="U81" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V81" s="48">
@@ -7571,7 +7814,7 @@
     <row r="82" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A82" s="71"/>
       <c r="B82" s="40">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C82" s="125"/>
       <c r="D82" s="125"/>
@@ -7583,21 +7826,21 @@
       <c r="J82" s="68"/>
       <c r="K82" s="68"/>
       <c r="L82" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M82" s="138"/>
       <c r="N82" s="42"/>
       <c r="O82" s="66">
-        <f t="shared" si="78"/>
+        <f t="shared" ref="O82:O86" si="85">SUM(F82:H82)/20</f>
         <v>0</v>
       </c>
       <c r="P82" s="33">
-        <f t="shared" si="79"/>
+        <f t="shared" ref="P82:P86" si="86">SUM(I82:K82)/20</f>
         <v>0</v>
       </c>
       <c r="Q82" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R82" s="45">
@@ -7609,30 +7852,30 @@
         <v>0</v>
       </c>
       <c r="T82" s="46" t="e">
-        <f t="shared" si="80"/>
+        <f t="shared" ref="T82:T86" si="87">SUM(Q82:S82)</f>
         <v>#VALUE!</v>
       </c>
       <c r="U82" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V82" s="48">
-        <f t="shared" si="81"/>
+        <f t="shared" ref="V82:V86" si="88">SUM(F82:H82)*$V$3</f>
         <v>0</v>
       </c>
       <c r="W82" s="48">
-        <f t="shared" si="82"/>
+        <f t="shared" ref="W82:W86" si="89">SUM(I82:K82)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X82" s="49" t="e">
-        <f t="shared" si="83"/>
+        <f t="shared" ref="X82:X86" si="90">SUM(U82:W82)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A83" s="71"/>
       <c r="B83" s="40">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C83" s="125"/>
       <c r="D83" s="125"/>
@@ -7644,21 +7887,21 @@
       <c r="J83" s="68"/>
       <c r="K83" s="68"/>
       <c r="L83" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M83" s="138"/>
       <c r="N83" s="42"/>
       <c r="O83" s="66">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="P83" s="33">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="Q83" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R83" s="45">
@@ -7670,30 +7913,30 @@
         <v>0</v>
       </c>
       <c r="T83" s="46" t="e">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>#VALUE!</v>
       </c>
       <c r="U83" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V83" s="48">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="W83" s="48">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="X83" s="49" t="e">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A84" s="71"/>
       <c r="B84" s="40">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C84" s="125"/>
       <c r="D84" s="125"/>
@@ -7705,21 +7948,21 @@
       <c r="J84" s="68"/>
       <c r="K84" s="68"/>
       <c r="L84" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M84" s="138"/>
       <c r="N84" s="42"/>
       <c r="O84" s="66">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="P84" s="33">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="Q84" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R84" s="45">
@@ -7731,30 +7974,30 @@
         <v>0</v>
       </c>
       <c r="T84" s="46" t="e">
-        <f t="shared" si="80"/>
+        <f t="shared" si="87"/>
         <v>#VALUE!</v>
       </c>
       <c r="U84" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V84" s="48">
-        <f t="shared" si="81"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="W84" s="48">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="X84" s="49" t="e">
-        <f t="shared" si="83"/>
+        <f t="shared" si="90"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A85" s="71"/>
       <c r="B85" s="40">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C85" s="125"/>
       <c r="D85" s="125"/>
@@ -7766,21 +8009,21 @@
       <c r="J85" s="68"/>
       <c r="K85" s="68"/>
       <c r="L85" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M85" s="138"/>
       <c r="N85" s="42"/>
       <c r="O85" s="66">
-        <f t="shared" ref="O85:O132" si="84">SUM(F85:H85)/20</f>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="P85" s="33">
-        <f t="shared" ref="P85:P132" si="85">SUM(I85:K85)/20</f>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="Q85" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R85" s="45">
@@ -7792,30 +8035,30 @@
         <v>0</v>
       </c>
       <c r="T85" s="46" t="e">
-        <f t="shared" ref="T85:T132" si="86">SUM(Q85:S85)</f>
+        <f t="shared" si="87"/>
         <v>#VALUE!</v>
       </c>
       <c r="U85" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V85" s="48">
-        <f t="shared" ref="V85:V132" si="87">SUM(F85:H85)*$V$3</f>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="W85" s="48">
-        <f t="shared" ref="W85:W132" si="88">SUM(I85:K85)*$W$3</f>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="X85" s="49" t="e">
-        <f t="shared" ref="X85:X132" si="89">SUM(U85:W85)</f>
+        <f t="shared" si="90"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A86" s="71"/>
       <c r="B86" s="40">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C86" s="125"/>
       <c r="D86" s="125"/>
@@ -7827,21 +8070,21 @@
       <c r="J86" s="68"/>
       <c r="K86" s="68"/>
       <c r="L86" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M86" s="138"/>
       <c r="N86" s="42"/>
       <c r="O86" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="P86" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="Q86" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R86" s="45">
@@ -7853,30 +8096,30 @@
         <v>0</v>
       </c>
       <c r="T86" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>#VALUE!</v>
       </c>
       <c r="U86" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V86" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="W86" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="X86" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A87" s="71"/>
       <c r="B87" s="40">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C87" s="125"/>
       <c r="D87" s="125"/>
@@ -7888,21 +8131,21 @@
       <c r="J87" s="68"/>
       <c r="K87" s="68"/>
       <c r="L87" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M87" s="138"/>
       <c r="N87" s="42"/>
       <c r="O87" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" ref="O87:O134" si="91">SUM(F87:H87)/20</f>
         <v>0</v>
       </c>
       <c r="P87" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" ref="P87:P134" si="92">SUM(I87:K87)/20</f>
         <v>0</v>
       </c>
       <c r="Q87" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R87" s="45">
@@ -7914,30 +8157,30 @@
         <v>0</v>
       </c>
       <c r="T87" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" ref="T87:T134" si="93">SUM(Q87:S87)</f>
         <v>#VALUE!</v>
       </c>
       <c r="U87" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V87" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" ref="V87:V134" si="94">SUM(F87:H87)*$V$3</f>
         <v>0</v>
       </c>
       <c r="W87" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" ref="W87:W134" si="95">SUM(I87:K87)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X87" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" ref="X87:X134" si="96">SUM(U87:W87)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A88" s="71"/>
       <c r="B88" s="40">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C88" s="125"/>
       <c r="D88" s="125"/>
@@ -7949,21 +8192,21 @@
       <c r="J88" s="68"/>
       <c r="K88" s="68"/>
       <c r="L88" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M88" s="138"/>
       <c r="N88" s="42"/>
       <c r="O88" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P88" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q88" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R88" s="45">
@@ -7975,30 +8218,30 @@
         <v>0</v>
       </c>
       <c r="T88" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U88" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V88" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W88" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X88" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="89" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A89" s="71"/>
       <c r="B89" s="40">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C89" s="125"/>
       <c r="D89" s="125"/>
@@ -8010,21 +8253,21 @@
       <c r="J89" s="68"/>
       <c r="K89" s="68"/>
       <c r="L89" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M89" s="138"/>
       <c r="N89" s="42"/>
       <c r="O89" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P89" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q89" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R89" s="45">
@@ -8036,30 +8279,30 @@
         <v>0</v>
       </c>
       <c r="T89" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U89" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V89" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W89" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X89" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="90" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A90" s="71"/>
       <c r="B90" s="40">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C90" s="125"/>
       <c r="D90" s="125"/>
@@ -8071,21 +8314,21 @@
       <c r="J90" s="68"/>
       <c r="K90" s="68"/>
       <c r="L90" s="124">
-        <f t="shared" si="77"/>
-        <v>0</v>
-      </c>
-      <c r="M90" s="139"/>
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="M90" s="138"/>
       <c r="N90" s="42"/>
       <c r="O90" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P90" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q90" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R90" s="45">
@@ -8097,30 +8340,30 @@
         <v>0</v>
       </c>
       <c r="T90" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U90" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V90" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W90" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X90" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A91" s="71"/>
       <c r="B91" s="40">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C91" s="125"/>
       <c r="D91" s="125"/>
@@ -8132,21 +8375,21 @@
       <c r="J91" s="68"/>
       <c r="K91" s="68"/>
       <c r="L91" s="124">
-        <f t="shared" si="77"/>
-        <v>0</v>
-      </c>
-      <c r="M91" s="139"/>
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="M91" s="138"/>
       <c r="N91" s="42"/>
       <c r="O91" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P91" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q91" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R91" s="45">
@@ -8158,30 +8401,30 @@
         <v>0</v>
       </c>
       <c r="T91" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U91" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V91" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W91" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X91" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A92" s="71"/>
       <c r="B92" s="40">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C92" s="125"/>
       <c r="D92" s="125"/>
@@ -8193,21 +8436,21 @@
       <c r="J92" s="68"/>
       <c r="K92" s="68"/>
       <c r="L92" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M92" s="139"/>
       <c r="N92" s="42"/>
       <c r="O92" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P92" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q92" s="44" t="e">
-        <f t="shared" si="69"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R92" s="45">
@@ -8219,30 +8462,30 @@
         <v>0</v>
       </c>
       <c r="T92" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U92" s="47" t="e">
-        <f t="shared" si="70"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V92" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W92" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X92" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A93" s="71"/>
       <c r="B93" s="40">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C93" s="125"/>
       <c r="D93" s="125"/>
@@ -8254,21 +8497,21 @@
       <c r="J93" s="68"/>
       <c r="K93" s="68"/>
       <c r="L93" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M93" s="139"/>
       <c r="N93" s="42"/>
       <c r="O93" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P93" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q93" s="44" t="e">
-        <f t="shared" ref="Q93:Q124" si="90">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R93" s="45">
@@ -8280,30 +8523,30 @@
         <v>0</v>
       </c>
       <c r="T93" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U93" s="47" t="e">
-        <f t="shared" ref="U93:U124" si="91">SUM(E93:E93)*$U$3</f>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V93" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W93" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X93" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A94" s="71"/>
       <c r="B94" s="40">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C94" s="125"/>
       <c r="D94" s="125"/>
@@ -8315,21 +8558,21 @@
       <c r="J94" s="68"/>
       <c r="K94" s="68"/>
       <c r="L94" s="124">
-        <f t="shared" si="77"/>
-        <v>0</v>
-      </c>
-      <c r="M94" s="138"/>
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="M94" s="139"/>
       <c r="N94" s="42"/>
       <c r="O94" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P94" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q94" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="76"/>
         <v>#VALUE!</v>
       </c>
       <c r="R94" s="45">
@@ -8341,30 +8584,30 @@
         <v>0</v>
       </c>
       <c r="T94" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U94" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="77"/>
         <v>#VALUE!</v>
       </c>
       <c r="V94" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W94" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X94" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A95" s="71"/>
       <c r="B95" s="40">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C95" s="125"/>
       <c r="D95" s="125"/>
@@ -8376,21 +8619,21 @@
       <c r="J95" s="68"/>
       <c r="K95" s="68"/>
       <c r="L95" s="124">
-        <f t="shared" si="77"/>
-        <v>0</v>
-      </c>
-      <c r="M95" s="138"/>
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="M95" s="139"/>
       <c r="N95" s="42"/>
       <c r="O95" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P95" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q95" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" ref="Q95:Q126" si="97">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="R95" s="45">
@@ -8402,30 +8645,30 @@
         <v>0</v>
       </c>
       <c r="T95" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U95" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" ref="U95:U126" si="98">SUM(E95:E95)*$U$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="V95" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W95" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X95" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A96" s="71"/>
       <c r="B96" s="40">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C96" s="125"/>
       <c r="D96" s="125"/>
@@ -8437,21 +8680,21 @@
       <c r="J96" s="68"/>
       <c r="K96" s="68"/>
       <c r="L96" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M96" s="138"/>
       <c r="N96" s="42"/>
       <c r="O96" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P96" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q96" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R96" s="45">
@@ -8463,30 +8706,30 @@
         <v>0</v>
       </c>
       <c r="T96" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U96" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V96" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W96" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X96" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A97" s="71"/>
       <c r="B97" s="40">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C97" s="125"/>
       <c r="D97" s="125"/>
@@ -8498,21 +8741,21 @@
       <c r="J97" s="68"/>
       <c r="K97" s="68"/>
       <c r="L97" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M97" s="138"/>
       <c r="N97" s="42"/>
       <c r="O97" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P97" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q97" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R97" s="45">
@@ -8524,30 +8767,30 @@
         <v>0</v>
       </c>
       <c r="T97" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U97" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V97" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W97" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X97" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="98" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A98" s="71"/>
       <c r="B98" s="40">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C98" s="125"/>
       <c r="D98" s="125"/>
@@ -8559,21 +8802,21 @@
       <c r="J98" s="68"/>
       <c r="K98" s="68"/>
       <c r="L98" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M98" s="138"/>
       <c r="N98" s="42"/>
       <c r="O98" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P98" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q98" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R98" s="45">
@@ -8585,30 +8828,30 @@
         <v>0</v>
       </c>
       <c r="T98" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U98" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V98" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W98" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X98" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="99" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A99" s="71"/>
       <c r="B99" s="40">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C99" s="125"/>
       <c r="D99" s="125"/>
@@ -8620,21 +8863,21 @@
       <c r="J99" s="68"/>
       <c r="K99" s="68"/>
       <c r="L99" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M99" s="138"/>
       <c r="N99" s="42"/>
       <c r="O99" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P99" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q99" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R99" s="45">
@@ -8646,30 +8889,30 @@
         <v>0</v>
       </c>
       <c r="T99" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U99" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V99" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W99" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X99" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A100" s="71"/>
       <c r="B100" s="40">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C100" s="125"/>
       <c r="D100" s="125"/>
@@ -8681,21 +8924,21 @@
       <c r="J100" s="68"/>
       <c r="K100" s="68"/>
       <c r="L100" s="124">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M100" s="138"/>
       <c r="N100" s="42"/>
       <c r="O100" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P100" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q100" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R100" s="45">
@@ -8707,30 +8950,30 @@
         <v>0</v>
       </c>
       <c r="T100" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U100" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V100" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W100" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X100" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A101" s="71"/>
       <c r="B101" s="40">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C101" s="125"/>
       <c r="D101" s="125"/>
@@ -8742,21 +8985,21 @@
       <c r="J101" s="68"/>
       <c r="K101" s="68"/>
       <c r="L101" s="124">
-        <f t="shared" ref="L101:L132" si="92">SUM(E101:K101)/40</f>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M101" s="138"/>
       <c r="N101" s="42"/>
       <c r="O101" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P101" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q101" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R101" s="45">
@@ -8768,30 +9011,30 @@
         <v>0</v>
       </c>
       <c r="T101" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U101" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V101" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W101" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X101" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="102" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A102" s="71"/>
       <c r="B102" s="40">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C102" s="125"/>
       <c r="D102" s="125"/>
@@ -8803,21 +9046,21 @@
       <c r="J102" s="68"/>
       <c r="K102" s="68"/>
       <c r="L102" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="M102" s="138"/>
       <c r="N102" s="42"/>
       <c r="O102" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P102" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q102" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R102" s="45">
@@ -8829,30 +9072,30 @@
         <v>0</v>
       </c>
       <c r="T102" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U102" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V102" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W102" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X102" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A103" s="71"/>
       <c r="B103" s="40">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C103" s="125"/>
       <c r="D103" s="125"/>
@@ -8864,21 +9107,21 @@
       <c r="J103" s="68"/>
       <c r="K103" s="68"/>
       <c r="L103" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" ref="L103:L134" si="99">SUM(E103:K103)/40</f>
         <v>0</v>
       </c>
       <c r="M103" s="138"/>
       <c r="N103" s="42"/>
       <c r="O103" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P103" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q103" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R103" s="45">
@@ -8890,30 +9133,30 @@
         <v>0</v>
       </c>
       <c r="T103" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U103" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V103" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W103" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X103" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A104" s="71"/>
       <c r="B104" s="40">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C104" s="125"/>
       <c r="D104" s="125"/>
@@ -8925,21 +9168,21 @@
       <c r="J104" s="68"/>
       <c r="K104" s="68"/>
       <c r="L104" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M104" s="138"/>
       <c r="N104" s="42"/>
       <c r="O104" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P104" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q104" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R104" s="45">
@@ -8951,30 +9194,30 @@
         <v>0</v>
       </c>
       <c r="T104" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U104" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V104" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W104" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X104" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="105" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A105" s="71"/>
       <c r="B105" s="40">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C105" s="125"/>
       <c r="D105" s="125"/>
@@ -8986,21 +9229,21 @@
       <c r="J105" s="68"/>
       <c r="K105" s="68"/>
       <c r="L105" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M105" s="138"/>
       <c r="N105" s="42"/>
       <c r="O105" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P105" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q105" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R105" s="45">
@@ -9012,30 +9255,30 @@
         <v>0</v>
       </c>
       <c r="T105" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U105" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V105" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W105" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X105" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A106" s="71"/>
       <c r="B106" s="40">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C106" s="125"/>
       <c r="D106" s="125"/>
@@ -9047,21 +9290,21 @@
       <c r="J106" s="68"/>
       <c r="K106" s="68"/>
       <c r="L106" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M106" s="138"/>
       <c r="N106" s="42"/>
       <c r="O106" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P106" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q106" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R106" s="45">
@@ -9073,30 +9316,30 @@
         <v>0</v>
       </c>
       <c r="T106" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U106" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V106" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W106" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X106" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A107" s="71"/>
       <c r="B107" s="40">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C107" s="125"/>
       <c r="D107" s="125"/>
@@ -9108,21 +9351,21 @@
       <c r="J107" s="68"/>
       <c r="K107" s="68"/>
       <c r="L107" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M107" s="138"/>
       <c r="N107" s="42"/>
       <c r="O107" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P107" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q107" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R107" s="45">
@@ -9134,30 +9377,30 @@
         <v>0</v>
       </c>
       <c r="T107" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U107" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V107" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W107" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X107" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A108" s="71"/>
       <c r="B108" s="40">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C108" s="125"/>
       <c r="D108" s="125"/>
@@ -9169,21 +9412,21 @@
       <c r="J108" s="68"/>
       <c r="K108" s="68"/>
       <c r="L108" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M108" s="138"/>
       <c r="N108" s="42"/>
       <c r="O108" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P108" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q108" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R108" s="45">
@@ -9195,30 +9438,30 @@
         <v>0</v>
       </c>
       <c r="T108" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U108" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V108" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W108" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X108" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A109" s="71"/>
       <c r="B109" s="40">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C109" s="125"/>
       <c r="D109" s="125"/>
@@ -9230,21 +9473,21 @@
       <c r="J109" s="68"/>
       <c r="K109" s="68"/>
       <c r="L109" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M109" s="138"/>
       <c r="N109" s="42"/>
       <c r="O109" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P109" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q109" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R109" s="45">
@@ -9256,30 +9499,30 @@
         <v>0</v>
       </c>
       <c r="T109" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U109" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V109" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W109" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X109" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A110" s="71"/>
       <c r="B110" s="40">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C110" s="125"/>
       <c r="D110" s="125"/>
@@ -9291,21 +9534,21 @@
       <c r="J110" s="68"/>
       <c r="K110" s="68"/>
       <c r="L110" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M110" s="138"/>
       <c r="N110" s="42"/>
       <c r="O110" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P110" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q110" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R110" s="45">
@@ -9317,30 +9560,30 @@
         <v>0</v>
       </c>
       <c r="T110" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U110" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V110" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W110" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X110" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A111" s="71"/>
       <c r="B111" s="40">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C111" s="125"/>
       <c r="D111" s="125"/>
@@ -9352,21 +9595,21 @@
       <c r="J111" s="68"/>
       <c r="K111" s="68"/>
       <c r="L111" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M111" s="138"/>
       <c r="N111" s="42"/>
       <c r="O111" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P111" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q111" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R111" s="45">
@@ -9378,30 +9621,30 @@
         <v>0</v>
       </c>
       <c r="T111" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U111" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V111" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W111" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X111" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="112" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A112" s="71"/>
       <c r="B112" s="40">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C112" s="125"/>
       <c r="D112" s="125"/>
@@ -9413,21 +9656,21 @@
       <c r="J112" s="68"/>
       <c r="K112" s="68"/>
       <c r="L112" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M112" s="138"/>
       <c r="N112" s="42"/>
       <c r="O112" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P112" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q112" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R112" s="45">
@@ -9439,30 +9682,30 @@
         <v>0</v>
       </c>
       <c r="T112" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U112" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V112" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W112" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X112" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A113" s="71"/>
       <c r="B113" s="40">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C113" s="125"/>
       <c r="D113" s="125"/>
@@ -9474,21 +9717,21 @@
       <c r="J113" s="68"/>
       <c r="K113" s="68"/>
       <c r="L113" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M113" s="138"/>
       <c r="N113" s="42"/>
       <c r="O113" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P113" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q113" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R113" s="45">
@@ -9500,30 +9743,30 @@
         <v>0</v>
       </c>
       <c r="T113" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U113" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V113" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W113" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X113" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A114" s="71"/>
       <c r="B114" s="40">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C114" s="125"/>
       <c r="D114" s="125"/>
@@ -9535,21 +9778,21 @@
       <c r="J114" s="68"/>
       <c r="K114" s="68"/>
       <c r="L114" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M114" s="138"/>
       <c r="N114" s="42"/>
       <c r="O114" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P114" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q114" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R114" s="45">
@@ -9561,30 +9804,30 @@
         <v>0</v>
       </c>
       <c r="T114" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U114" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V114" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W114" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X114" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A115" s="71"/>
       <c r="B115" s="40">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C115" s="125"/>
       <c r="D115" s="125"/>
@@ -9596,21 +9839,21 @@
       <c r="J115" s="68"/>
       <c r="K115" s="68"/>
       <c r="L115" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M115" s="138"/>
       <c r="N115" s="42"/>
       <c r="O115" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P115" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q115" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R115" s="45">
@@ -9622,30 +9865,30 @@
         <v>0</v>
       </c>
       <c r="T115" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U115" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V115" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W115" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X115" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A116" s="71"/>
       <c r="B116" s="40">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C116" s="125"/>
       <c r="D116" s="125"/>
@@ -9657,21 +9900,21 @@
       <c r="J116" s="68"/>
       <c r="K116" s="68"/>
       <c r="L116" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M116" s="138"/>
       <c r="N116" s="42"/>
       <c r="O116" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P116" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q116" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R116" s="45">
@@ -9683,30 +9926,30 @@
         <v>0</v>
       </c>
       <c r="T116" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U116" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V116" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W116" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X116" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A117" s="71"/>
       <c r="B117" s="40">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C117" s="125"/>
       <c r="D117" s="125"/>
@@ -9718,21 +9961,21 @@
       <c r="J117" s="68"/>
       <c r="K117" s="68"/>
       <c r="L117" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M117" s="138"/>
       <c r="N117" s="42"/>
       <c r="O117" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P117" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q117" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R117" s="45">
@@ -9744,30 +9987,30 @@
         <v>0</v>
       </c>
       <c r="T117" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U117" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V117" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W117" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X117" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A118" s="71"/>
       <c r="B118" s="40">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C118" s="125"/>
       <c r="D118" s="125"/>
@@ -9779,21 +10022,21 @@
       <c r="J118" s="68"/>
       <c r="K118" s="68"/>
       <c r="L118" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M118" s="138"/>
       <c r="N118" s="42"/>
       <c r="O118" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P118" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q118" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R118" s="45">
@@ -9805,30 +10048,30 @@
         <v>0</v>
       </c>
       <c r="T118" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U118" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V118" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W118" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X118" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="119" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A119" s="71"/>
       <c r="B119" s="40">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C119" s="125"/>
       <c r="D119" s="125"/>
@@ -9840,21 +10083,21 @@
       <c r="J119" s="68"/>
       <c r="K119" s="68"/>
       <c r="L119" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M119" s="138"/>
       <c r="N119" s="42"/>
       <c r="O119" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P119" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q119" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R119" s="45">
@@ -9866,30 +10109,30 @@
         <v>0</v>
       </c>
       <c r="T119" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U119" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V119" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W119" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X119" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="120" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A120" s="71"/>
       <c r="B120" s="40">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C120" s="125"/>
       <c r="D120" s="125"/>
@@ -9901,21 +10144,21 @@
       <c r="J120" s="68"/>
       <c r="K120" s="68"/>
       <c r="L120" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M120" s="138"/>
       <c r="N120" s="42"/>
       <c r="O120" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P120" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q120" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R120" s="45">
@@ -9927,30 +10170,30 @@
         <v>0</v>
       </c>
       <c r="T120" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U120" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V120" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W120" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X120" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="121" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A121" s="71"/>
       <c r="B121" s="40">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C121" s="125"/>
       <c r="D121" s="125"/>
@@ -9962,21 +10205,21 @@
       <c r="J121" s="68"/>
       <c r="K121" s="68"/>
       <c r="L121" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M121" s="138"/>
       <c r="N121" s="42"/>
       <c r="O121" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P121" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q121" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R121" s="45">
@@ -9988,30 +10231,30 @@
         <v>0</v>
       </c>
       <c r="T121" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U121" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V121" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W121" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X121" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="122" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A122" s="71"/>
       <c r="B122" s="40">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C122" s="125"/>
       <c r="D122" s="125"/>
@@ -10023,21 +10266,21 @@
       <c r="J122" s="68"/>
       <c r="K122" s="68"/>
       <c r="L122" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M122" s="138"/>
       <c r="N122" s="42"/>
       <c r="O122" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P122" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q122" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R122" s="45">
@@ -10049,30 +10292,30 @@
         <v>0</v>
       </c>
       <c r="T122" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U122" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V122" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W122" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X122" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="123" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A123" s="71"/>
       <c r="B123" s="40">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C123" s="125"/>
       <c r="D123" s="125"/>
@@ -10084,21 +10327,21 @@
       <c r="J123" s="68"/>
       <c r="K123" s="68"/>
       <c r="L123" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M123" s="138"/>
       <c r="N123" s="42"/>
       <c r="O123" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P123" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q123" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R123" s="45">
@@ -10110,30 +10353,30 @@
         <v>0</v>
       </c>
       <c r="T123" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U123" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V123" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W123" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X123" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="124" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A124" s="71"/>
       <c r="B124" s="40">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C124" s="125"/>
       <c r="D124" s="125"/>
@@ -10145,21 +10388,21 @@
       <c r="J124" s="68"/>
       <c r="K124" s="68"/>
       <c r="L124" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M124" s="138"/>
       <c r="N124" s="42"/>
       <c r="O124" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P124" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q124" s="44" t="e">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R124" s="45">
@@ -10171,29 +10414,31 @@
         <v>0</v>
       </c>
       <c r="T124" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U124" s="47" t="e">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V124" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W124" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X124" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="125" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A125" s="71"/>
-      <c r="B125" s="40"/>
+      <c r="B125" s="40">
+        <v>119</v>
+      </c>
       <c r="C125" s="125"/>
       <c r="D125" s="125"/>
       <c r="E125" s="68"/>
@@ -10204,21 +10449,21 @@
       <c r="J125" s="68"/>
       <c r="K125" s="68"/>
       <c r="L125" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M125" s="138"/>
       <c r="N125" s="42"/>
       <c r="O125" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P125" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q125" s="44" t="e">
-        <f t="shared" ref="Q125:Q133" si="93">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R125" s="45">
@@ -10230,29 +10475,31 @@
         <v>0</v>
       </c>
       <c r="T125" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U125" s="47" t="e">
-        <f t="shared" ref="U125:U133" si="94">SUM(E125:E125)*$U$3</f>
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
       <c r="V125" s="48">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="W125" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X125" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="126" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A126" s="71"/>
-      <c r="B126" s="40"/>
+      <c r="B126" s="40">
+        <v>120</v>
+      </c>
       <c r="C126" s="125"/>
       <c r="D126" s="125"/>
       <c r="E126" s="68"/>
@@ -10263,24 +10510,21 @@
       <c r="J126" s="68"/>
       <c r="K126" s="68"/>
       <c r="L126" s="124">
-        <f t="shared" si="92"/>
-        <v>0</v>
-      </c>
-      <c r="M126" s="138">
-        <f t="shared" ref="M126:M133" si="95">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="99"/>
+        <v>0</v>
+      </c>
+      <c r="M126" s="138"/>
       <c r="N126" s="42"/>
       <c r="O126" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P126" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q126" s="44" t="e">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>#VALUE!</v>
       </c>
       <c r="R126" s="45">
@@ -10292,23 +10536,23 @@
         <v>0</v>
       </c>
       <c r="T126" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U126" s="47" t="e">
+        <f t="shared" si="98"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V126" s="48">
         <f t="shared" si="94"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V126" s="48">
-        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="W126" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X126" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10325,24 +10569,21 @@
       <c r="J127" s="68"/>
       <c r="K127" s="68"/>
       <c r="L127" s="124">
-        <f t="shared" si="92"/>
-        <v>0</v>
-      </c>
-      <c r="M127" s="138">
-        <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="99"/>
+        <v>0</v>
+      </c>
+      <c r="M127" s="138"/>
       <c r="N127" s="42"/>
       <c r="O127" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P127" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q127" s="44" t="e">
-        <f t="shared" si="93"/>
+        <f t="shared" ref="Q127:Q135" si="100">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="R127" s="45">
@@ -10354,23 +10595,23 @@
         <v>0</v>
       </c>
       <c r="T127" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U127" s="47" t="e">
+        <f t="shared" ref="U127:U135" si="101">SUM(E127:E127)*$U$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V127" s="48">
         <f t="shared" si="94"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V127" s="48">
-        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="W127" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X127" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10387,24 +10628,24 @@
       <c r="J128" s="68"/>
       <c r="K128" s="68"/>
       <c r="L128" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M128" s="138">
-        <f t="shared" si="95"/>
+        <f t="shared" ref="M128:M135" si="102">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N128" s="42"/>
       <c r="O128" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P128" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q128" s="44" t="e">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="R128" s="45">
@@ -10416,23 +10657,23 @@
         <v>0</v>
       </c>
       <c r="T128" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U128" s="47" t="e">
+        <f t="shared" si="101"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V128" s="48">
         <f t="shared" si="94"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V128" s="48">
-        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="W128" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X128" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10449,24 +10690,24 @@
       <c r="J129" s="68"/>
       <c r="K129" s="68"/>
       <c r="L129" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M129" s="138">
-        <f t="shared" si="95"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="N129" s="42"/>
       <c r="O129" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P129" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q129" s="44" t="e">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="R129" s="45">
@@ -10478,23 +10719,23 @@
         <v>0</v>
       </c>
       <c r="T129" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U129" s="47" t="e">
+        <f t="shared" si="101"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V129" s="48">
         <f t="shared" si="94"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V129" s="48">
-        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="W129" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X129" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10511,24 +10752,24 @@
       <c r="J130" s="68"/>
       <c r="K130" s="68"/>
       <c r="L130" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M130" s="138">
-        <f t="shared" si="95"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="N130" s="42"/>
       <c r="O130" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P130" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q130" s="44" t="e">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="R130" s="45">
@@ -10540,23 +10781,23 @@
         <v>0</v>
       </c>
       <c r="T130" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U130" s="47" t="e">
+        <f t="shared" si="101"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V130" s="48">
         <f t="shared" si="94"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V130" s="48">
-        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="W130" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X130" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10573,24 +10814,24 @@
       <c r="J131" s="68"/>
       <c r="K131" s="68"/>
       <c r="L131" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M131" s="138">
-        <f t="shared" si="95"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="N131" s="42"/>
       <c r="O131" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P131" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q131" s="44" t="e">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="R131" s="45">
@@ -10602,23 +10843,23 @@
         <v>0</v>
       </c>
       <c r="T131" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U131" s="47" t="e">
+        <f t="shared" si="101"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V131" s="48">
         <f t="shared" si="94"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V131" s="48">
-        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="W131" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X131" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10635,24 +10876,24 @@
       <c r="J132" s="68"/>
       <c r="K132" s="68"/>
       <c r="L132" s="124">
-        <f t="shared" si="92"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="M132" s="138">
-        <f t="shared" si="95"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="N132" s="42"/>
       <c r="O132" s="66">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="P132" s="33">
-        <f t="shared" si="85"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="Q132" s="44" t="e">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="R132" s="45">
@@ -10664,80 +10905,57 @@
         <v>0</v>
       </c>
       <c r="T132" s="46" t="e">
-        <f t="shared" si="86"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U132" s="47" t="e">
+        <f t="shared" si="101"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V132" s="48">
         <f t="shared" si="94"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V132" s="48">
-        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="W132" s="48">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X132" s="49" t="e">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="71"/>
-      <c r="B133" s="154" t="s">
-        <v>11</v>
-      </c>
-      <c r="C133" s="154"/>
-      <c r="D133" s="135"/>
-      <c r="E133" s="140">
-        <f t="shared" ref="E133:K133" si="96">SUM(E6:E61)</f>
-        <v>0</v>
-      </c>
-      <c r="F133" s="140">
-        <f t="shared" si="96"/>
-        <v>942</v>
-      </c>
-      <c r="G133" s="140">
-        <f t="shared" si="96"/>
-        <v>710</v>
-      </c>
-      <c r="H133" s="140">
-        <f t="shared" si="96"/>
-        <v>1211</v>
-      </c>
-      <c r="I133" s="140">
-        <f t="shared" si="96"/>
-        <v>755</v>
-      </c>
-      <c r="J133" s="140">
-        <f t="shared" si="96"/>
-        <v>757</v>
-      </c>
-      <c r="K133" s="140">
-        <f t="shared" si="96"/>
-        <v>1120</v>
-      </c>
+      <c r="B133" s="40"/>
+      <c r="C133" s="125"/>
+      <c r="D133" s="125"/>
+      <c r="E133" s="68"/>
+      <c r="F133" s="68"/>
+      <c r="G133" s="68"/>
+      <c r="H133" s="124"/>
+      <c r="I133" s="68"/>
+      <c r="J133" s="68"/>
+      <c r="K133" s="68"/>
       <c r="L133" s="124">
-        <f t="shared" ref="L133" si="97">SUM(E133:K133)/40</f>
-        <v>137.375</v>
+        <f t="shared" si="99"/>
+        <v>0</v>
       </c>
       <c r="M133" s="138">
-        <f t="shared" si="95"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="N133" s="42"/>
       <c r="O133" s="66">
-        <f t="shared" ref="O133:O137" si="98">SUM(F133:H133)/20</f>
-        <v>143.15</v>
+        <f t="shared" si="91"/>
+        <v>0</v>
       </c>
       <c r="P133" s="33">
-        <f t="shared" ref="P133:P137" si="99">SUM(I133:K133)/20</f>
-        <v>131.6</v>
+        <f t="shared" si="92"/>
+        <v>0</v>
       </c>
       <c r="Q133" s="44" t="e">
-        <f t="shared" si="93"/>
+        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="R133" s="45">
@@ -10749,385 +10967,532 @@
         <v>0</v>
       </c>
       <c r="T133" s="46" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
       <c r="U133" s="47" t="e">
+        <f t="shared" si="101"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V133" s="48">
         <f t="shared" si="94"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V133" s="48">
-        <f t="shared" ref="V133:V137" si="100">SUM(F133:H133)*$V$3</f>
         <v>0</v>
       </c>
       <c r="W133" s="48">
-        <f t="shared" ref="W133:W137" si="101">SUM(I133:K133)*$W$3</f>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="X133" s="49" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="134" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A134" s="71"/>
-      <c r="B134" s="99">
-        <v>0</v>
-      </c>
-      <c r="C134" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="D134" s="119"/>
-      <c r="E134" s="100"/>
-      <c r="F134" s="101"/>
-      <c r="G134" s="101"/>
-      <c r="H134" s="102"/>
-      <c r="I134" s="101"/>
-      <c r="J134" s="101"/>
-      <c r="K134" s="102"/>
-      <c r="L134" s="103">
-        <f>SUM(E134:K134)</f>
-        <v>0</v>
-      </c>
-      <c r="M134" s="32"/>
+      <c r="B134" s="40"/>
+      <c r="C134" s="125"/>
+      <c r="D134" s="125"/>
+      <c r="E134" s="68"/>
+      <c r="F134" s="68"/>
+      <c r="G134" s="68"/>
+      <c r="H134" s="124"/>
+      <c r="I134" s="68"/>
+      <c r="J134" s="68"/>
+      <c r="K134" s="68"/>
+      <c r="L134" s="124">
+        <f t="shared" si="99"/>
+        <v>0</v>
+      </c>
+      <c r="M134" s="138">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
       <c r="N134" s="42"/>
-      <c r="O134" s="66"/>
-      <c r="P134" s="33"/>
-      <c r="Q134" s="44"/>
-      <c r="R134" s="45"/>
-      <c r="S134" s="45"/>
-      <c r="T134" s="46"/>
-      <c r="U134" s="47"/>
-      <c r="V134" s="48"/>
-      <c r="W134" s="48"/>
-      <c r="X134" s="49"/>
+      <c r="O134" s="66">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="P134" s="33">
+        <f t="shared" si="92"/>
+        <v>0</v>
+      </c>
+      <c r="Q134" s="44" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R134" s="45">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S134" s="45">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T134" s="46" t="e">
+        <f t="shared" si="93"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U134" s="47" t="e">
+        <f t="shared" si="101"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V134" s="48">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="W134" s="48">
+        <f t="shared" si="95"/>
+        <v>0</v>
+      </c>
+      <c r="X134" s="49" t="e">
+        <f t="shared" si="96"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A135" s="71"/>
-      <c r="B135" s="40">
+      <c r="B135" s="152" t="s">
+        <v>11</v>
+      </c>
+      <c r="C135" s="152"/>
+      <c r="D135" s="135"/>
+      <c r="E135" s="140">
+        <f>SUM(E6:E63)</f>
+        <v>0</v>
+      </c>
+      <c r="F135" s="140">
+        <f>SUM(F6:F63)</f>
+        <v>1261</v>
+      </c>
+      <c r="G135" s="140">
+        <f>SUM(G6:G63)</f>
+        <v>990</v>
+      </c>
+      <c r="H135" s="140">
+        <f>SUM(H6:H63)</f>
+        <v>2571</v>
+      </c>
+      <c r="I135" s="140">
+        <f>SUM(I6:I63)</f>
+        <v>2155</v>
+      </c>
+      <c r="J135" s="140">
+        <f>SUM(J6:J63)</f>
+        <v>2637</v>
+      </c>
+      <c r="K135" s="140">
+        <f>SUM(K6:K63)</f>
+        <v>3160</v>
+      </c>
+      <c r="L135" s="124">
+        <f t="shared" ref="L135" si="103">SUM(E135:K135)/40</f>
+        <v>319.35000000000002</v>
+      </c>
+      <c r="M135" s="138">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="N135" s="42"/>
+      <c r="O135" s="66">
+        <f t="shared" ref="O135:O139" si="104">SUM(F135:H135)/20</f>
+        <v>241.1</v>
+      </c>
+      <c r="P135" s="33">
+        <f t="shared" ref="P135:P139" si="105">SUM(I135:K135)/20</f>
+        <v>397.6</v>
+      </c>
+      <c r="Q135" s="44" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R135" s="45">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S135" s="45">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T135" s="46" t="e">
+        <f t="shared" si="15"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U135" s="47" t="e">
+        <f t="shared" si="101"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V135" s="48">
+        <f t="shared" ref="V135:V139" si="106">SUM(F135:H135)*$V$3</f>
+        <v>0</v>
+      </c>
+      <c r="W135" s="48">
+        <f t="shared" ref="W135:W139" si="107">SUM(I135:K135)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X135" s="49" t="e">
+        <f t="shared" si="34"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A136" s="71"/>
+      <c r="B136" s="99">
+        <v>0</v>
+      </c>
+      <c r="C136" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="D136" s="119"/>
+      <c r="E136" s="100"/>
+      <c r="F136" s="101"/>
+      <c r="G136" s="101"/>
+      <c r="H136" s="102"/>
+      <c r="I136" s="101"/>
+      <c r="J136" s="101"/>
+      <c r="K136" s="102"/>
+      <c r="L136" s="103">
+        <f>SUM(E136:K136)</f>
+        <v>0</v>
+      </c>
+      <c r="M136" s="32"/>
+      <c r="N136" s="42"/>
+      <c r="O136" s="66"/>
+      <c r="P136" s="33"/>
+      <c r="Q136" s="44"/>
+      <c r="R136" s="45"/>
+      <c r="S136" s="45"/>
+      <c r="T136" s="46"/>
+      <c r="U136" s="47"/>
+      <c r="V136" s="48"/>
+      <c r="W136" s="48"/>
+      <c r="X136" s="49"/>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A137" s="71"/>
+      <c r="B137" s="40">
         <v>1</v>
       </c>
-      <c r="C135" s="50" t="s">
+      <c r="C137" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="D135" s="119"/>
-      <c r="E135" s="67"/>
-      <c r="F135" s="43"/>
-      <c r="G135" s="68"/>
-      <c r="H135" s="42"/>
-      <c r="I135" s="43"/>
-      <c r="J135" s="68"/>
-      <c r="K135" s="69"/>
-      <c r="L135" s="41">
-        <f>SUM(E135:K135)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M135" s="32">
+      <c r="D137" s="119"/>
+      <c r="E137" s="67"/>
+      <c r="F137" s="43"/>
+      <c r="G137" s="68"/>
+      <c r="H137" s="42"/>
+      <c r="I137" s="43"/>
+      <c r="J137" s="68"/>
+      <c r="K137" s="69"/>
+      <c r="L137" s="41">
+        <f>SUM(E137:K137)/40</f>
+        <v>0</v>
+      </c>
+      <c r="M137" s="32">
         <f>SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
-      <c r="N135" s="42">
+      <c r="N137" s="42">
         <f>SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
         <v>3.5513000000000003</v>
       </c>
-      <c r="O135" s="66">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="P135" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="Q135" s="44" t="e">
+      <c r="O137" s="66">
+        <f t="shared" si="104"/>
+        <v>0</v>
+      </c>
+      <c r="P137" s="33">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="Q137" s="44" t="e">
         <f>SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R135" s="45">
+      <c r="R137" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S135" s="45">
+      <c r="S137" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T135" s="46" t="e">
+      <c r="T137" s="46" t="e">
         <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
-      <c r="U135" s="47" t="e">
-        <f>SUM(E135:E135)*$U$3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V135" s="48">
-        <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="W135" s="48">
-        <f t="shared" si="101"/>
-        <v>0</v>
-      </c>
-      <c r="X135" s="49" t="e">
+      <c r="U137" s="47" t="e">
+        <f>SUM(E137:E137)*$U$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V137" s="48">
+        <f t="shared" si="106"/>
+        <v>0</v>
+      </c>
+      <c r="W137" s="48">
+        <f t="shared" si="107"/>
+        <v>0</v>
+      </c>
+      <c r="X137" s="49" t="e">
         <f t="shared" si="16"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="136" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="B136" s="40">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="B138" s="40">
         <v>2</v>
       </c>
-      <c r="C136" s="50" t="s">
+      <c r="C138" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="D136" s="119"/>
-      <c r="E136" s="67"/>
-      <c r="F136" s="43"/>
-      <c r="G136" s="68"/>
-      <c r="H136" s="42"/>
-      <c r="I136" s="43"/>
-      <c r="J136" s="68"/>
-      <c r="K136" s="69"/>
-      <c r="L136" s="41">
-        <f>SUM(E136:K136)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M136" s="32">
+      <c r="D138" s="119"/>
+      <c r="E138" s="67"/>
+      <c r="F138" s="43"/>
+      <c r="G138" s="68"/>
+      <c r="H138" s="42"/>
+      <c r="I138" s="43"/>
+      <c r="J138" s="68"/>
+      <c r="K138" s="69"/>
+      <c r="L138" s="41">
+        <f>SUM(E138:K138)/40</f>
+        <v>0</v>
+      </c>
+      <c r="M138" s="32">
         <f>SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
-      <c r="N136" s="42">
+      <c r="N138" s="42">
         <f>SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
         <v>3.5513000000000003</v>
       </c>
-      <c r="O136" s="66">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="P136" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="Q136" s="44" t="e">
+      <c r="O138" s="66">
+        <f t="shared" si="104"/>
+        <v>0</v>
+      </c>
+      <c r="P138" s="33">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="Q138" s="44" t="e">
         <f>SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R136" s="45">
+      <c r="R138" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S136" s="45">
+      <c r="S138" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T136" s="46" t="e">
+      <c r="T138" s="46" t="e">
         <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
-      <c r="U136" s="47" t="e">
-        <f>SUM(E136:E136)*$U$3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V136" s="48">
-        <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="W136" s="48">
-        <f t="shared" si="101"/>
-        <v>0</v>
-      </c>
-      <c r="X136" s="49" t="e">
+      <c r="U138" s="47" t="e">
+        <f>SUM(E138:E138)*$U$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V138" s="48">
+        <f t="shared" si="106"/>
+        <v>0</v>
+      </c>
+      <c r="W138" s="48">
+        <f t="shared" si="107"/>
+        <v>0</v>
+      </c>
+      <c r="X138" s="49" t="e">
         <f t="shared" si="16"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="137" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="166" t="s">
+    <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B139" s="164" t="s">
         <v>68</v>
       </c>
-      <c r="C137" s="167"/>
-      <c r="D137" s="128"/>
-      <c r="E137" s="76">
-        <f>SUM(E135:E136)</f>
-        <v>0</v>
-      </c>
-      <c r="F137" s="76">
-        <f t="shared" ref="F137:K137" si="102">SUM(F135:F136)</f>
-        <v>0</v>
-      </c>
-      <c r="G137" s="76">
-        <f t="shared" si="102"/>
-        <v>0</v>
-      </c>
-      <c r="H137" s="76">
-        <f t="shared" si="102"/>
-        <v>0</v>
-      </c>
-      <c r="I137" s="76">
-        <f t="shared" si="102"/>
-        <v>0</v>
-      </c>
-      <c r="J137" s="76">
-        <f t="shared" si="102"/>
-        <v>0</v>
-      </c>
-      <c r="K137" s="76">
-        <f t="shared" si="102"/>
-        <v>0</v>
-      </c>
-      <c r="L137" s="104">
-        <f>SUM(L134:L136)</f>
-        <v>0</v>
-      </c>
-      <c r="M137" s="52">
+      <c r="C139" s="165"/>
+      <c r="D139" s="128"/>
+      <c r="E139" s="76">
+        <f>SUM(E137:E138)</f>
+        <v>0</v>
+      </c>
+      <c r="F139" s="76">
+        <f t="shared" ref="F139:K139" si="108">SUM(F137:F138)</f>
+        <v>0</v>
+      </c>
+      <c r="G139" s="76">
+        <f t="shared" si="108"/>
+        <v>0</v>
+      </c>
+      <c r="H139" s="76">
+        <f t="shared" si="108"/>
+        <v>0</v>
+      </c>
+      <c r="I139" s="76">
+        <f t="shared" si="108"/>
+        <v>0</v>
+      </c>
+      <c r="J139" s="76">
+        <f t="shared" si="108"/>
+        <v>0</v>
+      </c>
+      <c r="K139" s="76">
+        <f t="shared" si="108"/>
+        <v>0</v>
+      </c>
+      <c r="L139" s="104">
+        <f>SUM(L136:L138)</f>
+        <v>0</v>
+      </c>
+      <c r="M139" s="52">
         <f>SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
-      <c r="N137" s="51">
+      <c r="N139" s="51">
         <f>SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
         <v>3.5513000000000003</v>
       </c>
-      <c r="O137" s="66">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="P137" s="33">
-        <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="Q137" s="44" t="e">
+      <c r="O139" s="66">
+        <f t="shared" si="104"/>
+        <v>0</v>
+      </c>
+      <c r="P139" s="33">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="Q139" s="44" t="e">
         <f>SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R137" s="45">
+      <c r="R139" s="45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S137" s="45">
+      <c r="S139" s="45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T137" s="46" t="e">
+      <c r="T139" s="46" t="e">
         <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
-      <c r="U137" s="47" t="e">
-        <f>SUM(E137:E137)*$U$3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V137" s="48">
-        <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="W137" s="48">
-        <f t="shared" si="101"/>
-        <v>0</v>
-      </c>
-      <c r="X137" s="49" t="e">
+      <c r="U139" s="47" t="e">
+        <f>SUM(E139:E139)*$U$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V139" s="48">
+        <f t="shared" si="106"/>
+        <v>0</v>
+      </c>
+      <c r="W139" s="48">
+        <f t="shared" si="107"/>
+        <v>0</v>
+      </c>
+      <c r="X139" s="49" t="e">
         <f t="shared" si="16"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="138" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="155" t="s">
+    <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B140" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="156"/>
-      <c r="D138" s="129"/>
-      <c r="E138" s="77">
-        <f>SUM(E133,E137)</f>
-        <v>0</v>
-      </c>
-      <c r="F138" s="77">
-        <f t="shared" ref="F138:K138" si="103">SUM(F133,F137)</f>
-        <v>942</v>
-      </c>
-      <c r="G138" s="77">
-        <f t="shared" si="103"/>
-        <v>710</v>
-      </c>
-      <c r="H138" s="77">
-        <f t="shared" si="103"/>
-        <v>1211</v>
-      </c>
-      <c r="I138" s="77">
-        <f t="shared" si="103"/>
-        <v>755</v>
-      </c>
-      <c r="J138" s="77">
-        <f t="shared" si="103"/>
-        <v>757</v>
-      </c>
-      <c r="K138" s="77">
-        <f t="shared" si="103"/>
-        <v>1120</v>
-      </c>
-      <c r="L138" s="53">
-        <f>SUM(E138:K138)/40</f>
-        <v>137.375</v>
-      </c>
-      <c r="M138" s="56">
-        <f>SUM(M5:M137)</f>
-        <v>596</v>
-      </c>
-      <c r="N138" s="54">
-        <f t="shared" ref="N138:X138" si="104">SUM(N5:N137)</f>
+      <c r="C140" s="154"/>
+      <c r="D140" s="129"/>
+      <c r="E140" s="77">
+        <f>SUM(E135,E139)</f>
+        <v>0</v>
+      </c>
+      <c r="F140" s="77">
+        <f t="shared" ref="F140:K140" si="109">SUM(F135,F139)</f>
+        <v>1261</v>
+      </c>
+      <c r="G140" s="77">
+        <f t="shared" si="109"/>
+        <v>990</v>
+      </c>
+      <c r="H140" s="77">
+        <f t="shared" si="109"/>
+        <v>2571</v>
+      </c>
+      <c r="I140" s="77">
+        <f t="shared" si="109"/>
+        <v>2155</v>
+      </c>
+      <c r="J140" s="77">
+        <f t="shared" si="109"/>
+        <v>2637</v>
+      </c>
+      <c r="K140" s="77">
+        <f t="shared" si="109"/>
+        <v>3160</v>
+      </c>
+      <c r="L140" s="53">
+        <f>SUM(E140:K140)/40</f>
+        <v>319.35000000000002</v>
+      </c>
+      <c r="M140" s="56">
+        <f>SUM(M5:M139)</f>
+        <v>784</v>
+      </c>
+      <c r="N140" s="54">
+        <f t="shared" ref="N140:X140" si="110">SUM(N5:N139)</f>
         <v>10.6539</v>
       </c>
-      <c r="O138" s="55">
-        <f t="shared" si="104"/>
-        <v>289.8</v>
-      </c>
-      <c r="P138" s="57">
-        <f t="shared" si="104"/>
-        <v>265.2</v>
-      </c>
-      <c r="Q138" s="58" t="e">
-        <f t="shared" si="104"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="R138" s="59">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="S138" s="59">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="T138" s="60" t="e">
-        <f t="shared" si="104"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="U138" s="61" t="e">
-        <f t="shared" si="104"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V138" s="62">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="W138" s="62">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="X138" s="63" t="e">
-        <f t="shared" si="104"/>
+      <c r="O140" s="55">
+        <f t="shared" si="110"/>
+        <v>485.7</v>
+      </c>
+      <c r="P140" s="57">
+        <f t="shared" si="110"/>
+        <v>797.2</v>
+      </c>
+      <c r="Q140" s="58" t="e">
+        <f t="shared" si="110"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R140" s="59">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="S140" s="59">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="T140" s="60" t="e">
+        <f t="shared" si="110"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U140" s="61" t="e">
+        <f t="shared" si="110"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V140" s="62">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="W140" s="62">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="X140" s="63" t="e">
+        <f t="shared" si="110"/>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B140:C140"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B139:C139"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="Q3:T3"/>
     <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B135:C135"/>
   </mergeCells>
-  <conditionalFormatting sqref="C46:D60">
+  <conditionalFormatting sqref="C48:D62">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11161,25 +11526,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="168" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="171"/>
-      <c r="G3" s="172"/>
-      <c r="H3" s="174" t="s">
+      <c r="D3" s="169"/>
+      <c r="E3" s="169"/>
+      <c r="F3" s="169"/>
+      <c r="G3" s="170"/>
+      <c r="H3" s="172" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="175"/>
-      <c r="K3" s="176" t="s">
+      <c r="I3" s="173"/>
+      <c r="K3" s="174" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="176"/>
-      <c r="M3" s="176"/>
-      <c r="N3" s="176"/>
-      <c r="O3" s="176"/>
-      <c r="P3" s="176"/>
+      <c r="L3" s="174"/>
+      <c r="M3" s="174"/>
+      <c r="N3" s="174"/>
+      <c r="O3" s="174"/>
+      <c r="P3" s="174"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="91"/>
@@ -11225,22 +11590,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="80">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="E5" s="72">
-        <v>140</v>
-      </c>
-      <c r="F5" s="72"/>
+        <v>232</v>
+      </c>
+      <c r="F5" s="72">
+        <v>90</v>
+      </c>
       <c r="G5" s="94">
         <f>SUM(D5:F5)</f>
-        <v>232</v>
+        <v>481</v>
       </c>
       <c r="H5" s="87">
         <v>10000</v>
       </c>
       <c r="I5" s="88">
         <f>G5-H5</f>
-        <v>-9768</v>
+        <v>-9519</v>
       </c>
       <c r="K5" s="132" t="s">
         <v>1</v>
@@ -11260,7 +11627,7 @@
       <c r="Q5">
         <v>267.20999999999998</v>
       </c>
-      <c r="R5" s="177">
+      <c r="R5" s="141">
         <f>N5-Q5</f>
         <v>51.94</v>
       </c>
@@ -11271,19 +11638,19 @@
       </c>
       <c r="D6" s="96">
         <f>D5*40</f>
-        <v>3680</v>
+        <v>6360</v>
       </c>
       <c r="E6" s="96">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>5600</v>
+        <v>9280</v>
       </c>
       <c r="F6" s="96">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="G6" s="97">
         <f>SUM(D6:F6)</f>
-        <v>9280</v>
+        <v>19240</v>
       </c>
       <c r="H6" s="89">
         <f>H5*40</f>
@@ -11291,7 +11658,7 @@
       </c>
       <c r="I6" s="90">
         <f>G6-H6</f>
-        <v>-390720</v>
+        <v>-380760</v>
       </c>
       <c r="K6" s="132" t="s">
         <v>2</v>
@@ -11311,7 +11678,7 @@
       <c r="Q6">
         <v>174.27</v>
       </c>
-      <c r="R6" s="177">
+      <c r="R6" s="141">
         <f t="shared" ref="R6:R10" si="2">N6-Q6</f>
         <v>163.25499999999997</v>
       </c>
@@ -11353,7 +11720,7 @@
       <c r="Q7">
         <v>76.239999999999995</v>
       </c>
-      <c r="R7" s="177">
+      <c r="R7" s="141">
         <f t="shared" si="2"/>
         <v>224.70999999999998</v>
       </c>
@@ -11406,7 +11773,7 @@
       <c r="Q8">
         <v>84.3</v>
       </c>
-      <c r="R8" s="177">
+      <c r="R8" s="141">
         <f t="shared" si="2"/>
         <v>156.75</v>
       </c>
@@ -11440,11 +11807,11 @@
       </c>
       <c r="D9" s="98">
         <f>D8-D5</f>
-        <v>-92</v>
+        <v>-159</v>
       </c>
       <c r="E9" s="98">
         <f>E8-E5</f>
-        <v>-140</v>
+        <v>-232</v>
       </c>
       <c r="K9" s="132" t="s">
         <v>5</v>
@@ -11466,7 +11833,7 @@
       <c r="Q9">
         <v>109.17</v>
       </c>
-      <c r="R9" s="177">
+      <c r="R9" s="141">
         <f t="shared" si="2"/>
         <v>158.505</v>
       </c>
@@ -11515,7 +11882,7 @@
       <c r="Q10">
         <v>198.35</v>
       </c>
-      <c r="R10" s="177">
+      <c r="R10" s="141">
         <f t="shared" si="2"/>
         <v>69.150000000000006</v>
       </c>
@@ -11542,14 +11909,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="173" t="s">
+      <c r="C11" s="171" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="173"/>
-      <c r="F11" s="173" t="s">
+      <c r="D11" s="171"/>
+      <c r="F11" s="171" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="173"/>
+      <c r="G11" s="171"/>
       <c r="K11" s="132" t="s">
         <v>7</v>
       </c>
@@ -11601,7 +11968,7 @@
       </c>
       <c r="G12" s="83">
         <f>D12+G5</f>
-        <v>4432</v>
+        <v>4681</v>
       </c>
       <c r="K12" s="132" t="s">
         <v>11</v>
@@ -11653,12 +12020,12 @@
       </c>
       <c r="G13" s="83">
         <f>G12*40</f>
-        <v>177280</v>
-      </c>
-      <c r="S13" s="168" t="s">
+        <v>187240</v>
+      </c>
+      <c r="S13" s="166" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="168"/>
+      <c r="T13" s="166"/>
       <c r="U13" s="120">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -11718,7 +12085,7 @@
         <v>51.94</v>
       </c>
       <c r="S17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -11738,7 +12105,7 @@
         <v>163.25499999999997</v>
       </c>
       <c r="S18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -11761,17 +12128,17 @@
         <v>224.70999999999998</v>
       </c>
       <c r="S19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="169" t="s">
+      <c r="D20" s="167" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="169"/>
-      <c r="F20" s="169"/>
-      <c r="G20" s="169"/>
-      <c r="H20" s="169"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="167"/>
+      <c r="G20" s="167"/>
+      <c r="H20" s="167"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
@@ -11788,7 +12155,7 @@
         <v>156.75</v>
       </c>
       <c r="S20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -11823,7 +12190,7 @@
         <v>158.505</v>
       </c>
       <c r="S21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -11855,7 +12222,7 @@
         <v>69.150000000000006</v>
       </c>
       <c r="S22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52415CC2-4CA2-410F-9125-11C670AEA902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D175B6A-A446-4188-A6F7-28353D660152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="191">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -508,6 +508,93 @@
   </si>
   <si>
     <t>Risen Store Thoker Free Ctn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Zahor Ilahi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zahoor Ilahi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadbagh </t>
+  </si>
+  <si>
+    <t>Gourmet Food Begam Kot</t>
+  </si>
+  <si>
+    <t>Begam Kot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet food Kot abdul malik </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kot Abdul Malik </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Shadra </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadra Town </t>
+  </si>
+  <si>
+    <t>Gourmet Food Bilal Gunj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilal Gunj </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Qilla Gujjer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qilla Gujjer Singh </t>
+  </si>
+  <si>
+    <t>Imamia Colony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Badami Bagh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Badami Bagh </t>
+  </si>
+  <si>
+    <t>Gourmet Food Awan Market</t>
+  </si>
+  <si>
+    <t>Awan Market</t>
+  </si>
+  <si>
+    <t>Rehmanpura</t>
+  </si>
+  <si>
+    <t>Gourmet Food Ismail Nagar</t>
+  </si>
+  <si>
+    <t>Ismail Nagar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Kanah </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kanah </t>
+  </si>
+  <si>
+    <t>Imperia Departmental Store</t>
+  </si>
+  <si>
+    <t>Wahdat Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pak Madina </t>
+  </si>
+  <si>
+    <t>Shaikhupura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB Traders (Risen) Shadbagh </t>
+  </si>
+  <si>
+    <t>Shadbagh</t>
   </si>
 </sst>
 </file>
@@ -1375,7 +1462,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1844,6 +1931,15 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2439,7 +2535,7 @@
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="142">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C1" s="142"/>
       <c r="D1" s="142"/>
@@ -5598,7 +5694,7 @@
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A44" s="134">
+      <c r="A44" s="175">
         <v>46301</v>
       </c>
       <c r="B44" s="40">
@@ -5679,7 +5775,7 @@
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A45" s="134">
+      <c r="A45" s="175">
         <v>46301</v>
       </c>
       <c r="B45" s="40">
@@ -5760,7 +5856,7 @@
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A46" s="134">
+      <c r="A46" s="175">
         <v>46301</v>
       </c>
       <c r="B46" s="40">
@@ -5839,7 +5935,7 @@
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A47" s="134">
+      <c r="A47" s="175">
         <v>46301</v>
       </c>
       <c r="B47" s="40">
@@ -5910,7 +6006,7 @@
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A48" s="134">
+      <c r="A48" s="175">
         <v>46301</v>
       </c>
       <c r="B48" s="40">
@@ -5979,7 +6075,7 @@
       </c>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A49" s="134">
+      <c r="A49" s="175">
         <v>46301</v>
       </c>
       <c r="B49" s="40">
@@ -6032,7 +6128,7 @@
       <c r="X49" s="49"/>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A50" s="134">
+      <c r="A50" s="175">
         <v>46301</v>
       </c>
       <c r="B50" s="40">
@@ -6089,7 +6185,7 @@
       <c r="X50" s="49"/>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A51" s="134">
+      <c r="A51" s="175">
         <v>46301</v>
       </c>
       <c r="B51" s="40">
@@ -6148,7 +6244,7 @@
       <c r="X51" s="49"/>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A52" s="134">
+      <c r="A52" s="175">
         <v>46301</v>
       </c>
       <c r="B52" s="40">
@@ -6207,7 +6303,7 @@
       <c r="X52" s="49"/>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A53" s="134">
+      <c r="A53" s="175">
         <v>46301</v>
       </c>
       <c r="B53" s="40">
@@ -6266,28 +6362,40 @@
       <c r="X53" s="49"/>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A54" s="71"/>
+      <c r="A54" s="134">
+        <v>46302</v>
+      </c>
       <c r="B54" s="40">
         <v>48</v>
       </c>
-      <c r="C54" s="131"/>
-      <c r="D54" s="131"/>
-      <c r="E54" s="68"/>
-      <c r="F54" s="68"/>
-      <c r="G54" s="68"/>
-      <c r="H54" s="124"/>
-      <c r="I54" s="68"/>
-      <c r="J54" s="68"/>
-      <c r="K54" s="68"/>
+      <c r="C54" s="176" t="s">
+        <v>162</v>
+      </c>
+      <c r="D54" s="176" t="s">
+        <v>163</v>
+      </c>
+      <c r="E54" s="177"/>
+      <c r="F54" s="177"/>
+      <c r="G54" s="177">
+        <v>40</v>
+      </c>
+      <c r="H54" s="178">
+        <v>40</v>
+      </c>
+      <c r="I54" s="177"/>
+      <c r="J54" s="177"/>
+      <c r="K54" s="177"/>
       <c r="L54" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M54" s="138"/>
+        <v>2</v>
+      </c>
+      <c r="M54" s="138">
+        <v>18</v>
+      </c>
       <c r="N54" s="42"/>
       <c r="O54" s="66">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P54" s="33">
         <f t="shared" si="73"/>
@@ -6309,32 +6417,48 @@
       <c r="X54" s="49"/>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A55" s="71"/>
+      <c r="A55" s="134">
+        <v>46302</v>
+      </c>
       <c r="B55" s="40">
         <v>49</v>
       </c>
-      <c r="C55" s="125"/>
-      <c r="D55" s="125"/>
-      <c r="E55" s="68"/>
-      <c r="F55" s="68"/>
-      <c r="G55" s="68"/>
-      <c r="H55" s="124"/>
-      <c r="I55" s="68"/>
-      <c r="J55" s="68"/>
-      <c r="K55" s="68"/>
+      <c r="C55" s="179" t="s">
+        <v>106</v>
+      </c>
+      <c r="D55" s="179" t="s">
+        <v>164</v>
+      </c>
+      <c r="E55" s="177"/>
+      <c r="F55" s="177"/>
+      <c r="G55" s="177">
+        <v>40</v>
+      </c>
+      <c r="H55" s="178">
+        <v>40</v>
+      </c>
+      <c r="I55" s="177"/>
+      <c r="J55" s="177">
+        <v>40</v>
+      </c>
+      <c r="K55" s="177">
+        <v>40</v>
+      </c>
       <c r="L55" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M55" s="138"/>
+        <v>4</v>
+      </c>
+      <c r="M55" s="138">
+        <v>18</v>
+      </c>
       <c r="N55" s="42"/>
       <c r="O55" s="66">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P55" s="33">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q55" s="44"/>
       <c r="R55" s="45"/>
@@ -6352,32 +6476,44 @@
       <c r="X55" s="49"/>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A56" s="71"/>
+      <c r="A56" s="134">
+        <v>46302</v>
+      </c>
       <c r="B56" s="40">
         <v>50</v>
       </c>
-      <c r="C56" s="125"/>
-      <c r="D56" s="125"/>
-      <c r="E56" s="68"/>
-      <c r="F56" s="68"/>
-      <c r="G56" s="68"/>
-      <c r="H56" s="124"/>
-      <c r="I56" s="68"/>
-      <c r="J56" s="68"/>
-      <c r="K56" s="68"/>
+      <c r="C56" s="179" t="s">
+        <v>165</v>
+      </c>
+      <c r="D56" s="179" t="s">
+        <v>166</v>
+      </c>
+      <c r="E56" s="177"/>
+      <c r="F56" s="177"/>
+      <c r="G56" s="177"/>
+      <c r="H56" s="178">
+        <v>40</v>
+      </c>
+      <c r="I56" s="177">
+        <v>40</v>
+      </c>
+      <c r="J56" s="177"/>
+      <c r="K56" s="177"/>
       <c r="L56" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M56" s="138"/>
+        <v>2</v>
+      </c>
+      <c r="M56" s="138">
+        <v>18</v>
+      </c>
       <c r="N56" s="42"/>
       <c r="O56" s="66">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P56" s="33">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q56" s="44"/>
       <c r="R56" s="45"/>
@@ -6395,24 +6531,36 @@
       <c r="X56" s="49"/>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A57" s="71"/>
+      <c r="A57" s="134">
+        <v>46302</v>
+      </c>
       <c r="B57" s="40">
         <v>51</v>
       </c>
-      <c r="C57" s="125"/>
-      <c r="D57" s="125"/>
-      <c r="E57" s="68"/>
-      <c r="F57" s="68"/>
-      <c r="G57" s="68"/>
-      <c r="H57" s="124"/>
-      <c r="I57" s="68"/>
-      <c r="J57" s="68"/>
-      <c r="K57" s="68"/>
+      <c r="C57" s="179" t="s">
+        <v>167</v>
+      </c>
+      <c r="D57" s="179" t="s">
+        <v>168</v>
+      </c>
+      <c r="E57" s="177"/>
+      <c r="F57" s="177"/>
+      <c r="G57" s="177"/>
+      <c r="H57" s="178"/>
+      <c r="I57" s="177">
+        <v>40</v>
+      </c>
+      <c r="J57" s="177">
+        <v>40</v>
+      </c>
+      <c r="K57" s="177"/>
       <c r="L57" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M57" s="138"/>
+        <v>2</v>
+      </c>
+      <c r="M57" s="138">
+        <v>18</v>
+      </c>
       <c r="N57" s="42"/>
       <c r="O57" s="66">
         <f t="shared" si="72"/>
@@ -6420,7 +6568,7 @@
       </c>
       <c r="P57" s="33">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q57" s="44"/>
       <c r="R57" s="45"/>
@@ -6438,32 +6586,48 @@
       <c r="X57" s="49"/>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A58" s="71"/>
+      <c r="A58" s="134">
+        <v>46302</v>
+      </c>
       <c r="B58" s="40">
         <v>52</v>
       </c>
-      <c r="C58" s="125"/>
-      <c r="D58" s="125"/>
-      <c r="E58" s="68"/>
-      <c r="F58" s="68"/>
-      <c r="G58" s="68"/>
-      <c r="H58" s="124"/>
-      <c r="I58" s="68"/>
-      <c r="J58" s="68"/>
-      <c r="K58" s="68"/>
+      <c r="C58" s="179" t="s">
+        <v>169</v>
+      </c>
+      <c r="D58" s="179" t="s">
+        <v>170</v>
+      </c>
+      <c r="E58" s="177"/>
+      <c r="F58" s="177"/>
+      <c r="G58" s="177">
+        <v>40</v>
+      </c>
+      <c r="H58" s="178"/>
+      <c r="I58" s="177">
+        <v>40</v>
+      </c>
+      <c r="J58" s="177">
+        <v>40</v>
+      </c>
+      <c r="K58" s="177">
+        <v>40</v>
+      </c>
       <c r="L58" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M58" s="138"/>
+        <v>4</v>
+      </c>
+      <c r="M58" s="138">
+        <v>18</v>
+      </c>
       <c r="N58" s="42"/>
       <c r="O58" s="66">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P58" s="33">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q58" s="44"/>
       <c r="R58" s="45"/>
@@ -6481,32 +6645,48 @@
       <c r="X58" s="49"/>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A59" s="71"/>
+      <c r="A59" s="134">
+        <v>46302</v>
+      </c>
       <c r="B59" s="40">
         <v>53</v>
       </c>
-      <c r="C59" s="125"/>
-      <c r="D59" s="125"/>
-      <c r="E59" s="68"/>
-      <c r="F59" s="68"/>
-      <c r="G59" s="68"/>
-      <c r="H59" s="124"/>
-      <c r="I59" s="68"/>
-      <c r="J59" s="68"/>
-      <c r="K59" s="68"/>
+      <c r="C59" s="179" t="s">
+        <v>171</v>
+      </c>
+      <c r="D59" s="179" t="s">
+        <v>172</v>
+      </c>
+      <c r="E59" s="177"/>
+      <c r="F59" s="177"/>
+      <c r="G59" s="177"/>
+      <c r="H59" s="178">
+        <v>40</v>
+      </c>
+      <c r="I59" s="177">
+        <v>40</v>
+      </c>
+      <c r="J59" s="177">
+        <v>40</v>
+      </c>
+      <c r="K59" s="177">
+        <v>40</v>
+      </c>
       <c r="L59" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M59" s="138"/>
+        <v>4</v>
+      </c>
+      <c r="M59" s="138">
+        <v>18</v>
+      </c>
       <c r="N59" s="42"/>
       <c r="O59" s="66">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P59" s="33">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q59" s="44"/>
       <c r="R59" s="45"/>
@@ -6524,32 +6704,50 @@
       <c r="X59" s="49"/>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A60" s="71"/>
+      <c r="A60" s="134">
+        <v>46302</v>
+      </c>
       <c r="B60" s="40">
         <v>54</v>
       </c>
-      <c r="C60" s="125"/>
-      <c r="D60" s="125"/>
-      <c r="E60" s="68"/>
-      <c r="F60" s="68"/>
-      <c r="G60" s="68"/>
-      <c r="H60" s="124"/>
-      <c r="I60" s="68"/>
-      <c r="J60" s="68"/>
-      <c r="K60" s="68"/>
+      <c r="C60" s="179" t="s">
+        <v>173</v>
+      </c>
+      <c r="D60" s="179" t="s">
+        <v>174</v>
+      </c>
+      <c r="E60" s="177"/>
+      <c r="F60" s="177">
+        <v>40</v>
+      </c>
+      <c r="G60" s="177">
+        <v>40</v>
+      </c>
+      <c r="H60" s="178">
+        <v>40</v>
+      </c>
+      <c r="I60" s="177">
+        <v>40</v>
+      </c>
+      <c r="J60" s="177"/>
+      <c r="K60" s="177">
+        <v>40</v>
+      </c>
       <c r="L60" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M60" s="138"/>
+        <v>5</v>
+      </c>
+      <c r="M60" s="138">
+        <v>18</v>
+      </c>
       <c r="N60" s="42"/>
       <c r="O60" s="66">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P60" s="33">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q60" s="44"/>
       <c r="R60" s="45"/>
@@ -6567,24 +6765,38 @@
       <c r="X60" s="49"/>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A61" s="71"/>
+      <c r="A61" s="134">
+        <v>46302</v>
+      </c>
       <c r="B61" s="40">
         <v>55</v>
       </c>
-      <c r="C61" s="125"/>
-      <c r="D61" s="125"/>
-      <c r="E61" s="68"/>
-      <c r="F61" s="68"/>
-      <c r="G61" s="68"/>
-      <c r="H61" s="124"/>
-      <c r="I61" s="68"/>
-      <c r="J61" s="68"/>
-      <c r="K61" s="68"/>
+      <c r="C61" s="179" t="s">
+        <v>111</v>
+      </c>
+      <c r="D61" s="179" t="s">
+        <v>175</v>
+      </c>
+      <c r="E61" s="177"/>
+      <c r="F61" s="177"/>
+      <c r="G61" s="177"/>
+      <c r="H61" s="178"/>
+      <c r="I61" s="177">
+        <v>40</v>
+      </c>
+      <c r="J61" s="177">
+        <v>40</v>
+      </c>
+      <c r="K61" s="177">
+        <v>40</v>
+      </c>
       <c r="L61" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M61" s="138"/>
+        <v>3</v>
+      </c>
+      <c r="M61" s="138">
+        <v>18</v>
+      </c>
       <c r="N61" s="42"/>
       <c r="O61" s="66">
         <f t="shared" si="72"/>
@@ -6592,7 +6804,7 @@
       </c>
       <c r="P61" s="33">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q61" s="44"/>
       <c r="R61" s="45"/>
@@ -6610,32 +6822,48 @@
       <c r="X61" s="49"/>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A62" s="71"/>
+      <c r="A62" s="134">
+        <v>46302</v>
+      </c>
       <c r="B62" s="40">
         <v>56</v>
       </c>
-      <c r="C62" s="125"/>
-      <c r="D62" s="125"/>
-      <c r="E62" s="68"/>
-      <c r="F62" s="68"/>
-      <c r="G62" s="68"/>
-      <c r="H62" s="124"/>
-      <c r="I62" s="68"/>
-      <c r="J62" s="68"/>
-      <c r="K62" s="68"/>
+      <c r="C62" s="179" t="s">
+        <v>176</v>
+      </c>
+      <c r="D62" s="179" t="s">
+        <v>177</v>
+      </c>
+      <c r="E62" s="177"/>
+      <c r="F62" s="177"/>
+      <c r="G62" s="177">
+        <v>40</v>
+      </c>
+      <c r="H62" s="178">
+        <v>40</v>
+      </c>
+      <c r="I62" s="177">
+        <v>40</v>
+      </c>
+      <c r="J62" s="177"/>
+      <c r="K62" s="177">
+        <v>40</v>
+      </c>
       <c r="L62" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M62" s="138"/>
+        <v>4</v>
+      </c>
+      <c r="M62" s="138">
+        <v>18</v>
+      </c>
       <c r="N62" s="42"/>
       <c r="O62" s="66">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P62" s="33">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q62" s="44"/>
       <c r="R62" s="45"/>
@@ -6653,32 +6881,44 @@
       <c r="X62" s="49"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A63" s="71"/>
+      <c r="A63" s="134">
+        <v>46302</v>
+      </c>
       <c r="B63" s="40">
         <v>57</v>
       </c>
-      <c r="C63" s="125"/>
-      <c r="D63" s="125"/>
-      <c r="E63" s="68"/>
-      <c r="F63" s="68"/>
-      <c r="G63" s="68"/>
-      <c r="H63" s="124"/>
-      <c r="I63" s="68"/>
-      <c r="J63" s="68"/>
-      <c r="K63" s="68"/>
+      <c r="C63" s="179" t="s">
+        <v>96</v>
+      </c>
+      <c r="D63" s="179" t="s">
+        <v>180</v>
+      </c>
+      <c r="E63" s="177"/>
+      <c r="F63" s="177"/>
+      <c r="G63" s="177"/>
+      <c r="H63" s="178">
+        <v>40</v>
+      </c>
+      <c r="I63" s="177"/>
+      <c r="J63" s="177">
+        <v>40</v>
+      </c>
+      <c r="K63" s="177"/>
       <c r="L63" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M63" s="138"/>
+        <v>2</v>
+      </c>
+      <c r="M63" s="138">
+        <v>18</v>
+      </c>
       <c r="N63" s="42"/>
       <c r="O63" s="66">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P63" s="33">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q63" s="44" t="e">
         <f t="shared" ref="Q63:Q94" si="76">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
@@ -6714,24 +6954,38 @@
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A64" s="71"/>
+      <c r="A64" s="134">
+        <v>46302</v>
+      </c>
       <c r="B64" s="40">
         <v>58</v>
       </c>
-      <c r="C64" s="125"/>
-      <c r="D64" s="125"/>
-      <c r="E64" s="68"/>
-      <c r="F64" s="68"/>
-      <c r="G64" s="68"/>
-      <c r="H64" s="124"/>
-      <c r="I64" s="68"/>
-      <c r="J64" s="68"/>
-      <c r="K64" s="68"/>
+      <c r="C64" s="179" t="s">
+        <v>178</v>
+      </c>
+      <c r="D64" s="179" t="s">
+        <v>179</v>
+      </c>
+      <c r="E64" s="177"/>
+      <c r="F64" s="177"/>
+      <c r="G64" s="177"/>
+      <c r="H64" s="178"/>
+      <c r="I64" s="177">
+        <v>40</v>
+      </c>
+      <c r="J64" s="177">
+        <v>40</v>
+      </c>
+      <c r="K64" s="177">
+        <v>40</v>
+      </c>
       <c r="L64" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M64" s="138"/>
+        <v>3</v>
+      </c>
+      <c r="M64" s="138">
+        <v>18</v>
+      </c>
       <c r="N64" s="42"/>
       <c r="O64" s="66">
         <f t="shared" ref="O64:O81" si="78">SUM(F64:H64)/20</f>
@@ -6739,7 +6993,7 @@
       </c>
       <c r="P64" s="33">
         <f t="shared" ref="P64:P81" si="79">SUM(I64:K64)/20</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q64" s="44" t="e">
         <f t="shared" si="76"/>
@@ -6775,24 +7029,36 @@
       </c>
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A65" s="71"/>
+      <c r="A65" s="134">
+        <v>46302</v>
+      </c>
       <c r="B65" s="40">
         <v>59</v>
       </c>
-      <c r="C65" s="125"/>
-      <c r="D65" s="125"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="68"/>
-      <c r="G65" s="68"/>
-      <c r="H65" s="124"/>
-      <c r="I65" s="68"/>
-      <c r="J65" s="68"/>
-      <c r="K65" s="68"/>
+      <c r="C65" s="179" t="s">
+        <v>181</v>
+      </c>
+      <c r="D65" s="179" t="s">
+        <v>182</v>
+      </c>
+      <c r="E65" s="177"/>
+      <c r="F65" s="177"/>
+      <c r="G65" s="177"/>
+      <c r="H65" s="178"/>
+      <c r="I65" s="177"/>
+      <c r="J65" s="177">
+        <v>40</v>
+      </c>
+      <c r="K65" s="177">
+        <v>40</v>
+      </c>
       <c r="L65" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M65" s="138"/>
+        <v>2</v>
+      </c>
+      <c r="M65" s="138">
+        <v>18</v>
+      </c>
       <c r="N65" s="42"/>
       <c r="O65" s="66">
         <f t="shared" si="78"/>
@@ -6800,7 +7066,7 @@
       </c>
       <c r="P65" s="33">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q65" s="44" t="e">
         <f t="shared" si="76"/>
@@ -6836,32 +7102,50 @@
       </c>
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A66" s="71"/>
+      <c r="A66" s="134">
+        <v>46302</v>
+      </c>
       <c r="B66" s="40">
         <v>60</v>
       </c>
-      <c r="C66" s="125"/>
-      <c r="D66" s="125"/>
-      <c r="E66" s="68"/>
-      <c r="F66" s="68"/>
-      <c r="G66" s="68"/>
-      <c r="H66" s="124"/>
-      <c r="I66" s="68"/>
-      <c r="J66" s="68"/>
-      <c r="K66" s="68"/>
+      <c r="C66" s="179" t="s">
+        <v>183</v>
+      </c>
+      <c r="D66" s="179" t="s">
+        <v>184</v>
+      </c>
+      <c r="E66" s="177"/>
+      <c r="F66" s="177">
+        <v>40</v>
+      </c>
+      <c r="G66" s="177"/>
+      <c r="H66" s="178">
+        <v>40</v>
+      </c>
+      <c r="I66" s="177">
+        <v>40</v>
+      </c>
+      <c r="J66" s="177">
+        <v>40</v>
+      </c>
+      <c r="K66" s="177">
+        <v>40</v>
+      </c>
       <c r="L66" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M66" s="138"/>
+        <v>5</v>
+      </c>
+      <c r="M66" s="138">
+        <v>18</v>
+      </c>
       <c r="N66" s="42"/>
       <c r="O66" s="66">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P66" s="33">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q66" s="44" t="e">
         <f t="shared" si="76"/>
@@ -6897,32 +7181,52 @@
       </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A67" s="71"/>
+      <c r="A67" s="134">
+        <v>46302</v>
+      </c>
       <c r="B67" s="40">
         <v>61</v>
       </c>
-      <c r="C67" s="125"/>
-      <c r="D67" s="125"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="68"/>
-      <c r="G67" s="68"/>
-      <c r="H67" s="124"/>
-      <c r="I67" s="68"/>
-      <c r="J67" s="68"/>
-      <c r="K67" s="68"/>
+      <c r="C67" s="179" t="s">
+        <v>185</v>
+      </c>
+      <c r="D67" s="179" t="s">
+        <v>186</v>
+      </c>
+      <c r="E67" s="177"/>
+      <c r="F67" s="177">
+        <v>40</v>
+      </c>
+      <c r="G67" s="177">
+        <v>40</v>
+      </c>
+      <c r="H67" s="178">
+        <v>80</v>
+      </c>
+      <c r="I67" s="177">
+        <v>40</v>
+      </c>
+      <c r="J67" s="177">
+        <v>40</v>
+      </c>
+      <c r="K67" s="177">
+        <v>80</v>
+      </c>
       <c r="L67" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M67" s="138"/>
+        <v>8</v>
+      </c>
+      <c r="M67" s="138">
+        <v>10</v>
+      </c>
       <c r="N67" s="42"/>
       <c r="O67" s="66">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P67" s="33">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q67" s="44" t="e">
         <f t="shared" si="76"/>
@@ -6958,32 +7262,48 @@
       </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A68" s="71"/>
+      <c r="A68" s="134">
+        <v>46302</v>
+      </c>
       <c r="B68" s="40">
         <v>62</v>
       </c>
-      <c r="C68" s="125"/>
-      <c r="D68" s="125"/>
-      <c r="E68" s="68"/>
-      <c r="F68" s="68"/>
-      <c r="G68" s="68"/>
-      <c r="H68" s="124"/>
-      <c r="I68" s="68"/>
-      <c r="J68" s="68"/>
-      <c r="K68" s="68"/>
+      <c r="C68" s="179" t="s">
+        <v>187</v>
+      </c>
+      <c r="D68" s="179" t="s">
+        <v>188</v>
+      </c>
+      <c r="E68" s="177"/>
+      <c r="F68" s="177">
+        <v>80</v>
+      </c>
+      <c r="G68" s="177"/>
+      <c r="H68" s="178">
+        <v>160</v>
+      </c>
+      <c r="I68" s="177"/>
+      <c r="J68" s="177">
+        <v>160</v>
+      </c>
+      <c r="K68" s="177">
+        <v>160</v>
+      </c>
       <c r="L68" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M68" s="138"/>
+        <v>14</v>
+      </c>
+      <c r="M68" s="138">
+        <v>12</v>
+      </c>
       <c r="N68" s="42"/>
       <c r="O68" s="66">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P68" s="33">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q68" s="44" t="e">
         <f t="shared" si="76"/>
@@ -7019,24 +7339,38 @@
       </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A69" s="71"/>
+      <c r="A69" s="134">
+        <v>46302</v>
+      </c>
       <c r="B69" s="40">
         <v>63</v>
       </c>
-      <c r="C69" s="125"/>
-      <c r="D69" s="125"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="68"/>
-      <c r="G69" s="68"/>
-      <c r="H69" s="124"/>
-      <c r="I69" s="68"/>
-      <c r="J69" s="68"/>
-      <c r="K69" s="68"/>
+      <c r="C69" s="179" t="s">
+        <v>189</v>
+      </c>
+      <c r="D69" s="179" t="s">
+        <v>190</v>
+      </c>
+      <c r="E69" s="177"/>
+      <c r="F69" s="177"/>
+      <c r="G69" s="177"/>
+      <c r="H69" s="178"/>
+      <c r="I69" s="177">
+        <v>120</v>
+      </c>
+      <c r="J69" s="177">
+        <v>80</v>
+      </c>
+      <c r="K69" s="177">
+        <v>120</v>
+      </c>
       <c r="L69" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M69" s="138"/>
+        <v>8</v>
+      </c>
+      <c r="M69" s="138">
+        <v>14</v>
+      </c>
       <c r="N69" s="42"/>
       <c r="O69" s="66">
         <f t="shared" si="78"/>
@@ -7044,7 +7378,7 @@
       </c>
       <c r="P69" s="33">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q69" s="44" t="e">
         <f t="shared" si="76"/>
@@ -11057,36 +11391,36 @@
       <c r="C135" s="152"/>
       <c r="D135" s="135"/>
       <c r="E135" s="140">
-        <f>SUM(E6:E63)</f>
+        <f t="shared" ref="E135:K135" si="103">SUM(E6:E63)</f>
         <v>0</v>
       </c>
       <c r="F135" s="140">
-        <f>SUM(F6:F63)</f>
-        <v>1261</v>
+        <f t="shared" si="103"/>
+        <v>1301</v>
       </c>
       <c r="G135" s="140">
-        <f>SUM(G6:G63)</f>
-        <v>990</v>
+        <f t="shared" si="103"/>
+        <v>1190</v>
       </c>
       <c r="H135" s="140">
-        <f>SUM(H6:H63)</f>
-        <v>2571</v>
+        <f t="shared" si="103"/>
+        <v>2851</v>
       </c>
       <c r="I135" s="140">
-        <f>SUM(I6:I63)</f>
-        <v>2155</v>
+        <f t="shared" si="103"/>
+        <v>2435</v>
       </c>
       <c r="J135" s="140">
-        <f>SUM(J6:J63)</f>
-        <v>2637</v>
+        <f t="shared" si="103"/>
+        <v>2877</v>
       </c>
       <c r="K135" s="140">
-        <f>SUM(K6:K63)</f>
-        <v>3160</v>
+        <f t="shared" si="103"/>
+        <v>3400</v>
       </c>
       <c r="L135" s="124">
-        <f t="shared" ref="L135" si="103">SUM(E135:K135)/40</f>
-        <v>319.35000000000002</v>
+        <f t="shared" ref="L135" si="104">SUM(E135:K135)/40</f>
+        <v>351.35</v>
       </c>
       <c r="M135" s="138">
         <f t="shared" si="102"/>
@@ -11094,12 +11428,12 @@
       </c>
       <c r="N135" s="42"/>
       <c r="O135" s="66">
-        <f t="shared" ref="O135:O139" si="104">SUM(F135:H135)/20</f>
-        <v>241.1</v>
+        <f t="shared" ref="O135:O139" si="105">SUM(F135:H135)/20</f>
+        <v>267.10000000000002</v>
       </c>
       <c r="P135" s="33">
-        <f t="shared" ref="P135:P139" si="105">SUM(I135:K135)/20</f>
-        <v>397.6</v>
+        <f t="shared" ref="P135:P139" si="106">SUM(I135:K135)/20</f>
+        <v>435.6</v>
       </c>
       <c r="Q135" s="44" t="e">
         <f t="shared" si="100"/>
@@ -11122,11 +11456,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="V135" s="48">
-        <f t="shared" ref="V135:V139" si="106">SUM(F135:H135)*$V$3</f>
+        <f t="shared" ref="V135:V139" si="107">SUM(F135:H135)*$V$3</f>
         <v>0</v>
       </c>
       <c r="W135" s="48">
-        <f t="shared" ref="W135:W139" si="107">SUM(I135:K135)*$W$3</f>
+        <f t="shared" ref="W135:W139" si="108">SUM(I135:K135)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X135" s="49" t="e">
@@ -11196,11 +11530,11 @@
         <v>3.5513000000000003</v>
       </c>
       <c r="O137" s="66">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="P137" s="33">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="Q137" s="44" t="e">
@@ -11224,11 +11558,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="V137" s="48">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="W137" s="48">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X137" s="49" t="e">
@@ -11264,11 +11598,11 @@
         <v>3.5513000000000003</v>
       </c>
       <c r="O138" s="66">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="P138" s="33">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="Q138" s="44" t="e">
@@ -11292,11 +11626,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="V138" s="48">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="W138" s="48">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X138" s="49" t="e">
@@ -11315,27 +11649,27 @@
         <v>0</v>
       </c>
       <c r="F139" s="76">
-        <f t="shared" ref="F139:K139" si="108">SUM(F137:F138)</f>
+        <f t="shared" ref="F139:K139" si="109">SUM(F137:F138)</f>
         <v>0</v>
       </c>
       <c r="G139" s="76">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="H139" s="76">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="I139" s="76">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="J139" s="76">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="K139" s="76">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="L139" s="104">
@@ -11351,11 +11685,11 @@
         <v>3.5513000000000003</v>
       </c>
       <c r="O139" s="66">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
       <c r="P139" s="33">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="Q139" s="44" t="e">
@@ -11379,11 +11713,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="V139" s="48">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="W139" s="48">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="X139" s="49" t="e">
@@ -11402,79 +11736,79 @@
         <v>0</v>
       </c>
       <c r="F140" s="77">
-        <f t="shared" ref="F140:K140" si="109">SUM(F135,F139)</f>
-        <v>1261</v>
+        <f t="shared" ref="F140:K140" si="110">SUM(F135,F139)</f>
+        <v>1301</v>
       </c>
       <c r="G140" s="77">
-        <f t="shared" si="109"/>
-        <v>990</v>
+        <f t="shared" si="110"/>
+        <v>1190</v>
       </c>
       <c r="H140" s="77">
-        <f t="shared" si="109"/>
-        <v>2571</v>
+        <f t="shared" si="110"/>
+        <v>2851</v>
       </c>
       <c r="I140" s="77">
-        <f t="shared" si="109"/>
-        <v>2155</v>
+        <f t="shared" si="110"/>
+        <v>2435</v>
       </c>
       <c r="J140" s="77">
-        <f t="shared" si="109"/>
-        <v>2637</v>
+        <f t="shared" si="110"/>
+        <v>2877</v>
       </c>
       <c r="K140" s="77">
-        <f t="shared" si="109"/>
-        <v>3160</v>
+        <f t="shared" si="110"/>
+        <v>3400</v>
       </c>
       <c r="L140" s="53">
         <f>SUM(E140:K140)/40</f>
-        <v>319.35000000000002</v>
+        <v>351.35</v>
       </c>
       <c r="M140" s="56">
         <f>SUM(M5:M139)</f>
-        <v>784</v>
+        <v>1054</v>
       </c>
       <c r="N140" s="54">
-        <f t="shared" ref="N140:X140" si="110">SUM(N5:N139)</f>
+        <f t="shared" ref="N140:X140" si="111">SUM(N5:N139)</f>
         <v>10.6539</v>
       </c>
       <c r="O140" s="55">
-        <f t="shared" si="110"/>
-        <v>485.7</v>
+        <f t="shared" si="111"/>
+        <v>561.70000000000005</v>
       </c>
       <c r="P140" s="57">
-        <f t="shared" si="110"/>
-        <v>797.2</v>
+        <f t="shared" si="111"/>
+        <v>929.2</v>
       </c>
       <c r="Q140" s="58" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>#VALUE!</v>
       </c>
       <c r="R140" s="59">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0</v>
       </c>
       <c r="S140" s="59">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0</v>
       </c>
       <c r="T140" s="60" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>#VALUE!</v>
       </c>
       <c r="U140" s="61" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>#VALUE!</v>
       </c>
       <c r="V140" s="62">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0</v>
       </c>
       <c r="W140" s="62">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0</v>
       </c>
       <c r="X140" s="63" t="e">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11590,24 +11924,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="80">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="E5" s="72">
-        <v>232</v>
+        <v>304</v>
       </c>
       <c r="F5" s="72">
         <v>90</v>
       </c>
       <c r="G5" s="94">
         <f>SUM(D5:F5)</f>
-        <v>481</v>
+        <v>571</v>
       </c>
       <c r="H5" s="87">
         <v>10000</v>
       </c>
       <c r="I5" s="88">
         <f>G5-H5</f>
-        <v>-9519</v>
+        <v>-9429</v>
       </c>
       <c r="K5" s="132" t="s">
         <v>1</v>
@@ -11638,11 +11972,11 @@
       </c>
       <c r="D6" s="96">
         <f>D5*40</f>
-        <v>6360</v>
+        <v>7080</v>
       </c>
       <c r="E6" s="96">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>9280</v>
+        <v>12160</v>
       </c>
       <c r="F6" s="96">
         <f t="shared" si="1"/>
@@ -11650,7 +11984,7 @@
       </c>
       <c r="G6" s="97">
         <f>SUM(D6:F6)</f>
-        <v>19240</v>
+        <v>22840</v>
       </c>
       <c r="H6" s="89">
         <f>H5*40</f>
@@ -11658,7 +11992,7 @@
       </c>
       <c r="I6" s="90">
         <f>G6-H6</f>
-        <v>-380760</v>
+        <v>-377160</v>
       </c>
       <c r="K6" s="132" t="s">
         <v>2</v>
@@ -11807,11 +12141,11 @@
       </c>
       <c r="D9" s="98">
         <f>D8-D5</f>
-        <v>-159</v>
+        <v>-177</v>
       </c>
       <c r="E9" s="98">
         <f>E8-E5</f>
-        <v>-232</v>
+        <v>-304</v>
       </c>
       <c r="K9" s="132" t="s">
         <v>5</v>
@@ -11968,7 +12302,7 @@
       </c>
       <c r="G12" s="83">
         <f>D12+G5</f>
-        <v>4681</v>
+        <v>4771</v>
       </c>
       <c r="K12" s="132" t="s">
         <v>11</v>
@@ -12020,7 +12354,7 @@
       </c>
       <c r="G13" s="83">
         <f>G12*40</f>
-        <v>187240</v>
+        <v>190840</v>
       </c>
       <c r="S13" s="166" t="s">
         <v>83</v>

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D175B6A-A446-4188-A6F7-28353D660152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C8DF992-E76B-4145-8136-7FCDD9A1E85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="203">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -595,6 +595,42 @@
   </si>
   <si>
     <t>Shadbagh</t>
+  </si>
+  <si>
+    <t>Abdullah Traders SD</t>
+  </si>
+  <si>
+    <t>Server Hayat Colony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best Buy Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cavelary Fround </t>
+  </si>
+  <si>
+    <t>Decent Departmental Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khokhar Chowk </t>
+  </si>
+  <si>
+    <t>MB Traders (Risen)</t>
+  </si>
+  <si>
+    <t>Askari 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweera </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shadman </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usman Canvinious </t>
+  </si>
+  <si>
+    <t>LDA Avenue</t>
   </si>
 </sst>
 </file>
@@ -1462,7 +1498,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1833,112 +1869,122 @@
     </xf>
     <xf numFmtId="1" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2533,13 +2579,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="142">
+      <c r="B1" s="145">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
-      </c>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
+        <v>46304</v>
+      </c>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2561,10 +2607,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="163" t="s">
+      <c r="A2" s="166" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="143" t="s">
+      <c r="B2" s="146" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2594,13 +2640,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="155"/>
-      <c r="M2" s="156"/>
-      <c r="N2" s="157"/>
-      <c r="O2" s="158" t="s">
+      <c r="L2" s="158"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="160"/>
+      <c r="O2" s="161" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="159"/>
+      <c r="P2" s="162"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2619,8 +2665,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="163"/>
-      <c r="B3" s="144"/>
+      <c r="A3" s="166"/>
+      <c r="B3" s="147"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2648,29 +2694,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="160" t="s">
+      <c r="L3" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="161"/>
-      <c r="N3" s="162"/>
+      <c r="M3" s="164"/>
+      <c r="N3" s="165"/>
       <c r="O3" s="64"/>
       <c r="P3" s="65"/>
-      <c r="Q3" s="146" t="s">
+      <c r="Q3" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="147"/>
-      <c r="S3" s="147"/>
-      <c r="T3" s="148"/>
-      <c r="U3" s="149" t="s">
+      <c r="R3" s="150"/>
+      <c r="S3" s="150"/>
+      <c r="T3" s="151"/>
+      <c r="U3" s="152" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="150"/>
-      <c r="W3" s="150"/>
-      <c r="X3" s="151"/>
+      <c r="V3" s="153"/>
+      <c r="W3" s="153"/>
+      <c r="X3" s="154"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="163"/>
-      <c r="B4" s="145"/>
+      <c r="A4" s="166"/>
+      <c r="B4" s="148"/>
       <c r="C4" s="130" t="s">
         <v>90</v>
       </c>
@@ -5694,7 +5740,7 @@
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A44" s="175">
+      <c r="A44" s="71">
         <v>46301</v>
       </c>
       <c r="B44" s="40">
@@ -5775,7 +5821,7 @@
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A45" s="175">
+      <c r="A45" s="71">
         <v>46301</v>
       </c>
       <c r="B45" s="40">
@@ -5856,7 +5902,7 @@
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A46" s="175">
+      <c r="A46" s="71">
         <v>46301</v>
       </c>
       <c r="B46" s="40">
@@ -5935,7 +5981,7 @@
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A47" s="175">
+      <c r="A47" s="71">
         <v>46301</v>
       </c>
       <c r="B47" s="40">
@@ -6006,7 +6052,7 @@
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A48" s="175">
+      <c r="A48" s="71">
         <v>46301</v>
       </c>
       <c r="B48" s="40">
@@ -6075,7 +6121,7 @@
       </c>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A49" s="175">
+      <c r="A49" s="71">
         <v>46301</v>
       </c>
       <c r="B49" s="40">
@@ -6128,7 +6174,7 @@
       <c r="X49" s="49"/>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A50" s="175">
+      <c r="A50" s="71">
         <v>46301</v>
       </c>
       <c r="B50" s="40">
@@ -6185,7 +6231,7 @@
       <c r="X50" s="49"/>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A51" s="175">
+      <c r="A51" s="71">
         <v>46301</v>
       </c>
       <c r="B51" s="40">
@@ -6244,7 +6290,7 @@
       <c r="X51" s="49"/>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A52" s="175">
+      <c r="A52" s="71">
         <v>46301</v>
       </c>
       <c r="B52" s="40">
@@ -6303,7 +6349,7 @@
       <c r="X52" s="49"/>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A53" s="175">
+      <c r="A53" s="71">
         <v>46301</v>
       </c>
       <c r="B53" s="40">
@@ -6362,29 +6408,29 @@
       <c r="X53" s="49"/>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A54" s="134">
+      <c r="A54" s="178">
         <v>46302</v>
       </c>
-      <c r="B54" s="40">
+      <c r="B54" s="179">
         <v>48</v>
       </c>
-      <c r="C54" s="176" t="s">
+      <c r="C54" s="180" t="s">
         <v>162</v>
       </c>
-      <c r="D54" s="176" t="s">
+      <c r="D54" s="180" t="s">
         <v>163</v>
       </c>
-      <c r="E54" s="177"/>
-      <c r="F54" s="177"/>
-      <c r="G54" s="177">
-        <v>40</v>
-      </c>
-      <c r="H54" s="178">
-        <v>40</v>
-      </c>
-      <c r="I54" s="177"/>
-      <c r="J54" s="177"/>
-      <c r="K54" s="177"/>
+      <c r="E54" s="181"/>
+      <c r="F54" s="181"/>
+      <c r="G54" s="181">
+        <v>40</v>
+      </c>
+      <c r="H54" s="182">
+        <v>40</v>
+      </c>
+      <c r="I54" s="181"/>
+      <c r="J54" s="181"/>
+      <c r="K54" s="181"/>
       <c r="L54" s="124">
         <f t="shared" si="64"/>
         <v>2</v>
@@ -6417,31 +6463,31 @@
       <c r="X54" s="49"/>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A55" s="134">
+      <c r="A55" s="178">
         <v>46302</v>
       </c>
-      <c r="B55" s="40">
+      <c r="B55" s="179">
         <v>49</v>
       </c>
-      <c r="C55" s="179" t="s">
+      <c r="C55" s="183" t="s">
         <v>106</v>
       </c>
-      <c r="D55" s="179" t="s">
+      <c r="D55" s="183" t="s">
         <v>164</v>
       </c>
-      <c r="E55" s="177"/>
-      <c r="F55" s="177"/>
-      <c r="G55" s="177">
-        <v>40</v>
-      </c>
-      <c r="H55" s="178">
-        <v>40</v>
-      </c>
-      <c r="I55" s="177"/>
-      <c r="J55" s="177">
-        <v>40</v>
-      </c>
-      <c r="K55" s="177">
+      <c r="E55" s="181"/>
+      <c r="F55" s="181"/>
+      <c r="G55" s="181">
+        <v>40</v>
+      </c>
+      <c r="H55" s="182">
+        <v>40</v>
+      </c>
+      <c r="I55" s="181"/>
+      <c r="J55" s="181">
+        <v>40</v>
+      </c>
+      <c r="K55" s="181">
         <v>40</v>
       </c>
       <c r="L55" s="124">
@@ -6476,29 +6522,29 @@
       <c r="X55" s="49"/>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A56" s="134">
+      <c r="A56" s="178">
         <v>46302</v>
       </c>
-      <c r="B56" s="40">
+      <c r="B56" s="179">
         <v>50</v>
       </c>
-      <c r="C56" s="179" t="s">
+      <c r="C56" s="183" t="s">
         <v>165</v>
       </c>
-      <c r="D56" s="179" t="s">
+      <c r="D56" s="183" t="s">
         <v>166</v>
       </c>
-      <c r="E56" s="177"/>
-      <c r="F56" s="177"/>
-      <c r="G56" s="177"/>
-      <c r="H56" s="178">
-        <v>40</v>
-      </c>
-      <c r="I56" s="177">
-        <v>40</v>
-      </c>
-      <c r="J56" s="177"/>
-      <c r="K56" s="177"/>
+      <c r="E56" s="181"/>
+      <c r="F56" s="181"/>
+      <c r="G56" s="181"/>
+      <c r="H56" s="182">
+        <v>40</v>
+      </c>
+      <c r="I56" s="181">
+        <v>40</v>
+      </c>
+      <c r="J56" s="181"/>
+      <c r="K56" s="181"/>
       <c r="L56" s="124">
         <f t="shared" si="64"/>
         <v>2</v>
@@ -6531,29 +6577,29 @@
       <c r="X56" s="49"/>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A57" s="134">
+      <c r="A57" s="178">
         <v>46302</v>
       </c>
-      <c r="B57" s="40">
+      <c r="B57" s="179">
         <v>51</v>
       </c>
-      <c r="C57" s="179" t="s">
+      <c r="C57" s="183" t="s">
         <v>167</v>
       </c>
-      <c r="D57" s="179" t="s">
+      <c r="D57" s="183" t="s">
         <v>168</v>
       </c>
-      <c r="E57" s="177"/>
-      <c r="F57" s="177"/>
-      <c r="G57" s="177"/>
-      <c r="H57" s="178"/>
-      <c r="I57" s="177">
-        <v>40</v>
-      </c>
-      <c r="J57" s="177">
-        <v>40</v>
-      </c>
-      <c r="K57" s="177"/>
+      <c r="E57" s="181"/>
+      <c r="F57" s="181"/>
+      <c r="G57" s="181"/>
+      <c r="H57" s="182"/>
+      <c r="I57" s="181">
+        <v>40</v>
+      </c>
+      <c r="J57" s="181">
+        <v>40</v>
+      </c>
+      <c r="K57" s="181"/>
       <c r="L57" s="124">
         <f t="shared" si="64"/>
         <v>2</v>
@@ -6586,31 +6632,31 @@
       <c r="X57" s="49"/>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A58" s="134">
+      <c r="A58" s="178">
         <v>46302</v>
       </c>
-      <c r="B58" s="40">
+      <c r="B58" s="179">
         <v>52</v>
       </c>
-      <c r="C58" s="179" t="s">
+      <c r="C58" s="183" t="s">
         <v>169</v>
       </c>
-      <c r="D58" s="179" t="s">
+      <c r="D58" s="183" t="s">
         <v>170</v>
       </c>
-      <c r="E58" s="177"/>
-      <c r="F58" s="177"/>
-      <c r="G58" s="177">
-        <v>40</v>
-      </c>
-      <c r="H58" s="178"/>
-      <c r="I58" s="177">
-        <v>40</v>
-      </c>
-      <c r="J58" s="177">
-        <v>40</v>
-      </c>
-      <c r="K58" s="177">
+      <c r="E58" s="181"/>
+      <c r="F58" s="181"/>
+      <c r="G58" s="181">
+        <v>40</v>
+      </c>
+      <c r="H58" s="182"/>
+      <c r="I58" s="181">
+        <v>40</v>
+      </c>
+      <c r="J58" s="181">
+        <v>40</v>
+      </c>
+      <c r="K58" s="181">
         <v>40</v>
       </c>
       <c r="L58" s="124">
@@ -6645,31 +6691,31 @@
       <c r="X58" s="49"/>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A59" s="134">
+      <c r="A59" s="178">
         <v>46302</v>
       </c>
-      <c r="B59" s="40">
+      <c r="B59" s="179">
         <v>53</v>
       </c>
-      <c r="C59" s="179" t="s">
+      <c r="C59" s="183" t="s">
         <v>171</v>
       </c>
-      <c r="D59" s="179" t="s">
+      <c r="D59" s="183" t="s">
         <v>172</v>
       </c>
-      <c r="E59" s="177"/>
-      <c r="F59" s="177"/>
-      <c r="G59" s="177"/>
-      <c r="H59" s="178">
-        <v>40</v>
-      </c>
-      <c r="I59" s="177">
-        <v>40</v>
-      </c>
-      <c r="J59" s="177">
-        <v>40</v>
-      </c>
-      <c r="K59" s="177">
+      <c r="E59" s="181"/>
+      <c r="F59" s="181"/>
+      <c r="G59" s="181"/>
+      <c r="H59" s="182">
+        <v>40</v>
+      </c>
+      <c r="I59" s="181">
+        <v>40</v>
+      </c>
+      <c r="J59" s="181">
+        <v>40</v>
+      </c>
+      <c r="K59" s="181">
         <v>40</v>
       </c>
       <c r="L59" s="124">
@@ -6704,33 +6750,33 @@
       <c r="X59" s="49"/>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A60" s="134">
+      <c r="A60" s="178">
         <v>46302</v>
       </c>
-      <c r="B60" s="40">
+      <c r="B60" s="179">
         <v>54</v>
       </c>
-      <c r="C60" s="179" t="s">
+      <c r="C60" s="183" t="s">
         <v>173</v>
       </c>
-      <c r="D60" s="179" t="s">
+      <c r="D60" s="183" t="s">
         <v>174</v>
       </c>
-      <c r="E60" s="177"/>
-      <c r="F60" s="177">
-        <v>40</v>
-      </c>
-      <c r="G60" s="177">
-        <v>40</v>
-      </c>
-      <c r="H60" s="178">
-        <v>40</v>
-      </c>
-      <c r="I60" s="177">
-        <v>40</v>
-      </c>
-      <c r="J60" s="177"/>
-      <c r="K60" s="177">
+      <c r="E60" s="181"/>
+      <c r="F60" s="181">
+        <v>40</v>
+      </c>
+      <c r="G60" s="181">
+        <v>40</v>
+      </c>
+      <c r="H60" s="182">
+        <v>40</v>
+      </c>
+      <c r="I60" s="181">
+        <v>40</v>
+      </c>
+      <c r="J60" s="181"/>
+      <c r="K60" s="181">
         <v>40</v>
       </c>
       <c r="L60" s="124">
@@ -6765,29 +6811,29 @@
       <c r="X60" s="49"/>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A61" s="134">
+      <c r="A61" s="178">
         <v>46302</v>
       </c>
-      <c r="B61" s="40">
+      <c r="B61" s="179">
         <v>55</v>
       </c>
-      <c r="C61" s="179" t="s">
+      <c r="C61" s="183" t="s">
         <v>111</v>
       </c>
-      <c r="D61" s="179" t="s">
+      <c r="D61" s="183" t="s">
         <v>175</v>
       </c>
-      <c r="E61" s="177"/>
-      <c r="F61" s="177"/>
-      <c r="G61" s="177"/>
-      <c r="H61" s="178"/>
-      <c r="I61" s="177">
-        <v>40</v>
-      </c>
-      <c r="J61" s="177">
-        <v>40</v>
-      </c>
-      <c r="K61" s="177">
+      <c r="E61" s="181"/>
+      <c r="F61" s="181"/>
+      <c r="G61" s="181"/>
+      <c r="H61" s="182"/>
+      <c r="I61" s="181">
+        <v>40</v>
+      </c>
+      <c r="J61" s="181">
+        <v>40</v>
+      </c>
+      <c r="K61" s="181">
         <v>40</v>
       </c>
       <c r="L61" s="124">
@@ -6822,31 +6868,31 @@
       <c r="X61" s="49"/>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A62" s="134">
+      <c r="A62" s="178">
         <v>46302</v>
       </c>
-      <c r="B62" s="40">
+      <c r="B62" s="179">
         <v>56</v>
       </c>
-      <c r="C62" s="179" t="s">
+      <c r="C62" s="183" t="s">
         <v>176</v>
       </c>
-      <c r="D62" s="179" t="s">
+      <c r="D62" s="183" t="s">
         <v>177</v>
       </c>
-      <c r="E62" s="177"/>
-      <c r="F62" s="177"/>
-      <c r="G62" s="177">
-        <v>40</v>
-      </c>
-      <c r="H62" s="178">
-        <v>40</v>
-      </c>
-      <c r="I62" s="177">
-        <v>40</v>
-      </c>
-      <c r="J62" s="177"/>
-      <c r="K62" s="177">
+      <c r="E62" s="181"/>
+      <c r="F62" s="181"/>
+      <c r="G62" s="181">
+        <v>40</v>
+      </c>
+      <c r="H62" s="182">
+        <v>40</v>
+      </c>
+      <c r="I62" s="181">
+        <v>40</v>
+      </c>
+      <c r="J62" s="181"/>
+      <c r="K62" s="181">
         <v>40</v>
       </c>
       <c r="L62" s="124">
@@ -6881,29 +6927,29 @@
       <c r="X62" s="49"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A63" s="134">
+      <c r="A63" s="178">
         <v>46302</v>
       </c>
-      <c r="B63" s="40">
+      <c r="B63" s="179">
         <v>57</v>
       </c>
-      <c r="C63" s="179" t="s">
+      <c r="C63" s="183" t="s">
         <v>96</v>
       </c>
-      <c r="D63" s="179" t="s">
+      <c r="D63" s="183" t="s">
         <v>180</v>
       </c>
-      <c r="E63" s="177"/>
-      <c r="F63" s="177"/>
-      <c r="G63" s="177"/>
-      <c r="H63" s="178">
-        <v>40</v>
-      </c>
-      <c r="I63" s="177"/>
-      <c r="J63" s="177">
-        <v>40</v>
-      </c>
-      <c r="K63" s="177"/>
+      <c r="E63" s="181"/>
+      <c r="F63" s="181"/>
+      <c r="G63" s="181"/>
+      <c r="H63" s="182">
+        <v>40</v>
+      </c>
+      <c r="I63" s="181"/>
+      <c r="J63" s="181">
+        <v>40</v>
+      </c>
+      <c r="K63" s="181"/>
       <c r="L63" s="124">
         <f t="shared" si="64"/>
         <v>2</v>
@@ -6954,29 +7000,29 @@
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A64" s="134">
+      <c r="A64" s="178">
         <v>46302</v>
       </c>
-      <c r="B64" s="40">
+      <c r="B64" s="179">
         <v>58</v>
       </c>
-      <c r="C64" s="179" t="s">
+      <c r="C64" s="183" t="s">
         <v>178</v>
       </c>
-      <c r="D64" s="179" t="s">
+      <c r="D64" s="183" t="s">
         <v>179</v>
       </c>
-      <c r="E64" s="177"/>
-      <c r="F64" s="177"/>
-      <c r="G64" s="177"/>
-      <c r="H64" s="178"/>
-      <c r="I64" s="177">
-        <v>40</v>
-      </c>
-      <c r="J64" s="177">
-        <v>40</v>
-      </c>
-      <c r="K64" s="177">
+      <c r="E64" s="181"/>
+      <c r="F64" s="181"/>
+      <c r="G64" s="181"/>
+      <c r="H64" s="182"/>
+      <c r="I64" s="181">
+        <v>40</v>
+      </c>
+      <c r="J64" s="181">
+        <v>40</v>
+      </c>
+      <c r="K64" s="181">
         <v>40</v>
       </c>
       <c r="L64" s="124">
@@ -7029,27 +7075,27 @@
       </c>
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A65" s="134">
+      <c r="A65" s="178">
         <v>46302</v>
       </c>
-      <c r="B65" s="40">
+      <c r="B65" s="179">
         <v>59</v>
       </c>
-      <c r="C65" s="179" t="s">
+      <c r="C65" s="183" t="s">
         <v>181</v>
       </c>
-      <c r="D65" s="179" t="s">
+      <c r="D65" s="183" t="s">
         <v>182</v>
       </c>
-      <c r="E65" s="177"/>
-      <c r="F65" s="177"/>
-      <c r="G65" s="177"/>
-      <c r="H65" s="178"/>
-      <c r="I65" s="177"/>
-      <c r="J65" s="177">
-        <v>40</v>
-      </c>
-      <c r="K65" s="177">
+      <c r="E65" s="181"/>
+      <c r="F65" s="181"/>
+      <c r="G65" s="181"/>
+      <c r="H65" s="182"/>
+      <c r="I65" s="181"/>
+      <c r="J65" s="181">
+        <v>40</v>
+      </c>
+      <c r="K65" s="181">
         <v>40</v>
       </c>
       <c r="L65" s="124">
@@ -7102,33 +7148,33 @@
       </c>
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A66" s="134">
+      <c r="A66" s="178">
         <v>46302</v>
       </c>
-      <c r="B66" s="40">
+      <c r="B66" s="179">
         <v>60</v>
       </c>
-      <c r="C66" s="179" t="s">
+      <c r="C66" s="183" t="s">
         <v>183</v>
       </c>
-      <c r="D66" s="179" t="s">
+      <c r="D66" s="183" t="s">
         <v>184</v>
       </c>
-      <c r="E66" s="177"/>
-      <c r="F66" s="177">
-        <v>40</v>
-      </c>
-      <c r="G66" s="177"/>
-      <c r="H66" s="178">
-        <v>40</v>
-      </c>
-      <c r="I66" s="177">
-        <v>40</v>
-      </c>
-      <c r="J66" s="177">
-        <v>40</v>
-      </c>
-      <c r="K66" s="177">
+      <c r="E66" s="181"/>
+      <c r="F66" s="181">
+        <v>40</v>
+      </c>
+      <c r="G66" s="181"/>
+      <c r="H66" s="182">
+        <v>40</v>
+      </c>
+      <c r="I66" s="181">
+        <v>40</v>
+      </c>
+      <c r="J66" s="181">
+        <v>40</v>
+      </c>
+      <c r="K66" s="181">
         <v>40</v>
       </c>
       <c r="L66" s="124">
@@ -7181,35 +7227,35 @@
       </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A67" s="134">
+      <c r="A67" s="178">
         <v>46302</v>
       </c>
-      <c r="B67" s="40">
+      <c r="B67" s="179">
         <v>61</v>
       </c>
-      <c r="C67" s="179" t="s">
+      <c r="C67" s="183" t="s">
         <v>185</v>
       </c>
-      <c r="D67" s="179" t="s">
+      <c r="D67" s="183" t="s">
         <v>186</v>
       </c>
-      <c r="E67" s="177"/>
-      <c r="F67" s="177">
-        <v>40</v>
-      </c>
-      <c r="G67" s="177">
-        <v>40</v>
-      </c>
-      <c r="H67" s="178">
+      <c r="E67" s="181"/>
+      <c r="F67" s="181">
+        <v>40</v>
+      </c>
+      <c r="G67" s="181">
+        <v>40</v>
+      </c>
+      <c r="H67" s="182">
         <v>80</v>
       </c>
-      <c r="I67" s="177">
-        <v>40</v>
-      </c>
-      <c r="J67" s="177">
-        <v>40</v>
-      </c>
-      <c r="K67" s="177">
+      <c r="I67" s="181">
+        <v>40</v>
+      </c>
+      <c r="J67" s="181">
+        <v>40</v>
+      </c>
+      <c r="K67" s="181">
         <v>80</v>
       </c>
       <c r="L67" s="124">
@@ -7262,31 +7308,31 @@
       </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A68" s="134">
+      <c r="A68" s="178">
         <v>46302</v>
       </c>
-      <c r="B68" s="40">
+      <c r="B68" s="179">
         <v>62</v>
       </c>
-      <c r="C68" s="179" t="s">
+      <c r="C68" s="183" t="s">
         <v>187</v>
       </c>
-      <c r="D68" s="179" t="s">
+      <c r="D68" s="183" t="s">
         <v>188</v>
       </c>
-      <c r="E68" s="177"/>
-      <c r="F68" s="177">
+      <c r="E68" s="181"/>
+      <c r="F68" s="181">
         <v>80</v>
       </c>
-      <c r="G68" s="177"/>
-      <c r="H68" s="178">
+      <c r="G68" s="181"/>
+      <c r="H68" s="182">
         <v>160</v>
       </c>
-      <c r="I68" s="177"/>
-      <c r="J68" s="177">
+      <c r="I68" s="181"/>
+      <c r="J68" s="181">
         <v>160</v>
       </c>
-      <c r="K68" s="177">
+      <c r="K68" s="181">
         <v>160</v>
       </c>
       <c r="L68" s="124">
@@ -7339,29 +7385,29 @@
       </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A69" s="134">
+      <c r="A69" s="178">
         <v>46302</v>
       </c>
-      <c r="B69" s="40">
+      <c r="B69" s="179">
         <v>63</v>
       </c>
-      <c r="C69" s="179" t="s">
+      <c r="C69" s="183" t="s">
         <v>189</v>
       </c>
-      <c r="D69" s="179" t="s">
+      <c r="D69" s="183" t="s">
         <v>190</v>
       </c>
-      <c r="E69" s="177"/>
-      <c r="F69" s="177"/>
-      <c r="G69" s="177"/>
-      <c r="H69" s="178"/>
-      <c r="I69" s="177">
+      <c r="E69" s="181"/>
+      <c r="F69" s="181"/>
+      <c r="G69" s="181"/>
+      <c r="H69" s="182"/>
+      <c r="I69" s="181">
         <v>120</v>
       </c>
-      <c r="J69" s="177">
+      <c r="J69" s="181">
         <v>80</v>
       </c>
-      <c r="K69" s="177">
+      <c r="K69" s="181">
         <v>120</v>
       </c>
       <c r="L69" s="124">
@@ -7414,32 +7460,52 @@
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A70" s="71"/>
-      <c r="B70" s="40">
+      <c r="A70" s="178">
+        <v>46302</v>
+      </c>
+      <c r="B70" s="179">
         <v>64</v>
       </c>
-      <c r="C70" s="125"/>
-      <c r="D70" s="125"/>
-      <c r="E70" s="68"/>
-      <c r="F70" s="68"/>
-      <c r="G70" s="68"/>
-      <c r="H70" s="124"/>
-      <c r="I70" s="68"/>
-      <c r="J70" s="68"/>
-      <c r="K70" s="68"/>
+      <c r="C70" s="183" t="s">
+        <v>191</v>
+      </c>
+      <c r="D70" s="183" t="s">
+        <v>192</v>
+      </c>
+      <c r="E70" s="181"/>
+      <c r="F70" s="181">
+        <v>400</v>
+      </c>
+      <c r="G70" s="181">
+        <v>400</v>
+      </c>
+      <c r="H70" s="182">
+        <v>0</v>
+      </c>
+      <c r="I70" s="181">
+        <v>600</v>
+      </c>
+      <c r="J70" s="181">
+        <v>800</v>
+      </c>
+      <c r="K70" s="181">
+        <v>800</v>
+      </c>
       <c r="L70" s="124">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="M70" s="138"/>
+        <v>75</v>
+      </c>
+      <c r="M70" s="138">
+        <v>14</v>
+      </c>
       <c r="N70" s="42"/>
       <c r="O70" s="66">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P70" s="33">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="Q70" s="44" t="e">
         <f t="shared" si="76"/>
@@ -7475,32 +7541,52 @@
       </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A71" s="71"/>
-      <c r="B71" s="40">
+      <c r="A71" s="134">
+        <v>46303</v>
+      </c>
+      <c r="B71" s="135">
         <v>65</v>
       </c>
-      <c r="C71" s="125"/>
-      <c r="D71" s="125"/>
-      <c r="E71" s="68"/>
-      <c r="F71" s="68"/>
-      <c r="G71" s="68"/>
-      <c r="H71" s="124"/>
-      <c r="I71" s="68"/>
-      <c r="J71" s="68"/>
-      <c r="K71" s="68"/>
+      <c r="C71" s="144" t="s">
+        <v>193</v>
+      </c>
+      <c r="D71" s="144" t="s">
+        <v>194</v>
+      </c>
+      <c r="E71" s="142"/>
+      <c r="F71" s="142">
+        <v>80</v>
+      </c>
+      <c r="G71" s="142">
+        <v>80</v>
+      </c>
+      <c r="H71" s="143">
+        <v>80</v>
+      </c>
+      <c r="I71" s="142">
+        <v>80</v>
+      </c>
+      <c r="J71" s="142">
+        <v>80</v>
+      </c>
+      <c r="K71" s="142">
+        <v>80</v>
+      </c>
       <c r="L71" s="124">
         <f t="shared" ref="L71:L102" si="84">SUM(E71:K71)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M71" s="138"/>
+        <v>12</v>
+      </c>
+      <c r="M71" s="138">
+        <v>14</v>
+      </c>
       <c r="N71" s="42"/>
       <c r="O71" s="66">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P71" s="33">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q71" s="44" t="e">
         <f t="shared" si="76"/>
@@ -7536,32 +7622,50 @@
       </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A72" s="71"/>
-      <c r="B72" s="40">
+      <c r="A72" s="134">
+        <v>46303</v>
+      </c>
+      <c r="B72" s="135">
         <v>66</v>
       </c>
-      <c r="C72" s="125"/>
-      <c r="D72" s="125"/>
-      <c r="E72" s="68"/>
-      <c r="F72" s="68"/>
-      <c r="G72" s="68"/>
-      <c r="H72" s="124"/>
-      <c r="I72" s="68"/>
-      <c r="J72" s="68"/>
-      <c r="K72" s="68"/>
+      <c r="C72" s="144" t="s">
+        <v>195</v>
+      </c>
+      <c r="D72" s="144" t="s">
+        <v>186</v>
+      </c>
+      <c r="E72" s="142"/>
+      <c r="F72" s="142"/>
+      <c r="G72" s="142">
+        <v>80</v>
+      </c>
+      <c r="H72" s="143">
+        <v>120</v>
+      </c>
+      <c r="I72" s="142">
+        <v>80</v>
+      </c>
+      <c r="J72" s="142">
+        <v>80</v>
+      </c>
+      <c r="K72" s="142">
+        <v>80</v>
+      </c>
       <c r="L72" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M72" s="138"/>
+        <v>11</v>
+      </c>
+      <c r="M72" s="138">
+        <v>12</v>
+      </c>
       <c r="N72" s="42"/>
       <c r="O72" s="66">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P72" s="33">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q72" s="44" t="e">
         <f t="shared" si="76"/>
@@ -7597,32 +7701,52 @@
       </c>
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A73" s="71"/>
-      <c r="B73" s="40">
+      <c r="A73" s="134">
+        <v>46303</v>
+      </c>
+      <c r="B73" s="135">
         <v>67</v>
       </c>
-      <c r="C73" s="125"/>
-      <c r="D73" s="125"/>
-      <c r="E73" s="68"/>
-      <c r="F73" s="68"/>
-      <c r="G73" s="68"/>
-      <c r="H73" s="124"/>
-      <c r="I73" s="68"/>
-      <c r="J73" s="68"/>
-      <c r="K73" s="68"/>
+      <c r="C73" s="144" t="s">
+        <v>113</v>
+      </c>
+      <c r="D73" s="144" t="s">
+        <v>196</v>
+      </c>
+      <c r="E73" s="142"/>
+      <c r="F73" s="142">
+        <v>40</v>
+      </c>
+      <c r="G73" s="142">
+        <v>40</v>
+      </c>
+      <c r="H73" s="143">
+        <v>40</v>
+      </c>
+      <c r="I73" s="142">
+        <v>40</v>
+      </c>
+      <c r="J73" s="142">
+        <v>40</v>
+      </c>
+      <c r="K73" s="142">
+        <v>40</v>
+      </c>
       <c r="L73" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M73" s="138"/>
+        <v>6</v>
+      </c>
+      <c r="M73" s="138">
+        <v>15</v>
+      </c>
       <c r="N73" s="42"/>
       <c r="O73" s="66">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P73" s="33">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q73" s="44" t="e">
         <f t="shared" si="76"/>
@@ -7658,32 +7782,48 @@
       </c>
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A74" s="71"/>
-      <c r="B74" s="40">
+      <c r="A74" s="134">
+        <v>46303</v>
+      </c>
+      <c r="B74" s="135">
         <v>68</v>
       </c>
-      <c r="C74" s="125"/>
-      <c r="D74" s="125"/>
-      <c r="E74" s="68"/>
-      <c r="F74" s="68"/>
-      <c r="G74" s="68"/>
-      <c r="H74" s="124"/>
-      <c r="I74" s="68"/>
-      <c r="J74" s="68"/>
-      <c r="K74" s="68"/>
+      <c r="C74" s="144" t="s">
+        <v>197</v>
+      </c>
+      <c r="D74" s="144" t="s">
+        <v>198</v>
+      </c>
+      <c r="E74" s="142"/>
+      <c r="F74" s="142"/>
+      <c r="G74" s="142">
+        <v>40</v>
+      </c>
+      <c r="H74" s="143"/>
+      <c r="I74" s="142">
+        <v>40</v>
+      </c>
+      <c r="J74" s="142">
+        <v>20</v>
+      </c>
+      <c r="K74" s="142">
+        <v>80</v>
+      </c>
       <c r="L74" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M74" s="138"/>
+        <v>4.5</v>
+      </c>
+      <c r="M74" s="138">
+        <v>14</v>
+      </c>
       <c r="N74" s="42"/>
       <c r="O74" s="66">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P74" s="33">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q74" s="44" t="e">
         <f t="shared" si="76"/>
@@ -7719,32 +7859,52 @@
       </c>
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A75" s="71"/>
-      <c r="B75" s="40">
+      <c r="A75" s="134">
+        <v>46303</v>
+      </c>
+      <c r="B75" s="135">
         <v>69</v>
       </c>
-      <c r="C75" s="125"/>
-      <c r="D75" s="125"/>
-      <c r="E75" s="68"/>
-      <c r="F75" s="68"/>
-      <c r="G75" s="68"/>
-      <c r="H75" s="124"/>
-      <c r="I75" s="68"/>
-      <c r="J75" s="68"/>
-      <c r="K75" s="68"/>
+      <c r="C75" s="144" t="s">
+        <v>199</v>
+      </c>
+      <c r="D75" s="144" t="s">
+        <v>200</v>
+      </c>
+      <c r="E75" s="142"/>
+      <c r="F75" s="142">
+        <v>200</v>
+      </c>
+      <c r="G75" s="142">
+        <v>200</v>
+      </c>
+      <c r="H75" s="143">
+        <v>200</v>
+      </c>
+      <c r="I75" s="142">
+        <v>200</v>
+      </c>
+      <c r="J75" s="142">
+        <v>200</v>
+      </c>
+      <c r="K75" s="142">
+        <v>200</v>
+      </c>
       <c r="L75" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M75" s="138"/>
+        <v>30</v>
+      </c>
+      <c r="M75" s="138">
+        <v>12</v>
+      </c>
       <c r="N75" s="42"/>
       <c r="O75" s="66">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P75" s="33">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q75" s="44" t="e">
         <f t="shared" si="76"/>
@@ -7780,32 +7940,52 @@
       </c>
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A76" s="71"/>
-      <c r="B76" s="40">
+      <c r="A76" s="134">
+        <v>46303</v>
+      </c>
+      <c r="B76" s="135">
         <v>70</v>
       </c>
-      <c r="C76" s="125"/>
-      <c r="D76" s="125"/>
-      <c r="E76" s="68"/>
-      <c r="F76" s="68"/>
-      <c r="G76" s="68"/>
-      <c r="H76" s="124"/>
-      <c r="I76" s="68"/>
-      <c r="J76" s="68"/>
-      <c r="K76" s="68"/>
+      <c r="C76" s="144" t="s">
+        <v>201</v>
+      </c>
+      <c r="D76" s="144" t="s">
+        <v>202</v>
+      </c>
+      <c r="E76" s="142"/>
+      <c r="F76" s="142">
+        <v>40</v>
+      </c>
+      <c r="G76" s="142">
+        <v>40</v>
+      </c>
+      <c r="H76" s="143">
+        <v>40</v>
+      </c>
+      <c r="I76" s="142">
+        <v>40</v>
+      </c>
+      <c r="J76" s="142">
+        <v>40</v>
+      </c>
+      <c r="K76" s="142">
+        <v>40</v>
+      </c>
       <c r="L76" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M76" s="138"/>
+        <v>6</v>
+      </c>
+      <c r="M76" s="138">
+        <v>10</v>
+      </c>
       <c r="N76" s="42"/>
       <c r="O76" s="66">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P76" s="33">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q76" s="44" t="e">
         <f t="shared" si="76"/>
@@ -11385,10 +11565,10 @@
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A135" s="71"/>
-      <c r="B135" s="152" t="s">
+      <c r="B135" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="C135" s="152"/>
+      <c r="C135" s="155"/>
       <c r="D135" s="135"/>
       <c r="E135" s="140">
         <f t="shared" ref="E135:K135" si="103">SUM(E6:E63)</f>
@@ -11639,10 +11819,10 @@
       </c>
     </row>
     <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B139" s="164" t="s">
+      <c r="B139" s="167" t="s">
         <v>68</v>
       </c>
-      <c r="C139" s="165"/>
+      <c r="C139" s="168"/>
       <c r="D139" s="128"/>
       <c r="E139" s="76">
         <f>SUM(E137:E138)</f>
@@ -11726,10 +11906,10 @@
       </c>
     </row>
     <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B140" s="153" t="s">
+      <c r="B140" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="C140" s="154"/>
+      <c r="C140" s="157"/>
       <c r="D140" s="129"/>
       <c r="E140" s="77">
         <f>SUM(E135,E139)</f>
@@ -11765,7 +11945,7 @@
       </c>
       <c r="M140" s="56">
         <f>SUM(M5:M139)</f>
-        <v>1054</v>
+        <v>1145</v>
       </c>
       <c r="N140" s="54">
         <f t="shared" ref="N140:X140" si="111">SUM(N5:N139)</f>
@@ -11773,11 +11953,11 @@
       </c>
       <c r="O140" s="55">
         <f t="shared" si="111"/>
-        <v>561.70000000000005</v>
+        <v>667.7</v>
       </c>
       <c r="P140" s="57">
         <f t="shared" si="111"/>
-        <v>929.2</v>
+        <v>1112.2</v>
       </c>
       <c r="Q140" s="58" t="e">
         <f t="shared" si="111"/>
@@ -11860,25 +12040,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="171" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="169"/>
-      <c r="E3" s="169"/>
-      <c r="F3" s="169"/>
-      <c r="G3" s="170"/>
-      <c r="H3" s="172" t="s">
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="173"/>
+      <c r="H3" s="175" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="173"/>
-      <c r="K3" s="174" t="s">
+      <c r="I3" s="176"/>
+      <c r="K3" s="177" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="174"/>
-      <c r="M3" s="174"/>
-      <c r="N3" s="174"/>
-      <c r="O3" s="174"/>
-      <c r="P3" s="174"/>
+      <c r="L3" s="177"/>
+      <c r="M3" s="177"/>
+      <c r="N3" s="177"/>
+      <c r="O3" s="177"/>
+      <c r="P3" s="177"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="91"/>
@@ -11924,24 +12104,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="80">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="E5" s="72">
-        <v>304</v>
+        <v>374</v>
       </c>
       <c r="F5" s="72">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="G5" s="94">
         <f>SUM(D5:F5)</f>
-        <v>571</v>
+        <v>747</v>
       </c>
       <c r="H5" s="87">
         <v>10000</v>
       </c>
       <c r="I5" s="88">
         <f>G5-H5</f>
-        <v>-9429</v>
+        <v>-9253</v>
       </c>
       <c r="K5" s="132" t="s">
         <v>1</v>
@@ -11972,19 +12152,19 @@
       </c>
       <c r="D6" s="96">
         <f>D5*40</f>
-        <v>7080</v>
+        <v>8320</v>
       </c>
       <c r="E6" s="96">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>12160</v>
+        <v>14960</v>
       </c>
       <c r="F6" s="96">
         <f t="shared" si="1"/>
-        <v>3600</v>
+        <v>6600</v>
       </c>
       <c r="G6" s="97">
         <f>SUM(D6:F6)</f>
-        <v>22840</v>
+        <v>29880</v>
       </c>
       <c r="H6" s="89">
         <f>H5*40</f>
@@ -11992,7 +12172,7 @@
       </c>
       <c r="I6" s="90">
         <f>G6-H6</f>
-        <v>-377160</v>
+        <v>-370120</v>
       </c>
       <c r="K6" s="132" t="s">
         <v>2</v>
@@ -12141,11 +12321,11 @@
       </c>
       <c r="D9" s="98">
         <f>D8-D5</f>
-        <v>-177</v>
+        <v>-208</v>
       </c>
       <c r="E9" s="98">
         <f>E8-E5</f>
-        <v>-304</v>
+        <v>-374</v>
       </c>
       <c r="K9" s="132" t="s">
         <v>5</v>
@@ -12243,14 +12423,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="171" t="s">
+      <c r="C11" s="174" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="171"/>
-      <c r="F11" s="171" t="s">
+      <c r="D11" s="174"/>
+      <c r="F11" s="174" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="171"/>
+      <c r="G11" s="174"/>
       <c r="K11" s="132" t="s">
         <v>7</v>
       </c>
@@ -12302,7 +12482,7 @@
       </c>
       <c r="G12" s="83">
         <f>D12+G5</f>
-        <v>4771</v>
+        <v>4947</v>
       </c>
       <c r="K12" s="132" t="s">
         <v>11</v>
@@ -12354,12 +12534,12 @@
       </c>
       <c r="G13" s="83">
         <f>G12*40</f>
-        <v>190840</v>
-      </c>
-      <c r="S13" s="166" t="s">
+        <v>197880</v>
+      </c>
+      <c r="S13" s="169" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="166"/>
+      <c r="T13" s="169"/>
       <c r="U13" s="120">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -12466,13 +12646,13 @@
       </c>
     </row>
     <row r="20" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="167" t="s">
+      <c r="D20" s="170" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="167"/>
-      <c r="F20" s="167"/>
-      <c r="G20" s="167"/>
-      <c r="H20" s="167"/>
+      <c r="E20" s="170"/>
+      <c r="F20" s="170"/>
+      <c r="G20" s="170"/>
+      <c r="H20" s="170"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C8DF992-E76B-4145-8136-7FCDD9A1E85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE196407-1A33-4552-9828-D0DC9A889BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="213">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -631,6 +631,36 @@
   </si>
   <si>
     <t>LDA Avenue</t>
+  </si>
+  <si>
+    <t>Goourmet Food Krishan Nager</t>
+  </si>
+  <si>
+    <t>Goourmet Food Poonch Road</t>
+  </si>
+  <si>
+    <t>Goourmet Food Shaheed Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goourmet Food Gulshan Ravi </t>
+  </si>
+  <si>
+    <t>Goourmet Food Riwind Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goourmet Food Chung </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goourmet Food Moter Way </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goourmet Food Rustum Park </t>
+  </si>
+  <si>
+    <t>Nabeel Traders  SD</t>
+  </si>
+  <si>
+    <t>Mughalpura</t>
   </si>
 </sst>
 </file>
@@ -1498,7 +1528,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="184">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1876,6 +1906,45 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1907,45 +1976,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1979,13 +2009,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2579,13 +2608,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="145">
+      <c r="B1" s="158">
         <f ca="1">TODAY()</f>
-        <v>46304</v>
-      </c>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
+        <v>46305</v>
+      </c>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2607,10 +2636,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="166" t="s">
+      <c r="A2" s="155" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="146" t="s">
+      <c r="B2" s="159" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2640,13 +2669,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="158"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="160"/>
-      <c r="O2" s="161" t="s">
+      <c r="L2" s="147"/>
+      <c r="M2" s="148"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="150" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="162"/>
+      <c r="P2" s="151"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2665,8 +2694,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="166"/>
-      <c r="B3" s="147"/>
+      <c r="A3" s="155"/>
+      <c r="B3" s="160"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2694,29 +2723,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="163" t="s">
+      <c r="L3" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="164"/>
-      <c r="N3" s="165"/>
+      <c r="M3" s="153"/>
+      <c r="N3" s="154"/>
       <c r="O3" s="64"/>
       <c r="P3" s="65"/>
-      <c r="Q3" s="149" t="s">
+      <c r="Q3" s="162" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="150"/>
-      <c r="S3" s="150"/>
-      <c r="T3" s="151"/>
-      <c r="U3" s="152" t="s">
+      <c r="R3" s="163"/>
+      <c r="S3" s="163"/>
+      <c r="T3" s="164"/>
+      <c r="U3" s="165" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="153"/>
-      <c r="W3" s="153"/>
-      <c r="X3" s="154"/>
+      <c r="V3" s="166"/>
+      <c r="W3" s="166"/>
+      <c r="X3" s="167"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="166"/>
-      <c r="B4" s="148"/>
+      <c r="A4" s="155"/>
+      <c r="B4" s="161"/>
       <c r="C4" s="130" t="s">
         <v>90</v>
       </c>
@@ -6408,29 +6437,29 @@
       <c r="X53" s="49"/>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A54" s="178">
+      <c r="A54" s="71">
         <v>46302</v>
       </c>
-      <c r="B54" s="179">
+      <c r="B54" s="40">
         <v>48</v>
       </c>
-      <c r="C54" s="180" t="s">
+      <c r="C54" s="131" t="s">
         <v>162</v>
       </c>
-      <c r="D54" s="180" t="s">
+      <c r="D54" s="131" t="s">
         <v>163</v>
       </c>
-      <c r="E54" s="181"/>
-      <c r="F54" s="181"/>
-      <c r="G54" s="181">
-        <v>40</v>
-      </c>
-      <c r="H54" s="182">
-        <v>40</v>
-      </c>
-      <c r="I54" s="181"/>
-      <c r="J54" s="181"/>
-      <c r="K54" s="181"/>
+      <c r="E54" s="68"/>
+      <c r="F54" s="68"/>
+      <c r="G54" s="68">
+        <v>40</v>
+      </c>
+      <c r="H54" s="124">
+        <v>40</v>
+      </c>
+      <c r="I54" s="68"/>
+      <c r="J54" s="68"/>
+      <c r="K54" s="68"/>
       <c r="L54" s="124">
         <f t="shared" si="64"/>
         <v>2</v>
@@ -6463,31 +6492,31 @@
       <c r="X54" s="49"/>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A55" s="178">
+      <c r="A55" s="71">
         <v>46302</v>
       </c>
-      <c r="B55" s="179">
+      <c r="B55" s="40">
         <v>49</v>
       </c>
-      <c r="C55" s="183" t="s">
+      <c r="C55" s="125" t="s">
         <v>106</v>
       </c>
-      <c r="D55" s="183" t="s">
+      <c r="D55" s="125" t="s">
         <v>164</v>
       </c>
-      <c r="E55" s="181"/>
-      <c r="F55" s="181"/>
-      <c r="G55" s="181">
-        <v>40</v>
-      </c>
-      <c r="H55" s="182">
-        <v>40</v>
-      </c>
-      <c r="I55" s="181"/>
-      <c r="J55" s="181">
-        <v>40</v>
-      </c>
-      <c r="K55" s="181">
+      <c r="E55" s="68"/>
+      <c r="F55" s="68"/>
+      <c r="G55" s="68">
+        <v>40</v>
+      </c>
+      <c r="H55" s="124">
+        <v>40</v>
+      </c>
+      <c r="I55" s="68"/>
+      <c r="J55" s="68">
+        <v>40</v>
+      </c>
+      <c r="K55" s="68">
         <v>40</v>
       </c>
       <c r="L55" s="124">
@@ -6522,29 +6551,29 @@
       <c r="X55" s="49"/>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A56" s="178">
+      <c r="A56" s="71">
         <v>46302</v>
       </c>
-      <c r="B56" s="179">
+      <c r="B56" s="40">
         <v>50</v>
       </c>
-      <c r="C56" s="183" t="s">
+      <c r="C56" s="125" t="s">
         <v>165</v>
       </c>
-      <c r="D56" s="183" t="s">
+      <c r="D56" s="125" t="s">
         <v>166</v>
       </c>
-      <c r="E56" s="181"/>
-      <c r="F56" s="181"/>
-      <c r="G56" s="181"/>
-      <c r="H56" s="182">
-        <v>40</v>
-      </c>
-      <c r="I56" s="181">
-        <v>40</v>
-      </c>
-      <c r="J56" s="181"/>
-      <c r="K56" s="181"/>
+      <c r="E56" s="68"/>
+      <c r="F56" s="68"/>
+      <c r="G56" s="68"/>
+      <c r="H56" s="124">
+        <v>40</v>
+      </c>
+      <c r="I56" s="68">
+        <v>40</v>
+      </c>
+      <c r="J56" s="68"/>
+      <c r="K56" s="68"/>
       <c r="L56" s="124">
         <f t="shared" si="64"/>
         <v>2</v>
@@ -6577,29 +6606,29 @@
       <c r="X56" s="49"/>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A57" s="178">
+      <c r="A57" s="71">
         <v>46302</v>
       </c>
-      <c r="B57" s="179">
+      <c r="B57" s="40">
         <v>51</v>
       </c>
-      <c r="C57" s="183" t="s">
+      <c r="C57" s="125" t="s">
         <v>167</v>
       </c>
-      <c r="D57" s="183" t="s">
+      <c r="D57" s="125" t="s">
         <v>168</v>
       </c>
-      <c r="E57" s="181"/>
-      <c r="F57" s="181"/>
-      <c r="G57" s="181"/>
-      <c r="H57" s="182"/>
-      <c r="I57" s="181">
-        <v>40</v>
-      </c>
-      <c r="J57" s="181">
-        <v>40</v>
-      </c>
-      <c r="K57" s="181"/>
+      <c r="E57" s="68"/>
+      <c r="F57" s="68"/>
+      <c r="G57" s="68"/>
+      <c r="H57" s="124"/>
+      <c r="I57" s="68">
+        <v>40</v>
+      </c>
+      <c r="J57" s="68">
+        <v>40</v>
+      </c>
+      <c r="K57" s="68"/>
       <c r="L57" s="124">
         <f t="shared" si="64"/>
         <v>2</v>
@@ -6632,31 +6661,31 @@
       <c r="X57" s="49"/>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A58" s="178">
+      <c r="A58" s="71">
         <v>46302</v>
       </c>
-      <c r="B58" s="179">
+      <c r="B58" s="40">
         <v>52</v>
       </c>
-      <c r="C58" s="183" t="s">
+      <c r="C58" s="125" t="s">
         <v>169</v>
       </c>
-      <c r="D58" s="183" t="s">
+      <c r="D58" s="125" t="s">
         <v>170</v>
       </c>
-      <c r="E58" s="181"/>
-      <c r="F58" s="181"/>
-      <c r="G58" s="181">
-        <v>40</v>
-      </c>
-      <c r="H58" s="182"/>
-      <c r="I58" s="181">
-        <v>40</v>
-      </c>
-      <c r="J58" s="181">
-        <v>40</v>
-      </c>
-      <c r="K58" s="181">
+      <c r="E58" s="68"/>
+      <c r="F58" s="68"/>
+      <c r="G58" s="68">
+        <v>40</v>
+      </c>
+      <c r="H58" s="124"/>
+      <c r="I58" s="68">
+        <v>40</v>
+      </c>
+      <c r="J58" s="68">
+        <v>40</v>
+      </c>
+      <c r="K58" s="68">
         <v>40</v>
       </c>
       <c r="L58" s="124">
@@ -6691,31 +6720,31 @@
       <c r="X58" s="49"/>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A59" s="178">
+      <c r="A59" s="71">
         <v>46302</v>
       </c>
-      <c r="B59" s="179">
+      <c r="B59" s="40">
         <v>53</v>
       </c>
-      <c r="C59" s="183" t="s">
+      <c r="C59" s="125" t="s">
         <v>171</v>
       </c>
-      <c r="D59" s="183" t="s">
+      <c r="D59" s="125" t="s">
         <v>172</v>
       </c>
-      <c r="E59" s="181"/>
-      <c r="F59" s="181"/>
-      <c r="G59" s="181"/>
-      <c r="H59" s="182">
-        <v>40</v>
-      </c>
-      <c r="I59" s="181">
-        <v>40</v>
-      </c>
-      <c r="J59" s="181">
-        <v>40</v>
-      </c>
-      <c r="K59" s="181">
+      <c r="E59" s="68"/>
+      <c r="F59" s="68"/>
+      <c r="G59" s="68"/>
+      <c r="H59" s="124">
+        <v>40</v>
+      </c>
+      <c r="I59" s="68">
+        <v>40</v>
+      </c>
+      <c r="J59" s="68">
+        <v>40</v>
+      </c>
+      <c r="K59" s="68">
         <v>40</v>
       </c>
       <c r="L59" s="124">
@@ -6750,33 +6779,33 @@
       <c r="X59" s="49"/>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A60" s="178">
+      <c r="A60" s="71">
         <v>46302</v>
       </c>
-      <c r="B60" s="179">
+      <c r="B60" s="40">
         <v>54</v>
       </c>
-      <c r="C60" s="183" t="s">
+      <c r="C60" s="125" t="s">
         <v>173</v>
       </c>
-      <c r="D60" s="183" t="s">
+      <c r="D60" s="125" t="s">
         <v>174</v>
       </c>
-      <c r="E60" s="181"/>
-      <c r="F60" s="181">
-        <v>40</v>
-      </c>
-      <c r="G60" s="181">
-        <v>40</v>
-      </c>
-      <c r="H60" s="182">
-        <v>40</v>
-      </c>
-      <c r="I60" s="181">
-        <v>40</v>
-      </c>
-      <c r="J60" s="181"/>
-      <c r="K60" s="181">
+      <c r="E60" s="68"/>
+      <c r="F60" s="68">
+        <v>40</v>
+      </c>
+      <c r="G60" s="68">
+        <v>40</v>
+      </c>
+      <c r="H60" s="124">
+        <v>40</v>
+      </c>
+      <c r="I60" s="68">
+        <v>40</v>
+      </c>
+      <c r="J60" s="68"/>
+      <c r="K60" s="68">
         <v>40</v>
       </c>
       <c r="L60" s="124">
@@ -6811,29 +6840,29 @@
       <c r="X60" s="49"/>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A61" s="178">
+      <c r="A61" s="71">
         <v>46302</v>
       </c>
-      <c r="B61" s="179">
+      <c r="B61" s="40">
         <v>55</v>
       </c>
-      <c r="C61" s="183" t="s">
+      <c r="C61" s="125" t="s">
         <v>111</v>
       </c>
-      <c r="D61" s="183" t="s">
+      <c r="D61" s="125" t="s">
         <v>175</v>
       </c>
-      <c r="E61" s="181"/>
-      <c r="F61" s="181"/>
-      <c r="G61" s="181"/>
-      <c r="H61" s="182"/>
-      <c r="I61" s="181">
-        <v>40</v>
-      </c>
-      <c r="J61" s="181">
-        <v>40</v>
-      </c>
-      <c r="K61" s="181">
+      <c r="E61" s="68"/>
+      <c r="F61" s="68"/>
+      <c r="G61" s="68"/>
+      <c r="H61" s="124"/>
+      <c r="I61" s="68">
+        <v>40</v>
+      </c>
+      <c r="J61" s="68">
+        <v>40</v>
+      </c>
+      <c r="K61" s="68">
         <v>40</v>
       </c>
       <c r="L61" s="124">
@@ -6868,31 +6897,31 @@
       <c r="X61" s="49"/>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A62" s="178">
+      <c r="A62" s="71">
         <v>46302</v>
       </c>
-      <c r="B62" s="179">
+      <c r="B62" s="40">
         <v>56</v>
       </c>
-      <c r="C62" s="183" t="s">
+      <c r="C62" s="125" t="s">
         <v>176</v>
       </c>
-      <c r="D62" s="183" t="s">
+      <c r="D62" s="125" t="s">
         <v>177</v>
       </c>
-      <c r="E62" s="181"/>
-      <c r="F62" s="181"/>
-      <c r="G62" s="181">
-        <v>40</v>
-      </c>
-      <c r="H62" s="182">
-        <v>40</v>
-      </c>
-      <c r="I62" s="181">
-        <v>40</v>
-      </c>
-      <c r="J62" s="181"/>
-      <c r="K62" s="181">
+      <c r="E62" s="68"/>
+      <c r="F62" s="68"/>
+      <c r="G62" s="68">
+        <v>40</v>
+      </c>
+      <c r="H62" s="124">
+        <v>40</v>
+      </c>
+      <c r="I62" s="68">
+        <v>40</v>
+      </c>
+      <c r="J62" s="68"/>
+      <c r="K62" s="68">
         <v>40</v>
       </c>
       <c r="L62" s="124">
@@ -6927,29 +6956,29 @@
       <c r="X62" s="49"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A63" s="178">
+      <c r="A63" s="71">
         <v>46302</v>
       </c>
-      <c r="B63" s="179">
+      <c r="B63" s="40">
         <v>57</v>
       </c>
-      <c r="C63" s="183" t="s">
+      <c r="C63" s="125" t="s">
         <v>96</v>
       </c>
-      <c r="D63" s="183" t="s">
+      <c r="D63" s="125" t="s">
         <v>180</v>
       </c>
-      <c r="E63" s="181"/>
-      <c r="F63" s="181"/>
-      <c r="G63" s="181"/>
-      <c r="H63" s="182">
-        <v>40</v>
-      </c>
-      <c r="I63" s="181"/>
-      <c r="J63" s="181">
-        <v>40</v>
-      </c>
-      <c r="K63" s="181"/>
+      <c r="E63" s="68"/>
+      <c r="F63" s="68"/>
+      <c r="G63" s="68"/>
+      <c r="H63" s="124">
+        <v>40</v>
+      </c>
+      <c r="I63" s="68"/>
+      <c r="J63" s="68">
+        <v>40</v>
+      </c>
+      <c r="K63" s="68"/>
       <c r="L63" s="124">
         <f t="shared" si="64"/>
         <v>2</v>
@@ -7000,29 +7029,29 @@
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A64" s="178">
+      <c r="A64" s="71">
         <v>46302</v>
       </c>
-      <c r="B64" s="179">
+      <c r="B64" s="40">
         <v>58</v>
       </c>
-      <c r="C64" s="183" t="s">
+      <c r="C64" s="125" t="s">
         <v>178</v>
       </c>
-      <c r="D64" s="183" t="s">
+      <c r="D64" s="125" t="s">
         <v>179</v>
       </c>
-      <c r="E64" s="181"/>
-      <c r="F64" s="181"/>
-      <c r="G64" s="181"/>
-      <c r="H64" s="182"/>
-      <c r="I64" s="181">
-        <v>40</v>
-      </c>
-      <c r="J64" s="181">
-        <v>40</v>
-      </c>
-      <c r="K64" s="181">
+      <c r="E64" s="68"/>
+      <c r="F64" s="68"/>
+      <c r="G64" s="68"/>
+      <c r="H64" s="124"/>
+      <c r="I64" s="68">
+        <v>40</v>
+      </c>
+      <c r="J64" s="68">
+        <v>40</v>
+      </c>
+      <c r="K64" s="68">
         <v>40</v>
       </c>
       <c r="L64" s="124">
@@ -7075,27 +7104,27 @@
       </c>
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A65" s="178">
+      <c r="A65" s="71">
         <v>46302</v>
       </c>
-      <c r="B65" s="179">
+      <c r="B65" s="40">
         <v>59</v>
       </c>
-      <c r="C65" s="183" t="s">
+      <c r="C65" s="125" t="s">
         <v>181</v>
       </c>
-      <c r="D65" s="183" t="s">
+      <c r="D65" s="125" t="s">
         <v>182</v>
       </c>
-      <c r="E65" s="181"/>
-      <c r="F65" s="181"/>
-      <c r="G65" s="181"/>
-      <c r="H65" s="182"/>
-      <c r="I65" s="181"/>
-      <c r="J65" s="181">
-        <v>40</v>
-      </c>
-      <c r="K65" s="181">
+      <c r="E65" s="68"/>
+      <c r="F65" s="68"/>
+      <c r="G65" s="68"/>
+      <c r="H65" s="124"/>
+      <c r="I65" s="68"/>
+      <c r="J65" s="68">
+        <v>40</v>
+      </c>
+      <c r="K65" s="68">
         <v>40</v>
       </c>
       <c r="L65" s="124">
@@ -7148,33 +7177,33 @@
       </c>
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A66" s="178">
+      <c r="A66" s="71">
         <v>46302</v>
       </c>
-      <c r="B66" s="179">
+      <c r="B66" s="40">
         <v>60</v>
       </c>
-      <c r="C66" s="183" t="s">
+      <c r="C66" s="125" t="s">
         <v>183</v>
       </c>
-      <c r="D66" s="183" t="s">
+      <c r="D66" s="125" t="s">
         <v>184</v>
       </c>
-      <c r="E66" s="181"/>
-      <c r="F66" s="181">
-        <v>40</v>
-      </c>
-      <c r="G66" s="181"/>
-      <c r="H66" s="182">
-        <v>40</v>
-      </c>
-      <c r="I66" s="181">
-        <v>40</v>
-      </c>
-      <c r="J66" s="181">
-        <v>40</v>
-      </c>
-      <c r="K66" s="181">
+      <c r="E66" s="68"/>
+      <c r="F66" s="68">
+        <v>40</v>
+      </c>
+      <c r="G66" s="68"/>
+      <c r="H66" s="124">
+        <v>40</v>
+      </c>
+      <c r="I66" s="68">
+        <v>40</v>
+      </c>
+      <c r="J66" s="68">
+        <v>40</v>
+      </c>
+      <c r="K66" s="68">
         <v>40</v>
       </c>
       <c r="L66" s="124">
@@ -7227,35 +7256,35 @@
       </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A67" s="178">
+      <c r="A67" s="71">
         <v>46302</v>
       </c>
-      <c r="B67" s="179">
+      <c r="B67" s="40">
         <v>61</v>
       </c>
-      <c r="C67" s="183" t="s">
+      <c r="C67" s="125" t="s">
         <v>185</v>
       </c>
-      <c r="D67" s="183" t="s">
+      <c r="D67" s="125" t="s">
         <v>186</v>
       </c>
-      <c r="E67" s="181"/>
-      <c r="F67" s="181">
-        <v>40</v>
-      </c>
-      <c r="G67" s="181">
-        <v>40</v>
-      </c>
-      <c r="H67" s="182">
+      <c r="E67" s="68"/>
+      <c r="F67" s="68">
+        <v>40</v>
+      </c>
+      <c r="G67" s="68">
+        <v>40</v>
+      </c>
+      <c r="H67" s="124">
         <v>80</v>
       </c>
-      <c r="I67" s="181">
-        <v>40</v>
-      </c>
-      <c r="J67" s="181">
-        <v>40</v>
-      </c>
-      <c r="K67" s="181">
+      <c r="I67" s="68">
+        <v>40</v>
+      </c>
+      <c r="J67" s="68">
+        <v>40</v>
+      </c>
+      <c r="K67" s="68">
         <v>80</v>
       </c>
       <c r="L67" s="124">
@@ -7308,31 +7337,31 @@
       </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A68" s="178">
+      <c r="A68" s="71">
         <v>46302</v>
       </c>
-      <c r="B68" s="179">
+      <c r="B68" s="40">
         <v>62</v>
       </c>
-      <c r="C68" s="183" t="s">
+      <c r="C68" s="125" t="s">
         <v>187</v>
       </c>
-      <c r="D68" s="183" t="s">
+      <c r="D68" s="125" t="s">
         <v>188</v>
       </c>
-      <c r="E68" s="181"/>
-      <c r="F68" s="181">
+      <c r="E68" s="68"/>
+      <c r="F68" s="68">
         <v>80</v>
       </c>
-      <c r="G68" s="181"/>
-      <c r="H68" s="182">
+      <c r="G68" s="68"/>
+      <c r="H68" s="124">
         <v>160</v>
       </c>
-      <c r="I68" s="181"/>
-      <c r="J68" s="181">
+      <c r="I68" s="68"/>
+      <c r="J68" s="68">
         <v>160</v>
       </c>
-      <c r="K68" s="181">
+      <c r="K68" s="68">
         <v>160</v>
       </c>
       <c r="L68" s="124">
@@ -7385,29 +7414,29 @@
       </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A69" s="178">
+      <c r="A69" s="71">
         <v>46302</v>
       </c>
-      <c r="B69" s="179">
+      <c r="B69" s="40">
         <v>63</v>
       </c>
-      <c r="C69" s="183" t="s">
+      <c r="C69" s="125" t="s">
         <v>189</v>
       </c>
-      <c r="D69" s="183" t="s">
+      <c r="D69" s="125" t="s">
         <v>190</v>
       </c>
-      <c r="E69" s="181"/>
-      <c r="F69" s="181"/>
-      <c r="G69" s="181"/>
-      <c r="H69" s="182"/>
-      <c r="I69" s="181">
+      <c r="E69" s="68"/>
+      <c r="F69" s="68"/>
+      <c r="G69" s="68"/>
+      <c r="H69" s="124"/>
+      <c r="I69" s="68">
         <v>120</v>
       </c>
-      <c r="J69" s="181">
+      <c r="J69" s="68">
         <v>80</v>
       </c>
-      <c r="K69" s="181">
+      <c r="K69" s="68">
         <v>120</v>
       </c>
       <c r="L69" s="124">
@@ -7460,35 +7489,35 @@
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A70" s="178">
+      <c r="A70" s="71">
         <v>46302</v>
       </c>
-      <c r="B70" s="179">
+      <c r="B70" s="40">
         <v>64</v>
       </c>
-      <c r="C70" s="183" t="s">
+      <c r="C70" s="125" t="s">
         <v>191</v>
       </c>
-      <c r="D70" s="183" t="s">
+      <c r="D70" s="125" t="s">
         <v>192</v>
       </c>
-      <c r="E70" s="181"/>
-      <c r="F70" s="181">
+      <c r="E70" s="68"/>
+      <c r="F70" s="68">
         <v>400</v>
       </c>
-      <c r="G70" s="181">
+      <c r="G70" s="68">
         <v>400</v>
       </c>
-      <c r="H70" s="182">
-        <v>0</v>
-      </c>
-      <c r="I70" s="181">
+      <c r="H70" s="124">
+        <v>0</v>
+      </c>
+      <c r="I70" s="68">
         <v>600</v>
       </c>
-      <c r="J70" s="181">
+      <c r="J70" s="68">
         <v>800</v>
       </c>
-      <c r="K70" s="181">
+      <c r="K70" s="68">
         <v>800</v>
       </c>
       <c r="L70" s="124">
@@ -7541,35 +7570,35 @@
       </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A71" s="134">
+      <c r="A71" s="178">
         <v>46303</v>
       </c>
-      <c r="B71" s="135">
+      <c r="B71" s="179">
         <v>65</v>
       </c>
-      <c r="C71" s="144" t="s">
+      <c r="C71" s="180" t="s">
         <v>193</v>
       </c>
-      <c r="D71" s="144" t="s">
+      <c r="D71" s="180" t="s">
         <v>194</v>
       </c>
-      <c r="E71" s="142"/>
-      <c r="F71" s="142">
+      <c r="E71" s="181"/>
+      <c r="F71" s="181">
         <v>80</v>
       </c>
-      <c r="G71" s="142">
+      <c r="G71" s="181">
         <v>80</v>
       </c>
-      <c r="H71" s="143">
+      <c r="H71" s="182">
         <v>80</v>
       </c>
-      <c r="I71" s="142">
+      <c r="I71" s="181">
         <v>80</v>
       </c>
-      <c r="J71" s="142">
+      <c r="J71" s="181">
         <v>80</v>
       </c>
-      <c r="K71" s="142">
+      <c r="K71" s="181">
         <v>80</v>
       </c>
       <c r="L71" s="124">
@@ -7622,33 +7651,33 @@
       </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A72" s="134">
+      <c r="A72" s="178">
         <v>46303</v>
       </c>
-      <c r="B72" s="135">
+      <c r="B72" s="179">
         <v>66</v>
       </c>
-      <c r="C72" s="144" t="s">
+      <c r="C72" s="180" t="s">
         <v>195</v>
       </c>
-      <c r="D72" s="144" t="s">
+      <c r="D72" s="180" t="s">
         <v>186</v>
       </c>
-      <c r="E72" s="142"/>
-      <c r="F72" s="142"/>
-      <c r="G72" s="142">
+      <c r="E72" s="181"/>
+      <c r="F72" s="181"/>
+      <c r="G72" s="181">
         <v>80</v>
       </c>
-      <c r="H72" s="143">
+      <c r="H72" s="182">
         <v>120</v>
       </c>
-      <c r="I72" s="142">
+      <c r="I72" s="181">
         <v>80</v>
       </c>
-      <c r="J72" s="142">
+      <c r="J72" s="181">
         <v>80</v>
       </c>
-      <c r="K72" s="142">
+      <c r="K72" s="181">
         <v>80</v>
       </c>
       <c r="L72" s="124">
@@ -7701,35 +7730,35 @@
       </c>
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A73" s="134">
+      <c r="A73" s="178">
         <v>46303</v>
       </c>
-      <c r="B73" s="135">
+      <c r="B73" s="179">
         <v>67</v>
       </c>
-      <c r="C73" s="144" t="s">
+      <c r="C73" s="180" t="s">
         <v>113</v>
       </c>
-      <c r="D73" s="144" t="s">
+      <c r="D73" s="180" t="s">
         <v>196</v>
       </c>
-      <c r="E73" s="142"/>
-      <c r="F73" s="142">
-        <v>40</v>
-      </c>
-      <c r="G73" s="142">
-        <v>40</v>
-      </c>
-      <c r="H73" s="143">
-        <v>40</v>
-      </c>
-      <c r="I73" s="142">
-        <v>40</v>
-      </c>
-      <c r="J73" s="142">
-        <v>40</v>
-      </c>
-      <c r="K73" s="142">
+      <c r="E73" s="181"/>
+      <c r="F73" s="181">
+        <v>40</v>
+      </c>
+      <c r="G73" s="181">
+        <v>40</v>
+      </c>
+      <c r="H73" s="182">
+        <v>40</v>
+      </c>
+      <c r="I73" s="181">
+        <v>40</v>
+      </c>
+      <c r="J73" s="181">
+        <v>40</v>
+      </c>
+      <c r="K73" s="181">
         <v>40</v>
       </c>
       <c r="L73" s="124">
@@ -7782,31 +7811,31 @@
       </c>
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A74" s="134">
+      <c r="A74" s="178">
         <v>46303</v>
       </c>
-      <c r="B74" s="135">
+      <c r="B74" s="179">
         <v>68</v>
       </c>
-      <c r="C74" s="144" t="s">
+      <c r="C74" s="180" t="s">
         <v>197</v>
       </c>
-      <c r="D74" s="144" t="s">
+      <c r="D74" s="180" t="s">
         <v>198</v>
       </c>
-      <c r="E74" s="142"/>
-      <c r="F74" s="142"/>
-      <c r="G74" s="142">
-        <v>40</v>
-      </c>
-      <c r="H74" s="143"/>
-      <c r="I74" s="142">
-        <v>40</v>
-      </c>
-      <c r="J74" s="142">
+      <c r="E74" s="181"/>
+      <c r="F74" s="181"/>
+      <c r="G74" s="181">
+        <v>40</v>
+      </c>
+      <c r="H74" s="182"/>
+      <c r="I74" s="181">
+        <v>40</v>
+      </c>
+      <c r="J74" s="181">
         <v>20</v>
       </c>
-      <c r="K74" s="142">
+      <c r="K74" s="181">
         <v>80</v>
       </c>
       <c r="L74" s="124">
@@ -7859,35 +7888,35 @@
       </c>
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A75" s="134">
+      <c r="A75" s="178">
         <v>46303</v>
       </c>
-      <c r="B75" s="135">
+      <c r="B75" s="179">
         <v>69</v>
       </c>
-      <c r="C75" s="144" t="s">
+      <c r="C75" s="180" t="s">
         <v>199</v>
       </c>
-      <c r="D75" s="144" t="s">
+      <c r="D75" s="180" t="s">
         <v>200</v>
       </c>
-      <c r="E75" s="142"/>
-      <c r="F75" s="142">
+      <c r="E75" s="181"/>
+      <c r="F75" s="181">
         <v>200</v>
       </c>
-      <c r="G75" s="142">
+      <c r="G75" s="181">
         <v>200</v>
       </c>
-      <c r="H75" s="143">
+      <c r="H75" s="182">
         <v>200</v>
       </c>
-      <c r="I75" s="142">
+      <c r="I75" s="181">
         <v>200</v>
       </c>
-      <c r="J75" s="142">
+      <c r="J75" s="181">
         <v>200</v>
       </c>
-      <c r="K75" s="142">
+      <c r="K75" s="181">
         <v>200</v>
       </c>
       <c r="L75" s="124">
@@ -7940,35 +7969,35 @@
       </c>
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A76" s="134">
+      <c r="A76" s="178">
         <v>46303</v>
       </c>
-      <c r="B76" s="135">
+      <c r="B76" s="179">
         <v>70</v>
       </c>
-      <c r="C76" s="144" t="s">
+      <c r="C76" s="180" t="s">
         <v>201</v>
       </c>
-      <c r="D76" s="144" t="s">
+      <c r="D76" s="180" t="s">
         <v>202</v>
       </c>
-      <c r="E76" s="142"/>
-      <c r="F76" s="142">
-        <v>40</v>
-      </c>
-      <c r="G76" s="142">
-        <v>40</v>
-      </c>
-      <c r="H76" s="143">
-        <v>40</v>
-      </c>
-      <c r="I76" s="142">
-        <v>40</v>
-      </c>
-      <c r="J76" s="142">
-        <v>40</v>
-      </c>
-      <c r="K76" s="142">
+      <c r="E76" s="181"/>
+      <c r="F76" s="181">
+        <v>40</v>
+      </c>
+      <c r="G76" s="181">
+        <v>40</v>
+      </c>
+      <c r="H76" s="182">
+        <v>40</v>
+      </c>
+      <c r="I76" s="181">
+        <v>40</v>
+      </c>
+      <c r="J76" s="181">
+        <v>40</v>
+      </c>
+      <c r="K76" s="181">
         <v>40</v>
       </c>
       <c r="L76" s="124">
@@ -8021,32 +8050,50 @@
       </c>
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A77" s="71"/>
-      <c r="B77" s="40">
+      <c r="A77" s="134">
+        <v>46304</v>
+      </c>
+      <c r="B77" s="135">
         <v>71</v>
       </c>
-      <c r="C77" s="125"/>
-      <c r="D77" s="125"/>
-      <c r="E77" s="68"/>
-      <c r="F77" s="68"/>
-      <c r="G77" s="68"/>
-      <c r="H77" s="124"/>
-      <c r="I77" s="68"/>
-      <c r="J77" s="68"/>
-      <c r="K77" s="68"/>
+      <c r="C77" s="144" t="s">
+        <v>23</v>
+      </c>
+      <c r="D77" s="144" t="s">
+        <v>112</v>
+      </c>
+      <c r="E77" s="142"/>
+      <c r="F77" s="142">
+        <v>120</v>
+      </c>
+      <c r="G77" s="142"/>
+      <c r="H77" s="143">
+        <v>80</v>
+      </c>
+      <c r="I77" s="142">
+        <v>160</v>
+      </c>
+      <c r="J77" s="142">
+        <v>120</v>
+      </c>
+      <c r="K77" s="142">
+        <v>400</v>
+      </c>
       <c r="L77" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M77" s="138"/>
+        <v>22</v>
+      </c>
+      <c r="M77" s="138">
+        <v>8</v>
+      </c>
       <c r="N77" s="42"/>
       <c r="O77" s="66">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P77" s="33">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q77" s="44" t="e">
         <f t="shared" si="76"/>
@@ -8082,32 +8129,44 @@
       </c>
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A78" s="71"/>
-      <c r="B78" s="40">
+      <c r="A78" s="134">
+        <v>46304</v>
+      </c>
+      <c r="B78" s="135">
         <v>72</v>
       </c>
-      <c r="C78" s="125"/>
-      <c r="D78" s="125"/>
-      <c r="E78" s="68"/>
-      <c r="F78" s="68"/>
-      <c r="G78" s="68"/>
-      <c r="H78" s="124"/>
-      <c r="I78" s="68"/>
-      <c r="J78" s="68"/>
-      <c r="K78" s="68"/>
+      <c r="C78" s="144" t="s">
+        <v>129</v>
+      </c>
+      <c r="D78" s="144"/>
+      <c r="E78" s="142"/>
+      <c r="F78" s="142"/>
+      <c r="G78" s="142">
+        <v>40</v>
+      </c>
+      <c r="H78" s="143"/>
+      <c r="I78" s="142"/>
+      <c r="J78" s="142">
+        <v>40</v>
+      </c>
+      <c r="K78" s="142">
+        <v>40</v>
+      </c>
       <c r="L78" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M78" s="138"/>
+        <v>3</v>
+      </c>
+      <c r="M78" s="138">
+        <v>18</v>
+      </c>
       <c r="N78" s="42"/>
       <c r="O78" s="66">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P78" s="33">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q78" s="44" t="e">
         <f t="shared" si="76"/>
@@ -8143,32 +8202,42 @@
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A79" s="71"/>
-      <c r="B79" s="40">
+      <c r="A79" s="134">
+        <v>46304</v>
+      </c>
+      <c r="B79" s="135">
         <v>73</v>
       </c>
-      <c r="C79" s="125"/>
-      <c r="D79" s="125"/>
-      <c r="E79" s="68"/>
-      <c r="F79" s="68"/>
-      <c r="G79" s="68"/>
-      <c r="H79" s="124"/>
-      <c r="I79" s="68"/>
-      <c r="J79" s="68"/>
-      <c r="K79" s="68"/>
+      <c r="C79" s="144" t="s">
+        <v>203</v>
+      </c>
+      <c r="D79" s="144"/>
+      <c r="E79" s="142"/>
+      <c r="F79" s="142">
+        <v>40</v>
+      </c>
+      <c r="G79" s="142"/>
+      <c r="H79" s="143"/>
+      <c r="I79" s="142"/>
+      <c r="J79" s="142"/>
+      <c r="K79" s="142">
+        <v>40</v>
+      </c>
       <c r="L79" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M79" s="138"/>
+        <v>2</v>
+      </c>
+      <c r="M79" s="138">
+        <v>18</v>
+      </c>
       <c r="N79" s="42"/>
       <c r="O79" s="66">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P79" s="33">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q79" s="44" t="e">
         <f t="shared" si="76"/>
@@ -8204,32 +8273,46 @@
       </c>
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A80" s="71"/>
-      <c r="B80" s="40">
+      <c r="A80" s="134">
+        <v>46304</v>
+      </c>
+      <c r="B80" s="135">
         <v>74</v>
       </c>
-      <c r="C80" s="125"/>
-      <c r="D80" s="125"/>
-      <c r="E80" s="68"/>
-      <c r="F80" s="68"/>
-      <c r="G80" s="68"/>
-      <c r="H80" s="124"/>
-      <c r="I80" s="68"/>
-      <c r="J80" s="68"/>
-      <c r="K80" s="68"/>
+      <c r="C80" s="144" t="s">
+        <v>204</v>
+      </c>
+      <c r="D80" s="144"/>
+      <c r="E80" s="142"/>
+      <c r="F80" s="142">
+        <v>40</v>
+      </c>
+      <c r="G80" s="142">
+        <v>40</v>
+      </c>
+      <c r="H80" s="143"/>
+      <c r="I80" s="142"/>
+      <c r="J80" s="142">
+        <v>40</v>
+      </c>
+      <c r="K80" s="142">
+        <v>40</v>
+      </c>
       <c r="L80" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M80" s="138"/>
+        <v>4</v>
+      </c>
+      <c r="M80" s="138">
+        <v>18</v>
+      </c>
       <c r="N80" s="42"/>
       <c r="O80" s="66">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P80" s="33">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q80" s="44" t="e">
         <f t="shared" si="76"/>
@@ -8265,24 +8348,34 @@
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A81" s="71"/>
-      <c r="B81" s="40">
+      <c r="A81" s="134">
+        <v>46304</v>
+      </c>
+      <c r="B81" s="135">
         <v>75</v>
       </c>
-      <c r="C81" s="125"/>
-      <c r="D81" s="125"/>
-      <c r="E81" s="68"/>
-      <c r="F81" s="68"/>
-      <c r="G81" s="68"/>
-      <c r="H81" s="124"/>
-      <c r="I81" s="68"/>
-      <c r="J81" s="68"/>
-      <c r="K81" s="68"/>
+      <c r="C81" s="144" t="s">
+        <v>205</v>
+      </c>
+      <c r="D81" s="144"/>
+      <c r="E81" s="142"/>
+      <c r="F81" s="142"/>
+      <c r="G81" s="142"/>
+      <c r="H81" s="143"/>
+      <c r="I81" s="142">
+        <v>40</v>
+      </c>
+      <c r="J81" s="142"/>
+      <c r="K81" s="142">
+        <v>40</v>
+      </c>
       <c r="L81" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M81" s="138"/>
+        <v>2</v>
+      </c>
+      <c r="M81" s="138">
+        <v>18</v>
+      </c>
       <c r="N81" s="42"/>
       <c r="O81" s="66">
         <f t="shared" si="78"/>
@@ -8290,7 +8383,7 @@
       </c>
       <c r="P81" s="33">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q81" s="44" t="e">
         <f t="shared" si="76"/>
@@ -8326,24 +8419,36 @@
       </c>
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A82" s="71"/>
-      <c r="B82" s="40">
+      <c r="A82" s="134">
+        <v>46304</v>
+      </c>
+      <c r="B82" s="135">
         <v>76</v>
       </c>
-      <c r="C82" s="125"/>
-      <c r="D82" s="125"/>
-      <c r="E82" s="68"/>
-      <c r="F82" s="68"/>
-      <c r="G82" s="68"/>
-      <c r="H82" s="124"/>
-      <c r="I82" s="68"/>
-      <c r="J82" s="68"/>
-      <c r="K82" s="68"/>
+      <c r="C82" s="144" t="s">
+        <v>206</v>
+      </c>
+      <c r="D82" s="144"/>
+      <c r="E82" s="142"/>
+      <c r="F82" s="142"/>
+      <c r="G82" s="142"/>
+      <c r="H82" s="143"/>
+      <c r="I82" s="142">
+        <v>20</v>
+      </c>
+      <c r="J82" s="142">
+        <v>20</v>
+      </c>
+      <c r="K82" s="142">
+        <v>20</v>
+      </c>
       <c r="L82" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M82" s="138"/>
+        <v>1.5</v>
+      </c>
+      <c r="M82" s="138">
+        <v>18</v>
+      </c>
       <c r="N82" s="42"/>
       <c r="O82" s="66">
         <f t="shared" ref="O82:O86" si="85">SUM(F82:H82)/20</f>
@@ -8351,7 +8456,7 @@
       </c>
       <c r="P82" s="33">
         <f t="shared" ref="P82:P86" si="86">SUM(I82:K82)/20</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q82" s="44" t="e">
         <f t="shared" si="76"/>
@@ -8387,32 +8492,42 @@
       </c>
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A83" s="71"/>
-      <c r="B83" s="40">
+      <c r="A83" s="134">
+        <v>46304</v>
+      </c>
+      <c r="B83" s="135">
         <v>77</v>
       </c>
-      <c r="C83" s="125"/>
-      <c r="D83" s="125"/>
-      <c r="E83" s="68"/>
-      <c r="F83" s="68"/>
-      <c r="G83" s="68"/>
-      <c r="H83" s="124"/>
-      <c r="I83" s="68"/>
-      <c r="J83" s="68"/>
-      <c r="K83" s="68"/>
+      <c r="C83" s="144" t="s">
+        <v>207</v>
+      </c>
+      <c r="D83" s="144"/>
+      <c r="E83" s="142"/>
+      <c r="F83" s="142">
+        <v>40</v>
+      </c>
+      <c r="G83" s="142"/>
+      <c r="H83" s="143"/>
+      <c r="I83" s="142">
+        <v>40</v>
+      </c>
+      <c r="J83" s="142"/>
+      <c r="K83" s="142"/>
       <c r="L83" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M83" s="138"/>
+        <v>2</v>
+      </c>
+      <c r="M83" s="138">
+        <v>18</v>
+      </c>
       <c r="N83" s="42"/>
       <c r="O83" s="66">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P83" s="33">
         <f t="shared" si="86"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q83" s="44" t="e">
         <f t="shared" si="76"/>
@@ -8448,32 +8563,46 @@
       </c>
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A84" s="71"/>
-      <c r="B84" s="40">
+      <c r="A84" s="134">
+        <v>46304</v>
+      </c>
+      <c r="B84" s="135">
         <v>78</v>
       </c>
-      <c r="C84" s="125"/>
-      <c r="D84" s="125"/>
-      <c r="E84" s="68"/>
-      <c r="F84" s="68"/>
-      <c r="G84" s="68"/>
-      <c r="H84" s="124"/>
-      <c r="I84" s="68"/>
-      <c r="J84" s="68"/>
-      <c r="K84" s="68"/>
+      <c r="C84" s="144" t="s">
+        <v>208</v>
+      </c>
+      <c r="D84" s="144"/>
+      <c r="E84" s="142"/>
+      <c r="F84" s="142">
+        <v>40</v>
+      </c>
+      <c r="G84" s="142">
+        <v>40</v>
+      </c>
+      <c r="H84" s="143"/>
+      <c r="I84" s="142"/>
+      <c r="J84" s="142">
+        <v>40</v>
+      </c>
+      <c r="K84" s="142">
+        <v>40</v>
+      </c>
       <c r="L84" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M84" s="138"/>
+        <v>4</v>
+      </c>
+      <c r="M84" s="138">
+        <v>18</v>
+      </c>
       <c r="N84" s="42"/>
       <c r="O84" s="66">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P84" s="33">
         <f t="shared" si="86"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q84" s="44" t="e">
         <f t="shared" si="76"/>
@@ -8509,32 +8638,46 @@
       </c>
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A85" s="71"/>
-      <c r="B85" s="40">
+      <c r="A85" s="134">
+        <v>46304</v>
+      </c>
+      <c r="B85" s="135">
         <v>79</v>
       </c>
-      <c r="C85" s="125"/>
-      <c r="D85" s="125"/>
-      <c r="E85" s="68"/>
-      <c r="F85" s="68"/>
-      <c r="G85" s="68"/>
-      <c r="H85" s="124"/>
-      <c r="I85" s="68"/>
-      <c r="J85" s="68"/>
-      <c r="K85" s="68"/>
+      <c r="C85" s="144" t="s">
+        <v>209</v>
+      </c>
+      <c r="D85" s="144"/>
+      <c r="E85" s="142"/>
+      <c r="F85" s="142"/>
+      <c r="G85" s="142">
+        <v>40</v>
+      </c>
+      <c r="H85" s="143"/>
+      <c r="I85" s="142">
+        <v>40</v>
+      </c>
+      <c r="J85" s="142">
+        <v>40</v>
+      </c>
+      <c r="K85" s="142">
+        <v>40</v>
+      </c>
       <c r="L85" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M85" s="138"/>
+        <v>4</v>
+      </c>
+      <c r="M85" s="138">
+        <v>18</v>
+      </c>
       <c r="N85" s="42"/>
       <c r="O85" s="66">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P85" s="33">
         <f t="shared" si="86"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q85" s="44" t="e">
         <f t="shared" si="76"/>
@@ -8570,24 +8713,34 @@
       </c>
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A86" s="71"/>
-      <c r="B86" s="40">
+      <c r="A86" s="134">
+        <v>46304</v>
+      </c>
+      <c r="B86" s="135">
         <v>80</v>
       </c>
-      <c r="C86" s="125"/>
-      <c r="D86" s="125"/>
-      <c r="E86" s="68"/>
-      <c r="F86" s="68"/>
-      <c r="G86" s="68"/>
-      <c r="H86" s="124"/>
-      <c r="I86" s="68"/>
-      <c r="J86" s="68"/>
-      <c r="K86" s="68"/>
+      <c r="C86" s="144" t="s">
+        <v>210</v>
+      </c>
+      <c r="D86" s="144"/>
+      <c r="E86" s="142"/>
+      <c r="F86" s="142"/>
+      <c r="G86" s="142"/>
+      <c r="H86" s="143"/>
+      <c r="I86" s="142">
+        <v>40</v>
+      </c>
+      <c r="J86" s="142"/>
+      <c r="K86" s="142">
+        <v>40</v>
+      </c>
       <c r="L86" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M86" s="138"/>
+        <v>2</v>
+      </c>
+      <c r="M86" s="138">
+        <v>18</v>
+      </c>
       <c r="N86" s="42"/>
       <c r="O86" s="66">
         <f t="shared" si="85"/>
@@ -8595,7 +8748,7 @@
       </c>
       <c r="P86" s="33">
         <f t="shared" si="86"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q86" s="44" t="e">
         <f t="shared" si="76"/>
@@ -8631,24 +8784,38 @@
       </c>
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A87" s="71"/>
-      <c r="B87" s="40">
+      <c r="A87" s="134">
+        <v>46304</v>
+      </c>
+      <c r="B87" s="135">
         <v>81</v>
       </c>
-      <c r="C87" s="125"/>
-      <c r="D87" s="125"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="68"/>
-      <c r="G87" s="68"/>
-      <c r="H87" s="124"/>
-      <c r="I87" s="68"/>
-      <c r="J87" s="68"/>
-      <c r="K87" s="68"/>
+      <c r="C87" s="144" t="s">
+        <v>211</v>
+      </c>
+      <c r="D87" s="144" t="s">
+        <v>212</v>
+      </c>
+      <c r="E87" s="142"/>
+      <c r="F87" s="142"/>
+      <c r="G87" s="142"/>
+      <c r="H87" s="143"/>
+      <c r="I87" s="142">
+        <v>3000</v>
+      </c>
+      <c r="J87" s="142">
+        <v>2000</v>
+      </c>
+      <c r="K87" s="142">
+        <v>3000</v>
+      </c>
       <c r="L87" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M87" s="138"/>
+        <v>200</v>
+      </c>
+      <c r="M87" s="138">
+        <v>16</v>
+      </c>
       <c r="N87" s="42"/>
       <c r="O87" s="66">
         <f t="shared" ref="O87:O134" si="91">SUM(F87:H87)/20</f>
@@ -8656,7 +8823,7 @@
       </c>
       <c r="P87" s="33">
         <f t="shared" ref="P87:P134" si="92">SUM(I87:K87)/20</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Q87" s="44" t="e">
         <f t="shared" si="76"/>
@@ -11565,10 +11732,10 @@
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A135" s="71"/>
-      <c r="B135" s="155" t="s">
+      <c r="B135" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="C135" s="155"/>
+      <c r="C135" s="168"/>
       <c r="D135" s="135"/>
       <c r="E135" s="140">
         <f t="shared" ref="E135:K135" si="103">SUM(E6:E63)</f>
@@ -11819,10 +11986,10 @@
       </c>
     </row>
     <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B139" s="167" t="s">
+      <c r="B139" s="156" t="s">
         <v>68</v>
       </c>
-      <c r="C139" s="168"/>
+      <c r="C139" s="157"/>
       <c r="D139" s="128"/>
       <c r="E139" s="76">
         <f>SUM(E137:E138)</f>
@@ -11906,10 +12073,10 @@
       </c>
     </row>
     <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B140" s="156" t="s">
+      <c r="B140" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="C140" s="157"/>
+      <c r="C140" s="146"/>
       <c r="D140" s="129"/>
       <c r="E140" s="77">
         <f>SUM(E135,E139)</f>
@@ -11945,7 +12112,7 @@
       </c>
       <c r="M140" s="56">
         <f>SUM(M5:M139)</f>
-        <v>1145</v>
+        <v>1331</v>
       </c>
       <c r="N140" s="54">
         <f t="shared" ref="N140:X140" si="111">SUM(N5:N139)</f>
@@ -11953,11 +12120,11 @@
       </c>
       <c r="O140" s="55">
         <f t="shared" si="111"/>
-        <v>667.7</v>
+        <v>693.7</v>
       </c>
       <c r="P140" s="57">
         <f t="shared" si="111"/>
-        <v>1112.2</v>
+        <v>1579.1999999999998</v>
       </c>
       <c r="Q140" s="58" t="e">
         <f t="shared" si="111"/>
@@ -11994,17 +12161,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B135:C135"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B135:C135"/>
   </mergeCells>
   <conditionalFormatting sqref="C48:D62">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12104,24 +12271,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="80">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="E5" s="72">
-        <v>374</v>
+        <v>420</v>
       </c>
       <c r="F5" s="72">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="G5" s="94">
         <f>SUM(D5:F5)</f>
-        <v>747</v>
+        <v>1018</v>
       </c>
       <c r="H5" s="87">
         <v>10000</v>
       </c>
       <c r="I5" s="88">
         <f>G5-H5</f>
-        <v>-9253</v>
+        <v>-8982</v>
       </c>
       <c r="K5" s="132" t="s">
         <v>1</v>
@@ -12152,19 +12319,19 @@
       </c>
       <c r="D6" s="96">
         <f>D5*40</f>
-        <v>8320</v>
+        <v>9320</v>
       </c>
       <c r="E6" s="96">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>14960</v>
+        <v>16800</v>
       </c>
       <c r="F6" s="96">
         <f t="shared" si="1"/>
-        <v>6600</v>
+        <v>14600</v>
       </c>
       <c r="G6" s="97">
         <f>SUM(D6:F6)</f>
-        <v>29880</v>
+        <v>40720</v>
       </c>
       <c r="H6" s="89">
         <f>H5*40</f>
@@ -12172,7 +12339,7 @@
       </c>
       <c r="I6" s="90">
         <f>G6-H6</f>
-        <v>-370120</v>
+        <v>-359280</v>
       </c>
       <c r="K6" s="132" t="s">
         <v>2</v>
@@ -12321,11 +12488,11 @@
       </c>
       <c r="D9" s="98">
         <f>D8-D5</f>
-        <v>-208</v>
+        <v>-233</v>
       </c>
       <c r="E9" s="98">
         <f>E8-E5</f>
-        <v>-374</v>
+        <v>-420</v>
       </c>
       <c r="K9" s="132" t="s">
         <v>5</v>
@@ -12482,7 +12649,7 @@
       </c>
       <c r="G12" s="83">
         <f>D12+G5</f>
-        <v>4947</v>
+        <v>5218</v>
       </c>
       <c r="K12" s="132" t="s">
         <v>11</v>
@@ -12534,7 +12701,7 @@
       </c>
       <c r="G13" s="83">
         <f>G12*40</f>
-        <v>197880</v>
+        <v>208720</v>
       </c>
       <c r="S13" s="169" t="s">
         <v>83</v>

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE196407-1A33-4552-9828-D0DC9A889BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D8811B-541A-490F-9F6A-056EF175A88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1528,7 +1528,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1906,6 +1906,39 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1945,39 +1978,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2004,17 +2004,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2608,13 +2597,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="158">
+      <c r="B1" s="145">
         <f ca="1">TODAY()</f>
         <v>46305</v>
       </c>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2636,10 +2625,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="166" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="146" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2669,13 +2658,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="147"/>
-      <c r="M2" s="148"/>
-      <c r="N2" s="149"/>
-      <c r="O2" s="150" t="s">
+      <c r="L2" s="158"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="160"/>
+      <c r="O2" s="161" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="151"/>
+      <c r="P2" s="162"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2694,8 +2683,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="155"/>
-      <c r="B3" s="160"/>
+      <c r="A3" s="166"/>
+      <c r="B3" s="147"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2723,29 +2712,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="152" t="s">
+      <c r="L3" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="153"/>
-      <c r="N3" s="154"/>
+      <c r="M3" s="164"/>
+      <c r="N3" s="165"/>
       <c r="O3" s="64"/>
       <c r="P3" s="65"/>
-      <c r="Q3" s="162" t="s">
+      <c r="Q3" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="163"/>
-      <c r="S3" s="163"/>
-      <c r="T3" s="164"/>
-      <c r="U3" s="165" t="s">
+      <c r="R3" s="150"/>
+      <c r="S3" s="150"/>
+      <c r="T3" s="151"/>
+      <c r="U3" s="152" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="166"/>
-      <c r="W3" s="166"/>
-      <c r="X3" s="167"/>
+      <c r="V3" s="153"/>
+      <c r="W3" s="153"/>
+      <c r="X3" s="154"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="155"/>
-      <c r="B4" s="161"/>
+      <c r="A4" s="166"/>
+      <c r="B4" s="148"/>
       <c r="C4" s="130" t="s">
         <v>90</v>
       </c>
@@ -7570,35 +7559,35 @@
       </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A71" s="178">
+      <c r="A71" s="71">
         <v>46303</v>
       </c>
-      <c r="B71" s="179">
+      <c r="B71" s="40">
         <v>65</v>
       </c>
-      <c r="C71" s="180" t="s">
+      <c r="C71" s="125" t="s">
         <v>193</v>
       </c>
-      <c r="D71" s="180" t="s">
+      <c r="D71" s="125" t="s">
         <v>194</v>
       </c>
-      <c r="E71" s="181"/>
-      <c r="F71" s="181">
+      <c r="E71" s="68"/>
+      <c r="F71" s="68">
         <v>80</v>
       </c>
-      <c r="G71" s="181">
+      <c r="G71" s="68">
         <v>80</v>
       </c>
-      <c r="H71" s="182">
+      <c r="H71" s="124">
         <v>80</v>
       </c>
-      <c r="I71" s="181">
+      <c r="I71" s="68">
         <v>80</v>
       </c>
-      <c r="J71" s="181">
+      <c r="J71" s="68">
         <v>80</v>
       </c>
-      <c r="K71" s="181">
+      <c r="K71" s="68">
         <v>80</v>
       </c>
       <c r="L71" s="124">
@@ -7651,33 +7640,33 @@
       </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A72" s="178">
+      <c r="A72" s="71">
         <v>46303</v>
       </c>
-      <c r="B72" s="179">
+      <c r="B72" s="40">
         <v>66</v>
       </c>
-      <c r="C72" s="180" t="s">
+      <c r="C72" s="125" t="s">
         <v>195</v>
       </c>
-      <c r="D72" s="180" t="s">
+      <c r="D72" s="125" t="s">
         <v>186</v>
       </c>
-      <c r="E72" s="181"/>
-      <c r="F72" s="181"/>
-      <c r="G72" s="181">
+      <c r="E72" s="68"/>
+      <c r="F72" s="68"/>
+      <c r="G72" s="68">
         <v>80</v>
       </c>
-      <c r="H72" s="182">
+      <c r="H72" s="124">
         <v>120</v>
       </c>
-      <c r="I72" s="181">
+      <c r="I72" s="68">
         <v>80</v>
       </c>
-      <c r="J72" s="181">
+      <c r="J72" s="68">
         <v>80</v>
       </c>
-      <c r="K72" s="181">
+      <c r="K72" s="68">
         <v>80</v>
       </c>
       <c r="L72" s="124">
@@ -7730,35 +7719,35 @@
       </c>
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A73" s="178">
+      <c r="A73" s="71">
         <v>46303</v>
       </c>
-      <c r="B73" s="179">
+      <c r="B73" s="40">
         <v>67</v>
       </c>
-      <c r="C73" s="180" t="s">
+      <c r="C73" s="125" t="s">
         <v>113</v>
       </c>
-      <c r="D73" s="180" t="s">
+      <c r="D73" s="125" t="s">
         <v>196</v>
       </c>
-      <c r="E73" s="181"/>
-      <c r="F73" s="181">
-        <v>40</v>
-      </c>
-      <c r="G73" s="181">
-        <v>40</v>
-      </c>
-      <c r="H73" s="182">
-        <v>40</v>
-      </c>
-      <c r="I73" s="181">
-        <v>40</v>
-      </c>
-      <c r="J73" s="181">
-        <v>40</v>
-      </c>
-      <c r="K73" s="181">
+      <c r="E73" s="68"/>
+      <c r="F73" s="68">
+        <v>40</v>
+      </c>
+      <c r="G73" s="68">
+        <v>40</v>
+      </c>
+      <c r="H73" s="124">
+        <v>40</v>
+      </c>
+      <c r="I73" s="68">
+        <v>40</v>
+      </c>
+      <c r="J73" s="68">
+        <v>40</v>
+      </c>
+      <c r="K73" s="68">
         <v>40</v>
       </c>
       <c r="L73" s="124">
@@ -7811,31 +7800,31 @@
       </c>
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A74" s="178">
+      <c r="A74" s="71">
         <v>46303</v>
       </c>
-      <c r="B74" s="179">
+      <c r="B74" s="40">
         <v>68</v>
       </c>
-      <c r="C74" s="180" t="s">
+      <c r="C74" s="125" t="s">
         <v>197</v>
       </c>
-      <c r="D74" s="180" t="s">
+      <c r="D74" s="125" t="s">
         <v>198</v>
       </c>
-      <c r="E74" s="181"/>
-      <c r="F74" s="181"/>
-      <c r="G74" s="181">
-        <v>40</v>
-      </c>
-      <c r="H74" s="182"/>
-      <c r="I74" s="181">
-        <v>40</v>
-      </c>
-      <c r="J74" s="181">
+      <c r="E74" s="68"/>
+      <c r="F74" s="68"/>
+      <c r="G74" s="68">
+        <v>40</v>
+      </c>
+      <c r="H74" s="124"/>
+      <c r="I74" s="68">
+        <v>40</v>
+      </c>
+      <c r="J74" s="68">
         <v>20</v>
       </c>
-      <c r="K74" s="181">
+      <c r="K74" s="68">
         <v>80</v>
       </c>
       <c r="L74" s="124">
@@ -7888,35 +7877,35 @@
       </c>
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A75" s="178">
+      <c r="A75" s="71">
         <v>46303</v>
       </c>
-      <c r="B75" s="179">
+      <c r="B75" s="40">
         <v>69</v>
       </c>
-      <c r="C75" s="180" t="s">
+      <c r="C75" s="125" t="s">
         <v>199</v>
       </c>
-      <c r="D75" s="180" t="s">
+      <c r="D75" s="125" t="s">
         <v>200</v>
       </c>
-      <c r="E75" s="181"/>
-      <c r="F75" s="181">
+      <c r="E75" s="68"/>
+      <c r="F75" s="68">
         <v>200</v>
       </c>
-      <c r="G75" s="181">
+      <c r="G75" s="68">
         <v>200</v>
       </c>
-      <c r="H75" s="182">
+      <c r="H75" s="124">
         <v>200</v>
       </c>
-      <c r="I75" s="181">
+      <c r="I75" s="68">
         <v>200</v>
       </c>
-      <c r="J75" s="181">
+      <c r="J75" s="68">
         <v>200</v>
       </c>
-      <c r="K75" s="181">
+      <c r="K75" s="68">
         <v>200</v>
       </c>
       <c r="L75" s="124">
@@ -7969,35 +7958,35 @@
       </c>
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A76" s="178">
+      <c r="A76" s="71">
         <v>46303</v>
       </c>
-      <c r="B76" s="179">
+      <c r="B76" s="40">
         <v>70</v>
       </c>
-      <c r="C76" s="180" t="s">
+      <c r="C76" s="125" t="s">
         <v>201</v>
       </c>
-      <c r="D76" s="180" t="s">
+      <c r="D76" s="125" t="s">
         <v>202</v>
       </c>
-      <c r="E76" s="181"/>
-      <c r="F76" s="181">
-        <v>40</v>
-      </c>
-      <c r="G76" s="181">
-        <v>40</v>
-      </c>
-      <c r="H76" s="182">
-        <v>40</v>
-      </c>
-      <c r="I76" s="181">
-        <v>40</v>
-      </c>
-      <c r="J76" s="181">
-        <v>40</v>
-      </c>
-      <c r="K76" s="181">
+      <c r="E76" s="68"/>
+      <c r="F76" s="68">
+        <v>40</v>
+      </c>
+      <c r="G76" s="68">
+        <v>40</v>
+      </c>
+      <c r="H76" s="124">
+        <v>40</v>
+      </c>
+      <c r="I76" s="68">
+        <v>40</v>
+      </c>
+      <c r="J76" s="68">
+        <v>40</v>
+      </c>
+      <c r="K76" s="68">
         <v>40</v>
       </c>
       <c r="L76" s="124">
@@ -11732,10 +11721,10 @@
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A135" s="71"/>
-      <c r="B135" s="168" t="s">
+      <c r="B135" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="C135" s="168"/>
+      <c r="C135" s="155"/>
       <c r="D135" s="135"/>
       <c r="E135" s="140">
         <f t="shared" ref="E135:K135" si="103">SUM(E6:E63)</f>
@@ -11986,10 +11975,10 @@
       </c>
     </row>
     <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B139" s="156" t="s">
+      <c r="B139" s="167" t="s">
         <v>68</v>
       </c>
-      <c r="C139" s="157"/>
+      <c r="C139" s="168"/>
       <c r="D139" s="128"/>
       <c r="E139" s="76">
         <f>SUM(E137:E138)</f>
@@ -12073,10 +12062,10 @@
       </c>
     </row>
     <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B140" s="145" t="s">
+      <c r="B140" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="C140" s="146"/>
+      <c r="C140" s="157"/>
       <c r="D140" s="129"/>
       <c r="E140" s="77">
         <f>SUM(E135,E139)</f>
@@ -12161,17 +12150,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B135:C135"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B135:C135"/>
   </mergeCells>
   <conditionalFormatting sqref="C48:D62">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D8811B-541A-490F-9F6A-056EF175A88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080568C2-4405-4BC4-9B08-15CFB0E546FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="217">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -661,6 +661,18 @@
   </si>
   <si>
     <t>Mughalpura</t>
+  </si>
+  <si>
+    <t>Al Rehmat Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EME Society </t>
+  </si>
+  <si>
+    <t>Euro Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Behria Town </t>
   </si>
 </sst>
 </file>
@@ -1528,7 +1540,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1906,6 +1918,45 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1939,45 +1990,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2004,6 +2016,17 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2597,13 +2620,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="145">
+      <c r="B1" s="158">
         <f ca="1">TODAY()</f>
-        <v>46305</v>
-      </c>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
+        <v>46307</v>
+      </c>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2625,10 +2648,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="166" t="s">
+      <c r="A2" s="155" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="146" t="s">
+      <c r="B2" s="159" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2658,13 +2681,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="158"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="160"/>
-      <c r="O2" s="161" t="s">
+      <c r="L2" s="147"/>
+      <c r="M2" s="148"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="150" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="162"/>
+      <c r="P2" s="151"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2683,8 +2706,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="166"/>
-      <c r="B3" s="147"/>
+      <c r="A3" s="155"/>
+      <c r="B3" s="160"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2712,29 +2735,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="163" t="s">
+      <c r="L3" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="164"/>
-      <c r="N3" s="165"/>
+      <c r="M3" s="153"/>
+      <c r="N3" s="154"/>
       <c r="O3" s="64"/>
       <c r="P3" s="65"/>
-      <c r="Q3" s="149" t="s">
+      <c r="Q3" s="162" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="150"/>
-      <c r="S3" s="150"/>
-      <c r="T3" s="151"/>
-      <c r="U3" s="152" t="s">
+      <c r="R3" s="163"/>
+      <c r="S3" s="163"/>
+      <c r="T3" s="164"/>
+      <c r="U3" s="165" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="153"/>
-      <c r="W3" s="153"/>
-      <c r="X3" s="154"/>
+      <c r="V3" s="166"/>
+      <c r="W3" s="166"/>
+      <c r="X3" s="167"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="166"/>
-      <c r="B4" s="148"/>
+      <c r="A4" s="155"/>
+      <c r="B4" s="161"/>
       <c r="C4" s="130" t="s">
         <v>90</v>
       </c>
@@ -8039,36 +8062,36 @@
       </c>
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A77" s="134">
+      <c r="A77" s="178">
         <v>46304</v>
       </c>
-      <c r="B77" s="135">
+      <c r="B77" s="179">
         <v>71</v>
       </c>
-      <c r="C77" s="144" t="s">
+      <c r="C77" s="180" t="s">
         <v>23</v>
       </c>
-      <c r="D77" s="144" t="s">
+      <c r="D77" s="180" t="s">
         <v>112</v>
       </c>
-      <c r="E77" s="142"/>
-      <c r="F77" s="142">
+      <c r="E77" s="181"/>
+      <c r="F77" s="181">
         <v>120</v>
       </c>
-      <c r="G77" s="142"/>
-      <c r="H77" s="143">
+      <c r="G77" s="181"/>
+      <c r="H77" s="182">
         <v>80</v>
       </c>
-      <c r="I77" s="142">
+      <c r="I77" s="181">
         <v>160</v>
       </c>
-      <c r="J77" s="142">
+      <c r="J77" s="181">
         <v>120</v>
       </c>
-      <c r="K77" s="142">
+      <c r="K77" s="181">
         <v>400</v>
       </c>
-      <c r="L77" s="124">
+      <c r="L77" s="182">
         <f t="shared" si="84"/>
         <v>22</v>
       </c>
@@ -8118,30 +8141,30 @@
       </c>
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A78" s="134">
+      <c r="A78" s="178">
         <v>46304</v>
       </c>
-      <c r="B78" s="135">
+      <c r="B78" s="179">
         <v>72</v>
       </c>
-      <c r="C78" s="144" t="s">
+      <c r="C78" s="180" t="s">
         <v>129</v>
       </c>
-      <c r="D78" s="144"/>
-      <c r="E78" s="142"/>
-      <c r="F78" s="142"/>
-      <c r="G78" s="142">
-        <v>40</v>
-      </c>
-      <c r="H78" s="143"/>
-      <c r="I78" s="142"/>
-      <c r="J78" s="142">
-        <v>40</v>
-      </c>
-      <c r="K78" s="142">
-        <v>40</v>
-      </c>
-      <c r="L78" s="124">
+      <c r="D78" s="180"/>
+      <c r="E78" s="181"/>
+      <c r="F78" s="181"/>
+      <c r="G78" s="181">
+        <v>40</v>
+      </c>
+      <c r="H78" s="182"/>
+      <c r="I78" s="181"/>
+      <c r="J78" s="181">
+        <v>40</v>
+      </c>
+      <c r="K78" s="181">
+        <v>40</v>
+      </c>
+      <c r="L78" s="182">
         <f t="shared" si="84"/>
         <v>3</v>
       </c>
@@ -8191,28 +8214,28 @@
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A79" s="134">
+      <c r="A79" s="178">
         <v>46304</v>
       </c>
-      <c r="B79" s="135">
+      <c r="B79" s="179">
         <v>73</v>
       </c>
-      <c r="C79" s="144" t="s">
+      <c r="C79" s="180" t="s">
         <v>203</v>
       </c>
-      <c r="D79" s="144"/>
-      <c r="E79" s="142"/>
-      <c r="F79" s="142">
-        <v>40</v>
-      </c>
-      <c r="G79" s="142"/>
-      <c r="H79" s="143"/>
-      <c r="I79" s="142"/>
-      <c r="J79" s="142"/>
-      <c r="K79" s="142">
-        <v>40</v>
-      </c>
-      <c r="L79" s="124">
+      <c r="D79" s="180"/>
+      <c r="E79" s="181"/>
+      <c r="F79" s="181">
+        <v>40</v>
+      </c>
+      <c r="G79" s="181"/>
+      <c r="H79" s="182"/>
+      <c r="I79" s="181"/>
+      <c r="J79" s="181"/>
+      <c r="K79" s="181">
+        <v>40</v>
+      </c>
+      <c r="L79" s="182">
         <f t="shared" si="84"/>
         <v>2</v>
       </c>
@@ -8262,32 +8285,32 @@
       </c>
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A80" s="134">
+      <c r="A80" s="178">
         <v>46304</v>
       </c>
-      <c r="B80" s="135">
+      <c r="B80" s="179">
         <v>74</v>
       </c>
-      <c r="C80" s="144" t="s">
+      <c r="C80" s="180" t="s">
         <v>204</v>
       </c>
-      <c r="D80" s="144"/>
-      <c r="E80" s="142"/>
-      <c r="F80" s="142">
-        <v>40</v>
-      </c>
-      <c r="G80" s="142">
-        <v>40</v>
-      </c>
-      <c r="H80" s="143"/>
-      <c r="I80" s="142"/>
-      <c r="J80" s="142">
-        <v>40</v>
-      </c>
-      <c r="K80" s="142">
-        <v>40</v>
-      </c>
-      <c r="L80" s="124">
+      <c r="D80" s="180"/>
+      <c r="E80" s="181"/>
+      <c r="F80" s="181">
+        <v>40</v>
+      </c>
+      <c r="G80" s="181">
+        <v>40</v>
+      </c>
+      <c r="H80" s="182"/>
+      <c r="I80" s="181"/>
+      <c r="J80" s="181">
+        <v>40</v>
+      </c>
+      <c r="K80" s="181">
+        <v>40</v>
+      </c>
+      <c r="L80" s="182">
         <f t="shared" si="84"/>
         <v>4</v>
       </c>
@@ -8337,28 +8360,28 @@
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A81" s="134">
+      <c r="A81" s="178">
         <v>46304</v>
       </c>
-      <c r="B81" s="135">
+      <c r="B81" s="179">
         <v>75</v>
       </c>
-      <c r="C81" s="144" t="s">
+      <c r="C81" s="180" t="s">
         <v>205</v>
       </c>
-      <c r="D81" s="144"/>
-      <c r="E81" s="142"/>
-      <c r="F81" s="142"/>
-      <c r="G81" s="142"/>
-      <c r="H81" s="143"/>
-      <c r="I81" s="142">
-        <v>40</v>
-      </c>
-      <c r="J81" s="142"/>
-      <c r="K81" s="142">
-        <v>40</v>
-      </c>
-      <c r="L81" s="124">
+      <c r="D81" s="180"/>
+      <c r="E81" s="181"/>
+      <c r="F81" s="181"/>
+      <c r="G81" s="181"/>
+      <c r="H81" s="182"/>
+      <c r="I81" s="181">
+        <v>40</v>
+      </c>
+      <c r="J81" s="181"/>
+      <c r="K81" s="181">
+        <v>40</v>
+      </c>
+      <c r="L81" s="182">
         <f t="shared" si="84"/>
         <v>2</v>
       </c>
@@ -8408,30 +8431,30 @@
       </c>
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A82" s="134">
+      <c r="A82" s="178">
         <v>46304</v>
       </c>
-      <c r="B82" s="135">
+      <c r="B82" s="179">
         <v>76</v>
       </c>
-      <c r="C82" s="144" t="s">
+      <c r="C82" s="180" t="s">
         <v>206</v>
       </c>
-      <c r="D82" s="144"/>
-      <c r="E82" s="142"/>
-      <c r="F82" s="142"/>
-      <c r="G82" s="142"/>
-      <c r="H82" s="143"/>
-      <c r="I82" s="142">
+      <c r="D82" s="180"/>
+      <c r="E82" s="181"/>
+      <c r="F82" s="181"/>
+      <c r="G82" s="181"/>
+      <c r="H82" s="182"/>
+      <c r="I82" s="181">
         <v>20</v>
       </c>
-      <c r="J82" s="142">
+      <c r="J82" s="181">
         <v>20</v>
       </c>
-      <c r="K82" s="142">
+      <c r="K82" s="181">
         <v>20</v>
       </c>
-      <c r="L82" s="124">
+      <c r="L82" s="182">
         <f t="shared" si="84"/>
         <v>1.5</v>
       </c>
@@ -8481,28 +8504,28 @@
       </c>
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A83" s="134">
+      <c r="A83" s="178">
         <v>46304</v>
       </c>
-      <c r="B83" s="135">
+      <c r="B83" s="179">
         <v>77</v>
       </c>
-      <c r="C83" s="144" t="s">
+      <c r="C83" s="180" t="s">
         <v>207</v>
       </c>
-      <c r="D83" s="144"/>
-      <c r="E83" s="142"/>
-      <c r="F83" s="142">
-        <v>40</v>
-      </c>
-      <c r="G83" s="142"/>
-      <c r="H83" s="143"/>
-      <c r="I83" s="142">
-        <v>40</v>
-      </c>
-      <c r="J83" s="142"/>
-      <c r="K83" s="142"/>
-      <c r="L83" s="124">
+      <c r="D83" s="180"/>
+      <c r="E83" s="181"/>
+      <c r="F83" s="181">
+        <v>40</v>
+      </c>
+      <c r="G83" s="181"/>
+      <c r="H83" s="182"/>
+      <c r="I83" s="181">
+        <v>40</v>
+      </c>
+      <c r="J83" s="181"/>
+      <c r="K83" s="181"/>
+      <c r="L83" s="182">
         <f t="shared" si="84"/>
         <v>2</v>
       </c>
@@ -8552,32 +8575,32 @@
       </c>
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A84" s="134">
+      <c r="A84" s="178">
         <v>46304</v>
       </c>
-      <c r="B84" s="135">
+      <c r="B84" s="179">
         <v>78</v>
       </c>
-      <c r="C84" s="144" t="s">
+      <c r="C84" s="180" t="s">
         <v>208</v>
       </c>
-      <c r="D84" s="144"/>
-      <c r="E84" s="142"/>
-      <c r="F84" s="142">
-        <v>40</v>
-      </c>
-      <c r="G84" s="142">
-        <v>40</v>
-      </c>
-      <c r="H84" s="143"/>
-      <c r="I84" s="142"/>
-      <c r="J84" s="142">
-        <v>40</v>
-      </c>
-      <c r="K84" s="142">
-        <v>40</v>
-      </c>
-      <c r="L84" s="124">
+      <c r="D84" s="180"/>
+      <c r="E84" s="181"/>
+      <c r="F84" s="181">
+        <v>40</v>
+      </c>
+      <c r="G84" s="181">
+        <v>40</v>
+      </c>
+      <c r="H84" s="182"/>
+      <c r="I84" s="181"/>
+      <c r="J84" s="181">
+        <v>40</v>
+      </c>
+      <c r="K84" s="181">
+        <v>40</v>
+      </c>
+      <c r="L84" s="182">
         <f t="shared" si="84"/>
         <v>4</v>
       </c>
@@ -8627,32 +8650,32 @@
       </c>
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A85" s="134">
+      <c r="A85" s="178">
         <v>46304</v>
       </c>
-      <c r="B85" s="135">
+      <c r="B85" s="179">
         <v>79</v>
       </c>
-      <c r="C85" s="144" t="s">
+      <c r="C85" s="180" t="s">
         <v>209</v>
       </c>
-      <c r="D85" s="144"/>
-      <c r="E85" s="142"/>
-      <c r="F85" s="142"/>
-      <c r="G85" s="142">
-        <v>40</v>
-      </c>
-      <c r="H85" s="143"/>
-      <c r="I85" s="142">
-        <v>40</v>
-      </c>
-      <c r="J85" s="142">
-        <v>40</v>
-      </c>
-      <c r="K85" s="142">
-        <v>40</v>
-      </c>
-      <c r="L85" s="124">
+      <c r="D85" s="180"/>
+      <c r="E85" s="181"/>
+      <c r="F85" s="181"/>
+      <c r="G85" s="181">
+        <v>40</v>
+      </c>
+      <c r="H85" s="182"/>
+      <c r="I85" s="181">
+        <v>40</v>
+      </c>
+      <c r="J85" s="181">
+        <v>40</v>
+      </c>
+      <c r="K85" s="181">
+        <v>40</v>
+      </c>
+      <c r="L85" s="182">
         <f t="shared" si="84"/>
         <v>4</v>
       </c>
@@ -8702,28 +8725,28 @@
       </c>
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A86" s="134">
+      <c r="A86" s="178">
         <v>46304</v>
       </c>
-      <c r="B86" s="135">
+      <c r="B86" s="179">
         <v>80</v>
       </c>
-      <c r="C86" s="144" t="s">
+      <c r="C86" s="180" t="s">
         <v>210</v>
       </c>
-      <c r="D86" s="144"/>
-      <c r="E86" s="142"/>
-      <c r="F86" s="142"/>
-      <c r="G86" s="142"/>
-      <c r="H86" s="143"/>
-      <c r="I86" s="142">
-        <v>40</v>
-      </c>
-      <c r="J86" s="142"/>
-      <c r="K86" s="142">
-        <v>40</v>
-      </c>
-      <c r="L86" s="124">
+      <c r="D86" s="180"/>
+      <c r="E86" s="181"/>
+      <c r="F86" s="181"/>
+      <c r="G86" s="181"/>
+      <c r="H86" s="182"/>
+      <c r="I86" s="181">
+        <v>40</v>
+      </c>
+      <c r="J86" s="181"/>
+      <c r="K86" s="181">
+        <v>40</v>
+      </c>
+      <c r="L86" s="182">
         <f t="shared" si="84"/>
         <v>2</v>
       </c>
@@ -8773,32 +8796,32 @@
       </c>
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A87" s="134">
+      <c r="A87" s="178">
         <v>46304</v>
       </c>
-      <c r="B87" s="135">
+      <c r="B87" s="179">
         <v>81</v>
       </c>
-      <c r="C87" s="144" t="s">
+      <c r="C87" s="180" t="s">
         <v>211</v>
       </c>
-      <c r="D87" s="144" t="s">
+      <c r="D87" s="180" t="s">
         <v>212</v>
       </c>
-      <c r="E87" s="142"/>
-      <c r="F87" s="142"/>
-      <c r="G87" s="142"/>
-      <c r="H87" s="143"/>
-      <c r="I87" s="142">
+      <c r="E87" s="181"/>
+      <c r="F87" s="181"/>
+      <c r="G87" s="181"/>
+      <c r="H87" s="182"/>
+      <c r="I87" s="181">
         <v>3000</v>
       </c>
-      <c r="J87" s="142">
+      <c r="J87" s="181">
         <v>2000</v>
       </c>
-      <c r="K87" s="142">
+      <c r="K87" s="181">
         <v>3000</v>
       </c>
-      <c r="L87" s="124">
+      <c r="L87" s="182">
         <f t="shared" si="84"/>
         <v>200</v>
       </c>
@@ -8848,32 +8871,44 @@
       </c>
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A88" s="71"/>
-      <c r="B88" s="40">
+      <c r="A88" s="134">
+        <v>46305</v>
+      </c>
+      <c r="B88" s="135">
         <v>82</v>
       </c>
-      <c r="C88" s="125"/>
-      <c r="D88" s="125"/>
-      <c r="E88" s="68"/>
-      <c r="F88" s="68"/>
-      <c r="G88" s="68"/>
-      <c r="H88" s="124"/>
-      <c r="I88" s="68"/>
-      <c r="J88" s="68"/>
-      <c r="K88" s="68"/>
+      <c r="C88" s="144" t="s">
+        <v>213</v>
+      </c>
+      <c r="D88" s="144" t="s">
+        <v>214</v>
+      </c>
+      <c r="E88" s="142"/>
+      <c r="F88" s="142"/>
+      <c r="G88" s="142">
+        <v>40</v>
+      </c>
+      <c r="H88" s="143"/>
+      <c r="I88" s="142"/>
+      <c r="J88" s="142">
+        <v>40</v>
+      </c>
+      <c r="K88" s="142"/>
       <c r="L88" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M88" s="138"/>
+        <v>2</v>
+      </c>
+      <c r="M88" s="138">
+        <v>10</v>
+      </c>
       <c r="N88" s="42"/>
       <c r="O88" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P88" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q88" s="44" t="e">
         <f t="shared" si="76"/>
@@ -8909,32 +8944,52 @@
       </c>
     </row>
     <row r="89" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A89" s="71"/>
-      <c r="B89" s="40">
+      <c r="A89" s="134">
+        <v>46305</v>
+      </c>
+      <c r="B89" s="135">
         <v>83</v>
       </c>
-      <c r="C89" s="125"/>
-      <c r="D89" s="125"/>
-      <c r="E89" s="68"/>
-      <c r="F89" s="68"/>
-      <c r="G89" s="68"/>
-      <c r="H89" s="124"/>
-      <c r="I89" s="68"/>
-      <c r="J89" s="68"/>
-      <c r="K89" s="68"/>
+      <c r="C89" s="144" t="s">
+        <v>215</v>
+      </c>
+      <c r="D89" s="144" t="s">
+        <v>216</v>
+      </c>
+      <c r="E89" s="142"/>
+      <c r="F89" s="142">
+        <v>400</v>
+      </c>
+      <c r="G89" s="142">
+        <v>400</v>
+      </c>
+      <c r="H89" s="143">
+        <v>400</v>
+      </c>
+      <c r="I89" s="142">
+        <v>400</v>
+      </c>
+      <c r="J89" s="142">
+        <v>400</v>
+      </c>
+      <c r="K89" s="142">
+        <v>400</v>
+      </c>
       <c r="L89" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M89" s="138"/>
+        <v>60</v>
+      </c>
+      <c r="M89" s="138">
+        <v>14</v>
+      </c>
       <c r="N89" s="42"/>
       <c r="O89" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P89" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Q89" s="44" t="e">
         <f t="shared" si="76"/>
@@ -8970,32 +9025,48 @@
       </c>
     </row>
     <row r="90" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A90" s="71"/>
-      <c r="B90" s="40">
+      <c r="A90" s="134">
+        <v>46305</v>
+      </c>
+      <c r="B90" s="135">
         <v>84</v>
       </c>
-      <c r="C90" s="125"/>
-      <c r="D90" s="125"/>
-      <c r="E90" s="68"/>
-      <c r="F90" s="68"/>
-      <c r="G90" s="68"/>
-      <c r="H90" s="124"/>
-      <c r="I90" s="68"/>
-      <c r="J90" s="68"/>
-      <c r="K90" s="68"/>
+      <c r="C90" s="144" t="s">
+        <v>127</v>
+      </c>
+      <c r="D90" s="144" t="s">
+        <v>128</v>
+      </c>
+      <c r="E90" s="142"/>
+      <c r="F90" s="142"/>
+      <c r="G90" s="142">
+        <v>38</v>
+      </c>
+      <c r="H90" s="143">
+        <v>40</v>
+      </c>
+      <c r="I90" s="142">
+        <v>40</v>
+      </c>
+      <c r="J90" s="142">
+        <v>40</v>
+      </c>
+      <c r="K90" s="142"/>
       <c r="L90" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M90" s="138"/>
+        <v>3.95</v>
+      </c>
+      <c r="M90" s="138">
+        <v>14</v>
+      </c>
       <c r="N90" s="42"/>
       <c r="O90" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P90" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q90" s="44" t="e">
         <f t="shared" si="76"/>
@@ -11721,10 +11792,10 @@
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A135" s="71"/>
-      <c r="B135" s="155" t="s">
+      <c r="B135" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="C135" s="155"/>
+      <c r="C135" s="168"/>
       <c r="D135" s="135"/>
       <c r="E135" s="140">
         <f t="shared" ref="E135:K135" si="103">SUM(E6:E63)</f>
@@ -11975,10 +12046,10 @@
       </c>
     </row>
     <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B139" s="167" t="s">
+      <c r="B139" s="156" t="s">
         <v>68</v>
       </c>
-      <c r="C139" s="168"/>
+      <c r="C139" s="157"/>
       <c r="D139" s="128"/>
       <c r="E139" s="76">
         <f>SUM(E137:E138)</f>
@@ -12062,10 +12133,10 @@
       </c>
     </row>
     <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B140" s="156" t="s">
+      <c r="B140" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="C140" s="157"/>
+      <c r="C140" s="146"/>
       <c r="D140" s="129"/>
       <c r="E140" s="77">
         <f>SUM(E135,E139)</f>
@@ -12101,7 +12172,7 @@
       </c>
       <c r="M140" s="56">
         <f>SUM(M5:M139)</f>
-        <v>1331</v>
+        <v>1369</v>
       </c>
       <c r="N140" s="54">
         <f t="shared" ref="N140:X140" si="111">SUM(N5:N139)</f>
@@ -12109,11 +12180,11 @@
       </c>
       <c r="O140" s="55">
         <f t="shared" si="111"/>
-        <v>693.7</v>
+        <v>759.6</v>
       </c>
       <c r="P140" s="57">
         <f t="shared" si="111"/>
-        <v>1579.1999999999998</v>
+        <v>1645.1999999999998</v>
       </c>
       <c r="Q140" s="58" t="e">
         <f t="shared" si="111"/>
@@ -12150,17 +12221,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B135:C135"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B135:C135"/>
   </mergeCells>
   <conditionalFormatting sqref="C48:D62">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12260,24 +12331,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="80">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="E5" s="72">
-        <v>420</v>
+        <v>486</v>
       </c>
       <c r="F5" s="72">
         <v>365</v>
       </c>
       <c r="G5" s="94">
         <f>SUM(D5:F5)</f>
-        <v>1018</v>
+        <v>1107</v>
       </c>
       <c r="H5" s="87">
         <v>10000</v>
       </c>
       <c r="I5" s="88">
         <f>G5-H5</f>
-        <v>-8982</v>
+        <v>-8893</v>
       </c>
       <c r="K5" s="132" t="s">
         <v>1</v>
@@ -12308,11 +12379,11 @@
       </c>
       <c r="D6" s="96">
         <f>D5*40</f>
-        <v>9320</v>
+        <v>10240</v>
       </c>
       <c r="E6" s="96">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>16800</v>
+        <v>19440</v>
       </c>
       <c r="F6" s="96">
         <f t="shared" si="1"/>
@@ -12320,7 +12391,7 @@
       </c>
       <c r="G6" s="97">
         <f>SUM(D6:F6)</f>
-        <v>40720</v>
+        <v>44280</v>
       </c>
       <c r="H6" s="89">
         <f>H5*40</f>
@@ -12328,7 +12399,7 @@
       </c>
       <c r="I6" s="90">
         <f>G6-H6</f>
-        <v>-359280</v>
+        <v>-355720</v>
       </c>
       <c r="K6" s="132" t="s">
         <v>2</v>
@@ -12477,11 +12548,11 @@
       </c>
       <c r="D9" s="98">
         <f>D8-D5</f>
-        <v>-233</v>
+        <v>-256</v>
       </c>
       <c r="E9" s="98">
         <f>E8-E5</f>
-        <v>-420</v>
+        <v>-486</v>
       </c>
       <c r="K9" s="132" t="s">
         <v>5</v>
@@ -12638,7 +12709,7 @@
       </c>
       <c r="G12" s="83">
         <f>D12+G5</f>
-        <v>5218</v>
+        <v>5307</v>
       </c>
       <c r="K12" s="132" t="s">
         <v>11</v>
@@ -12690,7 +12761,7 @@
       </c>
       <c r="G13" s="83">
         <f>G12*40</f>
-        <v>208720</v>
+        <v>212280</v>
       </c>
       <c r="S13" s="169" t="s">
         <v>83</v>

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080568C2-4405-4BC4-9B08-15CFB0E546FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DE149B-4E60-4CC0-9CBA-972513E26FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="220">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -673,6 +673,15 @@
   </si>
   <si>
     <t xml:space="preserve">Behria Town </t>
+  </si>
+  <si>
+    <t>Academy Road</t>
+  </si>
+  <si>
+    <t>Gourmet Shadman to Daroghewala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet K Block To military </t>
   </si>
 </sst>
 </file>
@@ -1540,7 +1549,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1918,6 +1927,39 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1957,39 +1999,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2016,17 +2025,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2620,13 +2618,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="158">
+      <c r="B1" s="145">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
-      </c>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
+        <v>46309</v>
+      </c>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2648,10 +2646,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="166" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="146" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2681,13 +2679,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="147"/>
-      <c r="M2" s="148"/>
-      <c r="N2" s="149"/>
-      <c r="O2" s="150" t="s">
+      <c r="L2" s="158"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="160"/>
+      <c r="O2" s="161" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="151"/>
+      <c r="P2" s="162"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2706,8 +2704,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="155"/>
-      <c r="B3" s="160"/>
+      <c r="A3" s="166"/>
+      <c r="B3" s="147"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2735,29 +2733,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="152" t="s">
+      <c r="L3" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="153"/>
-      <c r="N3" s="154"/>
+      <c r="M3" s="164"/>
+      <c r="N3" s="165"/>
       <c r="O3" s="64"/>
       <c r="P3" s="65"/>
-      <c r="Q3" s="162" t="s">
+      <c r="Q3" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="163"/>
-      <c r="S3" s="163"/>
-      <c r="T3" s="164"/>
-      <c r="U3" s="165" t="s">
+      <c r="R3" s="150"/>
+      <c r="S3" s="150"/>
+      <c r="T3" s="151"/>
+      <c r="U3" s="152" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="166"/>
-      <c r="W3" s="166"/>
-      <c r="X3" s="167"/>
+      <c r="V3" s="153"/>
+      <c r="W3" s="153"/>
+      <c r="X3" s="154"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="155"/>
-      <c r="B4" s="161"/>
+      <c r="A4" s="166"/>
+      <c r="B4" s="148"/>
       <c r="C4" s="130" t="s">
         <v>90</v>
       </c>
@@ -8062,36 +8060,36 @@
       </c>
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A77" s="178">
+      <c r="A77" s="71">
         <v>46304</v>
       </c>
-      <c r="B77" s="179">
+      <c r="B77" s="40">
         <v>71</v>
       </c>
-      <c r="C77" s="180" t="s">
+      <c r="C77" s="125" t="s">
         <v>23</v>
       </c>
-      <c r="D77" s="180" t="s">
+      <c r="D77" s="125" t="s">
         <v>112</v>
       </c>
-      <c r="E77" s="181"/>
-      <c r="F77" s="181">
+      <c r="E77" s="68"/>
+      <c r="F77" s="68">
         <v>120</v>
       </c>
-      <c r="G77" s="181"/>
-      <c r="H77" s="182">
+      <c r="G77" s="68"/>
+      <c r="H77" s="124">
         <v>80</v>
       </c>
-      <c r="I77" s="181">
+      <c r="I77" s="68">
         <v>160</v>
       </c>
-      <c r="J77" s="181">
+      <c r="J77" s="68">
         <v>120</v>
       </c>
-      <c r="K77" s="181">
+      <c r="K77" s="68">
         <v>400</v>
       </c>
-      <c r="L77" s="182">
+      <c r="L77" s="124">
         <f t="shared" si="84"/>
         <v>22</v>
       </c>
@@ -8141,30 +8139,30 @@
       </c>
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A78" s="178">
+      <c r="A78" s="71">
         <v>46304</v>
       </c>
-      <c r="B78" s="179">
+      <c r="B78" s="40">
         <v>72</v>
       </c>
-      <c r="C78" s="180" t="s">
+      <c r="C78" s="125" t="s">
         <v>129</v>
       </c>
-      <c r="D78" s="180"/>
-      <c r="E78" s="181"/>
-      <c r="F78" s="181"/>
-      <c r="G78" s="181">
-        <v>40</v>
-      </c>
-      <c r="H78" s="182"/>
-      <c r="I78" s="181"/>
-      <c r="J78" s="181">
-        <v>40</v>
-      </c>
-      <c r="K78" s="181">
-        <v>40</v>
-      </c>
-      <c r="L78" s="182">
+      <c r="D78" s="125"/>
+      <c r="E78" s="68"/>
+      <c r="F78" s="68"/>
+      <c r="G78" s="68">
+        <v>40</v>
+      </c>
+      <c r="H78" s="124"/>
+      <c r="I78" s="68"/>
+      <c r="J78" s="68">
+        <v>40</v>
+      </c>
+      <c r="K78" s="68">
+        <v>40</v>
+      </c>
+      <c r="L78" s="124">
         <f t="shared" si="84"/>
         <v>3</v>
       </c>
@@ -8214,28 +8212,28 @@
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A79" s="178">
+      <c r="A79" s="71">
         <v>46304</v>
       </c>
-      <c r="B79" s="179">
+      <c r="B79" s="40">
         <v>73</v>
       </c>
-      <c r="C79" s="180" t="s">
+      <c r="C79" s="125" t="s">
         <v>203</v>
       </c>
-      <c r="D79" s="180"/>
-      <c r="E79" s="181"/>
-      <c r="F79" s="181">
-        <v>40</v>
-      </c>
-      <c r="G79" s="181"/>
-      <c r="H79" s="182"/>
-      <c r="I79" s="181"/>
-      <c r="J79" s="181"/>
-      <c r="K79" s="181">
-        <v>40</v>
-      </c>
-      <c r="L79" s="182">
+      <c r="D79" s="125"/>
+      <c r="E79" s="68"/>
+      <c r="F79" s="68">
+        <v>40</v>
+      </c>
+      <c r="G79" s="68"/>
+      <c r="H79" s="124"/>
+      <c r="I79" s="68"/>
+      <c r="J79" s="68"/>
+      <c r="K79" s="68">
+        <v>40</v>
+      </c>
+      <c r="L79" s="124">
         <f t="shared" si="84"/>
         <v>2</v>
       </c>
@@ -8285,32 +8283,32 @@
       </c>
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A80" s="178">
+      <c r="A80" s="71">
         <v>46304</v>
       </c>
-      <c r="B80" s="179">
+      <c r="B80" s="40">
         <v>74</v>
       </c>
-      <c r="C80" s="180" t="s">
+      <c r="C80" s="125" t="s">
         <v>204</v>
       </c>
-      <c r="D80" s="180"/>
-      <c r="E80" s="181"/>
-      <c r="F80" s="181">
-        <v>40</v>
-      </c>
-      <c r="G80" s="181">
-        <v>40</v>
-      </c>
-      <c r="H80" s="182"/>
-      <c r="I80" s="181"/>
-      <c r="J80" s="181">
-        <v>40</v>
-      </c>
-      <c r="K80" s="181">
-        <v>40</v>
-      </c>
-      <c r="L80" s="182">
+      <c r="D80" s="125"/>
+      <c r="E80" s="68"/>
+      <c r="F80" s="68">
+        <v>40</v>
+      </c>
+      <c r="G80" s="68">
+        <v>40</v>
+      </c>
+      <c r="H80" s="124"/>
+      <c r="I80" s="68"/>
+      <c r="J80" s="68">
+        <v>40</v>
+      </c>
+      <c r="K80" s="68">
+        <v>40</v>
+      </c>
+      <c r="L80" s="124">
         <f t="shared" si="84"/>
         <v>4</v>
       </c>
@@ -8360,28 +8358,28 @@
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A81" s="178">
+      <c r="A81" s="71">
         <v>46304</v>
       </c>
-      <c r="B81" s="179">
+      <c r="B81" s="40">
         <v>75</v>
       </c>
-      <c r="C81" s="180" t="s">
+      <c r="C81" s="125" t="s">
         <v>205</v>
       </c>
-      <c r="D81" s="180"/>
-      <c r="E81" s="181"/>
-      <c r="F81" s="181"/>
-      <c r="G81" s="181"/>
-      <c r="H81" s="182"/>
-      <c r="I81" s="181">
-        <v>40</v>
-      </c>
-      <c r="J81" s="181"/>
-      <c r="K81" s="181">
-        <v>40</v>
-      </c>
-      <c r="L81" s="182">
+      <c r="D81" s="125"/>
+      <c r="E81" s="68"/>
+      <c r="F81" s="68"/>
+      <c r="G81" s="68"/>
+      <c r="H81" s="124"/>
+      <c r="I81" s="68">
+        <v>40</v>
+      </c>
+      <c r="J81" s="68"/>
+      <c r="K81" s="68">
+        <v>40</v>
+      </c>
+      <c r="L81" s="124">
         <f t="shared" si="84"/>
         <v>2</v>
       </c>
@@ -8431,30 +8429,30 @@
       </c>
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A82" s="178">
+      <c r="A82" s="71">
         <v>46304</v>
       </c>
-      <c r="B82" s="179">
+      <c r="B82" s="40">
         <v>76</v>
       </c>
-      <c r="C82" s="180" t="s">
+      <c r="C82" s="125" t="s">
         <v>206</v>
       </c>
-      <c r="D82" s="180"/>
-      <c r="E82" s="181"/>
-      <c r="F82" s="181"/>
-      <c r="G82" s="181"/>
-      <c r="H82" s="182"/>
-      <c r="I82" s="181">
+      <c r="D82" s="125"/>
+      <c r="E82" s="68"/>
+      <c r="F82" s="68"/>
+      <c r="G82" s="68"/>
+      <c r="H82" s="124"/>
+      <c r="I82" s="68">
         <v>20</v>
       </c>
-      <c r="J82" s="181">
+      <c r="J82" s="68">
         <v>20</v>
       </c>
-      <c r="K82" s="181">
+      <c r="K82" s="68">
         <v>20</v>
       </c>
-      <c r="L82" s="182">
+      <c r="L82" s="124">
         <f t="shared" si="84"/>
         <v>1.5</v>
       </c>
@@ -8504,28 +8502,28 @@
       </c>
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A83" s="178">
+      <c r="A83" s="71">
         <v>46304</v>
       </c>
-      <c r="B83" s="179">
+      <c r="B83" s="40">
         <v>77</v>
       </c>
-      <c r="C83" s="180" t="s">
+      <c r="C83" s="125" t="s">
         <v>207</v>
       </c>
-      <c r="D83" s="180"/>
-      <c r="E83" s="181"/>
-      <c r="F83" s="181">
-        <v>40</v>
-      </c>
-      <c r="G83" s="181"/>
-      <c r="H83" s="182"/>
-      <c r="I83" s="181">
-        <v>40</v>
-      </c>
-      <c r="J83" s="181"/>
-      <c r="K83" s="181"/>
-      <c r="L83" s="182">
+      <c r="D83" s="125"/>
+      <c r="E83" s="68"/>
+      <c r="F83" s="68">
+        <v>40</v>
+      </c>
+      <c r="G83" s="68"/>
+      <c r="H83" s="124"/>
+      <c r="I83" s="68">
+        <v>40</v>
+      </c>
+      <c r="J83" s="68"/>
+      <c r="K83" s="68"/>
+      <c r="L83" s="124">
         <f t="shared" si="84"/>
         <v>2</v>
       </c>
@@ -8575,32 +8573,32 @@
       </c>
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A84" s="178">
+      <c r="A84" s="71">
         <v>46304</v>
       </c>
-      <c r="B84" s="179">
+      <c r="B84" s="40">
         <v>78</v>
       </c>
-      <c r="C84" s="180" t="s">
+      <c r="C84" s="125" t="s">
         <v>208</v>
       </c>
-      <c r="D84" s="180"/>
-      <c r="E84" s="181"/>
-      <c r="F84" s="181">
-        <v>40</v>
-      </c>
-      <c r="G84" s="181">
-        <v>40</v>
-      </c>
-      <c r="H84" s="182"/>
-      <c r="I84" s="181"/>
-      <c r="J84" s="181">
-        <v>40</v>
-      </c>
-      <c r="K84" s="181">
-        <v>40</v>
-      </c>
-      <c r="L84" s="182">
+      <c r="D84" s="125"/>
+      <c r="E84" s="68"/>
+      <c r="F84" s="68">
+        <v>40</v>
+      </c>
+      <c r="G84" s="68">
+        <v>40</v>
+      </c>
+      <c r="H84" s="124"/>
+      <c r="I84" s="68"/>
+      <c r="J84" s="68">
+        <v>40</v>
+      </c>
+      <c r="K84" s="68">
+        <v>40</v>
+      </c>
+      <c r="L84" s="124">
         <f t="shared" si="84"/>
         <v>4</v>
       </c>
@@ -8650,32 +8648,32 @@
       </c>
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A85" s="178">
+      <c r="A85" s="71">
         <v>46304</v>
       </c>
-      <c r="B85" s="179">
+      <c r="B85" s="40">
         <v>79</v>
       </c>
-      <c r="C85" s="180" t="s">
+      <c r="C85" s="125" t="s">
         <v>209</v>
       </c>
-      <c r="D85" s="180"/>
-      <c r="E85" s="181"/>
-      <c r="F85" s="181"/>
-      <c r="G85" s="181">
-        <v>40</v>
-      </c>
-      <c r="H85" s="182"/>
-      <c r="I85" s="181">
-        <v>40</v>
-      </c>
-      <c r="J85" s="181">
-        <v>40</v>
-      </c>
-      <c r="K85" s="181">
-        <v>40</v>
-      </c>
-      <c r="L85" s="182">
+      <c r="D85" s="125"/>
+      <c r="E85" s="68"/>
+      <c r="F85" s="68"/>
+      <c r="G85" s="68">
+        <v>40</v>
+      </c>
+      <c r="H85" s="124"/>
+      <c r="I85" s="68">
+        <v>40</v>
+      </c>
+      <c r="J85" s="68">
+        <v>40</v>
+      </c>
+      <c r="K85" s="68">
+        <v>40</v>
+      </c>
+      <c r="L85" s="124">
         <f t="shared" si="84"/>
         <v>4</v>
       </c>
@@ -8725,28 +8723,28 @@
       </c>
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A86" s="178">
+      <c r="A86" s="71">
         <v>46304</v>
       </c>
-      <c r="B86" s="179">
+      <c r="B86" s="40">
         <v>80</v>
       </c>
-      <c r="C86" s="180" t="s">
+      <c r="C86" s="125" t="s">
         <v>210</v>
       </c>
-      <c r="D86" s="180"/>
-      <c r="E86" s="181"/>
-      <c r="F86" s="181"/>
-      <c r="G86" s="181"/>
-      <c r="H86" s="182"/>
-      <c r="I86" s="181">
-        <v>40</v>
-      </c>
-      <c r="J86" s="181"/>
-      <c r="K86" s="181">
-        <v>40</v>
-      </c>
-      <c r="L86" s="182">
+      <c r="D86" s="125"/>
+      <c r="E86" s="68"/>
+      <c r="F86" s="68"/>
+      <c r="G86" s="68"/>
+      <c r="H86" s="124"/>
+      <c r="I86" s="68">
+        <v>40</v>
+      </c>
+      <c r="J86" s="68"/>
+      <c r="K86" s="68">
+        <v>40</v>
+      </c>
+      <c r="L86" s="124">
         <f t="shared" si="84"/>
         <v>2</v>
       </c>
@@ -8796,32 +8794,32 @@
       </c>
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A87" s="178">
+      <c r="A87" s="71">
         <v>46304</v>
       </c>
-      <c r="B87" s="179">
+      <c r="B87" s="40">
         <v>81</v>
       </c>
-      <c r="C87" s="180" t="s">
+      <c r="C87" s="125" t="s">
         <v>211</v>
       </c>
-      <c r="D87" s="180" t="s">
+      <c r="D87" s="125" t="s">
         <v>212</v>
       </c>
-      <c r="E87" s="181"/>
-      <c r="F87" s="181"/>
-      <c r="G87" s="181"/>
-      <c r="H87" s="182"/>
-      <c r="I87" s="181">
+      <c r="E87" s="68"/>
+      <c r="F87" s="68"/>
+      <c r="G87" s="68"/>
+      <c r="H87" s="124"/>
+      <c r="I87" s="68">
         <v>3000</v>
       </c>
-      <c r="J87" s="181">
+      <c r="J87" s="68">
         <v>2000</v>
       </c>
-      <c r="K87" s="181">
+      <c r="K87" s="68">
         <v>3000</v>
       </c>
-      <c r="L87" s="182">
+      <c r="L87" s="124">
         <f t="shared" si="84"/>
         <v>200</v>
       </c>
@@ -8871,29 +8869,29 @@
       </c>
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A88" s="134">
+      <c r="A88" s="71">
         <v>46305</v>
       </c>
-      <c r="B88" s="135">
+      <c r="B88" s="40">
         <v>82</v>
       </c>
-      <c r="C88" s="144" t="s">
+      <c r="C88" s="125" t="s">
         <v>213</v>
       </c>
-      <c r="D88" s="144" t="s">
+      <c r="D88" s="125" t="s">
         <v>214</v>
       </c>
-      <c r="E88" s="142"/>
-      <c r="F88" s="142"/>
-      <c r="G88" s="142">
-        <v>40</v>
-      </c>
-      <c r="H88" s="143"/>
-      <c r="I88" s="142"/>
-      <c r="J88" s="142">
-        <v>40</v>
-      </c>
-      <c r="K88" s="142"/>
+      <c r="E88" s="68"/>
+      <c r="F88" s="68"/>
+      <c r="G88" s="68">
+        <v>40</v>
+      </c>
+      <c r="H88" s="124"/>
+      <c r="I88" s="68"/>
+      <c r="J88" s="68">
+        <v>40</v>
+      </c>
+      <c r="K88" s="68"/>
       <c r="L88" s="124">
         <f t="shared" si="84"/>
         <v>2</v>
@@ -8944,35 +8942,35 @@
       </c>
     </row>
     <row r="89" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A89" s="134">
+      <c r="A89" s="71">
         <v>46305</v>
       </c>
-      <c r="B89" s="135">
+      <c r="B89" s="40">
         <v>83</v>
       </c>
-      <c r="C89" s="144" t="s">
+      <c r="C89" s="125" t="s">
         <v>215</v>
       </c>
-      <c r="D89" s="144" t="s">
+      <c r="D89" s="125" t="s">
         <v>216</v>
       </c>
-      <c r="E89" s="142"/>
-      <c r="F89" s="142">
+      <c r="E89" s="68"/>
+      <c r="F89" s="68">
         <v>400</v>
       </c>
-      <c r="G89" s="142">
+      <c r="G89" s="68">
         <v>400</v>
       </c>
-      <c r="H89" s="143">
+      <c r="H89" s="124">
         <v>400</v>
       </c>
-      <c r="I89" s="142">
+      <c r="I89" s="68">
         <v>400</v>
       </c>
-      <c r="J89" s="142">
+      <c r="J89" s="68">
         <v>400</v>
       </c>
-      <c r="K89" s="142">
+      <c r="K89" s="68">
         <v>400</v>
       </c>
       <c r="L89" s="124">
@@ -9025,33 +9023,33 @@
       </c>
     </row>
     <row r="90" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A90" s="134">
+      <c r="A90" s="71">
         <v>46305</v>
       </c>
-      <c r="B90" s="135">
+      <c r="B90" s="40">
         <v>84</v>
       </c>
-      <c r="C90" s="144" t="s">
+      <c r="C90" s="125" t="s">
         <v>127</v>
       </c>
-      <c r="D90" s="144" t="s">
+      <c r="D90" s="125" t="s">
         <v>128</v>
       </c>
-      <c r="E90" s="142"/>
-      <c r="F90" s="142"/>
-      <c r="G90" s="142">
+      <c r="E90" s="68"/>
+      <c r="F90" s="68"/>
+      <c r="G90" s="68">
         <v>38</v>
       </c>
-      <c r="H90" s="143">
-        <v>40</v>
-      </c>
-      <c r="I90" s="142">
-        <v>40</v>
-      </c>
-      <c r="J90" s="142">
-        <v>40</v>
-      </c>
-      <c r="K90" s="142"/>
+      <c r="H90" s="124">
+        <v>40</v>
+      </c>
+      <c r="I90" s="68">
+        <v>40</v>
+      </c>
+      <c r="J90" s="68">
+        <v>40</v>
+      </c>
+      <c r="K90" s="68"/>
       <c r="L90" s="124">
         <f t="shared" si="84"/>
         <v>3.95</v>
@@ -9102,32 +9100,52 @@
       </c>
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A91" s="71"/>
-      <c r="B91" s="40">
+      <c r="A91" s="134">
+        <v>46306</v>
+      </c>
+      <c r="B91" s="135">
         <v>85</v>
       </c>
-      <c r="C91" s="125"/>
-      <c r="D91" s="125"/>
-      <c r="E91" s="68"/>
-      <c r="F91" s="68"/>
-      <c r="G91" s="68"/>
-      <c r="H91" s="124"/>
-      <c r="I91" s="68"/>
-      <c r="J91" s="68"/>
-      <c r="K91" s="68"/>
+      <c r="C91" s="144" t="s">
+        <v>215</v>
+      </c>
+      <c r="D91" s="144" t="s">
+        <v>217</v>
+      </c>
+      <c r="E91" s="142"/>
+      <c r="F91" s="142">
+        <v>40</v>
+      </c>
+      <c r="G91" s="142">
+        <v>40</v>
+      </c>
+      <c r="H91" s="143">
+        <v>40</v>
+      </c>
+      <c r="I91" s="142">
+        <v>40</v>
+      </c>
+      <c r="J91" s="142">
+        <v>40</v>
+      </c>
+      <c r="K91" s="142">
+        <v>40</v>
+      </c>
       <c r="L91" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M91" s="138"/>
+        <v>6</v>
+      </c>
+      <c r="M91" s="138">
+        <v>14</v>
+      </c>
       <c r="N91" s="42"/>
       <c r="O91" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P91" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q91" s="44" t="e">
         <f t="shared" si="76"/>
@@ -9163,32 +9181,50 @@
       </c>
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A92" s="71"/>
-      <c r="B92" s="40">
+      <c r="A92" s="134">
+        <v>46306</v>
+      </c>
+      <c r="B92" s="135">
         <v>86</v>
       </c>
-      <c r="C92" s="125"/>
-      <c r="D92" s="125"/>
-      <c r="E92" s="68"/>
-      <c r="F92" s="68"/>
-      <c r="G92" s="68"/>
-      <c r="H92" s="124"/>
-      <c r="I92" s="68"/>
-      <c r="J92" s="68"/>
-      <c r="K92" s="68"/>
+      <c r="C92" s="144" t="s">
+        <v>218</v>
+      </c>
+      <c r="D92" s="144"/>
+      <c r="E92" s="142"/>
+      <c r="F92" s="142">
+        <v>200</v>
+      </c>
+      <c r="G92" s="142">
+        <v>280</v>
+      </c>
+      <c r="H92" s="143">
+        <v>320</v>
+      </c>
+      <c r="I92" s="142">
+        <v>360</v>
+      </c>
+      <c r="J92" s="142">
+        <v>320</v>
+      </c>
+      <c r="K92" s="142">
+        <v>440</v>
+      </c>
       <c r="L92" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M92" s="139"/>
+        <v>48</v>
+      </c>
+      <c r="M92" s="139">
+        <v>18</v>
+      </c>
       <c r="N92" s="42"/>
       <c r="O92" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P92" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="Q92" s="44" t="e">
         <f t="shared" si="76"/>
@@ -9224,32 +9260,50 @@
       </c>
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
-      <c r="B93" s="40">
+      <c r="A93" s="134">
+        <v>46306</v>
+      </c>
+      <c r="B93" s="135">
         <v>87</v>
       </c>
-      <c r="C93" s="125"/>
-      <c r="D93" s="125"/>
-      <c r="E93" s="68"/>
-      <c r="F93" s="68"/>
-      <c r="G93" s="68"/>
-      <c r="H93" s="124"/>
-      <c r="I93" s="68"/>
-      <c r="J93" s="68"/>
-      <c r="K93" s="68"/>
+      <c r="C93" s="144" t="s">
+        <v>219</v>
+      </c>
+      <c r="D93" s="144"/>
+      <c r="E93" s="142"/>
+      <c r="F93" s="142">
+        <v>200</v>
+      </c>
+      <c r="G93" s="142">
+        <v>120</v>
+      </c>
+      <c r="H93" s="143">
+        <v>120</v>
+      </c>
+      <c r="I93" s="142">
+        <v>280</v>
+      </c>
+      <c r="J93" s="142">
+        <v>360</v>
+      </c>
+      <c r="K93" s="142">
+        <v>440</v>
+      </c>
       <c r="L93" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M93" s="139"/>
+        <v>38</v>
+      </c>
+      <c r="M93" s="139">
+        <v>18</v>
+      </c>
       <c r="N93" s="42"/>
       <c r="O93" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P93" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="Q93" s="44" t="e">
         <f t="shared" si="76"/>
@@ -9285,28 +9339,38 @@
       </c>
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
-      <c r="B94" s="40">
+      <c r="A94" s="134">
+        <v>46306</v>
+      </c>
+      <c r="B94" s="135">
         <v>88</v>
       </c>
-      <c r="C94" s="125"/>
-      <c r="D94" s="125"/>
-      <c r="E94" s="68"/>
-      <c r="F94" s="68"/>
-      <c r="G94" s="68"/>
-      <c r="H94" s="124"/>
-      <c r="I94" s="68"/>
-      <c r="J94" s="68"/>
-      <c r="K94" s="68"/>
+      <c r="C94" s="144" t="s">
+        <v>211</v>
+      </c>
+      <c r="D94" s="144" t="s">
+        <v>212</v>
+      </c>
+      <c r="E94" s="142"/>
+      <c r="F94" s="142">
+        <v>600</v>
+      </c>
+      <c r="G94" s="142"/>
+      <c r="H94" s="143"/>
+      <c r="I94" s="142"/>
+      <c r="J94" s="142"/>
+      <c r="K94" s="142"/>
       <c r="L94" s="124">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M94" s="139"/>
+        <v>15</v>
+      </c>
+      <c r="M94" s="139">
+        <v>16</v>
+      </c>
       <c r="N94" s="42"/>
       <c r="O94" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P94" s="33">
         <f t="shared" si="92"/>
@@ -9346,19 +9410,21 @@
       </c>
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
-      <c r="B95" s="40">
+      <c r="A95" s="134">
+        <v>46306</v>
+      </c>
+      <c r="B95" s="135">
         <v>89</v>
       </c>
-      <c r="C95" s="125"/>
-      <c r="D95" s="125"/>
-      <c r="E95" s="68"/>
-      <c r="F95" s="68"/>
-      <c r="G95" s="68"/>
-      <c r="H95" s="124"/>
-      <c r="I95" s="68"/>
-      <c r="J95" s="68"/>
-      <c r="K95" s="68"/>
+      <c r="C95" s="144"/>
+      <c r="D95" s="144"/>
+      <c r="E95" s="142"/>
+      <c r="F95" s="142"/>
+      <c r="G95" s="142"/>
+      <c r="H95" s="143"/>
+      <c r="I95" s="142"/>
+      <c r="J95" s="142"/>
+      <c r="K95" s="142"/>
       <c r="L95" s="124">
         <f t="shared" si="84"/>
         <v>0</v>
@@ -11792,10 +11858,10 @@
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A135" s="71"/>
-      <c r="B135" s="168" t="s">
+      <c r="B135" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="C135" s="168"/>
+      <c r="C135" s="155"/>
       <c r="D135" s="135"/>
       <c r="E135" s="140">
         <f t="shared" ref="E135:K135" si="103">SUM(E6:E63)</f>
@@ -12046,10 +12112,10 @@
       </c>
     </row>
     <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B139" s="156" t="s">
+      <c r="B139" s="167" t="s">
         <v>68</v>
       </c>
-      <c r="C139" s="157"/>
+      <c r="C139" s="168"/>
       <c r="D139" s="128"/>
       <c r="E139" s="76">
         <f>SUM(E137:E138)</f>
@@ -12133,10 +12199,10 @@
       </c>
     </row>
     <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B140" s="145" t="s">
+      <c r="B140" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="C140" s="146"/>
+      <c r="C140" s="157"/>
       <c r="D140" s="129"/>
       <c r="E140" s="77">
         <f>SUM(E135,E139)</f>
@@ -12172,7 +12238,7 @@
       </c>
       <c r="M140" s="56">
         <f>SUM(M5:M139)</f>
-        <v>1369</v>
+        <v>1435</v>
       </c>
       <c r="N140" s="54">
         <f t="shared" ref="N140:X140" si="111">SUM(N5:N139)</f>
@@ -12180,11 +12246,11 @@
       </c>
       <c r="O140" s="55">
         <f t="shared" si="111"/>
-        <v>759.6</v>
+        <v>857.6</v>
       </c>
       <c r="P140" s="57">
         <f t="shared" si="111"/>
-        <v>1645.1999999999998</v>
+        <v>1761.1999999999998</v>
       </c>
       <c r="Q140" s="58" t="e">
         <f t="shared" si="111"/>
@@ -12221,17 +12287,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B135:C135"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B135:C135"/>
   </mergeCells>
   <conditionalFormatting sqref="C48:D62">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12331,24 +12397,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="80">
-        <v>256</v>
+        <v>301</v>
       </c>
       <c r="E5" s="72">
-        <v>486</v>
+        <v>578</v>
       </c>
       <c r="F5" s="72">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="G5" s="94">
         <f>SUM(D5:F5)</f>
-        <v>1107</v>
+        <v>1259</v>
       </c>
       <c r="H5" s="87">
         <v>10000</v>
       </c>
       <c r="I5" s="88">
         <f>G5-H5</f>
-        <v>-8893</v>
+        <v>-8741</v>
       </c>
       <c r="K5" s="132" t="s">
         <v>1</v>
@@ -12357,11 +12423,11 @@
         <v>70</v>
       </c>
       <c r="M5" s="5">
-        <v>12766</v>
+        <v>9122</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>319.14999999999998</v>
+        <v>228.05</v>
       </c>
       <c r="O5" s="74"/>
       <c r="P5" s="133"/>
@@ -12370,7 +12436,7 @@
       </c>
       <c r="R5" s="141">
         <f>N5-Q5</f>
-        <v>51.94</v>
+        <v>-39.159999999999968</v>
       </c>
     </row>
     <row r="6" spans="3:26" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
@@ -12379,19 +12445,19 @@
       </c>
       <c r="D6" s="96">
         <f>D5*40</f>
-        <v>10240</v>
+        <v>12040</v>
       </c>
       <c r="E6" s="96">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>19440</v>
+        <v>23120</v>
       </c>
       <c r="F6" s="96">
         <f t="shared" si="1"/>
-        <v>14600</v>
+        <v>15200</v>
       </c>
       <c r="G6" s="97">
         <f>SUM(D6:F6)</f>
-        <v>44280</v>
+        <v>50360</v>
       </c>
       <c r="H6" s="89">
         <f>H5*40</f>
@@ -12399,7 +12465,7 @@
       </c>
       <c r="I6" s="90">
         <f>G6-H6</f>
-        <v>-355720</v>
+        <v>-349640</v>
       </c>
       <c r="K6" s="132" t="s">
         <v>2</v>
@@ -12408,11 +12474,11 @@
         <v>70</v>
       </c>
       <c r="M6" s="5">
-        <v>13501</v>
+        <v>10173</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>337.52499999999998</v>
+        <v>254.32499999999999</v>
       </c>
       <c r="O6" s="74"/>
       <c r="P6" s="133"/>
@@ -12421,7 +12487,7 @@
       </c>
       <c r="R6" s="141">
         <f t="shared" ref="R6:R10" si="2">N6-Q6</f>
-        <v>163.25499999999997</v>
+        <v>80.054999999999978</v>
       </c>
       <c r="S6" s="116"/>
       <c r="T6" s="116"/>
@@ -12450,11 +12516,11 @@
         <v>70</v>
       </c>
       <c r="M7" s="5">
-        <v>12038</v>
+        <v>7936</v>
       </c>
       <c r="N7" s="6">
         <f t="shared" si="0"/>
-        <v>300.95</v>
+        <v>198.4</v>
       </c>
       <c r="O7" s="74"/>
       <c r="P7" s="133"/>
@@ -12463,7 +12529,7 @@
       </c>
       <c r="R7" s="141">
         <f t="shared" si="2"/>
-        <v>224.70999999999998</v>
+        <v>122.16000000000001</v>
       </c>
       <c r="S7" s="121" t="s">
         <v>85</v>
@@ -12501,11 +12567,11 @@
         <v>120</v>
       </c>
       <c r="M8" s="5">
-        <v>9642</v>
+        <v>417</v>
       </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>241.05</v>
+        <v>10.425000000000001</v>
       </c>
       <c r="O8" s="74">
         <v>50</v>
@@ -12516,7 +12582,7 @@
       </c>
       <c r="R8" s="141">
         <f t="shared" si="2"/>
-        <v>156.75</v>
+        <v>-73.875</v>
       </c>
       <c r="S8" s="72">
         <v>120</v>
@@ -12548,11 +12614,11 @@
       </c>
       <c r="D9" s="98">
         <f>D8-D5</f>
-        <v>-256</v>
+        <v>-301</v>
       </c>
       <c r="E9" s="98">
         <f>E8-E5</f>
-        <v>-486</v>
+        <v>-578</v>
       </c>
       <c r="K9" s="132" t="s">
         <v>5</v>
@@ -12561,11 +12627,11 @@
         <v>120</v>
       </c>
       <c r="M9" s="5">
-        <v>10707</v>
+        <v>2454</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>267.67500000000001</v>
+        <v>61.35</v>
       </c>
       <c r="O9" s="74">
         <v>23</v>
@@ -12576,7 +12642,7 @@
       </c>
       <c r="R9" s="141">
         <f t="shared" si="2"/>
-        <v>158.505</v>
+        <v>-47.82</v>
       </c>
       <c r="S9" s="72">
         <v>120</v>
@@ -12612,11 +12678,11 @@
         <v>120</v>
       </c>
       <c r="M10" s="5">
-        <v>10700</v>
+        <v>68</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>267.5</v>
+        <v>1.7</v>
       </c>
       <c r="O10" s="74"/>
       <c r="P10" s="133"/>
@@ -12625,7 +12691,7 @@
       </c>
       <c r="R10" s="141">
         <f t="shared" si="2"/>
-        <v>69.150000000000006</v>
+        <v>-196.65</v>
       </c>
       <c r="S10" s="72">
         <v>120</v>
@@ -12709,7 +12775,7 @@
       </c>
       <c r="G12" s="83">
         <f>D12+G5</f>
-        <v>5307</v>
+        <v>5459</v>
       </c>
       <c r="K12" s="132" t="s">
         <v>11</v>
@@ -12717,11 +12783,11 @@
       <c r="L12" s="74"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>69362</v>
+        <v>30178</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>1734.05</v>
+        <v>754.45</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
@@ -12761,7 +12827,7 @@
       </c>
       <c r="G13" s="83">
         <f>G12*40</f>
-        <v>212280</v>
+        <v>218360</v>
       </c>
       <c r="S13" s="169" t="s">
         <v>83</v>
@@ -12820,7 +12886,7 @@
       <c r="N17" s="113"/>
       <c r="O17" s="114">
         <f>N17-M5</f>
-        <v>-12766</v>
+        <v>-9122</v>
       </c>
       <c r="R17">
         <v>51.94</v>
@@ -12840,7 +12906,7 @@
       <c r="N18" s="5"/>
       <c r="O18" s="114">
         <f>N18-M6</f>
-        <v>-13501</v>
+        <v>-10173</v>
       </c>
       <c r="R18">
         <v>163.25499999999997</v>
@@ -12863,7 +12929,7 @@
       <c r="N19" s="5"/>
       <c r="O19" s="114">
         <f t="shared" ref="O19:O23" si="5">N19-M7</f>
-        <v>-12038</v>
+        <v>-7936</v>
       </c>
       <c r="R19">
         <v>224.70999999999998</v>
@@ -12890,7 +12956,7 @@
       <c r="N20" s="5"/>
       <c r="O20" s="114">
         <f t="shared" si="5"/>
-        <v>-9642</v>
+        <v>-417</v>
       </c>
       <c r="R20">
         <v>156.75</v>
@@ -12925,7 +12991,7 @@
       <c r="N21" s="5"/>
       <c r="O21" s="114">
         <f t="shared" si="5"/>
-        <v>-10707</v>
+        <v>-2454</v>
       </c>
       <c r="R21">
         <v>158.505</v>
@@ -12957,7 +13023,7 @@
       <c r="N22" s="5"/>
       <c r="O22" s="114">
         <f t="shared" si="5"/>
-        <v>-10700</v>
+        <v>-68</v>
       </c>
       <c r="R22">
         <v>69.150000000000006</v>
@@ -13019,7 +13085,7 @@
       </c>
       <c r="O24" s="109">
         <f>SUM(O17:O23)</f>
-        <v>-69362</v>
+        <v>-30178</v>
       </c>
     </row>
     <row r="25" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -13049,7 +13115,7 @@
       </c>
       <c r="O25" s="109">
         <f>O24/40</f>
-        <v>-1734.05</v>
+        <v>-754.45</v>
       </c>
     </row>
     <row r="26" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DE149B-4E60-4CC0-9CBA-972513E26FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEF6F8F-7011-439A-ACD7-694EBCEE104D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="231">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -682,6 +682,39 @@
   </si>
   <si>
     <t xml:space="preserve">Gourmet K Block To military </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lutaf Mega Mart </t>
+  </si>
+  <si>
+    <t>Ranger Head Quarter</t>
+  </si>
+  <si>
+    <t>Risen  Fatehgher</t>
+  </si>
+  <si>
+    <t>Fatrhgher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zubaida Traders </t>
+  </si>
+  <si>
+    <t>Attari darbar</t>
+  </si>
+  <si>
+    <t>Euro GT Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euro Rangers </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euro Fateh Gher </t>
+  </si>
+  <si>
+    <t>Fateh Gher</t>
+  </si>
+  <si>
+    <t>Gourmet College Road</t>
   </si>
 </sst>
 </file>
@@ -1549,7 +1582,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1927,6 +1960,45 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1960,45 +2032,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2025,6 +2058,28 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2618,13 +2673,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="145">
+      <c r="B1" s="158">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
-      </c>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
+        <v>46312</v>
+      </c>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2646,10 +2701,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="166" t="s">
+      <c r="A2" s="155" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="146" t="s">
+      <c r="B2" s="159" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2679,13 +2734,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="158"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="160"/>
-      <c r="O2" s="161" t="s">
+      <c r="L2" s="147"/>
+      <c r="M2" s="148"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="150" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="162"/>
+      <c r="P2" s="151"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2704,8 +2759,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="166"/>
-      <c r="B3" s="147"/>
+      <c r="A3" s="155"/>
+      <c r="B3" s="160"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2733,29 +2788,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="163" t="s">
+      <c r="L3" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="164"/>
-      <c r="N3" s="165"/>
+      <c r="M3" s="153"/>
+      <c r="N3" s="154"/>
       <c r="O3" s="64"/>
       <c r="P3" s="65"/>
-      <c r="Q3" s="149" t="s">
+      <c r="Q3" s="162" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="150"/>
-      <c r="S3" s="150"/>
-      <c r="T3" s="151"/>
-      <c r="U3" s="152" t="s">
+      <c r="R3" s="163"/>
+      <c r="S3" s="163"/>
+      <c r="T3" s="164"/>
+      <c r="U3" s="165" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="153"/>
-      <c r="W3" s="153"/>
-      <c r="X3" s="154"/>
+      <c r="V3" s="166"/>
+      <c r="W3" s="166"/>
+      <c r="X3" s="167"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="166"/>
-      <c r="B4" s="148"/>
+      <c r="A4" s="155"/>
+      <c r="B4" s="161"/>
       <c r="C4" s="130" t="s">
         <v>90</v>
       </c>
@@ -9100,35 +9155,35 @@
       </c>
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A91" s="134">
+      <c r="A91" s="178">
         <v>46306</v>
       </c>
-      <c r="B91" s="135">
+      <c r="B91" s="179">
         <v>85</v>
       </c>
-      <c r="C91" s="144" t="s">
+      <c r="C91" s="180" t="s">
         <v>215</v>
       </c>
-      <c r="D91" s="144" t="s">
+      <c r="D91" s="180" t="s">
         <v>217</v>
       </c>
-      <c r="E91" s="142"/>
-      <c r="F91" s="142">
-        <v>40</v>
-      </c>
-      <c r="G91" s="142">
-        <v>40</v>
-      </c>
-      <c r="H91" s="143">
-        <v>40</v>
-      </c>
-      <c r="I91" s="142">
-        <v>40</v>
-      </c>
-      <c r="J91" s="142">
-        <v>40</v>
-      </c>
-      <c r="K91" s="142">
+      <c r="E91" s="181"/>
+      <c r="F91" s="181">
+        <v>40</v>
+      </c>
+      <c r="G91" s="181">
+        <v>40</v>
+      </c>
+      <c r="H91" s="182">
+        <v>40</v>
+      </c>
+      <c r="I91" s="181">
+        <v>40</v>
+      </c>
+      <c r="J91" s="181">
+        <v>40</v>
+      </c>
+      <c r="K91" s="181">
         <v>40</v>
       </c>
       <c r="L91" s="124">
@@ -9181,33 +9236,33 @@
       </c>
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A92" s="134">
+      <c r="A92" s="178">
         <v>46306</v>
       </c>
-      <c r="B92" s="135">
+      <c r="B92" s="179">
         <v>86</v>
       </c>
-      <c r="C92" s="144" t="s">
+      <c r="C92" s="180" t="s">
         <v>218</v>
       </c>
-      <c r="D92" s="144"/>
-      <c r="E92" s="142"/>
-      <c r="F92" s="142">
+      <c r="D92" s="180"/>
+      <c r="E92" s="181"/>
+      <c r="F92" s="181">
         <v>200</v>
       </c>
-      <c r="G92" s="142">
+      <c r="G92" s="181">
         <v>280</v>
       </c>
-      <c r="H92" s="143">
+      <c r="H92" s="182">
         <v>320</v>
       </c>
-      <c r="I92" s="142">
+      <c r="I92" s="181">
         <v>360</v>
       </c>
-      <c r="J92" s="142">
+      <c r="J92" s="181">
         <v>320</v>
       </c>
-      <c r="K92" s="142">
+      <c r="K92" s="181">
         <v>440</v>
       </c>
       <c r="L92" s="124">
@@ -9260,33 +9315,33 @@
       </c>
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A93" s="134">
+      <c r="A93" s="178">
         <v>46306</v>
       </c>
-      <c r="B93" s="135">
+      <c r="B93" s="179">
         <v>87</v>
       </c>
-      <c r="C93" s="144" t="s">
+      <c r="C93" s="180" t="s">
         <v>219</v>
       </c>
-      <c r="D93" s="144"/>
-      <c r="E93" s="142"/>
-      <c r="F93" s="142">
+      <c r="D93" s="180"/>
+      <c r="E93" s="181"/>
+      <c r="F93" s="181">
         <v>200</v>
       </c>
-      <c r="G93" s="142">
+      <c r="G93" s="181">
         <v>120</v>
       </c>
-      <c r="H93" s="143">
+      <c r="H93" s="182">
         <v>120</v>
       </c>
-      <c r="I93" s="142">
+      <c r="I93" s="181">
         <v>280</v>
       </c>
-      <c r="J93" s="142">
+      <c r="J93" s="181">
         <v>360</v>
       </c>
-      <c r="K93" s="142">
+      <c r="K93" s="181">
         <v>440</v>
       </c>
       <c r="L93" s="124">
@@ -9339,27 +9394,27 @@
       </c>
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A94" s="134">
+      <c r="A94" s="178">
         <v>46306</v>
       </c>
-      <c r="B94" s="135">
+      <c r="B94" s="179">
         <v>88</v>
       </c>
-      <c r="C94" s="144" t="s">
+      <c r="C94" s="180" t="s">
         <v>211</v>
       </c>
-      <c r="D94" s="144" t="s">
+      <c r="D94" s="180" t="s">
         <v>212</v>
       </c>
-      <c r="E94" s="142"/>
-      <c r="F94" s="142">
+      <c r="E94" s="181"/>
+      <c r="F94" s="181">
         <v>600</v>
       </c>
-      <c r="G94" s="142"/>
-      <c r="H94" s="143"/>
-      <c r="I94" s="142"/>
-      <c r="J94" s="142"/>
-      <c r="K94" s="142"/>
+      <c r="G94" s="181"/>
+      <c r="H94" s="182"/>
+      <c r="I94" s="181"/>
+      <c r="J94" s="181"/>
+      <c r="K94" s="181"/>
       <c r="L94" s="124">
         <f t="shared" si="84"/>
         <v>15</v>
@@ -9410,34 +9465,48 @@
       </c>
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A95" s="134">
-        <v>46306</v>
-      </c>
-      <c r="B95" s="135">
+      <c r="A95" s="183">
+        <v>46310</v>
+      </c>
+      <c r="B95" s="184">
         <v>89</v>
       </c>
-      <c r="C95" s="144"/>
-      <c r="D95" s="144"/>
-      <c r="E95" s="142"/>
-      <c r="F95" s="142"/>
-      <c r="G95" s="142"/>
-      <c r="H95" s="143"/>
-      <c r="I95" s="142"/>
-      <c r="J95" s="142"/>
-      <c r="K95" s="142"/>
-      <c r="L95" s="124">
+      <c r="C95" s="185" t="s">
+        <v>220</v>
+      </c>
+      <c r="D95" s="185" t="s">
+        <v>221</v>
+      </c>
+      <c r="E95" s="186"/>
+      <c r="F95" s="186">
+        <v>-2</v>
+      </c>
+      <c r="G95" s="186">
+        <v>-2</v>
+      </c>
+      <c r="H95" s="187"/>
+      <c r="I95" s="186">
+        <v>200</v>
+      </c>
+      <c r="J95" s="186">
+        <v>200</v>
+      </c>
+      <c r="K95" s="186"/>
+      <c r="L95" s="187">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M95" s="139"/>
+        <v>9.9</v>
+      </c>
+      <c r="M95" s="139">
+        <v>10</v>
+      </c>
       <c r="N95" s="42"/>
       <c r="O95" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="P95" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q95" s="44" t="e">
         <f t="shared" ref="Q95:Q126" si="97">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
@@ -9473,24 +9542,34 @@
       </c>
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
-      <c r="B96" s="40">
+      <c r="A96" s="183">
+        <v>46310</v>
+      </c>
+      <c r="B96" s="184">
         <v>90</v>
       </c>
-      <c r="C96" s="125"/>
-      <c r="D96" s="125"/>
-      <c r="E96" s="68"/>
-      <c r="F96" s="68"/>
-      <c r="G96" s="68"/>
-      <c r="H96" s="124"/>
-      <c r="I96" s="68"/>
-      <c r="J96" s="68"/>
-      <c r="K96" s="68"/>
-      <c r="L96" s="124">
+      <c r="C96" s="185" t="s">
+        <v>222</v>
+      </c>
+      <c r="D96" s="185" t="s">
+        <v>223</v>
+      </c>
+      <c r="E96" s="186"/>
+      <c r="F96" s="186"/>
+      <c r="G96" s="186"/>
+      <c r="H96" s="187"/>
+      <c r="I96" s="186"/>
+      <c r="J96" s="186">
+        <v>158</v>
+      </c>
+      <c r="K96" s="186"/>
+      <c r="L96" s="187">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M96" s="138"/>
+        <v>3.95</v>
+      </c>
+      <c r="M96" s="138">
+        <v>14</v>
+      </c>
       <c r="N96" s="42"/>
       <c r="O96" s="66">
         <f t="shared" si="91"/>
@@ -9498,7 +9577,7 @@
       </c>
       <c r="P96" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q96" s="44" t="e">
         <f t="shared" si="97"/>
@@ -9534,32 +9613,52 @@
       </c>
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A97" s="71"/>
-      <c r="B97" s="40">
+      <c r="A97" s="183">
+        <v>46310</v>
+      </c>
+      <c r="B97" s="184">
         <v>91</v>
       </c>
-      <c r="C97" s="125"/>
-      <c r="D97" s="125"/>
-      <c r="E97" s="68"/>
-      <c r="F97" s="68"/>
-      <c r="G97" s="68"/>
-      <c r="H97" s="124"/>
-      <c r="I97" s="68"/>
-      <c r="J97" s="68"/>
-      <c r="K97" s="68"/>
-      <c r="L97" s="124">
+      <c r="C97" s="185" t="s">
+        <v>224</v>
+      </c>
+      <c r="D97" s="185" t="s">
+        <v>225</v>
+      </c>
+      <c r="E97" s="186"/>
+      <c r="F97" s="186">
+        <v>398</v>
+      </c>
+      <c r="G97" s="186">
+        <v>399</v>
+      </c>
+      <c r="H97" s="187">
+        <v>800</v>
+      </c>
+      <c r="I97" s="186">
+        <v>1199</v>
+      </c>
+      <c r="J97" s="186">
+        <v>799</v>
+      </c>
+      <c r="K97" s="186">
+        <v>1998</v>
+      </c>
+      <c r="L97" s="187">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M97" s="138"/>
+        <v>139.82499999999999</v>
+      </c>
+      <c r="M97" s="138">
+        <v>18</v>
+      </c>
       <c r="N97" s="42"/>
       <c r="O97" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>79.849999999999994</v>
       </c>
       <c r="P97" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>199.8</v>
       </c>
       <c r="Q97" s="44" t="e">
         <f t="shared" si="97"/>
@@ -9595,32 +9694,52 @@
       </c>
     </row>
     <row r="98" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A98" s="71"/>
-      <c r="B98" s="40">
+      <c r="A98" s="183">
+        <v>46310</v>
+      </c>
+      <c r="B98" s="184">
         <v>92</v>
       </c>
-      <c r="C98" s="125"/>
-      <c r="D98" s="125"/>
-      <c r="E98" s="68"/>
-      <c r="F98" s="68"/>
-      <c r="G98" s="68"/>
-      <c r="H98" s="124"/>
-      <c r="I98" s="68"/>
-      <c r="J98" s="68"/>
-      <c r="K98" s="68"/>
-      <c r="L98" s="124">
+      <c r="C98" s="185" t="s">
+        <v>226</v>
+      </c>
+      <c r="D98" s="185" t="s">
+        <v>156</v>
+      </c>
+      <c r="E98" s="186"/>
+      <c r="F98" s="186">
+        <v>120</v>
+      </c>
+      <c r="G98" s="186">
+        <v>120</v>
+      </c>
+      <c r="H98" s="187">
+        <v>120</v>
+      </c>
+      <c r="I98" s="186">
+        <v>120</v>
+      </c>
+      <c r="J98" s="186">
+        <v>120</v>
+      </c>
+      <c r="K98" s="186">
+        <v>120</v>
+      </c>
+      <c r="L98" s="187">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M98" s="138"/>
+        <v>18</v>
+      </c>
+      <c r="M98" s="138">
+        <v>14</v>
+      </c>
       <c r="N98" s="42"/>
       <c r="O98" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P98" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q98" s="44" t="e">
         <f t="shared" si="97"/>
@@ -9656,32 +9775,52 @@
       </c>
     </row>
     <row r="99" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A99" s="71"/>
-      <c r="B99" s="40">
+      <c r="A99" s="183">
+        <v>46310</v>
+      </c>
+      <c r="B99" s="184">
         <v>93</v>
       </c>
-      <c r="C99" s="125"/>
-      <c r="D99" s="125"/>
-      <c r="E99" s="68"/>
-      <c r="F99" s="68"/>
-      <c r="G99" s="68"/>
-      <c r="H99" s="124"/>
-      <c r="I99" s="68"/>
-      <c r="J99" s="68"/>
-      <c r="K99" s="68"/>
-      <c r="L99" s="124">
+      <c r="C99" s="185" t="s">
+        <v>227</v>
+      </c>
+      <c r="D99" s="185" t="s">
+        <v>221</v>
+      </c>
+      <c r="E99" s="186"/>
+      <c r="F99" s="186">
+        <v>40</v>
+      </c>
+      <c r="G99" s="186">
+        <v>40</v>
+      </c>
+      <c r="H99" s="187">
+        <v>40</v>
+      </c>
+      <c r="I99" s="186">
+        <v>40</v>
+      </c>
+      <c r="J99" s="186">
+        <v>40</v>
+      </c>
+      <c r="K99" s="186">
+        <v>40</v>
+      </c>
+      <c r="L99" s="187">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M99" s="138"/>
+        <v>6</v>
+      </c>
+      <c r="M99" s="138">
+        <v>14</v>
+      </c>
       <c r="N99" s="42"/>
       <c r="O99" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P99" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q99" s="44" t="e">
         <f t="shared" si="97"/>
@@ -9717,32 +9856,52 @@
       </c>
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A100" s="71"/>
-      <c r="B100" s="40">
+      <c r="A100" s="183">
+        <v>46310</v>
+      </c>
+      <c r="B100" s="184">
         <v>94</v>
       </c>
-      <c r="C100" s="125"/>
-      <c r="D100" s="125"/>
-      <c r="E100" s="68"/>
-      <c r="F100" s="68"/>
-      <c r="G100" s="68"/>
-      <c r="H100" s="124"/>
-      <c r="I100" s="68"/>
-      <c r="J100" s="68"/>
-      <c r="K100" s="68"/>
-      <c r="L100" s="124">
+      <c r="C100" s="185" t="s">
+        <v>228</v>
+      </c>
+      <c r="D100" s="185" t="s">
+        <v>229</v>
+      </c>
+      <c r="E100" s="186"/>
+      <c r="F100" s="186">
+        <v>120</v>
+      </c>
+      <c r="G100" s="186">
+        <v>120</v>
+      </c>
+      <c r="H100" s="187">
+        <v>120</v>
+      </c>
+      <c r="I100" s="186">
+        <v>120</v>
+      </c>
+      <c r="J100" s="186">
+        <v>120</v>
+      </c>
+      <c r="K100" s="186">
+        <v>120</v>
+      </c>
+      <c r="L100" s="187">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M100" s="138"/>
+        <v>18</v>
+      </c>
+      <c r="M100" s="138">
+        <v>14</v>
+      </c>
       <c r="N100" s="42"/>
       <c r="O100" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P100" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q100" s="44" t="e">
         <f t="shared" si="97"/>
@@ -9778,32 +9937,42 @@
       </c>
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A101" s="71"/>
-      <c r="B101" s="40">
+      <c r="A101" s="183">
+        <v>46310</v>
+      </c>
+      <c r="B101" s="184">
         <v>95</v>
       </c>
-      <c r="C101" s="125"/>
-      <c r="D101" s="125"/>
-      <c r="E101" s="68"/>
-      <c r="F101" s="68"/>
-      <c r="G101" s="68"/>
-      <c r="H101" s="124"/>
-      <c r="I101" s="68"/>
-      <c r="J101" s="68"/>
-      <c r="K101" s="68"/>
-      <c r="L101" s="124">
+      <c r="C101" s="185" t="s">
+        <v>230</v>
+      </c>
+      <c r="D101" s="185"/>
+      <c r="E101" s="186"/>
+      <c r="F101" s="186"/>
+      <c r="G101" s="186"/>
+      <c r="H101" s="187">
+        <v>2</v>
+      </c>
+      <c r="I101" s="186">
+        <v>2</v>
+      </c>
+      <c r="J101" s="186"/>
+      <c r="K101" s="186"/>
+      <c r="L101" s="187">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M101" s="138"/>
+        <v>0.1</v>
+      </c>
+      <c r="M101" s="138">
+        <v>18</v>
+      </c>
       <c r="N101" s="42"/>
       <c r="O101" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P101" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q101" s="44" t="e">
         <f t="shared" si="97"/>
@@ -9839,32 +10008,52 @@
       </c>
     </row>
     <row r="102" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A102" s="71"/>
-      <c r="B102" s="40">
+      <c r="A102" s="134">
+        <v>46310</v>
+      </c>
+      <c r="B102" s="135">
         <v>96</v>
       </c>
-      <c r="C102" s="125"/>
-      <c r="D102" s="125"/>
-      <c r="E102" s="68"/>
-      <c r="F102" s="68"/>
-      <c r="G102" s="68"/>
-      <c r="H102" s="124"/>
-      <c r="I102" s="68"/>
-      <c r="J102" s="68"/>
-      <c r="K102" s="68"/>
-      <c r="L102" s="124">
+      <c r="C102" s="144" t="s">
+        <v>211</v>
+      </c>
+      <c r="D102" s="144" t="s">
+        <v>212</v>
+      </c>
+      <c r="E102" s="142"/>
+      <c r="F102" s="142">
+        <v>200</v>
+      </c>
+      <c r="G102" s="142">
+        <v>200</v>
+      </c>
+      <c r="H102" s="143">
+        <v>200</v>
+      </c>
+      <c r="I102" s="142">
+        <v>2800</v>
+      </c>
+      <c r="J102" s="142">
+        <v>2400</v>
+      </c>
+      <c r="K102" s="142">
+        <v>2800</v>
+      </c>
+      <c r="L102" s="143">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="M102" s="138"/>
+        <v>215</v>
+      </c>
+      <c r="M102" s="138">
+        <v>16</v>
+      </c>
       <c r="N102" s="42"/>
       <c r="O102" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P102" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Q102" s="44" t="e">
         <f t="shared" si="97"/>
@@ -11858,10 +12047,10 @@
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A135" s="71"/>
-      <c r="B135" s="155" t="s">
+      <c r="B135" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="C135" s="155"/>
+      <c r="C135" s="168"/>
       <c r="D135" s="135"/>
       <c r="E135" s="140">
         <f t="shared" ref="E135:K135" si="103">SUM(E6:E63)</f>
@@ -12112,10 +12301,10 @@
       </c>
     </row>
     <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B139" s="167" t="s">
+      <c r="B139" s="156" t="s">
         <v>68</v>
       </c>
-      <c r="C139" s="168"/>
+      <c r="C139" s="157"/>
       <c r="D139" s="128"/>
       <c r="E139" s="76">
         <f>SUM(E137:E138)</f>
@@ -12199,10 +12388,10 @@
       </c>
     </row>
     <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B140" s="156" t="s">
+      <c r="B140" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="C140" s="157"/>
+      <c r="C140" s="146"/>
       <c r="D140" s="129"/>
       <c r="E140" s="77">
         <f>SUM(E135,E139)</f>
@@ -12238,7 +12427,7 @@
       </c>
       <c r="M140" s="56">
         <f>SUM(M5:M139)</f>
-        <v>1435</v>
+        <v>1553</v>
       </c>
       <c r="N140" s="54">
         <f t="shared" ref="N140:X140" si="111">SUM(N5:N139)</f>
@@ -12246,11 +12435,11 @@
       </c>
       <c r="O140" s="55">
         <f t="shared" si="111"/>
-        <v>857.6</v>
+        <v>1009.35</v>
       </c>
       <c r="P140" s="57">
         <f t="shared" si="111"/>
-        <v>1761.1999999999998</v>
+        <v>2431</v>
       </c>
       <c r="Q140" s="58" t="e">
         <f t="shared" si="111"/>
@@ -12287,17 +12476,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B135:C135"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B135:C135"/>
   </mergeCells>
   <conditionalFormatting sqref="C48:D62">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12397,24 +12586,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="80">
-        <v>301</v>
+        <v>375</v>
       </c>
       <c r="E5" s="72">
-        <v>578</v>
+        <v>774</v>
       </c>
       <c r="F5" s="72">
-        <v>380</v>
+        <v>595</v>
       </c>
       <c r="G5" s="94">
         <f>SUM(D5:F5)</f>
-        <v>1259</v>
+        <v>1744</v>
       </c>
       <c r="H5" s="87">
         <v>10000</v>
       </c>
       <c r="I5" s="88">
         <f>G5-H5</f>
-        <v>-8741</v>
+        <v>-8256</v>
       </c>
       <c r="K5" s="132" t="s">
         <v>1</v>
@@ -12445,19 +12634,19 @@
       </c>
       <c r="D6" s="96">
         <f>D5*40</f>
-        <v>12040</v>
+        <v>15000</v>
       </c>
       <c r="E6" s="96">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>23120</v>
+        <v>30960</v>
       </c>
       <c r="F6" s="96">
         <f t="shared" si="1"/>
-        <v>15200</v>
+        <v>23800</v>
       </c>
       <c r="G6" s="97">
         <f>SUM(D6:F6)</f>
-        <v>50360</v>
+        <v>69760</v>
       </c>
       <c r="H6" s="89">
         <f>H5*40</f>
@@ -12465,7 +12654,7 @@
       </c>
       <c r="I6" s="90">
         <f>G6-H6</f>
-        <v>-349640</v>
+        <v>-330240</v>
       </c>
       <c r="K6" s="132" t="s">
         <v>2</v>
@@ -12614,11 +12803,11 @@
       </c>
       <c r="D9" s="98">
         <f>D8-D5</f>
-        <v>-301</v>
+        <v>-375</v>
       </c>
       <c r="E9" s="98">
         <f>E8-E5</f>
-        <v>-578</v>
+        <v>-774</v>
       </c>
       <c r="K9" s="132" t="s">
         <v>5</v>
@@ -12775,7 +12964,7 @@
       </c>
       <c r="G12" s="83">
         <f>D12+G5</f>
-        <v>5459</v>
+        <v>5944</v>
       </c>
       <c r="K12" s="132" t="s">
         <v>11</v>
@@ -12827,7 +13016,7 @@
       </c>
       <c r="G13" s="83">
         <f>G12*40</f>
-        <v>218360</v>
+        <v>237760</v>
       </c>
       <c r="S13" s="169" t="s">
         <v>83</v>

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEF6F8F-7011-439A-ACD7-694EBCEE104D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AAA668F-667F-43FD-BCFE-78E52233ED5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="243">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -715,6 +715,42 @@
   </si>
   <si>
     <t>Gourmet College Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warehouse </t>
+  </si>
+  <si>
+    <t>Euro Hyper Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HKB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y block </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajwa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canal Garden </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naqshbandi </t>
+  </si>
+  <si>
+    <t>Raheem Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iqbal town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafaqat Stons </t>
+  </si>
+  <si>
+    <t>Sabzazar</t>
+  </si>
+  <si>
+    <t>Fatehgher</t>
   </si>
 </sst>
 </file>
@@ -1582,7 +1618,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1960,116 +1996,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2080,6 +2006,105 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2673,13 +2698,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="158">
+      <c r="B1" s="163">
         <f ca="1">TODAY()</f>
-        <v>46312</v>
-      </c>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
+        <v>46314</v>
+      </c>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2701,10 +2726,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="160" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="164" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2734,13 +2759,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="147"/>
-      <c r="M2" s="148"/>
-      <c r="N2" s="149"/>
-      <c r="O2" s="150" t="s">
+      <c r="L2" s="152"/>
+      <c r="M2" s="153"/>
+      <c r="N2" s="154"/>
+      <c r="O2" s="155" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="151"/>
+      <c r="P2" s="156"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2759,8 +2784,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="155"/>
-      <c r="B3" s="160"/>
+      <c r="A3" s="160"/>
+      <c r="B3" s="165"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2788,29 +2813,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="152" t="s">
+      <c r="L3" s="157" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="153"/>
-      <c r="N3" s="154"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="159"/>
       <c r="O3" s="64"/>
       <c r="P3" s="65"/>
-      <c r="Q3" s="162" t="s">
+      <c r="Q3" s="167" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="163"/>
-      <c r="S3" s="163"/>
-      <c r="T3" s="164"/>
-      <c r="U3" s="165" t="s">
+      <c r="R3" s="168"/>
+      <c r="S3" s="168"/>
+      <c r="T3" s="169"/>
+      <c r="U3" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="166"/>
-      <c r="W3" s="166"/>
-      <c r="X3" s="167"/>
+      <c r="V3" s="171"/>
+      <c r="W3" s="171"/>
+      <c r="X3" s="172"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="155"/>
-      <c r="B4" s="161"/>
+      <c r="A4" s="160"/>
+      <c r="B4" s="166"/>
       <c r="C4" s="130" t="s">
         <v>90</v>
       </c>
@@ -9155,35 +9180,35 @@
       </c>
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A91" s="178">
+      <c r="A91" s="71">
         <v>46306</v>
       </c>
-      <c r="B91" s="179">
+      <c r="B91" s="40">
         <v>85</v>
       </c>
-      <c r="C91" s="180" t="s">
+      <c r="C91" s="125" t="s">
         <v>215</v>
       </c>
-      <c r="D91" s="180" t="s">
+      <c r="D91" s="125" t="s">
         <v>217</v>
       </c>
-      <c r="E91" s="181"/>
-      <c r="F91" s="181">
-        <v>40</v>
-      </c>
-      <c r="G91" s="181">
-        <v>40</v>
-      </c>
-      <c r="H91" s="182">
-        <v>40</v>
-      </c>
-      <c r="I91" s="181">
-        <v>40</v>
-      </c>
-      <c r="J91" s="181">
-        <v>40</v>
-      </c>
-      <c r="K91" s="181">
+      <c r="E91" s="68"/>
+      <c r="F91" s="68">
+        <v>40</v>
+      </c>
+      <c r="G91" s="68">
+        <v>40</v>
+      </c>
+      <c r="H91" s="124">
+        <v>40</v>
+      </c>
+      <c r="I91" s="68">
+        <v>40</v>
+      </c>
+      <c r="J91" s="68">
+        <v>40</v>
+      </c>
+      <c r="K91" s="68">
         <v>40</v>
       </c>
       <c r="L91" s="124">
@@ -9236,33 +9261,33 @@
       </c>
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A92" s="178">
+      <c r="A92" s="71">
         <v>46306</v>
       </c>
-      <c r="B92" s="179">
+      <c r="B92" s="40">
         <v>86</v>
       </c>
-      <c r="C92" s="180" t="s">
+      <c r="C92" s="125" t="s">
         <v>218</v>
       </c>
-      <c r="D92" s="180"/>
-      <c r="E92" s="181"/>
-      <c r="F92" s="181">
+      <c r="D92" s="125"/>
+      <c r="E92" s="68"/>
+      <c r="F92" s="68">
         <v>200</v>
       </c>
-      <c r="G92" s="181">
+      <c r="G92" s="68">
         <v>280</v>
       </c>
-      <c r="H92" s="182">
+      <c r="H92" s="124">
         <v>320</v>
       </c>
-      <c r="I92" s="181">
+      <c r="I92" s="68">
         <v>360</v>
       </c>
-      <c r="J92" s="181">
+      <c r="J92" s="68">
         <v>320</v>
       </c>
-      <c r="K92" s="181">
+      <c r="K92" s="68">
         <v>440</v>
       </c>
       <c r="L92" s="124">
@@ -9315,33 +9340,33 @@
       </c>
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A93" s="178">
+      <c r="A93" s="71">
         <v>46306</v>
       </c>
-      <c r="B93" s="179">
+      <c r="B93" s="40">
         <v>87</v>
       </c>
-      <c r="C93" s="180" t="s">
+      <c r="C93" s="125" t="s">
         <v>219</v>
       </c>
-      <c r="D93" s="180"/>
-      <c r="E93" s="181"/>
-      <c r="F93" s="181">
+      <c r="D93" s="125"/>
+      <c r="E93" s="68"/>
+      <c r="F93" s="68">
         <v>200</v>
       </c>
-      <c r="G93" s="181">
+      <c r="G93" s="68">
         <v>120</v>
       </c>
-      <c r="H93" s="182">
+      <c r="H93" s="124">
         <v>120</v>
       </c>
-      <c r="I93" s="181">
+      <c r="I93" s="68">
         <v>280</v>
       </c>
-      <c r="J93" s="181">
+      <c r="J93" s="68">
         <v>360</v>
       </c>
-      <c r="K93" s="181">
+      <c r="K93" s="68">
         <v>440</v>
       </c>
       <c r="L93" s="124">
@@ -9394,27 +9419,27 @@
       </c>
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A94" s="178">
+      <c r="A94" s="71">
         <v>46306</v>
       </c>
-      <c r="B94" s="179">
+      <c r="B94" s="40">
         <v>88</v>
       </c>
-      <c r="C94" s="180" t="s">
+      <c r="C94" s="125" t="s">
         <v>211</v>
       </c>
-      <c r="D94" s="180" t="s">
+      <c r="D94" s="125" t="s">
         <v>212</v>
       </c>
-      <c r="E94" s="181"/>
-      <c r="F94" s="181">
+      <c r="E94" s="68"/>
+      <c r="F94" s="68">
         <v>600</v>
       </c>
-      <c r="G94" s="181"/>
-      <c r="H94" s="182"/>
-      <c r="I94" s="181"/>
-      <c r="J94" s="181"/>
-      <c r="K94" s="181"/>
+      <c r="G94" s="68"/>
+      <c r="H94" s="124"/>
+      <c r="I94" s="68"/>
+      <c r="J94" s="68"/>
+      <c r="K94" s="68"/>
       <c r="L94" s="124">
         <f t="shared" si="84"/>
         <v>15</v>
@@ -9465,34 +9490,34 @@
       </c>
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A95" s="183">
+      <c r="A95" s="145">
         <v>46310</v>
       </c>
-      <c r="B95" s="184">
+      <c r="B95" s="146">
         <v>89</v>
       </c>
-      <c r="C95" s="185" t="s">
+      <c r="C95" s="147" t="s">
         <v>220</v>
       </c>
-      <c r="D95" s="185" t="s">
+      <c r="D95" s="147" t="s">
         <v>221</v>
       </c>
-      <c r="E95" s="186"/>
-      <c r="F95" s="186">
+      <c r="E95" s="148"/>
+      <c r="F95" s="148">
         <v>-2</v>
       </c>
-      <c r="G95" s="186">
+      <c r="G95" s="148">
         <v>-2</v>
       </c>
-      <c r="H95" s="187"/>
-      <c r="I95" s="186">
+      <c r="H95" s="149"/>
+      <c r="I95" s="148">
         <v>200</v>
       </c>
-      <c r="J95" s="186">
+      <c r="J95" s="148">
         <v>200</v>
       </c>
-      <c r="K95" s="186"/>
-      <c r="L95" s="187">
+      <c r="K95" s="148"/>
+      <c r="L95" s="149">
         <f t="shared" si="84"/>
         <v>9.9</v>
       </c>
@@ -9542,28 +9567,28 @@
       </c>
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A96" s="183">
+      <c r="A96" s="145">
         <v>46310</v>
       </c>
-      <c r="B96" s="184">
+      <c r="B96" s="146">
         <v>90</v>
       </c>
-      <c r="C96" s="185" t="s">
+      <c r="C96" s="147" t="s">
         <v>222</v>
       </c>
-      <c r="D96" s="185" t="s">
+      <c r="D96" s="147" t="s">
         <v>223</v>
       </c>
-      <c r="E96" s="186"/>
-      <c r="F96" s="186"/>
-      <c r="G96" s="186"/>
-      <c r="H96" s="187"/>
-      <c r="I96" s="186"/>
-      <c r="J96" s="186">
+      <c r="E96" s="148"/>
+      <c r="F96" s="148"/>
+      <c r="G96" s="148"/>
+      <c r="H96" s="149"/>
+      <c r="I96" s="148"/>
+      <c r="J96" s="148">
         <v>158</v>
       </c>
-      <c r="K96" s="186"/>
-      <c r="L96" s="187">
+      <c r="K96" s="148"/>
+      <c r="L96" s="149">
         <f t="shared" si="84"/>
         <v>3.95</v>
       </c>
@@ -9613,38 +9638,38 @@
       </c>
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A97" s="183">
+      <c r="A97" s="145">
         <v>46310</v>
       </c>
-      <c r="B97" s="184">
+      <c r="B97" s="146">
         <v>91</v>
       </c>
-      <c r="C97" s="185" t="s">
+      <c r="C97" s="147" t="s">
         <v>224</v>
       </c>
-      <c r="D97" s="185" t="s">
+      <c r="D97" s="147" t="s">
         <v>225</v>
       </c>
-      <c r="E97" s="186"/>
-      <c r="F97" s="186">
+      <c r="E97" s="148"/>
+      <c r="F97" s="148">
         <v>398</v>
       </c>
-      <c r="G97" s="186">
+      <c r="G97" s="148">
         <v>399</v>
       </c>
-      <c r="H97" s="187">
+      <c r="H97" s="149">
         <v>800</v>
       </c>
-      <c r="I97" s="186">
+      <c r="I97" s="148">
         <v>1199</v>
       </c>
-      <c r="J97" s="186">
+      <c r="J97" s="148">
         <v>799</v>
       </c>
-      <c r="K97" s="186">
+      <c r="K97" s="148">
         <v>1998</v>
       </c>
-      <c r="L97" s="187">
+      <c r="L97" s="149">
         <f t="shared" si="84"/>
         <v>139.82499999999999</v>
       </c>
@@ -9694,38 +9719,38 @@
       </c>
     </row>
     <row r="98" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A98" s="183">
+      <c r="A98" s="145">
         <v>46310</v>
       </c>
-      <c r="B98" s="184">
+      <c r="B98" s="146">
         <v>92</v>
       </c>
-      <c r="C98" s="185" t="s">
+      <c r="C98" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="D98" s="185" t="s">
+      <c r="D98" s="147" t="s">
         <v>156</v>
       </c>
-      <c r="E98" s="186"/>
-      <c r="F98" s="186">
+      <c r="E98" s="148"/>
+      <c r="F98" s="148">
         <v>120</v>
       </c>
-      <c r="G98" s="186">
+      <c r="G98" s="148">
         <v>120</v>
       </c>
-      <c r="H98" s="187">
+      <c r="H98" s="149">
         <v>120</v>
       </c>
-      <c r="I98" s="186">
+      <c r="I98" s="148">
         <v>120</v>
       </c>
-      <c r="J98" s="186">
+      <c r="J98" s="148">
         <v>120</v>
       </c>
-      <c r="K98" s="186">
+      <c r="K98" s="148">
         <v>120</v>
       </c>
-      <c r="L98" s="187">
+      <c r="L98" s="149">
         <f t="shared" si="84"/>
         <v>18</v>
       </c>
@@ -9775,38 +9800,38 @@
       </c>
     </row>
     <row r="99" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A99" s="183">
+      <c r="A99" s="145">
         <v>46310</v>
       </c>
-      <c r="B99" s="184">
+      <c r="B99" s="146">
         <v>93</v>
       </c>
-      <c r="C99" s="185" t="s">
+      <c r="C99" s="147" t="s">
         <v>227</v>
       </c>
-      <c r="D99" s="185" t="s">
+      <c r="D99" s="147" t="s">
         <v>221</v>
       </c>
-      <c r="E99" s="186"/>
-      <c r="F99" s="186">
-        <v>40</v>
-      </c>
-      <c r="G99" s="186">
-        <v>40</v>
-      </c>
-      <c r="H99" s="187">
-        <v>40</v>
-      </c>
-      <c r="I99" s="186">
-        <v>40</v>
-      </c>
-      <c r="J99" s="186">
-        <v>40</v>
-      </c>
-      <c r="K99" s="186">
-        <v>40</v>
-      </c>
-      <c r="L99" s="187">
+      <c r="E99" s="148"/>
+      <c r="F99" s="148">
+        <v>40</v>
+      </c>
+      <c r="G99" s="148">
+        <v>40</v>
+      </c>
+      <c r="H99" s="149">
+        <v>40</v>
+      </c>
+      <c r="I99" s="148">
+        <v>40</v>
+      </c>
+      <c r="J99" s="148">
+        <v>40</v>
+      </c>
+      <c r="K99" s="148">
+        <v>40</v>
+      </c>
+      <c r="L99" s="149">
         <f t="shared" si="84"/>
         <v>6</v>
       </c>
@@ -9856,38 +9881,38 @@
       </c>
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A100" s="183">
+      <c r="A100" s="145">
         <v>46310</v>
       </c>
-      <c r="B100" s="184">
+      <c r="B100" s="146">
         <v>94</v>
       </c>
-      <c r="C100" s="185" t="s">
+      <c r="C100" s="147" t="s">
         <v>228</v>
       </c>
-      <c r="D100" s="185" t="s">
+      <c r="D100" s="147" t="s">
         <v>229</v>
       </c>
-      <c r="E100" s="186"/>
-      <c r="F100" s="186">
+      <c r="E100" s="148"/>
+      <c r="F100" s="148">
         <v>120</v>
       </c>
-      <c r="G100" s="186">
+      <c r="G100" s="148">
         <v>120</v>
       </c>
-      <c r="H100" s="187">
+      <c r="H100" s="149">
         <v>120</v>
       </c>
-      <c r="I100" s="186">
+      <c r="I100" s="148">
         <v>120</v>
       </c>
-      <c r="J100" s="186">
+      <c r="J100" s="148">
         <v>120</v>
       </c>
-      <c r="K100" s="186">
+      <c r="K100" s="148">
         <v>120</v>
       </c>
-      <c r="L100" s="187">
+      <c r="L100" s="149">
         <f t="shared" si="84"/>
         <v>18</v>
       </c>
@@ -9937,28 +9962,28 @@
       </c>
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A101" s="183">
+      <c r="A101" s="145">
         <v>46310</v>
       </c>
-      <c r="B101" s="184">
+      <c r="B101" s="146">
         <v>95</v>
       </c>
-      <c r="C101" s="185" t="s">
+      <c r="C101" s="147" t="s">
         <v>230</v>
       </c>
-      <c r="D101" s="185"/>
-      <c r="E101" s="186"/>
-      <c r="F101" s="186"/>
-      <c r="G101" s="186"/>
-      <c r="H101" s="187">
+      <c r="D101" s="147"/>
+      <c r="E101" s="148"/>
+      <c r="F101" s="148"/>
+      <c r="G101" s="148"/>
+      <c r="H101" s="149">
         <v>2</v>
       </c>
-      <c r="I101" s="186">
+      <c r="I101" s="148">
         <v>2</v>
       </c>
-      <c r="J101" s="186"/>
-      <c r="K101" s="186"/>
-      <c r="L101" s="187">
+      <c r="J101" s="148"/>
+      <c r="K101" s="148"/>
+      <c r="L101" s="149">
         <f t="shared" si="84"/>
         <v>0.1</v>
       </c>
@@ -10089,32 +10114,52 @@
       </c>
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A103" s="71"/>
+      <c r="A103" s="134">
+        <v>46312</v>
+      </c>
       <c r="B103" s="40">
         <v>97</v>
       </c>
-      <c r="C103" s="125"/>
-      <c r="D103" s="125"/>
+      <c r="C103" s="125" t="s">
+        <v>23</v>
+      </c>
+      <c r="D103" s="125" t="s">
+        <v>231</v>
+      </c>
       <c r="E103" s="68"/>
-      <c r="F103" s="68"/>
-      <c r="G103" s="68"/>
-      <c r="H103" s="124"/>
-      <c r="I103" s="68"/>
-      <c r="J103" s="68"/>
-      <c r="K103" s="68"/>
+      <c r="F103" s="68">
+        <v>80</v>
+      </c>
+      <c r="G103" s="68">
+        <v>120</v>
+      </c>
+      <c r="H103" s="124">
+        <v>80</v>
+      </c>
+      <c r="I103" s="68">
+        <v>120</v>
+      </c>
+      <c r="J103" s="68">
+        <v>80</v>
+      </c>
+      <c r="K103" s="68">
+        <v>280</v>
+      </c>
       <c r="L103" s="124">
         <f t="shared" ref="L103:L134" si="99">SUM(E103:K103)/40</f>
-        <v>0</v>
-      </c>
-      <c r="M103" s="138"/>
+        <v>19</v>
+      </c>
+      <c r="M103" s="138">
+        <v>8</v>
+      </c>
       <c r="N103" s="42"/>
       <c r="O103" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P103" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q103" s="44" t="e">
         <f t="shared" si="97"/>
@@ -10150,24 +10195,36 @@
       </c>
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A104" s="71"/>
+      <c r="A104" s="134">
+        <v>46312</v>
+      </c>
       <c r="B104" s="40">
         <v>98</v>
       </c>
-      <c r="C104" s="125"/>
+      <c r="C104" s="125" t="s">
+        <v>232</v>
+      </c>
       <c r="D104" s="125"/>
       <c r="E104" s="68"/>
       <c r="F104" s="68"/>
       <c r="G104" s="68"/>
       <c r="H104" s="124"/>
-      <c r="I104" s="68"/>
-      <c r="J104" s="68"/>
-      <c r="K104" s="68"/>
+      <c r="I104" s="68">
+        <v>800</v>
+      </c>
+      <c r="J104" s="68">
+        <v>720</v>
+      </c>
+      <c r="K104" s="68">
+        <v>880</v>
+      </c>
       <c r="L104" s="124">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M104" s="138"/>
+        <v>60</v>
+      </c>
+      <c r="M104" s="138">
+        <v>14</v>
+      </c>
       <c r="N104" s="42"/>
       <c r="O104" s="66">
         <f t="shared" si="91"/>
@@ -10175,7 +10232,7 @@
       </c>
       <c r="P104" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q104" s="44" t="e">
         <f t="shared" si="97"/>
@@ -10211,32 +10268,52 @@
       </c>
     </row>
     <row r="105" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A105" s="71"/>
+      <c r="A105" s="134">
+        <v>46312</v>
+      </c>
       <c r="B105" s="40">
         <v>99</v>
       </c>
-      <c r="C105" s="125"/>
-      <c r="D105" s="125"/>
+      <c r="C105" s="125" t="s">
+        <v>233</v>
+      </c>
+      <c r="D105" s="125" t="s">
+        <v>234</v>
+      </c>
       <c r="E105" s="68"/>
-      <c r="F105" s="68"/>
-      <c r="G105" s="68"/>
-      <c r="H105" s="124"/>
-      <c r="I105" s="68"/>
-      <c r="J105" s="68"/>
-      <c r="K105" s="68"/>
+      <c r="F105" s="68">
+        <v>40</v>
+      </c>
+      <c r="G105" s="68">
+        <v>40</v>
+      </c>
+      <c r="H105" s="124">
+        <v>40</v>
+      </c>
+      <c r="I105" s="68">
+        <v>40</v>
+      </c>
+      <c r="J105" s="68">
+        <v>40</v>
+      </c>
+      <c r="K105" s="68">
+        <v>40</v>
+      </c>
       <c r="L105" s="124">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M105" s="138"/>
+        <v>6</v>
+      </c>
+      <c r="M105" s="138">
+        <v>10</v>
+      </c>
       <c r="N105" s="42"/>
       <c r="O105" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P105" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q105" s="44" t="e">
         <f t="shared" si="97"/>
@@ -10272,32 +10349,52 @@
       </c>
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A106" s="71"/>
+      <c r="A106" s="134">
+        <v>46312</v>
+      </c>
       <c r="B106" s="40">
         <v>100</v>
       </c>
-      <c r="C106" s="125"/>
-      <c r="D106" s="125"/>
+      <c r="C106" s="125" t="s">
+        <v>235</v>
+      </c>
+      <c r="D106" s="125" t="s">
+        <v>236</v>
+      </c>
       <c r="E106" s="68"/>
-      <c r="F106" s="68"/>
-      <c r="G106" s="68"/>
-      <c r="H106" s="124"/>
-      <c r="I106" s="68"/>
-      <c r="J106" s="68"/>
-      <c r="K106" s="68"/>
+      <c r="F106" s="68">
+        <v>40</v>
+      </c>
+      <c r="G106" s="68">
+        <v>40</v>
+      </c>
+      <c r="H106" s="124">
+        <v>40</v>
+      </c>
+      <c r="I106" s="68">
+        <v>40</v>
+      </c>
+      <c r="J106" s="68">
+        <v>40</v>
+      </c>
+      <c r="K106" s="68">
+        <v>40</v>
+      </c>
       <c r="L106" s="124">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M106" s="138"/>
+        <v>6</v>
+      </c>
+      <c r="M106" s="138">
+        <v>10</v>
+      </c>
       <c r="N106" s="42"/>
       <c r="O106" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P106" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q106" s="44" t="e">
         <f t="shared" si="97"/>
@@ -10333,32 +10430,52 @@
       </c>
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A107" s="71"/>
+      <c r="A107" s="134">
+        <v>46312</v>
+      </c>
       <c r="B107" s="40">
         <v>101</v>
       </c>
-      <c r="C107" s="125"/>
-      <c r="D107" s="125"/>
+      <c r="C107" s="125" t="s">
+        <v>237</v>
+      </c>
+      <c r="D107" s="125" t="s">
+        <v>112</v>
+      </c>
       <c r="E107" s="68"/>
-      <c r="F107" s="68"/>
-      <c r="G107" s="68"/>
-      <c r="H107" s="124"/>
-      <c r="I107" s="68"/>
-      <c r="J107" s="68"/>
-      <c r="K107" s="68"/>
+      <c r="F107" s="68">
+        <v>120</v>
+      </c>
+      <c r="G107" s="68">
+        <v>120</v>
+      </c>
+      <c r="H107" s="124">
+        <v>120</v>
+      </c>
+      <c r="I107" s="68">
+        <v>120</v>
+      </c>
+      <c r="J107" s="68">
+        <v>120</v>
+      </c>
+      <c r="K107" s="68">
+        <v>120</v>
+      </c>
       <c r="L107" s="124">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M107" s="138"/>
+        <v>18</v>
+      </c>
+      <c r="M107" s="138">
+        <v>14</v>
+      </c>
       <c r="N107" s="42"/>
       <c r="O107" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P107" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q107" s="44" t="e">
         <f t="shared" si="97"/>
@@ -10394,32 +10511,52 @@
       </c>
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A108" s="71"/>
+      <c r="A108" s="134">
+        <v>46312</v>
+      </c>
       <c r="B108" s="40">
         <v>102</v>
       </c>
-      <c r="C108" s="125"/>
-      <c r="D108" s="125"/>
+      <c r="C108" s="125" t="s">
+        <v>238</v>
+      </c>
+      <c r="D108" s="125" t="s">
+        <v>239</v>
+      </c>
       <c r="E108" s="68"/>
-      <c r="F108" s="68"/>
-      <c r="G108" s="68"/>
-      <c r="H108" s="124"/>
-      <c r="I108" s="68"/>
-      <c r="J108" s="68"/>
-      <c r="K108" s="68"/>
+      <c r="F108" s="68">
+        <v>80</v>
+      </c>
+      <c r="G108" s="68">
+        <v>0</v>
+      </c>
+      <c r="H108" s="124">
+        <v>160</v>
+      </c>
+      <c r="I108" s="68">
+        <v>160</v>
+      </c>
+      <c r="J108" s="68">
+        <v>200</v>
+      </c>
+      <c r="K108" s="68">
+        <v>320</v>
+      </c>
       <c r="L108" s="124">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="138"/>
+        <v>23</v>
+      </c>
+      <c r="M108" s="138">
+        <v>14</v>
+      </c>
       <c r="N108" s="42"/>
       <c r="O108" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P108" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q108" s="44" t="e">
         <f t="shared" si="97"/>
@@ -10455,32 +10592,50 @@
       </c>
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A109" s="71"/>
+      <c r="A109" s="134">
+        <v>46312</v>
+      </c>
       <c r="B109" s="40">
         <v>103</v>
       </c>
-      <c r="C109" s="125"/>
-      <c r="D109" s="125"/>
+      <c r="C109" s="125" t="s">
+        <v>240</v>
+      </c>
+      <c r="D109" s="125" t="s">
+        <v>241</v>
+      </c>
       <c r="E109" s="68"/>
       <c r="F109" s="68"/>
-      <c r="G109" s="68"/>
-      <c r="H109" s="124"/>
-      <c r="I109" s="68"/>
-      <c r="J109" s="68"/>
-      <c r="K109" s="68"/>
+      <c r="G109" s="68">
+        <v>200</v>
+      </c>
+      <c r="H109" s="124">
+        <v>200</v>
+      </c>
+      <c r="I109" s="68">
+        <v>200</v>
+      </c>
+      <c r="J109" s="68">
+        <v>200</v>
+      </c>
+      <c r="K109" s="68">
+        <v>200</v>
+      </c>
       <c r="L109" s="124">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M109" s="138"/>
+        <v>25</v>
+      </c>
+      <c r="M109" s="138">
+        <v>14</v>
+      </c>
       <c r="N109" s="42"/>
       <c r="O109" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P109" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q109" s="44" t="e">
         <f t="shared" si="97"/>
@@ -10516,24 +10671,34 @@
       </c>
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A110" s="71"/>
+      <c r="A110" s="134">
+        <v>46312</v>
+      </c>
       <c r="B110" s="40">
         <v>104</v>
       </c>
-      <c r="C110" s="125"/>
-      <c r="D110" s="125"/>
+      <c r="C110" s="125" t="s">
+        <v>240</v>
+      </c>
+      <c r="D110" s="125" t="s">
+        <v>242</v>
+      </c>
       <c r="E110" s="68"/>
       <c r="F110" s="68"/>
       <c r="G110" s="68"/>
       <c r="H110" s="124"/>
       <c r="I110" s="68"/>
-      <c r="J110" s="68"/>
+      <c r="J110" s="68">
+        <v>158</v>
+      </c>
       <c r="K110" s="68"/>
       <c r="L110" s="124">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M110" s="138"/>
+        <v>3.95</v>
+      </c>
+      <c r="M110" s="138">
+        <v>14</v>
+      </c>
       <c r="N110" s="42"/>
       <c r="O110" s="66">
         <f t="shared" si="91"/>
@@ -10541,7 +10706,7 @@
       </c>
       <c r="P110" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q110" s="44" t="e">
         <f t="shared" si="97"/>
@@ -10577,32 +10742,48 @@
       </c>
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A111" s="71"/>
+      <c r="A111" s="134">
+        <v>46312</v>
+      </c>
       <c r="B111" s="40">
         <v>105</v>
       </c>
-      <c r="C111" s="125"/>
+      <c r="C111" s="125" t="s">
+        <v>189</v>
+      </c>
       <c r="D111" s="125"/>
       <c r="E111" s="68"/>
       <c r="F111" s="68"/>
-      <c r="G111" s="68"/>
-      <c r="H111" s="124"/>
-      <c r="I111" s="68"/>
-      <c r="J111" s="68"/>
-      <c r="K111" s="68"/>
+      <c r="G111" s="68">
+        <v>80</v>
+      </c>
+      <c r="H111" s="124">
+        <v>160</v>
+      </c>
+      <c r="I111" s="68">
+        <v>80</v>
+      </c>
+      <c r="J111" s="68">
+        <v>80</v>
+      </c>
+      <c r="K111" s="68">
+        <v>120</v>
+      </c>
       <c r="L111" s="124">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M111" s="138"/>
+        <v>13</v>
+      </c>
+      <c r="M111" s="138">
+        <v>14</v>
+      </c>
       <c r="N111" s="42"/>
       <c r="O111" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P111" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q111" s="44" t="e">
         <f t="shared" si="97"/>
@@ -12047,10 +12228,10 @@
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A135" s="71"/>
-      <c r="B135" s="168" t="s">
+      <c r="B135" s="173" t="s">
         <v>11</v>
       </c>
-      <c r="C135" s="168"/>
+      <c r="C135" s="173"/>
       <c r="D135" s="135"/>
       <c r="E135" s="140">
         <f t="shared" ref="E135:K135" si="103">SUM(E6:E63)</f>
@@ -12301,10 +12482,10 @@
       </c>
     </row>
     <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B139" s="156" t="s">
+      <c r="B139" s="161" t="s">
         <v>68</v>
       </c>
-      <c r="C139" s="157"/>
+      <c r="C139" s="162"/>
       <c r="D139" s="128"/>
       <c r="E139" s="76">
         <f>SUM(E137:E138)</f>
@@ -12388,10 +12569,10 @@
       </c>
     </row>
     <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B140" s="145" t="s">
+      <c r="B140" s="150" t="s">
         <v>11</v>
       </c>
-      <c r="C140" s="146"/>
+      <c r="C140" s="151"/>
       <c r="D140" s="129"/>
       <c r="E140" s="77">
         <f>SUM(E135,E139)</f>
@@ -12427,7 +12608,7 @@
       </c>
       <c r="M140" s="56">
         <f>SUM(M5:M139)</f>
-        <v>1553</v>
+        <v>1665</v>
       </c>
       <c r="N140" s="54">
         <f t="shared" ref="N140:X140" si="111">SUM(N5:N139)</f>
@@ -12435,11 +12616,11 @@
       </c>
       <c r="O140" s="55">
         <f t="shared" si="111"/>
-        <v>1009.35</v>
+        <v>1097.3499999999999</v>
       </c>
       <c r="P140" s="57">
         <f t="shared" si="111"/>
-        <v>2431</v>
+        <v>2690.8999999999996</v>
       </c>
       <c r="Q140" s="58" t="e">
         <f t="shared" si="111"/>
@@ -12522,25 +12703,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="171" t="s">
+      <c r="C3" s="176" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="172"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="175" t="s">
+      <c r="D3" s="177"/>
+      <c r="E3" s="177"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="178"/>
+      <c r="H3" s="180" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="176"/>
-      <c r="K3" s="177" t="s">
+      <c r="I3" s="181"/>
+      <c r="K3" s="182" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="177"/>
-      <c r="M3" s="177"/>
-      <c r="N3" s="177"/>
-      <c r="O3" s="177"/>
-      <c r="P3" s="177"/>
+      <c r="L3" s="182"/>
+      <c r="M3" s="182"/>
+      <c r="N3" s="182"/>
+      <c r="O3" s="182"/>
+      <c r="P3" s="182"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="91"/>
@@ -12586,24 +12767,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="80">
-        <v>375</v>
+        <v>418</v>
       </c>
       <c r="E5" s="72">
-        <v>774</v>
+        <v>948</v>
       </c>
       <c r="F5" s="72">
         <v>595</v>
       </c>
       <c r="G5" s="94">
         <f>SUM(D5:F5)</f>
-        <v>1744</v>
+        <v>1961</v>
       </c>
       <c r="H5" s="87">
         <v>10000</v>
       </c>
       <c r="I5" s="88">
         <f>G5-H5</f>
-        <v>-8256</v>
+        <v>-8039</v>
       </c>
       <c r="K5" s="132" t="s">
         <v>1</v>
@@ -12612,11 +12793,11 @@
         <v>70</v>
       </c>
       <c r="M5" s="5">
-        <v>9122</v>
+        <v>6676</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>228.05</v>
+        <v>166.9</v>
       </c>
       <c r="O5" s="74"/>
       <c r="P5" s="133"/>
@@ -12625,7 +12806,7 @@
       </c>
       <c r="R5" s="141">
         <f>N5-Q5</f>
-        <v>-39.159999999999968</v>
+        <v>-100.30999999999997</v>
       </c>
     </row>
     <row r="6" spans="3:26" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
@@ -12634,11 +12815,11 @@
       </c>
       <c r="D6" s="96">
         <f>D5*40</f>
-        <v>15000</v>
+        <v>16720</v>
       </c>
       <c r="E6" s="96">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>30960</v>
+        <v>37920</v>
       </c>
       <c r="F6" s="96">
         <f t="shared" si="1"/>
@@ -12646,7 +12827,7 @@
       </c>
       <c r="G6" s="97">
         <f>SUM(D6:F6)</f>
-        <v>69760</v>
+        <v>78440</v>
       </c>
       <c r="H6" s="89">
         <f>H5*40</f>
@@ -12654,7 +12835,7 @@
       </c>
       <c r="I6" s="90">
         <f>G6-H6</f>
-        <v>-330240</v>
+        <v>-321560</v>
       </c>
       <c r="K6" s="132" t="s">
         <v>2</v>
@@ -12663,11 +12844,11 @@
         <v>70</v>
       </c>
       <c r="M6" s="5">
-        <v>10173</v>
+        <v>7876</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>254.32499999999999</v>
+        <v>196.9</v>
       </c>
       <c r="O6" s="74"/>
       <c r="P6" s="133"/>
@@ -12676,7 +12857,7 @@
       </c>
       <c r="R6" s="141">
         <f t="shared" ref="R6:R10" si="2">N6-Q6</f>
-        <v>80.054999999999978</v>
+        <v>22.629999999999995</v>
       </c>
       <c r="S6" s="116"/>
       <c r="T6" s="116"/>
@@ -12705,11 +12886,11 @@
         <v>70</v>
       </c>
       <c r="M7" s="5">
-        <v>7936</v>
+        <v>4133</v>
       </c>
       <c r="N7" s="6">
         <f t="shared" si="0"/>
-        <v>198.4</v>
+        <v>103.325</v>
       </c>
       <c r="O7" s="74"/>
       <c r="P7" s="133"/>
@@ -12718,7 +12899,7 @@
       </c>
       <c r="R7" s="141">
         <f t="shared" si="2"/>
-        <v>122.16000000000001</v>
+        <v>27.085000000000008</v>
       </c>
       <c r="S7" s="121" t="s">
         <v>85</v>
@@ -12756,11 +12937,11 @@
         <v>120</v>
       </c>
       <c r="M8" s="5">
-        <v>417</v>
+        <v>6558</v>
       </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>10.425000000000001</v>
+        <v>163.95</v>
       </c>
       <c r="O8" s="74">
         <v>50</v>
@@ -12771,7 +12952,7 @@
       </c>
       <c r="R8" s="141">
         <f t="shared" si="2"/>
-        <v>-73.875</v>
+        <v>79.649999999999991</v>
       </c>
       <c r="S8" s="72">
         <v>120</v>
@@ -12803,11 +12984,11 @@
       </c>
       <c r="D9" s="98">
         <f>D8-D5</f>
-        <v>-375</v>
+        <v>-418</v>
       </c>
       <c r="E9" s="98">
         <f>E8-E5</f>
-        <v>-774</v>
+        <v>-948</v>
       </c>
       <c r="K9" s="132" t="s">
         <v>5</v>
@@ -12816,11 +12997,11 @@
         <v>120</v>
       </c>
       <c r="M9" s="5">
-        <v>2454</v>
+        <v>7576</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>61.35</v>
+        <v>189.4</v>
       </c>
       <c r="O9" s="74">
         <v>23</v>
@@ -12831,7 +13012,7 @@
       </c>
       <c r="R9" s="141">
         <f t="shared" si="2"/>
-        <v>-47.82</v>
+        <v>80.23</v>
       </c>
       <c r="S9" s="72">
         <v>120</v>
@@ -12867,11 +13048,11 @@
         <v>120</v>
       </c>
       <c r="M10" s="5">
-        <v>68</v>
+        <v>4776</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>1.7</v>
+        <v>119.4</v>
       </c>
       <c r="O10" s="74"/>
       <c r="P10" s="133"/>
@@ -12880,7 +13061,7 @@
       </c>
       <c r="R10" s="141">
         <f t="shared" si="2"/>
-        <v>-196.65</v>
+        <v>-78.949999999999989</v>
       </c>
       <c r="S10" s="72">
         <v>120</v>
@@ -12905,26 +13086,24 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="174" t="s">
+      <c r="C11" s="179" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="174"/>
-      <c r="F11" s="174" t="s">
+      <c r="D11" s="179"/>
+      <c r="F11" s="179" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="174"/>
+      <c r="G11" s="179"/>
       <c r="K11" s="132" t="s">
         <v>7</v>
       </c>
       <c r="L11" s="7">
         <v>60</v>
       </c>
-      <c r="M11" s="5">
-        <v>8</v>
-      </c>
+      <c r="M11" s="5"/>
       <c r="N11" s="6">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O11" s="74">
         <v>125</v>
@@ -12964,7 +13143,7 @@
       </c>
       <c r="G12" s="83">
         <f>D12+G5</f>
-        <v>5944</v>
+        <v>6161</v>
       </c>
       <c r="K12" s="132" t="s">
         <v>11</v>
@@ -12972,11 +13151,11 @@
       <c r="L12" s="74"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>30178</v>
+        <v>37595</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>754.45</v>
+        <v>939.875</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
@@ -13016,12 +13195,12 @@
       </c>
       <c r="G13" s="83">
         <f>G12*40</f>
-        <v>237760</v>
-      </c>
-      <c r="S13" s="169" t="s">
+        <v>246440</v>
+      </c>
+      <c r="S13" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="169"/>
+      <c r="T13" s="174"/>
       <c r="U13" s="120">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -13075,7 +13254,7 @@
       <c r="N17" s="113"/>
       <c r="O17" s="114">
         <f>N17-M5</f>
-        <v>-9122</v>
+        <v>-6676</v>
       </c>
       <c r="R17">
         <v>51.94</v>
@@ -13095,7 +13274,7 @@
       <c r="N18" s="5"/>
       <c r="O18" s="114">
         <f>N18-M6</f>
-        <v>-10173</v>
+        <v>-7876</v>
       </c>
       <c r="R18">
         <v>163.25499999999997</v>
@@ -13118,7 +13297,7 @@
       <c r="N19" s="5"/>
       <c r="O19" s="114">
         <f t="shared" ref="O19:O23" si="5">N19-M7</f>
-        <v>-7936</v>
+        <v>-4133</v>
       </c>
       <c r="R19">
         <v>224.70999999999998</v>
@@ -13128,13 +13307,13 @@
       </c>
     </row>
     <row r="20" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="170" t="s">
+      <c r="D20" s="175" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="170"/>
-      <c r="F20" s="170"/>
-      <c r="G20" s="170"/>
-      <c r="H20" s="170"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="175"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="175"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
@@ -13145,7 +13324,7 @@
       <c r="N20" s="5"/>
       <c r="O20" s="114">
         <f t="shared" si="5"/>
-        <v>-417</v>
+        <v>-6558</v>
       </c>
       <c r="R20">
         <v>156.75</v>
@@ -13180,7 +13359,7 @@
       <c r="N21" s="5"/>
       <c r="O21" s="114">
         <f t="shared" si="5"/>
-        <v>-2454</v>
+        <v>-7576</v>
       </c>
       <c r="R21">
         <v>158.505</v>
@@ -13212,7 +13391,7 @@
       <c r="N22" s="5"/>
       <c r="O22" s="114">
         <f t="shared" si="5"/>
-        <v>-68</v>
+        <v>-4776</v>
       </c>
       <c r="R22">
         <v>69.150000000000006</v>
@@ -13244,7 +13423,7 @@
       <c r="N23" s="5"/>
       <c r="O23" s="114">
         <f t="shared" si="5"/>
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -13274,7 +13453,7 @@
       </c>
       <c r="O24" s="109">
         <f>SUM(O17:O23)</f>
-        <v>-30178</v>
+        <v>-37595</v>
       </c>
     </row>
     <row r="25" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -13304,7 +13483,7 @@
       </c>
       <c r="O25" s="109">
         <f>O24/40</f>
-        <v>-754.45</v>
+        <v>-939.875</v>
       </c>
     </row>
     <row r="26" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AAA668F-667F-43FD-BCFE-78E52233ED5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{986760EA-F121-4242-9885-D55841D0EC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="252">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -751,6 +751,33 @@
   </si>
   <si>
     <t>Fatehgher</t>
+  </si>
+  <si>
+    <t>Riwind Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Askari Punjab Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Punjab Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aslam Cash N carry </t>
+  </si>
+  <si>
+    <t>College Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euro Model Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euto NFC Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NFC Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umer Cash N Carry </t>
   </si>
 </sst>
 </file>
@@ -1996,15 +2023,37 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2046,39 +2095,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2105,6 +2121,17 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2698,13 +2725,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="163">
+      <c r="B1" s="145">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
-      </c>
-      <c r="C1" s="163"/>
-      <c r="D1" s="163"/>
-      <c r="E1" s="163"/>
+        <v>46315</v>
+      </c>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2726,10 +2753,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="160" t="s">
+      <c r="A2" s="166" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="164" t="s">
+      <c r="B2" s="146" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2759,13 +2786,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="152"/>
-      <c r="M2" s="153"/>
-      <c r="N2" s="154"/>
-      <c r="O2" s="155" t="s">
+      <c r="L2" s="158"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="160"/>
+      <c r="O2" s="161" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="156"/>
+      <c r="P2" s="162"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2784,8 +2811,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="160"/>
-      <c r="B3" s="165"/>
+      <c r="A3" s="166"/>
+      <c r="B3" s="147"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2813,29 +2840,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="157" t="s">
+      <c r="L3" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="158"/>
-      <c r="N3" s="159"/>
+      <c r="M3" s="164"/>
+      <c r="N3" s="165"/>
       <c r="O3" s="64"/>
       <c r="P3" s="65"/>
-      <c r="Q3" s="167" t="s">
+      <c r="Q3" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="168"/>
-      <c r="S3" s="168"/>
-      <c r="T3" s="169"/>
-      <c r="U3" s="170" t="s">
+      <c r="R3" s="150"/>
+      <c r="S3" s="150"/>
+      <c r="T3" s="151"/>
+      <c r="U3" s="152" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="171"/>
-      <c r="W3" s="171"/>
-      <c r="X3" s="172"/>
+      <c r="V3" s="153"/>
+      <c r="W3" s="153"/>
+      <c r="X3" s="154"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="160"/>
-      <c r="B4" s="166"/>
+      <c r="A4" s="166"/>
+      <c r="B4" s="148"/>
       <c r="C4" s="130" t="s">
         <v>90</v>
       </c>
@@ -9490,34 +9517,34 @@
       </c>
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A95" s="145">
+      <c r="A95" s="178">
         <v>46310</v>
       </c>
-      <c r="B95" s="146">
+      <c r="B95" s="179">
         <v>89</v>
       </c>
-      <c r="C95" s="147" t="s">
+      <c r="C95" s="180" t="s">
         <v>220</v>
       </c>
-      <c r="D95" s="147" t="s">
+      <c r="D95" s="180" t="s">
         <v>221</v>
       </c>
-      <c r="E95" s="148"/>
-      <c r="F95" s="148">
+      <c r="E95" s="181"/>
+      <c r="F95" s="181">
         <v>-2</v>
       </c>
-      <c r="G95" s="148">
+      <c r="G95" s="181">
         <v>-2</v>
       </c>
-      <c r="H95" s="149"/>
-      <c r="I95" s="148">
+      <c r="H95" s="182"/>
+      <c r="I95" s="181">
         <v>200</v>
       </c>
-      <c r="J95" s="148">
+      <c r="J95" s="181">
         <v>200</v>
       </c>
-      <c r="K95" s="148"/>
-      <c r="L95" s="149">
+      <c r="K95" s="181"/>
+      <c r="L95" s="182">
         <f t="shared" si="84"/>
         <v>9.9</v>
       </c>
@@ -9567,28 +9594,28 @@
       </c>
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A96" s="145">
+      <c r="A96" s="178">
         <v>46310</v>
       </c>
-      <c r="B96" s="146">
+      <c r="B96" s="179">
         <v>90</v>
       </c>
-      <c r="C96" s="147" t="s">
+      <c r="C96" s="180" t="s">
         <v>222</v>
       </c>
-      <c r="D96" s="147" t="s">
+      <c r="D96" s="180" t="s">
         <v>223</v>
       </c>
-      <c r="E96" s="148"/>
-      <c r="F96" s="148"/>
-      <c r="G96" s="148"/>
-      <c r="H96" s="149"/>
-      <c r="I96" s="148"/>
-      <c r="J96" s="148">
+      <c r="E96" s="181"/>
+      <c r="F96" s="181"/>
+      <c r="G96" s="181"/>
+      <c r="H96" s="182"/>
+      <c r="I96" s="181"/>
+      <c r="J96" s="181">
         <v>158</v>
       </c>
-      <c r="K96" s="148"/>
-      <c r="L96" s="149">
+      <c r="K96" s="181"/>
+      <c r="L96" s="182">
         <f t="shared" si="84"/>
         <v>3.95</v>
       </c>
@@ -9638,38 +9665,38 @@
       </c>
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A97" s="145">
+      <c r="A97" s="178">
         <v>46310</v>
       </c>
-      <c r="B97" s="146">
+      <c r="B97" s="179">
         <v>91</v>
       </c>
-      <c r="C97" s="147" t="s">
+      <c r="C97" s="180" t="s">
         <v>224</v>
       </c>
-      <c r="D97" s="147" t="s">
+      <c r="D97" s="180" t="s">
         <v>225</v>
       </c>
-      <c r="E97" s="148"/>
-      <c r="F97" s="148">
+      <c r="E97" s="181"/>
+      <c r="F97" s="181">
         <v>398</v>
       </c>
-      <c r="G97" s="148">
+      <c r="G97" s="181">
         <v>399</v>
       </c>
-      <c r="H97" s="149">
+      <c r="H97" s="182">
         <v>800</v>
       </c>
-      <c r="I97" s="148">
+      <c r="I97" s="181">
         <v>1199</v>
       </c>
-      <c r="J97" s="148">
+      <c r="J97" s="181">
         <v>799</v>
       </c>
-      <c r="K97" s="148">
+      <c r="K97" s="181">
         <v>1998</v>
       </c>
-      <c r="L97" s="149">
+      <c r="L97" s="182">
         <f t="shared" si="84"/>
         <v>139.82499999999999</v>
       </c>
@@ -9719,38 +9746,38 @@
       </c>
     </row>
     <row r="98" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A98" s="145">
+      <c r="A98" s="178">
         <v>46310</v>
       </c>
-      <c r="B98" s="146">
+      <c r="B98" s="179">
         <v>92</v>
       </c>
-      <c r="C98" s="147" t="s">
+      <c r="C98" s="180" t="s">
         <v>226</v>
       </c>
-      <c r="D98" s="147" t="s">
+      <c r="D98" s="180" t="s">
         <v>156</v>
       </c>
-      <c r="E98" s="148"/>
-      <c r="F98" s="148">
+      <c r="E98" s="181"/>
+      <c r="F98" s="181">
         <v>120</v>
       </c>
-      <c r="G98" s="148">
+      <c r="G98" s="181">
         <v>120</v>
       </c>
-      <c r="H98" s="149">
+      <c r="H98" s="182">
         <v>120</v>
       </c>
-      <c r="I98" s="148">
+      <c r="I98" s="181">
         <v>120</v>
       </c>
-      <c r="J98" s="148">
+      <c r="J98" s="181">
         <v>120</v>
       </c>
-      <c r="K98" s="148">
+      <c r="K98" s="181">
         <v>120</v>
       </c>
-      <c r="L98" s="149">
+      <c r="L98" s="182">
         <f t="shared" si="84"/>
         <v>18</v>
       </c>
@@ -9800,38 +9827,38 @@
       </c>
     </row>
     <row r="99" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A99" s="145">
+      <c r="A99" s="178">
         <v>46310</v>
       </c>
-      <c r="B99" s="146">
+      <c r="B99" s="179">
         <v>93</v>
       </c>
-      <c r="C99" s="147" t="s">
+      <c r="C99" s="180" t="s">
         <v>227</v>
       </c>
-      <c r="D99" s="147" t="s">
+      <c r="D99" s="180" t="s">
         <v>221</v>
       </c>
-      <c r="E99" s="148"/>
-      <c r="F99" s="148">
-        <v>40</v>
-      </c>
-      <c r="G99" s="148">
-        <v>40</v>
-      </c>
-      <c r="H99" s="149">
-        <v>40</v>
-      </c>
-      <c r="I99" s="148">
-        <v>40</v>
-      </c>
-      <c r="J99" s="148">
-        <v>40</v>
-      </c>
-      <c r="K99" s="148">
-        <v>40</v>
-      </c>
-      <c r="L99" s="149">
+      <c r="E99" s="181"/>
+      <c r="F99" s="181">
+        <v>40</v>
+      </c>
+      <c r="G99" s="181">
+        <v>40</v>
+      </c>
+      <c r="H99" s="182">
+        <v>40</v>
+      </c>
+      <c r="I99" s="181">
+        <v>40</v>
+      </c>
+      <c r="J99" s="181">
+        <v>40</v>
+      </c>
+      <c r="K99" s="181">
+        <v>40</v>
+      </c>
+      <c r="L99" s="182">
         <f t="shared" si="84"/>
         <v>6</v>
       </c>
@@ -9881,38 +9908,38 @@
       </c>
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A100" s="145">
+      <c r="A100" s="178">
         <v>46310</v>
       </c>
-      <c r="B100" s="146">
+      <c r="B100" s="179">
         <v>94</v>
       </c>
-      <c r="C100" s="147" t="s">
+      <c r="C100" s="180" t="s">
         <v>228</v>
       </c>
-      <c r="D100" s="147" t="s">
+      <c r="D100" s="180" t="s">
         <v>229</v>
       </c>
-      <c r="E100" s="148"/>
-      <c r="F100" s="148">
+      <c r="E100" s="181"/>
+      <c r="F100" s="181">
         <v>120</v>
       </c>
-      <c r="G100" s="148">
+      <c r="G100" s="181">
         <v>120</v>
       </c>
-      <c r="H100" s="149">
+      <c r="H100" s="182">
         <v>120</v>
       </c>
-      <c r="I100" s="148">
+      <c r="I100" s="181">
         <v>120</v>
       </c>
-      <c r="J100" s="148">
+      <c r="J100" s="181">
         <v>120</v>
       </c>
-      <c r="K100" s="148">
+      <c r="K100" s="181">
         <v>120</v>
       </c>
-      <c r="L100" s="149">
+      <c r="L100" s="182">
         <f t="shared" si="84"/>
         <v>18</v>
       </c>
@@ -9962,28 +9989,28 @@
       </c>
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A101" s="145">
+      <c r="A101" s="178">
         <v>46310</v>
       </c>
-      <c r="B101" s="146">
+      <c r="B101" s="179">
         <v>95</v>
       </c>
-      <c r="C101" s="147" t="s">
+      <c r="C101" s="180" t="s">
         <v>230</v>
       </c>
-      <c r="D101" s="147"/>
-      <c r="E101" s="148"/>
-      <c r="F101" s="148"/>
-      <c r="G101" s="148"/>
-      <c r="H101" s="149">
+      <c r="D101" s="180"/>
+      <c r="E101" s="181"/>
+      <c r="F101" s="181"/>
+      <c r="G101" s="181"/>
+      <c r="H101" s="182">
         <v>2</v>
       </c>
-      <c r="I101" s="148">
+      <c r="I101" s="181">
         <v>2</v>
       </c>
-      <c r="J101" s="148"/>
-      <c r="K101" s="148"/>
-      <c r="L101" s="149">
+      <c r="J101" s="181"/>
+      <c r="K101" s="181"/>
+      <c r="L101" s="182">
         <f t="shared" si="84"/>
         <v>0.1</v>
       </c>
@@ -10033,38 +10060,38 @@
       </c>
     </row>
     <row r="102" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A102" s="134">
+      <c r="A102" s="178">
         <v>46310</v>
       </c>
-      <c r="B102" s="135">
+      <c r="B102" s="179">
         <v>96</v>
       </c>
-      <c r="C102" s="144" t="s">
+      <c r="C102" s="180" t="s">
         <v>211</v>
       </c>
-      <c r="D102" s="144" t="s">
+      <c r="D102" s="180" t="s">
         <v>212</v>
       </c>
-      <c r="E102" s="142"/>
-      <c r="F102" s="142">
+      <c r="E102" s="181"/>
+      <c r="F102" s="181">
         <v>200</v>
       </c>
-      <c r="G102" s="142">
+      <c r="G102" s="181">
         <v>200</v>
       </c>
-      <c r="H102" s="143">
+      <c r="H102" s="182">
         <v>200</v>
       </c>
-      <c r="I102" s="142">
+      <c r="I102" s="181">
         <v>2800</v>
       </c>
-      <c r="J102" s="142">
+      <c r="J102" s="181">
         <v>2400</v>
       </c>
-      <c r="K102" s="142">
+      <c r="K102" s="181">
         <v>2800</v>
       </c>
-      <c r="L102" s="143">
+      <c r="L102" s="182">
         <f t="shared" si="84"/>
         <v>215</v>
       </c>
@@ -10114,38 +10141,38 @@
       </c>
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A103" s="134">
+      <c r="A103" s="178">
         <v>46312</v>
       </c>
-      <c r="B103" s="40">
+      <c r="B103" s="179">
         <v>97</v>
       </c>
-      <c r="C103" s="125" t="s">
+      <c r="C103" s="180" t="s">
         <v>23</v>
       </c>
-      <c r="D103" s="125" t="s">
+      <c r="D103" s="180" t="s">
         <v>231</v>
       </c>
-      <c r="E103" s="68"/>
-      <c r="F103" s="68">
+      <c r="E103" s="181"/>
+      <c r="F103" s="181">
         <v>80</v>
       </c>
-      <c r="G103" s="68">
+      <c r="G103" s="181">
         <v>120</v>
       </c>
-      <c r="H103" s="124">
+      <c r="H103" s="182">
         <v>80</v>
       </c>
-      <c r="I103" s="68">
+      <c r="I103" s="181">
         <v>120</v>
       </c>
-      <c r="J103" s="68">
+      <c r="J103" s="181">
         <v>80</v>
       </c>
-      <c r="K103" s="68">
+      <c r="K103" s="181">
         <v>280</v>
       </c>
-      <c r="L103" s="124">
+      <c r="L103" s="182">
         <f t="shared" ref="L103:L134" si="99">SUM(E103:K103)/40</f>
         <v>19</v>
       </c>
@@ -10195,30 +10222,30 @@
       </c>
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A104" s="134">
+      <c r="A104" s="178">
         <v>46312</v>
       </c>
-      <c r="B104" s="40">
+      <c r="B104" s="179">
         <v>98</v>
       </c>
-      <c r="C104" s="125" t="s">
+      <c r="C104" s="180" t="s">
         <v>232</v>
       </c>
-      <c r="D104" s="125"/>
-      <c r="E104" s="68"/>
-      <c r="F104" s="68"/>
-      <c r="G104" s="68"/>
-      <c r="H104" s="124"/>
-      <c r="I104" s="68">
+      <c r="D104" s="180"/>
+      <c r="E104" s="181"/>
+      <c r="F104" s="181"/>
+      <c r="G104" s="181"/>
+      <c r="H104" s="182"/>
+      <c r="I104" s="181">
         <v>800</v>
       </c>
-      <c r="J104" s="68">
+      <c r="J104" s="181">
         <v>720</v>
       </c>
-      <c r="K104" s="68">
+      <c r="K104" s="181">
         <v>880</v>
       </c>
-      <c r="L104" s="124">
+      <c r="L104" s="182">
         <f t="shared" si="99"/>
         <v>60</v>
       </c>
@@ -10268,38 +10295,38 @@
       </c>
     </row>
     <row r="105" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A105" s="134">
+      <c r="A105" s="178">
         <v>46312</v>
       </c>
-      <c r="B105" s="40">
+      <c r="B105" s="179">
         <v>99</v>
       </c>
-      <c r="C105" s="125" t="s">
+      <c r="C105" s="180" t="s">
         <v>233</v>
       </c>
-      <c r="D105" s="125" t="s">
+      <c r="D105" s="180" t="s">
         <v>234</v>
       </c>
-      <c r="E105" s="68"/>
-      <c r="F105" s="68">
-        <v>40</v>
-      </c>
-      <c r="G105" s="68">
-        <v>40</v>
-      </c>
-      <c r="H105" s="124">
-        <v>40</v>
-      </c>
-      <c r="I105" s="68">
-        <v>40</v>
-      </c>
-      <c r="J105" s="68">
-        <v>40</v>
-      </c>
-      <c r="K105" s="68">
-        <v>40</v>
-      </c>
-      <c r="L105" s="124">
+      <c r="E105" s="181"/>
+      <c r="F105" s="181">
+        <v>40</v>
+      </c>
+      <c r="G105" s="181">
+        <v>40</v>
+      </c>
+      <c r="H105" s="182">
+        <v>40</v>
+      </c>
+      <c r="I105" s="181">
+        <v>40</v>
+      </c>
+      <c r="J105" s="181">
+        <v>40</v>
+      </c>
+      <c r="K105" s="181">
+        <v>40</v>
+      </c>
+      <c r="L105" s="182">
         <f t="shared" si="99"/>
         <v>6</v>
       </c>
@@ -10349,38 +10376,38 @@
       </c>
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A106" s="134">
+      <c r="A106" s="178">
         <v>46312</v>
       </c>
-      <c r="B106" s="40">
+      <c r="B106" s="179">
         <v>100</v>
       </c>
-      <c r="C106" s="125" t="s">
+      <c r="C106" s="180" t="s">
         <v>235</v>
       </c>
-      <c r="D106" s="125" t="s">
+      <c r="D106" s="180" t="s">
         <v>236</v>
       </c>
-      <c r="E106" s="68"/>
-      <c r="F106" s="68">
-        <v>40</v>
-      </c>
-      <c r="G106" s="68">
-        <v>40</v>
-      </c>
-      <c r="H106" s="124">
-        <v>40</v>
-      </c>
-      <c r="I106" s="68">
-        <v>40</v>
-      </c>
-      <c r="J106" s="68">
-        <v>40</v>
-      </c>
-      <c r="K106" s="68">
-        <v>40</v>
-      </c>
-      <c r="L106" s="124">
+      <c r="E106" s="181"/>
+      <c r="F106" s="181">
+        <v>40</v>
+      </c>
+      <c r="G106" s="181">
+        <v>40</v>
+      </c>
+      <c r="H106" s="182">
+        <v>40</v>
+      </c>
+      <c r="I106" s="181">
+        <v>40</v>
+      </c>
+      <c r="J106" s="181">
+        <v>40</v>
+      </c>
+      <c r="K106" s="181">
+        <v>40</v>
+      </c>
+      <c r="L106" s="182">
         <f t="shared" si="99"/>
         <v>6</v>
       </c>
@@ -10430,38 +10457,38 @@
       </c>
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A107" s="134">
+      <c r="A107" s="178">
         <v>46312</v>
       </c>
-      <c r="B107" s="40">
+      <c r="B107" s="179">
         <v>101</v>
       </c>
-      <c r="C107" s="125" t="s">
+      <c r="C107" s="180" t="s">
         <v>237</v>
       </c>
-      <c r="D107" s="125" t="s">
+      <c r="D107" s="180" t="s">
         <v>112</v>
       </c>
-      <c r="E107" s="68"/>
-      <c r="F107" s="68">
+      <c r="E107" s="181"/>
+      <c r="F107" s="181">
         <v>120</v>
       </c>
-      <c r="G107" s="68">
+      <c r="G107" s="181">
         <v>120</v>
       </c>
-      <c r="H107" s="124">
+      <c r="H107" s="182">
         <v>120</v>
       </c>
-      <c r="I107" s="68">
+      <c r="I107" s="181">
         <v>120</v>
       </c>
-      <c r="J107" s="68">
+      <c r="J107" s="181">
         <v>120</v>
       </c>
-      <c r="K107" s="68">
+      <c r="K107" s="181">
         <v>120</v>
       </c>
-      <c r="L107" s="124">
+      <c r="L107" s="182">
         <f t="shared" si="99"/>
         <v>18</v>
       </c>
@@ -10511,38 +10538,38 @@
       </c>
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A108" s="134">
+      <c r="A108" s="178">
         <v>46312</v>
       </c>
-      <c r="B108" s="40">
+      <c r="B108" s="179">
         <v>102</v>
       </c>
-      <c r="C108" s="125" t="s">
+      <c r="C108" s="180" t="s">
         <v>238</v>
       </c>
-      <c r="D108" s="125" t="s">
+      <c r="D108" s="180" t="s">
         <v>239</v>
       </c>
-      <c r="E108" s="68"/>
-      <c r="F108" s="68">
+      <c r="E108" s="181"/>
+      <c r="F108" s="181">
         <v>80</v>
       </c>
-      <c r="G108" s="68">
-        <v>0</v>
-      </c>
-      <c r="H108" s="124">
+      <c r="G108" s="181">
+        <v>0</v>
+      </c>
+      <c r="H108" s="182">
         <v>160</v>
       </c>
-      <c r="I108" s="68">
+      <c r="I108" s="181">
         <v>160</v>
       </c>
-      <c r="J108" s="68">
+      <c r="J108" s="181">
         <v>200</v>
       </c>
-      <c r="K108" s="68">
+      <c r="K108" s="181">
         <v>320</v>
       </c>
-      <c r="L108" s="124">
+      <c r="L108" s="182">
         <f t="shared" si="99"/>
         <v>23</v>
       </c>
@@ -10592,36 +10619,36 @@
       </c>
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A109" s="134">
+      <c r="A109" s="178">
         <v>46312</v>
       </c>
-      <c r="B109" s="40">
+      <c r="B109" s="179">
         <v>103</v>
       </c>
-      <c r="C109" s="125" t="s">
+      <c r="C109" s="180" t="s">
         <v>240</v>
       </c>
-      <c r="D109" s="125" t="s">
+      <c r="D109" s="180" t="s">
         <v>241</v>
       </c>
-      <c r="E109" s="68"/>
-      <c r="F109" s="68"/>
-      <c r="G109" s="68">
+      <c r="E109" s="181"/>
+      <c r="F109" s="181"/>
+      <c r="G109" s="181">
         <v>200</v>
       </c>
-      <c r="H109" s="124">
+      <c r="H109" s="182">
         <v>200</v>
       </c>
-      <c r="I109" s="68">
+      <c r="I109" s="181">
         <v>200</v>
       </c>
-      <c r="J109" s="68">
+      <c r="J109" s="181">
         <v>200</v>
       </c>
-      <c r="K109" s="68">
+      <c r="K109" s="181">
         <v>200</v>
       </c>
-      <c r="L109" s="124">
+      <c r="L109" s="182">
         <f t="shared" si="99"/>
         <v>25</v>
       </c>
@@ -10671,28 +10698,28 @@
       </c>
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A110" s="134">
+      <c r="A110" s="178">
         <v>46312</v>
       </c>
-      <c r="B110" s="40">
+      <c r="B110" s="179">
         <v>104</v>
       </c>
-      <c r="C110" s="125" t="s">
+      <c r="C110" s="180" t="s">
         <v>240</v>
       </c>
-      <c r="D110" s="125" t="s">
+      <c r="D110" s="180" t="s">
         <v>242</v>
       </c>
-      <c r="E110" s="68"/>
-      <c r="F110" s="68"/>
-      <c r="G110" s="68"/>
-      <c r="H110" s="124"/>
-      <c r="I110" s="68"/>
-      <c r="J110" s="68">
+      <c r="E110" s="181"/>
+      <c r="F110" s="181"/>
+      <c r="G110" s="181"/>
+      <c r="H110" s="182"/>
+      <c r="I110" s="181"/>
+      <c r="J110" s="181">
         <v>158</v>
       </c>
-      <c r="K110" s="68"/>
-      <c r="L110" s="124">
+      <c r="K110" s="181"/>
+      <c r="L110" s="182">
         <f t="shared" si="99"/>
         <v>3.95</v>
       </c>
@@ -10742,34 +10769,34 @@
       </c>
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A111" s="134">
+      <c r="A111" s="178">
         <v>46312</v>
       </c>
-      <c r="B111" s="40">
+      <c r="B111" s="179">
         <v>105</v>
       </c>
-      <c r="C111" s="125" t="s">
+      <c r="C111" s="180" t="s">
         <v>189</v>
       </c>
-      <c r="D111" s="125"/>
-      <c r="E111" s="68"/>
-      <c r="F111" s="68"/>
-      <c r="G111" s="68">
+      <c r="D111" s="180"/>
+      <c r="E111" s="181"/>
+      <c r="F111" s="181"/>
+      <c r="G111" s="181">
         <v>80</v>
       </c>
-      <c r="H111" s="124">
+      <c r="H111" s="182">
         <v>160</v>
       </c>
-      <c r="I111" s="68">
+      <c r="I111" s="181">
         <v>80</v>
       </c>
-      <c r="J111" s="68">
+      <c r="J111" s="181">
         <v>80</v>
       </c>
-      <c r="K111" s="68">
+      <c r="K111" s="181">
         <v>120</v>
       </c>
-      <c r="L111" s="124">
+      <c r="L111" s="182">
         <f t="shared" si="99"/>
         <v>13</v>
       </c>
@@ -10819,24 +10846,38 @@
       </c>
     </row>
     <row r="112" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A112" s="71"/>
-      <c r="B112" s="40">
+      <c r="A112" s="134">
+        <v>46314</v>
+      </c>
+      <c r="B112" s="135">
         <v>106</v>
       </c>
-      <c r="C112" s="125"/>
-      <c r="D112" s="125"/>
-      <c r="E112" s="68"/>
-      <c r="F112" s="68"/>
-      <c r="G112" s="68"/>
-      <c r="H112" s="124"/>
-      <c r="I112" s="68"/>
-      <c r="J112" s="68"/>
-      <c r="K112" s="68"/>
+      <c r="C112" s="144" t="s">
+        <v>232</v>
+      </c>
+      <c r="D112" s="144" t="s">
+        <v>243</v>
+      </c>
+      <c r="E112" s="142"/>
+      <c r="F112" s="142"/>
+      <c r="G112" s="142"/>
+      <c r="H112" s="143"/>
+      <c r="I112" s="142">
+        <v>800</v>
+      </c>
+      <c r="J112" s="142">
+        <v>720</v>
+      </c>
+      <c r="K112" s="142">
+        <v>880</v>
+      </c>
       <c r="L112" s="124">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M112" s="138"/>
+        <v>60</v>
+      </c>
+      <c r="M112" s="138">
+        <v>14</v>
+      </c>
       <c r="N112" s="42"/>
       <c r="O112" s="66">
         <f t="shared" si="91"/>
@@ -10844,7 +10885,7 @@
       </c>
       <c r="P112" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q112" s="44" t="e">
         <f t="shared" si="97"/>
@@ -10880,24 +10921,38 @@
       </c>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A113" s="71"/>
-      <c r="B113" s="40">
+      <c r="A113" s="134">
+        <v>46314</v>
+      </c>
+      <c r="B113" s="135">
         <v>107</v>
       </c>
-      <c r="C113" s="125"/>
-      <c r="D113" s="125"/>
-      <c r="E113" s="68"/>
-      <c r="F113" s="68"/>
-      <c r="G113" s="68"/>
-      <c r="H113" s="124"/>
-      <c r="I113" s="68"/>
-      <c r="J113" s="68"/>
-      <c r="K113" s="68"/>
+      <c r="C113" s="144" t="s">
+        <v>244</v>
+      </c>
+      <c r="D113" s="144" t="s">
+        <v>245</v>
+      </c>
+      <c r="E113" s="142"/>
+      <c r="F113" s="142"/>
+      <c r="G113" s="142"/>
+      <c r="H113" s="143"/>
+      <c r="I113" s="142">
+        <v>80</v>
+      </c>
+      <c r="J113" s="142">
+        <v>80</v>
+      </c>
+      <c r="K113" s="142">
+        <v>120</v>
+      </c>
       <c r="L113" s="124">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M113" s="138"/>
+        <v>7</v>
+      </c>
+      <c r="M113" s="138">
+        <v>12</v>
+      </c>
       <c r="N113" s="42"/>
       <c r="O113" s="66">
         <f t="shared" si="91"/>
@@ -10905,7 +10960,7 @@
       </c>
       <c r="P113" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q113" s="44" t="e">
         <f t="shared" si="97"/>
@@ -10941,24 +10996,36 @@
       </c>
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A114" s="71"/>
-      <c r="B114" s="40">
+      <c r="A114" s="134">
+        <v>46314</v>
+      </c>
+      <c r="B114" s="135">
         <v>108</v>
       </c>
-      <c r="C114" s="125"/>
-      <c r="D114" s="125"/>
-      <c r="E114" s="68"/>
-      <c r="F114" s="68"/>
-      <c r="G114" s="68"/>
-      <c r="H114" s="124"/>
-      <c r="I114" s="68"/>
-      <c r="J114" s="68"/>
-      <c r="K114" s="68"/>
+      <c r="C114" s="144" t="s">
+        <v>246</v>
+      </c>
+      <c r="D114" s="144" t="s">
+        <v>247</v>
+      </c>
+      <c r="E114" s="142"/>
+      <c r="F114" s="142"/>
+      <c r="G114" s="142"/>
+      <c r="H114" s="143"/>
+      <c r="I114" s="142">
+        <v>80</v>
+      </c>
+      <c r="J114" s="142"/>
+      <c r="K114" s="142">
+        <v>120</v>
+      </c>
       <c r="L114" s="124">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M114" s="138"/>
+        <v>5</v>
+      </c>
+      <c r="M114" s="138">
+        <v>10</v>
+      </c>
       <c r="N114" s="42"/>
       <c r="O114" s="66">
         <f t="shared" si="91"/>
@@ -10966,7 +11033,7 @@
       </c>
       <c r="P114" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q114" s="44" t="e">
         <f t="shared" si="97"/>
@@ -11002,24 +11069,34 @@
       </c>
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A115" s="71"/>
-      <c r="B115" s="40">
+      <c r="A115" s="134">
+        <v>46314</v>
+      </c>
+      <c r="B115" s="135">
         <v>109</v>
       </c>
-      <c r="C115" s="125"/>
-      <c r="D115" s="125"/>
-      <c r="E115" s="68"/>
-      <c r="F115" s="68"/>
-      <c r="G115" s="68"/>
-      <c r="H115" s="124"/>
-      <c r="I115" s="68"/>
-      <c r="J115" s="68"/>
-      <c r="K115" s="68"/>
+      <c r="C115" s="144" t="s">
+        <v>248</v>
+      </c>
+      <c r="D115" s="144" t="s">
+        <v>121</v>
+      </c>
+      <c r="E115" s="142"/>
+      <c r="F115" s="142"/>
+      <c r="G115" s="142"/>
+      <c r="H115" s="143"/>
+      <c r="I115" s="142"/>
+      <c r="J115" s="142"/>
+      <c r="K115" s="142">
+        <v>40</v>
+      </c>
       <c r="L115" s="124">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M115" s="138"/>
+        <v>1</v>
+      </c>
+      <c r="M115" s="138">
+        <v>14</v>
+      </c>
       <c r="N115" s="42"/>
       <c r="O115" s="66">
         <f t="shared" si="91"/>
@@ -11027,7 +11104,7 @@
       </c>
       <c r="P115" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q115" s="44" t="e">
         <f t="shared" si="97"/>
@@ -11063,32 +11140,52 @@
       </c>
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A116" s="71"/>
-      <c r="B116" s="40">
+      <c r="A116" s="134">
+        <v>46314</v>
+      </c>
+      <c r="B116" s="135">
         <v>110</v>
       </c>
-      <c r="C116" s="125"/>
-      <c r="D116" s="125"/>
-      <c r="E116" s="68"/>
-      <c r="F116" s="68"/>
-      <c r="G116" s="68"/>
-      <c r="H116" s="124"/>
-      <c r="I116" s="68"/>
-      <c r="J116" s="68"/>
-      <c r="K116" s="68"/>
+      <c r="C116" s="144" t="s">
+        <v>249</v>
+      </c>
+      <c r="D116" s="144" t="s">
+        <v>250</v>
+      </c>
+      <c r="E116" s="142"/>
+      <c r="F116" s="142">
+        <v>80</v>
+      </c>
+      <c r="G116" s="142">
+        <v>80</v>
+      </c>
+      <c r="H116" s="143">
+        <v>80</v>
+      </c>
+      <c r="I116" s="142">
+        <v>120</v>
+      </c>
+      <c r="J116" s="142">
+        <v>120</v>
+      </c>
+      <c r="K116" s="142">
+        <v>80</v>
+      </c>
       <c r="L116" s="124">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M116" s="138"/>
+        <v>14</v>
+      </c>
+      <c r="M116" s="138">
+        <v>14</v>
+      </c>
       <c r="N116" s="42"/>
       <c r="O116" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P116" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q116" s="44" t="e">
         <f t="shared" si="97"/>
@@ -11124,32 +11221,52 @@
       </c>
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A117" s="71"/>
-      <c r="B117" s="40">
+      <c r="A117" s="134">
+        <v>46314</v>
+      </c>
+      <c r="B117" s="135">
         <v>111</v>
       </c>
-      <c r="C117" s="125"/>
-      <c r="D117" s="125"/>
-      <c r="E117" s="68"/>
-      <c r="F117" s="68"/>
-      <c r="G117" s="68"/>
-      <c r="H117" s="124"/>
-      <c r="I117" s="68"/>
-      <c r="J117" s="68"/>
-      <c r="K117" s="68"/>
+      <c r="C117" s="144" t="s">
+        <v>116</v>
+      </c>
+      <c r="D117" s="144" t="s">
+        <v>121</v>
+      </c>
+      <c r="E117" s="142"/>
+      <c r="F117" s="142">
+        <v>40</v>
+      </c>
+      <c r="G117" s="142">
+        <v>40</v>
+      </c>
+      <c r="H117" s="143">
+        <v>40</v>
+      </c>
+      <c r="I117" s="142">
+        <v>0</v>
+      </c>
+      <c r="J117" s="142">
+        <v>40</v>
+      </c>
+      <c r="K117" s="142">
+        <v>0</v>
+      </c>
       <c r="L117" s="124">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M117" s="138"/>
+        <v>4</v>
+      </c>
+      <c r="M117" s="138">
+        <v>14</v>
+      </c>
       <c r="N117" s="42"/>
       <c r="O117" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P117" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q117" s="44" t="e">
         <f t="shared" si="97"/>
@@ -11185,32 +11302,52 @@
       </c>
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A118" s="71"/>
-      <c r="B118" s="40">
+      <c r="A118" s="134">
+        <v>46314</v>
+      </c>
+      <c r="B118" s="135">
         <v>112</v>
       </c>
-      <c r="C118" s="125"/>
-      <c r="D118" s="125"/>
-      <c r="E118" s="68"/>
-      <c r="F118" s="68"/>
-      <c r="G118" s="68"/>
-      <c r="H118" s="124"/>
-      <c r="I118" s="68"/>
-      <c r="J118" s="68"/>
-      <c r="K118" s="68"/>
+      <c r="C118" s="144" t="s">
+        <v>116</v>
+      </c>
+      <c r="D118" s="144" t="s">
+        <v>123</v>
+      </c>
+      <c r="E118" s="142"/>
+      <c r="F118" s="142">
+        <v>40</v>
+      </c>
+      <c r="G118" s="142">
+        <v>0</v>
+      </c>
+      <c r="H118" s="143">
+        <v>280</v>
+      </c>
+      <c r="I118" s="142">
+        <v>160</v>
+      </c>
+      <c r="J118" s="142">
+        <v>80</v>
+      </c>
+      <c r="K118" s="142">
+        <v>320</v>
+      </c>
       <c r="L118" s="124">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M118" s="138"/>
+        <v>22</v>
+      </c>
+      <c r="M118" s="138">
+        <v>14</v>
+      </c>
       <c r="N118" s="42"/>
       <c r="O118" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="P118" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q118" s="44" t="e">
         <f t="shared" si="97"/>
@@ -11246,32 +11383,52 @@
       </c>
     </row>
     <row r="119" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A119" s="71"/>
-      <c r="B119" s="40">
+      <c r="A119" s="134">
+        <v>46314</v>
+      </c>
+      <c r="B119" s="135">
         <v>113</v>
       </c>
-      <c r="C119" s="125"/>
-      <c r="D119" s="125"/>
-      <c r="E119" s="68"/>
-      <c r="F119" s="68"/>
-      <c r="G119" s="68"/>
-      <c r="H119" s="124"/>
-      <c r="I119" s="68"/>
-      <c r="J119" s="68"/>
-      <c r="K119" s="68"/>
+      <c r="C119" s="144" t="s">
+        <v>116</v>
+      </c>
+      <c r="D119" s="144" t="s">
+        <v>122</v>
+      </c>
+      <c r="E119" s="142"/>
+      <c r="F119" s="142">
+        <v>40</v>
+      </c>
+      <c r="G119" s="142">
+        <v>0</v>
+      </c>
+      <c r="H119" s="143">
+        <v>400</v>
+      </c>
+      <c r="I119" s="142">
+        <v>120</v>
+      </c>
+      <c r="J119" s="142">
+        <v>320</v>
+      </c>
+      <c r="K119" s="142">
+        <v>320</v>
+      </c>
       <c r="L119" s="124">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M119" s="138"/>
+        <v>30</v>
+      </c>
+      <c r="M119" s="138">
+        <v>14</v>
+      </c>
       <c r="N119" s="42"/>
       <c r="O119" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P119" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Q119" s="44" t="e">
         <f t="shared" si="97"/>
@@ -11307,32 +11464,52 @@
       </c>
     </row>
     <row r="120" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A120" s="71"/>
-      <c r="B120" s="40">
+      <c r="A120" s="134">
+        <v>46314</v>
+      </c>
+      <c r="B120" s="135">
         <v>114</v>
       </c>
-      <c r="C120" s="125"/>
-      <c r="D120" s="125"/>
-      <c r="E120" s="68"/>
-      <c r="F120" s="68"/>
-      <c r="G120" s="68"/>
-      <c r="H120" s="124"/>
-      <c r="I120" s="68"/>
-      <c r="J120" s="68"/>
-      <c r="K120" s="68"/>
+      <c r="C120" s="144" t="s">
+        <v>251</v>
+      </c>
+      <c r="D120" s="144" t="s">
+        <v>245</v>
+      </c>
+      <c r="E120" s="142"/>
+      <c r="F120" s="142">
+        <v>80</v>
+      </c>
+      <c r="G120" s="142">
+        <v>80</v>
+      </c>
+      <c r="H120" s="143">
+        <v>120</v>
+      </c>
+      <c r="I120" s="142">
+        <v>40</v>
+      </c>
+      <c r="J120" s="142">
+        <v>40</v>
+      </c>
+      <c r="K120" s="142">
+        <v>120</v>
+      </c>
       <c r="L120" s="124">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M120" s="138"/>
+        <v>12</v>
+      </c>
+      <c r="M120" s="138">
+        <v>12.5</v>
+      </c>
       <c r="N120" s="42"/>
       <c r="O120" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P120" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q120" s="44" t="e">
         <f t="shared" si="97"/>
@@ -12228,10 +12405,10 @@
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A135" s="71"/>
-      <c r="B135" s="173" t="s">
+      <c r="B135" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="C135" s="173"/>
+      <c r="C135" s="155"/>
       <c r="D135" s="135"/>
       <c r="E135" s="140">
         <f t="shared" ref="E135:K135" si="103">SUM(E6:E63)</f>
@@ -12482,10 +12659,10 @@
       </c>
     </row>
     <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B139" s="161" t="s">
+      <c r="B139" s="167" t="s">
         <v>68</v>
       </c>
-      <c r="C139" s="162"/>
+      <c r="C139" s="168"/>
       <c r="D139" s="128"/>
       <c r="E139" s="76">
         <f>SUM(E137:E138)</f>
@@ -12569,10 +12746,10 @@
       </c>
     </row>
     <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B140" s="150" t="s">
+      <c r="B140" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="C140" s="151"/>
+      <c r="C140" s="157"/>
       <c r="D140" s="129"/>
       <c r="E140" s="77">
         <f>SUM(E135,E139)</f>
@@ -12608,7 +12785,7 @@
       </c>
       <c r="M140" s="56">
         <f>SUM(M5:M139)</f>
-        <v>1665</v>
+        <v>1783.5</v>
       </c>
       <c r="N140" s="54">
         <f t="shared" ref="N140:X140" si="111">SUM(N5:N139)</f>
@@ -12616,11 +12793,11 @@
       </c>
       <c r="O140" s="55">
         <f t="shared" si="111"/>
-        <v>1097.3499999999999</v>
+        <v>1167.3499999999999</v>
       </c>
       <c r="P140" s="57">
         <f t="shared" si="111"/>
-        <v>2690.8999999999996</v>
+        <v>2930.8999999999996</v>
       </c>
       <c r="Q140" s="58" t="e">
         <f t="shared" si="111"/>
@@ -12657,17 +12834,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B135:C135"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B135:C135"/>
   </mergeCells>
   <conditionalFormatting sqref="C48:D62">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12703,25 +12880,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="176" t="s">
+      <c r="C3" s="171" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="177"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="178"/>
-      <c r="H3" s="180" t="s">
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="173"/>
+      <c r="H3" s="175" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="181"/>
-      <c r="K3" s="182" t="s">
+      <c r="I3" s="176"/>
+      <c r="K3" s="177" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="182"/>
-      <c r="M3" s="182"/>
-      <c r="N3" s="182"/>
-      <c r="O3" s="182"/>
-      <c r="P3" s="182"/>
+      <c r="L3" s="177"/>
+      <c r="M3" s="177"/>
+      <c r="N3" s="177"/>
+      <c r="O3" s="177"/>
+      <c r="P3" s="177"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="91"/>
@@ -12767,24 +12944,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="80">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="E5" s="72">
-        <v>948</v>
+        <v>1103</v>
       </c>
       <c r="F5" s="72">
         <v>595</v>
       </c>
       <c r="G5" s="94">
         <f>SUM(D5:F5)</f>
-        <v>1961</v>
+        <v>2160</v>
       </c>
       <c r="H5" s="87">
         <v>10000</v>
       </c>
       <c r="I5" s="88">
         <f>G5-H5</f>
-        <v>-8039</v>
+        <v>-7840</v>
       </c>
       <c r="K5" s="132" t="s">
         <v>1</v>
@@ -12815,11 +12992,11 @@
       </c>
       <c r="D6" s="96">
         <f>D5*40</f>
-        <v>16720</v>
+        <v>18480</v>
       </c>
       <c r="E6" s="96">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>37920</v>
+        <v>44120</v>
       </c>
       <c r="F6" s="96">
         <f t="shared" si="1"/>
@@ -12827,7 +13004,7 @@
       </c>
       <c r="G6" s="97">
         <f>SUM(D6:F6)</f>
-        <v>78440</v>
+        <v>86400</v>
       </c>
       <c r="H6" s="89">
         <f>H5*40</f>
@@ -12835,7 +13012,7 @@
       </c>
       <c r="I6" s="90">
         <f>G6-H6</f>
-        <v>-321560</v>
+        <v>-313600</v>
       </c>
       <c r="K6" s="132" t="s">
         <v>2</v>
@@ -12984,11 +13161,11 @@
       </c>
       <c r="D9" s="98">
         <f>D8-D5</f>
-        <v>-418</v>
+        <v>-462</v>
       </c>
       <c r="E9" s="98">
         <f>E8-E5</f>
-        <v>-948</v>
+        <v>-1103</v>
       </c>
       <c r="K9" s="132" t="s">
         <v>5</v>
@@ -13086,14 +13263,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="179" t="s">
+      <c r="C11" s="174" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="179"/>
-      <c r="F11" s="179" t="s">
+      <c r="D11" s="174"/>
+      <c r="F11" s="174" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="179"/>
+      <c r="G11" s="174"/>
       <c r="K11" s="132" t="s">
         <v>7</v>
       </c>
@@ -13143,7 +13320,7 @@
       </c>
       <c r="G12" s="83">
         <f>D12+G5</f>
-        <v>6161</v>
+        <v>6360</v>
       </c>
       <c r="K12" s="132" t="s">
         <v>11</v>
@@ -13195,12 +13372,12 @@
       </c>
       <c r="G13" s="83">
         <f>G12*40</f>
-        <v>246440</v>
-      </c>
-      <c r="S13" s="174" t="s">
+        <v>254400</v>
+      </c>
+      <c r="S13" s="169" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="174"/>
+      <c r="T13" s="169"/>
       <c r="U13" s="120">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -13307,13 +13484,13 @@
       </c>
     </row>
     <row r="20" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="175" t="s">
+      <c r="D20" s="170" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="175"/>
-      <c r="F20" s="175"/>
-      <c r="G20" s="175"/>
-      <c r="H20" s="175"/>
+      <c r="E20" s="170"/>
+      <c r="F20" s="170"/>
+      <c r="G20" s="170"/>
+      <c r="H20" s="170"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{986760EA-F121-4242-9885-D55841D0EC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C9E68E-0116-443C-9A8F-95DF52B8BBA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="256">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -778,6 +778,18 @@
   </si>
   <si>
     <t xml:space="preserve">Umer Cash N Carry </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HA Mega Mart </t>
+  </si>
+  <si>
+    <t>Fatah Gher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vip </t>
+  </si>
+  <si>
+    <t>Sadar Bazar</t>
   </si>
 </sst>
 </file>
@@ -2023,6 +2035,45 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2054,45 +2105,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2725,13 +2737,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="145">
+      <c r="B1" s="158">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
-      </c>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
+        <v>46316</v>
+      </c>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2753,10 +2765,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="166" t="s">
+      <c r="A2" s="155" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="146" t="s">
+      <c r="B2" s="159" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2786,13 +2798,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="158"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="160"/>
-      <c r="O2" s="161" t="s">
+      <c r="L2" s="147"/>
+      <c r="M2" s="148"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="150" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="162"/>
+      <c r="P2" s="151"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2811,8 +2823,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="166"/>
-      <c r="B3" s="147"/>
+      <c r="A3" s="155"/>
+      <c r="B3" s="160"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2840,29 +2852,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="163" t="s">
+      <c r="L3" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="164"/>
-      <c r="N3" s="165"/>
+      <c r="M3" s="153"/>
+      <c r="N3" s="154"/>
       <c r="O3" s="64"/>
       <c r="P3" s="65"/>
-      <c r="Q3" s="149" t="s">
+      <c r="Q3" s="162" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="150"/>
-      <c r="S3" s="150"/>
-      <c r="T3" s="151"/>
-      <c r="U3" s="152" t="s">
+      <c r="R3" s="163"/>
+      <c r="S3" s="163"/>
+      <c r="T3" s="164"/>
+      <c r="U3" s="165" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="153"/>
-      <c r="W3" s="153"/>
-      <c r="X3" s="154"/>
+      <c r="V3" s="166"/>
+      <c r="W3" s="166"/>
+      <c r="X3" s="167"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="166"/>
-      <c r="B4" s="148"/>
+      <c r="A4" s="155"/>
+      <c r="B4" s="161"/>
       <c r="C4" s="130" t="s">
         <v>90</v>
       </c>
@@ -9517,34 +9529,34 @@
       </c>
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A95" s="178">
+      <c r="A95" s="71">
         <v>46310</v>
       </c>
-      <c r="B95" s="179">
+      <c r="B95" s="40">
         <v>89</v>
       </c>
-      <c r="C95" s="180" t="s">
+      <c r="C95" s="125" t="s">
         <v>220</v>
       </c>
-      <c r="D95" s="180" t="s">
+      <c r="D95" s="125" t="s">
         <v>221</v>
       </c>
-      <c r="E95" s="181"/>
-      <c r="F95" s="181">
+      <c r="E95" s="68"/>
+      <c r="F95" s="68">
         <v>-2</v>
       </c>
-      <c r="G95" s="181">
+      <c r="G95" s="68">
         <v>-2</v>
       </c>
-      <c r="H95" s="182"/>
-      <c r="I95" s="181">
+      <c r="H95" s="124"/>
+      <c r="I95" s="68">
         <v>200</v>
       </c>
-      <c r="J95" s="181">
+      <c r="J95" s="68">
         <v>200</v>
       </c>
-      <c r="K95" s="181"/>
-      <c r="L95" s="182">
+      <c r="K95" s="68"/>
+      <c r="L95" s="124">
         <f t="shared" si="84"/>
         <v>9.9</v>
       </c>
@@ -9594,28 +9606,28 @@
       </c>
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A96" s="178">
+      <c r="A96" s="71">
         <v>46310</v>
       </c>
-      <c r="B96" s="179">
+      <c r="B96" s="40">
         <v>90</v>
       </c>
-      <c r="C96" s="180" t="s">
+      <c r="C96" s="125" t="s">
         <v>222</v>
       </c>
-      <c r="D96" s="180" t="s">
+      <c r="D96" s="125" t="s">
         <v>223</v>
       </c>
-      <c r="E96" s="181"/>
-      <c r="F96" s="181"/>
-      <c r="G96" s="181"/>
-      <c r="H96" s="182"/>
-      <c r="I96" s="181"/>
-      <c r="J96" s="181">
+      <c r="E96" s="68"/>
+      <c r="F96" s="68"/>
+      <c r="G96" s="68"/>
+      <c r="H96" s="124"/>
+      <c r="I96" s="68"/>
+      <c r="J96" s="68">
         <v>158</v>
       </c>
-      <c r="K96" s="181"/>
-      <c r="L96" s="182">
+      <c r="K96" s="68"/>
+      <c r="L96" s="124">
         <f t="shared" si="84"/>
         <v>3.95</v>
       </c>
@@ -9665,38 +9677,38 @@
       </c>
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A97" s="178">
+      <c r="A97" s="71">
         <v>46310</v>
       </c>
-      <c r="B97" s="179">
+      <c r="B97" s="40">
         <v>91</v>
       </c>
-      <c r="C97" s="180" t="s">
+      <c r="C97" s="125" t="s">
         <v>224</v>
       </c>
-      <c r="D97" s="180" t="s">
+      <c r="D97" s="125" t="s">
         <v>225</v>
       </c>
-      <c r="E97" s="181"/>
-      <c r="F97" s="181">
+      <c r="E97" s="68"/>
+      <c r="F97" s="68">
         <v>398</v>
       </c>
-      <c r="G97" s="181">
+      <c r="G97" s="68">
         <v>399</v>
       </c>
-      <c r="H97" s="182">
+      <c r="H97" s="124">
         <v>800</v>
       </c>
-      <c r="I97" s="181">
+      <c r="I97" s="68">
         <v>1199</v>
       </c>
-      <c r="J97" s="181">
+      <c r="J97" s="68">
         <v>799</v>
       </c>
-      <c r="K97" s="181">
+      <c r="K97" s="68">
         <v>1998</v>
       </c>
-      <c r="L97" s="182">
+      <c r="L97" s="124">
         <f t="shared" si="84"/>
         <v>139.82499999999999</v>
       </c>
@@ -9746,38 +9758,38 @@
       </c>
     </row>
     <row r="98" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A98" s="178">
+      <c r="A98" s="71">
         <v>46310</v>
       </c>
-      <c r="B98" s="179">
+      <c r="B98" s="40">
         <v>92</v>
       </c>
-      <c r="C98" s="180" t="s">
+      <c r="C98" s="125" t="s">
         <v>226</v>
       </c>
-      <c r="D98" s="180" t="s">
+      <c r="D98" s="125" t="s">
         <v>156</v>
       </c>
-      <c r="E98" s="181"/>
-      <c r="F98" s="181">
+      <c r="E98" s="68"/>
+      <c r="F98" s="68">
         <v>120</v>
       </c>
-      <c r="G98" s="181">
+      <c r="G98" s="68">
         <v>120</v>
       </c>
-      <c r="H98" s="182">
+      <c r="H98" s="124">
         <v>120</v>
       </c>
-      <c r="I98" s="181">
+      <c r="I98" s="68">
         <v>120</v>
       </c>
-      <c r="J98" s="181">
+      <c r="J98" s="68">
         <v>120</v>
       </c>
-      <c r="K98" s="181">
+      <c r="K98" s="68">
         <v>120</v>
       </c>
-      <c r="L98" s="182">
+      <c r="L98" s="124">
         <f t="shared" si="84"/>
         <v>18</v>
       </c>
@@ -9827,38 +9839,38 @@
       </c>
     </row>
     <row r="99" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A99" s="178">
+      <c r="A99" s="71">
         <v>46310</v>
       </c>
-      <c r="B99" s="179">
+      <c r="B99" s="40">
         <v>93</v>
       </c>
-      <c r="C99" s="180" t="s">
+      <c r="C99" s="125" t="s">
         <v>227</v>
       </c>
-      <c r="D99" s="180" t="s">
+      <c r="D99" s="125" t="s">
         <v>221</v>
       </c>
-      <c r="E99" s="181"/>
-      <c r="F99" s="181">
-        <v>40</v>
-      </c>
-      <c r="G99" s="181">
-        <v>40</v>
-      </c>
-      <c r="H99" s="182">
-        <v>40</v>
-      </c>
-      <c r="I99" s="181">
-        <v>40</v>
-      </c>
-      <c r="J99" s="181">
-        <v>40</v>
-      </c>
-      <c r="K99" s="181">
-        <v>40</v>
-      </c>
-      <c r="L99" s="182">
+      <c r="E99" s="68"/>
+      <c r="F99" s="68">
+        <v>40</v>
+      </c>
+      <c r="G99" s="68">
+        <v>40</v>
+      </c>
+      <c r="H99" s="124">
+        <v>40</v>
+      </c>
+      <c r="I99" s="68">
+        <v>40</v>
+      </c>
+      <c r="J99" s="68">
+        <v>40</v>
+      </c>
+      <c r="K99" s="68">
+        <v>40</v>
+      </c>
+      <c r="L99" s="124">
         <f t="shared" si="84"/>
         <v>6</v>
       </c>
@@ -9908,38 +9920,38 @@
       </c>
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A100" s="178">
+      <c r="A100" s="71">
         <v>46310</v>
       </c>
-      <c r="B100" s="179">
+      <c r="B100" s="40">
         <v>94</v>
       </c>
-      <c r="C100" s="180" t="s">
+      <c r="C100" s="125" t="s">
         <v>228</v>
       </c>
-      <c r="D100" s="180" t="s">
+      <c r="D100" s="125" t="s">
         <v>229</v>
       </c>
-      <c r="E100" s="181"/>
-      <c r="F100" s="181">
+      <c r="E100" s="68"/>
+      <c r="F100" s="68">
         <v>120</v>
       </c>
-      <c r="G100" s="181">
+      <c r="G100" s="68">
         <v>120</v>
       </c>
-      <c r="H100" s="182">
+      <c r="H100" s="124">
         <v>120</v>
       </c>
-      <c r="I100" s="181">
+      <c r="I100" s="68">
         <v>120</v>
       </c>
-      <c r="J100" s="181">
+      <c r="J100" s="68">
         <v>120</v>
       </c>
-      <c r="K100" s="181">
+      <c r="K100" s="68">
         <v>120</v>
       </c>
-      <c r="L100" s="182">
+      <c r="L100" s="124">
         <f t="shared" si="84"/>
         <v>18</v>
       </c>
@@ -9989,28 +10001,28 @@
       </c>
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A101" s="178">
+      <c r="A101" s="71">
         <v>46310</v>
       </c>
-      <c r="B101" s="179">
+      <c r="B101" s="40">
         <v>95</v>
       </c>
-      <c r="C101" s="180" t="s">
+      <c r="C101" s="125" t="s">
         <v>230</v>
       </c>
-      <c r="D101" s="180"/>
-      <c r="E101" s="181"/>
-      <c r="F101" s="181"/>
-      <c r="G101" s="181"/>
-      <c r="H101" s="182">
+      <c r="D101" s="125"/>
+      <c r="E101" s="68"/>
+      <c r="F101" s="68"/>
+      <c r="G101" s="68"/>
+      <c r="H101" s="124">
         <v>2</v>
       </c>
-      <c r="I101" s="181">
+      <c r="I101" s="68">
         <v>2</v>
       </c>
-      <c r="J101" s="181"/>
-      <c r="K101" s="181"/>
-      <c r="L101" s="182">
+      <c r="J101" s="68"/>
+      <c r="K101" s="68"/>
+      <c r="L101" s="124">
         <f t="shared" si="84"/>
         <v>0.1</v>
       </c>
@@ -10060,38 +10072,38 @@
       </c>
     </row>
     <row r="102" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A102" s="178">
+      <c r="A102" s="71">
         <v>46310</v>
       </c>
-      <c r="B102" s="179">
+      <c r="B102" s="40">
         <v>96</v>
       </c>
-      <c r="C102" s="180" t="s">
+      <c r="C102" s="125" t="s">
         <v>211</v>
       </c>
-      <c r="D102" s="180" t="s">
+      <c r="D102" s="125" t="s">
         <v>212</v>
       </c>
-      <c r="E102" s="181"/>
-      <c r="F102" s="181">
+      <c r="E102" s="68"/>
+      <c r="F102" s="68">
         <v>200</v>
       </c>
-      <c r="G102" s="181">
+      <c r="G102" s="68">
         <v>200</v>
       </c>
-      <c r="H102" s="182">
+      <c r="H102" s="124">
         <v>200</v>
       </c>
-      <c r="I102" s="181">
+      <c r="I102" s="68">
         <v>2800</v>
       </c>
-      <c r="J102" s="181">
+      <c r="J102" s="68">
         <v>2400</v>
       </c>
-      <c r="K102" s="181">
+      <c r="K102" s="68">
         <v>2800</v>
       </c>
-      <c r="L102" s="182">
+      <c r="L102" s="124">
         <f t="shared" si="84"/>
         <v>215</v>
       </c>
@@ -10141,38 +10153,38 @@
       </c>
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A103" s="178">
+      <c r="A103" s="71">
         <v>46312</v>
       </c>
-      <c r="B103" s="179">
+      <c r="B103" s="40">
         <v>97</v>
       </c>
-      <c r="C103" s="180" t="s">
+      <c r="C103" s="125" t="s">
         <v>23</v>
       </c>
-      <c r="D103" s="180" t="s">
+      <c r="D103" s="125" t="s">
         <v>231</v>
       </c>
-      <c r="E103" s="181"/>
-      <c r="F103" s="181">
+      <c r="E103" s="68"/>
+      <c r="F103" s="68">
         <v>80</v>
       </c>
-      <c r="G103" s="181">
+      <c r="G103" s="68">
         <v>120</v>
       </c>
-      <c r="H103" s="182">
+      <c r="H103" s="124">
         <v>80</v>
       </c>
-      <c r="I103" s="181">
+      <c r="I103" s="68">
         <v>120</v>
       </c>
-      <c r="J103" s="181">
+      <c r="J103" s="68">
         <v>80</v>
       </c>
-      <c r="K103" s="181">
+      <c r="K103" s="68">
         <v>280</v>
       </c>
-      <c r="L103" s="182">
+      <c r="L103" s="124">
         <f t="shared" ref="L103:L134" si="99">SUM(E103:K103)/40</f>
         <v>19</v>
       </c>
@@ -10222,30 +10234,30 @@
       </c>
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A104" s="178">
+      <c r="A104" s="71">
         <v>46312</v>
       </c>
-      <c r="B104" s="179">
+      <c r="B104" s="40">
         <v>98</v>
       </c>
-      <c r="C104" s="180" t="s">
+      <c r="C104" s="125" t="s">
         <v>232</v>
       </c>
-      <c r="D104" s="180"/>
-      <c r="E104" s="181"/>
-      <c r="F104" s="181"/>
-      <c r="G104" s="181"/>
-      <c r="H104" s="182"/>
-      <c r="I104" s="181">
+      <c r="D104" s="125"/>
+      <c r="E104" s="68"/>
+      <c r="F104" s="68"/>
+      <c r="G104" s="68"/>
+      <c r="H104" s="124"/>
+      <c r="I104" s="68">
         <v>800</v>
       </c>
-      <c r="J104" s="181">
+      <c r="J104" s="68">
         <v>720</v>
       </c>
-      <c r="K104" s="181">
+      <c r="K104" s="68">
         <v>880</v>
       </c>
-      <c r="L104" s="182">
+      <c r="L104" s="124">
         <f t="shared" si="99"/>
         <v>60</v>
       </c>
@@ -10295,38 +10307,38 @@
       </c>
     </row>
     <row r="105" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A105" s="178">
+      <c r="A105" s="71">
         <v>46312</v>
       </c>
-      <c r="B105" s="179">
+      <c r="B105" s="40">
         <v>99</v>
       </c>
-      <c r="C105" s="180" t="s">
+      <c r="C105" s="125" t="s">
         <v>233</v>
       </c>
-      <c r="D105" s="180" t="s">
+      <c r="D105" s="125" t="s">
         <v>234</v>
       </c>
-      <c r="E105" s="181"/>
-      <c r="F105" s="181">
-        <v>40</v>
-      </c>
-      <c r="G105" s="181">
-        <v>40</v>
-      </c>
-      <c r="H105" s="182">
-        <v>40</v>
-      </c>
-      <c r="I105" s="181">
-        <v>40</v>
-      </c>
-      <c r="J105" s="181">
-        <v>40</v>
-      </c>
-      <c r="K105" s="181">
-        <v>40</v>
-      </c>
-      <c r="L105" s="182">
+      <c r="E105" s="68"/>
+      <c r="F105" s="68">
+        <v>40</v>
+      </c>
+      <c r="G105" s="68">
+        <v>40</v>
+      </c>
+      <c r="H105" s="124">
+        <v>40</v>
+      </c>
+      <c r="I105" s="68">
+        <v>40</v>
+      </c>
+      <c r="J105" s="68">
+        <v>40</v>
+      </c>
+      <c r="K105" s="68">
+        <v>40</v>
+      </c>
+      <c r="L105" s="124">
         <f t="shared" si="99"/>
         <v>6</v>
       </c>
@@ -10376,38 +10388,38 @@
       </c>
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A106" s="178">
+      <c r="A106" s="71">
         <v>46312</v>
       </c>
-      <c r="B106" s="179">
+      <c r="B106" s="40">
         <v>100</v>
       </c>
-      <c r="C106" s="180" t="s">
+      <c r="C106" s="125" t="s">
         <v>235</v>
       </c>
-      <c r="D106" s="180" t="s">
+      <c r="D106" s="125" t="s">
         <v>236</v>
       </c>
-      <c r="E106" s="181"/>
-      <c r="F106" s="181">
-        <v>40</v>
-      </c>
-      <c r="G106" s="181">
-        <v>40</v>
-      </c>
-      <c r="H106" s="182">
-        <v>40</v>
-      </c>
-      <c r="I106" s="181">
-        <v>40</v>
-      </c>
-      <c r="J106" s="181">
-        <v>40</v>
-      </c>
-      <c r="K106" s="181">
-        <v>40</v>
-      </c>
-      <c r="L106" s="182">
+      <c r="E106" s="68"/>
+      <c r="F106" s="68">
+        <v>40</v>
+      </c>
+      <c r="G106" s="68">
+        <v>40</v>
+      </c>
+      <c r="H106" s="124">
+        <v>40</v>
+      </c>
+      <c r="I106" s="68">
+        <v>40</v>
+      </c>
+      <c r="J106" s="68">
+        <v>40</v>
+      </c>
+      <c r="K106" s="68">
+        <v>40</v>
+      </c>
+      <c r="L106" s="124">
         <f t="shared" si="99"/>
         <v>6</v>
       </c>
@@ -10457,38 +10469,38 @@
       </c>
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A107" s="178">
+      <c r="A107" s="71">
         <v>46312</v>
       </c>
-      <c r="B107" s="179">
+      <c r="B107" s="40">
         <v>101</v>
       </c>
-      <c r="C107" s="180" t="s">
+      <c r="C107" s="125" t="s">
         <v>237</v>
       </c>
-      <c r="D107" s="180" t="s">
+      <c r="D107" s="125" t="s">
         <v>112</v>
       </c>
-      <c r="E107" s="181"/>
-      <c r="F107" s="181">
+      <c r="E107" s="68"/>
+      <c r="F107" s="68">
         <v>120</v>
       </c>
-      <c r="G107" s="181">
+      <c r="G107" s="68">
         <v>120</v>
       </c>
-      <c r="H107" s="182">
+      <c r="H107" s="124">
         <v>120</v>
       </c>
-      <c r="I107" s="181">
+      <c r="I107" s="68">
         <v>120</v>
       </c>
-      <c r="J107" s="181">
+      <c r="J107" s="68">
         <v>120</v>
       </c>
-      <c r="K107" s="181">
+      <c r="K107" s="68">
         <v>120</v>
       </c>
-      <c r="L107" s="182">
+      <c r="L107" s="124">
         <f t="shared" si="99"/>
         <v>18</v>
       </c>
@@ -10538,38 +10550,38 @@
       </c>
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A108" s="178">
+      <c r="A108" s="71">
         <v>46312</v>
       </c>
-      <c r="B108" s="179">
+      <c r="B108" s="40">
         <v>102</v>
       </c>
-      <c r="C108" s="180" t="s">
+      <c r="C108" s="125" t="s">
         <v>238</v>
       </c>
-      <c r="D108" s="180" t="s">
+      <c r="D108" s="125" t="s">
         <v>239</v>
       </c>
-      <c r="E108" s="181"/>
-      <c r="F108" s="181">
+      <c r="E108" s="68"/>
+      <c r="F108" s="68">
         <v>80</v>
       </c>
-      <c r="G108" s="181">
-        <v>0</v>
-      </c>
-      <c r="H108" s="182">
+      <c r="G108" s="68">
+        <v>0</v>
+      </c>
+      <c r="H108" s="124">
         <v>160</v>
       </c>
-      <c r="I108" s="181">
+      <c r="I108" s="68">
         <v>160</v>
       </c>
-      <c r="J108" s="181">
+      <c r="J108" s="68">
         <v>200</v>
       </c>
-      <c r="K108" s="181">
+      <c r="K108" s="68">
         <v>320</v>
       </c>
-      <c r="L108" s="182">
+      <c r="L108" s="124">
         <f t="shared" si="99"/>
         <v>23</v>
       </c>
@@ -10619,36 +10631,36 @@
       </c>
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A109" s="178">
+      <c r="A109" s="71">
         <v>46312</v>
       </c>
-      <c r="B109" s="179">
+      <c r="B109" s="40">
         <v>103</v>
       </c>
-      <c r="C109" s="180" t="s">
+      <c r="C109" s="125" t="s">
         <v>240</v>
       </c>
-      <c r="D109" s="180" t="s">
+      <c r="D109" s="125" t="s">
         <v>241</v>
       </c>
-      <c r="E109" s="181"/>
-      <c r="F109" s="181"/>
-      <c r="G109" s="181">
+      <c r="E109" s="68"/>
+      <c r="F109" s="68"/>
+      <c r="G109" s="68">
         <v>200</v>
       </c>
-      <c r="H109" s="182">
+      <c r="H109" s="124">
         <v>200</v>
       </c>
-      <c r="I109" s="181">
+      <c r="I109" s="68">
         <v>200</v>
       </c>
-      <c r="J109" s="181">
+      <c r="J109" s="68">
         <v>200</v>
       </c>
-      <c r="K109" s="181">
+      <c r="K109" s="68">
         <v>200</v>
       </c>
-      <c r="L109" s="182">
+      <c r="L109" s="124">
         <f t="shared" si="99"/>
         <v>25</v>
       </c>
@@ -10698,28 +10710,28 @@
       </c>
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A110" s="178">
+      <c r="A110" s="71">
         <v>46312</v>
       </c>
-      <c r="B110" s="179">
+      <c r="B110" s="40">
         <v>104</v>
       </c>
-      <c r="C110" s="180" t="s">
+      <c r="C110" s="125" t="s">
         <v>240</v>
       </c>
-      <c r="D110" s="180" t="s">
+      <c r="D110" s="125" t="s">
         <v>242</v>
       </c>
-      <c r="E110" s="181"/>
-      <c r="F110" s="181"/>
-      <c r="G110" s="181"/>
-      <c r="H110" s="182"/>
-      <c r="I110" s="181"/>
-      <c r="J110" s="181">
+      <c r="E110" s="68"/>
+      <c r="F110" s="68"/>
+      <c r="G110" s="68"/>
+      <c r="H110" s="124"/>
+      <c r="I110" s="68"/>
+      <c r="J110" s="68">
         <v>158</v>
       </c>
-      <c r="K110" s="181"/>
-      <c r="L110" s="182">
+      <c r="K110" s="68"/>
+      <c r="L110" s="124">
         <f t="shared" si="99"/>
         <v>3.95</v>
       </c>
@@ -10769,34 +10781,34 @@
       </c>
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A111" s="178">
+      <c r="A111" s="71">
         <v>46312</v>
       </c>
-      <c r="B111" s="179">
+      <c r="B111" s="40">
         <v>105</v>
       </c>
-      <c r="C111" s="180" t="s">
+      <c r="C111" s="125" t="s">
         <v>189</v>
       </c>
-      <c r="D111" s="180"/>
-      <c r="E111" s="181"/>
-      <c r="F111" s="181"/>
-      <c r="G111" s="181">
+      <c r="D111" s="125"/>
+      <c r="E111" s="68"/>
+      <c r="F111" s="68"/>
+      <c r="G111" s="68">
         <v>80</v>
       </c>
-      <c r="H111" s="182">
+      <c r="H111" s="124">
         <v>160</v>
       </c>
-      <c r="I111" s="181">
+      <c r="I111" s="68">
         <v>80</v>
       </c>
-      <c r="J111" s="181">
+      <c r="J111" s="68">
         <v>80</v>
       </c>
-      <c r="K111" s="181">
+      <c r="K111" s="68">
         <v>120</v>
       </c>
-      <c r="L111" s="182">
+      <c r="L111" s="124">
         <f t="shared" si="99"/>
         <v>13</v>
       </c>
@@ -10846,29 +10858,29 @@
       </c>
     </row>
     <row r="112" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A112" s="134">
+      <c r="A112" s="178">
         <v>46314</v>
       </c>
-      <c r="B112" s="135">
+      <c r="B112" s="179">
         <v>106</v>
       </c>
-      <c r="C112" s="144" t="s">
+      <c r="C112" s="180" t="s">
         <v>232</v>
       </c>
-      <c r="D112" s="144" t="s">
+      <c r="D112" s="180" t="s">
         <v>243</v>
       </c>
-      <c r="E112" s="142"/>
-      <c r="F112" s="142"/>
-      <c r="G112" s="142"/>
-      <c r="H112" s="143"/>
-      <c r="I112" s="142">
+      <c r="E112" s="181"/>
+      <c r="F112" s="181"/>
+      <c r="G112" s="181"/>
+      <c r="H112" s="182"/>
+      <c r="I112" s="181">
         <v>800</v>
       </c>
-      <c r="J112" s="142">
+      <c r="J112" s="181">
         <v>720</v>
       </c>
-      <c r="K112" s="142">
+      <c r="K112" s="181">
         <v>880</v>
       </c>
       <c r="L112" s="124">
@@ -10921,29 +10933,29 @@
       </c>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A113" s="134">
+      <c r="A113" s="178">
         <v>46314</v>
       </c>
-      <c r="B113" s="135">
+      <c r="B113" s="179">
         <v>107</v>
       </c>
-      <c r="C113" s="144" t="s">
+      <c r="C113" s="180" t="s">
         <v>244</v>
       </c>
-      <c r="D113" s="144" t="s">
+      <c r="D113" s="180" t="s">
         <v>245</v>
       </c>
-      <c r="E113" s="142"/>
-      <c r="F113" s="142"/>
-      <c r="G113" s="142"/>
-      <c r="H113" s="143"/>
-      <c r="I113" s="142">
+      <c r="E113" s="181"/>
+      <c r="F113" s="181"/>
+      <c r="G113" s="181"/>
+      <c r="H113" s="182"/>
+      <c r="I113" s="181">
         <v>80</v>
       </c>
-      <c r="J113" s="142">
+      <c r="J113" s="181">
         <v>80</v>
       </c>
-      <c r="K113" s="142">
+      <c r="K113" s="181">
         <v>120</v>
       </c>
       <c r="L113" s="124">
@@ -10996,27 +11008,27 @@
       </c>
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A114" s="134">
+      <c r="A114" s="178">
         <v>46314</v>
       </c>
-      <c r="B114" s="135">
+      <c r="B114" s="179">
         <v>108</v>
       </c>
-      <c r="C114" s="144" t="s">
+      <c r="C114" s="180" t="s">
         <v>246</v>
       </c>
-      <c r="D114" s="144" t="s">
+      <c r="D114" s="180" t="s">
         <v>247</v>
       </c>
-      <c r="E114" s="142"/>
-      <c r="F114" s="142"/>
-      <c r="G114" s="142"/>
-      <c r="H114" s="143"/>
-      <c r="I114" s="142">
+      <c r="E114" s="181"/>
+      <c r="F114" s="181"/>
+      <c r="G114" s="181"/>
+      <c r="H114" s="182"/>
+      <c r="I114" s="181">
         <v>80</v>
       </c>
-      <c r="J114" s="142"/>
-      <c r="K114" s="142">
+      <c r="J114" s="181"/>
+      <c r="K114" s="181">
         <v>120</v>
       </c>
       <c r="L114" s="124">
@@ -11069,25 +11081,25 @@
       </c>
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A115" s="134">
+      <c r="A115" s="178">
         <v>46314</v>
       </c>
-      <c r="B115" s="135">
+      <c r="B115" s="179">
         <v>109</v>
       </c>
-      <c r="C115" s="144" t="s">
+      <c r="C115" s="180" t="s">
         <v>248</v>
       </c>
-      <c r="D115" s="144" t="s">
+      <c r="D115" s="180" t="s">
         <v>121</v>
       </c>
-      <c r="E115" s="142"/>
-      <c r="F115" s="142"/>
-      <c r="G115" s="142"/>
-      <c r="H115" s="143"/>
-      <c r="I115" s="142"/>
-      <c r="J115" s="142"/>
-      <c r="K115" s="142">
+      <c r="E115" s="181"/>
+      <c r="F115" s="181"/>
+      <c r="G115" s="181"/>
+      <c r="H115" s="182"/>
+      <c r="I115" s="181"/>
+      <c r="J115" s="181"/>
+      <c r="K115" s="181">
         <v>40</v>
       </c>
       <c r="L115" s="124">
@@ -11140,35 +11152,35 @@
       </c>
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A116" s="134">
+      <c r="A116" s="178">
         <v>46314</v>
       </c>
-      <c r="B116" s="135">
+      <c r="B116" s="179">
         <v>110</v>
       </c>
-      <c r="C116" s="144" t="s">
+      <c r="C116" s="180" t="s">
         <v>249</v>
       </c>
-      <c r="D116" s="144" t="s">
+      <c r="D116" s="180" t="s">
         <v>250</v>
       </c>
-      <c r="E116" s="142"/>
-      <c r="F116" s="142">
+      <c r="E116" s="181"/>
+      <c r="F116" s="181">
         <v>80</v>
       </c>
-      <c r="G116" s="142">
+      <c r="G116" s="181">
         <v>80</v>
       </c>
-      <c r="H116" s="143">
+      <c r="H116" s="182">
         <v>80</v>
       </c>
-      <c r="I116" s="142">
+      <c r="I116" s="181">
         <v>120</v>
       </c>
-      <c r="J116" s="142">
+      <c r="J116" s="181">
         <v>120</v>
       </c>
-      <c r="K116" s="142">
+      <c r="K116" s="181">
         <v>80</v>
       </c>
       <c r="L116" s="124">
@@ -11221,35 +11233,35 @@
       </c>
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A117" s="134">
+      <c r="A117" s="178">
         <v>46314</v>
       </c>
-      <c r="B117" s="135">
+      <c r="B117" s="179">
         <v>111</v>
       </c>
-      <c r="C117" s="144" t="s">
+      <c r="C117" s="180" t="s">
         <v>116</v>
       </c>
-      <c r="D117" s="144" t="s">
+      <c r="D117" s="180" t="s">
         <v>121</v>
       </c>
-      <c r="E117" s="142"/>
-      <c r="F117" s="142">
-        <v>40</v>
-      </c>
-      <c r="G117" s="142">
-        <v>40</v>
-      </c>
-      <c r="H117" s="143">
-        <v>40</v>
-      </c>
-      <c r="I117" s="142">
-        <v>0</v>
-      </c>
-      <c r="J117" s="142">
-        <v>40</v>
-      </c>
-      <c r="K117" s="142">
+      <c r="E117" s="181"/>
+      <c r="F117" s="181">
+        <v>40</v>
+      </c>
+      <c r="G117" s="181">
+        <v>40</v>
+      </c>
+      <c r="H117" s="182">
+        <v>40</v>
+      </c>
+      <c r="I117" s="181">
+        <v>0</v>
+      </c>
+      <c r="J117" s="181">
+        <v>40</v>
+      </c>
+      <c r="K117" s="181">
         <v>0</v>
       </c>
       <c r="L117" s="124">
@@ -11302,35 +11314,35 @@
       </c>
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A118" s="134">
+      <c r="A118" s="178">
         <v>46314</v>
       </c>
-      <c r="B118" s="135">
+      <c r="B118" s="179">
         <v>112</v>
       </c>
-      <c r="C118" s="144" t="s">
+      <c r="C118" s="180" t="s">
         <v>116</v>
       </c>
-      <c r="D118" s="144" t="s">
+      <c r="D118" s="180" t="s">
         <v>123</v>
       </c>
-      <c r="E118" s="142"/>
-      <c r="F118" s="142">
-        <v>40</v>
-      </c>
-      <c r="G118" s="142">
-        <v>0</v>
-      </c>
-      <c r="H118" s="143">
+      <c r="E118" s="181"/>
+      <c r="F118" s="181">
+        <v>40</v>
+      </c>
+      <c r="G118" s="181">
+        <v>0</v>
+      </c>
+      <c r="H118" s="182">
         <v>280</v>
       </c>
-      <c r="I118" s="142">
+      <c r="I118" s="181">
         <v>160</v>
       </c>
-      <c r="J118" s="142">
+      <c r="J118" s="181">
         <v>80</v>
       </c>
-      <c r="K118" s="142">
+      <c r="K118" s="181">
         <v>320</v>
       </c>
       <c r="L118" s="124">
@@ -11383,35 +11395,35 @@
       </c>
     </row>
     <row r="119" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A119" s="134">
+      <c r="A119" s="178">
         <v>46314</v>
       </c>
-      <c r="B119" s="135">
+      <c r="B119" s="179">
         <v>113</v>
       </c>
-      <c r="C119" s="144" t="s">
+      <c r="C119" s="180" t="s">
         <v>116</v>
       </c>
-      <c r="D119" s="144" t="s">
+      <c r="D119" s="180" t="s">
         <v>122</v>
       </c>
-      <c r="E119" s="142"/>
-      <c r="F119" s="142">
-        <v>40</v>
-      </c>
-      <c r="G119" s="142">
-        <v>0</v>
-      </c>
-      <c r="H119" s="143">
+      <c r="E119" s="181"/>
+      <c r="F119" s="181">
+        <v>40</v>
+      </c>
+      <c r="G119" s="181">
+        <v>0</v>
+      </c>
+      <c r="H119" s="182">
         <v>400</v>
       </c>
-      <c r="I119" s="142">
+      <c r="I119" s="181">
         <v>120</v>
       </c>
-      <c r="J119" s="142">
+      <c r="J119" s="181">
         <v>320</v>
       </c>
-      <c r="K119" s="142">
+      <c r="K119" s="181">
         <v>320</v>
       </c>
       <c r="L119" s="124">
@@ -11464,35 +11476,35 @@
       </c>
     </row>
     <row r="120" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A120" s="134">
+      <c r="A120" s="178">
         <v>46314</v>
       </c>
-      <c r="B120" s="135">
+      <c r="B120" s="179">
         <v>114</v>
       </c>
-      <c r="C120" s="144" t="s">
+      <c r="C120" s="180" t="s">
         <v>251</v>
       </c>
-      <c r="D120" s="144" t="s">
+      <c r="D120" s="180" t="s">
         <v>245</v>
       </c>
-      <c r="E120" s="142"/>
-      <c r="F120" s="142">
+      <c r="E120" s="181"/>
+      <c r="F120" s="181">
         <v>80</v>
       </c>
-      <c r="G120" s="142">
+      <c r="G120" s="181">
         <v>80</v>
       </c>
-      <c r="H120" s="143">
+      <c r="H120" s="182">
         <v>120</v>
       </c>
-      <c r="I120" s="142">
-        <v>40</v>
-      </c>
-      <c r="J120" s="142">
-        <v>40</v>
-      </c>
-      <c r="K120" s="142">
+      <c r="I120" s="181">
+        <v>40</v>
+      </c>
+      <c r="J120" s="181">
+        <v>40</v>
+      </c>
+      <c r="K120" s="181">
         <v>120</v>
       </c>
       <c r="L120" s="124">
@@ -11545,32 +11557,52 @@
       </c>
     </row>
     <row r="121" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A121" s="71"/>
-      <c r="B121" s="40">
+      <c r="A121" s="134">
+        <v>46315</v>
+      </c>
+      <c r="B121" s="135">
         <v>115</v>
       </c>
-      <c r="C121" s="125"/>
-      <c r="D121" s="125"/>
-      <c r="E121" s="68"/>
-      <c r="F121" s="68"/>
-      <c r="G121" s="68"/>
-      <c r="H121" s="124"/>
-      <c r="I121" s="68"/>
-      <c r="J121" s="68"/>
-      <c r="K121" s="68"/>
-      <c r="L121" s="124">
+      <c r="C121" s="144" t="s">
+        <v>252</v>
+      </c>
+      <c r="D121" s="144" t="s">
+        <v>253</v>
+      </c>
+      <c r="E121" s="142"/>
+      <c r="F121" s="142">
+        <v>80</v>
+      </c>
+      <c r="G121" s="142">
+        <v>80</v>
+      </c>
+      <c r="H121" s="143">
+        <v>120</v>
+      </c>
+      <c r="I121" s="142">
+        <v>80</v>
+      </c>
+      <c r="J121" s="142">
+        <v>80</v>
+      </c>
+      <c r="K121" s="142">
+        <v>120</v>
+      </c>
+      <c r="L121" s="143">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M121" s="138"/>
+        <v>14</v>
+      </c>
+      <c r="M121" s="138">
+        <v>12</v>
+      </c>
       <c r="N121" s="42"/>
       <c r="O121" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P121" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q121" s="44" t="e">
         <f t="shared" si="97"/>
@@ -11606,32 +11638,52 @@
       </c>
     </row>
     <row r="122" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A122" s="71"/>
-      <c r="B122" s="40">
+      <c r="A122" s="134">
+        <v>46315</v>
+      </c>
+      <c r="B122" s="135">
         <v>116</v>
       </c>
-      <c r="C122" s="125"/>
-      <c r="D122" s="125"/>
-      <c r="E122" s="68"/>
-      <c r="F122" s="68"/>
-      <c r="G122" s="68"/>
-      <c r="H122" s="124"/>
-      <c r="I122" s="68"/>
-      <c r="J122" s="68"/>
-      <c r="K122" s="68"/>
-      <c r="L122" s="124">
+      <c r="C122" s="144" t="s">
+        <v>116</v>
+      </c>
+      <c r="D122" s="144" t="s">
+        <v>125</v>
+      </c>
+      <c r="E122" s="142"/>
+      <c r="F122" s="142">
+        <v>12</v>
+      </c>
+      <c r="G122" s="142">
+        <v>0</v>
+      </c>
+      <c r="H122" s="143">
+        <v>37</v>
+      </c>
+      <c r="I122" s="142">
+        <v>37</v>
+      </c>
+      <c r="J122" s="142">
+        <v>0</v>
+      </c>
+      <c r="K122" s="142">
+        <v>147</v>
+      </c>
+      <c r="L122" s="143">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M122" s="138"/>
+        <v>5.8250000000000002</v>
+      </c>
+      <c r="M122" s="138">
+        <v>14</v>
+      </c>
       <c r="N122" s="42"/>
       <c r="O122" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="P122" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="Q122" s="44" t="e">
         <f t="shared" si="97"/>
@@ -11667,32 +11719,52 @@
       </c>
     </row>
     <row r="123" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A123" s="71"/>
-      <c r="B123" s="40">
+      <c r="A123" s="134">
+        <v>46315</v>
+      </c>
+      <c r="B123" s="135">
         <v>117</v>
       </c>
-      <c r="C123" s="125"/>
-      <c r="D123" s="125"/>
-      <c r="E123" s="68"/>
-      <c r="F123" s="68"/>
-      <c r="G123" s="68"/>
-      <c r="H123" s="124"/>
-      <c r="I123" s="68"/>
-      <c r="J123" s="68"/>
-      <c r="K123" s="68"/>
-      <c r="L123" s="124">
+      <c r="C123" s="144" t="s">
+        <v>116</v>
+      </c>
+      <c r="D123" s="144" t="s">
+        <v>124</v>
+      </c>
+      <c r="E123" s="142"/>
+      <c r="F123" s="142">
+        <v>80</v>
+      </c>
+      <c r="G123" s="142">
+        <v>0</v>
+      </c>
+      <c r="H123" s="143">
+        <v>0</v>
+      </c>
+      <c r="I123" s="142">
+        <v>0</v>
+      </c>
+      <c r="J123" s="142">
+        <v>40</v>
+      </c>
+      <c r="K123" s="142">
+        <v>0</v>
+      </c>
+      <c r="L123" s="143">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M123" s="138"/>
+        <v>3</v>
+      </c>
+      <c r="M123" s="138">
+        <v>14</v>
+      </c>
       <c r="N123" s="42"/>
       <c r="O123" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P123" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q123" s="44" t="e">
         <f t="shared" si="97"/>
@@ -11728,32 +11800,52 @@
       </c>
     </row>
     <row r="124" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A124" s="71"/>
-      <c r="B124" s="40">
+      <c r="A124" s="134">
+        <v>46315</v>
+      </c>
+      <c r="B124" s="135">
         <v>118</v>
       </c>
-      <c r="C124" s="125"/>
-      <c r="D124" s="125"/>
-      <c r="E124" s="68"/>
-      <c r="F124" s="68"/>
-      <c r="G124" s="68"/>
-      <c r="H124" s="124"/>
-      <c r="I124" s="68"/>
-      <c r="J124" s="68"/>
-      <c r="K124" s="68"/>
-      <c r="L124" s="124">
+      <c r="C124" s="144" t="s">
+        <v>116</v>
+      </c>
+      <c r="D124" s="144" t="s">
+        <v>216</v>
+      </c>
+      <c r="E124" s="142"/>
+      <c r="F124" s="142">
+        <v>0</v>
+      </c>
+      <c r="G124" s="142">
+        <v>0</v>
+      </c>
+      <c r="H124" s="143">
+        <v>40</v>
+      </c>
+      <c r="I124" s="142">
+        <v>80</v>
+      </c>
+      <c r="J124" s="142">
+        <v>80</v>
+      </c>
+      <c r="K124" s="142">
+        <v>160</v>
+      </c>
+      <c r="L124" s="143">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M124" s="138"/>
+        <v>9</v>
+      </c>
+      <c r="M124" s="138">
+        <v>14</v>
+      </c>
       <c r="N124" s="42"/>
       <c r="O124" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P124" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q124" s="44" t="e">
         <f t="shared" si="97"/>
@@ -11789,24 +11881,38 @@
       </c>
     </row>
     <row r="125" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A125" s="71"/>
-      <c r="B125" s="40">
+      <c r="A125" s="134">
+        <v>46315</v>
+      </c>
+      <c r="B125" s="135">
         <v>119</v>
       </c>
-      <c r="C125" s="125"/>
-      <c r="D125" s="125"/>
-      <c r="E125" s="68"/>
-      <c r="F125" s="68"/>
-      <c r="G125" s="68"/>
-      <c r="H125" s="124"/>
-      <c r="I125" s="68"/>
-      <c r="J125" s="68"/>
-      <c r="K125" s="68"/>
-      <c r="L125" s="124">
+      <c r="C125" s="144" t="s">
+        <v>254</v>
+      </c>
+      <c r="D125" s="144" t="s">
+        <v>255</v>
+      </c>
+      <c r="E125" s="142"/>
+      <c r="F125" s="142"/>
+      <c r="G125" s="142"/>
+      <c r="H125" s="143"/>
+      <c r="I125" s="142">
+        <v>80</v>
+      </c>
+      <c r="J125" s="142">
+        <v>120</v>
+      </c>
+      <c r="K125" s="142">
+        <v>400</v>
+      </c>
+      <c r="L125" s="143">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M125" s="138"/>
+        <v>15</v>
+      </c>
+      <c r="M125" s="138">
+        <v>12</v>
+      </c>
       <c r="N125" s="42"/>
       <c r="O125" s="66">
         <f t="shared" si="91"/>
@@ -11814,7 +11920,7 @@
       </c>
       <c r="P125" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q125" s="44" t="e">
         <f t="shared" si="97"/>
@@ -11850,7 +11956,9 @@
       </c>
     </row>
     <row r="126" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A126" s="71"/>
+      <c r="A126" s="134">
+        <v>46315</v>
+      </c>
       <c r="B126" s="40">
         <v>120</v>
       </c>
@@ -12405,10 +12513,10 @@
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A135" s="71"/>
-      <c r="B135" s="155" t="s">
+      <c r="B135" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="C135" s="155"/>
+      <c r="C135" s="168"/>
       <c r="D135" s="135"/>
       <c r="E135" s="140">
         <f t="shared" ref="E135:K135" si="103">SUM(E6:E63)</f>
@@ -12659,10 +12767,10 @@
       </c>
     </row>
     <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B139" s="167" t="s">
+      <c r="B139" s="156" t="s">
         <v>68</v>
       </c>
-      <c r="C139" s="168"/>
+      <c r="C139" s="157"/>
       <c r="D139" s="128"/>
       <c r="E139" s="76">
         <f>SUM(E137:E138)</f>
@@ -12746,10 +12854,10 @@
       </c>
     </row>
     <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B140" s="156" t="s">
+      <c r="B140" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="C140" s="157"/>
+      <c r="C140" s="146"/>
       <c r="D140" s="129"/>
       <c r="E140" s="77">
         <f>SUM(E135,E139)</f>
@@ -12785,7 +12893,7 @@
       </c>
       <c r="M140" s="56">
         <f>SUM(M5:M139)</f>
-        <v>1783.5</v>
+        <v>1849.5</v>
       </c>
       <c r="N140" s="54">
         <f t="shared" ref="N140:X140" si="111">SUM(N5:N139)</f>
@@ -12793,11 +12901,11 @@
       </c>
       <c r="O140" s="55">
         <f t="shared" si="111"/>
-        <v>1167.3499999999999</v>
+        <v>1189.8000000000002</v>
       </c>
       <c r="P140" s="57">
         <f t="shared" si="111"/>
-        <v>2930.8999999999996</v>
+        <v>3002.0999999999995</v>
       </c>
       <c r="Q140" s="58" t="e">
         <f t="shared" si="111"/>
@@ -12834,17 +12942,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B135:C135"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B135:C135"/>
   </mergeCells>
   <conditionalFormatting sqref="C48:D62">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12944,24 +13052,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="80">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="E5" s="72">
-        <v>1103</v>
+        <v>1150</v>
       </c>
       <c r="F5" s="72">
         <v>595</v>
       </c>
       <c r="G5" s="94">
         <f>SUM(D5:F5)</f>
-        <v>2160</v>
+        <v>2239</v>
       </c>
       <c r="H5" s="87">
         <v>10000</v>
       </c>
       <c r="I5" s="88">
         <f>G5-H5</f>
-        <v>-7840</v>
+        <v>-7761</v>
       </c>
       <c r="K5" s="132" t="s">
         <v>1</v>
@@ -12992,11 +13100,11 @@
       </c>
       <c r="D6" s="96">
         <f>D5*40</f>
-        <v>18480</v>
+        <v>19760</v>
       </c>
       <c r="E6" s="96">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>44120</v>
+        <v>46000</v>
       </c>
       <c r="F6" s="96">
         <f t="shared" si="1"/>
@@ -13004,7 +13112,7 @@
       </c>
       <c r="G6" s="97">
         <f>SUM(D6:F6)</f>
-        <v>86400</v>
+        <v>89560</v>
       </c>
       <c r="H6" s="89">
         <f>H5*40</f>
@@ -13012,7 +13120,7 @@
       </c>
       <c r="I6" s="90">
         <f>G6-H6</f>
-        <v>-313600</v>
+        <v>-310440</v>
       </c>
       <c r="K6" s="132" t="s">
         <v>2</v>
@@ -13161,11 +13269,11 @@
       </c>
       <c r="D9" s="98">
         <f>D8-D5</f>
-        <v>-462</v>
+        <v>-494</v>
       </c>
       <c r="E9" s="98">
         <f>E8-E5</f>
-        <v>-1103</v>
+        <v>-1150</v>
       </c>
       <c r="K9" s="132" t="s">
         <v>5</v>
@@ -13320,7 +13428,7 @@
       </c>
       <c r="G12" s="83">
         <f>D12+G5</f>
-        <v>6360</v>
+        <v>6439</v>
       </c>
       <c r="K12" s="132" t="s">
         <v>11</v>
@@ -13372,7 +13480,7 @@
       </c>
       <c r="G13" s="83">
         <f>G12*40</f>
-        <v>254400</v>
+        <v>257560</v>
       </c>
       <c r="S13" s="169" t="s">
         <v>83</v>

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C9E68E-0116-443C-9A8F-95DF52B8BBA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C60345F7-7B19-42A4-8CE1-F57B624F4A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="259">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -790,6 +790,15 @@
   </si>
   <si>
     <t>Sadar Bazar</t>
+  </si>
+  <si>
+    <t>Euro G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake City Management </t>
+  </si>
+  <si>
+    <t>Shekhpura</t>
   </si>
 </sst>
 </file>
@@ -2035,6 +2044,39 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2072,39 +2114,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2737,13 +2746,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="158">
+      <c r="B1" s="145">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
-      </c>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
+        <v>46317</v>
+      </c>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2765,10 +2774,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="166" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="146" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2798,13 +2807,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="147"/>
-      <c r="M2" s="148"/>
-      <c r="N2" s="149"/>
-      <c r="O2" s="150" t="s">
+      <c r="L2" s="158"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="160"/>
+      <c r="O2" s="161" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="151"/>
+      <c r="P2" s="162"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2823,8 +2832,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="155"/>
-      <c r="B3" s="160"/>
+      <c r="A3" s="166"/>
+      <c r="B3" s="147"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2852,29 +2861,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="152" t="s">
+      <c r="L3" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="153"/>
-      <c r="N3" s="154"/>
+      <c r="M3" s="164"/>
+      <c r="N3" s="165"/>
       <c r="O3" s="64"/>
       <c r="P3" s="65"/>
-      <c r="Q3" s="162" t="s">
+      <c r="Q3" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="163"/>
-      <c r="S3" s="163"/>
-      <c r="T3" s="164"/>
-      <c r="U3" s="165" t="s">
+      <c r="R3" s="150"/>
+      <c r="S3" s="150"/>
+      <c r="T3" s="151"/>
+      <c r="U3" s="152" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="166"/>
-      <c r="W3" s="166"/>
-      <c r="X3" s="167"/>
+      <c r="V3" s="153"/>
+      <c r="W3" s="153"/>
+      <c r="X3" s="154"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="155"/>
-      <c r="B4" s="161"/>
+      <c r="A4" s="166"/>
+      <c r="B4" s="148"/>
       <c r="C4" s="130" t="s">
         <v>90</v>
       </c>
@@ -10858,29 +10867,29 @@
       </c>
     </row>
     <row r="112" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A112" s="178">
+      <c r="A112" s="71">
         <v>46314</v>
       </c>
-      <c r="B112" s="179">
+      <c r="B112" s="40">
         <v>106</v>
       </c>
-      <c r="C112" s="180" t="s">
+      <c r="C112" s="125" t="s">
         <v>232</v>
       </c>
-      <c r="D112" s="180" t="s">
+      <c r="D112" s="125" t="s">
         <v>243</v>
       </c>
-      <c r="E112" s="181"/>
-      <c r="F112" s="181"/>
-      <c r="G112" s="181"/>
-      <c r="H112" s="182"/>
-      <c r="I112" s="181">
+      <c r="E112" s="68"/>
+      <c r="F112" s="68"/>
+      <c r="G112" s="68"/>
+      <c r="H112" s="124"/>
+      <c r="I112" s="68">
         <v>800</v>
       </c>
-      <c r="J112" s="181">
+      <c r="J112" s="68">
         <v>720</v>
       </c>
-      <c r="K112" s="181">
+      <c r="K112" s="68">
         <v>880</v>
       </c>
       <c r="L112" s="124">
@@ -10933,29 +10942,29 @@
       </c>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A113" s="178">
+      <c r="A113" s="71">
         <v>46314</v>
       </c>
-      <c r="B113" s="179">
+      <c r="B113" s="40">
         <v>107</v>
       </c>
-      <c r="C113" s="180" t="s">
+      <c r="C113" s="125" t="s">
         <v>244</v>
       </c>
-      <c r="D113" s="180" t="s">
+      <c r="D113" s="125" t="s">
         <v>245</v>
       </c>
-      <c r="E113" s="181"/>
-      <c r="F113" s="181"/>
-      <c r="G113" s="181"/>
-      <c r="H113" s="182"/>
-      <c r="I113" s="181">
+      <c r="E113" s="68"/>
+      <c r="F113" s="68"/>
+      <c r="G113" s="68"/>
+      <c r="H113" s="124"/>
+      <c r="I113" s="68">
         <v>80</v>
       </c>
-      <c r="J113" s="181">
+      <c r="J113" s="68">
         <v>80</v>
       </c>
-      <c r="K113" s="181">
+      <c r="K113" s="68">
         <v>120</v>
       </c>
       <c r="L113" s="124">
@@ -11008,27 +11017,27 @@
       </c>
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A114" s="178">
+      <c r="A114" s="71">
         <v>46314</v>
       </c>
-      <c r="B114" s="179">
+      <c r="B114" s="40">
         <v>108</v>
       </c>
-      <c r="C114" s="180" t="s">
+      <c r="C114" s="125" t="s">
         <v>246</v>
       </c>
-      <c r="D114" s="180" t="s">
+      <c r="D114" s="125" t="s">
         <v>247</v>
       </c>
-      <c r="E114" s="181"/>
-      <c r="F114" s="181"/>
-      <c r="G114" s="181"/>
-      <c r="H114" s="182"/>
-      <c r="I114" s="181">
+      <c r="E114" s="68"/>
+      <c r="F114" s="68"/>
+      <c r="G114" s="68"/>
+      <c r="H114" s="124"/>
+      <c r="I114" s="68">
         <v>80</v>
       </c>
-      <c r="J114" s="181"/>
-      <c r="K114" s="181">
+      <c r="J114" s="68"/>
+      <c r="K114" s="68">
         <v>120</v>
       </c>
       <c r="L114" s="124">
@@ -11081,25 +11090,25 @@
       </c>
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A115" s="178">
+      <c r="A115" s="71">
         <v>46314</v>
       </c>
-      <c r="B115" s="179">
+      <c r="B115" s="40">
         <v>109</v>
       </c>
-      <c r="C115" s="180" t="s">
+      <c r="C115" s="125" t="s">
         <v>248</v>
       </c>
-      <c r="D115" s="180" t="s">
+      <c r="D115" s="125" t="s">
         <v>121</v>
       </c>
-      <c r="E115" s="181"/>
-      <c r="F115" s="181"/>
-      <c r="G115" s="181"/>
-      <c r="H115" s="182"/>
-      <c r="I115" s="181"/>
-      <c r="J115" s="181"/>
-      <c r="K115" s="181">
+      <c r="E115" s="68"/>
+      <c r="F115" s="68"/>
+      <c r="G115" s="68"/>
+      <c r="H115" s="124"/>
+      <c r="I115" s="68"/>
+      <c r="J115" s="68"/>
+      <c r="K115" s="68">
         <v>40</v>
       </c>
       <c r="L115" s="124">
@@ -11152,35 +11161,35 @@
       </c>
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A116" s="178">
+      <c r="A116" s="71">
         <v>46314</v>
       </c>
-      <c r="B116" s="179">
+      <c r="B116" s="40">
         <v>110</v>
       </c>
-      <c r="C116" s="180" t="s">
+      <c r="C116" s="125" t="s">
         <v>249</v>
       </c>
-      <c r="D116" s="180" t="s">
+      <c r="D116" s="125" t="s">
         <v>250</v>
       </c>
-      <c r="E116" s="181"/>
-      <c r="F116" s="181">
+      <c r="E116" s="68"/>
+      <c r="F116" s="68">
         <v>80</v>
       </c>
-      <c r="G116" s="181">
+      <c r="G116" s="68">
         <v>80</v>
       </c>
-      <c r="H116" s="182">
+      <c r="H116" s="124">
         <v>80</v>
       </c>
-      <c r="I116" s="181">
+      <c r="I116" s="68">
         <v>120</v>
       </c>
-      <c r="J116" s="181">
+      <c r="J116" s="68">
         <v>120</v>
       </c>
-      <c r="K116" s="181">
+      <c r="K116" s="68">
         <v>80</v>
       </c>
       <c r="L116" s="124">
@@ -11233,35 +11242,35 @@
       </c>
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A117" s="178">
+      <c r="A117" s="71">
         <v>46314</v>
       </c>
-      <c r="B117" s="179">
+      <c r="B117" s="40">
         <v>111</v>
       </c>
-      <c r="C117" s="180" t="s">
+      <c r="C117" s="125" t="s">
         <v>116</v>
       </c>
-      <c r="D117" s="180" t="s">
+      <c r="D117" s="125" t="s">
         <v>121</v>
       </c>
-      <c r="E117" s="181"/>
-      <c r="F117" s="181">
-        <v>40</v>
-      </c>
-      <c r="G117" s="181">
-        <v>40</v>
-      </c>
-      <c r="H117" s="182">
-        <v>40</v>
-      </c>
-      <c r="I117" s="181">
-        <v>0</v>
-      </c>
-      <c r="J117" s="181">
-        <v>40</v>
-      </c>
-      <c r="K117" s="181">
+      <c r="E117" s="68"/>
+      <c r="F117" s="68">
+        <v>40</v>
+      </c>
+      <c r="G117" s="68">
+        <v>40</v>
+      </c>
+      <c r="H117" s="124">
+        <v>40</v>
+      </c>
+      <c r="I117" s="68">
+        <v>0</v>
+      </c>
+      <c r="J117" s="68">
+        <v>40</v>
+      </c>
+      <c r="K117" s="68">
         <v>0</v>
       </c>
       <c r="L117" s="124">
@@ -11314,35 +11323,35 @@
       </c>
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A118" s="178">
+      <c r="A118" s="71">
         <v>46314</v>
       </c>
-      <c r="B118" s="179">
+      <c r="B118" s="40">
         <v>112</v>
       </c>
-      <c r="C118" s="180" t="s">
+      <c r="C118" s="125" t="s">
         <v>116</v>
       </c>
-      <c r="D118" s="180" t="s">
+      <c r="D118" s="125" t="s">
         <v>123</v>
       </c>
-      <c r="E118" s="181"/>
-      <c r="F118" s="181">
-        <v>40</v>
-      </c>
-      <c r="G118" s="181">
-        <v>0</v>
-      </c>
-      <c r="H118" s="182">
+      <c r="E118" s="68"/>
+      <c r="F118" s="68">
+        <v>40</v>
+      </c>
+      <c r="G118" s="68">
+        <v>0</v>
+      </c>
+      <c r="H118" s="124">
         <v>280</v>
       </c>
-      <c r="I118" s="181">
+      <c r="I118" s="68">
         <v>160</v>
       </c>
-      <c r="J118" s="181">
+      <c r="J118" s="68">
         <v>80</v>
       </c>
-      <c r="K118" s="181">
+      <c r="K118" s="68">
         <v>320</v>
       </c>
       <c r="L118" s="124">
@@ -11395,35 +11404,35 @@
       </c>
     </row>
     <row r="119" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A119" s="178">
+      <c r="A119" s="71">
         <v>46314</v>
       </c>
-      <c r="B119" s="179">
+      <c r="B119" s="40">
         <v>113</v>
       </c>
-      <c r="C119" s="180" t="s">
+      <c r="C119" s="125" t="s">
         <v>116</v>
       </c>
-      <c r="D119" s="180" t="s">
+      <c r="D119" s="125" t="s">
         <v>122</v>
       </c>
-      <c r="E119" s="181"/>
-      <c r="F119" s="181">
-        <v>40</v>
-      </c>
-      <c r="G119" s="181">
-        <v>0</v>
-      </c>
-      <c r="H119" s="182">
+      <c r="E119" s="68"/>
+      <c r="F119" s="68">
+        <v>40</v>
+      </c>
+      <c r="G119" s="68">
+        <v>0</v>
+      </c>
+      <c r="H119" s="124">
         <v>400</v>
       </c>
-      <c r="I119" s="181">
+      <c r="I119" s="68">
         <v>120</v>
       </c>
-      <c r="J119" s="181">
+      <c r="J119" s="68">
         <v>320</v>
       </c>
-      <c r="K119" s="181">
+      <c r="K119" s="68">
         <v>320</v>
       </c>
       <c r="L119" s="124">
@@ -11476,35 +11485,35 @@
       </c>
     </row>
     <row r="120" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A120" s="178">
+      <c r="A120" s="71">
         <v>46314</v>
       </c>
-      <c r="B120" s="179">
+      <c r="B120" s="40">
         <v>114</v>
       </c>
-      <c r="C120" s="180" t="s">
+      <c r="C120" s="125" t="s">
         <v>251</v>
       </c>
-      <c r="D120" s="180" t="s">
+      <c r="D120" s="125" t="s">
         <v>245</v>
       </c>
-      <c r="E120" s="181"/>
-      <c r="F120" s="181">
+      <c r="E120" s="68"/>
+      <c r="F120" s="68">
         <v>80</v>
       </c>
-      <c r="G120" s="181">
+      <c r="G120" s="68">
         <v>80</v>
       </c>
-      <c r="H120" s="182">
+      <c r="H120" s="124">
         <v>120</v>
       </c>
-      <c r="I120" s="181">
-        <v>40</v>
-      </c>
-      <c r="J120" s="181">
-        <v>40</v>
-      </c>
-      <c r="K120" s="181">
+      <c r="I120" s="68">
+        <v>40</v>
+      </c>
+      <c r="J120" s="68">
+        <v>40</v>
+      </c>
+      <c r="K120" s="68">
         <v>120</v>
       </c>
       <c r="L120" s="124">
@@ -11557,38 +11566,38 @@
       </c>
     </row>
     <row r="121" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A121" s="134">
+      <c r="A121" s="178">
         <v>46315</v>
       </c>
-      <c r="B121" s="135">
+      <c r="B121" s="179">
         <v>115</v>
       </c>
-      <c r="C121" s="144" t="s">
+      <c r="C121" s="180" t="s">
         <v>252</v>
       </c>
-      <c r="D121" s="144" t="s">
+      <c r="D121" s="180" t="s">
         <v>253</v>
       </c>
-      <c r="E121" s="142"/>
-      <c r="F121" s="142">
+      <c r="E121" s="181"/>
+      <c r="F121" s="181">
         <v>80</v>
       </c>
-      <c r="G121" s="142">
+      <c r="G121" s="181">
         <v>80</v>
       </c>
-      <c r="H121" s="143">
+      <c r="H121" s="182">
         <v>120</v>
       </c>
-      <c r="I121" s="142">
+      <c r="I121" s="181">
         <v>80</v>
       </c>
-      <c r="J121" s="142">
+      <c r="J121" s="181">
         <v>80</v>
       </c>
-      <c r="K121" s="142">
+      <c r="K121" s="181">
         <v>120</v>
       </c>
-      <c r="L121" s="143">
+      <c r="L121" s="182">
         <f t="shared" si="99"/>
         <v>14</v>
       </c>
@@ -11638,38 +11647,38 @@
       </c>
     </row>
     <row r="122" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A122" s="134">
+      <c r="A122" s="178">
         <v>46315</v>
       </c>
-      <c r="B122" s="135">
+      <c r="B122" s="179">
         <v>116</v>
       </c>
-      <c r="C122" s="144" t="s">
+      <c r="C122" s="180" t="s">
         <v>116</v>
       </c>
-      <c r="D122" s="144" t="s">
+      <c r="D122" s="180" t="s">
         <v>125</v>
       </c>
-      <c r="E122" s="142"/>
-      <c r="F122" s="142">
+      <c r="E122" s="181"/>
+      <c r="F122" s="181">
         <v>12</v>
       </c>
-      <c r="G122" s="142">
-        <v>0</v>
-      </c>
-      <c r="H122" s="143">
+      <c r="G122" s="181">
+        <v>0</v>
+      </c>
+      <c r="H122" s="182">
         <v>37</v>
       </c>
-      <c r="I122" s="142">
+      <c r="I122" s="181">
         <v>37</v>
       </c>
-      <c r="J122" s="142">
-        <v>0</v>
-      </c>
-      <c r="K122" s="142">
+      <c r="J122" s="181">
+        <v>0</v>
+      </c>
+      <c r="K122" s="181">
         <v>147</v>
       </c>
-      <c r="L122" s="143">
+      <c r="L122" s="182">
         <f t="shared" si="99"/>
         <v>5.8250000000000002</v>
       </c>
@@ -11719,38 +11728,38 @@
       </c>
     </row>
     <row r="123" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A123" s="134">
+      <c r="A123" s="178">
         <v>46315</v>
       </c>
-      <c r="B123" s="135">
+      <c r="B123" s="179">
         <v>117</v>
       </c>
-      <c r="C123" s="144" t="s">
+      <c r="C123" s="180" t="s">
         <v>116</v>
       </c>
-      <c r="D123" s="144" t="s">
+      <c r="D123" s="180" t="s">
         <v>124</v>
       </c>
-      <c r="E123" s="142"/>
-      <c r="F123" s="142">
+      <c r="E123" s="181"/>
+      <c r="F123" s="181">
         <v>80</v>
       </c>
-      <c r="G123" s="142">
-        <v>0</v>
-      </c>
-      <c r="H123" s="143">
-        <v>0</v>
-      </c>
-      <c r="I123" s="142">
-        <v>0</v>
-      </c>
-      <c r="J123" s="142">
-        <v>40</v>
-      </c>
-      <c r="K123" s="142">
-        <v>0</v>
-      </c>
-      <c r="L123" s="143">
+      <c r="G123" s="181">
+        <v>0</v>
+      </c>
+      <c r="H123" s="182">
+        <v>0</v>
+      </c>
+      <c r="I123" s="181">
+        <v>0</v>
+      </c>
+      <c r="J123" s="181">
+        <v>40</v>
+      </c>
+      <c r="K123" s="181">
+        <v>0</v>
+      </c>
+      <c r="L123" s="182">
         <f t="shared" si="99"/>
         <v>3</v>
       </c>
@@ -11800,38 +11809,38 @@
       </c>
     </row>
     <row r="124" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A124" s="134">
+      <c r="A124" s="178">
         <v>46315</v>
       </c>
-      <c r="B124" s="135">
+      <c r="B124" s="179">
         <v>118</v>
       </c>
-      <c r="C124" s="144" t="s">
+      <c r="C124" s="180" t="s">
         <v>116</v>
       </c>
-      <c r="D124" s="144" t="s">
+      <c r="D124" s="180" t="s">
         <v>216</v>
       </c>
-      <c r="E124" s="142"/>
-      <c r="F124" s="142">
-        <v>0</v>
-      </c>
-      <c r="G124" s="142">
-        <v>0</v>
-      </c>
-      <c r="H124" s="143">
-        <v>40</v>
-      </c>
-      <c r="I124" s="142">
+      <c r="E124" s="181"/>
+      <c r="F124" s="181">
+        <v>0</v>
+      </c>
+      <c r="G124" s="181">
+        <v>0</v>
+      </c>
+      <c r="H124" s="182">
+        <v>40</v>
+      </c>
+      <c r="I124" s="181">
         <v>80</v>
       </c>
-      <c r="J124" s="142">
+      <c r="J124" s="181">
         <v>80</v>
       </c>
-      <c r="K124" s="142">
+      <c r="K124" s="181">
         <v>160</v>
       </c>
-      <c r="L124" s="143">
+      <c r="L124" s="182">
         <f t="shared" si="99"/>
         <v>9</v>
       </c>
@@ -11881,32 +11890,32 @@
       </c>
     </row>
     <row r="125" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A125" s="134">
+      <c r="A125" s="178">
         <v>46315</v>
       </c>
-      <c r="B125" s="135">
+      <c r="B125" s="179">
         <v>119</v>
       </c>
-      <c r="C125" s="144" t="s">
+      <c r="C125" s="180" t="s">
         <v>254</v>
       </c>
-      <c r="D125" s="144" t="s">
+      <c r="D125" s="180" t="s">
         <v>255</v>
       </c>
-      <c r="E125" s="142"/>
-      <c r="F125" s="142"/>
-      <c r="G125" s="142"/>
-      <c r="H125" s="143"/>
-      <c r="I125" s="142">
+      <c r="E125" s="181"/>
+      <c r="F125" s="181"/>
+      <c r="G125" s="181"/>
+      <c r="H125" s="182"/>
+      <c r="I125" s="181">
         <v>80</v>
       </c>
-      <c r="J125" s="142">
+      <c r="J125" s="181">
         <v>120</v>
       </c>
-      <c r="K125" s="142">
+      <c r="K125" s="181">
         <v>400</v>
       </c>
-      <c r="L125" s="143">
+      <c r="L125" s="182">
         <f t="shared" si="99"/>
         <v>15</v>
       </c>
@@ -11957,33 +11966,51 @@
     </row>
     <row r="126" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A126" s="134">
-        <v>46315</v>
-      </c>
-      <c r="B126" s="40">
+        <v>46316</v>
+      </c>
+      <c r="B126" s="135">
         <v>120</v>
       </c>
-      <c r="C126" s="125"/>
-      <c r="D126" s="125"/>
-      <c r="E126" s="68"/>
-      <c r="F126" s="68"/>
-      <c r="G126" s="68"/>
-      <c r="H126" s="124"/>
-      <c r="I126" s="68"/>
-      <c r="J126" s="68"/>
-      <c r="K126" s="68"/>
-      <c r="L126" s="124">
+      <c r="C126" s="144" t="s">
+        <v>256</v>
+      </c>
+      <c r="D126" s="144" t="s">
+        <v>115</v>
+      </c>
+      <c r="E126" s="142"/>
+      <c r="F126" s="142">
+        <v>200</v>
+      </c>
+      <c r="G126" s="142">
+        <v>200</v>
+      </c>
+      <c r="H126" s="143">
+        <v>200</v>
+      </c>
+      <c r="I126" s="142">
+        <v>200</v>
+      </c>
+      <c r="J126" s="142">
+        <v>200</v>
+      </c>
+      <c r="K126" s="142">
+        <v>200</v>
+      </c>
+      <c r="L126" s="143">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M126" s="138"/>
+        <v>30</v>
+      </c>
+      <c r="M126" s="138">
+        <v>14</v>
+      </c>
       <c r="N126" s="42"/>
       <c r="O126" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P126" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q126" s="44" t="e">
         <f t="shared" si="97"/>
@@ -12019,30 +12046,48 @@
       </c>
     </row>
     <row r="127" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A127" s="71"/>
-      <c r="B127" s="40"/>
-      <c r="C127" s="125"/>
-      <c r="D127" s="125"/>
-      <c r="E127" s="68"/>
-      <c r="F127" s="68"/>
-      <c r="G127" s="68"/>
-      <c r="H127" s="124"/>
-      <c r="I127" s="68"/>
-      <c r="J127" s="68"/>
-      <c r="K127" s="68"/>
-      <c r="L127" s="124">
+      <c r="A127" s="134">
+        <v>46316</v>
+      </c>
+      <c r="B127" s="135">
+        <v>121</v>
+      </c>
+      <c r="C127" s="144" t="s">
+        <v>257</v>
+      </c>
+      <c r="D127" s="144" t="s">
+        <v>160</v>
+      </c>
+      <c r="E127" s="142"/>
+      <c r="F127" s="142"/>
+      <c r="G127" s="142"/>
+      <c r="H127" s="143">
+        <v>40</v>
+      </c>
+      <c r="I127" s="142">
+        <v>40</v>
+      </c>
+      <c r="J127" s="142">
+        <v>40</v>
+      </c>
+      <c r="K127" s="142">
+        <v>40</v>
+      </c>
+      <c r="L127" s="143">
         <f t="shared" si="99"/>
-        <v>0</v>
-      </c>
-      <c r="M127" s="138"/>
+        <v>4</v>
+      </c>
+      <c r="M127" s="138">
+        <v>10</v>
+      </c>
       <c r="N127" s="42"/>
       <c r="O127" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P127" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q127" s="44" t="e">
         <f t="shared" ref="Q127:Q135" si="100">SUMPRODUCT($E$4:$E$4,$E$6:$E$6)*$Q$3</f>
@@ -12078,33 +12123,52 @@
       </c>
     </row>
     <row r="128" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A128" s="71"/>
-      <c r="B128" s="40"/>
-      <c r="C128" s="125"/>
-      <c r="D128" s="125"/>
-      <c r="E128" s="68"/>
-      <c r="F128" s="68"/>
-      <c r="G128" s="68"/>
-      <c r="H128" s="124"/>
-      <c r="I128" s="68"/>
-      <c r="J128" s="68"/>
-      <c r="K128" s="68"/>
-      <c r="L128" s="124">
+      <c r="A128" s="134">
+        <v>46316</v>
+      </c>
+      <c r="B128" s="135">
+        <v>122</v>
+      </c>
+      <c r="C128" s="144" t="s">
+        <v>116</v>
+      </c>
+      <c r="D128" s="144" t="s">
+        <v>118</v>
+      </c>
+      <c r="E128" s="142"/>
+      <c r="F128" s="142">
+        <v>40</v>
+      </c>
+      <c r="G128" s="142">
+        <v>0</v>
+      </c>
+      <c r="H128" s="143">
+        <v>40</v>
+      </c>
+      <c r="I128" s="142">
+        <v>0</v>
+      </c>
+      <c r="J128" s="142">
+        <v>80</v>
+      </c>
+      <c r="K128" s="142">
+        <v>160</v>
+      </c>
+      <c r="L128" s="143">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M128" s="138">
-        <f t="shared" ref="M128:M135" si="102">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N128" s="42"/>
       <c r="O128" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P128" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q128" s="44" t="e">
         <f t="shared" si="100"/>
@@ -12140,29 +12204,38 @@
       </c>
     </row>
     <row r="129" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A129" s="71"/>
-      <c r="B129" s="40"/>
-      <c r="C129" s="125"/>
-      <c r="D129" s="125"/>
-      <c r="E129" s="68"/>
-      <c r="F129" s="68"/>
-      <c r="G129" s="68"/>
-      <c r="H129" s="124"/>
-      <c r="I129" s="68"/>
-      <c r="J129" s="68"/>
-      <c r="K129" s="68"/>
-      <c r="L129" s="124">
+      <c r="A129" s="134">
+        <v>46316</v>
+      </c>
+      <c r="B129" s="135">
+        <v>123</v>
+      </c>
+      <c r="C129" s="144" t="s">
+        <v>116</v>
+      </c>
+      <c r="D129" s="144" t="s">
+        <v>258</v>
+      </c>
+      <c r="E129" s="142"/>
+      <c r="F129" s="142"/>
+      <c r="G129" s="142"/>
+      <c r="H129" s="143">
+        <v>80</v>
+      </c>
+      <c r="I129" s="142"/>
+      <c r="J129" s="142"/>
+      <c r="K129" s="142"/>
+      <c r="L129" s="143">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M129" s="138">
-        <f t="shared" si="102"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N129" s="42"/>
       <c r="O129" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P129" s="33">
         <f t="shared" si="92"/>
@@ -12202,33 +12275,52 @@
       </c>
     </row>
     <row r="130" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A130" s="71"/>
-      <c r="B130" s="40"/>
-      <c r="C130" s="125"/>
-      <c r="D130" s="125"/>
-      <c r="E130" s="68"/>
-      <c r="F130" s="68"/>
-      <c r="G130" s="68"/>
-      <c r="H130" s="124"/>
-      <c r="I130" s="68"/>
-      <c r="J130" s="68"/>
-      <c r="K130" s="68"/>
-      <c r="L130" s="124">
+      <c r="A130" s="134">
+        <v>46316</v>
+      </c>
+      <c r="B130" s="135">
+        <v>124</v>
+      </c>
+      <c r="C130" s="144" t="s">
+        <v>116</v>
+      </c>
+      <c r="D130" s="144" t="s">
+        <v>120</v>
+      </c>
+      <c r="E130" s="142"/>
+      <c r="F130" s="142">
+        <v>0</v>
+      </c>
+      <c r="G130" s="142">
+        <v>0</v>
+      </c>
+      <c r="H130" s="143">
+        <v>80</v>
+      </c>
+      <c r="I130" s="142">
+        <v>40</v>
+      </c>
+      <c r="J130" s="142">
+        <v>40</v>
+      </c>
+      <c r="K130" s="142">
+        <v>0</v>
+      </c>
+      <c r="L130" s="143">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M130" s="138">
-        <f t="shared" si="102"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N130" s="42"/>
       <c r="O130" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P130" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q130" s="44" t="e">
         <f t="shared" si="100"/>
@@ -12264,33 +12356,52 @@
       </c>
     </row>
     <row r="131" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A131" s="71"/>
-      <c r="B131" s="40"/>
-      <c r="C131" s="125"/>
-      <c r="D131" s="125"/>
-      <c r="E131" s="68"/>
-      <c r="F131" s="68"/>
-      <c r="G131" s="68"/>
-      <c r="H131" s="124"/>
-      <c r="I131" s="68"/>
-      <c r="J131" s="68"/>
-      <c r="K131" s="68"/>
-      <c r="L131" s="124">
+      <c r="A131" s="134">
+        <v>46316</v>
+      </c>
+      <c r="B131" s="135">
+        <v>125</v>
+      </c>
+      <c r="C131" s="144" t="s">
+        <v>224</v>
+      </c>
+      <c r="D131" s="144" t="s">
+        <v>225</v>
+      </c>
+      <c r="E131" s="142"/>
+      <c r="F131" s="142">
+        <v>400</v>
+      </c>
+      <c r="G131" s="142">
+        <v>400</v>
+      </c>
+      <c r="H131" s="143">
+        <v>600</v>
+      </c>
+      <c r="I131" s="142">
+        <v>600</v>
+      </c>
+      <c r="J131" s="142">
+        <v>1000</v>
+      </c>
+      <c r="K131" s="142">
+        <v>2000</v>
+      </c>
+      <c r="L131" s="143">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="M131" s="138">
-        <f t="shared" si="102"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N131" s="42"/>
       <c r="O131" s="66">
         <f t="shared" si="91"/>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="P131" s="33">
         <f t="shared" si="92"/>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="Q131" s="44" t="e">
         <f t="shared" si="100"/>
@@ -12326,8 +12437,12 @@
       </c>
     </row>
     <row r="132" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A132" s="71"/>
-      <c r="B132" s="40"/>
+      <c r="A132" s="134">
+        <v>46316</v>
+      </c>
+      <c r="B132" s="179">
+        <v>126</v>
+      </c>
       <c r="C132" s="125"/>
       <c r="D132" s="125"/>
       <c r="E132" s="68"/>
@@ -12342,7 +12457,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="138">
-        <f t="shared" si="102"/>
+        <f t="shared" ref="M128:M135" si="102">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N132" s="42"/>
@@ -12389,7 +12504,9 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="71"/>
-      <c r="B133" s="40"/>
+      <c r="B133" s="179">
+        <v>127</v>
+      </c>
       <c r="C133" s="125"/>
       <c r="D133" s="125"/>
       <c r="E133" s="68"/>
@@ -12451,7 +12568,9 @@
     </row>
     <row r="134" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A134" s="71"/>
-      <c r="B134" s="40"/>
+      <c r="B134" s="179">
+        <v>128</v>
+      </c>
       <c r="C134" s="125"/>
       <c r="D134" s="125"/>
       <c r="E134" s="68"/>
@@ -12513,10 +12632,10 @@
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A135" s="71"/>
-      <c r="B135" s="168" t="s">
+      <c r="B135" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="C135" s="168"/>
+      <c r="C135" s="155"/>
       <c r="D135" s="135"/>
       <c r="E135" s="140">
         <f t="shared" ref="E135:K135" si="103">SUM(E6:E63)</f>
@@ -12767,10 +12886,10 @@
       </c>
     </row>
     <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B139" s="156" t="s">
+      <c r="B139" s="167" t="s">
         <v>68</v>
       </c>
-      <c r="C139" s="157"/>
+      <c r="C139" s="168"/>
       <c r="D139" s="128"/>
       <c r="E139" s="76">
         <f>SUM(E137:E138)</f>
@@ -12854,10 +12973,10 @@
       </c>
     </row>
     <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B140" s="145" t="s">
+      <c r="B140" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="C140" s="146"/>
+      <c r="C140" s="157"/>
       <c r="D140" s="129"/>
       <c r="E140" s="77">
         <f>SUM(E135,E139)</f>
@@ -12893,7 +13012,7 @@
       </c>
       <c r="M140" s="56">
         <f>SUM(M5:M139)</f>
-        <v>1849.5</v>
+        <v>1933.5</v>
       </c>
       <c r="N140" s="54">
         <f t="shared" ref="N140:X140" si="111">SUM(N5:N139)</f>
@@ -12901,11 +13020,11 @@
       </c>
       <c r="O140" s="55">
         <f t="shared" si="111"/>
-        <v>1189.8000000000002</v>
+        <v>1303.8000000000002</v>
       </c>
       <c r="P140" s="57">
         <f t="shared" si="111"/>
-        <v>3002.0999999999995</v>
+        <v>3234.0999999999995</v>
       </c>
       <c r="Q140" s="58" t="e">
         <f t="shared" si="111"/>
@@ -12942,17 +13061,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B135:C135"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B135:C135"/>
   </mergeCells>
   <conditionalFormatting sqref="C48:D62">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -13052,24 +13171,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="80">
-        <v>494</v>
+        <v>547</v>
       </c>
       <c r="E5" s="72">
-        <v>1150</v>
+        <v>1323</v>
       </c>
       <c r="F5" s="72">
         <v>595</v>
       </c>
       <c r="G5" s="94">
         <f>SUM(D5:F5)</f>
-        <v>2239</v>
+        <v>2465</v>
       </c>
       <c r="H5" s="87">
         <v>10000</v>
       </c>
       <c r="I5" s="88">
         <f>G5-H5</f>
-        <v>-7761</v>
+        <v>-7535</v>
       </c>
       <c r="K5" s="132" t="s">
         <v>1</v>
@@ -13100,11 +13219,11 @@
       </c>
       <c r="D6" s="96">
         <f>D5*40</f>
-        <v>19760</v>
+        <v>21880</v>
       </c>
       <c r="E6" s="96">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>46000</v>
+        <v>52920</v>
       </c>
       <c r="F6" s="96">
         <f t="shared" si="1"/>
@@ -13112,7 +13231,7 @@
       </c>
       <c r="G6" s="97">
         <f>SUM(D6:F6)</f>
-        <v>89560</v>
+        <v>98600</v>
       </c>
       <c r="H6" s="89">
         <f>H5*40</f>
@@ -13120,7 +13239,7 @@
       </c>
       <c r="I6" s="90">
         <f>G6-H6</f>
-        <v>-310440</v>
+        <v>-301400</v>
       </c>
       <c r="K6" s="132" t="s">
         <v>2</v>
@@ -13269,11 +13388,11 @@
       </c>
       <c r="D9" s="98">
         <f>D8-D5</f>
-        <v>-494</v>
+        <v>-547</v>
       </c>
       <c r="E9" s="98">
         <f>E8-E5</f>
-        <v>-1150</v>
+        <v>-1323</v>
       </c>
       <c r="K9" s="132" t="s">
         <v>5</v>
@@ -13428,7 +13547,7 @@
       </c>
       <c r="G12" s="83">
         <f>D12+G5</f>
-        <v>6439</v>
+        <v>6665</v>
       </c>
       <c r="K12" s="132" t="s">
         <v>11</v>
@@ -13480,7 +13599,7 @@
       </c>
       <c r="G13" s="83">
         <f>G12*40</f>
-        <v>257560</v>
+        <v>266600</v>
       </c>
       <c r="S13" s="169" t="s">
         <v>83</v>

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C60345F7-7B19-42A4-8CE1-F57B624F4A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1E211A-9BCE-40BD-945F-0791B7119441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1666,7 +1666,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2044,6 +2044,45 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2077,45 +2116,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2142,17 +2142,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2746,13 +2735,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="145">
+      <c r="B1" s="158">
         <f ca="1">TODAY()</f>
         <v>46317</v>
       </c>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2774,10 +2763,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="166" t="s">
+      <c r="A2" s="155" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="146" t="s">
+      <c r="B2" s="159" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2807,13 +2796,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="158"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="160"/>
-      <c r="O2" s="161" t="s">
+      <c r="L2" s="147"/>
+      <c r="M2" s="148"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="150" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="162"/>
+      <c r="P2" s="151"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2832,8 +2821,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="166"/>
-      <c r="B3" s="147"/>
+      <c r="A3" s="155"/>
+      <c r="B3" s="160"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2861,29 +2850,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="163" t="s">
+      <c r="L3" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="164"/>
-      <c r="N3" s="165"/>
+      <c r="M3" s="153"/>
+      <c r="N3" s="154"/>
       <c r="O3" s="64"/>
       <c r="P3" s="65"/>
-      <c r="Q3" s="149" t="s">
+      <c r="Q3" s="162" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="150"/>
-      <c r="S3" s="150"/>
-      <c r="T3" s="151"/>
-      <c r="U3" s="152" t="s">
+      <c r="R3" s="163"/>
+      <c r="S3" s="163"/>
+      <c r="T3" s="164"/>
+      <c r="U3" s="165" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="153"/>
-      <c r="W3" s="153"/>
-      <c r="X3" s="154"/>
+      <c r="V3" s="166"/>
+      <c r="W3" s="166"/>
+      <c r="X3" s="167"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="166"/>
-      <c r="B4" s="148"/>
+      <c r="A4" s="155"/>
+      <c r="B4" s="161"/>
       <c r="C4" s="130" t="s">
         <v>90</v>
       </c>
@@ -11566,38 +11555,38 @@
       </c>
     </row>
     <row r="121" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A121" s="178">
+      <c r="A121" s="71">
         <v>46315</v>
       </c>
-      <c r="B121" s="179">
+      <c r="B121" s="40">
         <v>115</v>
       </c>
-      <c r="C121" s="180" t="s">
+      <c r="C121" s="125" t="s">
         <v>252</v>
       </c>
-      <c r="D121" s="180" t="s">
+      <c r="D121" s="125" t="s">
         <v>253</v>
       </c>
-      <c r="E121" s="181"/>
-      <c r="F121" s="181">
+      <c r="E121" s="68"/>
+      <c r="F121" s="68">
         <v>80</v>
       </c>
-      <c r="G121" s="181">
+      <c r="G121" s="68">
         <v>80</v>
       </c>
-      <c r="H121" s="182">
+      <c r="H121" s="124">
         <v>120</v>
       </c>
-      <c r="I121" s="181">
+      <c r="I121" s="68">
         <v>80</v>
       </c>
-      <c r="J121" s="181">
+      <c r="J121" s="68">
         <v>80</v>
       </c>
-      <c r="K121" s="181">
+      <c r="K121" s="68">
         <v>120</v>
       </c>
-      <c r="L121" s="182">
+      <c r="L121" s="124">
         <f t="shared" si="99"/>
         <v>14</v>
       </c>
@@ -11647,38 +11636,38 @@
       </c>
     </row>
     <row r="122" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A122" s="178">
+      <c r="A122" s="71">
         <v>46315</v>
       </c>
-      <c r="B122" s="179">
+      <c r="B122" s="40">
         <v>116</v>
       </c>
-      <c r="C122" s="180" t="s">
+      <c r="C122" s="125" t="s">
         <v>116</v>
       </c>
-      <c r="D122" s="180" t="s">
+      <c r="D122" s="125" t="s">
         <v>125</v>
       </c>
-      <c r="E122" s="181"/>
-      <c r="F122" s="181">
+      <c r="E122" s="68"/>
+      <c r="F122" s="68">
         <v>12</v>
       </c>
-      <c r="G122" s="181">
-        <v>0</v>
-      </c>
-      <c r="H122" s="182">
+      <c r="G122" s="68">
+        <v>0</v>
+      </c>
+      <c r="H122" s="124">
         <v>37</v>
       </c>
-      <c r="I122" s="181">
+      <c r="I122" s="68">
         <v>37</v>
       </c>
-      <c r="J122" s="181">
-        <v>0</v>
-      </c>
-      <c r="K122" s="181">
+      <c r="J122" s="68">
+        <v>0</v>
+      </c>
+      <c r="K122" s="68">
         <v>147</v>
       </c>
-      <c r="L122" s="182">
+      <c r="L122" s="124">
         <f t="shared" si="99"/>
         <v>5.8250000000000002</v>
       </c>
@@ -11728,38 +11717,38 @@
       </c>
     </row>
     <row r="123" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A123" s="178">
+      <c r="A123" s="71">
         <v>46315</v>
       </c>
-      <c r="B123" s="179">
+      <c r="B123" s="40">
         <v>117</v>
       </c>
-      <c r="C123" s="180" t="s">
+      <c r="C123" s="125" t="s">
         <v>116</v>
       </c>
-      <c r="D123" s="180" t="s">
+      <c r="D123" s="125" t="s">
         <v>124</v>
       </c>
-      <c r="E123" s="181"/>
-      <c r="F123" s="181">
+      <c r="E123" s="68"/>
+      <c r="F123" s="68">
         <v>80</v>
       </c>
-      <c r="G123" s="181">
-        <v>0</v>
-      </c>
-      <c r="H123" s="182">
-        <v>0</v>
-      </c>
-      <c r="I123" s="181">
-        <v>0</v>
-      </c>
-      <c r="J123" s="181">
-        <v>40</v>
-      </c>
-      <c r="K123" s="181">
-        <v>0</v>
-      </c>
-      <c r="L123" s="182">
+      <c r="G123" s="68">
+        <v>0</v>
+      </c>
+      <c r="H123" s="124">
+        <v>0</v>
+      </c>
+      <c r="I123" s="68">
+        <v>0</v>
+      </c>
+      <c r="J123" s="68">
+        <v>40</v>
+      </c>
+      <c r="K123" s="68">
+        <v>0</v>
+      </c>
+      <c r="L123" s="124">
         <f t="shared" si="99"/>
         <v>3</v>
       </c>
@@ -11809,38 +11798,38 @@
       </c>
     </row>
     <row r="124" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A124" s="178">
+      <c r="A124" s="71">
         <v>46315</v>
       </c>
-      <c r="B124" s="179">
+      <c r="B124" s="40">
         <v>118</v>
       </c>
-      <c r="C124" s="180" t="s">
+      <c r="C124" s="125" t="s">
         <v>116</v>
       </c>
-      <c r="D124" s="180" t="s">
+      <c r="D124" s="125" t="s">
         <v>216</v>
       </c>
-      <c r="E124" s="181"/>
-      <c r="F124" s="181">
-        <v>0</v>
-      </c>
-      <c r="G124" s="181">
-        <v>0</v>
-      </c>
-      <c r="H124" s="182">
-        <v>40</v>
-      </c>
-      <c r="I124" s="181">
+      <c r="E124" s="68"/>
+      <c r="F124" s="68">
+        <v>0</v>
+      </c>
+      <c r="G124" s="68">
+        <v>0</v>
+      </c>
+      <c r="H124" s="124">
+        <v>40</v>
+      </c>
+      <c r="I124" s="68">
         <v>80</v>
       </c>
-      <c r="J124" s="181">
+      <c r="J124" s="68">
         <v>80</v>
       </c>
-      <c r="K124" s="181">
+      <c r="K124" s="68">
         <v>160</v>
       </c>
-      <c r="L124" s="182">
+      <c r="L124" s="124">
         <f t="shared" si="99"/>
         <v>9</v>
       </c>
@@ -11890,32 +11879,32 @@
       </c>
     </row>
     <row r="125" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A125" s="178">
+      <c r="A125" s="71">
         <v>46315</v>
       </c>
-      <c r="B125" s="179">
+      <c r="B125" s="40">
         <v>119</v>
       </c>
-      <c r="C125" s="180" t="s">
+      <c r="C125" s="125" t="s">
         <v>254</v>
       </c>
-      <c r="D125" s="180" t="s">
+      <c r="D125" s="125" t="s">
         <v>255</v>
       </c>
-      <c r="E125" s="181"/>
-      <c r="F125" s="181"/>
-      <c r="G125" s="181"/>
-      <c r="H125" s="182"/>
-      <c r="I125" s="181">
+      <c r="E125" s="68"/>
+      <c r="F125" s="68"/>
+      <c r="G125" s="68"/>
+      <c r="H125" s="124"/>
+      <c r="I125" s="68">
         <v>80</v>
       </c>
-      <c r="J125" s="181">
+      <c r="J125" s="68">
         <v>120</v>
       </c>
-      <c r="K125" s="181">
+      <c r="K125" s="68">
         <v>400</v>
       </c>
-      <c r="L125" s="182">
+      <c r="L125" s="124">
         <f t="shared" si="99"/>
         <v>15</v>
       </c>
@@ -12440,7 +12429,7 @@
       <c r="A132" s="134">
         <v>46316</v>
       </c>
-      <c r="B132" s="179">
+      <c r="B132" s="40">
         <v>126</v>
       </c>
       <c r="C132" s="125"/>
@@ -12457,7 +12446,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="138">
-        <f t="shared" ref="M128:M135" si="102">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
+        <f t="shared" ref="M132:M135" si="102">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N132" s="42"/>
@@ -12504,7 +12493,7 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" s="71"/>
-      <c r="B133" s="179">
+      <c r="B133" s="40">
         <v>127</v>
       </c>
       <c r="C133" s="125"/>
@@ -12568,7 +12557,7 @@
     </row>
     <row r="134" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A134" s="71"/>
-      <c r="B134" s="179">
+      <c r="B134" s="40">
         <v>128</v>
       </c>
       <c r="C134" s="125"/>
@@ -12632,10 +12621,10 @@
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A135" s="71"/>
-      <c r="B135" s="155" t="s">
+      <c r="B135" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="C135" s="155"/>
+      <c r="C135" s="168"/>
       <c r="D135" s="135"/>
       <c r="E135" s="140">
         <f t="shared" ref="E135:K135" si="103">SUM(E6:E63)</f>
@@ -12886,10 +12875,10 @@
       </c>
     </row>
     <row r="139" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B139" s="167" t="s">
+      <c r="B139" s="156" t="s">
         <v>68</v>
       </c>
-      <c r="C139" s="168"/>
+      <c r="C139" s="157"/>
       <c r="D139" s="128"/>
       <c r="E139" s="76">
         <f>SUM(E137:E138)</f>
@@ -12973,10 +12962,10 @@
       </c>
     </row>
     <row r="140" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B140" s="156" t="s">
+      <c r="B140" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="C140" s="157"/>
+      <c r="C140" s="146"/>
       <c r="D140" s="129"/>
       <c r="E140" s="77">
         <f>SUM(E135,E139)</f>
@@ -13061,17 +13050,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B135:C135"/>
     <mergeCell ref="B140:C140"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B135:C135"/>
   </mergeCells>
   <conditionalFormatting sqref="C48:D62">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -13197,11 +13186,11 @@
         <v>70</v>
       </c>
       <c r="M5" s="5">
-        <v>6676</v>
+        <v>4151</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>166.9</v>
+        <v>103.77500000000001</v>
       </c>
       <c r="O5" s="74"/>
       <c r="P5" s="133"/>
@@ -13210,7 +13199,7 @@
       </c>
       <c r="R5" s="141">
         <f>N5-Q5</f>
-        <v>-100.30999999999997</v>
+        <v>-163.43499999999997</v>
       </c>
     </row>
     <row r="6" spans="3:26" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
@@ -13248,11 +13237,11 @@
         <v>70</v>
       </c>
       <c r="M6" s="5">
-        <v>7876</v>
+        <v>5191</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>196.9</v>
+        <v>129.77500000000001</v>
       </c>
       <c r="O6" s="74"/>
       <c r="P6" s="133"/>
@@ -13261,7 +13250,7 @@
       </c>
       <c r="R6" s="141">
         <f t="shared" ref="R6:R10" si="2">N6-Q6</f>
-        <v>22.629999999999995</v>
+        <v>-44.495000000000005</v>
       </c>
       <c r="S6" s="116"/>
       <c r="T6" s="116"/>
@@ -13290,11 +13279,11 @@
         <v>70</v>
       </c>
       <c r="M7" s="5">
-        <v>4133</v>
+        <v>1303</v>
       </c>
       <c r="N7" s="6">
         <f t="shared" si="0"/>
-        <v>103.325</v>
+        <v>32.575000000000003</v>
       </c>
       <c r="O7" s="74"/>
       <c r="P7" s="133"/>
@@ -13303,7 +13292,7 @@
       </c>
       <c r="R7" s="141">
         <f t="shared" si="2"/>
-        <v>27.085000000000008</v>
+        <v>-43.664999999999992</v>
       </c>
       <c r="S7" s="121" t="s">
         <v>85</v>
@@ -13341,11 +13330,11 @@
         <v>120</v>
       </c>
       <c r="M8" s="5">
-        <v>6558</v>
+        <v>3247</v>
       </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>163.95</v>
+        <v>81.174999999999997</v>
       </c>
       <c r="O8" s="74">
         <v>50</v>
@@ -13356,7 +13345,7 @@
       </c>
       <c r="R8" s="141">
         <f t="shared" si="2"/>
-        <v>79.649999999999991</v>
+        <v>-3.125</v>
       </c>
       <c r="S8" s="72">
         <v>120</v>
@@ -13401,11 +13390,11 @@
         <v>120</v>
       </c>
       <c r="M9" s="5">
-        <v>7576</v>
+        <v>17623</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>189.4</v>
+        <v>440.57499999999999</v>
       </c>
       <c r="O9" s="74">
         <v>23</v>
@@ -13416,7 +13405,7 @@
       </c>
       <c r="R9" s="141">
         <f t="shared" si="2"/>
-        <v>80.23</v>
+        <v>331.40499999999997</v>
       </c>
       <c r="S9" s="72">
         <v>120</v>
@@ -13452,11 +13441,11 @@
         <v>120</v>
       </c>
       <c r="M10" s="5">
-        <v>4776</v>
+        <v>18667</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>119.4</v>
+        <v>466.67500000000001</v>
       </c>
       <c r="O10" s="74"/>
       <c r="P10" s="133"/>
@@ -13465,7 +13454,7 @@
       </c>
       <c r="R10" s="141">
         <f t="shared" si="2"/>
-        <v>-78.949999999999989</v>
+        <v>268.32500000000005</v>
       </c>
       <c r="S10" s="72">
         <v>120</v>
@@ -13555,11 +13544,11 @@
       <c r="L12" s="74"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>37595</v>
+        <v>50182</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>939.875</v>
+        <v>1254.55</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
@@ -13658,7 +13647,7 @@
       <c r="N17" s="113"/>
       <c r="O17" s="114">
         <f>N17-M5</f>
-        <v>-6676</v>
+        <v>-4151</v>
       </c>
       <c r="R17">
         <v>51.94</v>
@@ -13678,7 +13667,7 @@
       <c r="N18" s="5"/>
       <c r="O18" s="114">
         <f>N18-M6</f>
-        <v>-7876</v>
+        <v>-5191</v>
       </c>
       <c r="R18">
         <v>163.25499999999997</v>
@@ -13701,7 +13690,7 @@
       <c r="N19" s="5"/>
       <c r="O19" s="114">
         <f t="shared" ref="O19:O23" si="5">N19-M7</f>
-        <v>-4133</v>
+        <v>-1303</v>
       </c>
       <c r="R19">
         <v>224.70999999999998</v>
@@ -13728,7 +13717,7 @@
       <c r="N20" s="5"/>
       <c r="O20" s="114">
         <f t="shared" si="5"/>
-        <v>-6558</v>
+        <v>-3247</v>
       </c>
       <c r="R20">
         <v>156.75</v>
@@ -13763,7 +13752,7 @@
       <c r="N21" s="5"/>
       <c r="O21" s="114">
         <f t="shared" si="5"/>
-        <v>-7576</v>
+        <v>-17623</v>
       </c>
       <c r="R21">
         <v>158.505</v>
@@ -13795,7 +13784,7 @@
       <c r="N22" s="5"/>
       <c r="O22" s="114">
         <f t="shared" si="5"/>
-        <v>-4776</v>
+        <v>-18667</v>
       </c>
       <c r="R22">
         <v>69.150000000000006</v>
@@ -13857,7 +13846,7 @@
       </c>
       <c r="O24" s="109">
         <f>SUM(O17:O23)</f>
-        <v>-37595</v>
+        <v>-50182</v>
       </c>
     </row>
     <row r="25" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -13887,7 +13876,7 @@
       </c>
       <c r="O25" s="109">
         <f>O24/40</f>
-        <v>-939.875</v>
+        <v>-1254.55</v>
       </c>
     </row>
     <row r="26" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE9754C-39A7-4868-B126-9F745DEFA512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DC001C-3466-4FEE-A966-DD03D0A3E7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="265">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -811,6 +811,12 @@
   </si>
   <si>
     <t xml:space="preserve">Chatri Chowk </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aslam Super Market </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galaxy Super Market </t>
   </si>
 </sst>
 </file>
@@ -1604,7 +1610,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1909,93 +1915,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2037,9 +1956,6 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2049,7 +1965,110 @@
     <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2058,16 +2077,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2662,13 +2671,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="116">
+      <c r="B1" s="148">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
-      </c>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
+        <v>46319</v>
+      </c>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2690,10 +2699,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="135" t="s">
+      <c r="A2" s="146" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="149" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2723,13 +2732,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="127"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="129"/>
-      <c r="O2" s="130" t="s">
+      <c r="L2" s="138"/>
+      <c r="M2" s="139"/>
+      <c r="N2" s="140"/>
+      <c r="O2" s="141" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="131"/>
+      <c r="P2" s="142"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2748,8 +2757,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="135"/>
-      <c r="B3" s="118"/>
+      <c r="A3" s="146"/>
+      <c r="B3" s="150"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2777,29 +2786,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="132" t="s">
+      <c r="L3" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="133"/>
-      <c r="N3" s="134"/>
+      <c r="M3" s="144"/>
+      <c r="N3" s="145"/>
       <c r="O3" s="48"/>
       <c r="P3" s="49"/>
-      <c r="Q3" s="120" t="s">
+      <c r="Q3" s="152" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="121"/>
-      <c r="S3" s="121"/>
-      <c r="T3" s="122"/>
-      <c r="U3" s="123" t="s">
+      <c r="R3" s="153"/>
+      <c r="S3" s="153"/>
+      <c r="T3" s="154"/>
+      <c r="U3" s="155" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="124"/>
-      <c r="W3" s="124"/>
-      <c r="X3" s="125"/>
+      <c r="V3" s="156"/>
+      <c r="W3" s="156"/>
+      <c r="X3" s="157"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="135"/>
-      <c r="B4" s="119"/>
+      <c r="A4" s="146"/>
+      <c r="B4" s="151"/>
       <c r="C4" s="101" t="s">
         <v>90</v>
       </c>
@@ -11881,38 +11890,38 @@
       </c>
     </row>
     <row r="126" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A126" s="166">
+      <c r="A126" s="53">
         <v>46316</v>
       </c>
-      <c r="B126" s="167">
+      <c r="B126" s="39">
         <v>120</v>
       </c>
-      <c r="C126" s="168" t="s">
+      <c r="C126" s="98" t="s">
         <v>256</v>
       </c>
-      <c r="D126" s="168" t="s">
+      <c r="D126" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="E126" s="169"/>
-      <c r="F126" s="169">
+      <c r="E126" s="51"/>
+      <c r="F126" s="51">
         <v>200</v>
       </c>
-      <c r="G126" s="169">
+      <c r="G126" s="51">
         <v>200</v>
       </c>
-      <c r="H126" s="170">
+      <c r="H126" s="97">
         <v>200</v>
       </c>
-      <c r="I126" s="169">
+      <c r="I126" s="51">
         <v>200</v>
       </c>
-      <c r="J126" s="169">
+      <c r="J126" s="51">
         <v>200</v>
       </c>
-      <c r="K126" s="169">
+      <c r="K126" s="51">
         <v>200</v>
       </c>
-      <c r="L126" s="170">
+      <c r="L126" s="97">
         <f t="shared" si="99"/>
         <v>30</v>
       </c>
@@ -11962,34 +11971,34 @@
       </c>
     </row>
     <row r="127" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A127" s="166">
+      <c r="A127" s="53">
         <v>46316</v>
       </c>
-      <c r="B127" s="167">
+      <c r="B127" s="39">
         <v>121</v>
       </c>
-      <c r="C127" s="168" t="s">
+      <c r="C127" s="98" t="s">
         <v>257</v>
       </c>
-      <c r="D127" s="168" t="s">
+      <c r="D127" s="98" t="s">
         <v>160</v>
       </c>
-      <c r="E127" s="169"/>
-      <c r="F127" s="169"/>
-      <c r="G127" s="169"/>
-      <c r="H127" s="170">
-        <v>40</v>
-      </c>
-      <c r="I127" s="169">
-        <v>40</v>
-      </c>
-      <c r="J127" s="169">
-        <v>40</v>
-      </c>
-      <c r="K127" s="169">
-        <v>40</v>
-      </c>
-      <c r="L127" s="170">
+      <c r="E127" s="51"/>
+      <c r="F127" s="51"/>
+      <c r="G127" s="51"/>
+      <c r="H127" s="97">
+        <v>40</v>
+      </c>
+      <c r="I127" s="51">
+        <v>40</v>
+      </c>
+      <c r="J127" s="51">
+        <v>40</v>
+      </c>
+      <c r="K127" s="51">
+        <v>40</v>
+      </c>
+      <c r="L127" s="97">
         <f t="shared" si="99"/>
         <v>4</v>
       </c>
@@ -12039,38 +12048,38 @@
       </c>
     </row>
     <row r="128" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A128" s="166">
+      <c r="A128" s="53">
         <v>46316</v>
       </c>
-      <c r="B128" s="167">
+      <c r="B128" s="39">
         <v>122</v>
       </c>
-      <c r="C128" s="168" t="s">
+      <c r="C128" s="98" t="s">
         <v>116</v>
       </c>
-      <c r="D128" s="168" t="s">
+      <c r="D128" s="98" t="s">
         <v>118</v>
       </c>
-      <c r="E128" s="169"/>
-      <c r="F128" s="169">
-        <v>40</v>
-      </c>
-      <c r="G128" s="169">
-        <v>0</v>
-      </c>
-      <c r="H128" s="170">
-        <v>40</v>
-      </c>
-      <c r="I128" s="169">
-        <v>0</v>
-      </c>
-      <c r="J128" s="169">
+      <c r="E128" s="51"/>
+      <c r="F128" s="51">
+        <v>40</v>
+      </c>
+      <c r="G128" s="51">
+        <v>0</v>
+      </c>
+      <c r="H128" s="97">
+        <v>40</v>
+      </c>
+      <c r="I128" s="51">
+        <v>0</v>
+      </c>
+      <c r="J128" s="51">
         <v>80</v>
       </c>
-      <c r="K128" s="169">
+      <c r="K128" s="51">
         <v>160</v>
       </c>
-      <c r="L128" s="170">
+      <c r="L128" s="97">
         <f t="shared" si="99"/>
         <v>8</v>
       </c>
@@ -12120,28 +12129,28 @@
       </c>
     </row>
     <row r="129" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A129" s="166">
+      <c r="A129" s="53">
         <v>46316</v>
       </c>
-      <c r="B129" s="167">
+      <c r="B129" s="39">
         <v>123</v>
       </c>
-      <c r="C129" s="168" t="s">
+      <c r="C129" s="98" t="s">
         <v>116</v>
       </c>
-      <c r="D129" s="168" t="s">
+      <c r="D129" s="98" t="s">
         <v>258</v>
       </c>
-      <c r="E129" s="169"/>
-      <c r="F129" s="169"/>
-      <c r="G129" s="169"/>
-      <c r="H129" s="170">
+      <c r="E129" s="51"/>
+      <c r="F129" s="51"/>
+      <c r="G129" s="51"/>
+      <c r="H129" s="97">
         <v>80</v>
       </c>
-      <c r="I129" s="169"/>
-      <c r="J129" s="169"/>
-      <c r="K129" s="169"/>
-      <c r="L129" s="170">
+      <c r="I129" s="51"/>
+      <c r="J129" s="51"/>
+      <c r="K129" s="51"/>
+      <c r="L129" s="97">
         <f t="shared" si="99"/>
         <v>2</v>
       </c>
@@ -12191,38 +12200,38 @@
       </c>
     </row>
     <row r="130" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A130" s="166">
+      <c r="A130" s="53">
         <v>46316</v>
       </c>
-      <c r="B130" s="167">
+      <c r="B130" s="39">
         <v>124</v>
       </c>
-      <c r="C130" s="168" t="s">
+      <c r="C130" s="98" t="s">
         <v>116</v>
       </c>
-      <c r="D130" s="168" t="s">
+      <c r="D130" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="E130" s="169"/>
-      <c r="F130" s="169">
-        <v>0</v>
-      </c>
-      <c r="G130" s="169">
-        <v>0</v>
-      </c>
-      <c r="H130" s="170">
+      <c r="E130" s="51"/>
+      <c r="F130" s="51">
+        <v>0</v>
+      </c>
+      <c r="G130" s="51">
+        <v>0</v>
+      </c>
+      <c r="H130" s="97">
         <v>80</v>
       </c>
-      <c r="I130" s="169">
-        <v>40</v>
-      </c>
-      <c r="J130" s="169">
-        <v>40</v>
-      </c>
-      <c r="K130" s="169">
-        <v>0</v>
-      </c>
-      <c r="L130" s="170">
+      <c r="I130" s="51">
+        <v>40</v>
+      </c>
+      <c r="J130" s="51">
+        <v>40</v>
+      </c>
+      <c r="K130" s="51">
+        <v>0</v>
+      </c>
+      <c r="L130" s="97">
         <f t="shared" si="99"/>
         <v>4</v>
       </c>
@@ -12272,38 +12281,38 @@
       </c>
     </row>
     <row r="131" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A131" s="166">
+      <c r="A131" s="53">
         <v>46316</v>
       </c>
-      <c r="B131" s="167">
+      <c r="B131" s="39">
         <v>125</v>
       </c>
-      <c r="C131" s="168" t="s">
+      <c r="C131" s="98" t="s">
         <v>224</v>
       </c>
-      <c r="D131" s="168" t="s">
+      <c r="D131" s="98" t="s">
         <v>225</v>
       </c>
-      <c r="E131" s="169"/>
-      <c r="F131" s="169">
+      <c r="E131" s="51"/>
+      <c r="F131" s="51">
         <v>400</v>
       </c>
-      <c r="G131" s="169">
+      <c r="G131" s="51">
         <v>400</v>
       </c>
-      <c r="H131" s="170">
+      <c r="H131" s="97">
         <v>600</v>
       </c>
-      <c r="I131" s="169">
+      <c r="I131" s="51">
         <v>600</v>
       </c>
-      <c r="J131" s="169">
+      <c r="J131" s="51">
         <v>1000</v>
       </c>
-      <c r="K131" s="169">
+      <c r="K131" s="51">
         <v>2000</v>
       </c>
-      <c r="L131" s="170">
+      <c r="L131" s="97">
         <f t="shared" si="99"/>
         <v>125</v>
       </c>
@@ -12353,127 +12362,127 @@
       </c>
     </row>
     <row r="132" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A132" s="105">
+      <c r="A132" s="167">
         <v>46317</v>
       </c>
-      <c r="B132" s="171">
+      <c r="B132" s="168">
         <v>126</v>
       </c>
-      <c r="C132" s="172" t="s">
+      <c r="C132" s="169" t="s">
         <v>259</v>
       </c>
-      <c r="D132" s="172" t="s">
+      <c r="D132" s="169" t="s">
         <v>260</v>
       </c>
-      <c r="E132" s="173"/>
-      <c r="F132" s="173">
+      <c r="E132" s="170"/>
+      <c r="F132" s="170">
         <v>79</v>
       </c>
-      <c r="G132" s="173">
+      <c r="G132" s="170">
         <v>80</v>
       </c>
-      <c r="H132" s="174">
+      <c r="H132" s="171">
         <v>79</v>
       </c>
-      <c r="I132" s="173">
+      <c r="I132" s="170">
         <v>79</v>
       </c>
-      <c r="J132" s="173">
+      <c r="J132" s="170">
         <v>78</v>
       </c>
-      <c r="K132" s="173">
+      <c r="K132" s="170">
         <v>79</v>
       </c>
-      <c r="L132" s="147">
+      <c r="L132" s="118">
         <f t="shared" si="99"/>
         <v>11.85</v>
       </c>
-      <c r="M132" s="148">
+      <c r="M132" s="119">
         <v>14</v>
       </c>
       <c r="N132" s="47"/>
-      <c r="O132" s="149">
+      <c r="O132" s="120">
         <f t="shared" si="91"/>
         <v>11.9</v>
       </c>
-      <c r="P132" s="150">
+      <c r="P132" s="121">
         <f t="shared" si="92"/>
         <v>11.8</v>
       </c>
-      <c r="Q132" s="151" t="e">
+      <c r="Q132" s="122" t="e">
         <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R132" s="152">
+      <c r="R132" s="123">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S132" s="152">
+      <c r="S132" s="123">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T132" s="153" t="e">
+      <c r="T132" s="124" t="e">
         <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
-      <c r="U132" s="154" t="e">
+      <c r="U132" s="125" t="e">
         <f t="shared" si="101"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V132" s="155">
+      <c r="V132" s="126">
         <f t="shared" si="94"/>
         <v>0</v>
       </c>
-      <c r="W132" s="155">
+      <c r="W132" s="126">
         <f t="shared" si="95"/>
         <v>0</v>
       </c>
-      <c r="X132" s="156" t="e">
+      <c r="X132" s="127" t="e">
         <f t="shared" si="96"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A133" s="105">
+      <c r="A133" s="167">
         <v>46317</v>
       </c>
-      <c r="B133" s="106">
+      <c r="B133" s="172">
         <v>127</v>
       </c>
-      <c r="C133" s="115" t="s">
+      <c r="C133" s="173" t="s">
         <v>261</v>
       </c>
-      <c r="D133" s="115" t="s">
+      <c r="D133" s="173" t="s">
         <v>121</v>
       </c>
-      <c r="E133" s="113"/>
-      <c r="F133" s="113">
+      <c r="E133" s="174"/>
+      <c r="F133" s="174">
         <v>80</v>
       </c>
-      <c r="G133" s="113">
+      <c r="G133" s="174">
         <v>80</v>
       </c>
-      <c r="H133" s="114">
+      <c r="H133" s="175">
         <v>80</v>
       </c>
-      <c r="I133" s="113">
+      <c r="I133" s="174">
         <v>80</v>
       </c>
-      <c r="J133" s="113">
+      <c r="J133" s="174">
         <v>80</v>
       </c>
-      <c r="K133" s="113">
+      <c r="K133" s="174">
         <v>80</v>
       </c>
       <c r="L133" s="97">
         <f t="shared" si="99"/>
         <v>12</v>
       </c>
-      <c r="M133" s="148">
+      <c r="M133" s="119">
         <v>14</v>
       </c>
       <c r="N133" s="97"/>
-      <c r="O133" s="158">
+      <c r="O133" s="129">
         <f t="shared" si="91"/>
         <v>12</v>
       </c>
@@ -12493,7 +12502,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T133" s="159" t="e">
+      <c r="T133" s="130" t="e">
         <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
@@ -12515,35 +12524,35 @@
       </c>
     </row>
     <row r="134" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A134" s="105">
+      <c r="A134" s="167">
         <v>46317</v>
       </c>
-      <c r="B134" s="106">
+      <c r="B134" s="172">
         <v>128</v>
       </c>
-      <c r="C134" s="115" t="s">
+      <c r="C134" s="173" t="s">
         <v>113</v>
       </c>
-      <c r="D134" s="115" t="s">
+      <c r="D134" s="173" t="s">
         <v>262</v>
       </c>
-      <c r="E134" s="113"/>
-      <c r="F134" s="113">
+      <c r="E134" s="174"/>
+      <c r="F134" s="174">
         <v>1000</v>
       </c>
-      <c r="G134" s="113">
+      <c r="G134" s="174">
         <v>1000</v>
       </c>
-      <c r="H134" s="114">
+      <c r="H134" s="175">
         <v>1000</v>
       </c>
-      <c r="I134" s="113">
+      <c r="I134" s="174">
         <v>1000</v>
       </c>
-      <c r="J134" s="113">
+      <c r="J134" s="174">
         <v>1000</v>
       </c>
-      <c r="K134" s="113">
+      <c r="K134" s="174">
         <v>1000</v>
       </c>
       <c r="L134" s="97">
@@ -12554,41 +12563,41 @@
         <v>15</v>
       </c>
       <c r="N134" s="97"/>
-      <c r="O134" s="158"/>
+      <c r="O134" s="129"/>
       <c r="P134" s="51"/>
       <c r="Q134" s="109"/>
       <c r="R134" s="109"/>
       <c r="S134" s="109"/>
-      <c r="T134" s="159"/>
+      <c r="T134" s="130"/>
       <c r="U134" s="97"/>
       <c r="V134" s="97"/>
       <c r="W134" s="97"/>
       <c r="X134" s="114"/>
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A135" s="105">
+      <c r="A135" s="167">
         <v>46317</v>
       </c>
-      <c r="B135" s="106">
+      <c r="B135" s="172">
         <v>129</v>
       </c>
-      <c r="C135" s="115" t="s">
+      <c r="C135" s="173" t="s">
         <v>151</v>
       </c>
-      <c r="D135" s="115" t="s">
+      <c r="D135" s="173" t="s">
         <v>152</v>
       </c>
-      <c r="E135" s="113"/>
-      <c r="F135" s="113">
+      <c r="E135" s="174"/>
+      <c r="F135" s="174">
         <v>120</v>
       </c>
-      <c r="G135" s="113"/>
-      <c r="H135" s="114"/>
-      <c r="I135" s="113">
+      <c r="G135" s="174"/>
+      <c r="H135" s="175"/>
+      <c r="I135" s="174">
         <v>120</v>
       </c>
-      <c r="J135" s="113"/>
-      <c r="K135" s="113">
+      <c r="J135" s="174"/>
+      <c r="K135" s="174">
         <v>80</v>
       </c>
       <c r="L135" s="97">
@@ -12599,12 +12608,12 @@
         <v>14</v>
       </c>
       <c r="N135" s="97"/>
-      <c r="O135" s="158"/>
+      <c r="O135" s="129"/>
       <c r="P135" s="51"/>
       <c r="Q135" s="109"/>
       <c r="R135" s="109"/>
       <c r="S135" s="109"/>
-      <c r="T135" s="159"/>
+      <c r="T135" s="130"/>
       <c r="U135" s="97"/>
       <c r="V135" s="97"/>
       <c r="W135" s="97"/>
@@ -12612,35 +12621,50 @@
     </row>
     <row r="136" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A136" s="105">
-        <v>46317</v>
-      </c>
-      <c r="B136" s="167">
+        <v>46318</v>
+      </c>
+      <c r="B136" s="106">
         <v>130</v>
       </c>
-      <c r="C136" s="98"/>
-      <c r="D136" s="98"/>
-      <c r="E136" s="51"/>
-      <c r="F136" s="51"/>
-      <c r="G136" s="51"/>
-      <c r="H136" s="97"/>
-      <c r="I136" s="51"/>
-      <c r="J136" s="51"/>
-      <c r="K136" s="51"/>
-      <c r="L136" s="97">
+      <c r="C136" s="115" t="s">
+        <v>263</v>
+      </c>
+      <c r="D136" s="115" t="s">
+        <v>202</v>
+      </c>
+      <c r="E136" s="113"/>
+      <c r="F136" s="113">
+        <v>160</v>
+      </c>
+      <c r="G136" s="113">
+        <v>160</v>
+      </c>
+      <c r="H136" s="114">
+        <v>200</v>
+      </c>
+      <c r="I136" s="113">
+        <v>200</v>
+      </c>
+      <c r="J136" s="113">
+        <v>200</v>
+      </c>
+      <c r="K136" s="113">
+        <v>300</v>
+      </c>
+      <c r="L136" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>30.5</v>
       </c>
       <c r="M136" s="109">
-        <f t="shared" ref="M132:O173" si="103">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N136" s="97"/>
-      <c r="O136" s="158"/>
+      <c r="O136" s="129"/>
       <c r="P136" s="51"/>
       <c r="Q136" s="109"/>
       <c r="R136" s="109"/>
       <c r="S136" s="109"/>
-      <c r="T136" s="159"/>
+      <c r="T136" s="130"/>
       <c r="U136" s="97"/>
       <c r="V136" s="97"/>
       <c r="W136" s="97"/>
@@ -12648,35 +12672,50 @@
     </row>
     <row r="137" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A137" s="105">
-        <v>46317</v>
-      </c>
-      <c r="B137" s="167">
+        <v>46318</v>
+      </c>
+      <c r="B137" s="106">
         <v>131</v>
       </c>
-      <c r="C137" s="98"/>
-      <c r="D137" s="98"/>
-      <c r="E137" s="51"/>
-      <c r="F137" s="51"/>
-      <c r="G137" s="51"/>
-      <c r="H137" s="97"/>
-      <c r="I137" s="51"/>
-      <c r="J137" s="51"/>
-      <c r="K137" s="51"/>
-      <c r="L137" s="97">
+      <c r="C137" s="115" t="s">
+        <v>264</v>
+      </c>
+      <c r="D137" s="115" t="s">
+        <v>160</v>
+      </c>
+      <c r="E137" s="113"/>
+      <c r="F137" s="113">
+        <v>40</v>
+      </c>
+      <c r="G137" s="113">
+        <v>40</v>
+      </c>
+      <c r="H137" s="114">
+        <v>40</v>
+      </c>
+      <c r="I137" s="113">
+        <v>40</v>
+      </c>
+      <c r="J137" s="113">
+        <v>40</v>
+      </c>
+      <c r="K137" s="113">
+        <v>40</v>
+      </c>
+      <c r="L137" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M137" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N137" s="97"/>
-      <c r="O137" s="158"/>
+      <c r="O137" s="129"/>
       <c r="P137" s="51"/>
       <c r="Q137" s="109"/>
       <c r="R137" s="109"/>
       <c r="S137" s="109"/>
-      <c r="T137" s="159"/>
+      <c r="T137" s="130"/>
       <c r="U137" s="97"/>
       <c r="V137" s="97"/>
       <c r="W137" s="97"/>
@@ -12684,35 +12723,50 @@
     </row>
     <row r="138" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A138" s="105">
-        <v>46317</v>
-      </c>
-      <c r="B138" s="146">
+        <v>46318</v>
+      </c>
+      <c r="B138" s="136">
         <v>132</v>
       </c>
-      <c r="C138" s="98"/>
-      <c r="D138" s="98"/>
-      <c r="E138" s="51"/>
-      <c r="F138" s="51"/>
-      <c r="G138" s="51"/>
-      <c r="H138" s="97"/>
-      <c r="I138" s="51"/>
-      <c r="J138" s="51"/>
-      <c r="K138" s="51"/>
-      <c r="L138" s="97">
+      <c r="C138" s="115" t="s">
+        <v>113</v>
+      </c>
+      <c r="D138" s="115" t="s">
+        <v>114</v>
+      </c>
+      <c r="E138" s="113"/>
+      <c r="F138" s="113">
+        <v>120</v>
+      </c>
+      <c r="G138" s="113">
+        <v>80</v>
+      </c>
+      <c r="H138" s="114">
+        <v>80</v>
+      </c>
+      <c r="I138" s="113">
+        <v>120</v>
+      </c>
+      <c r="J138" s="113">
+        <v>80</v>
+      </c>
+      <c r="K138" s="113">
+        <v>120</v>
+      </c>
+      <c r="L138" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M138" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N138" s="97"/>
-      <c r="O138" s="158"/>
+      <c r="O138" s="129"/>
       <c r="P138" s="51"/>
       <c r="Q138" s="109"/>
       <c r="R138" s="109"/>
       <c r="S138" s="109"/>
-      <c r="T138" s="159"/>
+      <c r="T138" s="130"/>
       <c r="U138" s="97"/>
       <c r="V138" s="97"/>
       <c r="W138" s="97"/>
@@ -12720,7 +12774,7 @@
     </row>
     <row r="139" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A139" s="105">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B139" s="39">
         <v>133</v>
@@ -12739,16 +12793,16 @@
         <v>0</v>
       </c>
       <c r="M139" s="109">
-        <f t="shared" si="103"/>
+        <f t="shared" ref="M136:O173" si="103">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N139" s="97"/>
-      <c r="O139" s="158"/>
+      <c r="O139" s="129"/>
       <c r="P139" s="51"/>
       <c r="Q139" s="109"/>
       <c r="R139" s="109"/>
       <c r="S139" s="109"/>
-      <c r="T139" s="159"/>
+      <c r="T139" s="130"/>
       <c r="U139" s="97"/>
       <c r="V139" s="97"/>
       <c r="W139" s="97"/>
@@ -12758,7 +12812,7 @@
       <c r="A140" s="105">
         <v>46317</v>
       </c>
-      <c r="B140" s="167">
+      <c r="B140" s="39">
         <v>134</v>
       </c>
       <c r="C140" s="98"/>
@@ -12779,12 +12833,12 @@
         <v>0</v>
       </c>
       <c r="N140" s="97"/>
-      <c r="O140" s="158"/>
+      <c r="O140" s="129"/>
       <c r="P140" s="51"/>
       <c r="Q140" s="109"/>
       <c r="R140" s="109"/>
       <c r="S140" s="109"/>
-      <c r="T140" s="159"/>
+      <c r="T140" s="130"/>
       <c r="U140" s="97"/>
       <c r="V140" s="97"/>
       <c r="W140" s="97"/>
@@ -12794,7 +12848,7 @@
       <c r="A141" s="105">
         <v>46317</v>
       </c>
-      <c r="B141" s="167">
+      <c r="B141" s="39">
         <v>135</v>
       </c>
       <c r="C141" s="98"/>
@@ -12815,20 +12869,20 @@
         <v>0</v>
       </c>
       <c r="N141" s="97"/>
-      <c r="O141" s="158"/>
+      <c r="O141" s="129"/>
       <c r="P141" s="51"/>
       <c r="Q141" s="109"/>
       <c r="R141" s="109"/>
       <c r="S141" s="109"/>
-      <c r="T141" s="159"/>
+      <c r="T141" s="130"/>
       <c r="U141" s="97"/>
       <c r="V141" s="97"/>
       <c r="W141" s="97"/>
       <c r="X141" s="114"/>
     </row>
     <row r="142" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A142" s="157"/>
-      <c r="B142" s="167">
+      <c r="A142" s="128"/>
+      <c r="B142" s="39">
         <v>136</v>
       </c>
       <c r="C142" s="98"/>
@@ -12849,20 +12903,20 @@
         <v>0</v>
       </c>
       <c r="N142" s="97"/>
-      <c r="O142" s="158"/>
+      <c r="O142" s="129"/>
       <c r="P142" s="51"/>
       <c r="Q142" s="109"/>
       <c r="R142" s="109"/>
       <c r="S142" s="109"/>
-      <c r="T142" s="159"/>
+      <c r="T142" s="130"/>
       <c r="U142" s="97"/>
       <c r="V142" s="97"/>
       <c r="W142" s="97"/>
       <c r="X142" s="114"/>
     </row>
     <row r="143" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A143" s="157"/>
-      <c r="B143" s="167">
+      <c r="A143" s="128"/>
+      <c r="B143" s="39">
         <v>137</v>
       </c>
       <c r="C143" s="98"/>
@@ -12883,20 +12937,20 @@
         <v>0</v>
       </c>
       <c r="N143" s="97"/>
-      <c r="O143" s="158"/>
+      <c r="O143" s="129"/>
       <c r="P143" s="51"/>
       <c r="Q143" s="109"/>
       <c r="R143" s="109"/>
       <c r="S143" s="109"/>
-      <c r="T143" s="159"/>
+      <c r="T143" s="130"/>
       <c r="U143" s="97"/>
       <c r="V143" s="97"/>
       <c r="W143" s="97"/>
       <c r="X143" s="114"/>
     </row>
     <row r="144" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A144" s="157"/>
-      <c r="B144" s="146">
+      <c r="A144" s="128"/>
+      <c r="B144" s="117">
         <v>138</v>
       </c>
       <c r="C144" s="98"/>
@@ -12917,19 +12971,19 @@
         <v>0</v>
       </c>
       <c r="N144" s="97"/>
-      <c r="O144" s="158"/>
+      <c r="O144" s="129"/>
       <c r="P144" s="51"/>
       <c r="Q144" s="109"/>
       <c r="R144" s="109"/>
       <c r="S144" s="109"/>
-      <c r="T144" s="159"/>
+      <c r="T144" s="130"/>
       <c r="U144" s="97"/>
       <c r="V144" s="97"/>
       <c r="W144" s="97"/>
       <c r="X144" s="114"/>
     </row>
     <row r="145" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A145" s="157"/>
+      <c r="A145" s="128"/>
       <c r="B145" s="39">
         <v>139</v>
       </c>
@@ -12951,20 +13005,20 @@
         <v>0</v>
       </c>
       <c r="N145" s="97"/>
-      <c r="O145" s="158"/>
+      <c r="O145" s="129"/>
       <c r="P145" s="51"/>
       <c r="Q145" s="109"/>
       <c r="R145" s="109"/>
       <c r="S145" s="109"/>
-      <c r="T145" s="159"/>
+      <c r="T145" s="130"/>
       <c r="U145" s="97"/>
       <c r="V145" s="97"/>
       <c r="W145" s="97"/>
       <c r="X145" s="114"/>
     </row>
     <row r="146" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A146" s="157"/>
-      <c r="B146" s="167">
+      <c r="A146" s="128"/>
+      <c r="B146" s="39">
         <v>140</v>
       </c>
       <c r="C146" s="98"/>
@@ -12985,20 +13039,20 @@
         <v>0</v>
       </c>
       <c r="N146" s="97"/>
-      <c r="O146" s="158"/>
+      <c r="O146" s="129"/>
       <c r="P146" s="51"/>
       <c r="Q146" s="109"/>
       <c r="R146" s="109"/>
       <c r="S146" s="109"/>
-      <c r="T146" s="159"/>
+      <c r="T146" s="130"/>
       <c r="U146" s="97"/>
       <c r="V146" s="97"/>
       <c r="W146" s="97"/>
       <c r="X146" s="114"/>
     </row>
     <row r="147" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A147" s="157"/>
-      <c r="B147" s="167">
+      <c r="A147" s="128"/>
+      <c r="B147" s="39">
         <v>141</v>
       </c>
       <c r="C147" s="98"/>
@@ -13019,20 +13073,20 @@
         <v>0</v>
       </c>
       <c r="N147" s="97"/>
-      <c r="O147" s="158"/>
+      <c r="O147" s="129"/>
       <c r="P147" s="51"/>
       <c r="Q147" s="109"/>
       <c r="R147" s="109"/>
       <c r="S147" s="109"/>
-      <c r="T147" s="159"/>
+      <c r="T147" s="130"/>
       <c r="U147" s="97"/>
       <c r="V147" s="97"/>
       <c r="W147" s="97"/>
       <c r="X147" s="114"/>
     </row>
     <row r="148" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A148" s="157"/>
-      <c r="B148" s="167">
+      <c r="A148" s="128"/>
+      <c r="B148" s="39">
         <v>142</v>
       </c>
       <c r="C148" s="98"/>
@@ -13053,20 +13107,20 @@
         <v>0</v>
       </c>
       <c r="N148" s="97"/>
-      <c r="O148" s="158"/>
+      <c r="O148" s="129"/>
       <c r="P148" s="51"/>
       <c r="Q148" s="109"/>
       <c r="R148" s="109"/>
       <c r="S148" s="109"/>
-      <c r="T148" s="159"/>
+      <c r="T148" s="130"/>
       <c r="U148" s="97"/>
       <c r="V148" s="97"/>
       <c r="W148" s="97"/>
       <c r="X148" s="114"/>
     </row>
     <row r="149" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A149" s="157"/>
-      <c r="B149" s="167">
+      <c r="A149" s="128"/>
+      <c r="B149" s="39">
         <v>143</v>
       </c>
       <c r="C149" s="98"/>
@@ -13087,20 +13141,20 @@
         <v>0</v>
       </c>
       <c r="N149" s="97"/>
-      <c r="O149" s="158"/>
+      <c r="O149" s="129"/>
       <c r="P149" s="51"/>
       <c r="Q149" s="109"/>
       <c r="R149" s="109"/>
       <c r="S149" s="109"/>
-      <c r="T149" s="159"/>
+      <c r="T149" s="130"/>
       <c r="U149" s="97"/>
       <c r="V149" s="97"/>
       <c r="W149" s="97"/>
       <c r="X149" s="114"/>
     </row>
     <row r="150" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A150" s="157"/>
-      <c r="B150" s="146">
+      <c r="A150" s="128"/>
+      <c r="B150" s="117">
         <v>144</v>
       </c>
       <c r="C150" s="98"/>
@@ -13121,19 +13175,19 @@
         <v>0</v>
       </c>
       <c r="N150" s="97"/>
-      <c r="O150" s="158"/>
+      <c r="O150" s="129"/>
       <c r="P150" s="51"/>
       <c r="Q150" s="109"/>
       <c r="R150" s="109"/>
       <c r="S150" s="109"/>
-      <c r="T150" s="159"/>
+      <c r="T150" s="130"/>
       <c r="U150" s="97"/>
       <c r="V150" s="97"/>
       <c r="W150" s="97"/>
       <c r="X150" s="114"/>
     </row>
     <row r="151" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A151" s="157"/>
+      <c r="A151" s="128"/>
       <c r="B151" s="39">
         <v>145</v>
       </c>
@@ -13155,20 +13209,20 @@
         <v>0</v>
       </c>
       <c r="N151" s="97"/>
-      <c r="O151" s="158"/>
+      <c r="O151" s="129"/>
       <c r="P151" s="51"/>
       <c r="Q151" s="109"/>
       <c r="R151" s="109"/>
       <c r="S151" s="109"/>
-      <c r="T151" s="159"/>
+      <c r="T151" s="130"/>
       <c r="U151" s="97"/>
       <c r="V151" s="97"/>
       <c r="W151" s="97"/>
       <c r="X151" s="114"/>
     </row>
     <row r="152" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A152" s="157"/>
-      <c r="B152" s="167">
+      <c r="A152" s="128"/>
+      <c r="B152" s="39">
         <v>146</v>
       </c>
       <c r="C152" s="98"/>
@@ -13189,20 +13243,20 @@
         <v>0</v>
       </c>
       <c r="N152" s="97"/>
-      <c r="O152" s="158"/>
+      <c r="O152" s="129"/>
       <c r="P152" s="51"/>
       <c r="Q152" s="109"/>
       <c r="R152" s="109"/>
       <c r="S152" s="109"/>
-      <c r="T152" s="159"/>
+      <c r="T152" s="130"/>
       <c r="U152" s="97"/>
       <c r="V152" s="97"/>
       <c r="W152" s="97"/>
       <c r="X152" s="114"/>
     </row>
     <row r="153" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A153" s="157"/>
-      <c r="B153" s="167">
+      <c r="A153" s="128"/>
+      <c r="B153" s="39">
         <v>147</v>
       </c>
       <c r="C153" s="98"/>
@@ -13223,20 +13277,20 @@
         <v>0</v>
       </c>
       <c r="N153" s="97"/>
-      <c r="O153" s="158"/>
+      <c r="O153" s="129"/>
       <c r="P153" s="51"/>
       <c r="Q153" s="109"/>
       <c r="R153" s="109"/>
       <c r="S153" s="109"/>
-      <c r="T153" s="159"/>
+      <c r="T153" s="130"/>
       <c r="U153" s="97"/>
       <c r="V153" s="97"/>
       <c r="W153" s="97"/>
       <c r="X153" s="114"/>
     </row>
     <row r="154" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A154" s="157"/>
-      <c r="B154" s="167">
+      <c r="A154" s="128"/>
+      <c r="B154" s="39">
         <v>148</v>
       </c>
       <c r="C154" s="98"/>
@@ -13257,20 +13311,20 @@
         <v>0</v>
       </c>
       <c r="N154" s="97"/>
-      <c r="O154" s="158"/>
+      <c r="O154" s="129"/>
       <c r="P154" s="51"/>
       <c r="Q154" s="109"/>
       <c r="R154" s="109"/>
       <c r="S154" s="109"/>
-      <c r="T154" s="159"/>
+      <c r="T154" s="130"/>
       <c r="U154" s="97"/>
       <c r="V154" s="97"/>
       <c r="W154" s="97"/>
       <c r="X154" s="114"/>
     </row>
     <row r="155" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A155" s="157"/>
-      <c r="B155" s="167">
+      <c r="A155" s="128"/>
+      <c r="B155" s="39">
         <v>149</v>
       </c>
       <c r="C155" s="98"/>
@@ -13291,20 +13345,20 @@
         <v>0</v>
       </c>
       <c r="N155" s="97"/>
-      <c r="O155" s="158"/>
+      <c r="O155" s="129"/>
       <c r="P155" s="51"/>
       <c r="Q155" s="109"/>
       <c r="R155" s="109"/>
       <c r="S155" s="109"/>
-      <c r="T155" s="159"/>
+      <c r="T155" s="130"/>
       <c r="U155" s="97"/>
       <c r="V155" s="97"/>
       <c r="W155" s="97"/>
       <c r="X155" s="114"/>
     </row>
     <row r="156" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A156" s="157"/>
-      <c r="B156" s="146">
+      <c r="A156" s="128"/>
+      <c r="B156" s="117">
         <v>150</v>
       </c>
       <c r="C156" s="98"/>
@@ -13325,19 +13379,19 @@
         <v>0</v>
       </c>
       <c r="N156" s="97"/>
-      <c r="O156" s="158"/>
+      <c r="O156" s="129"/>
       <c r="P156" s="51"/>
       <c r="Q156" s="109"/>
       <c r="R156" s="109"/>
       <c r="S156" s="109"/>
-      <c r="T156" s="159"/>
+      <c r="T156" s="130"/>
       <c r="U156" s="97"/>
       <c r="V156" s="97"/>
       <c r="W156" s="97"/>
       <c r="X156" s="114"/>
     </row>
     <row r="157" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A157" s="157"/>
+      <c r="A157" s="128"/>
       <c r="B157" s="39">
         <v>151</v>
       </c>
@@ -13359,20 +13413,20 @@
         <v>0</v>
       </c>
       <c r="N157" s="97"/>
-      <c r="O157" s="158"/>
+      <c r="O157" s="129"/>
       <c r="P157" s="51"/>
       <c r="Q157" s="109"/>
       <c r="R157" s="109"/>
       <c r="S157" s="109"/>
-      <c r="T157" s="159"/>
+      <c r="T157" s="130"/>
       <c r="U157" s="97"/>
       <c r="V157" s="97"/>
       <c r="W157" s="97"/>
       <c r="X157" s="114"/>
     </row>
     <row r="158" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A158" s="157"/>
-      <c r="B158" s="167">
+      <c r="A158" s="128"/>
+      <c r="B158" s="39">
         <v>152</v>
       </c>
       <c r="C158" s="98"/>
@@ -13393,20 +13447,20 @@
         <v>0</v>
       </c>
       <c r="N158" s="97"/>
-      <c r="O158" s="158"/>
+      <c r="O158" s="129"/>
       <c r="P158" s="51"/>
       <c r="Q158" s="109"/>
       <c r="R158" s="109"/>
       <c r="S158" s="109"/>
-      <c r="T158" s="159"/>
+      <c r="T158" s="130"/>
       <c r="U158" s="97"/>
       <c r="V158" s="97"/>
       <c r="W158" s="97"/>
       <c r="X158" s="114"/>
     </row>
     <row r="159" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A159" s="157"/>
-      <c r="B159" s="167">
+      <c r="A159" s="128"/>
+      <c r="B159" s="39">
         <v>153</v>
       </c>
       <c r="C159" s="98"/>
@@ -13427,20 +13481,20 @@
         <v>0</v>
       </c>
       <c r="N159" s="97"/>
-      <c r="O159" s="158"/>
+      <c r="O159" s="129"/>
       <c r="P159" s="51"/>
       <c r="Q159" s="109"/>
       <c r="R159" s="109"/>
       <c r="S159" s="109"/>
-      <c r="T159" s="159"/>
+      <c r="T159" s="130"/>
       <c r="U159" s="97"/>
       <c r="V159" s="97"/>
       <c r="W159" s="97"/>
       <c r="X159" s="114"/>
     </row>
     <row r="160" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A160" s="157"/>
-      <c r="B160" s="167">
+      <c r="A160" s="128"/>
+      <c r="B160" s="39">
         <v>154</v>
       </c>
       <c r="C160" s="98"/>
@@ -13461,20 +13515,20 @@
         <v>0</v>
       </c>
       <c r="N160" s="97"/>
-      <c r="O160" s="158"/>
+      <c r="O160" s="129"/>
       <c r="P160" s="51"/>
       <c r="Q160" s="109"/>
       <c r="R160" s="109"/>
       <c r="S160" s="109"/>
-      <c r="T160" s="159"/>
+      <c r="T160" s="130"/>
       <c r="U160" s="97"/>
       <c r="V160" s="97"/>
       <c r="W160" s="97"/>
       <c r="X160" s="114"/>
     </row>
     <row r="161" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A161" s="157"/>
-      <c r="B161" s="167">
+      <c r="A161" s="128"/>
+      <c r="B161" s="39">
         <v>155</v>
       </c>
       <c r="C161" s="98"/>
@@ -13495,20 +13549,20 @@
         <v>0</v>
       </c>
       <c r="N161" s="97"/>
-      <c r="O161" s="158"/>
+      <c r="O161" s="129"/>
       <c r="P161" s="51"/>
       <c r="Q161" s="109"/>
       <c r="R161" s="109"/>
       <c r="S161" s="109"/>
-      <c r="T161" s="159"/>
+      <c r="T161" s="130"/>
       <c r="U161" s="97"/>
       <c r="V161" s="97"/>
       <c r="W161" s="97"/>
       <c r="X161" s="114"/>
     </row>
     <row r="162" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A162" s="157"/>
-      <c r="B162" s="146">
+      <c r="A162" s="128"/>
+      <c r="B162" s="117">
         <v>156</v>
       </c>
       <c r="C162" s="98"/>
@@ -13529,19 +13583,19 @@
         <v>0</v>
       </c>
       <c r="N162" s="97"/>
-      <c r="O162" s="158"/>
+      <c r="O162" s="129"/>
       <c r="P162" s="51"/>
       <c r="Q162" s="109"/>
       <c r="R162" s="109"/>
       <c r="S162" s="109"/>
-      <c r="T162" s="159"/>
+      <c r="T162" s="130"/>
       <c r="U162" s="97"/>
       <c r="V162" s="97"/>
       <c r="W162" s="97"/>
       <c r="X162" s="114"/>
     </row>
     <row r="163" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A163" s="157"/>
+      <c r="A163" s="128"/>
       <c r="B163" s="39">
         <v>157</v>
       </c>
@@ -13563,20 +13617,20 @@
         <v>0</v>
       </c>
       <c r="N163" s="97"/>
-      <c r="O163" s="158"/>
+      <c r="O163" s="129"/>
       <c r="P163" s="51"/>
       <c r="Q163" s="109"/>
       <c r="R163" s="109"/>
       <c r="S163" s="109"/>
-      <c r="T163" s="159"/>
+      <c r="T163" s="130"/>
       <c r="U163" s="97"/>
       <c r="V163" s="97"/>
       <c r="W163" s="97"/>
       <c r="X163" s="114"/>
     </row>
     <row r="164" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A164" s="157"/>
-      <c r="B164" s="167">
+      <c r="A164" s="128"/>
+      <c r="B164" s="39">
         <v>158</v>
       </c>
       <c r="C164" s="98"/>
@@ -13597,20 +13651,20 @@
         <v>0</v>
       </c>
       <c r="N164" s="97"/>
-      <c r="O164" s="158"/>
+      <c r="O164" s="129"/>
       <c r="P164" s="51"/>
       <c r="Q164" s="109"/>
       <c r="R164" s="109"/>
       <c r="S164" s="109"/>
-      <c r="T164" s="159"/>
+      <c r="T164" s="130"/>
       <c r="U164" s="97"/>
       <c r="V164" s="97"/>
       <c r="W164" s="97"/>
       <c r="X164" s="114"/>
     </row>
     <row r="165" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A165" s="157"/>
-      <c r="B165" s="167">
+      <c r="A165" s="128"/>
+      <c r="B165" s="39">
         <v>159</v>
       </c>
       <c r="C165" s="98"/>
@@ -13631,20 +13685,20 @@
         <v>0</v>
       </c>
       <c r="N165" s="97"/>
-      <c r="O165" s="158"/>
+      <c r="O165" s="129"/>
       <c r="P165" s="51"/>
       <c r="Q165" s="109"/>
       <c r="R165" s="109"/>
       <c r="S165" s="109"/>
-      <c r="T165" s="159"/>
+      <c r="T165" s="130"/>
       <c r="U165" s="97"/>
       <c r="V165" s="97"/>
       <c r="W165" s="97"/>
       <c r="X165" s="114"/>
     </row>
     <row r="166" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A166" s="157"/>
-      <c r="B166" s="167">
+      <c r="A166" s="128"/>
+      <c r="B166" s="39">
         <v>160</v>
       </c>
       <c r="C166" s="98"/>
@@ -13665,20 +13719,20 @@
         <v>0</v>
       </c>
       <c r="N166" s="97"/>
-      <c r="O166" s="158"/>
+      <c r="O166" s="129"/>
       <c r="P166" s="51"/>
       <c r="Q166" s="109"/>
       <c r="R166" s="109"/>
       <c r="S166" s="109"/>
-      <c r="T166" s="159"/>
+      <c r="T166" s="130"/>
       <c r="U166" s="97"/>
       <c r="V166" s="97"/>
       <c r="W166" s="97"/>
       <c r="X166" s="114"/>
     </row>
     <row r="167" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A167" s="157"/>
-      <c r="B167" s="167">
+      <c r="A167" s="128"/>
+      <c r="B167" s="39">
         <v>161</v>
       </c>
       <c r="C167" s="98"/>
@@ -13699,20 +13753,20 @@
         <v>0</v>
       </c>
       <c r="N167" s="97"/>
-      <c r="O167" s="158"/>
+      <c r="O167" s="129"/>
       <c r="P167" s="51"/>
       <c r="Q167" s="109"/>
       <c r="R167" s="109"/>
       <c r="S167" s="109"/>
-      <c r="T167" s="159"/>
+      <c r="T167" s="130"/>
       <c r="U167" s="97"/>
       <c r="V167" s="97"/>
       <c r="W167" s="97"/>
       <c r="X167" s="114"/>
     </row>
     <row r="168" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A168" s="157"/>
-      <c r="B168" s="146">
+      <c r="A168" s="128"/>
+      <c r="B168" s="117">
         <v>162</v>
       </c>
       <c r="C168" s="98"/>
@@ -13733,19 +13787,19 @@
         <v>0</v>
       </c>
       <c r="N168" s="97"/>
-      <c r="O168" s="158"/>
+      <c r="O168" s="129"/>
       <c r="P168" s="51"/>
       <c r="Q168" s="109"/>
       <c r="R168" s="109"/>
       <c r="S168" s="109"/>
-      <c r="T168" s="159"/>
+      <c r="T168" s="130"/>
       <c r="U168" s="97"/>
       <c r="V168" s="97"/>
       <c r="W168" s="97"/>
       <c r="X168" s="114"/>
     </row>
     <row r="169" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A169" s="157"/>
+      <c r="A169" s="128"/>
       <c r="B169" s="39">
         <v>163</v>
       </c>
@@ -13767,20 +13821,20 @@
         <v>0</v>
       </c>
       <c r="N169" s="97"/>
-      <c r="O169" s="158"/>
+      <c r="O169" s="129"/>
       <c r="P169" s="51"/>
       <c r="Q169" s="109"/>
       <c r="R169" s="109"/>
       <c r="S169" s="109"/>
-      <c r="T169" s="159"/>
+      <c r="T169" s="130"/>
       <c r="U169" s="97"/>
       <c r="V169" s="97"/>
       <c r="W169" s="97"/>
       <c r="X169" s="114"/>
     </row>
     <row r="170" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A170" s="157"/>
-      <c r="B170" s="167">
+      <c r="A170" s="128"/>
+      <c r="B170" s="39">
         <v>164</v>
       </c>
       <c r="C170" s="98"/>
@@ -13801,20 +13855,20 @@
         <v>0</v>
       </c>
       <c r="N170" s="97"/>
-      <c r="O170" s="158"/>
+      <c r="O170" s="129"/>
       <c r="P170" s="51"/>
       <c r="Q170" s="109"/>
       <c r="R170" s="109"/>
       <c r="S170" s="109"/>
-      <c r="T170" s="159"/>
+      <c r="T170" s="130"/>
       <c r="U170" s="97"/>
       <c r="V170" s="97"/>
       <c r="W170" s="97"/>
       <c r="X170" s="114"/>
     </row>
     <row r="171" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A171" s="157"/>
-      <c r="B171" s="167">
+      <c r="A171" s="128"/>
+      <c r="B171" s="39">
         <v>165</v>
       </c>
       <c r="C171" s="98"/>
@@ -13835,12 +13889,12 @@
         <v>0</v>
       </c>
       <c r="N171" s="97"/>
-      <c r="O171" s="158"/>
+      <c r="O171" s="129"/>
       <c r="P171" s="51"/>
       <c r="Q171" s="109"/>
       <c r="R171" s="109"/>
       <c r="S171" s="109"/>
-      <c r="T171" s="159"/>
+      <c r="T171" s="130"/>
       <c r="U171" s="97"/>
       <c r="V171" s="97"/>
       <c r="W171" s="97"/>
@@ -13848,10 +13902,10 @@
     </row>
     <row r="172" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A172" s="2"/>
-      <c r="B172" s="167">
+      <c r="B172" s="39">
         <v>166</v>
       </c>
-      <c r="C172" s="157"/>
+      <c r="C172" s="128"/>
       <c r="D172" s="39"/>
       <c r="E172" s="98"/>
       <c r="F172" s="98"/>
@@ -13877,7 +13931,7 @@
         <v>0</v>
       </c>
       <c r="P172" s="97"/>
-      <c r="Q172" s="158">
+      <c r="Q172" s="129">
         <f t="shared" si="91"/>
         <v>0</v>
       </c>
@@ -13897,7 +13951,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="V172" s="159" t="e">
+      <c r="V172" s="130" t="e">
         <f t="shared" si="93"/>
         <v>#VALUE!</v>
       </c>
@@ -13909,7 +13963,7 @@
         <f t="shared" si="94"/>
         <v>0</v>
       </c>
-      <c r="Y172" s="145">
+      <c r="Y172" s="116">
         <f t="shared" si="95"/>
         <v>0</v>
       </c>
@@ -13919,11 +13973,11 @@
       </c>
     </row>
     <row r="173" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A173" s="157"/>
-      <c r="B173" s="126" t="s">
+      <c r="A173" s="128"/>
+      <c r="B173" s="147" t="s">
         <v>11</v>
       </c>
-      <c r="C173" s="126"/>
+      <c r="C173" s="147"/>
       <c r="D173" s="106"/>
       <c r="E173" s="111">
         <f t="shared" ref="E173:K173" si="104">SUM(E6:E63)</f>
@@ -13962,7 +14016,7 @@
         <v>0</v>
       </c>
       <c r="N173" s="97"/>
-      <c r="O173" s="158">
+      <c r="O173" s="129">
         <f t="shared" ref="O173:O177" si="106">SUM(F173:H173)/20</f>
         <v>267.10000000000002</v>
       </c>
@@ -13982,7 +14036,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T173" s="159" t="e">
+      <c r="T173" s="130" t="e">
         <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
@@ -14004,7 +14058,7 @@
       </c>
     </row>
     <row r="174" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A174" s="157"/>
+      <c r="A174" s="128"/>
       <c r="B174" s="39">
         <v>0</v>
       </c>
@@ -14012,32 +14066,32 @@
         <v>67</v>
       </c>
       <c r="D174" s="98"/>
-      <c r="E174" s="160"/>
-      <c r="F174" s="160"/>
-      <c r="G174" s="160"/>
-      <c r="H174" s="160"/>
-      <c r="I174" s="160"/>
-      <c r="J174" s="160"/>
-      <c r="K174" s="160"/>
+      <c r="E174" s="131"/>
+      <c r="F174" s="131"/>
+      <c r="G174" s="131"/>
+      <c r="H174" s="131"/>
+      <c r="I174" s="131"/>
+      <c r="J174" s="131"/>
+      <c r="K174" s="131"/>
       <c r="L174" s="109">
         <f>SUM(E174:K174)</f>
         <v>0</v>
       </c>
       <c r="M174" s="109"/>
       <c r="N174" s="97"/>
-      <c r="O174" s="158"/>
+      <c r="O174" s="129"/>
       <c r="P174" s="51"/>
       <c r="Q174" s="109"/>
       <c r="R174" s="109"/>
       <c r="S174" s="109"/>
-      <c r="T174" s="159"/>
+      <c r="T174" s="130"/>
       <c r="U174" s="97"/>
       <c r="V174" s="97"/>
       <c r="W174" s="97"/>
       <c r="X174" s="114"/>
     </row>
     <row r="175" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A175" s="157"/>
+      <c r="A175" s="128"/>
       <c r="B175" s="39">
         <v>1</v>
       </c>
@@ -14064,7 +14118,7 @@
         <f>SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
         <v>3.5513000000000003</v>
       </c>
-      <c r="O175" s="158">
+      <c r="O175" s="129">
         <f t="shared" si="106"/>
         <v>0</v>
       </c>
@@ -14084,7 +14138,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T175" s="159" t="e">
+      <c r="T175" s="130" t="e">
         <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
@@ -14133,7 +14187,7 @@
         <f>SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
         <v>3.5513000000000003</v>
       </c>
-      <c r="O176" s="158">
+      <c r="O176" s="129">
         <f t="shared" si="106"/>
         <v>0</v>
       </c>
@@ -14153,7 +14207,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T176" s="159" t="e">
+      <c r="T176" s="130" t="e">
         <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
@@ -14176,10 +14230,10 @@
     </row>
     <row r="177" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A177" s="2"/>
-      <c r="B177" s="126" t="s">
+      <c r="B177" s="147" t="s">
         <v>68</v>
       </c>
-      <c r="C177" s="126"/>
+      <c r="C177" s="147"/>
       <c r="D177" s="106"/>
       <c r="E177" s="113">
         <f>SUM(E175:E176)</f>
@@ -14221,7 +14275,7 @@
         <f>SUMPRODUCT($E$3:$K$3,$E$6:$K$6)/1000</f>
         <v>3.5513000000000003</v>
       </c>
-      <c r="O177" s="158">
+      <c r="O177" s="129">
         <f t="shared" si="106"/>
         <v>0</v>
       </c>
@@ -14241,7 +14295,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T177" s="159" t="e">
+      <c r="T177" s="130" t="e">
         <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
@@ -14264,36 +14318,36 @@
     </row>
     <row r="178" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A178" s="2"/>
-      <c r="B178" s="161" t="s">
+      <c r="B178" s="137" t="s">
         <v>11</v>
       </c>
-      <c r="C178" s="161"/>
-      <c r="D178" s="162"/>
-      <c r="E178" s="163">
+      <c r="C178" s="137"/>
+      <c r="D178" s="132"/>
+      <c r="E178" s="133">
         <f>SUM(E173,E177)</f>
         <v>0</v>
       </c>
-      <c r="F178" s="163">
+      <c r="F178" s="133">
         <f t="shared" ref="F178:K178" si="111">SUM(F173,F177)</f>
         <v>1301</v>
       </c>
-      <c r="G178" s="163">
+      <c r="G178" s="133">
         <f t="shared" si="111"/>
         <v>1190</v>
       </c>
-      <c r="H178" s="163">
+      <c r="H178" s="133">
         <f t="shared" si="111"/>
         <v>2851</v>
       </c>
-      <c r="I178" s="163">
+      <c r="I178" s="133">
         <f t="shared" si="111"/>
         <v>2435</v>
       </c>
-      <c r="J178" s="163">
+      <c r="J178" s="133">
         <f t="shared" si="111"/>
         <v>2877</v>
       </c>
-      <c r="K178" s="163">
+      <c r="K178" s="133">
         <f t="shared" si="111"/>
         <v>3400</v>
       </c>
@@ -14301,9 +14355,9 @@
         <f>SUM(E178:K178)/40</f>
         <v>351.35</v>
       </c>
-      <c r="M178" s="164">
+      <c r="M178" s="134">
         <f>SUM(M5:M177)</f>
-        <v>1990.5</v>
+        <v>2027.5</v>
       </c>
       <c r="N178" s="39">
         <f t="shared" ref="N178:X178" si="112">SUM(N5:N177)</f>
@@ -14317,19 +14371,19 @@
         <f t="shared" si="112"/>
         <v>3257.8999999999996</v>
       </c>
-      <c r="Q178" s="164" t="e">
+      <c r="Q178" s="134" t="e">
         <f t="shared" si="112"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R178" s="164">
+      <c r="R178" s="134">
         <f t="shared" si="112"/>
         <v>0</v>
       </c>
-      <c r="S178" s="164" t="e">
+      <c r="S178" s="134" t="e">
         <f t="shared" si="112"/>
         <v>#VALUE!</v>
       </c>
-      <c r="T178" s="165" t="e">
+      <c r="T178" s="135" t="e">
         <f t="shared" si="112"/>
         <v>#VALUE!</v>
       </c>
@@ -14352,17 +14406,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B173:C173"/>
     <mergeCell ref="B178:C178"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B177:C177"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B173:C173"/>
   </mergeCells>
   <conditionalFormatting sqref="C48:D62">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -14398,25 +14452,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="138" t="s">
+      <c r="C3" s="160" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="142" t="s">
+      <c r="D3" s="161"/>
+      <c r="E3" s="161"/>
+      <c r="F3" s="161"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="164" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="143"/>
-      <c r="K3" s="144" t="s">
+      <c r="I3" s="165"/>
+      <c r="K3" s="166" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="144"/>
-      <c r="M3" s="144"/>
-      <c r="N3" s="144"/>
-      <c r="O3" s="144"/>
-      <c r="P3" s="144"/>
+      <c r="L3" s="166"/>
+      <c r="M3" s="166"/>
+      <c r="N3" s="166"/>
+      <c r="O3" s="166"/>
+      <c r="P3" s="166"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="71"/>
@@ -14462,24 +14516,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="60">
-        <v>547</v>
+        <v>657</v>
       </c>
       <c r="E5" s="54">
-        <v>1323</v>
+        <v>1556</v>
       </c>
       <c r="F5" s="54">
         <v>595</v>
       </c>
       <c r="G5" s="74">
         <f>SUM(D5:F5)</f>
-        <v>2465</v>
+        <v>2808</v>
       </c>
       <c r="H5" s="67">
         <v>10000</v>
       </c>
       <c r="I5" s="68">
         <f>G5-H5</f>
-        <v>-7535</v>
+        <v>-7192</v>
       </c>
       <c r="K5" s="103" t="s">
         <v>1</v>
@@ -14510,11 +14564,11 @@
       </c>
       <c r="D6" s="76">
         <f>D5*40</f>
-        <v>21880</v>
+        <v>26280</v>
       </c>
       <c r="E6" s="76">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>52920</v>
+        <v>62240</v>
       </c>
       <c r="F6" s="76">
         <f t="shared" si="1"/>
@@ -14522,7 +14576,7 @@
       </c>
       <c r="G6" s="77">
         <f>SUM(D6:F6)</f>
-        <v>98600</v>
+        <v>112320</v>
       </c>
       <c r="H6" s="69">
         <f>H5*40</f>
@@ -14530,7 +14584,7 @@
       </c>
       <c r="I6" s="70">
         <f>G6-H6</f>
-        <v>-301400</v>
+        <v>-287680</v>
       </c>
       <c r="K6" s="103" t="s">
         <v>2</v>
@@ -14679,11 +14733,11 @@
       </c>
       <c r="D9" s="78">
         <f>D8-D5</f>
-        <v>-547</v>
+        <v>-657</v>
       </c>
       <c r="E9" s="78">
         <f>E8-E5</f>
-        <v>-1323</v>
+        <v>-1556</v>
       </c>
       <c r="K9" s="103" t="s">
         <v>5</v>
@@ -14781,14 +14835,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="141" t="s">
+      <c r="C11" s="163" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="141"/>
-      <c r="F11" s="141" t="s">
+      <c r="D11" s="163"/>
+      <c r="F11" s="163" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="141"/>
+      <c r="G11" s="163"/>
       <c r="K11" s="103" t="s">
         <v>7</v>
       </c>
@@ -14838,7 +14892,7 @@
       </c>
       <c r="G12" s="63">
         <f>D12+G5</f>
-        <v>6665</v>
+        <v>7008</v>
       </c>
       <c r="K12" s="103" t="s">
         <v>11</v>
@@ -14890,12 +14944,12 @@
       </c>
       <c r="G13" s="63">
         <f>G12*40</f>
-        <v>266600</v>
-      </c>
-      <c r="S13" s="136" t="s">
+        <v>280320</v>
+      </c>
+      <c r="S13" s="158" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="136"/>
+      <c r="T13" s="158"/>
       <c r="U13" s="93">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -15002,13 +15056,13 @@
       </c>
     </row>
     <row r="20" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="137" t="s">
+      <c r="D20" s="159" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="137"/>
-      <c r="F20" s="137"/>
-      <c r="G20" s="137"/>
-      <c r="H20" s="137"/>
+      <c r="E20" s="159"/>
+      <c r="F20" s="159"/>
+      <c r="G20" s="159"/>
+      <c r="H20" s="159"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DC001C-3466-4FEE-A966-DD03D0A3E7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72B87F8-C625-4F8D-8EAB-BA05C8ED7265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="268">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -817,6 +817,15 @@
   </si>
   <si>
     <t xml:space="preserve">Galaxy Super Market </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Season </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KK Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gajumata </t>
   </si>
 </sst>
 </file>
@@ -1610,7 +1619,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1965,9 +1974,10 @@
     <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2057,27 +2067,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2450,7 +2439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B7:F24"/>
@@ -2661,6 +2650,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:Z178"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2671,13 +2661,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="148">
+      <c r="B1" s="149">
         <f ca="1">TODAY()</f>
-        <v>46319</v>
-      </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
+        <v>46321</v>
+      </c>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2699,10 +2689,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="146" t="s">
+      <c r="A2" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="149" t="s">
+      <c r="B2" s="150" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2732,13 +2722,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="138"/>
-      <c r="M2" s="139"/>
-      <c r="N2" s="140"/>
-      <c r="O2" s="141" t="s">
+      <c r="L2" s="139"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="142" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="142"/>
+      <c r="P2" s="143"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2757,8 +2747,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="146"/>
-      <c r="B3" s="150"/>
+      <c r="A3" s="147"/>
+      <c r="B3" s="151"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2786,29 +2776,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="143" t="s">
+      <c r="L3" s="144" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="144"/>
-      <c r="N3" s="145"/>
+      <c r="M3" s="145"/>
+      <c r="N3" s="146"/>
       <c r="O3" s="48"/>
       <c r="P3" s="49"/>
-      <c r="Q3" s="152" t="s">
+      <c r="Q3" s="153" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="153"/>
-      <c r="S3" s="153"/>
-      <c r="T3" s="154"/>
-      <c r="U3" s="155" t="s">
+      <c r="R3" s="154"/>
+      <c r="S3" s="154"/>
+      <c r="T3" s="155"/>
+      <c r="U3" s="156" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="156"/>
-      <c r="W3" s="156"/>
-      <c r="X3" s="157"/>
+      <c r="V3" s="157"/>
+      <c r="W3" s="157"/>
+      <c r="X3" s="158"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="146"/>
-      <c r="B4" s="151"/>
+      <c r="A4" s="147"/>
+      <c r="B4" s="152"/>
       <c r="C4" s="101" t="s">
         <v>90</v>
       </c>
@@ -12362,35 +12352,35 @@
       </c>
     </row>
     <row r="132" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A132" s="167">
+      <c r="A132" s="53">
         <v>46317</v>
       </c>
-      <c r="B132" s="168">
+      <c r="B132" s="117">
         <v>126</v>
       </c>
-      <c r="C132" s="169" t="s">
+      <c r="C132" s="136" t="s">
         <v>259</v>
       </c>
-      <c r="D132" s="169" t="s">
+      <c r="D132" s="136" t="s">
         <v>260</v>
       </c>
-      <c r="E132" s="170"/>
-      <c r="F132" s="170">
+      <c r="E132" s="137"/>
+      <c r="F132" s="137">
         <v>79</v>
       </c>
-      <c r="G132" s="170">
+      <c r="G132" s="137">
         <v>80</v>
       </c>
-      <c r="H132" s="171">
+      <c r="H132" s="118">
         <v>79</v>
       </c>
-      <c r="I132" s="170">
+      <c r="I132" s="137">
         <v>79</v>
       </c>
-      <c r="J132" s="170">
+      <c r="J132" s="137">
         <v>78</v>
       </c>
-      <c r="K132" s="170">
+      <c r="K132" s="137">
         <v>79</v>
       </c>
       <c r="L132" s="118">
@@ -12443,35 +12433,35 @@
       </c>
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A133" s="167">
+      <c r="A133" s="53">
         <v>46317</v>
       </c>
-      <c r="B133" s="172">
+      <c r="B133" s="39">
         <v>127</v>
       </c>
-      <c r="C133" s="173" t="s">
+      <c r="C133" s="98" t="s">
         <v>261</v>
       </c>
-      <c r="D133" s="173" t="s">
+      <c r="D133" s="98" t="s">
         <v>121</v>
       </c>
-      <c r="E133" s="174"/>
-      <c r="F133" s="174">
+      <c r="E133" s="51"/>
+      <c r="F133" s="51">
         <v>80</v>
       </c>
-      <c r="G133" s="174">
+      <c r="G133" s="51">
         <v>80</v>
       </c>
-      <c r="H133" s="175">
+      <c r="H133" s="97">
         <v>80</v>
       </c>
-      <c r="I133" s="174">
+      <c r="I133" s="51">
         <v>80</v>
       </c>
-      <c r="J133" s="174">
+      <c r="J133" s="51">
         <v>80</v>
       </c>
-      <c r="K133" s="174">
+      <c r="K133" s="51">
         <v>80</v>
       </c>
       <c r="L133" s="97">
@@ -12524,35 +12514,35 @@
       </c>
     </row>
     <row r="134" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A134" s="167">
+      <c r="A134" s="53">
         <v>46317</v>
       </c>
-      <c r="B134" s="172">
+      <c r="B134" s="39">
         <v>128</v>
       </c>
-      <c r="C134" s="173" t="s">
+      <c r="C134" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="D134" s="173" t="s">
+      <c r="D134" s="98" t="s">
         <v>262</v>
       </c>
-      <c r="E134" s="174"/>
-      <c r="F134" s="174">
+      <c r="E134" s="51"/>
+      <c r="F134" s="51">
         <v>1000</v>
       </c>
-      <c r="G134" s="174">
+      <c r="G134" s="51">
         <v>1000</v>
       </c>
-      <c r="H134" s="175">
+      <c r="H134" s="97">
         <v>1000</v>
       </c>
-      <c r="I134" s="174">
+      <c r="I134" s="51">
         <v>1000</v>
       </c>
-      <c r="J134" s="174">
+      <c r="J134" s="51">
         <v>1000</v>
       </c>
-      <c r="K134" s="174">
+      <c r="K134" s="51">
         <v>1000</v>
       </c>
       <c r="L134" s="97">
@@ -12575,29 +12565,29 @@
       <c r="X134" s="114"/>
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A135" s="167">
+      <c r="A135" s="53">
         <v>46317</v>
       </c>
-      <c r="B135" s="172">
+      <c r="B135" s="39">
         <v>129</v>
       </c>
-      <c r="C135" s="173" t="s">
+      <c r="C135" s="98" t="s">
         <v>151</v>
       </c>
-      <c r="D135" s="173" t="s">
+      <c r="D135" s="98" t="s">
         <v>152</v>
       </c>
-      <c r="E135" s="174"/>
-      <c r="F135" s="174">
+      <c r="E135" s="51"/>
+      <c r="F135" s="51">
         <v>120</v>
       </c>
-      <c r="G135" s="174"/>
-      <c r="H135" s="175"/>
-      <c r="I135" s="174">
+      <c r="G135" s="51"/>
+      <c r="H135" s="97"/>
+      <c r="I135" s="51">
         <v>120</v>
       </c>
-      <c r="J135" s="174"/>
-      <c r="K135" s="174">
+      <c r="J135" s="51"/>
+      <c r="K135" s="51">
         <v>80</v>
       </c>
       <c r="L135" s="97">
@@ -12620,38 +12610,38 @@
       <c r="X135" s="114"/>
     </row>
     <row r="136" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A136" s="105">
+      <c r="A136" s="53">
         <v>46318</v>
       </c>
-      <c r="B136" s="106">
+      <c r="B136" s="39">
         <v>130</v>
       </c>
-      <c r="C136" s="115" t="s">
+      <c r="C136" s="98" t="s">
         <v>263</v>
       </c>
-      <c r="D136" s="115" t="s">
+      <c r="D136" s="98" t="s">
         <v>202</v>
       </c>
-      <c r="E136" s="113"/>
-      <c r="F136" s="113">
+      <c r="E136" s="51"/>
+      <c r="F136" s="51">
         <v>160</v>
       </c>
-      <c r="G136" s="113">
+      <c r="G136" s="51">
         <v>160</v>
       </c>
-      <c r="H136" s="114">
+      <c r="H136" s="97">
         <v>200</v>
       </c>
-      <c r="I136" s="113">
+      <c r="I136" s="51">
         <v>200</v>
       </c>
-      <c r="J136" s="113">
+      <c r="J136" s="51">
         <v>200</v>
       </c>
-      <c r="K136" s="113">
+      <c r="K136" s="51">
         <v>300</v>
       </c>
-      <c r="L136" s="114">
+      <c r="L136" s="97">
         <f t="shared" si="102"/>
         <v>30.5</v>
       </c>
@@ -12671,38 +12661,38 @@
       <c r="X136" s="114"/>
     </row>
     <row r="137" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A137" s="105">
+      <c r="A137" s="53">
         <v>46318</v>
       </c>
-      <c r="B137" s="106">
+      <c r="B137" s="39">
         <v>131</v>
       </c>
-      <c r="C137" s="115" t="s">
+      <c r="C137" s="98" t="s">
         <v>264</v>
       </c>
-      <c r="D137" s="115" t="s">
+      <c r="D137" s="98" t="s">
         <v>160</v>
       </c>
-      <c r="E137" s="113"/>
-      <c r="F137" s="113">
-        <v>40</v>
-      </c>
-      <c r="G137" s="113">
-        <v>40</v>
-      </c>
-      <c r="H137" s="114">
-        <v>40</v>
-      </c>
-      <c r="I137" s="113">
-        <v>40</v>
-      </c>
-      <c r="J137" s="113">
-        <v>40</v>
-      </c>
-      <c r="K137" s="113">
-        <v>40</v>
-      </c>
-      <c r="L137" s="114">
+      <c r="E137" s="51"/>
+      <c r="F137" s="51">
+        <v>40</v>
+      </c>
+      <c r="G137" s="51">
+        <v>40</v>
+      </c>
+      <c r="H137" s="97">
+        <v>40</v>
+      </c>
+      <c r="I137" s="51">
+        <v>40</v>
+      </c>
+      <c r="J137" s="51">
+        <v>40</v>
+      </c>
+      <c r="K137" s="51">
+        <v>40</v>
+      </c>
+      <c r="L137" s="97">
         <f t="shared" si="102"/>
         <v>6</v>
       </c>
@@ -12722,38 +12712,38 @@
       <c r="X137" s="114"/>
     </row>
     <row r="138" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A138" s="105">
+      <c r="A138" s="53">
         <v>46318</v>
       </c>
-      <c r="B138" s="136">
+      <c r="B138" s="117">
         <v>132</v>
       </c>
-      <c r="C138" s="115" t="s">
+      <c r="C138" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="D138" s="115" t="s">
+      <c r="D138" s="98" t="s">
         <v>114</v>
       </c>
-      <c r="E138" s="113"/>
-      <c r="F138" s="113">
+      <c r="E138" s="51"/>
+      <c r="F138" s="51">
         <v>120</v>
       </c>
-      <c r="G138" s="113">
+      <c r="G138" s="51">
         <v>80</v>
       </c>
-      <c r="H138" s="114">
+      <c r="H138" s="97">
         <v>80</v>
       </c>
-      <c r="I138" s="113">
+      <c r="I138" s="51">
         <v>120</v>
       </c>
-      <c r="J138" s="113">
+      <c r="J138" s="51">
         <v>80</v>
       </c>
-      <c r="K138" s="113">
+      <c r="K138" s="51">
         <v>120</v>
       </c>
-      <c r="L138" s="114">
+      <c r="L138" s="97">
         <f t="shared" si="102"/>
         <v>15</v>
       </c>
@@ -12774,27 +12764,40 @@
     </row>
     <row r="139" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A139" s="105">
-        <v>46318</v>
-      </c>
-      <c r="B139" s="39">
+        <v>46319</v>
+      </c>
+      <c r="B139" s="106">
         <v>133</v>
       </c>
-      <c r="C139" s="98"/>
-      <c r="D139" s="98"/>
-      <c r="E139" s="51"/>
-      <c r="F139" s="51"/>
-      <c r="G139" s="51"/>
-      <c r="H139" s="97"/>
-      <c r="I139" s="51"/>
-      <c r="J139" s="51"/>
-      <c r="K139" s="51"/>
-      <c r="L139" s="97">
+      <c r="C139" s="115" t="s">
+        <v>265</v>
+      </c>
+      <c r="D139" s="115" t="s">
+        <v>160</v>
+      </c>
+      <c r="E139" s="113"/>
+      <c r="F139" s="113"/>
+      <c r="G139" s="113">
+        <v>120</v>
+      </c>
+      <c r="H139" s="114">
+        <v>80</v>
+      </c>
+      <c r="I139" s="113">
+        <v>200</v>
+      </c>
+      <c r="J139" s="113">
+        <v>120</v>
+      </c>
+      <c r="K139" s="113">
+        <v>200</v>
+      </c>
+      <c r="L139" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M139" s="109">
-        <f t="shared" ref="M136:O173" si="103">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N139" s="97"/>
       <c r="O139" s="129"/>
@@ -12810,27 +12813,40 @@
     </row>
     <row r="140" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A140" s="105">
-        <v>46317</v>
-      </c>
-      <c r="B140" s="39">
+        <v>46319</v>
+      </c>
+      <c r="B140" s="106">
         <v>134</v>
       </c>
-      <c r="C140" s="98"/>
-      <c r="D140" s="98"/>
-      <c r="E140" s="51"/>
-      <c r="F140" s="51"/>
-      <c r="G140" s="51"/>
-      <c r="H140" s="97"/>
-      <c r="I140" s="51"/>
-      <c r="J140" s="51"/>
-      <c r="K140" s="51"/>
-      <c r="L140" s="97">
+      <c r="C140" s="115" t="s">
+        <v>23</v>
+      </c>
+      <c r="D140" s="115" t="s">
+        <v>112</v>
+      </c>
+      <c r="E140" s="113"/>
+      <c r="F140" s="113">
+        <v>40</v>
+      </c>
+      <c r="G140" s="113">
+        <v>77</v>
+      </c>
+      <c r="H140" s="114"/>
+      <c r="I140" s="113">
+        <v>119</v>
+      </c>
+      <c r="J140" s="113">
+        <v>80</v>
+      </c>
+      <c r="K140" s="113">
+        <v>118</v>
+      </c>
+      <c r="L140" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>10.85</v>
       </c>
       <c r="M140" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N140" s="97"/>
       <c r="O140" s="129"/>
@@ -12846,27 +12862,36 @@
     </row>
     <row r="141" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A141" s="105">
-        <v>46317</v>
-      </c>
-      <c r="B141" s="39">
+        <v>46319</v>
+      </c>
+      <c r="B141" s="106">
         <v>135</v>
       </c>
-      <c r="C141" s="98"/>
-      <c r="D141" s="98"/>
-      <c r="E141" s="51"/>
-      <c r="F141" s="51"/>
-      <c r="G141" s="51"/>
-      <c r="H141" s="97"/>
-      <c r="I141" s="51"/>
-      <c r="J141" s="51"/>
-      <c r="K141" s="51"/>
-      <c r="L141" s="97">
+      <c r="C141" s="115" t="s">
+        <v>113</v>
+      </c>
+      <c r="D141" s="115" t="s">
+        <v>160</v>
+      </c>
+      <c r="E141" s="113"/>
+      <c r="F141" s="113"/>
+      <c r="G141" s="113"/>
+      <c r="H141" s="114"/>
+      <c r="I141" s="113">
+        <v>40</v>
+      </c>
+      <c r="J141" s="113">
+        <v>40</v>
+      </c>
+      <c r="K141" s="113">
+        <v>120</v>
+      </c>
+      <c r="L141" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M141" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N141" s="97"/>
       <c r="O141" s="129"/>
@@ -12881,26 +12906,43 @@
       <c r="X141" s="114"/>
     </row>
     <row r="142" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A142" s="128"/>
-      <c r="B142" s="39">
+      <c r="A142" s="105">
+        <v>46319</v>
+      </c>
+      <c r="B142" s="106">
         <v>136</v>
       </c>
-      <c r="C142" s="98"/>
-      <c r="D142" s="98"/>
-      <c r="E142" s="51"/>
-      <c r="F142" s="51"/>
-      <c r="G142" s="51"/>
-      <c r="H142" s="97"/>
-      <c r="I142" s="51"/>
-      <c r="J142" s="51"/>
-      <c r="K142" s="51"/>
-      <c r="L142" s="97">
+      <c r="C142" s="115" t="s">
+        <v>266</v>
+      </c>
+      <c r="D142" s="115" t="s">
+        <v>158</v>
+      </c>
+      <c r="E142" s="113"/>
+      <c r="F142" s="113">
+        <v>144</v>
+      </c>
+      <c r="G142" s="113">
+        <v>287</v>
+      </c>
+      <c r="H142" s="114">
+        <v>288</v>
+      </c>
+      <c r="I142" s="113">
+        <v>432</v>
+      </c>
+      <c r="J142" s="113">
+        <v>288</v>
+      </c>
+      <c r="K142" s="113">
+        <v>432</v>
+      </c>
+      <c r="L142" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>46.774999999999999</v>
       </c>
       <c r="M142" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="N142" s="97"/>
       <c r="O142" s="129"/>
@@ -12915,26 +12957,41 @@
       <c r="X142" s="114"/>
     </row>
     <row r="143" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A143" s="128"/>
-      <c r="B143" s="39">
+      <c r="A143" s="105">
+        <v>46319</v>
+      </c>
+      <c r="B143" s="106">
         <v>137</v>
       </c>
-      <c r="C143" s="98"/>
-      <c r="D143" s="98"/>
-      <c r="E143" s="51"/>
-      <c r="F143" s="51"/>
-      <c r="G143" s="51"/>
-      <c r="H143" s="97"/>
-      <c r="I143" s="51"/>
-      <c r="J143" s="51"/>
-      <c r="K143" s="51"/>
-      <c r="L143" s="97">
+      <c r="C143" s="115" t="s">
+        <v>240</v>
+      </c>
+      <c r="D143" s="115" t="s">
+        <v>267</v>
+      </c>
+      <c r="E143" s="113"/>
+      <c r="F143" s="113"/>
+      <c r="G143" s="113">
+        <v>198</v>
+      </c>
+      <c r="H143" s="114">
+        <v>80</v>
+      </c>
+      <c r="I143" s="113">
+        <v>120</v>
+      </c>
+      <c r="J143" s="113">
+        <v>240</v>
+      </c>
+      <c r="K143" s="113">
+        <v>80</v>
+      </c>
+      <c r="L143" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>17.95</v>
       </c>
       <c r="M143" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N143" s="97"/>
       <c r="O143" s="129"/>
@@ -12967,7 +13024,7 @@
         <v>0</v>
       </c>
       <c r="M144" s="109">
-        <f t="shared" si="103"/>
+        <f t="shared" ref="M144:O173" si="103">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N144" s="97"/>
@@ -13974,10 +14031,10 @@
     </row>
     <row r="173" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A173" s="128"/>
-      <c r="B173" s="147" t="s">
+      <c r="B173" s="148" t="s">
         <v>11</v>
       </c>
-      <c r="C173" s="147"/>
+      <c r="C173" s="148"/>
       <c r="D173" s="106"/>
       <c r="E173" s="111">
         <f t="shared" ref="E173:K173" si="104">SUM(E6:E63)</f>
@@ -14230,10 +14287,10 @@
     </row>
     <row r="177" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A177" s="2"/>
-      <c r="B177" s="147" t="s">
+      <c r="B177" s="148" t="s">
         <v>68</v>
       </c>
-      <c r="C177" s="147"/>
+      <c r="C177" s="148"/>
       <c r="D177" s="106"/>
       <c r="E177" s="113">
         <f>SUM(E175:E176)</f>
@@ -14318,10 +14375,10 @@
     </row>
     <row r="178" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A178" s="2"/>
-      <c r="B178" s="137" t="s">
+      <c r="B178" s="138" t="s">
         <v>11</v>
       </c>
-      <c r="C178" s="137"/>
+      <c r="C178" s="138"/>
       <c r="D178" s="132"/>
       <c r="E178" s="133">
         <f>SUM(E173,E177)</f>
@@ -14357,7 +14414,7 @@
       </c>
       <c r="M178" s="134">
         <f>SUM(M5:M177)</f>
-        <v>2027.5</v>
+        <v>2095</v>
       </c>
       <c r="N178" s="39">
         <f t="shared" ref="N178:X178" si="112">SUM(N5:N177)</f>
@@ -14428,6 +14485,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="C2:Z29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -14452,25 +14510,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="160" t="s">
+      <c r="C3" s="161" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="161"/>
-      <c r="E3" s="161"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="162"/>
-      <c r="H3" s="164" t="s">
+      <c r="D3" s="162"/>
+      <c r="E3" s="162"/>
+      <c r="F3" s="162"/>
+      <c r="G3" s="163"/>
+      <c r="H3" s="165" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="165"/>
-      <c r="K3" s="166" t="s">
+      <c r="I3" s="166"/>
+      <c r="K3" s="167" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="166"/>
-      <c r="M3" s="166"/>
-      <c r="N3" s="166"/>
-      <c r="O3" s="166"/>
-      <c r="P3" s="166"/>
+      <c r="L3" s="167"/>
+      <c r="M3" s="167"/>
+      <c r="N3" s="167"/>
+      <c r="O3" s="167"/>
+      <c r="P3" s="167"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="71"/>
@@ -14516,24 +14574,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="60">
-        <v>657</v>
+        <v>685</v>
       </c>
       <c r="E5" s="54">
-        <v>1556</v>
+        <v>1655</v>
       </c>
       <c r="F5" s="54">
         <v>595</v>
       </c>
       <c r="G5" s="74">
         <f>SUM(D5:F5)</f>
-        <v>2808</v>
+        <v>2935</v>
       </c>
       <c r="H5" s="67">
         <v>10000</v>
       </c>
       <c r="I5" s="68">
         <f>G5-H5</f>
-        <v>-7192</v>
+        <v>-7065</v>
       </c>
       <c r="K5" s="103" t="s">
         <v>1</v>
@@ -14564,11 +14622,11 @@
       </c>
       <c r="D6" s="76">
         <f>D5*40</f>
-        <v>26280</v>
+        <v>27400</v>
       </c>
       <c r="E6" s="76">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>62240</v>
+        <v>66200</v>
       </c>
       <c r="F6" s="76">
         <f t="shared" si="1"/>
@@ -14576,7 +14634,7 @@
       </c>
       <c r="G6" s="77">
         <f>SUM(D6:F6)</f>
-        <v>112320</v>
+        <v>117400</v>
       </c>
       <c r="H6" s="69">
         <f>H5*40</f>
@@ -14584,7 +14642,7 @@
       </c>
       <c r="I6" s="70">
         <f>G6-H6</f>
-        <v>-287680</v>
+        <v>-282600</v>
       </c>
       <c r="K6" s="103" t="s">
         <v>2</v>
@@ -14733,11 +14791,11 @@
       </c>
       <c r="D9" s="78">
         <f>D8-D5</f>
-        <v>-657</v>
+        <v>-685</v>
       </c>
       <c r="E9" s="78">
         <f>E8-E5</f>
-        <v>-1556</v>
+        <v>-1655</v>
       </c>
       <c r="K9" s="103" t="s">
         <v>5</v>
@@ -14835,14 +14893,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="163" t="s">
+      <c r="C11" s="164" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="163"/>
-      <c r="F11" s="163" t="s">
+      <c r="D11" s="164"/>
+      <c r="F11" s="164" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="163"/>
+      <c r="G11" s="164"/>
       <c r="K11" s="103" t="s">
         <v>7</v>
       </c>
@@ -14892,7 +14950,7 @@
       </c>
       <c r="G12" s="63">
         <f>D12+G5</f>
-        <v>7008</v>
+        <v>7135</v>
       </c>
       <c r="K12" s="103" t="s">
         <v>11</v>
@@ -14944,12 +15002,12 @@
       </c>
       <c r="G13" s="63">
         <f>G12*40</f>
-        <v>280320</v>
-      </c>
-      <c r="S13" s="158" t="s">
+        <v>285400</v>
+      </c>
+      <c r="S13" s="159" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="158"/>
+      <c r="T13" s="159"/>
       <c r="U13" s="93">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -15056,13 +15114,13 @@
       </c>
     </row>
     <row r="20" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="159" t="s">
+      <c r="D20" s="160" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="159"/>
-      <c r="F20" s="159"/>
-      <c r="G20" s="159"/>
-      <c r="H20" s="159"/>
+      <c r="E20" s="160"/>
+      <c r="F20" s="160"/>
+      <c r="G20" s="160"/>
+      <c r="H20" s="160"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72B87F8-C625-4F8D-8EAB-BA05C8ED7265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B072804-EBDB-4E61-A721-83631E4674C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="271">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -826,6 +826,15 @@
   </si>
   <si>
     <t xml:space="preserve">Gajumata </t>
+  </si>
+  <si>
+    <t>Euro Mega Store</t>
+  </si>
+  <si>
+    <t>DHA Phase 8</t>
+  </si>
+  <si>
+    <t>Askari 10</t>
   </si>
 </sst>
 </file>
@@ -1619,7 +1628,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1978,6 +1987,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2008,39 +2050,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2067,6 +2076,20 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2661,13 +2684,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="149">
+      <c r="B1" s="138">
         <f ca="1">TODAY()</f>
-        <v>46321</v>
-      </c>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
+        <v>46322</v>
+      </c>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2689,10 +2712,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="147" t="s">
+      <c r="A2" s="158" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="150" t="s">
+      <c r="B2" s="139" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2722,13 +2745,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="139"/>
-      <c r="M2" s="140"/>
-      <c r="N2" s="141"/>
-      <c r="O2" s="142" t="s">
+      <c r="L2" s="150"/>
+      <c r="M2" s="151"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="153" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="143"/>
+      <c r="P2" s="154"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2747,8 +2770,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="147"/>
-      <c r="B3" s="151"/>
+      <c r="A3" s="158"/>
+      <c r="B3" s="140"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2776,29 +2799,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="144" t="s">
+      <c r="L3" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="145"/>
-      <c r="N3" s="146"/>
+      <c r="M3" s="156"/>
+      <c r="N3" s="157"/>
       <c r="O3" s="48"/>
       <c r="P3" s="49"/>
-      <c r="Q3" s="153" t="s">
+      <c r="Q3" s="142" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="154"/>
-      <c r="S3" s="154"/>
-      <c r="T3" s="155"/>
-      <c r="U3" s="156" t="s">
+      <c r="R3" s="143"/>
+      <c r="S3" s="143"/>
+      <c r="T3" s="144"/>
+      <c r="U3" s="145" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="157"/>
-      <c r="W3" s="157"/>
-      <c r="X3" s="158"/>
+      <c r="V3" s="146"/>
+      <c r="W3" s="146"/>
+      <c r="X3" s="147"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="147"/>
-      <c r="B4" s="152"/>
+      <c r="A4" s="158"/>
+      <c r="B4" s="141"/>
       <c r="C4" s="101" t="s">
         <v>90</v>
       </c>
@@ -12763,36 +12786,36 @@
       <c r="X138" s="114"/>
     </row>
     <row r="139" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A139" s="105">
+      <c r="A139" s="168">
         <v>46319</v>
       </c>
-      <c r="B139" s="106">
+      <c r="B139" s="169">
         <v>133</v>
       </c>
-      <c r="C139" s="115" t="s">
+      <c r="C139" s="170" t="s">
         <v>265</v>
       </c>
-      <c r="D139" s="115" t="s">
+      <c r="D139" s="170" t="s">
         <v>160</v>
       </c>
-      <c r="E139" s="113"/>
-      <c r="F139" s="113"/>
-      <c r="G139" s="113">
+      <c r="E139" s="171"/>
+      <c r="F139" s="171"/>
+      <c r="G139" s="171">
         <v>120</v>
       </c>
-      <c r="H139" s="114">
+      <c r="H139" s="172">
         <v>80</v>
       </c>
-      <c r="I139" s="113">
+      <c r="I139" s="171">
         <v>200</v>
       </c>
-      <c r="J139" s="113">
+      <c r="J139" s="171">
         <v>120</v>
       </c>
-      <c r="K139" s="113">
+      <c r="K139" s="171">
         <v>200</v>
       </c>
-      <c r="L139" s="114">
+      <c r="L139" s="172">
         <f t="shared" si="102"/>
         <v>18</v>
       </c>
@@ -12812,36 +12835,36 @@
       <c r="X139" s="114"/>
     </row>
     <row r="140" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A140" s="105">
+      <c r="A140" s="168">
         <v>46319</v>
       </c>
-      <c r="B140" s="106">
+      <c r="B140" s="169">
         <v>134</v>
       </c>
-      <c r="C140" s="115" t="s">
+      <c r="C140" s="170" t="s">
         <v>23</v>
       </c>
-      <c r="D140" s="115" t="s">
+      <c r="D140" s="170" t="s">
         <v>112</v>
       </c>
-      <c r="E140" s="113"/>
-      <c r="F140" s="113">
-        <v>40</v>
-      </c>
-      <c r="G140" s="113">
+      <c r="E140" s="171"/>
+      <c r="F140" s="171">
+        <v>40</v>
+      </c>
+      <c r="G140" s="171">
         <v>77</v>
       </c>
-      <c r="H140" s="114"/>
-      <c r="I140" s="113">
+      <c r="H140" s="172"/>
+      <c r="I140" s="171">
         <v>119</v>
       </c>
-      <c r="J140" s="113">
+      <c r="J140" s="171">
         <v>80</v>
       </c>
-      <c r="K140" s="113">
+      <c r="K140" s="171">
         <v>118</v>
       </c>
-      <c r="L140" s="114">
+      <c r="L140" s="172">
         <f t="shared" si="102"/>
         <v>10.85</v>
       </c>
@@ -12861,32 +12884,32 @@
       <c r="X140" s="114"/>
     </row>
     <row r="141" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A141" s="105">
+      <c r="A141" s="168">
         <v>46319</v>
       </c>
-      <c r="B141" s="106">
+      <c r="B141" s="169">
         <v>135</v>
       </c>
-      <c r="C141" s="115" t="s">
+      <c r="C141" s="170" t="s">
         <v>113</v>
       </c>
-      <c r="D141" s="115" t="s">
+      <c r="D141" s="170" t="s">
         <v>160</v>
       </c>
-      <c r="E141" s="113"/>
-      <c r="F141" s="113"/>
-      <c r="G141" s="113"/>
-      <c r="H141" s="114"/>
-      <c r="I141" s="113">
-        <v>40</v>
-      </c>
-      <c r="J141" s="113">
-        <v>40</v>
-      </c>
-      <c r="K141" s="113">
+      <c r="E141" s="171"/>
+      <c r="F141" s="171"/>
+      <c r="G141" s="171"/>
+      <c r="H141" s="172"/>
+      <c r="I141" s="171">
+        <v>40</v>
+      </c>
+      <c r="J141" s="171">
+        <v>40</v>
+      </c>
+      <c r="K141" s="171">
         <v>120</v>
       </c>
-      <c r="L141" s="114">
+      <c r="L141" s="172">
         <f t="shared" si="102"/>
         <v>5</v>
       </c>
@@ -12906,38 +12929,38 @@
       <c r="X141" s="114"/>
     </row>
     <row r="142" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A142" s="105">
+      <c r="A142" s="168">
         <v>46319</v>
       </c>
-      <c r="B142" s="106">
+      <c r="B142" s="169">
         <v>136</v>
       </c>
-      <c r="C142" s="115" t="s">
+      <c r="C142" s="170" t="s">
         <v>266</v>
       </c>
-      <c r="D142" s="115" t="s">
+      <c r="D142" s="170" t="s">
         <v>158</v>
       </c>
-      <c r="E142" s="113"/>
-      <c r="F142" s="113">
+      <c r="E142" s="171"/>
+      <c r="F142" s="171">
         <v>144</v>
       </c>
-      <c r="G142" s="113">
+      <c r="G142" s="171">
         <v>287</v>
       </c>
-      <c r="H142" s="114">
+      <c r="H142" s="172">
         <v>288</v>
       </c>
-      <c r="I142" s="113">
+      <c r="I142" s="171">
         <v>432</v>
       </c>
-      <c r="J142" s="113">
+      <c r="J142" s="171">
         <v>288</v>
       </c>
-      <c r="K142" s="113">
+      <c r="K142" s="171">
         <v>432</v>
       </c>
-      <c r="L142" s="114">
+      <c r="L142" s="172">
         <f t="shared" si="102"/>
         <v>46.774999999999999</v>
       </c>
@@ -12957,36 +12980,36 @@
       <c r="X142" s="114"/>
     </row>
     <row r="143" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A143" s="105">
+      <c r="A143" s="168">
         <v>46319</v>
       </c>
-      <c r="B143" s="106">
+      <c r="B143" s="169">
         <v>137</v>
       </c>
-      <c r="C143" s="115" t="s">
+      <c r="C143" s="170" t="s">
         <v>240</v>
       </c>
-      <c r="D143" s="115" t="s">
+      <c r="D143" s="170" t="s">
         <v>267</v>
       </c>
-      <c r="E143" s="113"/>
-      <c r="F143" s="113"/>
-      <c r="G143" s="113">
+      <c r="E143" s="171"/>
+      <c r="F143" s="171"/>
+      <c r="G143" s="171">
         <v>198</v>
       </c>
-      <c r="H143" s="114">
+      <c r="H143" s="172">
         <v>80</v>
       </c>
-      <c r="I143" s="113">
+      <c r="I143" s="171">
         <v>120</v>
       </c>
-      <c r="J143" s="113">
+      <c r="J143" s="171">
         <v>240</v>
       </c>
-      <c r="K143" s="113">
+      <c r="K143" s="171">
         <v>80</v>
       </c>
-      <c r="L143" s="114">
+      <c r="L143" s="172">
         <f t="shared" si="102"/>
         <v>17.95</v>
       </c>
@@ -13006,26 +13029,41 @@
       <c r="X143" s="114"/>
     </row>
     <row r="144" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A144" s="128"/>
-      <c r="B144" s="117">
+      <c r="A144" s="105">
+        <v>46321</v>
+      </c>
+      <c r="B144" s="173">
         <v>138</v>
       </c>
-      <c r="C144" s="98"/>
-      <c r="D144" s="98"/>
-      <c r="E144" s="51"/>
-      <c r="F144" s="51"/>
-      <c r="G144" s="51"/>
-      <c r="H144" s="97"/>
-      <c r="I144" s="51"/>
-      <c r="J144" s="51"/>
-      <c r="K144" s="51"/>
-      <c r="L144" s="97">
+      <c r="C144" s="115" t="s">
+        <v>268</v>
+      </c>
+      <c r="D144" s="115" t="s">
+        <v>269</v>
+      </c>
+      <c r="E144" s="113"/>
+      <c r="F144" s="113">
+        <v>40</v>
+      </c>
+      <c r="G144" s="113">
+        <v>40</v>
+      </c>
+      <c r="H144" s="114"/>
+      <c r="I144" s="113">
+        <v>80</v>
+      </c>
+      <c r="J144" s="113">
+        <v>80</v>
+      </c>
+      <c r="K144" s="113">
+        <v>80</v>
+      </c>
+      <c r="L144" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M144" s="109">
-        <f t="shared" ref="M144:O173" si="103">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N144" s="97"/>
       <c r="O144" s="129"/>
@@ -13040,26 +13078,41 @@
       <c r="X144" s="114"/>
     </row>
     <row r="145" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A145" s="128"/>
-      <c r="B145" s="39">
+      <c r="A145" s="105">
+        <v>46321</v>
+      </c>
+      <c r="B145" s="106">
         <v>139</v>
       </c>
-      <c r="C145" s="98"/>
-      <c r="D145" s="98"/>
-      <c r="E145" s="51"/>
-      <c r="F145" s="51"/>
-      <c r="G145" s="51"/>
-      <c r="H145" s="97"/>
-      <c r="I145" s="51"/>
-      <c r="J145" s="51"/>
-      <c r="K145" s="51"/>
-      <c r="L145" s="97">
+      <c r="C145" s="115" t="s">
+        <v>113</v>
+      </c>
+      <c r="D145" s="115" t="s">
+        <v>270</v>
+      </c>
+      <c r="E145" s="113"/>
+      <c r="F145" s="113">
+        <v>40</v>
+      </c>
+      <c r="G145" s="113">
+        <v>40</v>
+      </c>
+      <c r="H145" s="114"/>
+      <c r="I145" s="113">
+        <v>40</v>
+      </c>
+      <c r="J145" s="113">
+        <v>40</v>
+      </c>
+      <c r="K145" s="113">
+        <v>40</v>
+      </c>
+      <c r="L145" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M145" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N145" s="97"/>
       <c r="O145" s="129"/>
@@ -13074,25 +13127,27 @@
       <c r="X145" s="114"/>
     </row>
     <row r="146" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A146" s="128"/>
-      <c r="B146" s="39">
+      <c r="A146" s="105">
+        <v>46321</v>
+      </c>
+      <c r="B146" s="106">
         <v>140</v>
       </c>
-      <c r="C146" s="98"/>
-      <c r="D146" s="98"/>
-      <c r="E146" s="51"/>
-      <c r="F146" s="51"/>
-      <c r="G146" s="51"/>
-      <c r="H146" s="97"/>
-      <c r="I146" s="51"/>
-      <c r="J146" s="51"/>
-      <c r="K146" s="51"/>
-      <c r="L146" s="97">
+      <c r="C146" s="115"/>
+      <c r="D146" s="115"/>
+      <c r="E146" s="113"/>
+      <c r="F146" s="113"/>
+      <c r="G146" s="113"/>
+      <c r="H146" s="114"/>
+      <c r="I146" s="113"/>
+      <c r="J146" s="113"/>
+      <c r="K146" s="113"/>
+      <c r="L146" s="114">
         <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="M146" s="109">
-        <f t="shared" si="103"/>
+        <f t="shared" ref="M144:O173" si="103">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N146" s="97"/>
@@ -13108,20 +13163,22 @@
       <c r="X146" s="114"/>
     </row>
     <row r="147" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A147" s="128"/>
-      <c r="B147" s="39">
+      <c r="A147" s="105">
+        <v>46321</v>
+      </c>
+      <c r="B147" s="106">
         <v>141</v>
       </c>
-      <c r="C147" s="98"/>
-      <c r="D147" s="98"/>
-      <c r="E147" s="51"/>
-      <c r="F147" s="51"/>
-      <c r="G147" s="51"/>
-      <c r="H147" s="97"/>
-      <c r="I147" s="51"/>
-      <c r="J147" s="51"/>
-      <c r="K147" s="51"/>
-      <c r="L147" s="97">
+      <c r="C147" s="115"/>
+      <c r="D147" s="115"/>
+      <c r="E147" s="113"/>
+      <c r="F147" s="113"/>
+      <c r="G147" s="113"/>
+      <c r="H147" s="114"/>
+      <c r="I147" s="113"/>
+      <c r="J147" s="113"/>
+      <c r="K147" s="113"/>
+      <c r="L147" s="114">
         <f t="shared" si="102"/>
         <v>0</v>
       </c>
@@ -14375,10 +14432,10 @@
     </row>
     <row r="178" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A178" s="2"/>
-      <c r="B178" s="138" t="s">
+      <c r="B178" s="149" t="s">
         <v>11</v>
       </c>
-      <c r="C178" s="138"/>
+      <c r="C178" s="149"/>
       <c r="D178" s="132"/>
       <c r="E178" s="133">
         <f>SUM(E173,E177)</f>
@@ -14414,7 +14471,7 @@
       </c>
       <c r="M178" s="134">
         <f>SUM(M5:M177)</f>
-        <v>2095</v>
+        <v>2124</v>
       </c>
       <c r="N178" s="39">
         <f t="shared" ref="N178:X178" si="112">SUM(N5:N177)</f>
@@ -14463,17 +14520,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B173:C173"/>
     <mergeCell ref="B178:C178"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B177:C177"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B173:C173"/>
   </mergeCells>
   <conditionalFormatting sqref="C48:D62">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -14600,11 +14657,11 @@
         <v>70</v>
       </c>
       <c r="M5" s="5">
-        <v>4151</v>
+        <v>2716</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>103.77500000000001</v>
+        <v>67.900000000000006</v>
       </c>
       <c r="O5" s="56"/>
       <c r="P5" s="104"/>
@@ -14613,7 +14670,7 @@
       </c>
       <c r="R5" s="112">
         <f>N5-Q5</f>
-        <v>-163.43499999999997</v>
+        <v>-199.30999999999997</v>
       </c>
     </row>
     <row r="6" spans="3:26" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
@@ -14651,11 +14708,11 @@
         <v>70</v>
       </c>
       <c r="M6" s="5">
-        <v>5191</v>
+        <v>3739</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>129.77500000000001</v>
+        <v>93.474999999999994</v>
       </c>
       <c r="O6" s="56"/>
       <c r="P6" s="104"/>
@@ -14664,7 +14721,7 @@
       </c>
       <c r="R6" s="112">
         <f t="shared" ref="R6:R10" si="2">N6-Q6</f>
-        <v>-44.495000000000005</v>
+        <v>-80.795000000000016</v>
       </c>
       <c r="S6" s="90"/>
       <c r="T6" s="90"/>
@@ -14693,11 +14750,11 @@
         <v>70</v>
       </c>
       <c r="M7" s="5">
-        <v>1303</v>
+        <v>0</v>
       </c>
       <c r="N7" s="6">
         <f t="shared" si="0"/>
-        <v>32.575000000000003</v>
+        <v>0</v>
       </c>
       <c r="O7" s="56"/>
       <c r="P7" s="104"/>
@@ -14706,7 +14763,7 @@
       </c>
       <c r="R7" s="112">
         <f t="shared" si="2"/>
-        <v>-43.664999999999992</v>
+        <v>-76.239999999999995</v>
       </c>
       <c r="S7" s="94" t="s">
         <v>85</v>
@@ -14744,11 +14801,11 @@
         <v>120</v>
       </c>
       <c r="M8" s="5">
-        <v>3247</v>
+        <v>439</v>
       </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>81.174999999999997</v>
+        <v>10.975</v>
       </c>
       <c r="O8" s="56">
         <v>50</v>
@@ -14759,7 +14816,7 @@
       </c>
       <c r="R8" s="112">
         <f t="shared" si="2"/>
-        <v>-3.125</v>
+        <v>-73.325000000000003</v>
       </c>
       <c r="S8" s="54">
         <v>120</v>
@@ -14804,11 +14861,11 @@
         <v>120</v>
       </c>
       <c r="M9" s="5">
-        <v>17623</v>
+        <v>14843</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>440.57499999999999</v>
+        <v>371.07499999999999</v>
       </c>
       <c r="O9" s="56">
         <v>23</v>
@@ -14819,7 +14876,7 @@
       </c>
       <c r="R9" s="112">
         <f t="shared" si="2"/>
-        <v>331.40499999999997</v>
+        <v>261.90499999999997</v>
       </c>
       <c r="S9" s="54">
         <v>120</v>
@@ -14855,11 +14912,11 @@
         <v>120</v>
       </c>
       <c r="M10" s="5">
-        <v>18667</v>
+        <v>14351</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>466.67500000000001</v>
+        <v>358.77499999999998</v>
       </c>
       <c r="O10" s="56"/>
       <c r="P10" s="104"/>
@@ -14868,7 +14925,7 @@
       </c>
       <c r="R10" s="112">
         <f t="shared" si="2"/>
-        <v>268.32500000000005</v>
+        <v>160.42499999999998</v>
       </c>
       <c r="S10" s="54">
         <v>120</v>
@@ -14907,10 +14964,12 @@
       <c r="L11" s="7">
         <v>60</v>
       </c>
-      <c r="M11" s="5"/>
+      <c r="M11" s="5">
+        <v>22</v>
+      </c>
       <c r="N11" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="O11" s="56">
         <v>125</v>
@@ -14958,11 +15017,11 @@
       <c r="L12" s="56"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>50182</v>
+        <v>36110</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>1254.55</v>
+        <v>902.74999999999989</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
@@ -15061,7 +15120,7 @@
       <c r="N17" s="87"/>
       <c r="O17" s="88">
         <f>N17-M5</f>
-        <v>-4151</v>
+        <v>-2716</v>
       </c>
       <c r="R17">
         <v>51.94</v>
@@ -15081,7 +15140,7 @@
       <c r="N18" s="5"/>
       <c r="O18" s="88">
         <f>N18-M6</f>
-        <v>-5191</v>
+        <v>-3739</v>
       </c>
       <c r="R18">
         <v>163.25499999999997</v>
@@ -15104,7 +15163,7 @@
       <c r="N19" s="5"/>
       <c r="O19" s="88">
         <f t="shared" ref="O19:O23" si="5">N19-M7</f>
-        <v>-1303</v>
+        <v>0</v>
       </c>
       <c r="R19">
         <v>224.70999999999998</v>
@@ -15131,7 +15190,7 @@
       <c r="N20" s="5"/>
       <c r="O20" s="88">
         <f t="shared" si="5"/>
-        <v>-3247</v>
+        <v>-439</v>
       </c>
       <c r="R20">
         <v>156.75</v>
@@ -15166,7 +15225,7 @@
       <c r="N21" s="5"/>
       <c r="O21" s="88">
         <f t="shared" si="5"/>
-        <v>-17623</v>
+        <v>-14843</v>
       </c>
       <c r="R21">
         <v>158.505</v>
@@ -15198,7 +15257,7 @@
       <c r="N22" s="5"/>
       <c r="O22" s="88">
         <f t="shared" si="5"/>
-        <v>-18667</v>
+        <v>-14351</v>
       </c>
       <c r="R22">
         <v>69.150000000000006</v>
@@ -15230,7 +15289,7 @@
       <c r="N23" s="5"/>
       <c r="O23" s="88">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="24" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -15260,7 +15319,7 @@
       </c>
       <c r="O24" s="83">
         <f>SUM(O17:O23)</f>
-        <v>-50182</v>
+        <v>-36110</v>
       </c>
     </row>
     <row r="25" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -15290,7 +15349,7 @@
       </c>
       <c r="O25" s="83">
         <f>O24/40</f>
-        <v>-1254.55</v>
+        <v>-902.75</v>
       </c>
     </row>
     <row r="26" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B072804-EBDB-4E61-A721-83631E4674C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4ED052-F196-4A22-A781-C30A8FB54BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="LMT" sheetId="2" r:id="rId2"/>
     <sheet name="S-P" sheetId="3" r:id="rId3"/>
+    <sheet name="Compair" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="324">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -835,6 +836,165 @@
   </si>
   <si>
     <t>Askari 10</t>
+  </si>
+  <si>
+    <t>Al Buraq Dipartmental Store</t>
+  </si>
+  <si>
+    <t>Samnaabad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euro Rachna </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rachna </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central Park </t>
+  </si>
+  <si>
+    <t>Sanda</t>
+  </si>
+  <si>
+    <t>Column A</t>
+  </si>
+  <si>
+    <t>Column B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Imamia </t>
+  </si>
+  <si>
+    <t>Jalal Sons 1</t>
+  </si>
+  <si>
+    <t>Rainbow Cash &amp; Carry1</t>
+  </si>
+  <si>
+    <t>Rainbow Cash &amp; Carry2</t>
+  </si>
+  <si>
+    <t>Rainbow Cash &amp; Carry3</t>
+  </si>
+  <si>
+    <t>Rainbow Cash &amp; Carry4</t>
+  </si>
+  <si>
+    <t>Rainbow Cash &amp; Carry5</t>
+  </si>
+  <si>
+    <t>Rainbow Cash &amp; Carry6</t>
+  </si>
+  <si>
+    <t>Rainbow Cash &amp; Carry7</t>
+  </si>
+  <si>
+    <t>Gourmet Food Shadbagh 4</t>
+  </si>
+  <si>
+    <t>Gourmet food Kot abdul malik 7</t>
+  </si>
+  <si>
+    <t>Gourmet Food Rehmanpura1</t>
+  </si>
+  <si>
+    <t>Jalal Sons 7</t>
+  </si>
+  <si>
+    <t>Clinix 9</t>
+  </si>
+  <si>
+    <t>Gourmet Food Islam Pura9</t>
+  </si>
+  <si>
+    <t>Al Rehmat Store9</t>
+  </si>
+  <si>
+    <t>Euro Store78</t>
+  </si>
+  <si>
+    <t>TN Traders 12</t>
+  </si>
+  <si>
+    <t>Nabeel Traders  SD 1</t>
+  </si>
+  <si>
+    <t>Clinix 5</t>
+  </si>
+  <si>
+    <t>Rafaqat Stons 8</t>
+  </si>
+  <si>
+    <t>Rafaqat Stons 7</t>
+  </si>
+  <si>
+    <t>SB Traders (Risen) Shadbagh 9</t>
+  </si>
+  <si>
+    <t>Euro Hyper Market5</t>
+  </si>
+  <si>
+    <t>Rainbow Cash &amp; Carry64</t>
+  </si>
+  <si>
+    <t>Rainbow Cash &amp; Carry14</t>
+  </si>
+  <si>
+    <t>Rainbow Cash &amp; Carry12</t>
+  </si>
+  <si>
+    <t>Umer Cash N Carry 123</t>
+  </si>
+  <si>
+    <t>Rainbow Cash &amp; Carry45</t>
+  </si>
+  <si>
+    <t>Rainbow Cash &amp; Carry65</t>
+  </si>
+  <si>
+    <t>Rainbow Cash &amp; Carry124</t>
+  </si>
+  <si>
+    <t>Rainbow Cash &amp; Carry42</t>
+  </si>
+  <si>
+    <t>Rainbow Cash &amp; Carry1247</t>
+  </si>
+  <si>
+    <t>Rainbow Cash &amp; Carry21</t>
+  </si>
+  <si>
+    <t>Zubaida Traders 7</t>
+  </si>
+  <si>
+    <t>Jalal Sons 78</t>
+  </si>
+  <si>
+    <t>CB Traders Risen Manawan 14</t>
+  </si>
+  <si>
+    <t>Jalal Sons 45</t>
+  </si>
+  <si>
+    <t>Clinix 45</t>
+  </si>
+  <si>
+    <t>Jalal Sons 12</t>
+  </si>
+  <si>
+    <t>Jalal Sons 1212</t>
+  </si>
+  <si>
+    <t>Al Buraq Dipartmental Store4</t>
+  </si>
+  <si>
+    <t>Jalal Sons 3</t>
+  </si>
+  <si>
+    <t>Raheem Store8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compare </t>
   </si>
 </sst>
 </file>
@@ -846,7 +1006,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -938,8 +1098,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -997,6 +1170,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1624,11 +1803,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1987,37 +2167,24 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2050,6 +2217,39 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2077,26 +2277,59 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal_Sheet3" xfId="2" xr:uid="{9CB8E494-756B-4254-8AD3-973B40813A69}"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2684,13 +2917,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="138">
+      <c r="B1" s="157">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
-      </c>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
+        <v>46323</v>
+      </c>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2712,10 +2945,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="158" t="s">
+      <c r="A2" s="155" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="139" t="s">
+      <c r="B2" s="158" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2745,13 +2978,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="150"/>
-      <c r="M2" s="151"/>
-      <c r="N2" s="152"/>
-      <c r="O2" s="153" t="s">
+      <c r="L2" s="147"/>
+      <c r="M2" s="148"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="150" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="154"/>
+      <c r="P2" s="151"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -2770,8 +3003,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="158"/>
-      <c r="B3" s="140"/>
+      <c r="A3" s="155"/>
+      <c r="B3" s="159"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -2799,29 +3032,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="155" t="s">
+      <c r="L3" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="156"/>
-      <c r="N3" s="157"/>
+      <c r="M3" s="153"/>
+      <c r="N3" s="154"/>
       <c r="O3" s="48"/>
       <c r="P3" s="49"/>
-      <c r="Q3" s="142" t="s">
+      <c r="Q3" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="143"/>
-      <c r="S3" s="143"/>
-      <c r="T3" s="144"/>
-      <c r="U3" s="145" t="s">
+      <c r="R3" s="162"/>
+      <c r="S3" s="162"/>
+      <c r="T3" s="163"/>
+      <c r="U3" s="164" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="146"/>
-      <c r="W3" s="146"/>
-      <c r="X3" s="147"/>
+      <c r="V3" s="165"/>
+      <c r="W3" s="165"/>
+      <c r="X3" s="166"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="158"/>
-      <c r="B4" s="141"/>
+      <c r="A4" s="155"/>
+      <c r="B4" s="160"/>
       <c r="C4" s="101" t="s">
         <v>90</v>
       </c>
@@ -6398,35 +6631,35 @@
       <c r="A52" s="53">
         <v>46301</v>
       </c>
-      <c r="B52" s="39">
+      <c r="B52" s="143">
         <v>46</v>
       </c>
-      <c r="C52" s="102" t="s">
+      <c r="C52" s="139" t="s">
         <v>153</v>
       </c>
-      <c r="D52" s="102" t="s">
+      <c r="D52" s="139" t="s">
         <v>154</v>
       </c>
-      <c r="E52" s="51"/>
-      <c r="F52" s="51"/>
-      <c r="G52" s="51"/>
-      <c r="H52" s="97">
+      <c r="E52" s="140"/>
+      <c r="F52" s="140"/>
+      <c r="G52" s="140"/>
+      <c r="H52" s="141">
         <v>600</v>
       </c>
-      <c r="I52" s="51">
+      <c r="I52" s="140">
         <v>800</v>
       </c>
-      <c r="J52" s="51">
+      <c r="J52" s="140">
         <v>1200</v>
       </c>
-      <c r="K52" s="51">
+      <c r="K52" s="140">
         <v>1000</v>
       </c>
-      <c r="L52" s="97">
+      <c r="L52" s="145">
         <f t="shared" si="64"/>
         <v>90</v>
       </c>
-      <c r="M52" s="109">
+      <c r="M52" s="142">
         <v>16</v>
       </c>
       <c r="N52" s="40"/>
@@ -7568,35 +7801,35 @@
       <c r="A70" s="53">
         <v>46302</v>
       </c>
-      <c r="B70" s="39">
+      <c r="B70" s="143">
         <v>64</v>
       </c>
-      <c r="C70" s="98" t="s">
+      <c r="C70" s="144" t="s">
         <v>191</v>
       </c>
-      <c r="D70" s="98" t="s">
+      <c r="D70" s="144" t="s">
         <v>192</v>
       </c>
-      <c r="E70" s="51"/>
-      <c r="F70" s="51">
+      <c r="E70" s="140"/>
+      <c r="F70" s="140">
         <v>400</v>
       </c>
-      <c r="G70" s="51">
+      <c r="G70" s="140">
         <v>400</v>
       </c>
-      <c r="H70" s="97">
-        <v>0</v>
-      </c>
-      <c r="I70" s="51">
+      <c r="H70" s="141">
+        <v>0</v>
+      </c>
+      <c r="I70" s="140">
         <v>600</v>
       </c>
-      <c r="J70" s="51">
+      <c r="J70" s="140">
         <v>800</v>
       </c>
-      <c r="K70" s="51">
+      <c r="K70" s="140">
         <v>800</v>
       </c>
-      <c r="L70" s="97">
+      <c r="L70" s="145">
         <f t="shared" si="64"/>
         <v>75</v>
       </c>
@@ -8863,29 +9096,29 @@
       <c r="A87" s="53">
         <v>46304</v>
       </c>
-      <c r="B87" s="39">
+      <c r="B87" s="143">
         <v>81</v>
       </c>
-      <c r="C87" s="98" t="s">
+      <c r="C87" s="144" t="s">
         <v>211</v>
       </c>
-      <c r="D87" s="98" t="s">
+      <c r="D87" s="144" t="s">
         <v>212</v>
       </c>
-      <c r="E87" s="51"/>
-      <c r="F87" s="51"/>
-      <c r="G87" s="51"/>
-      <c r="H87" s="97"/>
-      <c r="I87" s="51">
+      <c r="E87" s="140"/>
+      <c r="F87" s="140"/>
+      <c r="G87" s="140"/>
+      <c r="H87" s="141"/>
+      <c r="I87" s="140">
         <v>3000</v>
       </c>
-      <c r="J87" s="51">
+      <c r="J87" s="140">
         <v>2000</v>
       </c>
-      <c r="K87" s="51">
+      <c r="K87" s="140">
         <v>3000</v>
       </c>
-      <c r="L87" s="97">
+      <c r="L87" s="145">
         <f t="shared" si="84"/>
         <v>200</v>
       </c>
@@ -9408,25 +9641,25 @@
       <c r="A94" s="53">
         <v>46306</v>
       </c>
-      <c r="B94" s="39">
+      <c r="B94" s="143">
         <v>88</v>
       </c>
-      <c r="C94" s="98" t="s">
+      <c r="C94" s="144" t="s">
         <v>211</v>
       </c>
-      <c r="D94" s="98" t="s">
+      <c r="D94" s="144" t="s">
         <v>212</v>
       </c>
-      <c r="E94" s="51"/>
-      <c r="F94" s="51">
+      <c r="E94" s="140"/>
+      <c r="F94" s="140">
         <v>600</v>
       </c>
-      <c r="G94" s="51"/>
-      <c r="H94" s="97"/>
-      <c r="I94" s="51"/>
-      <c r="J94" s="51"/>
-      <c r="K94" s="51"/>
-      <c r="L94" s="97">
+      <c r="G94" s="140"/>
+      <c r="H94" s="141"/>
+      <c r="I94" s="140"/>
+      <c r="J94" s="140"/>
+      <c r="K94" s="140"/>
+      <c r="L94" s="145">
         <f t="shared" si="84"/>
         <v>15</v>
       </c>
@@ -10022,35 +10255,35 @@
       <c r="A102" s="53">
         <v>46310</v>
       </c>
-      <c r="B102" s="39">
+      <c r="B102" s="143">
         <v>96</v>
       </c>
-      <c r="C102" s="98" t="s">
+      <c r="C102" s="144" t="s">
         <v>211</v>
       </c>
-      <c r="D102" s="98" t="s">
+      <c r="D102" s="144" t="s">
         <v>212</v>
       </c>
-      <c r="E102" s="51"/>
-      <c r="F102" s="51">
+      <c r="E102" s="140"/>
+      <c r="F102" s="140">
         <v>200</v>
       </c>
-      <c r="G102" s="51">
+      <c r="G102" s="140">
         <v>200</v>
       </c>
-      <c r="H102" s="97">
+      <c r="H102" s="141">
         <v>200</v>
       </c>
-      <c r="I102" s="51">
+      <c r="I102" s="140">
         <v>2800</v>
       </c>
-      <c r="J102" s="51">
+      <c r="J102" s="140">
         <v>2400</v>
       </c>
-      <c r="K102" s="51">
+      <c r="K102" s="140">
         <v>2800</v>
       </c>
-      <c r="L102" s="97">
+      <c r="L102" s="145">
         <f t="shared" si="84"/>
         <v>215</v>
       </c>
@@ -12786,36 +13019,36 @@
       <c r="X138" s="114"/>
     </row>
     <row r="139" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A139" s="168">
+      <c r="A139" s="53">
         <v>46319</v>
       </c>
-      <c r="B139" s="169">
+      <c r="B139" s="39">
         <v>133</v>
       </c>
-      <c r="C139" s="170" t="s">
+      <c r="C139" s="98" t="s">
         <v>265</v>
       </c>
-      <c r="D139" s="170" t="s">
+      <c r="D139" s="98" t="s">
         <v>160</v>
       </c>
-      <c r="E139" s="171"/>
-      <c r="F139" s="171"/>
-      <c r="G139" s="171">
+      <c r="E139" s="51"/>
+      <c r="F139" s="51"/>
+      <c r="G139" s="51">
         <v>120</v>
       </c>
-      <c r="H139" s="172">
+      <c r="H139" s="97">
         <v>80</v>
       </c>
-      <c r="I139" s="171">
+      <c r="I139" s="51">
         <v>200</v>
       </c>
-      <c r="J139" s="171">
+      <c r="J139" s="51">
         <v>120</v>
       </c>
-      <c r="K139" s="171">
+      <c r="K139" s="51">
         <v>200</v>
       </c>
-      <c r="L139" s="172">
+      <c r="L139" s="97">
         <f t="shared" si="102"/>
         <v>18</v>
       </c>
@@ -12835,36 +13068,36 @@
       <c r="X139" s="114"/>
     </row>
     <row r="140" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A140" s="168">
+      <c r="A140" s="53">
         <v>46319</v>
       </c>
-      <c r="B140" s="169">
+      <c r="B140" s="39">
         <v>134</v>
       </c>
-      <c r="C140" s="170" t="s">
+      <c r="C140" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="D140" s="170" t="s">
+      <c r="D140" s="98" t="s">
         <v>112</v>
       </c>
-      <c r="E140" s="171"/>
-      <c r="F140" s="171">
-        <v>40</v>
-      </c>
-      <c r="G140" s="171">
+      <c r="E140" s="51"/>
+      <c r="F140" s="51">
+        <v>40</v>
+      </c>
+      <c r="G140" s="51">
         <v>77</v>
       </c>
-      <c r="H140" s="172"/>
-      <c r="I140" s="171">
+      <c r="H140" s="97"/>
+      <c r="I140" s="51">
         <v>119</v>
       </c>
-      <c r="J140" s="171">
+      <c r="J140" s="51">
         <v>80</v>
       </c>
-      <c r="K140" s="171">
+      <c r="K140" s="51">
         <v>118</v>
       </c>
-      <c r="L140" s="172">
+      <c r="L140" s="97">
         <f t="shared" si="102"/>
         <v>10.85</v>
       </c>
@@ -12884,32 +13117,32 @@
       <c r="X140" s="114"/>
     </row>
     <row r="141" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A141" s="168">
+      <c r="A141" s="53">
         <v>46319</v>
       </c>
-      <c r="B141" s="169">
+      <c r="B141" s="39">
         <v>135</v>
       </c>
-      <c r="C141" s="170" t="s">
+      <c r="C141" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="D141" s="170" t="s">
+      <c r="D141" s="98" t="s">
         <v>160</v>
       </c>
-      <c r="E141" s="171"/>
-      <c r="F141" s="171"/>
-      <c r="G141" s="171"/>
-      <c r="H141" s="172"/>
-      <c r="I141" s="171">
-        <v>40</v>
-      </c>
-      <c r="J141" s="171">
-        <v>40</v>
-      </c>
-      <c r="K141" s="171">
+      <c r="E141" s="51"/>
+      <c r="F141" s="51"/>
+      <c r="G141" s="51"/>
+      <c r="H141" s="97"/>
+      <c r="I141" s="51">
+        <v>40</v>
+      </c>
+      <c r="J141" s="51">
+        <v>40</v>
+      </c>
+      <c r="K141" s="51">
         <v>120</v>
       </c>
-      <c r="L141" s="172">
+      <c r="L141" s="97">
         <f t="shared" si="102"/>
         <v>5</v>
       </c>
@@ -12929,38 +13162,38 @@
       <c r="X141" s="114"/>
     </row>
     <row r="142" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A142" s="168">
+      <c r="A142" s="53">
         <v>46319</v>
       </c>
-      <c r="B142" s="169">
+      <c r="B142" s="39">
         <v>136</v>
       </c>
-      <c r="C142" s="170" t="s">
+      <c r="C142" s="98" t="s">
         <v>266</v>
       </c>
-      <c r="D142" s="170" t="s">
+      <c r="D142" s="98" t="s">
         <v>158</v>
       </c>
-      <c r="E142" s="171"/>
-      <c r="F142" s="171">
+      <c r="E142" s="51"/>
+      <c r="F142" s="51">
         <v>144</v>
       </c>
-      <c r="G142" s="171">
+      <c r="G142" s="51">
         <v>287</v>
       </c>
-      <c r="H142" s="172">
+      <c r="H142" s="97">
         <v>288</v>
       </c>
-      <c r="I142" s="171">
+      <c r="I142" s="51">
         <v>432</v>
       </c>
-      <c r="J142" s="171">
+      <c r="J142" s="51">
         <v>288</v>
       </c>
-      <c r="K142" s="171">
+      <c r="K142" s="51">
         <v>432</v>
       </c>
-      <c r="L142" s="172">
+      <c r="L142" s="97">
         <f t="shared" si="102"/>
         <v>46.774999999999999</v>
       </c>
@@ -12980,36 +13213,36 @@
       <c r="X142" s="114"/>
     </row>
     <row r="143" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A143" s="168">
+      <c r="A143" s="53">
         <v>46319</v>
       </c>
-      <c r="B143" s="169">
+      <c r="B143" s="39">
         <v>137</v>
       </c>
-      <c r="C143" s="170" t="s">
+      <c r="C143" s="98" t="s">
         <v>240</v>
       </c>
-      <c r="D143" s="170" t="s">
+      <c r="D143" s="98" t="s">
         <v>267</v>
       </c>
-      <c r="E143" s="171"/>
-      <c r="F143" s="171"/>
-      <c r="G143" s="171">
+      <c r="E143" s="51"/>
+      <c r="F143" s="51"/>
+      <c r="G143" s="51">
         <v>198</v>
       </c>
-      <c r="H143" s="172">
+      <c r="H143" s="97">
         <v>80</v>
       </c>
-      <c r="I143" s="171">
+      <c r="I143" s="51">
         <v>120</v>
       </c>
-      <c r="J143" s="171">
+      <c r="J143" s="51">
         <v>240</v>
       </c>
-      <c r="K143" s="171">
+      <c r="K143" s="51">
         <v>80</v>
       </c>
-      <c r="L143" s="172">
+      <c r="L143" s="97">
         <f t="shared" si="102"/>
         <v>17.95</v>
       </c>
@@ -13029,36 +13262,36 @@
       <c r="X143" s="114"/>
     </row>
     <row r="144" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A144" s="105">
+      <c r="A144" s="53">
         <v>46321</v>
       </c>
-      <c r="B144" s="173">
+      <c r="B144" s="117">
         <v>138</v>
       </c>
-      <c r="C144" s="115" t="s">
+      <c r="C144" s="98" t="s">
         <v>268</v>
       </c>
-      <c r="D144" s="115" t="s">
+      <c r="D144" s="98" t="s">
         <v>269</v>
       </c>
-      <c r="E144" s="113"/>
-      <c r="F144" s="113">
-        <v>40</v>
-      </c>
-      <c r="G144" s="113">
-        <v>40</v>
-      </c>
-      <c r="H144" s="114"/>
-      <c r="I144" s="113">
+      <c r="E144" s="51"/>
+      <c r="F144" s="51">
+        <v>40</v>
+      </c>
+      <c r="G144" s="51">
+        <v>40</v>
+      </c>
+      <c r="H144" s="97"/>
+      <c r="I144" s="51">
         <v>80</v>
       </c>
-      <c r="J144" s="113">
+      <c r="J144" s="51">
         <v>80</v>
       </c>
-      <c r="K144" s="113">
+      <c r="K144" s="51">
         <v>80</v>
       </c>
-      <c r="L144" s="114">
+      <c r="L144" s="97">
         <f t="shared" si="102"/>
         <v>8</v>
       </c>
@@ -13078,36 +13311,36 @@
       <c r="X144" s="114"/>
     </row>
     <row r="145" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A145" s="105">
+      <c r="A145" s="53">
         <v>46321</v>
       </c>
-      <c r="B145" s="106">
+      <c r="B145" s="39">
         <v>139</v>
       </c>
-      <c r="C145" s="115" t="s">
+      <c r="C145" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="D145" s="115" t="s">
+      <c r="D145" s="98" t="s">
         <v>270</v>
       </c>
-      <c r="E145" s="113"/>
-      <c r="F145" s="113">
-        <v>40</v>
-      </c>
-      <c r="G145" s="113">
-        <v>40</v>
-      </c>
-      <c r="H145" s="114"/>
-      <c r="I145" s="113">
-        <v>40</v>
-      </c>
-      <c r="J145" s="113">
-        <v>40</v>
-      </c>
-      <c r="K145" s="113">
-        <v>40</v>
-      </c>
-      <c r="L145" s="114">
+      <c r="E145" s="51"/>
+      <c r="F145" s="51">
+        <v>40</v>
+      </c>
+      <c r="G145" s="51">
+        <v>40</v>
+      </c>
+      <c r="H145" s="97"/>
+      <c r="I145" s="51">
+        <v>40</v>
+      </c>
+      <c r="J145" s="51">
+        <v>40</v>
+      </c>
+      <c r="K145" s="51">
+        <v>40</v>
+      </c>
+      <c r="L145" s="97">
         <f t="shared" si="102"/>
         <v>5</v>
       </c>
@@ -13128,27 +13361,32 @@
     </row>
     <row r="146" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A146" s="105">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B146" s="106">
         <v>140</v>
       </c>
-      <c r="C146" s="115"/>
-      <c r="D146" s="115"/>
+      <c r="C146" s="115" t="s">
+        <v>271</v>
+      </c>
+      <c r="D146" s="115" t="s">
+        <v>272</v>
+      </c>
       <c r="E146" s="113"/>
       <c r="F146" s="113"/>
       <c r="G146" s="113"/>
       <c r="H146" s="114"/>
       <c r="I146" s="113"/>
       <c r="J146" s="113"/>
-      <c r="K146" s="113"/>
+      <c r="K146" s="113">
+        <v>800</v>
+      </c>
       <c r="L146" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M146" s="109">
-        <f t="shared" ref="M144:O173" si="103">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N146" s="97"/>
       <c r="O146" s="129"/>
@@ -13164,27 +13402,36 @@
     </row>
     <row r="147" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A147" s="105">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B147" s="106">
         <v>141</v>
       </c>
-      <c r="C147" s="115"/>
-      <c r="D147" s="115"/>
+      <c r="C147" s="115" t="s">
+        <v>273</v>
+      </c>
+      <c r="D147" s="115" t="s">
+        <v>274</v>
+      </c>
       <c r="E147" s="113"/>
       <c r="F147" s="113"/>
-      <c r="G147" s="113"/>
+      <c r="G147" s="113">
+        <v>39</v>
+      </c>
       <c r="H147" s="114"/>
       <c r="I147" s="113"/>
-      <c r="J147" s="113"/>
-      <c r="K147" s="113"/>
+      <c r="J147" s="113">
+        <v>40</v>
+      </c>
+      <c r="K147" s="113">
+        <v>120</v>
+      </c>
       <c r="L147" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>4.9749999999999996</v>
       </c>
       <c r="M147" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N147" s="97"/>
       <c r="O147" s="129"/>
@@ -13199,26 +13446,43 @@
       <c r="X147" s="114"/>
     </row>
     <row r="148" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A148" s="128"/>
-      <c r="B148" s="39">
+      <c r="A148" s="105">
+        <v>46322</v>
+      </c>
+      <c r="B148" s="106">
         <v>142</v>
       </c>
-      <c r="C148" s="98"/>
-      <c r="D148" s="98"/>
-      <c r="E148" s="51"/>
-      <c r="F148" s="51"/>
-      <c r="G148" s="51"/>
-      <c r="H148" s="97"/>
-      <c r="I148" s="51"/>
-      <c r="J148" s="51"/>
-      <c r="K148" s="51"/>
-      <c r="L148" s="97">
+      <c r="C148" s="115" t="s">
+        <v>113</v>
+      </c>
+      <c r="D148" s="115" t="s">
+        <v>275</v>
+      </c>
+      <c r="E148" s="113"/>
+      <c r="F148" s="113">
+        <v>120</v>
+      </c>
+      <c r="G148" s="113">
+        <v>120</v>
+      </c>
+      <c r="H148" s="114">
+        <v>120</v>
+      </c>
+      <c r="I148" s="113">
+        <v>120</v>
+      </c>
+      <c r="J148" s="113">
+        <v>120</v>
+      </c>
+      <c r="K148" s="113">
+        <v>120</v>
+      </c>
+      <c r="L148" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M148" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N148" s="97"/>
       <c r="O148" s="129"/>
@@ -13233,26 +13497,37 @@
       <c r="X148" s="114"/>
     </row>
     <row r="149" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A149" s="128"/>
-      <c r="B149" s="39">
+      <c r="A149" s="105">
+        <v>46322</v>
+      </c>
+      <c r="B149" s="106">
         <v>143</v>
       </c>
-      <c r="C149" s="98"/>
-      <c r="D149" s="98"/>
-      <c r="E149" s="51"/>
-      <c r="F149" s="51"/>
-      <c r="G149" s="51"/>
-      <c r="H149" s="97"/>
-      <c r="I149" s="51"/>
-      <c r="J149" s="51"/>
-      <c r="K149" s="51"/>
-      <c r="L149" s="97">
+      <c r="C149" s="115" t="s">
+        <v>271</v>
+      </c>
+      <c r="D149" s="115" t="s">
+        <v>276</v>
+      </c>
+      <c r="E149" s="113"/>
+      <c r="F149" s="113"/>
+      <c r="G149" s="113"/>
+      <c r="H149" s="114"/>
+      <c r="I149" s="113">
+        <v>80</v>
+      </c>
+      <c r="J149" s="113">
+        <v>80</v>
+      </c>
+      <c r="K149" s="113">
+        <v>80</v>
+      </c>
+      <c r="L149" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M149" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N149" s="97"/>
       <c r="O149" s="129"/>
@@ -13267,26 +13542,41 @@
       <c r="X149" s="114"/>
     </row>
     <row r="150" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A150" s="128"/>
-      <c r="B150" s="117">
+      <c r="A150" s="105">
+        <v>46322</v>
+      </c>
+      <c r="B150" s="138">
         <v>144</v>
       </c>
-      <c r="C150" s="98"/>
-      <c r="D150" s="98"/>
-      <c r="E150" s="51"/>
-      <c r="F150" s="51"/>
-      <c r="G150" s="51"/>
-      <c r="H150" s="97"/>
-      <c r="I150" s="51"/>
-      <c r="J150" s="51"/>
-      <c r="K150" s="51"/>
-      <c r="L150" s="97">
+      <c r="C150" s="115" t="s">
+        <v>238</v>
+      </c>
+      <c r="D150" s="115" t="s">
+        <v>239</v>
+      </c>
+      <c r="E150" s="113"/>
+      <c r="F150" s="113">
+        <v>200</v>
+      </c>
+      <c r="G150" s="113">
+        <v>200</v>
+      </c>
+      <c r="H150" s="114"/>
+      <c r="I150" s="113">
+        <v>240</v>
+      </c>
+      <c r="J150" s="113">
+        <v>360</v>
+      </c>
+      <c r="K150" s="113">
+        <v>400</v>
+      </c>
+      <c r="L150" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M150" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N150" s="97"/>
       <c r="O150" s="129"/>
@@ -13319,7 +13609,7 @@
         <v>0</v>
       </c>
       <c r="M151" s="109">
-        <f t="shared" si="103"/>
+        <f t="shared" ref="M151:O173" si="103">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N151" s="97"/>
@@ -13921,14 +14211,16 @@
       <c r="D169" s="98"/>
       <c r="E169" s="51"/>
       <c r="F169" s="51"/>
-      <c r="G169" s="51"/>
+      <c r="G169" s="51">
+        <v>2347</v>
+      </c>
       <c r="H169" s="97"/>
       <c r="I169" s="51"/>
       <c r="J169" s="51"/>
       <c r="K169" s="51"/>
       <c r="L169" s="97">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>58.674999999999997</v>
       </c>
       <c r="M169" s="109">
         <f t="shared" si="103"/>
@@ -13955,14 +14247,16 @@
       <c r="D170" s="98"/>
       <c r="E170" s="51"/>
       <c r="F170" s="51"/>
-      <c r="G170" s="51"/>
+      <c r="G170" s="51">
+        <v>595</v>
+      </c>
       <c r="H170" s="97"/>
       <c r="I170" s="51"/>
       <c r="J170" s="51"/>
       <c r="K170" s="51"/>
       <c r="L170" s="97">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>14.875</v>
       </c>
       <c r="M170" s="109">
         <f t="shared" si="103"/>
@@ -13989,14 +14283,17 @@
       <c r="D171" s="98"/>
       <c r="E171" s="51"/>
       <c r="F171" s="51"/>
-      <c r="G171" s="51"/>
+      <c r="G171" s="51">
+        <f>G169-G170</f>
+        <v>1752</v>
+      </c>
       <c r="H171" s="97"/>
       <c r="I171" s="51"/>
       <c r="J171" s="51"/>
       <c r="K171" s="51"/>
       <c r="L171" s="97">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="M171" s="109">
         <f t="shared" si="103"/>
@@ -14088,10 +14385,10 @@
     </row>
     <row r="173" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A173" s="128"/>
-      <c r="B173" s="148" t="s">
+      <c r="B173" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="C173" s="148"/>
+      <c r="C173" s="156"/>
       <c r="D173" s="106"/>
       <c r="E173" s="111">
         <f t="shared" ref="E173:K173" si="104">SUM(E6:E63)</f>
@@ -14344,10 +14641,10 @@
     </row>
     <row r="177" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A177" s="2"/>
-      <c r="B177" s="148" t="s">
+      <c r="B177" s="156" t="s">
         <v>68</v>
       </c>
-      <c r="C177" s="148"/>
+      <c r="C177" s="156"/>
       <c r="D177" s="106"/>
       <c r="E177" s="113">
         <f>SUM(E175:E176)</f>
@@ -14432,10 +14729,10 @@
     </row>
     <row r="178" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A178" s="2"/>
-      <c r="B178" s="149" t="s">
+      <c r="B178" s="146" t="s">
         <v>11</v>
       </c>
-      <c r="C178" s="149"/>
+      <c r="C178" s="146"/>
       <c r="D178" s="132"/>
       <c r="E178" s="133">
         <f>SUM(E173,E177)</f>
@@ -14471,7 +14768,7 @@
       </c>
       <c r="M178" s="134">
         <f>SUM(M5:M177)</f>
-        <v>2124</v>
+        <v>2191</v>
       </c>
       <c r="N178" s="39">
         <f t="shared" ref="N178:X178" si="112">SUM(N5:N177)</f>
@@ -14520,20 +14817,20 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B173:C173"/>
     <mergeCell ref="B178:C178"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B177:C177"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B173:C173"/>
   </mergeCells>
   <conditionalFormatting sqref="C48:D62">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -14567,25 +14864,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="161" t="s">
+      <c r="C3" s="169" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="162"/>
-      <c r="E3" s="162"/>
-      <c r="F3" s="162"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="165" t="s">
+      <c r="D3" s="170"/>
+      <c r="E3" s="170"/>
+      <c r="F3" s="170"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="173" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="166"/>
-      <c r="K3" s="167" t="s">
+      <c r="I3" s="174"/>
+      <c r="K3" s="175" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="167"/>
-      <c r="M3" s="167"/>
-      <c r="N3" s="167"/>
-      <c r="O3" s="167"/>
-      <c r="P3" s="167"/>
+      <c r="L3" s="175"/>
+      <c r="M3" s="175"/>
+      <c r="N3" s="175"/>
+      <c r="O3" s="175"/>
+      <c r="P3" s="175"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="71"/>
@@ -14631,24 +14928,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="60">
-        <v>685</v>
+        <v>745</v>
       </c>
       <c r="E5" s="54">
-        <v>1655</v>
+        <v>1752</v>
       </c>
       <c r="F5" s="54">
         <v>595</v>
       </c>
       <c r="G5" s="74">
         <f>SUM(D5:F5)</f>
-        <v>2935</v>
+        <v>3092</v>
       </c>
       <c r="H5" s="67">
         <v>10000</v>
       </c>
       <c r="I5" s="68">
         <f>G5-H5</f>
-        <v>-7065</v>
+        <v>-6908</v>
       </c>
       <c r="K5" s="103" t="s">
         <v>1</v>
@@ -14679,11 +14976,11 @@
       </c>
       <c r="D6" s="76">
         <f>D5*40</f>
-        <v>27400</v>
+        <v>29800</v>
       </c>
       <c r="E6" s="76">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>66200</v>
+        <v>70080</v>
       </c>
       <c r="F6" s="76">
         <f t="shared" si="1"/>
@@ -14691,7 +14988,7 @@
       </c>
       <c r="G6" s="77">
         <f>SUM(D6:F6)</f>
-        <v>117400</v>
+        <v>123680</v>
       </c>
       <c r="H6" s="69">
         <f>H5*40</f>
@@ -14699,7 +14996,7 @@
       </c>
       <c r="I6" s="70">
         <f>G6-H6</f>
-        <v>-282600</v>
+        <v>-276320</v>
       </c>
       <c r="K6" s="103" t="s">
         <v>2</v>
@@ -14848,11 +15145,11 @@
       </c>
       <c r="D9" s="78">
         <f>D8-D5</f>
-        <v>-685</v>
+        <v>-745</v>
       </c>
       <c r="E9" s="78">
         <f>E8-E5</f>
-        <v>-1655</v>
+        <v>-1752</v>
       </c>
       <c r="K9" s="103" t="s">
         <v>5</v>
@@ -14950,14 +15247,14 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="164" t="s">
+      <c r="C11" s="172" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="164"/>
-      <c r="F11" s="164" t="s">
+      <c r="D11" s="172"/>
+      <c r="F11" s="172" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="164"/>
+      <c r="G11" s="172"/>
       <c r="K11" s="103" t="s">
         <v>7</v>
       </c>
@@ -15009,7 +15306,7 @@
       </c>
       <c r="G12" s="63">
         <f>D12+G5</f>
-        <v>7135</v>
+        <v>7292</v>
       </c>
       <c r="K12" s="103" t="s">
         <v>11</v>
@@ -15061,12 +15358,12 @@
       </c>
       <c r="G13" s="63">
         <f>G12*40</f>
-        <v>285400</v>
-      </c>
-      <c r="S13" s="159" t="s">
+        <v>291680</v>
+      </c>
+      <c r="S13" s="167" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="159"/>
+      <c r="T13" s="167"/>
       <c r="U13" s="93">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -15173,13 +15470,13 @@
       </c>
     </row>
     <row r="20" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="160" t="s">
+      <c r="D20" s="168" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="160"/>
-      <c r="F20" s="160"/>
-      <c r="G20" s="160"/>
-      <c r="H20" s="160"/>
+      <c r="E20" s="168"/>
+      <c r="F20" s="168"/>
+      <c r="G20" s="168"/>
+      <c r="H20" s="168"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
@@ -15425,4 +15722,1781 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8112F357-0A51-40B3-AD15-4EC4C2E25B0A}">
+  <dimension ref="A3:C149"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="176" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="102" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4">
+        <f>IF(COUNTIF($B:$B,A2)=0,A2,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="176" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="102" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" ref="C5:C68" si="0">IF(COUNTIF($B:$B,A3)=0,A3,"")</f>
+        <v>Column A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="176" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="102" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="176" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="102" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="176" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="102" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="176" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="176" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="102" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="176" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="102" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="176" t="s">
+        <v>102</v>
+      </c>
+      <c r="B12" s="102" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="176" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="102" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="176" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="102" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="176" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="102" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="176" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="102" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="176" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="102" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="176" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="102" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="176" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="102" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="176" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="102" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="176" t="s">
+        <v>279</v>
+      </c>
+      <c r="B21" s="102" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="176" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="102" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="176" t="s">
+        <v>280</v>
+      </c>
+      <c r="B23" s="102" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Gourmet Food Imamia </v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="176" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" s="102" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="176" t="s">
+        <v>281</v>
+      </c>
+      <c r="B25" s="102" t="s">
+        <v>116</v>
+      </c>
+      <c r="C25" t="str">
+        <f t="shared" si="0"/>
+        <v>Jalal Sons 1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="176" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="102" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="176" t="s">
+        <v>282</v>
+      </c>
+      <c r="B27" s="102" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" t="str">
+        <f t="shared" si="0"/>
+        <v>Rainbow Cash &amp; Carry1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="176" t="s">
+        <v>283</v>
+      </c>
+      <c r="B28" s="102" t="s">
+        <v>116</v>
+      </c>
+      <c r="C28" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="176" t="s">
+        <v>284</v>
+      </c>
+      <c r="B29" s="102" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" t="str">
+        <f t="shared" si="0"/>
+        <v>Rainbow Cash &amp; Carry2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="176" t="s">
+        <v>285</v>
+      </c>
+      <c r="B30" s="102" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" t="str">
+        <f t="shared" si="0"/>
+        <v>Rainbow Cash &amp; Carry3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="176" t="s">
+        <v>286</v>
+      </c>
+      <c r="B31" s="102" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" t="str">
+        <f t="shared" si="0"/>
+        <v>Rainbow Cash &amp; Carry4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="176" t="s">
+        <v>287</v>
+      </c>
+      <c r="B32" s="102" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" t="str">
+        <f t="shared" si="0"/>
+        <v>Rainbow Cash &amp; Carry5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="176" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" s="102" t="s">
+        <v>161</v>
+      </c>
+      <c r="C33" t="str">
+        <f t="shared" si="0"/>
+        <v>Rainbow Cash &amp; Carry6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="176" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="102" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" t="str">
+        <f t="shared" si="0"/>
+        <v>Rainbow Cash &amp; Carry7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="176" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" s="102" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="176" t="s">
+        <v>130</v>
+      </c>
+      <c r="B36" s="102" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="176" t="s">
+        <v>131</v>
+      </c>
+      <c r="B37" s="102" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="176" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" s="102" t="s">
+        <v>132</v>
+      </c>
+      <c r="C38" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="176" t="s">
+        <v>133</v>
+      </c>
+      <c r="B39" s="102" t="s">
+        <v>133</v>
+      </c>
+      <c r="C39" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="176" t="s">
+        <v>159</v>
+      </c>
+      <c r="B40" s="102" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="176" t="s">
+        <v>157</v>
+      </c>
+      <c r="B41" s="102" t="s">
+        <v>157</v>
+      </c>
+      <c r="C41" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="176" t="s">
+        <v>134</v>
+      </c>
+      <c r="B42" s="102" t="s">
+        <v>134</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="176" t="s">
+        <v>141</v>
+      </c>
+      <c r="B43" s="102" t="s">
+        <v>141</v>
+      </c>
+      <c r="C43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="176" t="s">
+        <v>143</v>
+      </c>
+      <c r="B44" s="102" t="s">
+        <v>143</v>
+      </c>
+      <c r="C44" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="176" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" s="102" t="s">
+        <v>145</v>
+      </c>
+      <c r="C45" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="176" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" s="102" t="s">
+        <v>147</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="176" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47" s="102" t="s">
+        <v>148</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="176" t="s">
+        <v>149</v>
+      </c>
+      <c r="B48" s="102" t="s">
+        <v>149</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="176" t="s">
+        <v>150</v>
+      </c>
+      <c r="B49" s="102" t="s">
+        <v>150</v>
+      </c>
+      <c r="C49" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="176" t="s">
+        <v>151</v>
+      </c>
+      <c r="B50" s="102" t="s">
+        <v>151</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="176" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" s="139" t="s">
+        <v>153</v>
+      </c>
+      <c r="C51" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="176" t="s">
+        <v>155</v>
+      </c>
+      <c r="B52" s="102" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="176" t="s">
+        <v>162</v>
+      </c>
+      <c r="B53" s="102" t="s">
+        <v>162</v>
+      </c>
+      <c r="C53" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="176" t="s">
+        <v>288</v>
+      </c>
+      <c r="B54" s="98" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="176" t="s">
+        <v>165</v>
+      </c>
+      <c r="B55" s="98" t="s">
+        <v>165</v>
+      </c>
+      <c r="C55" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" s="176" t="s">
+        <v>289</v>
+      </c>
+      <c r="B56" s="98" t="s">
+        <v>167</v>
+      </c>
+      <c r="C56" t="str">
+        <f t="shared" si="0"/>
+        <v>Gourmet Food Shadbagh 4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="176" t="s">
+        <v>169</v>
+      </c>
+      <c r="B57" s="98" t="s">
+        <v>169</v>
+      </c>
+      <c r="C57" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="176" t="s">
+        <v>171</v>
+      </c>
+      <c r="B58" s="98" t="s">
+        <v>171</v>
+      </c>
+      <c r="C58" t="str">
+        <f t="shared" si="0"/>
+        <v>Gourmet food Kot abdul malik 7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="176" t="s">
+        <v>173</v>
+      </c>
+      <c r="B59" s="98" t="s">
+        <v>173</v>
+      </c>
+      <c r="C59" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" s="176" t="s">
+        <v>111</v>
+      </c>
+      <c r="B60" s="98" t="s">
+        <v>111</v>
+      </c>
+      <c r="C60" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" s="176" t="s">
+        <v>176</v>
+      </c>
+      <c r="B61" s="98" t="s">
+        <v>176</v>
+      </c>
+      <c r="C61" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" s="176" t="s">
+        <v>290</v>
+      </c>
+      <c r="B62" s="98" t="s">
+        <v>96</v>
+      </c>
+      <c r="C62" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="176" t="s">
+        <v>178</v>
+      </c>
+      <c r="B63" s="98" t="s">
+        <v>178</v>
+      </c>
+      <c r="C63" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" s="176" t="s">
+        <v>181</v>
+      </c>
+      <c r="B64" s="98" t="s">
+        <v>181</v>
+      </c>
+      <c r="C64" t="str">
+        <f t="shared" si="0"/>
+        <v>Gourmet Food Rehmanpura1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" s="176" t="s">
+        <v>183</v>
+      </c>
+      <c r="B65" s="98" t="s">
+        <v>183</v>
+      </c>
+      <c r="C65" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" s="176" t="s">
+        <v>185</v>
+      </c>
+      <c r="B66" s="98" t="s">
+        <v>185</v>
+      </c>
+      <c r="C66" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" s="176" t="s">
+        <v>187</v>
+      </c>
+      <c r="B67" s="98" t="s">
+        <v>187</v>
+      </c>
+      <c r="C67" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" s="176" t="s">
+        <v>189</v>
+      </c>
+      <c r="B68" s="98" t="s">
+        <v>189</v>
+      </c>
+      <c r="C68" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" s="176" t="s">
+        <v>191</v>
+      </c>
+      <c r="B69" s="144" t="s">
+        <v>191</v>
+      </c>
+      <c r="C69" t="str">
+        <f t="shared" ref="C69:C132" si="1">IF(COUNTIF($B:$B,A67)=0,A67,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" s="176" t="s">
+        <v>193</v>
+      </c>
+      <c r="B70" s="98" t="s">
+        <v>193</v>
+      </c>
+      <c r="C70" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" s="176" t="s">
+        <v>195</v>
+      </c>
+      <c r="B71" s="98" t="s">
+        <v>195</v>
+      </c>
+      <c r="C71" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" s="176" t="s">
+        <v>291</v>
+      </c>
+      <c r="B72" s="98" t="s">
+        <v>113</v>
+      </c>
+      <c r="C72" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" s="176" t="s">
+        <v>197</v>
+      </c>
+      <c r="B73" s="98" t="s">
+        <v>197</v>
+      </c>
+      <c r="C73" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" s="176" t="s">
+        <v>199</v>
+      </c>
+      <c r="B74" s="98" t="s">
+        <v>199</v>
+      </c>
+      <c r="C74" t="str">
+        <f t="shared" si="1"/>
+        <v>Jalal Sons 7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" s="176" t="s">
+        <v>201</v>
+      </c>
+      <c r="B75" s="98" t="s">
+        <v>201</v>
+      </c>
+      <c r="C75" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" s="177" t="s">
+        <v>292</v>
+      </c>
+      <c r="B76" s="98" t="s">
+        <v>23</v>
+      </c>
+      <c r="C76" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" s="177" t="s">
+        <v>293</v>
+      </c>
+      <c r="B77" s="98" t="s">
+        <v>129</v>
+      </c>
+      <c r="C77" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" s="177" t="s">
+        <v>203</v>
+      </c>
+      <c r="B78" s="98" t="s">
+        <v>203</v>
+      </c>
+      <c r="C78" t="str">
+        <f t="shared" si="1"/>
+        <v>Clinix 9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" s="177" t="s">
+        <v>204</v>
+      </c>
+      <c r="B79" s="98" t="s">
+        <v>204</v>
+      </c>
+      <c r="C79" t="str">
+        <f t="shared" si="1"/>
+        <v>Gourmet Food Islam Pura9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" s="177" t="s">
+        <v>205</v>
+      </c>
+      <c r="B80" s="98" t="s">
+        <v>205</v>
+      </c>
+      <c r="C80" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" s="177" t="s">
+        <v>206</v>
+      </c>
+      <c r="B81" s="98" t="s">
+        <v>206</v>
+      </c>
+      <c r="C81" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" s="177" t="s">
+        <v>207</v>
+      </c>
+      <c r="B82" s="98" t="s">
+        <v>207</v>
+      </c>
+      <c r="C82" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" s="177" t="s">
+        <v>208</v>
+      </c>
+      <c r="B83" s="98" t="s">
+        <v>208</v>
+      </c>
+      <c r="C83" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" s="177" t="s">
+        <v>209</v>
+      </c>
+      <c r="B84" s="98" t="s">
+        <v>209</v>
+      </c>
+      <c r="C84" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" s="177" t="s">
+        <v>210</v>
+      </c>
+      <c r="B85" s="98" t="s">
+        <v>210</v>
+      </c>
+      <c r="C85" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" s="177" t="s">
+        <v>211</v>
+      </c>
+      <c r="B86" s="144" t="s">
+        <v>211</v>
+      </c>
+      <c r="C86" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" s="177" t="s">
+        <v>294</v>
+      </c>
+      <c r="B87" s="98" t="s">
+        <v>213</v>
+      </c>
+      <c r="C87" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" s="177" t="s">
+        <v>295</v>
+      </c>
+      <c r="B88" s="98" t="s">
+        <v>215</v>
+      </c>
+      <c r="C88" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" s="177" t="s">
+        <v>296</v>
+      </c>
+      <c r="B89" s="98" t="s">
+        <v>127</v>
+      </c>
+      <c r="C89" t="str">
+        <f t="shared" si="1"/>
+        <v>Al Rehmat Store9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" s="177" t="s">
+        <v>220</v>
+      </c>
+      <c r="B90" s="98" t="s">
+        <v>215</v>
+      </c>
+      <c r="C90" t="str">
+        <f t="shared" si="1"/>
+        <v>Euro Store78</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" s="177" t="s">
+        <v>222</v>
+      </c>
+      <c r="B91" s="98" t="s">
+        <v>218</v>
+      </c>
+      <c r="C91" t="str">
+        <f t="shared" si="1"/>
+        <v>TN Traders 12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" s="177" t="s">
+        <v>224</v>
+      </c>
+      <c r="B92" s="98" t="s">
+        <v>219</v>
+      </c>
+      <c r="C92" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" s="177" t="s">
+        <v>226</v>
+      </c>
+      <c r="B93" s="144" t="s">
+        <v>211</v>
+      </c>
+      <c r="C93" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" s="177" t="s">
+        <v>227</v>
+      </c>
+      <c r="B94" s="98" t="s">
+        <v>220</v>
+      </c>
+      <c r="C94" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" s="177" t="s">
+        <v>228</v>
+      </c>
+      <c r="B95" s="98" t="s">
+        <v>222</v>
+      </c>
+      <c r="C95" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" s="177" t="s">
+        <v>230</v>
+      </c>
+      <c r="B96" s="98" t="s">
+        <v>224</v>
+      </c>
+      <c r="C96" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" s="177" t="s">
+        <v>297</v>
+      </c>
+      <c r="B97" s="98" t="s">
+        <v>226</v>
+      </c>
+      <c r="C97" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" s="177" t="s">
+        <v>298</v>
+      </c>
+      <c r="B98" s="98" t="s">
+        <v>227</v>
+      </c>
+      <c r="C98" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" s="177" t="s">
+        <v>232</v>
+      </c>
+      <c r="B99" s="98" t="s">
+        <v>228</v>
+      </c>
+      <c r="C99" t="str">
+        <f t="shared" si="1"/>
+        <v>Nabeel Traders  SD 1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" s="177" t="s">
+        <v>233</v>
+      </c>
+      <c r="B100" s="98" t="s">
+        <v>230</v>
+      </c>
+      <c r="C100" t="str">
+        <f t="shared" si="1"/>
+        <v>Clinix 5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" s="177" t="s">
+        <v>235</v>
+      </c>
+      <c r="B101" s="144" t="s">
+        <v>211</v>
+      </c>
+      <c r="C101" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102" s="177" t="s">
+        <v>237</v>
+      </c>
+      <c r="B102" s="98" t="s">
+        <v>23</v>
+      </c>
+      <c r="C102" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103" s="177" t="s">
+        <v>238</v>
+      </c>
+      <c r="B103" s="98" t="s">
+        <v>232</v>
+      </c>
+      <c r="C103" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104" s="177" t="s">
+        <v>299</v>
+      </c>
+      <c r="B104" s="98" t="s">
+        <v>233</v>
+      </c>
+      <c r="C104" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" s="177" t="s">
+        <v>300</v>
+      </c>
+      <c r="B105" s="98" t="s">
+        <v>235</v>
+      </c>
+      <c r="C105" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106" s="177" t="s">
+        <v>301</v>
+      </c>
+      <c r="B106" s="98" t="s">
+        <v>237</v>
+      </c>
+      <c r="C106" t="str">
+        <f t="shared" si="1"/>
+        <v>Rafaqat Stons 8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107" s="177" t="s">
+        <v>302</v>
+      </c>
+      <c r="B107" s="98" t="s">
+        <v>238</v>
+      </c>
+      <c r="C107" t="str">
+        <f t="shared" si="1"/>
+        <v>Rafaqat Stons 7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108" s="177" t="s">
+        <v>244</v>
+      </c>
+      <c r="B108" s="98" t="s">
+        <v>240</v>
+      </c>
+      <c r="C108" t="str">
+        <f t="shared" si="1"/>
+        <v>SB Traders (Risen) Shadbagh 9</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" s="177" t="s">
+        <v>246</v>
+      </c>
+      <c r="B109" s="98" t="s">
+        <v>240</v>
+      </c>
+      <c r="C109" t="str">
+        <f t="shared" si="1"/>
+        <v>Euro Hyper Market5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110" s="177" t="s">
+        <v>248</v>
+      </c>
+      <c r="B110" s="98" t="s">
+        <v>189</v>
+      </c>
+      <c r="C110" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111" s="177" t="s">
+        <v>249</v>
+      </c>
+      <c r="B111" s="98" t="s">
+        <v>232</v>
+      </c>
+      <c r="C111" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112" s="177" t="s">
+        <v>303</v>
+      </c>
+      <c r="B112" s="98" t="s">
+        <v>244</v>
+      </c>
+      <c r="C112" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" s="177" t="s">
+        <v>304</v>
+      </c>
+      <c r="B113" s="98" t="s">
+        <v>246</v>
+      </c>
+      <c r="C113" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" s="177" t="s">
+        <v>305</v>
+      </c>
+      <c r="B114" s="98" t="s">
+        <v>248</v>
+      </c>
+      <c r="C114" t="str">
+        <f t="shared" si="1"/>
+        <v>Rainbow Cash &amp; Carry64</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" s="177" t="s">
+        <v>306</v>
+      </c>
+      <c r="B115" s="98" t="s">
+        <v>249</v>
+      </c>
+      <c r="C115" t="str">
+        <f t="shared" si="1"/>
+        <v>Rainbow Cash &amp; Carry14</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116" s="177" t="s">
+        <v>252</v>
+      </c>
+      <c r="B116" s="98" t="s">
+        <v>116</v>
+      </c>
+      <c r="C116" t="str">
+        <f t="shared" si="1"/>
+        <v>Rainbow Cash &amp; Carry12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" s="177" t="s">
+        <v>307</v>
+      </c>
+      <c r="B117" s="98" t="s">
+        <v>116</v>
+      </c>
+      <c r="C117" t="str">
+        <f t="shared" si="1"/>
+        <v>Umer Cash N Carry 123</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118" s="177" t="s">
+        <v>308</v>
+      </c>
+      <c r="B118" s="98" t="s">
+        <v>116</v>
+      </c>
+      <c r="C118" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119" s="177" t="s">
+        <v>309</v>
+      </c>
+      <c r="B119" s="98" t="s">
+        <v>251</v>
+      </c>
+      <c r="C119" t="str">
+        <f t="shared" si="1"/>
+        <v>Rainbow Cash &amp; Carry45</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A120" s="177" t="s">
+        <v>254</v>
+      </c>
+      <c r="B120" s="98" t="s">
+        <v>252</v>
+      </c>
+      <c r="C120" t="str">
+        <f t="shared" si="1"/>
+        <v>Rainbow Cash &amp; Carry65</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121" s="177" t="s">
+        <v>256</v>
+      </c>
+      <c r="B121" s="98" t="s">
+        <v>116</v>
+      </c>
+      <c r="C121" t="str">
+        <f t="shared" si="1"/>
+        <v>Rainbow Cash &amp; Carry124</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A122" s="177" t="s">
+        <v>257</v>
+      </c>
+      <c r="B122" s="98" t="s">
+        <v>116</v>
+      </c>
+      <c r="C122" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123" s="177" t="s">
+        <v>310</v>
+      </c>
+      <c r="B123" s="98" t="s">
+        <v>116</v>
+      </c>
+      <c r="C123" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A124" s="177" t="s">
+        <v>311</v>
+      </c>
+      <c r="B124" s="98" t="s">
+        <v>254</v>
+      </c>
+      <c r="C124" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A125" s="177" t="s">
+        <v>312</v>
+      </c>
+      <c r="B125" s="98" t="s">
+        <v>256</v>
+      </c>
+      <c r="C125" t="str">
+        <f t="shared" si="1"/>
+        <v>Rainbow Cash &amp; Carry42</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A126" s="177" t="s">
+        <v>313</v>
+      </c>
+      <c r="B126" s="98" t="s">
+        <v>257</v>
+      </c>
+      <c r="C126" t="str">
+        <f t="shared" si="1"/>
+        <v>Rainbow Cash &amp; Carry1247</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127" s="177" t="s">
+        <v>259</v>
+      </c>
+      <c r="B127" s="98" t="s">
+        <v>116</v>
+      </c>
+      <c r="C127" t="str">
+        <f t="shared" si="1"/>
+        <v>Rainbow Cash &amp; Carry21</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A128" s="177" t="s">
+        <v>261</v>
+      </c>
+      <c r="B128" s="98" t="s">
+        <v>116</v>
+      </c>
+      <c r="C128" t="str">
+        <f t="shared" si="1"/>
+        <v>Zubaida Traders 7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129" s="177" t="s">
+        <v>314</v>
+      </c>
+      <c r="B129" s="98" t="s">
+        <v>116</v>
+      </c>
+      <c r="C129" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130" s="177" t="s">
+        <v>315</v>
+      </c>
+      <c r="B130" s="98" t="s">
+        <v>224</v>
+      </c>
+      <c r="C130" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A131" s="177" t="s">
+        <v>263</v>
+      </c>
+      <c r="B131" s="136" t="s">
+        <v>259</v>
+      </c>
+      <c r="C131" t="str">
+        <f t="shared" si="1"/>
+        <v>Jalal Sons 78</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132" s="177" t="s">
+        <v>264</v>
+      </c>
+      <c r="B132" s="98" t="s">
+        <v>261</v>
+      </c>
+      <c r="C132" t="str">
+        <f t="shared" si="1"/>
+        <v>CB Traders Risen Manawan 14</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133" s="177" t="s">
+        <v>316</v>
+      </c>
+      <c r="B133" s="98" t="s">
+        <v>113</v>
+      </c>
+      <c r="C133" t="str">
+        <f t="shared" ref="C133:C149" si="2">IF(COUNTIF($B:$B,A131)=0,A131,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A134" s="177" t="s">
+        <v>265</v>
+      </c>
+      <c r="B134" s="98" t="s">
+        <v>151</v>
+      </c>
+      <c r="C134" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135" s="177" t="s">
+        <v>317</v>
+      </c>
+      <c r="B135" s="98" t="s">
+        <v>263</v>
+      </c>
+      <c r="C135" t="str">
+        <f t="shared" si="2"/>
+        <v>Jalal Sons 45</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A136" s="177" t="s">
+        <v>318</v>
+      </c>
+      <c r="B136" s="98" t="s">
+        <v>264</v>
+      </c>
+      <c r="C136" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A137" s="177" t="s">
+        <v>266</v>
+      </c>
+      <c r="B137" s="98" t="s">
+        <v>113</v>
+      </c>
+      <c r="C137" t="str">
+        <f t="shared" si="2"/>
+        <v>Clinix 45</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A138" s="177" t="s">
+        <v>240</v>
+      </c>
+      <c r="B138" s="98" t="s">
+        <v>265</v>
+      </c>
+      <c r="C138" t="str">
+        <f t="shared" si="2"/>
+        <v>Jalal Sons 12</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139" s="177" t="s">
+        <v>268</v>
+      </c>
+      <c r="B139" s="98" t="s">
+        <v>23</v>
+      </c>
+      <c r="C139" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140" s="177" t="s">
+        <v>319</v>
+      </c>
+      <c r="B140" s="98" t="s">
+        <v>113</v>
+      </c>
+      <c r="C140" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A141" s="177" t="s">
+        <v>320</v>
+      </c>
+      <c r="B141" s="98" t="s">
+        <v>266</v>
+      </c>
+      <c r="C141" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142" s="177" t="s">
+        <v>273</v>
+      </c>
+      <c r="B142" s="98" t="s">
+        <v>240</v>
+      </c>
+      <c r="C142" t="str">
+        <f t="shared" si="2"/>
+        <v>Jalal Sons 1212</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143" s="177" t="s">
+        <v>321</v>
+      </c>
+      <c r="B143" s="98" t="s">
+        <v>268</v>
+      </c>
+      <c r="C143" t="str">
+        <f t="shared" si="2"/>
+        <v>Al Buraq Dipartmental Store4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144" s="177" t="s">
+        <v>271</v>
+      </c>
+      <c r="B144" s="98" t="s">
+        <v>113</v>
+      </c>
+      <c r="C144" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145" s="177" t="s">
+        <v>322</v>
+      </c>
+      <c r="B145" s="115" t="s">
+        <v>271</v>
+      </c>
+      <c r="C145" t="str">
+        <f t="shared" si="2"/>
+        <v>Jalal Sons 3</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B146" s="115" t="s">
+        <v>273</v>
+      </c>
+      <c r="C146" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B147" s="115" t="s">
+        <v>113</v>
+      </c>
+      <c r="C147" t="str">
+        <f t="shared" si="2"/>
+        <v>Raheem Store8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B148" s="115" t="s">
+        <v>271</v>
+      </c>
+      <c r="C148">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B149" s="115" t="s">
+        <v>238</v>
+      </c>
+      <c r="C149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A4:A83">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22:A138">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A139:A145">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47:B61">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4ED052-F196-4A22-A781-C30A8FB54BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C2FFA28-82EE-41B6-B13B-42EC2C980193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="329">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -995,6 +995,21 @@
   </si>
   <si>
     <t xml:space="preserve">Compare </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euro Wapda Town </t>
+  </si>
+  <si>
+    <t>Family Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valencia Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euro G1 </t>
+  </si>
+  <si>
+    <t>Chicken Promo 4 in 1</t>
   </si>
 </sst>
 </file>
@@ -2167,9 +2182,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2185,6 +2197,48 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2217,39 +2271,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2276,12 +2297,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2917,13 +2932,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="157">
+      <c r="B1" s="148">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
-      </c>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
+        <v>46325</v>
+      </c>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -2945,10 +2960,10 @@
       <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="168" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="158" t="s">
+      <c r="B2" s="149" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2978,13 +2993,13 @@
       <c r="K2" s="14">
         <v>120</v>
       </c>
-      <c r="L2" s="147"/>
-      <c r="M2" s="148"/>
-      <c r="N2" s="149"/>
-      <c r="O2" s="150" t="s">
+      <c r="L2" s="160"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="162"/>
+      <c r="O2" s="163" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="151"/>
+      <c r="P2" s="164"/>
       <c r="Q2" s="17">
         <v>0.05</v>
       </c>
@@ -3003,8 +3018,8 @@
       <c r="X2" s="19"/>
     </row>
     <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="155"/>
-      <c r="B3" s="159"/>
+      <c r="A3" s="168"/>
+      <c r="B3" s="150"/>
       <c r="C3" s="22" t="s">
         <v>15</v>
       </c>
@@ -3032,29 +3047,29 @@
       <c r="K3" s="26">
         <v>72.64</v>
       </c>
-      <c r="L3" s="152" t="s">
+      <c r="L3" s="165" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="153"/>
-      <c r="N3" s="154"/>
+      <c r="M3" s="166"/>
+      <c r="N3" s="167"/>
       <c r="O3" s="48"/>
       <c r="P3" s="49"/>
-      <c r="Q3" s="161" t="s">
+      <c r="Q3" s="152" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="162"/>
-      <c r="S3" s="162"/>
-      <c r="T3" s="163"/>
-      <c r="U3" s="164" t="s">
+      <c r="R3" s="153"/>
+      <c r="S3" s="153"/>
+      <c r="T3" s="154"/>
+      <c r="U3" s="155" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="165"/>
-      <c r="W3" s="165"/>
-      <c r="X3" s="166"/>
+      <c r="V3" s="156"/>
+      <c r="W3" s="156"/>
+      <c r="X3" s="157"/>
     </row>
     <row r="4" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="155"/>
-      <c r="B4" s="160"/>
+      <c r="A4" s="168"/>
+      <c r="B4" s="151"/>
       <c r="C4" s="101" t="s">
         <v>90</v>
       </c>
@@ -6631,35 +6646,35 @@
       <c r="A52" s="53">
         <v>46301</v>
       </c>
-      <c r="B52" s="143">
+      <c r="B52" s="142">
         <v>46</v>
       </c>
-      <c r="C52" s="139" t="s">
+      <c r="C52" s="138" t="s">
         <v>153</v>
       </c>
-      <c r="D52" s="139" t="s">
+      <c r="D52" s="138" t="s">
         <v>154</v>
       </c>
-      <c r="E52" s="140"/>
-      <c r="F52" s="140"/>
-      <c r="G52" s="140"/>
-      <c r="H52" s="141">
+      <c r="E52" s="139"/>
+      <c r="F52" s="139"/>
+      <c r="G52" s="139"/>
+      <c r="H52" s="140">
         <v>600</v>
       </c>
-      <c r="I52" s="140">
+      <c r="I52" s="139">
         <v>800</v>
       </c>
-      <c r="J52" s="140">
+      <c r="J52" s="139">
         <v>1200</v>
       </c>
-      <c r="K52" s="140">
+      <c r="K52" s="139">
         <v>1000</v>
       </c>
-      <c r="L52" s="145">
+      <c r="L52" s="144">
         <f t="shared" si="64"/>
         <v>90</v>
       </c>
-      <c r="M52" s="142">
+      <c r="M52" s="141">
         <v>16</v>
       </c>
       <c r="N52" s="40"/>
@@ -7801,35 +7816,35 @@
       <c r="A70" s="53">
         <v>46302</v>
       </c>
-      <c r="B70" s="143">
+      <c r="B70" s="142">
         <v>64</v>
       </c>
-      <c r="C70" s="144" t="s">
+      <c r="C70" s="143" t="s">
         <v>191</v>
       </c>
-      <c r="D70" s="144" t="s">
+      <c r="D70" s="143" t="s">
         <v>192</v>
       </c>
-      <c r="E70" s="140"/>
-      <c r="F70" s="140">
+      <c r="E70" s="139"/>
+      <c r="F70" s="139">
         <v>400</v>
       </c>
-      <c r="G70" s="140">
+      <c r="G70" s="139">
         <v>400</v>
       </c>
-      <c r="H70" s="141">
-        <v>0</v>
-      </c>
-      <c r="I70" s="140">
+      <c r="H70" s="140">
+        <v>0</v>
+      </c>
+      <c r="I70" s="139">
         <v>600</v>
       </c>
-      <c r="J70" s="140">
+      <c r="J70" s="139">
         <v>800</v>
       </c>
-      <c r="K70" s="140">
+      <c r="K70" s="139">
         <v>800</v>
       </c>
-      <c r="L70" s="145">
+      <c r="L70" s="144">
         <f t="shared" si="64"/>
         <v>75</v>
       </c>
@@ -9096,29 +9111,29 @@
       <c r="A87" s="53">
         <v>46304</v>
       </c>
-      <c r="B87" s="143">
+      <c r="B87" s="142">
         <v>81</v>
       </c>
-      <c r="C87" s="144" t="s">
+      <c r="C87" s="143" t="s">
         <v>211</v>
       </c>
-      <c r="D87" s="144" t="s">
+      <c r="D87" s="143" t="s">
         <v>212</v>
       </c>
-      <c r="E87" s="140"/>
-      <c r="F87" s="140"/>
-      <c r="G87" s="140"/>
-      <c r="H87" s="141"/>
-      <c r="I87" s="140">
+      <c r="E87" s="139"/>
+      <c r="F87" s="139"/>
+      <c r="G87" s="139"/>
+      <c r="H87" s="140"/>
+      <c r="I87" s="139">
         <v>3000</v>
       </c>
-      <c r="J87" s="140">
+      <c r="J87" s="139">
         <v>2000</v>
       </c>
-      <c r="K87" s="140">
+      <c r="K87" s="139">
         <v>3000</v>
       </c>
-      <c r="L87" s="145">
+      <c r="L87" s="144">
         <f t="shared" si="84"/>
         <v>200</v>
       </c>
@@ -9641,25 +9656,25 @@
       <c r="A94" s="53">
         <v>46306</v>
       </c>
-      <c r="B94" s="143">
+      <c r="B94" s="142">
         <v>88</v>
       </c>
-      <c r="C94" s="144" t="s">
+      <c r="C94" s="143" t="s">
         <v>211</v>
       </c>
-      <c r="D94" s="144" t="s">
+      <c r="D94" s="143" t="s">
         <v>212</v>
       </c>
-      <c r="E94" s="140"/>
-      <c r="F94" s="140">
+      <c r="E94" s="139"/>
+      <c r="F94" s="139">
         <v>600</v>
       </c>
-      <c r="G94" s="140"/>
-      <c r="H94" s="141"/>
-      <c r="I94" s="140"/>
-      <c r="J94" s="140"/>
-      <c r="K94" s="140"/>
-      <c r="L94" s="145">
+      <c r="G94" s="139"/>
+      <c r="H94" s="140"/>
+      <c r="I94" s="139"/>
+      <c r="J94" s="139"/>
+      <c r="K94" s="139"/>
+      <c r="L94" s="144">
         <f t="shared" si="84"/>
         <v>15</v>
       </c>
@@ -10255,35 +10270,35 @@
       <c r="A102" s="53">
         <v>46310</v>
       </c>
-      <c r="B102" s="143">
+      <c r="B102" s="142">
         <v>96</v>
       </c>
-      <c r="C102" s="144" t="s">
+      <c r="C102" s="143" t="s">
         <v>211</v>
       </c>
-      <c r="D102" s="144" t="s">
+      <c r="D102" s="143" t="s">
         <v>212</v>
       </c>
-      <c r="E102" s="140"/>
-      <c r="F102" s="140">
+      <c r="E102" s="139"/>
+      <c r="F102" s="139">
         <v>200</v>
       </c>
-      <c r="G102" s="140">
+      <c r="G102" s="139">
         <v>200</v>
       </c>
-      <c r="H102" s="141">
+      <c r="H102" s="140">
         <v>200</v>
       </c>
-      <c r="I102" s="140">
+      <c r="I102" s="139">
         <v>2800</v>
       </c>
-      <c r="J102" s="140">
+      <c r="J102" s="139">
         <v>2400</v>
       </c>
-      <c r="K102" s="140">
+      <c r="K102" s="139">
         <v>2800</v>
       </c>
-      <c r="L102" s="145">
+      <c r="L102" s="144">
         <f t="shared" si="84"/>
         <v>215</v>
       </c>
@@ -13360,28 +13375,28 @@
       <c r="X145" s="114"/>
     </row>
     <row r="146" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A146" s="105">
+      <c r="A146" s="53">
         <v>46322</v>
       </c>
-      <c r="B146" s="106">
+      <c r="B146" s="39">
         <v>140</v>
       </c>
-      <c r="C146" s="115" t="s">
+      <c r="C146" s="98" t="s">
         <v>271</v>
       </c>
-      <c r="D146" s="115" t="s">
+      <c r="D146" s="98" t="s">
         <v>272</v>
       </c>
-      <c r="E146" s="113"/>
-      <c r="F146" s="113"/>
-      <c r="G146" s="113"/>
-      <c r="H146" s="114"/>
-      <c r="I146" s="113"/>
-      <c r="J146" s="113"/>
-      <c r="K146" s="113">
+      <c r="E146" s="51"/>
+      <c r="F146" s="51"/>
+      <c r="G146" s="51"/>
+      <c r="H146" s="97"/>
+      <c r="I146" s="51"/>
+      <c r="J146" s="51"/>
+      <c r="K146" s="51">
         <v>800</v>
       </c>
-      <c r="L146" s="114">
+      <c r="L146" s="97">
         <f t="shared" si="102"/>
         <v>20</v>
       </c>
@@ -13401,32 +13416,32 @@
       <c r="X146" s="114"/>
     </row>
     <row r="147" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A147" s="105">
+      <c r="A147" s="53">
         <v>46322</v>
       </c>
-      <c r="B147" s="106">
+      <c r="B147" s="39">
         <v>141</v>
       </c>
-      <c r="C147" s="115" t="s">
+      <c r="C147" s="98" t="s">
         <v>273</v>
       </c>
-      <c r="D147" s="115" t="s">
+      <c r="D147" s="98" t="s">
         <v>274</v>
       </c>
-      <c r="E147" s="113"/>
-      <c r="F147" s="113"/>
-      <c r="G147" s="113">
+      <c r="E147" s="51"/>
+      <c r="F147" s="51"/>
+      <c r="G147" s="51">
         <v>39</v>
       </c>
-      <c r="H147" s="114"/>
-      <c r="I147" s="113"/>
-      <c r="J147" s="113">
-        <v>40</v>
-      </c>
-      <c r="K147" s="113">
+      <c r="H147" s="97"/>
+      <c r="I147" s="51"/>
+      <c r="J147" s="51">
+        <v>40</v>
+      </c>
+      <c r="K147" s="51">
         <v>120</v>
       </c>
-      <c r="L147" s="114">
+      <c r="L147" s="97">
         <f t="shared" si="102"/>
         <v>4.9749999999999996</v>
       </c>
@@ -13446,38 +13461,38 @@
       <c r="X147" s="114"/>
     </row>
     <row r="148" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A148" s="105">
+      <c r="A148" s="53">
         <v>46322</v>
       </c>
-      <c r="B148" s="106">
+      <c r="B148" s="39">
         <v>142</v>
       </c>
-      <c r="C148" s="115" t="s">
+      <c r="C148" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="D148" s="115" t="s">
+      <c r="D148" s="98" t="s">
         <v>275</v>
       </c>
-      <c r="E148" s="113"/>
-      <c r="F148" s="113">
+      <c r="E148" s="51"/>
+      <c r="F148" s="51">
         <v>120</v>
       </c>
-      <c r="G148" s="113">
+      <c r="G148" s="51">
         <v>120</v>
       </c>
-      <c r="H148" s="114">
+      <c r="H148" s="97">
         <v>120</v>
       </c>
-      <c r="I148" s="113">
+      <c r="I148" s="51">
         <v>120</v>
       </c>
-      <c r="J148" s="113">
+      <c r="J148" s="51">
         <v>120</v>
       </c>
-      <c r="K148" s="113">
+      <c r="K148" s="51">
         <v>120</v>
       </c>
-      <c r="L148" s="114">
+      <c r="L148" s="97">
         <f t="shared" si="102"/>
         <v>18</v>
       </c>
@@ -13497,32 +13512,32 @@
       <c r="X148" s="114"/>
     </row>
     <row r="149" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A149" s="105">
+      <c r="A149" s="53">
         <v>46322</v>
       </c>
-      <c r="B149" s="106">
+      <c r="B149" s="39">
         <v>143</v>
       </c>
-      <c r="C149" s="115" t="s">
+      <c r="C149" s="98" t="s">
         <v>271</v>
       </c>
-      <c r="D149" s="115" t="s">
+      <c r="D149" s="98" t="s">
         <v>276</v>
       </c>
-      <c r="E149" s="113"/>
-      <c r="F149" s="113"/>
-      <c r="G149" s="113"/>
-      <c r="H149" s="114"/>
-      <c r="I149" s="113">
+      <c r="E149" s="51"/>
+      <c r="F149" s="51"/>
+      <c r="G149" s="51"/>
+      <c r="H149" s="97"/>
+      <c r="I149" s="51">
         <v>80</v>
       </c>
-      <c r="J149" s="113">
+      <c r="J149" s="51">
         <v>80</v>
       </c>
-      <c r="K149" s="113">
+      <c r="K149" s="51">
         <v>80</v>
       </c>
-      <c r="L149" s="114">
+      <c r="L149" s="97">
         <f t="shared" si="102"/>
         <v>6</v>
       </c>
@@ -13542,36 +13557,36 @@
       <c r="X149" s="114"/>
     </row>
     <row r="150" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A150" s="105">
+      <c r="A150" s="53">
         <v>46322</v>
       </c>
-      <c r="B150" s="138">
+      <c r="B150" s="117">
         <v>144</v>
       </c>
-      <c r="C150" s="115" t="s">
+      <c r="C150" s="98" t="s">
         <v>238</v>
       </c>
-      <c r="D150" s="115" t="s">
+      <c r="D150" s="98" t="s">
         <v>239</v>
       </c>
-      <c r="E150" s="113"/>
-      <c r="F150" s="113">
+      <c r="E150" s="51"/>
+      <c r="F150" s="51">
         <v>200</v>
       </c>
-      <c r="G150" s="113">
+      <c r="G150" s="51">
         <v>200</v>
       </c>
-      <c r="H150" s="114"/>
-      <c r="I150" s="113">
+      <c r="H150" s="97"/>
+      <c r="I150" s="51">
         <v>240</v>
       </c>
-      <c r="J150" s="113">
+      <c r="J150" s="51">
         <v>360</v>
       </c>
-      <c r="K150" s="113">
+      <c r="K150" s="51">
         <v>400</v>
       </c>
-      <c r="L150" s="114">
+      <c r="L150" s="97">
         <f t="shared" si="102"/>
         <v>35</v>
       </c>
@@ -13591,26 +13606,39 @@
       <c r="X150" s="114"/>
     </row>
     <row r="151" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A151" s="128"/>
+      <c r="A151" s="53">
+        <v>46323</v>
+      </c>
       <c r="B151" s="39">
         <v>145</v>
       </c>
-      <c r="C151" s="98"/>
-      <c r="D151" s="98"/>
+      <c r="C151" s="98" t="s">
+        <v>324</v>
+      </c>
+      <c r="D151" s="98" t="s">
+        <v>122</v>
+      </c>
       <c r="E151" s="51"/>
-      <c r="F151" s="51"/>
-      <c r="G151" s="51"/>
+      <c r="F151" s="51">
+        <v>120</v>
+      </c>
+      <c r="G151" s="51">
+        <v>120</v>
+      </c>
       <c r="H151" s="97"/>
       <c r="I151" s="51"/>
-      <c r="J151" s="51"/>
-      <c r="K151" s="51"/>
+      <c r="J151" s="51">
+        <v>120</v>
+      </c>
+      <c r="K151" s="51">
+        <v>120</v>
+      </c>
       <c r="L151" s="97">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M151" s="109">
-        <f t="shared" ref="M151:O173" si="103">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N151" s="97"/>
       <c r="O151" s="129"/>
@@ -13625,26 +13653,39 @@
       <c r="X151" s="114"/>
     </row>
     <row r="152" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A152" s="128"/>
+      <c r="A152" s="53">
+        <v>46323</v>
+      </c>
       <c r="B152" s="39">
         <v>146</v>
       </c>
-      <c r="C152" s="98"/>
-      <c r="D152" s="98"/>
+      <c r="C152" s="98" t="s">
+        <v>325</v>
+      </c>
+      <c r="D152" s="98" t="s">
+        <v>326</v>
+      </c>
       <c r="E152" s="51"/>
-      <c r="F152" s="51"/>
-      <c r="G152" s="51"/>
+      <c r="F152" s="51">
+        <v>40</v>
+      </c>
+      <c r="G152" s="51">
+        <v>40</v>
+      </c>
       <c r="H152" s="97"/>
       <c r="I152" s="51"/>
-      <c r="J152" s="51"/>
-      <c r="K152" s="51"/>
+      <c r="J152" s="51">
+        <v>40</v>
+      </c>
+      <c r="K152" s="51">
+        <v>160</v>
+      </c>
       <c r="L152" s="97">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M152" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N152" s="97"/>
       <c r="O152" s="129"/>
@@ -13659,26 +13700,39 @@
       <c r="X152" s="114"/>
     </row>
     <row r="153" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A153" s="128"/>
+      <c r="A153" s="53">
+        <v>46323</v>
+      </c>
       <c r="B153" s="39">
         <v>147</v>
       </c>
-      <c r="C153" s="98"/>
-      <c r="D153" s="98"/>
+      <c r="C153" s="98" t="s">
+        <v>238</v>
+      </c>
+      <c r="D153" s="98" t="s">
+        <v>122</v>
+      </c>
       <c r="E153" s="51"/>
       <c r="F153" s="51"/>
-      <c r="G153" s="51"/>
+      <c r="G153" s="51">
+        <v>115</v>
+      </c>
       <c r="H153" s="97"/>
-      <c r="I153" s="51"/>
-      <c r="J153" s="51"/>
-      <c r="K153" s="51"/>
+      <c r="I153" s="51">
+        <v>61</v>
+      </c>
+      <c r="J153" s="51">
+        <v>119</v>
+      </c>
+      <c r="K153" s="51">
+        <v>200</v>
+      </c>
       <c r="L153" s="97">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>12.375</v>
       </c>
       <c r="M153" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N153" s="97"/>
       <c r="O153" s="129"/>
@@ -13693,26 +13747,35 @@
       <c r="X153" s="114"/>
     </row>
     <row r="154" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A154" s="128"/>
-      <c r="B154" s="39">
+      <c r="A154" s="105">
+        <v>46324</v>
+      </c>
+      <c r="B154" s="106">
         <v>148</v>
       </c>
-      <c r="C154" s="98"/>
-      <c r="D154" s="98"/>
-      <c r="E154" s="51"/>
-      <c r="F154" s="51"/>
-      <c r="G154" s="51"/>
-      <c r="H154" s="97"/>
-      <c r="I154" s="51"/>
-      <c r="J154" s="51"/>
-      <c r="K154" s="51"/>
+      <c r="C154" s="115" t="s">
+        <v>195</v>
+      </c>
+      <c r="D154" s="115" t="s">
+        <v>115</v>
+      </c>
+      <c r="E154" s="113"/>
+      <c r="F154" s="113"/>
+      <c r="G154" s="113"/>
+      <c r="H154" s="114"/>
+      <c r="I154" s="113"/>
+      <c r="J154" s="113">
+        <v>120</v>
+      </c>
+      <c r="K154" s="113">
+        <v>120</v>
+      </c>
       <c r="L154" s="97">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M154" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N154" s="97"/>
       <c r="O154" s="129"/>
@@ -13727,26 +13790,35 @@
       <c r="X154" s="114"/>
     </row>
     <row r="155" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A155" s="128"/>
-      <c r="B155" s="39">
+      <c r="A155" s="105">
+        <v>46324</v>
+      </c>
+      <c r="B155" s="106">
         <v>149</v>
       </c>
-      <c r="C155" s="98"/>
-      <c r="D155" s="98"/>
-      <c r="E155" s="51"/>
-      <c r="F155" s="51"/>
-      <c r="G155" s="51"/>
-      <c r="H155" s="97"/>
-      <c r="I155" s="51"/>
-      <c r="J155" s="51"/>
-      <c r="K155" s="51"/>
+      <c r="C155" s="115" t="s">
+        <v>327</v>
+      </c>
+      <c r="D155" s="115" t="s">
+        <v>115</v>
+      </c>
+      <c r="E155" s="113"/>
+      <c r="F155" s="113"/>
+      <c r="G155" s="113"/>
+      <c r="H155" s="114"/>
+      <c r="I155" s="113"/>
+      <c r="J155" s="113">
+        <v>200</v>
+      </c>
+      <c r="K155" s="113">
+        <v>1000</v>
+      </c>
       <c r="L155" s="97">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M155" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N155" s="97"/>
       <c r="O155" s="129"/>
@@ -13761,25 +13833,41 @@
       <c r="X155" s="114"/>
     </row>
     <row r="156" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A156" s="128"/>
-      <c r="B156" s="117">
+      <c r="A156" s="105">
+        <v>46324</v>
+      </c>
+      <c r="B156" s="147">
         <v>150</v>
       </c>
-      <c r="C156" s="98"/>
-      <c r="D156" s="98"/>
-      <c r="E156" s="51"/>
-      <c r="F156" s="51"/>
-      <c r="G156" s="51"/>
-      <c r="H156" s="97"/>
-      <c r="I156" s="51"/>
-      <c r="J156" s="51"/>
-      <c r="K156" s="51"/>
+      <c r="C156" s="115" t="s">
+        <v>211</v>
+      </c>
+      <c r="D156" s="115" t="s">
+        <v>212</v>
+      </c>
+      <c r="E156" s="113">
+        <v>4000</v>
+      </c>
+      <c r="F156" s="113">
+        <v>1000</v>
+      </c>
+      <c r="G156" s="113">
+        <v>1000</v>
+      </c>
+      <c r="H156" s="114"/>
+      <c r="I156" s="113"/>
+      <c r="J156" s="113">
+        <v>3200</v>
+      </c>
+      <c r="K156" s="113">
+        <v>4800</v>
+      </c>
       <c r="L156" s="97">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="M156" s="109">
-        <f t="shared" si="103"/>
+        <f t="shared" ref="M156:O173" si="103">SUMPRODUCT($E$4:$K$4,$E$6:$K$6)</f>
         <v>0</v>
       </c>
       <c r="N156" s="97"/>
@@ -14385,10 +14473,10 @@
     </row>
     <row r="173" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A173" s="128"/>
-      <c r="B173" s="156" t="s">
+      <c r="B173" s="158" t="s">
         <v>11</v>
       </c>
-      <c r="C173" s="156"/>
+      <c r="C173" s="158"/>
       <c r="D173" s="106"/>
       <c r="E173" s="111">
         <f t="shared" ref="E173:K173" si="104">SUM(E6:E63)</f>
@@ -14641,10 +14729,10 @@
     </row>
     <row r="177" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A177" s="2"/>
-      <c r="B177" s="156" t="s">
+      <c r="B177" s="158" t="s">
         <v>68</v>
       </c>
-      <c r="C177" s="156"/>
+      <c r="C177" s="158"/>
       <c r="D177" s="106"/>
       <c r="E177" s="113">
         <f>SUM(E175:E176)</f>
@@ -14729,10 +14817,10 @@
     </row>
     <row r="178" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A178" s="2"/>
-      <c r="B178" s="146" t="s">
+      <c r="B178" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="C178" s="146"/>
+      <c r="C178" s="159"/>
       <c r="D178" s="132"/>
       <c r="E178" s="133">
         <f>SUM(E173,E177)</f>
@@ -14768,7 +14856,7 @@
       </c>
       <c r="M178" s="134">
         <f>SUM(M5:M177)</f>
-        <v>2191</v>
+        <v>2257</v>
       </c>
       <c r="N178" s="39">
         <f t="shared" ref="N178:X178" si="112">SUM(N5:N177)</f>
@@ -14817,17 +14905,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B173:C173"/>
     <mergeCell ref="B178:C178"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B177:C177"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="B173:C173"/>
   </mergeCells>
   <conditionalFormatting sqref="C48:D62">
     <cfRule type="duplicateValues" dxfId="4" priority="1"/>
@@ -14864,25 +14952,25 @@
   <sheetData>
     <row r="2" spans="3:26" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="169" t="s">
+      <c r="C3" s="171" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="170"/>
-      <c r="E3" s="170"/>
-      <c r="F3" s="170"/>
-      <c r="G3" s="171"/>
-      <c r="H3" s="173" t="s">
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="173"/>
+      <c r="H3" s="175" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="174"/>
-      <c r="K3" s="175" t="s">
+      <c r="I3" s="176"/>
+      <c r="K3" s="177" t="s">
         <v>64</v>
       </c>
-      <c r="L3" s="175"/>
-      <c r="M3" s="175"/>
-      <c r="N3" s="175"/>
-      <c r="O3" s="175"/>
-      <c r="P3" s="175"/>
+      <c r="L3" s="177"/>
+      <c r="M3" s="177"/>
+      <c r="N3" s="177"/>
+      <c r="O3" s="177"/>
+      <c r="P3" s="177"/>
     </row>
     <row r="4" spans="3:26" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="71"/>
@@ -14928,24 +15016,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="60">
-        <v>745</v>
+        <v>812</v>
       </c>
       <c r="E5" s="54">
-        <v>1752</v>
+        <v>1819</v>
       </c>
       <c r="F5" s="54">
-        <v>595</v>
+        <v>945</v>
       </c>
       <c r="G5" s="74">
         <f>SUM(D5:F5)</f>
-        <v>3092</v>
+        <v>3576</v>
       </c>
       <c r="H5" s="67">
         <v>10000</v>
       </c>
       <c r="I5" s="68">
         <f>G5-H5</f>
-        <v>-6908</v>
+        <v>-6424</v>
       </c>
       <c r="K5" s="103" t="s">
         <v>1</v>
@@ -14954,11 +15042,11 @@
         <v>70</v>
       </c>
       <c r="M5" s="5">
-        <v>2716</v>
+        <v>10440</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>67.900000000000006</v>
+        <v>261</v>
       </c>
       <c r="O5" s="56"/>
       <c r="P5" s="104"/>
@@ -14967,7 +15055,7 @@
       </c>
       <c r="R5" s="112">
         <f>N5-Q5</f>
-        <v>-199.30999999999997</v>
+        <v>-6.2099999999999795</v>
       </c>
     </row>
     <row r="6" spans="3:26" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
@@ -14976,19 +15064,19 @@
       </c>
       <c r="D6" s="76">
         <f>D5*40</f>
-        <v>29800</v>
+        <v>32480</v>
       </c>
       <c r="E6" s="76">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>70080</v>
+        <v>72760</v>
       </c>
       <c r="F6" s="76">
         <f t="shared" si="1"/>
-        <v>23800</v>
+        <v>37800</v>
       </c>
       <c r="G6" s="77">
         <f>SUM(D6:F6)</f>
-        <v>123680</v>
+        <v>143040</v>
       </c>
       <c r="H6" s="69">
         <f>H5*40</f>
@@ -14996,7 +15084,7 @@
       </c>
       <c r="I6" s="70">
         <f>G6-H6</f>
-        <v>-276320</v>
+        <v>-256960</v>
       </c>
       <c r="K6" s="103" t="s">
         <v>2</v>
@@ -15005,11 +15093,11 @@
         <v>70</v>
       </c>
       <c r="M6" s="5">
-        <v>3739</v>
+        <v>1176</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>93.474999999999994</v>
+        <v>29.4</v>
       </c>
       <c r="O6" s="56"/>
       <c r="P6" s="104"/>
@@ -15018,7 +15106,7 @@
       </c>
       <c r="R6" s="112">
         <f t="shared" ref="R6:R10" si="2">N6-Q6</f>
-        <v>-80.795000000000016</v>
+        <v>-144.87</v>
       </c>
       <c r="S6" s="90"/>
       <c r="T6" s="90"/>
@@ -15098,11 +15186,11 @@
         <v>120</v>
       </c>
       <c r="M8" s="5">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>10.975</v>
+        <v>0</v>
       </c>
       <c r="O8" s="56">
         <v>50</v>
@@ -15113,7 +15201,7 @@
       </c>
       <c r="R8" s="112">
         <f t="shared" si="2"/>
-        <v>-73.325000000000003</v>
+        <v>-84.3</v>
       </c>
       <c r="S8" s="54">
         <v>120</v>
@@ -15145,11 +15233,11 @@
       </c>
       <c r="D9" s="78">
         <f>D8-D5</f>
-        <v>-745</v>
+        <v>-812</v>
       </c>
       <c r="E9" s="78">
         <f>E8-E5</f>
-        <v>-1752</v>
+        <v>-1819</v>
       </c>
       <c r="K9" s="103" t="s">
         <v>5</v>
@@ -15158,11 +15246,11 @@
         <v>120</v>
       </c>
       <c r="M9" s="5">
-        <v>14843</v>
+        <v>9854</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>371.07499999999999</v>
+        <v>246.35</v>
       </c>
       <c r="O9" s="56">
         <v>23</v>
@@ -15173,7 +15261,7 @@
       </c>
       <c r="R9" s="112">
         <f t="shared" si="2"/>
-        <v>261.90499999999997</v>
+        <v>137.18</v>
       </c>
       <c r="S9" s="54">
         <v>120</v>
@@ -15209,11 +15297,11 @@
         <v>120</v>
       </c>
       <c r="M10" s="5">
-        <v>14351</v>
+        <v>15454</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>358.77499999999998</v>
+        <v>386.35</v>
       </c>
       <c r="O10" s="56"/>
       <c r="P10" s="104"/>
@@ -15222,7 +15310,7 @@
       </c>
       <c r="R10" s="112">
         <f t="shared" si="2"/>
-        <v>160.42499999999998</v>
+        <v>188.00000000000003</v>
       </c>
       <c r="S10" s="54">
         <v>120</v>
@@ -15247,26 +15335,26 @@
       </c>
     </row>
     <row r="11" spans="3:26" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="172" t="s">
+      <c r="C11" s="174" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="172"/>
-      <c r="F11" s="172" t="s">
+      <c r="D11" s="174"/>
+      <c r="F11" s="174" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="172"/>
+      <c r="G11" s="174"/>
       <c r="K11" s="103" t="s">
-        <v>7</v>
+        <v>328</v>
       </c>
       <c r="L11" s="7">
         <v>60</v>
       </c>
       <c r="M11" s="5">
-        <v>22</v>
+        <v>6462</v>
       </c>
       <c r="N11" s="6">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
+        <f>M11/12</f>
+        <v>538.5</v>
       </c>
       <c r="O11" s="56">
         <v>125</v>
@@ -15306,7 +15394,7 @@
       </c>
       <c r="G12" s="63">
         <f>D12+G5</f>
-        <v>7292</v>
+        <v>7776</v>
       </c>
       <c r="K12" s="103" t="s">
         <v>11</v>
@@ -15314,11 +15402,11 @@
       <c r="L12" s="56"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>36110</v>
+        <v>43386</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>902.74999999999989</v>
+        <v>1461.6</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
@@ -15358,12 +15446,12 @@
       </c>
       <c r="G13" s="63">
         <f>G12*40</f>
-        <v>291680</v>
-      </c>
-      <c r="S13" s="167" t="s">
+        <v>311040</v>
+      </c>
+      <c r="S13" s="169" t="s">
         <v>83</v>
       </c>
-      <c r="T13" s="167"/>
+      <c r="T13" s="169"/>
       <c r="U13" s="93">
         <f>SUM(U8:U12)</f>
         <v>100</v>
@@ -15417,7 +15505,7 @@
       <c r="N17" s="87"/>
       <c r="O17" s="88">
         <f>N17-M5</f>
-        <v>-2716</v>
+        <v>-10440</v>
       </c>
       <c r="R17">
         <v>51.94</v>
@@ -15437,7 +15525,7 @@
       <c r="N18" s="5"/>
       <c r="O18" s="88">
         <f>N18-M6</f>
-        <v>-3739</v>
+        <v>-1176</v>
       </c>
       <c r="R18">
         <v>163.25499999999997</v>
@@ -15470,13 +15558,13 @@
       </c>
     </row>
     <row r="20" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="D20" s="168" t="s">
+      <c r="D20" s="170" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="168"/>
-      <c r="F20" s="168"/>
-      <c r="G20" s="168"/>
-      <c r="H20" s="168"/>
+      <c r="E20" s="170"/>
+      <c r="F20" s="170"/>
+      <c r="G20" s="170"/>
+      <c r="H20" s="170"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
@@ -15487,7 +15575,7 @@
       <c r="N20" s="5"/>
       <c r="O20" s="88">
         <f t="shared" si="5"/>
-        <v>-439</v>
+        <v>0</v>
       </c>
       <c r="R20">
         <v>156.75</v>
@@ -15522,7 +15610,7 @@
       <c r="N21" s="5"/>
       <c r="O21" s="88">
         <f t="shared" si="5"/>
-        <v>-14843</v>
+        <v>-9854</v>
       </c>
       <c r="R21">
         <v>158.505</v>
@@ -15554,7 +15642,7 @@
       <c r="N22" s="5"/>
       <c r="O22" s="88">
         <f t="shared" si="5"/>
-        <v>-14351</v>
+        <v>-15454</v>
       </c>
       <c r="R22">
         <v>69.150000000000006</v>
@@ -15586,7 +15674,7 @@
       <c r="N23" s="5"/>
       <c r="O23" s="88">
         <f t="shared" si="5"/>
-        <v>-22</v>
+        <v>-6462</v>
       </c>
     </row>
     <row r="24" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -15616,7 +15704,7 @@
       </c>
       <c r="O24" s="83">
         <f>SUM(O17:O23)</f>
-        <v>-36110</v>
+        <v>-43386</v>
       </c>
     </row>
     <row r="25" spans="4:19" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -15646,7 +15734,7 @@
       </c>
       <c r="O25" s="83">
         <f>O24/40</f>
-        <v>-902.75</v>
+        <v>-1084.6500000000001</v>
       </c>
     </row>
     <row r="26" spans="4:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -15745,7 +15833,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="176" t="s">
+      <c r="A4" s="145" t="s">
         <v>94</v>
       </c>
       <c r="B4" s="102" t="s">
@@ -15757,7 +15845,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="176" t="s">
+      <c r="A5" s="145" t="s">
         <v>95</v>
       </c>
       <c r="B5" s="102" t="s">
@@ -15769,7 +15857,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="176" t="s">
+      <c r="A6" s="145" t="s">
         <v>96</v>
       </c>
       <c r="B6" s="102" t="s">
@@ -15781,7 +15869,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="176" t="s">
+      <c r="A7" s="145" t="s">
         <v>97</v>
       </c>
       <c r="B7" s="102" t="s">
@@ -15793,7 +15881,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="176" t="s">
+      <c r="A8" s="145" t="s">
         <v>98</v>
       </c>
       <c r="B8" s="102" t="s">
@@ -15805,7 +15893,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="176" t="s">
+      <c r="A9" s="145" t="s">
         <v>99</v>
       </c>
       <c r="B9" s="102" t="s">
@@ -15817,7 +15905,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="176" t="s">
+      <c r="A10" s="145" t="s">
         <v>100</v>
       </c>
       <c r="B10" s="102" t="s">
@@ -15829,7 +15917,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="176" t="s">
+      <c r="A11" s="145" t="s">
         <v>101</v>
       </c>
       <c r="B11" s="102" t="s">
@@ -15841,7 +15929,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="176" t="s">
+      <c r="A12" s="145" t="s">
         <v>102</v>
       </c>
       <c r="B12" s="102" t="s">
@@ -15853,7 +15941,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="176" t="s">
+      <c r="A13" s="145" t="s">
         <v>103</v>
       </c>
       <c r="B13" s="102" t="s">
@@ -15865,7 +15953,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="176" t="s">
+      <c r="A14" s="145" t="s">
         <v>104</v>
       </c>
       <c r="B14" s="102" t="s">
@@ -15877,7 +15965,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="176" t="s">
+      <c r="A15" s="145" t="s">
         <v>105</v>
       </c>
       <c r="B15" s="102" t="s">
@@ -15889,7 +15977,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="176" t="s">
+      <c r="A16" s="145" t="s">
         <v>106</v>
       </c>
       <c r="B16" s="102" t="s">
@@ -15901,7 +15989,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="176" t="s">
+      <c r="A17" s="145" t="s">
         <v>107</v>
       </c>
       <c r="B17" s="102" t="s">
@@ -15913,7 +16001,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="176" t="s">
+      <c r="A18" s="145" t="s">
         <v>108</v>
       </c>
       <c r="B18" s="102" t="s">
@@ -15925,7 +16013,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="176" t="s">
+      <c r="A19" s="145" t="s">
         <v>109</v>
       </c>
       <c r="B19" s="102" t="s">
@@ -15937,7 +16025,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="176" t="s">
+      <c r="A20" s="145" t="s">
         <v>110</v>
       </c>
       <c r="B20" s="102" t="s">
@@ -15949,7 +16037,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="176" t="s">
+      <c r="A21" s="145" t="s">
         <v>279</v>
       </c>
       <c r="B21" s="102" t="s">
@@ -15961,7 +16049,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="176" t="s">
+      <c r="A22" s="145" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="102" t="s">
@@ -15973,7 +16061,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="176" t="s">
+      <c r="A23" s="145" t="s">
         <v>280</v>
       </c>
       <c r="B23" s="102" t="s">
@@ -15985,7 +16073,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="176" t="s">
+      <c r="A24" s="145" t="s">
         <v>113</v>
       </c>
       <c r="B24" s="102" t="s">
@@ -15997,7 +16085,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="176" t="s">
+      <c r="A25" s="145" t="s">
         <v>281</v>
       </c>
       <c r="B25" s="102" t="s">
@@ -16009,7 +16097,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="176" t="s">
+      <c r="A26" s="145" t="s">
         <v>117</v>
       </c>
       <c r="B26" s="102" t="s">
@@ -16021,7 +16109,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="176" t="s">
+      <c r="A27" s="145" t="s">
         <v>282</v>
       </c>
       <c r="B27" s="102" t="s">
@@ -16033,7 +16121,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="176" t="s">
+      <c r="A28" s="145" t="s">
         <v>283</v>
       </c>
       <c r="B28" s="102" t="s">
@@ -16045,7 +16133,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="176" t="s">
+      <c r="A29" s="145" t="s">
         <v>284</v>
       </c>
       <c r="B29" s="102" t="s">
@@ -16057,7 +16145,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="176" t="s">
+      <c r="A30" s="145" t="s">
         <v>285</v>
       </c>
       <c r="B30" s="102" t="s">
@@ -16069,7 +16157,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="176" t="s">
+      <c r="A31" s="145" t="s">
         <v>286</v>
       </c>
       <c r="B31" s="102" t="s">
@@ -16081,7 +16169,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="176" t="s">
+      <c r="A32" s="145" t="s">
         <v>287</v>
       </c>
       <c r="B32" s="102" t="s">
@@ -16093,7 +16181,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="176" t="s">
+      <c r="A33" s="145" t="s">
         <v>161</v>
       </c>
       <c r="B33" s="102" t="s">
@@ -16105,7 +16193,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="176" t="s">
+      <c r="A34" s="145" t="s">
         <v>127</v>
       </c>
       <c r="B34" s="102" t="s">
@@ -16117,7 +16205,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="176" t="s">
+      <c r="A35" s="145" t="s">
         <v>129</v>
       </c>
       <c r="B35" s="102" t="s">
@@ -16129,7 +16217,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="176" t="s">
+      <c r="A36" s="145" t="s">
         <v>130</v>
       </c>
       <c r="B36" s="102" t="s">
@@ -16141,7 +16229,7 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="176" t="s">
+      <c r="A37" s="145" t="s">
         <v>131</v>
       </c>
       <c r="B37" s="102" t="s">
@@ -16153,7 +16241,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="176" t="s">
+      <c r="A38" s="145" t="s">
         <v>132</v>
       </c>
       <c r="B38" s="102" t="s">
@@ -16165,7 +16253,7 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="176" t="s">
+      <c r="A39" s="145" t="s">
         <v>133</v>
       </c>
       <c r="B39" s="102" t="s">
@@ -16177,7 +16265,7 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="176" t="s">
+      <c r="A40" s="145" t="s">
         <v>159</v>
       </c>
       <c r="B40" s="102" t="s">
@@ -16189,7 +16277,7 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="176" t="s">
+      <c r="A41" s="145" t="s">
         <v>157</v>
       </c>
       <c r="B41" s="102" t="s">
@@ -16201,7 +16289,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="176" t="s">
+      <c r="A42" s="145" t="s">
         <v>134</v>
       </c>
       <c r="B42" s="102" t="s">
@@ -16213,7 +16301,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="176" t="s">
+      <c r="A43" s="145" t="s">
         <v>141</v>
       </c>
       <c r="B43" s="102" t="s">
@@ -16225,7 +16313,7 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="176" t="s">
+      <c r="A44" s="145" t="s">
         <v>143</v>
       </c>
       <c r="B44" s="102" t="s">
@@ -16237,7 +16325,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="176" t="s">
+      <c r="A45" s="145" t="s">
         <v>145</v>
       </c>
       <c r="B45" s="102" t="s">
@@ -16249,7 +16337,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="176" t="s">
+      <c r="A46" s="145" t="s">
         <v>147</v>
       </c>
       <c r="B46" s="102" t="s">
@@ -16261,7 +16349,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="176" t="s">
+      <c r="A47" s="145" t="s">
         <v>148</v>
       </c>
       <c r="B47" s="102" t="s">
@@ -16273,7 +16361,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="176" t="s">
+      <c r="A48" s="145" t="s">
         <v>149</v>
       </c>
       <c r="B48" s="102" t="s">
@@ -16285,7 +16373,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="176" t="s">
+      <c r="A49" s="145" t="s">
         <v>150</v>
       </c>
       <c r="B49" s="102" t="s">
@@ -16297,7 +16385,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="176" t="s">
+      <c r="A50" s="145" t="s">
         <v>151</v>
       </c>
       <c r="B50" s="102" t="s">
@@ -16309,10 +16397,10 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="176" t="s">
+      <c r="A51" s="145" t="s">
         <v>153</v>
       </c>
-      <c r="B51" s="139" t="s">
+      <c r="B51" s="138" t="s">
         <v>153</v>
       </c>
       <c r="C51" t="str">
@@ -16321,7 +16409,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="176" t="s">
+      <c r="A52" s="145" t="s">
         <v>155</v>
       </c>
       <c r="B52" s="102" t="s">
@@ -16333,7 +16421,7 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="176" t="s">
+      <c r="A53" s="145" t="s">
         <v>162</v>
       </c>
       <c r="B53" s="102" t="s">
@@ -16345,7 +16433,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="176" t="s">
+      <c r="A54" s="145" t="s">
         <v>288</v>
       </c>
       <c r="B54" s="98" t="s">
@@ -16357,7 +16445,7 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="176" t="s">
+      <c r="A55" s="145" t="s">
         <v>165</v>
       </c>
       <c r="B55" s="98" t="s">
@@ -16369,7 +16457,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="176" t="s">
+      <c r="A56" s="145" t="s">
         <v>289</v>
       </c>
       <c r="B56" s="98" t="s">
@@ -16381,7 +16469,7 @@
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="176" t="s">
+      <c r="A57" s="145" t="s">
         <v>169</v>
       </c>
       <c r="B57" s="98" t="s">
@@ -16393,7 +16481,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="176" t="s">
+      <c r="A58" s="145" t="s">
         <v>171</v>
       </c>
       <c r="B58" s="98" t="s">
@@ -16405,7 +16493,7 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="176" t="s">
+      <c r="A59" s="145" t="s">
         <v>173</v>
       </c>
       <c r="B59" s="98" t="s">
@@ -16417,7 +16505,7 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="176" t="s">
+      <c r="A60" s="145" t="s">
         <v>111</v>
       </c>
       <c r="B60" s="98" t="s">
@@ -16429,7 +16517,7 @@
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="176" t="s">
+      <c r="A61" s="145" t="s">
         <v>176</v>
       </c>
       <c r="B61" s="98" t="s">
@@ -16441,7 +16529,7 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="176" t="s">
+      <c r="A62" s="145" t="s">
         <v>290</v>
       </c>
       <c r="B62" s="98" t="s">
@@ -16453,7 +16541,7 @@
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="176" t="s">
+      <c r="A63" s="145" t="s">
         <v>178</v>
       </c>
       <c r="B63" s="98" t="s">
@@ -16465,7 +16553,7 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="176" t="s">
+      <c r="A64" s="145" t="s">
         <v>181</v>
       </c>
       <c r="B64" s="98" t="s">
@@ -16477,7 +16565,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65" s="176" t="s">
+      <c r="A65" s="145" t="s">
         <v>183</v>
       </c>
       <c r="B65" s="98" t="s">
@@ -16489,7 +16577,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" s="176" t="s">
+      <c r="A66" s="145" t="s">
         <v>185</v>
       </c>
       <c r="B66" s="98" t="s">
@@ -16501,7 +16589,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" s="176" t="s">
+      <c r="A67" s="145" t="s">
         <v>187</v>
       </c>
       <c r="B67" s="98" t="s">
@@ -16513,7 +16601,7 @@
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" s="176" t="s">
+      <c r="A68" s="145" t="s">
         <v>189</v>
       </c>
       <c r="B68" s="98" t="s">
@@ -16525,10 +16613,10 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" s="176" t="s">
+      <c r="A69" s="145" t="s">
         <v>191</v>
       </c>
-      <c r="B69" s="144" t="s">
+      <c r="B69" s="143" t="s">
         <v>191</v>
       </c>
       <c r="C69" t="str">
@@ -16537,7 +16625,7 @@
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" s="176" t="s">
+      <c r="A70" s="145" t="s">
         <v>193</v>
       </c>
       <c r="B70" s="98" t="s">
@@ -16549,7 +16637,7 @@
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71" s="176" t="s">
+      <c r="A71" s="145" t="s">
         <v>195</v>
       </c>
       <c r="B71" s="98" t="s">
@@ -16561,7 +16649,7 @@
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72" s="176" t="s">
+      <c r="A72" s="145" t="s">
         <v>291</v>
       </c>
       <c r="B72" s="98" t="s">
@@ -16573,7 +16661,7 @@
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A73" s="176" t="s">
+      <c r="A73" s="145" t="s">
         <v>197</v>
       </c>
       <c r="B73" s="98" t="s">
@@ -16585,7 +16673,7 @@
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74" s="176" t="s">
+      <c r="A74" s="145" t="s">
         <v>199</v>
       </c>
       <c r="B74" s="98" t="s">
@@ -16597,7 +16685,7 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75" s="176" t="s">
+      <c r="A75" s="145" t="s">
         <v>201</v>
       </c>
       <c r="B75" s="98" t="s">
@@ -16609,7 +16697,7 @@
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76" s="177" t="s">
+      <c r="A76" s="146" t="s">
         <v>292</v>
       </c>
       <c r="B76" s="98" t="s">
@@ -16621,7 +16709,7 @@
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" s="177" t="s">
+      <c r="A77" s="146" t="s">
         <v>293</v>
       </c>
       <c r="B77" s="98" t="s">
@@ -16633,7 +16721,7 @@
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" s="177" t="s">
+      <c r="A78" s="146" t="s">
         <v>203</v>
       </c>
       <c r="B78" s="98" t="s">
@@ -16645,7 +16733,7 @@
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79" s="177" t="s">
+      <c r="A79" s="146" t="s">
         <v>204</v>
       </c>
       <c r="B79" s="98" t="s">
@@ -16657,7 +16745,7 @@
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80" s="177" t="s">
+      <c r="A80" s="146" t="s">
         <v>205</v>
       </c>
       <c r="B80" s="98" t="s">
@@ -16669,7 +16757,7 @@
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A81" s="177" t="s">
+      <c r="A81" s="146" t="s">
         <v>206</v>
       </c>
       <c r="B81" s="98" t="s">
@@ -16681,7 +16769,7 @@
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A82" s="177" t="s">
+      <c r="A82" s="146" t="s">
         <v>207</v>
       </c>
       <c r="B82" s="98" t="s">
@@ -16693,7 +16781,7 @@
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A83" s="177" t="s">
+      <c r="A83" s="146" t="s">
         <v>208</v>
       </c>
       <c r="B83" s="98" t="s">
@@ -16705,7 +16793,7 @@
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A84" s="177" t="s">
+      <c r="A84" s="146" t="s">
         <v>209</v>
       </c>
       <c r="B84" s="98" t="s">
@@ -16717,7 +16805,7 @@
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A85" s="177" t="s">
+      <c r="A85" s="146" t="s">
         <v>210</v>
       </c>
       <c r="B85" s="98" t="s">
@@ -16729,10 +16817,10 @@
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A86" s="177" t="s">
+      <c r="A86" s="146" t="s">
         <v>211</v>
       </c>
-      <c r="B86" s="144" t="s">
+      <c r="B86" s="143" t="s">
         <v>211</v>
       </c>
       <c r="C86" t="str">
@@ -16741,7 +16829,7 @@
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A87" s="177" t="s">
+      <c r="A87" s="146" t="s">
         <v>294</v>
       </c>
       <c r="B87" s="98" t="s">
@@ -16753,7 +16841,7 @@
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A88" s="177" t="s">
+      <c r="A88" s="146" t="s">
         <v>295</v>
       </c>
       <c r="B88" s="98" t="s">
@@ -16765,7 +16853,7 @@
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A89" s="177" t="s">
+      <c r="A89" s="146" t="s">
         <v>296</v>
       </c>
       <c r="B89" s="98" t="s">
@@ -16777,7 +16865,7 @@
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A90" s="177" t="s">
+      <c r="A90" s="146" t="s">
         <v>220</v>
       </c>
       <c r="B90" s="98" t="s">
@@ -16789,7 +16877,7 @@
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A91" s="177" t="s">
+      <c r="A91" s="146" t="s">
         <v>222</v>
       </c>
       <c r="B91" s="98" t="s">
@@ -16801,7 +16889,7 @@
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A92" s="177" t="s">
+      <c r="A92" s="146" t="s">
         <v>224</v>
       </c>
       <c r="B92" s="98" t="s">
@@ -16813,10 +16901,10 @@
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A93" s="177" t="s">
+      <c r="A93" s="146" t="s">
         <v>226</v>
       </c>
-      <c r="B93" s="144" t="s">
+      <c r="B93" s="143" t="s">
         <v>211</v>
       </c>
       <c r="C93" t="str">
@@ -16825,7 +16913,7 @@
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A94" s="177" t="s">
+      <c r="A94" s="146" t="s">
         <v>227</v>
       </c>
       <c r="B94" s="98" t="s">
@@ -16837,7 +16925,7 @@
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A95" s="177" t="s">
+      <c r="A95" s="146" t="s">
         <v>228</v>
       </c>
       <c r="B95" s="98" t="s">
@@ -16849,7 +16937,7 @@
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A96" s="177" t="s">
+      <c r="A96" s="146" t="s">
         <v>230</v>
       </c>
       <c r="B96" s="98" t="s">
@@ -16861,7 +16949,7 @@
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A97" s="177" t="s">
+      <c r="A97" s="146" t="s">
         <v>297</v>
       </c>
       <c r="B97" s="98" t="s">
@@ -16873,7 +16961,7 @@
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A98" s="177" t="s">
+      <c r="A98" s="146" t="s">
         <v>298</v>
       </c>
       <c r="B98" s="98" t="s">
@@ -16885,7 +16973,7 @@
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A99" s="177" t="s">
+      <c r="A99" s="146" t="s">
         <v>232</v>
       </c>
       <c r="B99" s="98" t="s">
@@ -16897,7 +16985,7 @@
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100" s="177" t="s">
+      <c r="A100" s="146" t="s">
         <v>233</v>
       </c>
       <c r="B100" s="98" t="s">
@@ -16909,10 +16997,10 @@
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A101" s="177" t="s">
+      <c r="A101" s="146" t="s">
         <v>235</v>
       </c>
-      <c r="B101" s="144" t="s">
+      <c r="B101" s="143" t="s">
         <v>211</v>
       </c>
       <c r="C101" t="str">
@@ -16921,7 +17009,7 @@
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A102" s="177" t="s">
+      <c r="A102" s="146" t="s">
         <v>237</v>
       </c>
       <c r="B102" s="98" t="s">
@@ -16933,7 +17021,7 @@
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A103" s="177" t="s">
+      <c r="A103" s="146" t="s">
         <v>238</v>
       </c>
       <c r="B103" s="98" t="s">
@@ -16945,7 +17033,7 @@
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A104" s="177" t="s">
+      <c r="A104" s="146" t="s">
         <v>299</v>
       </c>
       <c r="B104" s="98" t="s">
@@ -16957,7 +17045,7 @@
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A105" s="177" t="s">
+      <c r="A105" s="146" t="s">
         <v>300</v>
       </c>
       <c r="B105" s="98" t="s">
@@ -16969,7 +17057,7 @@
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A106" s="177" t="s">
+      <c r="A106" s="146" t="s">
         <v>301</v>
       </c>
       <c r="B106" s="98" t="s">
@@ -16981,7 +17069,7 @@
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A107" s="177" t="s">
+      <c r="A107" s="146" t="s">
         <v>302</v>
       </c>
       <c r="B107" s="98" t="s">
@@ -16993,7 +17081,7 @@
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A108" s="177" t="s">
+      <c r="A108" s="146" t="s">
         <v>244</v>
       </c>
       <c r="B108" s="98" t="s">
@@ -17005,7 +17093,7 @@
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A109" s="177" t="s">
+      <c r="A109" s="146" t="s">
         <v>246</v>
       </c>
       <c r="B109" s="98" t="s">
@@ -17017,7 +17105,7 @@
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A110" s="177" t="s">
+      <c r="A110" s="146" t="s">
         <v>248</v>
       </c>
       <c r="B110" s="98" t="s">
@@ -17029,7 +17117,7 @@
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A111" s="177" t="s">
+      <c r="A111" s="146" t="s">
         <v>249</v>
       </c>
       <c r="B111" s="98" t="s">
@@ -17041,7 +17129,7 @@
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A112" s="177" t="s">
+      <c r="A112" s="146" t="s">
         <v>303</v>
       </c>
       <c r="B112" s="98" t="s">
@@ -17053,7 +17141,7 @@
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A113" s="177" t="s">
+      <c r="A113" s="146" t="s">
         <v>304</v>
       </c>
       <c r="B113" s="98" t="s">
@@ -17065,7 +17153,7 @@
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A114" s="177" t="s">
+      <c r="A114" s="146" t="s">
         <v>305</v>
       </c>
       <c r="B114" s="98" t="s">
@@ -17077,7 +17165,7 @@
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A115" s="177" t="s">
+      <c r="A115" s="146" t="s">
         <v>306</v>
       </c>
       <c r="B115" s="98" t="s">
@@ -17089,7 +17177,7 @@
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A116" s="177" t="s">
+      <c r="A116" s="146" t="s">
         <v>252</v>
       </c>
       <c r="B116" s="98" t="s">
@@ -17101,7 +17189,7 @@
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A117" s="177" t="s">
+      <c r="A117" s="146" t="s">
         <v>307</v>
       </c>
       <c r="B117" s="98" t="s">
@@ -17113,7 +17201,7 @@
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A118" s="177" t="s">
+      <c r="A118" s="146" t="s">
         <v>308</v>
       </c>
       <c r="B118" s="98" t="s">
@@ -17125,7 +17213,7 @@
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A119" s="177" t="s">
+      <c r="A119" s="146" t="s">
         <v>309</v>
       </c>
       <c r="B119" s="98" t="s">
@@ -17137,7 +17225,7 @@
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A120" s="177" t="s">
+      <c r="A120" s="146" t="s">
         <v>254</v>
       </c>
       <c r="B120" s="98" t="s">
@@ -17149,7 +17237,7 @@
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A121" s="177" t="s">
+      <c r="A121" s="146" t="s">
         <v>256</v>
       </c>
       <c r="B121" s="98" t="s">
@@ -17161,7 +17249,7 @@
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A122" s="177" t="s">
+      <c r="A122" s="146" t="s">
         <v>257</v>
       </c>
       <c r="B122" s="98" t="s">
@@ -17173,7 +17261,7 @@
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A123" s="177" t="s">
+      <c r="A123" s="146" t="s">
         <v>310</v>
       </c>
       <c r="B123" s="98" t="s">
@@ -17185,7 +17273,7 @@
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A124" s="177" t="s">
+      <c r="A124" s="146" t="s">
         <v>311</v>
       </c>
       <c r="B124" s="98" t="s">
@@ -17197,7 +17285,7 @@
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A125" s="177" t="s">
+      <c r="A125" s="146" t="s">
         <v>312</v>
       </c>
       <c r="B125" s="98" t="s">
@@ -17209,7 +17297,7 @@
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A126" s="177" t="s">
+      <c r="A126" s="146" t="s">
         <v>313</v>
       </c>
       <c r="B126" s="98" t="s">
@@ -17221,7 +17309,7 @@
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A127" s="177" t="s">
+      <c r="A127" s="146" t="s">
         <v>259</v>
       </c>
       <c r="B127" s="98" t="s">
@@ -17233,7 +17321,7 @@
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A128" s="177" t="s">
+      <c r="A128" s="146" t="s">
         <v>261</v>
       </c>
       <c r="B128" s="98" t="s">
@@ -17245,7 +17333,7 @@
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A129" s="177" t="s">
+      <c r="A129" s="146" t="s">
         <v>314</v>
       </c>
       <c r="B129" s="98" t="s">
@@ -17257,7 +17345,7 @@
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A130" s="177" t="s">
+      <c r="A130" s="146" t="s">
         <v>315</v>
       </c>
       <c r="B130" s="98" t="s">
@@ -17269,7 +17357,7 @@
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A131" s="177" t="s">
+      <c r="A131" s="146" t="s">
         <v>263</v>
       </c>
       <c r="B131" s="136" t="s">
@@ -17281,7 +17369,7 @@
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A132" s="177" t="s">
+      <c r="A132" s="146" t="s">
         <v>264</v>
       </c>
       <c r="B132" s="98" t="s">
@@ -17293,7 +17381,7 @@
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A133" s="177" t="s">
+      <c r="A133" s="146" t="s">
         <v>316</v>
       </c>
       <c r="B133" s="98" t="s">
@@ -17305,7 +17393,7 @@
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A134" s="177" t="s">
+      <c r="A134" s="146" t="s">
         <v>265</v>
       </c>
       <c r="B134" s="98" t="s">
@@ -17317,7 +17405,7 @@
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A135" s="177" t="s">
+      <c r="A135" s="146" t="s">
         <v>317</v>
       </c>
       <c r="B135" s="98" t="s">
@@ -17329,7 +17417,7 @@
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A136" s="177" t="s">
+      <c r="A136" s="146" t="s">
         <v>318</v>
       </c>
       <c r="B136" s="98" t="s">
@@ -17341,7 +17429,7 @@
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A137" s="177" t="s">
+      <c r="A137" s="146" t="s">
         <v>266</v>
       </c>
       <c r="B137" s="98" t="s">
@@ -17353,7 +17441,7 @@
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A138" s="177" t="s">
+      <c r="A138" s="146" t="s">
         <v>240</v>
       </c>
       <c r="B138" s="98" t="s">
@@ -17365,7 +17453,7 @@
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A139" s="177" t="s">
+      <c r="A139" s="146" t="s">
         <v>268</v>
       </c>
       <c r="B139" s="98" t="s">
@@ -17377,7 +17465,7 @@
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A140" s="177" t="s">
+      <c r="A140" s="146" t="s">
         <v>319</v>
       </c>
       <c r="B140" s="98" t="s">
@@ -17389,7 +17477,7 @@
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A141" s="177" t="s">
+      <c r="A141" s="146" t="s">
         <v>320</v>
       </c>
       <c r="B141" s="98" t="s">
@@ -17401,7 +17489,7 @@
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A142" s="177" t="s">
+      <c r="A142" s="146" t="s">
         <v>273</v>
       </c>
       <c r="B142" s="98" t="s">
@@ -17413,7 +17501,7 @@
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A143" s="177" t="s">
+      <c r="A143" s="146" t="s">
         <v>321</v>
       </c>
       <c r="B143" s="98" t="s">
@@ -17425,7 +17513,7 @@
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A144" s="177" t="s">
+      <c r="A144" s="146" t="s">
         <v>271</v>
       </c>
       <c r="B144" s="98" t="s">
@@ -17437,7 +17525,7 @@
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A145" s="177" t="s">
+      <c r="A145" s="146" t="s">
         <v>322</v>
       </c>
       <c r="B145" s="115" t="s">

--- a/OCT_2026/Reports/LMT Orders.xlsx
+++ b/OCT_2026/Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C2FFA28-82EE-41B6-B13B-42EC2C980193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7BF51C-C370-477F-AB37-99CFF9F872F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="334">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -1010,6 +1010,21 @@
   </si>
   <si>
     <t>Chicken Promo 4 in 1</t>
+  </si>
+  <si>
+    <t>1030/2026</t>
+  </si>
+  <si>
+    <t>Shadra</t>
+  </si>
+  <si>
+    <t>Eme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victoria Dipartmental </t>
+  </si>
+  <si>
+    <t>Link Road Model T</t>
   </si>
 </sst>
 </file>
@@ -2934,7 +2949,7 @@
     <row r="1" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="148">
         <f ca="1">TODAY()</f>
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="C1" s="148"/>
       <c r="D1" s="148"/>
@@ -13747,27 +13762,27 @@
       <c r="X153" s="114"/>
     </row>
     <row r="154" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A154" s="105">
+      <c r="A154" s="53">
         <v>46324</v>
       </c>
-      <c r="B154" s="106">
+      <c r="B154" s="39">
         <v>148</v>
       </c>
-      <c r="C154" s="115" t="s">
+      <c r="C154" s="98" t="s">
         <v>195</v>
       </c>
-      <c r="D154" s="115" t="s">
+      <c r="D154" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="E154" s="113"/>
-      <c r="F154" s="113"/>
-      <c r="G154" s="113"/>
-      <c r="H154" s="114"/>
-      <c r="I154" s="113"/>
-      <c r="J154" s="113">
+      <c r="E154" s="51"/>
+      <c r="F154" s="51"/>
+      <c r="G154" s="51"/>
+      <c r="H154" s="97"/>
+      <c r="I154" s="51"/>
+      <c r="J154" s="51">
         <v>120</v>
       </c>
-      <c r="K154" s="113">
+      <c r="K154" s="51">
         <v>120</v>
       </c>
       <c r="L154" s="97">
@@ -13790,27 +13805,27 @@
       <c r="X154" s="114"/>
     </row>
     <row r="155" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A155" s="105">
+      <c r="A155" s="53">
         <v>46324</v>
       </c>
-      <c r="B155" s="106">
+      <c r="B155" s="39">
         <v>149</v>
       </c>
-      <c r="C155" s="115" t="s">
+      <c r="C155" s="98" t="s">
         <v>327</v>
       </c>
-      <c r="D155" s="115" t="s">
+      <c r="D155" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="E155" s="113"/>
-      <c r="F155" s="113"/>
-      <c r="G155" s="113"/>
-      <c r="H155" s="114"/>
-      <c r="I155" s="113"/>
-      <c r="J155" s="113">
+      <c r="E155" s="51"/>
+      <c r="F155" s="51"/>
+      <c r="G155" s="51"/>
+      <c r="H155" s="97"/>
+      <c r="I155" s="51"/>
+      <c r="J155" s="51">
         <v>200</v>
       </c>
-      <c r="K155" s="113">
+      <c r="K155" s="51">
         <v>1000</v>
       </c>
       <c r="L155" s="97">
@@ -13833,33 +13848,33 @@
       <c r="X155" s="114"/>
     </row>
     <row r="156" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A156" s="105">
+      <c r="A156" s="53">
         <v>46324</v>
       </c>
-      <c r="B156" s="147">
+      <c r="B156" s="117">
         <v>150</v>
       </c>
-      <c r="C156" s="115" t="s">
+      <c r="C156" s="98" t="s">
         <v>211</v>
       </c>
-      <c r="D156" s="115" t="s">
+      <c r="D156" s="98" t="s">
         <v>212</v>
       </c>
-      <c r="E156" s="113">
+      <c r="E156" s="51">
         <v>4000</v>
       </c>
-      <c r="F156" s="113">
+      <c r="F156" s="51">
         <v>1000</v>
       </c>
-      <c r="G156" s="113">
+      <c r="G156" s="51">
         <v>1000</v>
       </c>
-      <c r="H156" s="114"/>
-      <c r="I156" s="113"/>
-      <c r="J156" s="113">
+      <c r="H156" s="97"/>
+      <c r="I156" s="51"/>
+      <c r="J156" s="51">
         <v>3200</v>
       </c>
-      <c r="K156" s="113">
+      <c r="K156" s="51">
         <v>4800</v>
       </c>
       <c r="L156" s="97">
@@ -13883,26 +13898,39 @@
       <c r="X156" s="114"/>
     </row>
     <row r="157" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A157" s="128"/>
-      <c r="B157" s="39">
+      <c r="A157" s="105" t="s">
+        <v>329</v>
+      </c>
+      <c r="B157" s="106">
         <v>151</v>
       </c>
-      <c r="C157" s="98"/>
-      <c r="D157" s="98"/>
-      <c r="E157" s="51"/>
-      <c r="F157" s="51"/>
-      <c r="G157" s="51"/>
-      <c r="H157" s="97"/>
-      <c r="I157" s="51"/>
-      <c r="J157" s="51"/>
-      <c r="K157" s="51"/>
-      <c r="L157" s="97">
+      <c r="C157" s="115" t="s">
+        <v>23</v>
+      </c>
+      <c r="D157" s="115" t="s">
+        <v>112</v>
+      </c>
+      <c r="E157" s="113"/>
+      <c r="F157" s="113">
+        <v>40</v>
+      </c>
+      <c r="G157" s="113">
+        <v>40</v>
+      </c>
+      <c r="H157" s="114"/>
+      <c r="I157" s="113"/>
+      <c r="J157" s="113">
+        <v>160</v>
+      </c>
+      <c r="K157" s="113">
+        <v>240</v>
+      </c>
+      <c r="L157" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M157" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N157" s="97"/>
       <c r="O157" s="129"/>
@@ -13917,26 +13945,37 @@
       <c r="X157" s="114"/>
     </row>
     <row r="158" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A158" s="128"/>
-      <c r="B158" s="39">
+      <c r="A158" s="105" t="s">
+        <v>329</v>
+      </c>
+      <c r="B158" s="106">
         <v>152</v>
       </c>
-      <c r="C158" s="98"/>
-      <c r="D158" s="98"/>
-      <c r="E158" s="51"/>
-      <c r="F158" s="51"/>
-      <c r="G158" s="51"/>
-      <c r="H158" s="97"/>
-      <c r="I158" s="51"/>
-      <c r="J158" s="51"/>
-      <c r="K158" s="51"/>
-      <c r="L158" s="97">
+      <c r="C158" s="115" t="s">
+        <v>116</v>
+      </c>
+      <c r="D158" s="115" t="s">
+        <v>125</v>
+      </c>
+      <c r="E158" s="113"/>
+      <c r="F158" s="113"/>
+      <c r="G158" s="113">
+        <v>120</v>
+      </c>
+      <c r="H158" s="114"/>
+      <c r="I158" s="113"/>
+      <c r="J158" s="113">
+        <v>31</v>
+      </c>
+      <c r="K158" s="113">
+        <v>40</v>
+      </c>
+      <c r="L158" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>4.7750000000000004</v>
       </c>
       <c r="M158" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N158" s="97"/>
       <c r="O158" s="129"/>
@@ -13951,26 +13990,33 @@
       <c r="X158" s="114"/>
     </row>
     <row r="159" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A159" s="128"/>
-      <c r="B159" s="39">
+      <c r="A159" s="105" t="s">
+        <v>329</v>
+      </c>
+      <c r="B159" s="106">
         <v>153</v>
       </c>
-      <c r="C159" s="98"/>
-      <c r="D159" s="98"/>
-      <c r="E159" s="51"/>
-      <c r="F159" s="51"/>
-      <c r="G159" s="51"/>
-      <c r="H159" s="97"/>
-      <c r="I159" s="51"/>
-      <c r="J159" s="51"/>
-      <c r="K159" s="51"/>
-      <c r="L159" s="97">
+      <c r="C159" s="115" t="s">
+        <v>116</v>
+      </c>
+      <c r="D159" s="115" t="s">
+        <v>258</v>
+      </c>
+      <c r="E159" s="113"/>
+      <c r="F159" s="113"/>
+      <c r="G159" s="113"/>
+      <c r="H159" s="114"/>
+      <c r="I159" s="113"/>
+      <c r="J159" s="113"/>
+      <c r="K159" s="113">
+        <v>80</v>
+      </c>
+      <c r="L159" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M159" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N159" s="97"/>
       <c r="O159" s="129"/>
@@ -13985,26 +14031,37 @@
       <c r="X159" s="114"/>
     </row>
     <row r="160" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A160" s="128"/>
-      <c r="B160" s="39">
+      <c r="A160" s="105" t="s">
+        <v>329</v>
+      </c>
+      <c r="B160" s="106">
         <v>154</v>
       </c>
-      <c r="C160" s="98"/>
-      <c r="D160" s="98"/>
-      <c r="E160" s="51"/>
-      <c r="F160" s="51"/>
-      <c r="G160" s="51"/>
-      <c r="H160" s="97"/>
-      <c r="I160" s="51"/>
-      <c r="J160" s="51"/>
-      <c r="K160" s="51"/>
-      <c r="L160" s="97">
+      <c r="C160" s="115" t="s">
+        <v>116</v>
+      </c>
+      <c r="D160" s="115" t="s">
+        <v>330</v>
+      </c>
+      <c r="E160" s="113"/>
+      <c r="F160" s="113">
+        <v>40</v>
+      </c>
+      <c r="G160" s="113"/>
+      <c r="H160" s="114"/>
+      <c r="I160" s="113"/>
+      <c r="J160" s="113">
+        <v>40</v>
+      </c>
+      <c r="K160" s="113">
+        <v>80</v>
+      </c>
+      <c r="L160" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M160" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N160" s="97"/>
       <c r="O160" s="129"/>
@@ -14019,26 +14076,37 @@
       <c r="X160" s="114"/>
     </row>
     <row r="161" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A161" s="128"/>
-      <c r="B161" s="39">
+      <c r="A161" s="105" t="s">
+        <v>329</v>
+      </c>
+      <c r="B161" s="106">
         <v>155</v>
       </c>
-      <c r="C161" s="98"/>
-      <c r="D161" s="98"/>
-      <c r="E161" s="51"/>
-      <c r="F161" s="51"/>
-      <c r="G161" s="51"/>
-      <c r="H161" s="97"/>
-      <c r="I161" s="51"/>
-      <c r="J161" s="51"/>
-      <c r="K161" s="51"/>
-      <c r="L161" s="97">
+      <c r="C161" s="115" t="s">
+        <v>116</v>
+      </c>
+      <c r="D161" s="115" t="s">
+        <v>120</v>
+      </c>
+      <c r="E161" s="113"/>
+      <c r="F161" s="113">
+        <v>80</v>
+      </c>
+      <c r="G161" s="113">
+        <v>40</v>
+      </c>
+      <c r="H161" s="114"/>
+      <c r="I161" s="113"/>
+      <c r="J161" s="113">
+        <v>80</v>
+      </c>
+      <c r="K161" s="113"/>
+      <c r="L161" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M161" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N161" s="97"/>
       <c r="O161" s="129"/>
@@ -14053,26 +14121,37 @@
       <c r="X161" s="114"/>
     </row>
     <row r="162" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A162" s="128"/>
-      <c r="B162" s="117">
+      <c r="A162" s="105" t="s">
+        <v>329</v>
+      </c>
+      <c r="B162" s="147">
         <v>156</v>
       </c>
-      <c r="C162" s="98"/>
-      <c r="D162" s="98"/>
-      <c r="E162" s="51"/>
-      <c r="F162" s="51"/>
-      <c r="G162" s="51"/>
-      <c r="H162" s="97"/>
-      <c r="I162" s="51"/>
-      <c r="J162" s="51"/>
-      <c r="K162" s="51"/>
-      <c r="L162" s="97">
+      <c r="C162" s="115" t="s">
+        <v>116</v>
+      </c>
+      <c r="D162" s="115" t="s">
+        <v>121</v>
+      </c>
+      <c r="E162" s="113"/>
+      <c r="F162" s="113">
+        <v>40</v>
+      </c>
+      <c r="G162" s="113">
+        <v>40</v>
+      </c>
+      <c r="H162" s="114"/>
+      <c r="I162" s="113"/>
+      <c r="J162" s="113"/>
+      <c r="K162" s="113">
+        <v>40</v>
+      </c>
+      <c r="L162" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M162" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N162" s="97"/>
       <c r="O162" s="129"/>
@@ -14087,26 +14166,37 @@
       <c r="X162" s="114"/>
     </row>
     <row r="163" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A163" s="128"/>
-      <c r="B163" s="39">
+      <c r="A163" s="105" t="s">
+        <v>329</v>
+      </c>
+      <c r="B163" s="106">
         <v>157</v>
       </c>
-      <c r="C163" s="98"/>
-      <c r="D163" s="98"/>
-      <c r="E163" s="51"/>
-      <c r="F163" s="51"/>
-      <c r="G163" s="51"/>
-      <c r="H163" s="97"/>
-      <c r="I163" s="51"/>
-      <c r="J163" s="51"/>
-      <c r="K163" s="51"/>
-      <c r="L163" s="97">
+      <c r="C163" s="115" t="s">
+        <v>116</v>
+      </c>
+      <c r="D163" s="115" t="s">
+        <v>331</v>
+      </c>
+      <c r="E163" s="113"/>
+      <c r="F163" s="113">
+        <v>40</v>
+      </c>
+      <c r="G163" s="113">
+        <v>40</v>
+      </c>
+      <c r="H163" s="114"/>
+      <c r="I163" s="113"/>
+      <c r="J163" s="113"/>
+      <c r="K163" s="113">
+        <v>80</v>
+      </c>
+      <c r="L163" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M163" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N163" s="97"/>
       <c r="O163" s="129"/>
@@ -14121,26 +14211,35 @@
       <c r="X163" s="114"/>
     </row>
     <row r="164" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A164" s="128"/>
-      <c r="B164" s="39">
+      <c r="A164" s="105" t="s">
+        <v>329</v>
+      </c>
+      <c r="B164" s="106">
         <v>158</v>
       </c>
-      <c r="C164" s="98"/>
-      <c r="D164" s="98"/>
-      <c r="E164" s="51"/>
-      <c r="F164" s="51"/>
-      <c r="G164" s="51"/>
-      <c r="H164" s="97"/>
-      <c r="I164" s="51"/>
-      <c r="J164" s="51"/>
-      <c r="K164" s="51"/>
-      <c r="L164" s="97">
+      <c r="C164" s="115" t="s">
+        <v>116</v>
+      </c>
+      <c r="D164" s="115" t="s">
+        <v>216</v>
+      </c>
+      <c r="E164" s="113"/>
+      <c r="F164" s="113">
+        <v>40</v>
+      </c>
+      <c r="G164" s="113"/>
+      <c r="H164" s="114"/>
+      <c r="I164" s="113"/>
+      <c r="J164" s="113"/>
+      <c r="K164" s="113">
+        <v>40</v>
+      </c>
+      <c r="L164" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M164" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N164" s="97"/>
       <c r="O164" s="129"/>
@@ -14155,26 +14254,37 @@
       <c r="X164" s="114"/>
     </row>
     <row r="165" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A165" s="128"/>
-      <c r="B165" s="39">
+      <c r="A165" s="105" t="s">
+        <v>329</v>
+      </c>
+      <c r="B165" s="106">
         <v>159</v>
       </c>
-      <c r="C165" s="98"/>
-      <c r="D165" s="98"/>
-      <c r="E165" s="51"/>
-      <c r="F165" s="51"/>
-      <c r="G165" s="51"/>
-      <c r="H165" s="97"/>
-      <c r="I165" s="51"/>
-      <c r="J165" s="51"/>
-      <c r="K165" s="51"/>
-      <c r="L165" s="97">
+      <c r="C165" s="115" t="s">
+        <v>116</v>
+      </c>
+      <c r="D165" s="115" t="s">
+        <v>123</v>
+      </c>
+      <c r="E165" s="113"/>
+      <c r="F165" s="113">
+        <v>80</v>
+      </c>
+      <c r="G165" s="113"/>
+      <c r="H165" s="114"/>
+      <c r="I165" s="113"/>
+      <c r="J165" s="113">
+        <v>160</v>
+      </c>
+      <c r="K165" s="113">
+        <v>520</v>
+      </c>
+      <c r="L165" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M165" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N165" s="97"/>
       <c r="O165" s="129"/>
@@ -14189,26 +14299,35 @@
       <c r="X165" s="114"/>
     </row>
     <row r="166" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A166" s="128"/>
-      <c r="B166" s="39">
+      <c r="A166" s="105" t="s">
+        <v>329</v>
+      </c>
+      <c r="B166" s="106">
         <v>160</v>
       </c>
-      <c r="C166" s="98"/>
-      <c r="D166" s="98"/>
-      <c r="E166" s="51"/>
-      <c r="F166" s="51"/>
-      <c r="G166" s="51"/>
-      <c r="H166" s="97"/>
-      <c r="I166" s="51"/>
-      <c r="J166" s="51"/>
-      <c r="K166" s="51"/>
-      <c r="L166" s="97">
+      <c r="C166" s="115" t="s">
+        <v>116</v>
+      </c>
+      <c r="D166" s="115" t="s">
+        <v>122</v>
+      </c>
+      <c r="E166" s="113"/>
+      <c r="F166" s="113">
+        <v>80</v>
+      </c>
+      <c r="G166" s="113"/>
+      <c r="H166" s="114"/>
+      <c r="I166" s="113"/>
+      <c r="J166" s="113"/>
+      <c r="K166" s="113">
+        <v>200</v>
+      </c>
+      <c r="L166" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M166" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N166" s="97"/>
       <c r="O166" s="129"/>
@@ -14223,26 +14342,41 @@
       <c r="X166" s="114"/>
     </row>
     <row r="167" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A167" s="128"/>
-      <c r="B167" s="39">
+      <c r="A167" s="105" t="s">
+        <v>329</v>
+      </c>
+      <c r="B167" s="106">
         <v>161</v>
       </c>
-      <c r="C167" s="98"/>
-      <c r="D167" s="98"/>
-      <c r="E167" s="51"/>
-      <c r="F167" s="51"/>
-      <c r="G167" s="51"/>
-      <c r="H167" s="97"/>
-      <c r="I167" s="51"/>
-      <c r="J167" s="51"/>
-      <c r="K167" s="51"/>
-      <c r="L167" s="97">
+      <c r="C167" s="115" t="s">
+        <v>189</v>
+      </c>
+      <c r="D167" s="115" t="s">
+        <v>164</v>
+      </c>
+      <c r="E167" s="113">
+        <v>12</v>
+      </c>
+      <c r="F167" s="113">
+        <v>54</v>
+      </c>
+      <c r="G167" s="113">
+        <v>14</v>
+      </c>
+      <c r="H167" s="114"/>
+      <c r="I167" s="113"/>
+      <c r="J167" s="113">
+        <v>120</v>
+      </c>
+      <c r="K167" s="113">
+        <v>120</v>
+      </c>
+      <c r="L167" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M167" s="109">
-        <f t="shared" si="103"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N167" s="97"/>
       <c r="O167" s="129"/>
@@ -14257,22 +14391,30 @@
       <c r="X167" s="114"/>
     </row>
     <row r="168" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A168" s="128"/>
-      <c r="B168" s="117">
+      <c r="A168" s="105" t="s">
+        <v>329</v>
+      </c>
+      <c r="B168" s="147">
         <v>162</v>
       </c>
-      <c r="C168" s="98"/>
-      <c r="D168" s="98"/>
-      <c r="E168" s="51"/>
-      <c r="F168" s="51"/>
-      <c r="G168" s="51"/>
-      <c r="H168" s="97"/>
-      <c r="I168" s="51"/>
-      <c r="J168" s="51"/>
-      <c r="K168" s="51"/>
-      <c r="L168" s="97">
+      <c r="C168" s="115" t="s">
+        <v>332</v>
+      </c>
+      <c r="D168" s="115" t="s">
+        <v>333</v>
+      </c>
+      <c r="E168" s="113">
+        <v>240</v>
+      </c>
+      <c r="F168" s="113"/>
+      <c r="G168" s="113"/>
+      <c r="H168" s="114"/>
+      <c r="I168" s="113"/>
+      <c r="J168" s="113"/>
+      <c r="K168" s="113"/>
+      <c r="L168" s="114">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M168" s="109">
         <f t="shared" si="103"/>
@@ -14299,16 +14441,14 @@
       <c r="D169" s="98"/>
       <c r="E169" s="51"/>
       <c r="F169" s="51"/>
-      <c r="G169" s="51">
-        <v>2347</v>
-      </c>
+      <c r="G169" s="51"/>
       <c r="H169" s="97"/>
       <c r="I169" s="51"/>
       <c r="J169" s="51"/>
       <c r="K169" s="51"/>
       <c r="L169" s="97">
         <f t="shared" si="102"/>
-        <v>58.674999999999997</v>
+        <v>0</v>
       </c>
       <c r="M169" s="109">
         <f t="shared" si="103"/>
@@ -14335,16 +14475,14 @@
       <c r="D170" s="98"/>
       <c r="E170" s="51"/>
       <c r="F170" s="51"/>
-      <c r="G170" s="51">
-        <v>595</v>
-      </c>
+      <c r="G170" s="51"/>
       <c r="H170" s="97"/>
       <c r="I170" s="51"/>
       <c r="J170" s="51"/>
       <c r="K170" s="51"/>
       <c r="L170" s="97">
         <f t="shared" si="102"/>
-        <v>14.875</v>
+        <v>0</v>
       </c>
       <c r="M170" s="109">
         <f t="shared" si="103"/>
@@ -14371,17 +14509,14 @@
       <c r="D171" s="98"/>
       <c r="E171" s="51"/>
       <c r="F171" s="51"/>
-      <c r="G171" s="51">
-        <f>G169-G170</f>
-        <v>1752</v>
-      </c>
+      <c r="G171" s="51"/>
       <c r="H171" s="97"/>
       <c r="I171" s="51"/>
       <c r="J171" s="51"/>
       <c r="K171" s="51"/>
       <c r="L171" s="97">
         <f t="shared" si="102"/>
-        <v>43.8</v>
+        <v>0</v>
       </c>
       <c r="M171" s="109">
         <f t="shared" si="103"/>
@@ -14856,7 +14991,7 @@
       </c>
       <c r="M178" s="134">
         <f>SUM(M5:M177)</f>
-        <v>2257</v>
+        <v>2409</v>
       </c>
       <c r="N178" s="39">
         <f t="shared" ref="N178:X178" si="112">SUM(N5:N177)</f>
@@ -15016,24 +15151,24 @@
         <v>47</v>
       </c>
       <c r="D5" s="60">
-        <v>812</v>
+        <v>850</v>
       </c>
       <c r="E5" s="54">
-        <v>1819</v>
+        <v>1890</v>
       </c>
       <c r="F5" s="54">
         <v>945</v>
       </c>
       <c r="G5" s="74">
         <f>SUM(D5:F5)</f>
-        <v>3576</v>
+        <v>3685</v>
       </c>
       <c r="H5" s="67">
         <v>10000</v>
       </c>
       <c r="I5" s="68">
         <f>G5-H5</f>
-        <v>-6424</v>
+        <v>-6315</v>
       </c>
       <c r="K5" s="103" t="s">
         <v>1</v>
@@ -15045,7 +15180,7 @@
         <v>10440</v>
       </c>
       <c r="N5" s="6">
-        <f t="shared" ref="N5:N11" si="0">M5/40</f>
+        <f t="shared" ref="N5:N10" si="0">M5/40</f>
         <v>261</v>
       </c>
       <c r="O5" s="56"/>
@@ -15064,11 +15199,11 @@
       </c>
       <c r="D6" s="76">
         <f>D5*40</f>
-        <v>32480</v>
+        <v>34000</v>
       </c>
       <c r="E6" s="76">
         <f t="shared" ref="E6:F6" si="1">E5*40</f>
-        <v>72760</v>
+        <v>75600</v>
       </c>
       <c r="F6" s="76">
         <f t="shared" si="1"/>
@@ -15076,7 +15211,7 @@
       </c>
       <c r="G6" s="77">
         <f>SUM(D6:F6)</f>
-        <v>143040</v>
+        <v>147400</v>
       </c>
       <c r="H6" s="69">
         <f>H5*40</f>
@@ -15084,7 +15219,7 @@
       </c>
       <c r="I6" s="70">
         <f>G6-H6</f>
-        <v>-256960</v>
+        <v>-252600</v>
       </c>
       <c r="K6" s="103" t="s">
         <v>2</v>
@@ -15233,11 +15368,11 @@
       </c>
       <c r="D9" s="78">
         <f>D8-D5</f>
-        <v>-812</v>
+        <v>-850</v>
       </c>
       <c r="E9" s="78">
         <f>E8-E5</f>
-        <v>-1819</v>
+        <v>-1890</v>
       </c>
       <c r="K9" s="103" t="s">
         <v>5</v>
@@ -15394,7 +15529,7 @@
       </c>
       <c r="G12" s="63">
         <f>D12+G5</f>
-        <v>7776</v>
+        <v>7885</v>
       </c>
       <c r="K12" s="103" t="s">
         <v>11</v>
@@ -15446,7 +15581,7 @@
       </c>
       <c r="G13" s="63">
         <f>G12*40</f>
-        <v>311040</v>
+        <v>315400</v>
       </c>
       <c r="S13" s="169" t="s">
         <v>83</v>
